--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7554" uniqueCount="4707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7556" uniqueCount="4709">
   <si>
     <t>Entry</t>
   </si>
@@ -1326,7 +1326,7 @@
     <t>dreifa</t>
   </si>
   <si>
-    <t>to scatter, to sprinkle (with dative); to spread something (with dative "spread what" + á + accusative "on what")</t>
+    <t>to scatter, to sprinkle (with dative); to spread something (with dative "spread what" + ann + accusative "on what")</t>
   </si>
   <si>
     <t>dreki</t>
@@ -2997,7 +2997,7 @@
     <t>hengja</t>
   </si>
   <si>
-    <t>to hang onto (with accusative "what" + á + accusative "onto what")</t>
+    <t>to hang onto (with accusative "what" + ann + accusative "onto what")</t>
   </si>
   <si>
     <t>her</t>
@@ -3153,7 +3153,7 @@
     <t>hlusta</t>
   </si>
   <si>
-    <t>to listen, to heed (intransitive); to listen to (with á + accusative)</t>
+    <t>to listen, to heed (intransitive); to listen to (with ann + accusative)</t>
   </si>
   <si>
     <t>hlutr</t>
@@ -3285,7 +3285,7 @@
     <t>horfa</t>
   </si>
   <si>
-    <t>to stare, to gaze (with á + accusative)</t>
+    <t>to stare, to gaze (with ann + accusative)</t>
   </si>
   <si>
     <t>horn</t>
@@ -3585,7 +3585,7 @@
     <t>hyggja</t>
   </si>
   <si>
-    <t>to inspect, to examine (with á + accusative)</t>
+    <t>to inspect, to examine (with ann + accusative)</t>
   </si>
   <si>
     <t>hygli</t>
@@ -4479,7 +4479,7 @@
     <t>líðja</t>
   </si>
   <si>
-    <t>to touch (with á + accusative)</t>
+    <t>to touch (with ann + accusative)</t>
   </si>
   <si>
     <t>líf</t>
@@ -4509,7 +4509,7 @@
     <t>liggja</t>
   </si>
   <si>
-    <t>to lie down (intransitive or with á + accusative); to be located (with á + dative "where")</t>
+    <t>to lie down (intransitive or with ann + accusative); to be located (with ann + dative "where")</t>
   </si>
   <si>
     <t>líka</t>
@@ -4563,7 +4563,7 @@
     <t>lítja</t>
   </si>
   <si>
-    <t>to look (with á + accusative)</t>
+    <t>to look (with ann + accusative)</t>
   </si>
   <si>
     <t>litr</t>
@@ -6810,7 +6810,7 @@
     <t>skjúta</t>
   </si>
   <si>
-    <t>to shoot (intransitive or with á + accusative)</t>
+    <t>to shoot (intransitive or with ann + accusative)</t>
   </si>
   <si>
     <t>skoða</t>
@@ -6930,7 +6930,7 @@
     <t>skygna</t>
   </si>
   <si>
-    <t>to spy, to pry, to peer, to peek (with á + accusative), to peek from (with frá + dative "from where")</t>
+    <t>to spy, to pry, to peer, to peek (with ann + accusative), to peek from (with frá + dative "from where")</t>
   </si>
   <si>
     <t>skyldja</t>
@@ -7737,7 +7737,7 @@
     <t>svexa</t>
   </si>
   <si>
-    <t>to smear, to paint, to spread a thick liquid on something (with dative "spread what" + á + accusative "on what")</t>
+    <t>to smear, to paint, to spread a thick liquid on something (with dative "spread what" + ann + accusative "on what")</t>
   </si>
   <si>
     <t>svíkja</t>
@@ -13812,6 +13812,12 @@
   </si>
   <si>
     <t>i got hurt from the pot</t>
+  </si>
+  <si>
+    <t>hann fór án staks tals</t>
+  </si>
+  <si>
+    <t>he left without a word</t>
   </si>
   <si>
     <t>a</t>
@@ -47161,10 +47167,12 @@
       <c r="B19" s="39"/>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
+      <c r="E19" s="39" t="s">
+        <v>4586</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>4587</v>
+      </c>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="39"/>
@@ -47377,7 +47385,16 @@
       <c r="H40" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="51">
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H16"/>
+    <mergeCell ref="G17:H17"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="B2:C2"/>
@@ -47392,14 +47409,6 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E7:F7"/>
@@ -47420,6 +47429,7 @@
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="E11:F11"/>
@@ -47446,10 +47456,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="39" t="s">
-        <v>4586</v>
+        <v>4588</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>4587</v>
+        <v>4589</v>
       </c>
       <c r="C1" s="38"/>
     </row>
@@ -47458,34 +47468,34 @@
         <v>30</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>4588</v>
+        <v>4590</v>
       </c>
       <c r="C2" s="38"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="39" t="s">
-        <v>4589</v>
+        <v>4591</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>4590</v>
+        <v>4592</v>
       </c>
       <c r="C3" s="38"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="39" t="s">
-        <v>4591</v>
+        <v>4593</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>4592</v>
+        <v>4594</v>
       </c>
       <c r="C4" s="38"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="39" t="s">
-        <v>4593</v>
+        <v>4595</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>4594</v>
+        <v>4596</v>
       </c>
       <c r="C5" s="38"/>
     </row>
@@ -47494,61 +47504,61 @@
         <v>1182</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>4595</v>
+        <v>4597</v>
       </c>
       <c r="C6" s="38"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="39" t="s">
-        <v>4596</v>
+        <v>4598</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>4597</v>
+        <v>4599</v>
       </c>
       <c r="C7" s="38"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="39" t="s">
-        <v>4598</v>
+        <v>4600</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>4599</v>
+        <v>4601</v>
       </c>
       <c r="C8" s="38"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="39" t="s">
-        <v>4600</v>
+        <v>4602</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="C9" s="38"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="39" t="s">
-        <v>4602</v>
+        <v>4604</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>4603</v>
+        <v>4605</v>
       </c>
       <c r="C10" s="38"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="39" t="s">
-        <v>4604</v>
+        <v>4606</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>4605</v>
+        <v>4607</v>
       </c>
       <c r="C11" s="38"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="39" t="s">
-        <v>4606</v>
+        <v>4608</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>4607</v>
+        <v>4609</v>
       </c>
       <c r="C12" s="38"/>
     </row>
@@ -47557,7 +47567,7 @@
         <v>3508</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>4608</v>
+        <v>4610</v>
       </c>
       <c r="C13" s="38"/>
     </row>
@@ -47568,10 +47578,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="39" t="s">
-        <v>4609</v>
+        <v>4611</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>4610</v>
+        <v>4612</v>
       </c>
       <c r="C15" s="38"/>
     </row>
@@ -47580,7 +47590,7 @@
         <v>558</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>4611</v>
+        <v>4613</v>
       </c>
       <c r="C16" s="38"/>
     </row>
@@ -47591,235 +47601,235 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="39" t="s">
-        <v>4612</v>
+        <v>4614</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>4613</v>
+        <v>4615</v>
       </c>
       <c r="C18" s="38"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="39" t="s">
-        <v>4614</v>
+        <v>4616</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>4615</v>
+        <v>4617</v>
       </c>
       <c r="C19" s="38"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="39" t="s">
-        <v>4616</v>
+        <v>4618</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>4617</v>
+        <v>4619</v>
       </c>
       <c r="C20" s="38"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="39" t="s">
-        <v>4618</v>
+        <v>4620</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>4619</v>
+        <v>4621</v>
       </c>
       <c r="C21" s="38"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="39" t="s">
-        <v>4620</v>
+        <v>4622</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>4621</v>
+        <v>4623</v>
       </c>
       <c r="C22" s="38"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="39" t="s">
-        <v>4622</v>
+        <v>4624</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>4623</v>
+        <v>4625</v>
       </c>
       <c r="C23" s="38"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="39" t="s">
-        <v>4624</v>
+        <v>4626</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>4625</v>
+        <v>4627</v>
       </c>
       <c r="C24" s="38"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="39" t="s">
-        <v>4626</v>
+        <v>4628</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>4627</v>
+        <v>4629</v>
       </c>
       <c r="C25" s="38"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="39" t="s">
-        <v>4628</v>
+        <v>4630</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>4629</v>
+        <v>4631</v>
       </c>
       <c r="C26" s="38"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="39" t="s">
-        <v>4630</v>
+        <v>4632</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>4631</v>
+        <v>4633</v>
       </c>
       <c r="C27" s="38"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="39" t="s">
-        <v>4632</v>
+        <v>4634</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>4633</v>
+        <v>4635</v>
       </c>
       <c r="C28" s="38"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="39" t="s">
-        <v>4634</v>
+        <v>4636</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>4635</v>
+        <v>4637</v>
       </c>
       <c r="C29" s="38"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="39" t="s">
-        <v>4636</v>
+        <v>4638</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>4637</v>
+        <v>4639</v>
       </c>
       <c r="C30" s="38"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="39" t="s">
-        <v>4638</v>
+        <v>4640</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>4639</v>
+        <v>4641</v>
       </c>
       <c r="C31" s="38"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="39" t="s">
-        <v>4640</v>
+        <v>4642</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>4641</v>
+        <v>4643</v>
       </c>
       <c r="C32" s="38"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="39" t="s">
-        <v>4642</v>
+        <v>4644</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>4643</v>
+        <v>4645</v>
       </c>
       <c r="C33" s="38"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="39" t="s">
-        <v>4644</v>
+        <v>4646</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>4645</v>
+        <v>4647</v>
       </c>
       <c r="C34" s="38"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="39" t="s">
-        <v>4646</v>
+        <v>4648</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>4647</v>
+        <v>4649</v>
       </c>
       <c r="C35" s="38"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="39" t="s">
-        <v>4648</v>
+        <v>4650</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>4649</v>
+        <v>4651</v>
       </c>
       <c r="C36" s="38"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="39" t="s">
-        <v>4650</v>
+        <v>4652</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>4651</v>
+        <v>4653</v>
       </c>
       <c r="C37" s="38"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="39" t="s">
-        <v>4652</v>
+        <v>4654</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>4653</v>
+        <v>4655</v>
       </c>
       <c r="C38" s="38"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="39" t="s">
-        <v>4654</v>
+        <v>4656</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>4655</v>
+        <v>4657</v>
       </c>
       <c r="C39" s="38"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="39" t="s">
-        <v>4656</v>
+        <v>4658</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>4657</v>
+        <v>4659</v>
       </c>
       <c r="C40" s="38"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="39" t="s">
-        <v>4658</v>
+        <v>4660</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>4659</v>
+        <v>4661</v>
       </c>
       <c r="C41" s="38"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="39" t="s">
-        <v>4660</v>
+        <v>4662</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>4661</v>
+        <v>4663</v>
       </c>
       <c r="C42" s="38"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="39" t="s">
-        <v>4662</v>
+        <v>4664</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>4663</v>
+        <v>4665</v>
       </c>
       <c r="C43" s="38"/>
     </row>
@@ -47828,34 +47838,34 @@
         <v>542</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>4664</v>
+        <v>4666</v>
       </c>
       <c r="C44" s="38"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="39" t="s">
-        <v>4665</v>
+        <v>4667</v>
       </c>
       <c r="B45" s="39" t="s">
-        <v>4666</v>
+        <v>4668</v>
       </c>
       <c r="C45" s="38"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="39" t="s">
-        <v>4667</v>
+        <v>4669</v>
       </c>
       <c r="B46" s="39" t="s">
-        <v>4668</v>
+        <v>4670</v>
       </c>
       <c r="C46" s="38"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="39" t="s">
-        <v>4669</v>
+        <v>4671</v>
       </c>
       <c r="B47" s="39" t="s">
-        <v>4670</v>
+        <v>4672</v>
       </c>
       <c r="C47" s="38"/>
     </row>
@@ -47878,22 +47888,22 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="42" t="s">
-        <v>4671</v>
+        <v>4673</v>
       </c>
       <c r="C1" s="38"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="42" t="s">
-        <v>4672</v>
+        <v>4674</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>4673</v>
+        <v>4675</v>
       </c>
       <c r="C2" s="38"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="39" t="s">
-        <v>4674</v>
+        <v>4676</v>
       </c>
       <c r="B3" s="39" t="s">
         <v>558</v>
@@ -47902,88 +47912,88 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="39" t="s">
-        <v>4675</v>
+        <v>4677</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>4600</v>
+        <v>4602</v>
       </c>
       <c r="C4" s="38"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="39" t="s">
-        <v>4676</v>
+        <v>4678</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>4677</v>
+        <v>4679</v>
       </c>
       <c r="C5" s="38"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="39" t="s">
-        <v>4678</v>
+        <v>4680</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>4679</v>
+        <v>4681</v>
       </c>
       <c r="C6" s="38"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="39" t="s">
-        <v>4680</v>
+        <v>4682</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>4681</v>
+        <v>4683</v>
       </c>
       <c r="C7" s="38"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="39" t="s">
-        <v>4682</v>
+        <v>4684</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>4683</v>
+        <v>4685</v>
       </c>
       <c r="C8" s="38"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="39" t="s">
-        <v>4684</v>
+        <v>4686</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>4685</v>
+        <v>4687</v>
       </c>
       <c r="C9" s="38"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="39" t="s">
-        <v>4686</v>
+        <v>4688</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>4687</v>
+        <v>4689</v>
       </c>
       <c r="C10" s="38"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="39" t="s">
-        <v>4688</v>
+        <v>4690</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>4689</v>
+        <v>4691</v>
       </c>
       <c r="C11" s="38"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="39" t="s">
-        <v>4690</v>
+        <v>4692</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>4691</v>
+        <v>4693</v>
       </c>
       <c r="C12" s="38"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="39" t="s">
-        <v>4692</v>
+        <v>4694</v>
       </c>
       <c r="B13" s="39" t="s">
         <v>2700</v>
@@ -47992,64 +48002,64 @@
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="39" t="s">
-        <v>4693</v>
+        <v>4695</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>4694</v>
+        <v>4696</v>
       </c>
       <c r="C14" s="38"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="39" t="s">
-        <v>4695</v>
+        <v>4697</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>4696</v>
+        <v>4698</v>
       </c>
       <c r="C15" s="38"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="39" t="s">
-        <v>4697</v>
+        <v>4699</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>4698</v>
+        <v>4700</v>
       </c>
       <c r="C16" s="38"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="39" t="s">
-        <v>4699</v>
+        <v>4701</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>4700</v>
+        <v>4702</v>
       </c>
       <c r="C17" s="38"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="39" t="s">
-        <v>4701</v>
+        <v>4703</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>4702</v>
+        <v>4704</v>
       </c>
       <c r="C18" s="38"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="39" t="s">
-        <v>4703</v>
+        <v>4705</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>4704</v>
+        <v>4706</v>
       </c>
       <c r="C19" s="38"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="39" t="s">
-        <v>4705</v>
+        <v>4707</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>4706</v>
+        <v>4708</v>
       </c>
       <c r="C20" s="38"/>
     </row>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -13868,7 +13868,7 @@
     <t>ek støðva hann í at gera</t>
   </si>
   <si>
-    <t>hann forbannaði þey ór fara inn</t>
+    <t>hann forbannaði þá ór fara inn</t>
   </si>
   <si>
     <t>he forbade them from entering</t>
@@ -13940,7 +13940,7 @@
     <t>he left without a word</t>
   </si>
   <si>
-    <t>þetta er allt í óreði</t>
+    <t>þetta er allt í órøð</t>
   </si>
   <si>
     <t>this is all wrong</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7935" uniqueCount="4953">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7936" uniqueCount="4954">
   <si>
     <t>Entry</t>
   </si>
@@ -14538,7 +14538,10 @@
     <t>God made some men small and some men big, but man made steel and steel made them equal.</t>
   </si>
   <si>
-    <t>ek er sjá</t>
+    <t>(ek) se allt í glasi</t>
+  </si>
+  <si>
+    <t>everything's gone blurry (for me)</t>
   </si>
   <si>
     <t>a</t>
@@ -49354,8 +49357,9 @@
       <c r="E24" s="39" t="s">
         <v>4827</v>
       </c>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
+      <c r="G24" s="39" t="s">
+        <v>4828</v>
+      </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="39"/>
@@ -49518,7 +49522,7 @@
       <c r="H40" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="59">
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
@@ -49562,6 +49566,15 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F16"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="E19:F19"/>
@@ -49569,14 +49582,6 @@
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="E22:F23"/>
     <mergeCell ref="G22:H23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F16"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -49596,10 +49601,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="39" t="s">
-        <v>4828</v>
+        <v>4829</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>4829</v>
+        <v>4830</v>
       </c>
       <c r="C1" s="38"/>
     </row>
@@ -49608,34 +49613,34 @@
         <v>32</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>4830</v>
+        <v>4831</v>
       </c>
       <c r="C2" s="38"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="39" t="s">
-        <v>4831</v>
+        <v>4832</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>4832</v>
+        <v>4833</v>
       </c>
       <c r="C3" s="38"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="39" t="s">
-        <v>4833</v>
+        <v>4834</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>4834</v>
+        <v>4835</v>
       </c>
       <c r="C4" s="38"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="39" t="s">
-        <v>4835</v>
+        <v>4836</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>4836</v>
+        <v>4837</v>
       </c>
       <c r="C5" s="38"/>
     </row>
@@ -49644,61 +49649,61 @@
         <v>1298</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>4837</v>
+        <v>4838</v>
       </c>
       <c r="C6" s="38"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="39" t="s">
-        <v>4838</v>
+        <v>4839</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>4839</v>
+        <v>4840</v>
       </c>
       <c r="C7" s="38"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="39" t="s">
-        <v>4840</v>
+        <v>4841</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>4841</v>
+        <v>4842</v>
       </c>
       <c r="C8" s="38"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="39" t="s">
-        <v>4842</v>
+        <v>4843</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>4843</v>
+        <v>4844</v>
       </c>
       <c r="C9" s="38"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="39" t="s">
-        <v>4844</v>
+        <v>4845</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>4845</v>
+        <v>4846</v>
       </c>
       <c r="C10" s="38"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="39" t="s">
-        <v>4846</v>
+        <v>4847</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>4847</v>
+        <v>4848</v>
       </c>
       <c r="C11" s="38"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="39" t="s">
-        <v>4848</v>
+        <v>4849</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>4849</v>
+        <v>4850</v>
       </c>
       <c r="C12" s="38"/>
     </row>
@@ -49707,7 +49712,7 @@
         <v>3725</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>4850</v>
+        <v>4851</v>
       </c>
       <c r="C13" s="38"/>
     </row>
@@ -49718,10 +49723,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="39" t="s">
-        <v>4851</v>
+        <v>4852</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>4852</v>
+        <v>4853</v>
       </c>
       <c r="C15" s="38"/>
     </row>
@@ -49730,7 +49735,7 @@
         <v>624</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>4853</v>
+        <v>4854</v>
       </c>
       <c r="C16" s="38"/>
     </row>
@@ -49741,235 +49746,235 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="39" t="s">
-        <v>4854</v>
+        <v>4855</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>4855</v>
+        <v>4856</v>
       </c>
       <c r="C18" s="38"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="39" t="s">
-        <v>4856</v>
+        <v>4857</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>4857</v>
+        <v>4858</v>
       </c>
       <c r="C19" s="38"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="39" t="s">
-        <v>4858</v>
+        <v>4859</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>4859</v>
+        <v>4860</v>
       </c>
       <c r="C20" s="38"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="39" t="s">
-        <v>4860</v>
+        <v>4861</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>4861</v>
+        <v>4862</v>
       </c>
       <c r="C21" s="38"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="39" t="s">
-        <v>4862</v>
+        <v>4863</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>4863</v>
+        <v>4864</v>
       </c>
       <c r="C22" s="38"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="39" t="s">
-        <v>4864</v>
+        <v>4865</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>4865</v>
+        <v>4866</v>
       </c>
       <c r="C23" s="38"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="39" t="s">
-        <v>4866</v>
+        <v>4867</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>4867</v>
+        <v>4868</v>
       </c>
       <c r="C24" s="38"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="39" t="s">
-        <v>4868</v>
+        <v>4869</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>4869</v>
+        <v>4870</v>
       </c>
       <c r="C25" s="38"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="39" t="s">
-        <v>4870</v>
+        <v>4871</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>4871</v>
+        <v>4872</v>
       </c>
       <c r="C26" s="38"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="39" t="s">
-        <v>4872</v>
+        <v>4873</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>4873</v>
+        <v>4874</v>
       </c>
       <c r="C27" s="38"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="39" t="s">
-        <v>4874</v>
+        <v>4875</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>4875</v>
+        <v>4876</v>
       </c>
       <c r="C28" s="38"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="39" t="s">
-        <v>4876</v>
+        <v>4877</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>4877</v>
+        <v>4878</v>
       </c>
       <c r="C29" s="38"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="39" t="s">
-        <v>4878</v>
+        <v>4879</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>4879</v>
+        <v>4880</v>
       </c>
       <c r="C30" s="38"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="39" t="s">
-        <v>4880</v>
+        <v>4881</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>4881</v>
+        <v>4882</v>
       </c>
       <c r="C31" s="38"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="39" t="s">
-        <v>4882</v>
+        <v>4883</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>4883</v>
+        <v>4884</v>
       </c>
       <c r="C32" s="38"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="39" t="s">
-        <v>4884</v>
+        <v>4885</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>4885</v>
+        <v>4886</v>
       </c>
       <c r="C33" s="38"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="39" t="s">
-        <v>4886</v>
+        <v>4887</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>4887</v>
+        <v>4888</v>
       </c>
       <c r="C34" s="38"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="39" t="s">
-        <v>4888</v>
+        <v>4889</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>4889</v>
+        <v>4890</v>
       </c>
       <c r="C35" s="38"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="39" t="s">
-        <v>4890</v>
+        <v>4891</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>4891</v>
+        <v>4892</v>
       </c>
       <c r="C36" s="38"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="39" t="s">
-        <v>4892</v>
+        <v>4893</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>4893</v>
+        <v>4894</v>
       </c>
       <c r="C37" s="38"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="39" t="s">
-        <v>4894</v>
+        <v>4895</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>4895</v>
+        <v>4896</v>
       </c>
       <c r="C38" s="38"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="39" t="s">
-        <v>4896</v>
+        <v>4897</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>4897</v>
+        <v>4898</v>
       </c>
       <c r="C39" s="38"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="39" t="s">
-        <v>4898</v>
+        <v>4899</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>4899</v>
+        <v>4900</v>
       </c>
       <c r="C40" s="38"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="39" t="s">
-        <v>4900</v>
+        <v>4901</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>4901</v>
+        <v>4902</v>
       </c>
       <c r="C41" s="38"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="39" t="s">
-        <v>4902</v>
+        <v>4903</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>4903</v>
+        <v>4904</v>
       </c>
       <c r="C42" s="38"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="39" t="s">
-        <v>4904</v>
+        <v>4905</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>4905</v>
+        <v>4906</v>
       </c>
       <c r="C43" s="38"/>
     </row>
@@ -49978,34 +49983,34 @@
         <v>602</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>4906</v>
+        <v>4907</v>
       </c>
       <c r="C44" s="38"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="39" t="s">
-        <v>4907</v>
+        <v>4908</v>
       </c>
       <c r="B45" s="39" t="s">
-        <v>4908</v>
+        <v>4909</v>
       </c>
       <c r="C45" s="38"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="39" t="s">
-        <v>4909</v>
+        <v>4910</v>
       </c>
       <c r="B46" s="39" t="s">
-        <v>4910</v>
+        <v>4911</v>
       </c>
       <c r="C46" s="38"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="39" t="s">
-        <v>4911</v>
+        <v>4912</v>
       </c>
       <c r="B47" s="39" t="s">
-        <v>4912</v>
+        <v>4913</v>
       </c>
       <c r="C47" s="38"/>
     </row>
@@ -50028,22 +50033,22 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="43" t="s">
-        <v>4913</v>
+        <v>4914</v>
       </c>
       <c r="C1" s="38"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="43" t="s">
-        <v>4914</v>
+        <v>4915</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>4915</v>
+        <v>4916</v>
       </c>
       <c r="C2" s="38"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="39" t="s">
-        <v>4916</v>
+        <v>4917</v>
       </c>
       <c r="B3" s="39" t="s">
         <v>624</v>
@@ -50052,97 +50057,97 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="39" t="s">
-        <v>4917</v>
+        <v>4918</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>4842</v>
+        <v>4843</v>
       </c>
       <c r="C4" s="38"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="39" t="s">
-        <v>4918</v>
+        <v>4919</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>4919</v>
+        <v>4920</v>
       </c>
       <c r="C5" s="38"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="39" t="s">
-        <v>4920</v>
+        <v>4921</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>4921</v>
+        <v>4922</v>
       </c>
       <c r="C6" s="38"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="39" t="s">
-        <v>4922</v>
+        <v>4923</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>4923</v>
+        <v>4924</v>
       </c>
       <c r="C7" s="38"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="39" t="s">
-        <v>4924</v>
+        <v>4925</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>4925</v>
+        <v>4926</v>
       </c>
       <c r="C8" s="38"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="39" t="s">
-        <v>4926</v>
+        <v>4927</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>4927</v>
+        <v>4928</v>
       </c>
       <c r="C9" s="38"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="39" t="s">
-        <v>4928</v>
+        <v>4929</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>4929</v>
+        <v>4930</v>
       </c>
       <c r="C10" s="38"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="39" t="s">
-        <v>4930</v>
+        <v>4931</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>4931</v>
+        <v>4932</v>
       </c>
       <c r="C11" s="38"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="39" t="s">
-        <v>4932</v>
+        <v>4933</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>4933</v>
+        <v>4934</v>
       </c>
       <c r="C12" s="38"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="39" t="s">
-        <v>4934</v>
+        <v>4935</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>4935</v>
+        <v>4936</v>
       </c>
       <c r="C13" s="38"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="39" t="s">
-        <v>4936</v>
+        <v>4937</v>
       </c>
       <c r="B14" s="39" t="s">
         <v>2905</v>
@@ -50151,73 +50156,73 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="39" t="s">
-        <v>4937</v>
+        <v>4938</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>4938</v>
+        <v>4939</v>
       </c>
       <c r="C15" s="38"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="39" t="s">
-        <v>4939</v>
+        <v>4940</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>4940</v>
+        <v>4941</v>
       </c>
       <c r="C16" s="38"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="39" t="s">
-        <v>4941</v>
+        <v>4942</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>4942</v>
+        <v>4943</v>
       </c>
       <c r="C17" s="38"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="39" t="s">
-        <v>4943</v>
+        <v>4944</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>4944</v>
+        <v>4945</v>
       </c>
       <c r="C18" s="38"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="39" t="s">
-        <v>4945</v>
+        <v>4946</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>4946</v>
+        <v>4947</v>
       </c>
       <c r="C19" s="38"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="39" t="s">
-        <v>4947</v>
+        <v>4948</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>4948</v>
+        <v>4949</v>
       </c>
       <c r="C20" s="38"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="39" t="s">
-        <v>4949</v>
+        <v>4950</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>4950</v>
+        <v>4951</v>
       </c>
       <c r="C21" s="38"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="39" t="s">
-        <v>4951</v>
+        <v>4952</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>4952</v>
+        <v>4953</v>
       </c>
       <c r="C22" s="38"/>
     </row>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8570" uniqueCount="5355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8569" uniqueCount="5355">
   <si>
     <t>Entry</t>
   </si>
@@ -31630,9 +31630,7 @@
       <c r="C1220" s="3" t="s">
         <v>2472</v>
       </c>
-      <c r="D1220" s="3" t="s">
-        <v>282</v>
-      </c>
+      <c r="D1220" s="3"/>
     </row>
     <row r="1221" ht="18.75" customHeight="1">
       <c r="A1221" s="3" t="s">

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8569" uniqueCount="5355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8577" uniqueCount="5361">
   <si>
     <t>Entry</t>
   </si>
@@ -13617,7 +13617,7 @@
     <t>example: hylja</t>
   </si>
   <si>
-    <t>example fryrja</t>
+    <t>example rykkja</t>
   </si>
   <si>
     <t>example spyrja</t>
@@ -13632,7 +13632,7 @@
     <t>at hylja</t>
   </si>
   <si>
-    <t>at fryrja</t>
+    <t>at rykkja</t>
   </si>
   <si>
     <t>at spyrja</t>
@@ -13647,7 +13647,7 @@
     <t>huldið (huldinn)</t>
   </si>
   <si>
-    <t>frurt (frurðr)</t>
+    <t>rukkt (rukkinn)</t>
   </si>
   <si>
     <t>spurt (spurðr)</t>
@@ -13662,7 +13662,7 @@
     <t>hyljandi</t>
   </si>
   <si>
-    <t>fryrjandi</t>
+    <t>rykkjandi</t>
   </si>
   <si>
     <t>spyrjandi</t>
@@ -13683,10 +13683,10 @@
     <t>hulda</t>
   </si>
   <si>
-    <t>fryr</t>
-  </si>
-  <si>
-    <t>frurða</t>
+    <t>rykk</t>
+  </si>
+  <si>
+    <t>rukkta</t>
   </si>
   <si>
     <t>spyr</t>
@@ -13713,10 +13713,10 @@
     <t>huldir</t>
   </si>
   <si>
-    <t>fryrr</t>
-  </si>
-  <si>
-    <t>frurðir</t>
+    <t>rykkr</t>
+  </si>
+  <si>
+    <t>rukktir</t>
   </si>
   <si>
     <t>spyrr</t>
@@ -13737,7 +13737,7 @@
     <t>huldi</t>
   </si>
   <si>
-    <t>frurði</t>
+    <t>rukkti</t>
   </si>
   <si>
     <t>spurði</t>
@@ -13755,10 +13755,10 @@
     <t>huldum</t>
   </si>
   <si>
-    <t>fryrjum</t>
-  </si>
-  <si>
-    <t>frurðum</t>
+    <t>rykkjum</t>
+  </si>
+  <si>
+    <t>rukktum</t>
   </si>
   <si>
     <t>spyrjum</t>
@@ -13785,10 +13785,10 @@
     <t>hulduð</t>
   </si>
   <si>
-    <t>fryrjuð</t>
-  </si>
-  <si>
-    <t>frurðuð</t>
+    <t>rykkjuð</t>
+  </si>
+  <si>
+    <t>rukktuð</t>
   </si>
   <si>
     <t>spyrjuð</t>
@@ -13815,10 +13815,10 @@
     <t>huldu</t>
   </si>
   <si>
-    <t>fryrju</t>
-  </si>
-  <si>
-    <t>frurðu</t>
+    <t>rykkju</t>
+  </si>
+  <si>
+    <t>rukktu</t>
   </si>
   <si>
     <t>spyrju</t>
@@ -13839,16 +13839,34 @@
     <t>huldisk</t>
   </si>
   <si>
+    <t>rykksk</t>
+  </si>
+  <si>
+    <t>rukktisk</t>
+  </si>
+  <si>
     <t>hyljumsk</t>
   </si>
   <si>
     <t>huldumsk</t>
   </si>
   <si>
+    <t>rykkjumsk</t>
+  </si>
+  <si>
+    <t>rukktumsk</t>
+  </si>
+  <si>
     <t>hyljusk</t>
   </si>
   <si>
     <t>huldusk</t>
+  </si>
+  <si>
+    <t>rykkjusk</t>
+  </si>
+  <si>
+    <t>rukktusk</t>
   </si>
   <si>
     <t>strong verb a (no pattern)</t>
@@ -46581,8 +46599,12 @@
       <c r="F62" s="24" t="s">
         <v>4333</v>
       </c>
-      <c r="G62" s="38"/>
-      <c r="H62" s="38"/>
+      <c r="G62" s="8" t="s">
+        <v>4332</v>
+      </c>
+      <c r="H62" s="24" t="s">
+        <v>4333</v>
+      </c>
       <c r="I62" s="30"/>
       <c r="J62" s="38"/>
       <c r="K62" s="30"/>
@@ -46610,8 +46632,12 @@
       <c r="F63" s="25" t="s">
         <v>4593</v>
       </c>
-      <c r="G63" s="40"/>
-      <c r="H63" s="40"/>
+      <c r="G63" s="23" t="s">
+        <v>4594</v>
+      </c>
+      <c r="H63" s="25" t="s">
+        <v>4595</v>
+      </c>
       <c r="I63" s="10"/>
       <c r="J63" s="40"/>
       <c r="K63" s="10"/>
@@ -46633,8 +46659,8 @@
       <c r="D64" s="25"/>
       <c r="E64" s="26"/>
       <c r="F64" s="22"/>
-      <c r="G64" s="40"/>
-      <c r="H64" s="40"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="22"/>
       <c r="I64" s="10"/>
       <c r="J64" s="40"/>
       <c r="K64" s="10"/>
@@ -46656,8 +46682,8 @@
       <c r="D65" s="25"/>
       <c r="E65" s="26"/>
       <c r="F65" s="22"/>
-      <c r="G65" s="40"/>
-      <c r="H65" s="40"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="22"/>
       <c r="I65" s="10"/>
       <c r="J65" s="40"/>
       <c r="K65" s="10"/>
@@ -46680,13 +46706,17 @@
       <c r="C66" s="39"/>
       <c r="D66" s="25"/>
       <c r="E66" s="10" t="s">
-        <v>4594</v>
+        <v>4596</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>4595</v>
-      </c>
-      <c r="G66" s="40"/>
-      <c r="H66" s="40"/>
+        <v>4597</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>4598</v>
+      </c>
+      <c r="H66" s="25" t="s">
+        <v>4599</v>
+      </c>
       <c r="I66" s="10"/>
       <c r="J66" s="40"/>
       <c r="K66" s="10"/>
@@ -46707,13 +46737,17 @@
       <c r="C67" s="39"/>
       <c r="D67" s="25"/>
       <c r="E67" s="10" t="s">
-        <v>4596</v>
+        <v>4600</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>4597</v>
-      </c>
-      <c r="G67" s="40"/>
-      <c r="H67" s="40"/>
+        <v>4601</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>4602</v>
+      </c>
+      <c r="H67" s="25" t="s">
+        <v>4603</v>
+      </c>
       <c r="I67" s="10"/>
       <c r="J67" s="40"/>
       <c r="K67" s="10"/>
@@ -46735,8 +46769,8 @@
       <c r="D68" s="25"/>
       <c r="E68" s="33"/>
       <c r="F68" s="34"/>
-      <c r="G68" s="40"/>
-      <c r="H68" s="40"/>
+      <c r="G68" s="33"/>
+      <c r="H68" s="34"/>
       <c r="I68" s="10"/>
       <c r="J68" s="40"/>
       <c r="K68" s="10"/>
@@ -46793,27 +46827,27 @@
     </row>
     <row r="71" ht="18.75" customHeight="1">
       <c r="A71" s="18" t="s">
-        <v>4598</v>
+        <v>4604</v>
       </c>
       <c r="B71" s="19"/>
       <c r="C71" s="20" t="s">
-        <v>4599</v>
+        <v>4605</v>
       </c>
       <c r="D71" s="19"/>
       <c r="E71" s="18" t="s">
-        <v>4600</v>
+        <v>4606</v>
       </c>
       <c r="F71" s="41"/>
       <c r="G71" s="18" t="s">
-        <v>4601</v>
+        <v>4607</v>
       </c>
       <c r="H71" s="41"/>
       <c r="I71" s="18" t="s">
-        <v>4602</v>
+        <v>4608</v>
       </c>
       <c r="J71" s="19"/>
       <c r="K71" s="18" t="s">
-        <v>4603</v>
+        <v>4609</v>
       </c>
       <c r="L71" s="19"/>
     </row>
@@ -46823,22 +46857,22 @@
       </c>
       <c r="B72" s="22"/>
       <c r="C72" s="10" t="s">
-        <v>4604</v>
+        <v>4610</v>
       </c>
       <c r="D72" s="22"/>
       <c r="E72" s="10" t="s">
-        <v>4605</v>
+        <v>4611</v>
       </c>
       <c r="F72" s="22"/>
       <c r="G72" s="10" t="s">
-        <v>4606</v>
+        <v>4612</v>
       </c>
       <c r="I72" s="23" t="s">
-        <v>4607</v>
+        <v>4613</v>
       </c>
       <c r="J72" s="22"/>
       <c r="K72" s="23" t="s">
-        <v>4608</v>
+        <v>4614</v>
       </c>
       <c r="L72" s="22"/>
     </row>
@@ -46848,22 +46882,22 @@
       </c>
       <c r="B73" s="22"/>
       <c r="C73" s="10" t="s">
-        <v>4609</v>
+        <v>4615</v>
       </c>
       <c r="D73" s="22"/>
       <c r="E73" s="10" t="s">
-        <v>4610</v>
+        <v>4616</v>
       </c>
       <c r="F73" s="22"/>
       <c r="G73" s="10" t="s">
-        <v>4611</v>
+        <v>4617</v>
       </c>
       <c r="I73" s="23" t="s">
-        <v>4612</v>
+        <v>4618</v>
       </c>
       <c r="J73" s="22"/>
       <c r="K73" s="23" t="s">
-        <v>4613</v>
+        <v>4619</v>
       </c>
       <c r="L73" s="22"/>
     </row>
@@ -46873,22 +46907,22 @@
       </c>
       <c r="B74" s="22"/>
       <c r="C74" s="10" t="s">
-        <v>4614</v>
+        <v>4620</v>
       </c>
       <c r="D74" s="22"/>
       <c r="E74" s="10" t="s">
-        <v>4615</v>
+        <v>4621</v>
       </c>
       <c r="F74" s="22"/>
       <c r="G74" s="10" t="s">
-        <v>4616</v>
+        <v>4622</v>
       </c>
       <c r="I74" s="23" t="s">
-        <v>4617</v>
+        <v>4623</v>
       </c>
       <c r="J74" s="22"/>
       <c r="K74" s="23" t="s">
-        <v>4618</v>
+        <v>4624</v>
       </c>
       <c r="L74" s="22"/>
     </row>
@@ -46936,34 +46970,34 @@
         <v>644</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>4619</v>
+        <v>4625</v>
       </c>
       <c r="D76" s="25" t="s">
         <v>3326</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>4620</v>
+        <v>4626</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>4621</v>
+        <v>4627</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>4622</v>
+        <v>4628</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>4623</v>
+        <v>4629</v>
       </c>
       <c r="I76" s="23" t="s">
-        <v>4624</v>
+        <v>4630</v>
       </c>
       <c r="J76" s="25" t="s">
-        <v>4625</v>
+        <v>4631</v>
       </c>
       <c r="K76" s="23" t="s">
-        <v>4626</v>
+        <v>4632</v>
       </c>
       <c r="L76" s="25" t="s">
-        <v>4627</v>
+        <v>4633</v>
       </c>
     </row>
     <row r="77" ht="18.75" customHeight="1">
@@ -46972,34 +47006,34 @@
         <v>3648</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>4628</v>
+        <v>4634</v>
       </c>
       <c r="D77" s="25" t="s">
-        <v>4629</v>
+        <v>4635</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>4630</v>
+        <v>4636</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>4631</v>
+        <v>4637</v>
       </c>
       <c r="G77" s="10" t="s">
         <v>4121</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>4632</v>
+        <v>4638</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>4633</v>
+        <v>4639</v>
       </c>
       <c r="J77" s="25" t="s">
-        <v>4634</v>
+        <v>4640</v>
       </c>
       <c r="K77" s="23" t="s">
-        <v>4635</v>
+        <v>4641</v>
       </c>
       <c r="L77" s="25" t="s">
-        <v>4636</v>
+        <v>4642</v>
       </c>
     </row>
     <row r="78" ht="18.75" customHeight="1">
@@ -47008,34 +47042,34 @@
         <v>4348</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>4619</v>
+        <v>4625</v>
       </c>
       <c r="D78" s="25" t="s">
         <v>3326</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>4620</v>
+        <v>4626</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>4621</v>
+        <v>4627</v>
       </c>
       <c r="G78" s="10" t="s">
         <v>4121</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>4623</v>
+        <v>4629</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>4633</v>
+        <v>4639</v>
       </c>
       <c r="J78" s="25" t="s">
-        <v>4625</v>
+        <v>4631</v>
       </c>
       <c r="K78" s="23" t="s">
-        <v>4635</v>
+        <v>4641</v>
       </c>
       <c r="L78" s="25" t="s">
-        <v>4637</v>
+        <v>4643</v>
       </c>
     </row>
     <row r="79" ht="18.75" customHeight="1">
@@ -47046,34 +47080,34 @@
         <v>3488</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>4638</v>
+        <v>4644</v>
       </c>
       <c r="D79" s="25" t="s">
-        <v>4639</v>
+        <v>4645</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>4640</v>
+        <v>4646</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>4641</v>
+        <v>4647</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>4642</v>
+        <v>4648</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>4643</v>
+        <v>4649</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>4644</v>
+        <v>4650</v>
       </c>
       <c r="J79" s="25" t="s">
-        <v>4645</v>
+        <v>4651</v>
       </c>
       <c r="K79" s="23" t="s">
-        <v>4646</v>
+        <v>4652</v>
       </c>
       <c r="L79" s="25" t="s">
-        <v>4647</v>
+        <v>4653</v>
       </c>
     </row>
     <row r="80" ht="18.75" customHeight="1">
@@ -47082,34 +47116,34 @@
         <v>3604</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>4648</v>
+        <v>4654</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>4649</v>
+        <v>4655</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>4650</v>
+        <v>4656</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>4651</v>
+        <v>4657</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>4652</v>
+        <v>4658</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>4653</v>
+        <v>4659</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>4654</v>
+        <v>4660</v>
       </c>
       <c r="J80" s="25" t="s">
-        <v>4655</v>
+        <v>4661</v>
       </c>
       <c r="K80" s="23" t="s">
-        <v>4656</v>
+        <v>4662</v>
       </c>
       <c r="L80" s="25" t="s">
-        <v>4657</v>
+        <v>4663</v>
       </c>
     </row>
     <row r="81" ht="18.75" customHeight="1">
@@ -47118,34 +47152,34 @@
         <v>4373</v>
       </c>
       <c r="C81" s="27" t="s">
-        <v>4658</v>
+        <v>4664</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>4659</v>
+        <v>4665</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>4660</v>
+        <v>4666</v>
       </c>
       <c r="F81" s="28" t="s">
-        <v>4661</v>
+        <v>4667</v>
       </c>
       <c r="G81" s="27" t="s">
-        <v>4662</v>
+        <v>4668</v>
       </c>
       <c r="H81" s="27" t="s">
-        <v>4663</v>
+        <v>4669</v>
       </c>
       <c r="I81" s="23" t="s">
-        <v>4664</v>
+        <v>4670</v>
       </c>
       <c r="J81" s="25" t="s">
-        <v>4665</v>
+        <v>4671</v>
       </c>
       <c r="K81" s="23" t="s">
-        <v>4666</v>
+        <v>4672</v>
       </c>
       <c r="L81" s="25" t="s">
-        <v>4667</v>
+        <v>4673</v>
       </c>
     </row>
     <row r="82" ht="18.75" customHeight="1">
@@ -47187,16 +47221,16 @@
       <c r="G83" s="10"/>
       <c r="H83" s="10"/>
       <c r="I83" s="23" t="s">
-        <v>4668</v>
+        <v>4674</v>
       </c>
       <c r="J83" s="25" t="s">
-        <v>4669</v>
+        <v>4675</v>
       </c>
       <c r="K83" s="23" t="s">
-        <v>4670</v>
+        <v>4676</v>
       </c>
       <c r="L83" s="25" t="s">
-        <v>4671</v>
+        <v>4677</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10"/>
@@ -47258,16 +47292,16 @@
       <c r="G86" s="10"/>
       <c r="H86" s="10"/>
       <c r="I86" s="23" t="s">
-        <v>4672</v>
+        <v>4678</v>
       </c>
       <c r="J86" s="25" t="s">
-        <v>4673</v>
+        <v>4679</v>
       </c>
       <c r="K86" s="23" t="s">
-        <v>4674</v>
+        <v>4680</v>
       </c>
       <c r="L86" s="25" t="s">
-        <v>4675</v>
+        <v>4681</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10"/>
@@ -47287,16 +47321,16 @@
       <c r="G87" s="10"/>
       <c r="H87" s="10"/>
       <c r="I87" s="23" t="s">
-        <v>4676</v>
+        <v>4682</v>
       </c>
       <c r="J87" s="25" t="s">
-        <v>4677</v>
+        <v>4683</v>
       </c>
       <c r="K87" s="23" t="s">
-        <v>4678</v>
+        <v>4684</v>
       </c>
       <c r="L87" s="25" t="s">
-        <v>4679</v>
+        <v>4685</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10"/>
@@ -47350,27 +47384,27 @@
     </row>
     <row r="90" ht="18.75" customHeight="1">
       <c r="A90" s="18" t="s">
-        <v>4680</v>
+        <v>4686</v>
       </c>
       <c r="B90" s="19"/>
       <c r="C90" s="18" t="s">
-        <v>4681</v>
+        <v>4687</v>
       </c>
       <c r="D90" s="19"/>
       <c r="E90" s="18" t="s">
-        <v>4682</v>
+        <v>4688</v>
       </c>
       <c r="F90" s="19"/>
       <c r="G90" s="18" t="s">
-        <v>4683</v>
+        <v>4689</v>
       </c>
       <c r="H90" s="19"/>
       <c r="I90" s="18" t="s">
-        <v>4684</v>
+        <v>4690</v>
       </c>
       <c r="J90" s="19"/>
       <c r="K90" s="18" t="s">
-        <v>4685</v>
+        <v>4691</v>
       </c>
       <c r="L90" s="19"/>
       <c r="M90" s="10"/>
@@ -47383,27 +47417,27 @@
     </row>
     <row r="91" ht="18.75" customHeight="1">
       <c r="A91" s="23" t="s">
-        <v>4686</v>
+        <v>4692</v>
       </c>
       <c r="B91" s="22"/>
       <c r="C91" s="23" t="s">
-        <v>4687</v>
+        <v>4693</v>
       </c>
       <c r="D91" s="22"/>
       <c r="E91" s="23" t="s">
-        <v>4688</v>
+        <v>4694</v>
       </c>
       <c r="F91" s="22"/>
       <c r="G91" s="23" t="s">
-        <v>4689</v>
+        <v>4695</v>
       </c>
       <c r="H91" s="22"/>
       <c r="I91" s="23" t="s">
-        <v>4690</v>
+        <v>4696</v>
       </c>
       <c r="J91" s="22"/>
       <c r="K91" s="23" t="s">
-        <v>4691</v>
+        <v>4697</v>
       </c>
       <c r="L91" s="22"/>
       <c r="M91" s="10"/>
@@ -47416,27 +47450,27 @@
     </row>
     <row r="92" ht="18.75" customHeight="1">
       <c r="A92" s="23" t="s">
-        <v>4692</v>
+        <v>4698</v>
       </c>
       <c r="B92" s="22"/>
       <c r="C92" s="23" t="s">
-        <v>4693</v>
+        <v>4699</v>
       </c>
       <c r="D92" s="22"/>
       <c r="E92" s="23" t="s">
-        <v>4694</v>
+        <v>4700</v>
       </c>
       <c r="F92" s="22"/>
       <c r="G92" s="23" t="s">
-        <v>4695</v>
+        <v>4701</v>
       </c>
       <c r="H92" s="22"/>
       <c r="I92" s="23" t="s">
-        <v>4696</v>
+        <v>4702</v>
       </c>
       <c r="J92" s="22"/>
       <c r="K92" s="23" t="s">
-        <v>4697</v>
+        <v>4703</v>
       </c>
       <c r="L92" s="22"/>
       <c r="M92" s="10"/>
@@ -47449,27 +47483,27 @@
     </row>
     <row r="93" ht="18.75" customHeight="1">
       <c r="A93" s="23" t="s">
-        <v>4698</v>
+        <v>4704</v>
       </c>
       <c r="B93" s="22"/>
       <c r="C93" s="23" t="s">
-        <v>4698</v>
+        <v>4704</v>
       </c>
       <c r="D93" s="22"/>
       <c r="E93" s="23" t="s">
-        <v>4699</v>
+        <v>4705</v>
       </c>
       <c r="F93" s="22"/>
       <c r="G93" s="23" t="s">
-        <v>4700</v>
+        <v>4706</v>
       </c>
       <c r="H93" s="22"/>
       <c r="I93" s="23" t="s">
-        <v>4701</v>
+        <v>4707</v>
       </c>
       <c r="J93" s="22"/>
       <c r="K93" s="23" t="s">
-        <v>4702</v>
+        <v>4708</v>
       </c>
       <c r="L93" s="22"/>
       <c r="M93" s="10"/>
@@ -47527,40 +47561,40 @@
     </row>
     <row r="95" ht="18.75" customHeight="1">
       <c r="A95" s="23" t="s">
-        <v>4703</v>
+        <v>4709</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>4704</v>
+        <v>4710</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>4705</v>
+        <v>4711</v>
       </c>
       <c r="D95" s="25" t="s">
-        <v>4706</v>
+        <v>4712</v>
       </c>
       <c r="E95" s="23" t="s">
-        <v>4707</v>
+        <v>4713</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>4708</v>
+        <v>4714</v>
       </c>
       <c r="G95" s="23" t="s">
-        <v>4709</v>
+        <v>4715</v>
       </c>
       <c r="H95" s="25" t="s">
-        <v>4710</v>
+        <v>4716</v>
       </c>
       <c r="I95" s="23" t="s">
-        <v>4711</v>
+        <v>4717</v>
       </c>
       <c r="J95" s="25" t="s">
-        <v>4712</v>
+        <v>4718</v>
       </c>
       <c r="K95" s="23" t="s">
-        <v>4713</v>
+        <v>4719</v>
       </c>
       <c r="L95" s="25" t="s">
-        <v>4714</v>
+        <v>4720</v>
       </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10"/>
@@ -47572,40 +47606,40 @@
     </row>
     <row r="96" ht="18.75" customHeight="1">
       <c r="A96" s="23" t="s">
-        <v>4715</v>
+        <v>4721</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>4716</v>
+        <v>4722</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>4717</v>
+        <v>4723</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>4718</v>
+        <v>4724</v>
       </c>
       <c r="E96" s="23" t="s">
-        <v>4719</v>
+        <v>4725</v>
       </c>
       <c r="F96" s="25" t="s">
-        <v>4720</v>
+        <v>4726</v>
       </c>
       <c r="G96" s="23" t="s">
-        <v>4721</v>
+        <v>4727</v>
       </c>
       <c r="H96" s="25" t="s">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="I96" s="23" t="s">
         <v>1772</v>
       </c>
       <c r="J96" s="25" t="s">
-        <v>4723</v>
+        <v>4729</v>
       </c>
       <c r="K96" s="23" t="s">
-        <v>4724</v>
+        <v>4730</v>
       </c>
       <c r="L96" s="25" t="s">
-        <v>4725</v>
+        <v>4731</v>
       </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10"/>
@@ -47617,40 +47651,40 @@
     </row>
     <row r="97" ht="18.75" customHeight="1">
       <c r="A97" s="23" t="s">
+        <v>4721</v>
+      </c>
+      <c r="B97" s="25" t="s">
+        <v>4732</v>
+      </c>
+      <c r="C97" s="23" t="s">
+        <v>4723</v>
+      </c>
+      <c r="D97" s="25" t="s">
+        <v>4733</v>
+      </c>
+      <c r="E97" s="23" t="s">
+        <v>4725</v>
+      </c>
+      <c r="F97" s="25" t="s">
+        <v>4714</v>
+      </c>
+      <c r="G97" s="23" t="s">
         <v>4715</v>
       </c>
-      <c r="B97" s="25" t="s">
-        <v>4726</v>
-      </c>
-      <c r="C97" s="23" t="s">
-        <v>4717</v>
-      </c>
-      <c r="D97" s="25" t="s">
-        <v>4727</v>
-      </c>
-      <c r="E97" s="23" t="s">
-        <v>4719</v>
-      </c>
-      <c r="F97" s="25" t="s">
-        <v>4708</v>
-      </c>
-      <c r="G97" s="23" t="s">
-        <v>4709</v>
-      </c>
       <c r="H97" s="25" t="s">
-        <v>4728</v>
+        <v>4734</v>
       </c>
       <c r="I97" s="23" t="s">
         <v>1772</v>
       </c>
       <c r="J97" s="25" t="s">
-        <v>4729</v>
+        <v>4735</v>
       </c>
       <c r="K97" s="23" t="s">
-        <v>4724</v>
+        <v>4730</v>
       </c>
       <c r="L97" s="25" t="s">
-        <v>4714</v>
+        <v>4720</v>
       </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10"/>
@@ -47662,40 +47696,40 @@
     </row>
     <row r="98" ht="18.75" customHeight="1">
       <c r="A98" s="23" t="s">
-        <v>4730</v>
+        <v>4736</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>4731</v>
+        <v>4737</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>4732</v>
+        <v>4738</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>4733</v>
+        <v>4739</v>
       </c>
       <c r="E98" s="23" t="s">
-        <v>4734</v>
+        <v>4740</v>
       </c>
       <c r="F98" s="25" t="s">
-        <v>4735</v>
+        <v>4741</v>
       </c>
       <c r="G98" s="23" t="s">
-        <v>4736</v>
+        <v>4742</v>
       </c>
       <c r="H98" s="25" t="s">
-        <v>4737</v>
+        <v>4743</v>
       </c>
       <c r="I98" s="23" t="s">
-        <v>4738</v>
+        <v>4744</v>
       </c>
       <c r="J98" s="25" t="s">
-        <v>4739</v>
+        <v>4745</v>
       </c>
       <c r="K98" s="23" t="s">
-        <v>4740</v>
+        <v>4746</v>
       </c>
       <c r="L98" s="25" t="s">
-        <v>4741</v>
+        <v>4747</v>
       </c>
       <c r="M98" s="10"/>
       <c r="N98" s="10"/>
@@ -47707,40 +47741,40 @@
     </row>
     <row r="99" ht="18.75" customHeight="1">
       <c r="A99" s="23" t="s">
-        <v>4742</v>
+        <v>4748</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>4743</v>
+        <v>4749</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>4744</v>
+        <v>4750</v>
       </c>
       <c r="D99" s="25" t="s">
-        <v>4745</v>
+        <v>4751</v>
       </c>
       <c r="E99" s="23" t="s">
-        <v>4746</v>
+        <v>4752</v>
       </c>
       <c r="F99" s="25" t="s">
-        <v>4747</v>
+        <v>4753</v>
       </c>
       <c r="G99" s="23" t="s">
-        <v>4748</v>
+        <v>4754</v>
       </c>
       <c r="H99" s="25" t="s">
-        <v>4749</v>
+        <v>4755</v>
       </c>
       <c r="I99" s="23" t="s">
-        <v>4750</v>
+        <v>4756</v>
       </c>
       <c r="J99" s="25" t="s">
-        <v>4751</v>
+        <v>4757</v>
       </c>
       <c r="K99" s="23" t="s">
-        <v>4752</v>
+        <v>4758</v>
       </c>
       <c r="L99" s="25" t="s">
-        <v>4753</v>
+        <v>4759</v>
       </c>
       <c r="M99" s="10"/>
       <c r="N99" s="10"/>
@@ -47752,40 +47786,40 @@
     </row>
     <row r="100" ht="18.75" customHeight="1">
       <c r="A100" s="36" t="s">
-        <v>4754</v>
+        <v>4760</v>
       </c>
       <c r="B100" s="28" t="s">
-        <v>4755</v>
+        <v>4761</v>
       </c>
       <c r="C100" s="36" t="s">
-        <v>4756</v>
+        <v>4762</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>4757</v>
+        <v>4763</v>
       </c>
       <c r="E100" s="23" t="s">
-        <v>4758</v>
+        <v>4764</v>
       </c>
       <c r="F100" s="25" t="s">
-        <v>4759</v>
+        <v>4765</v>
       </c>
       <c r="G100" s="36" t="s">
-        <v>4760</v>
+        <v>4766</v>
       </c>
       <c r="H100" s="28" t="s">
-        <v>4761</v>
+        <v>4767</v>
       </c>
       <c r="I100" s="36" t="s">
-        <v>4762</v>
+        <v>4768</v>
       </c>
       <c r="J100" s="28" t="s">
-        <v>4763</v>
+        <v>4769</v>
       </c>
       <c r="K100" s="36" t="s">
-        <v>4764</v>
+        <v>4770</v>
       </c>
       <c r="L100" s="28" t="s">
-        <v>4765</v>
+        <v>4771</v>
       </c>
       <c r="M100" s="10"/>
       <c r="N100" s="10"/>
@@ -47822,10 +47856,10 @@
       <c r="A102" s="10"/>
       <c r="B102" s="10"/>
       <c r="E102" s="23" t="s">
-        <v>4766</v>
+        <v>4772</v>
       </c>
       <c r="F102" s="25" t="s">
-        <v>4767</v>
+        <v>4773</v>
       </c>
       <c r="G102" s="10"/>
       <c r="H102" s="10"/>
@@ -47883,10 +47917,10 @@
       <c r="A105" s="10"/>
       <c r="B105" s="10"/>
       <c r="E105" s="23" t="s">
-        <v>4768</v>
+        <v>4774</v>
       </c>
       <c r="F105" s="25" t="s">
-        <v>4769</v>
+        <v>4775</v>
       </c>
       <c r="G105" s="10"/>
       <c r="H105" s="10"/>
@@ -47906,10 +47940,10 @@
       <c r="A106" s="10"/>
       <c r="B106" s="10"/>
       <c r="E106" s="23" t="s">
-        <v>4770</v>
+        <v>4776</v>
       </c>
       <c r="F106" s="25" t="s">
-        <v>4771</v>
+        <v>4777</v>
       </c>
       <c r="G106" s="10"/>
       <c r="H106" s="10"/>
@@ -47967,19 +48001,19 @@
     </row>
     <row r="109" ht="18.75" customHeight="1">
       <c r="A109" s="18" t="s">
-        <v>4772</v>
+        <v>4778</v>
       </c>
       <c r="B109" s="19"/>
       <c r="C109" s="18" t="s">
-        <v>4773</v>
+        <v>4779</v>
       </c>
       <c r="D109" s="19"/>
       <c r="E109" s="18" t="s">
-        <v>4774</v>
+        <v>4780</v>
       </c>
       <c r="F109" s="19"/>
       <c r="G109" s="18" t="s">
-        <v>4775</v>
+        <v>4781</v>
       </c>
       <c r="H109" s="19"/>
       <c r="I109" s="10"/>
@@ -47996,19 +48030,19 @@
     </row>
     <row r="110" ht="18.75" customHeight="1">
       <c r="A110" s="23" t="s">
-        <v>4776</v>
+        <v>4782</v>
       </c>
       <c r="B110" s="22"/>
       <c r="C110" s="23" t="s">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D110" s="22"/>
       <c r="E110" s="23" t="s">
-        <v>4778</v>
+        <v>4784</v>
       </c>
       <c r="F110" s="22"/>
       <c r="G110" s="23" t="s">
-        <v>4779</v>
+        <v>4785</v>
       </c>
       <c r="H110" s="22"/>
       <c r="I110" s="10"/>
@@ -48025,19 +48059,19 @@
     </row>
     <row r="111" ht="18.75" customHeight="1">
       <c r="A111" s="23" t="s">
-        <v>4780</v>
+        <v>4786</v>
       </c>
       <c r="B111" s="22"/>
       <c r="C111" s="23" t="s">
-        <v>4781</v>
+        <v>4787</v>
       </c>
       <c r="D111" s="22"/>
       <c r="E111" s="23" t="s">
-        <v>4782</v>
+        <v>4788</v>
       </c>
       <c r="F111" s="22"/>
       <c r="G111" s="23" t="s">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="H111" s="22"/>
       <c r="I111" s="10"/>
@@ -48054,19 +48088,19 @@
     </row>
     <row r="112" ht="18.75" customHeight="1">
       <c r="A112" s="23" t="s">
-        <v>4784</v>
+        <v>4790</v>
       </c>
       <c r="B112" s="22"/>
       <c r="C112" s="23" t="s">
-        <v>4785</v>
+        <v>4791</v>
       </c>
       <c r="D112" s="22"/>
       <c r="E112" s="23" t="s">
-        <v>4786</v>
+        <v>4792</v>
       </c>
       <c r="F112" s="22"/>
       <c r="G112" s="23" t="s">
-        <v>4787</v>
+        <v>4793</v>
       </c>
       <c r="H112" s="22"/>
       <c r="I112" s="10"/>
@@ -48120,28 +48154,28 @@
     </row>
     <row r="114" ht="18.75" customHeight="1">
       <c r="A114" s="23" t="s">
-        <v>4788</v>
+        <v>4794</v>
       </c>
       <c r="B114" s="25" t="s">
         <v>4043</v>
       </c>
       <c r="C114" s="23" t="s">
-        <v>4789</v>
+        <v>4795</v>
       </c>
       <c r="D114" s="25" t="s">
-        <v>4790</v>
+        <v>4796</v>
       </c>
       <c r="E114" s="23" t="s">
-        <v>4791</v>
+        <v>4797</v>
       </c>
       <c r="F114" s="25" t="s">
-        <v>4792</v>
+        <v>4798</v>
       </c>
       <c r="G114" s="23" t="s">
-        <v>4793</v>
+        <v>4799</v>
       </c>
       <c r="H114" s="25" t="s">
-        <v>4794</v>
+        <v>4800</v>
       </c>
       <c r="I114" s="10"/>
       <c r="J114" s="10"/>
@@ -48157,28 +48191,28 @@
     </row>
     <row r="115" ht="18.75" customHeight="1">
       <c r="A115" s="23" t="s">
-        <v>4795</v>
+        <v>4801</v>
       </c>
       <c r="B115" s="25" t="s">
-        <v>4796</v>
+        <v>4802</v>
       </c>
       <c r="C115" s="23" t="s">
-        <v>4797</v>
+        <v>4803</v>
       </c>
       <c r="D115" s="25" t="s">
-        <v>4798</v>
+        <v>4804</v>
       </c>
       <c r="E115" s="23" t="s">
-        <v>4799</v>
+        <v>4805</v>
       </c>
       <c r="F115" s="25" t="s">
-        <v>4800</v>
+        <v>4806</v>
       </c>
       <c r="G115" s="23" t="s">
-        <v>4801</v>
+        <v>4807</v>
       </c>
       <c r="H115" s="25" t="s">
-        <v>4802</v>
+        <v>4808</v>
       </c>
       <c r="I115" s="10"/>
       <c r="J115" s="10"/>
@@ -48194,28 +48228,28 @@
     </row>
     <row r="116" ht="18.75" customHeight="1">
       <c r="A116" s="23" t="s">
-        <v>4795</v>
+        <v>4801</v>
       </c>
       <c r="B116" s="25" t="s">
         <v>4043</v>
       </c>
       <c r="C116" s="23" t="s">
-        <v>4797</v>
+        <v>4803</v>
       </c>
       <c r="D116" s="25" t="s">
-        <v>4790</v>
+        <v>4796</v>
       </c>
       <c r="E116" s="23" t="s">
-        <v>4799</v>
+        <v>4805</v>
       </c>
       <c r="F116" s="25" t="s">
-        <v>4792</v>
+        <v>4798</v>
       </c>
       <c r="G116" s="23" t="s">
-        <v>4801</v>
+        <v>4807</v>
       </c>
       <c r="H116" s="25" t="s">
-        <v>4803</v>
+        <v>4809</v>
       </c>
       <c r="I116" s="10"/>
       <c r="J116" s="10"/>
@@ -48231,28 +48265,28 @@
     </row>
     <row r="117" ht="18.75" customHeight="1">
       <c r="A117" s="23" t="s">
-        <v>4804</v>
+        <v>4810</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>4805</v>
+        <v>4811</v>
       </c>
       <c r="C117" s="23" t="s">
-        <v>4806</v>
+        <v>4812</v>
       </c>
       <c r="D117" s="25" t="s">
-        <v>4807</v>
+        <v>4813</v>
       </c>
       <c r="E117" s="23" t="s">
-        <v>4808</v>
+        <v>4814</v>
       </c>
       <c r="F117" s="25" t="s">
-        <v>4809</v>
+        <v>4815</v>
       </c>
       <c r="G117" s="23" t="s">
-        <v>4810</v>
+        <v>4816</v>
       </c>
       <c r="H117" s="25" t="s">
-        <v>4811</v>
+        <v>4817</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="10"/>
@@ -48268,28 +48302,28 @@
     </row>
     <row r="118" ht="18.75" customHeight="1">
       <c r="A118" s="23" t="s">
-        <v>4812</v>
+        <v>4818</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>4813</v>
+        <v>4819</v>
       </c>
       <c r="C118" s="23" t="s">
-        <v>4814</v>
+        <v>4820</v>
       </c>
       <c r="D118" s="25" t="s">
-        <v>4815</v>
+        <v>4821</v>
       </c>
       <c r="E118" s="23" t="s">
-        <v>4816</v>
+        <v>4822</v>
       </c>
       <c r="F118" s="25" t="s">
-        <v>4817</v>
+        <v>4823</v>
       </c>
       <c r="G118" s="23" t="s">
-        <v>4818</v>
+        <v>4824</v>
       </c>
       <c r="H118" s="25" t="s">
-        <v>4819</v>
+        <v>4825</v>
       </c>
       <c r="I118" s="10"/>
       <c r="J118" s="10"/>
@@ -48305,28 +48339,28 @@
     </row>
     <row r="119" ht="18.75" customHeight="1">
       <c r="A119" s="36" t="s">
-        <v>4820</v>
+        <v>4826</v>
       </c>
       <c r="B119" s="28" t="s">
-        <v>4821</v>
+        <v>4827</v>
       </c>
       <c r="C119" s="36" t="s">
-        <v>4822</v>
+        <v>4828</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>4823</v>
+        <v>4829</v>
       </c>
       <c r="E119" s="36" t="s">
-        <v>4824</v>
+        <v>4830</v>
       </c>
       <c r="F119" s="28" t="s">
-        <v>4825</v>
+        <v>4831</v>
       </c>
       <c r="G119" s="36" t="s">
-        <v>4826</v>
+        <v>4832</v>
       </c>
       <c r="H119" s="28" t="s">
-        <v>4827</v>
+        <v>4833</v>
       </c>
       <c r="I119" s="10"/>
       <c r="J119" s="10"/>
@@ -48363,34 +48397,34 @@
     </row>
     <row r="121" ht="18.75" customHeight="1">
       <c r="A121" s="18" t="s">
-        <v>4828</v>
+        <v>4834</v>
       </c>
       <c r="B121" s="19"/>
       <c r="C121" s="18" t="s">
-        <v>4829</v>
+        <v>4835</v>
       </c>
       <c r="D121" s="19"/>
       <c r="E121" s="18" t="s">
-        <v>4830</v>
+        <v>4836</v>
       </c>
       <c r="F121" s="19"/>
       <c r="G121" s="18" t="s">
-        <v>4831</v>
+        <v>4837</v>
       </c>
       <c r="H121" s="19"/>
       <c r="I121" s="18" t="s">
-        <v>4832</v>
+        <v>4838</v>
       </c>
       <c r="J121" s="19"/>
       <c r="K121" s="18" t="s">
-        <v>4833</v>
+        <v>4839</v>
       </c>
       <c r="L121" s="19"/>
       <c r="M121" s="10"/>
       <c r="N121" s="10"/>
       <c r="O121" s="10"/>
       <c r="P121" s="8" t="s">
-        <v>4834</v>
+        <v>4840</v>
       </c>
     </row>
     <row r="122" ht="18.75" customHeight="1">
@@ -48399,23 +48433,23 @@
       </c>
       <c r="B122" s="22"/>
       <c r="C122" s="23" t="s">
-        <v>4835</v>
+        <v>4841</v>
       </c>
       <c r="D122" s="22"/>
       <c r="E122" s="23" t="s">
-        <v>4836</v>
+        <v>4842</v>
       </c>
       <c r="F122" s="22"/>
       <c r="G122" s="23" t="s">
-        <v>4837</v>
+        <v>4843</v>
       </c>
       <c r="H122" s="22"/>
       <c r="I122" s="23" t="s">
-        <v>4838</v>
+        <v>4844</v>
       </c>
       <c r="J122" s="22"/>
       <c r="K122" s="23" t="s">
-        <v>4839</v>
+        <v>4845</v>
       </c>
       <c r="L122" s="22"/>
       <c r="M122" s="10"/>
@@ -48425,7 +48459,7 @@
         <v>4313</v>
       </c>
       <c r="Q122" s="10" t="s">
-        <v>4840</v>
+        <v>4846</v>
       </c>
     </row>
     <row r="123" ht="18.75" customHeight="1">
@@ -48434,23 +48468,23 @@
       </c>
       <c r="B123" s="22"/>
       <c r="C123" s="23" t="s">
-        <v>4841</v>
+        <v>4847</v>
       </c>
       <c r="D123" s="22"/>
       <c r="E123" s="23" t="s">
-        <v>4842</v>
+        <v>4848</v>
       </c>
       <c r="F123" s="22"/>
       <c r="G123" s="23" t="s">
-        <v>4843</v>
+        <v>4849</v>
       </c>
       <c r="H123" s="22"/>
       <c r="I123" s="23" t="s">
-        <v>4844</v>
+        <v>4850</v>
       </c>
       <c r="J123" s="22"/>
       <c r="K123" s="23" t="s">
-        <v>4845</v>
+        <v>4851</v>
       </c>
       <c r="L123" s="22"/>
       <c r="M123" s="10"/>
@@ -48460,7 +48494,7 @@
         <v>4319</v>
       </c>
       <c r="Q123" s="10" t="s">
-        <v>4846</v>
+        <v>4852</v>
       </c>
     </row>
     <row r="124" ht="18.75" customHeight="1">
@@ -48469,23 +48503,23 @@
       </c>
       <c r="B124" s="22"/>
       <c r="C124" s="23" t="s">
-        <v>4847</v>
+        <v>4853</v>
       </c>
       <c r="D124" s="22"/>
       <c r="E124" s="23" t="s">
-        <v>4848</v>
+        <v>4854</v>
       </c>
       <c r="F124" s="22"/>
       <c r="G124" s="23" t="s">
-        <v>4849</v>
+        <v>4855</v>
       </c>
       <c r="H124" s="22"/>
       <c r="I124" s="23" t="s">
-        <v>4850</v>
+        <v>4856</v>
       </c>
       <c r="J124" s="22"/>
       <c r="K124" s="23" t="s">
-        <v>4851</v>
+        <v>4857</v>
       </c>
       <c r="L124" s="22"/>
       <c r="M124" s="10"/>
@@ -48495,7 +48529,7 @@
         <v>4325</v>
       </c>
       <c r="Q124" s="10" t="s">
-        <v>4852</v>
+        <v>4858</v>
       </c>
     </row>
     <row r="125" ht="18.75" customHeight="1">
@@ -48556,28 +48590,28 @@
         <v>781</v>
       </c>
       <c r="D126" s="25" t="s">
-        <v>4853</v>
+        <v>4859</v>
       </c>
       <c r="E126" s="23" t="s">
-        <v>4854</v>
+        <v>4860</v>
       </c>
       <c r="F126" s="25" t="s">
-        <v>4855</v>
+        <v>4861</v>
       </c>
       <c r="G126" s="23" t="s">
-        <v>4856</v>
+        <v>4862</v>
       </c>
       <c r="H126" s="25" t="s">
-        <v>4857</v>
+        <v>4863</v>
       </c>
       <c r="I126" s="23" t="s">
-        <v>4858</v>
+        <v>4864</v>
       </c>
       <c r="J126" s="25" t="s">
-        <v>4859</v>
+        <v>4865</v>
       </c>
       <c r="K126" s="23" t="s">
-        <v>4860</v>
+        <v>4866</v>
       </c>
       <c r="L126" s="25" t="s">
         <v>3352</v>
@@ -48592,10 +48626,10 @@
         <v>644</v>
       </c>
       <c r="R126" s="10" t="s">
-        <v>4861</v>
+        <v>4867</v>
       </c>
       <c r="S126" s="10" t="s">
-        <v>4862</v>
+        <v>4868</v>
       </c>
     </row>
     <row r="127" ht="18.75" customHeight="1">
@@ -48604,34 +48638,34 @@
         <v>3648</v>
       </c>
       <c r="C127" s="23" t="s">
-        <v>4863</v>
+        <v>4869</v>
       </c>
       <c r="D127" s="25" t="s">
-        <v>4864</v>
+        <v>4870</v>
       </c>
       <c r="E127" s="23" t="s">
-        <v>4865</v>
+        <v>4871</v>
       </c>
       <c r="F127" s="25" t="s">
-        <v>4866</v>
+        <v>4872</v>
       </c>
       <c r="G127" s="23" t="s">
         <v>3408</v>
       </c>
       <c r="H127" s="25" t="s">
-        <v>4867</v>
+        <v>4873</v>
       </c>
       <c r="I127" s="23" t="s">
-        <v>4868</v>
+        <v>4874</v>
       </c>
       <c r="J127" s="25" t="s">
-        <v>4869</v>
+        <v>4875</v>
       </c>
       <c r="K127" s="23" t="s">
-        <v>4870</v>
+        <v>4876</v>
       </c>
       <c r="L127" s="25" t="s">
-        <v>4871</v>
+        <v>4877</v>
       </c>
       <c r="M127" s="10"/>
       <c r="N127" s="10"/>
@@ -48640,10 +48674,10 @@
         <v>3648</v>
       </c>
       <c r="R127" s="10" t="s">
-        <v>4872</v>
+        <v>4878</v>
       </c>
       <c r="S127" s="10" t="s">
-        <v>4873</v>
+        <v>4879</v>
       </c>
     </row>
     <row r="128" ht="18.75" customHeight="1">
@@ -48652,31 +48686,31 @@
         <v>4348</v>
       </c>
       <c r="C128" s="23" t="s">
-        <v>4863</v>
+        <v>4869</v>
       </c>
       <c r="D128" s="25" t="s">
-        <v>4853</v>
+        <v>4859</v>
       </c>
       <c r="E128" s="23" t="s">
-        <v>4865</v>
+        <v>4871</v>
       </c>
       <c r="F128" s="25" t="s">
-        <v>4855</v>
+        <v>4861</v>
       </c>
       <c r="G128" s="23" t="s">
         <v>3408</v>
       </c>
       <c r="H128" s="25" t="s">
-        <v>4857</v>
+        <v>4863</v>
       </c>
       <c r="I128" s="23" t="s">
-        <v>4868</v>
+        <v>4874</v>
       </c>
       <c r="J128" s="25" t="s">
-        <v>4859</v>
+        <v>4865</v>
       </c>
       <c r="K128" s="23" t="s">
-        <v>4870</v>
+        <v>4876</v>
       </c>
       <c r="L128" s="25" t="s">
         <v>3352</v>
@@ -48688,10 +48722,10 @@
         <v>4348</v>
       </c>
       <c r="R128" s="10" t="s">
-        <v>4872</v>
+        <v>4878</v>
       </c>
       <c r="S128" s="10" t="s">
-        <v>4862</v>
+        <v>4868</v>
       </c>
     </row>
     <row r="129" ht="18.75" customHeight="1">
@@ -48702,34 +48736,34 @@
         <v>3488</v>
       </c>
       <c r="C129" s="23" t="s">
-        <v>4874</v>
+        <v>4880</v>
       </c>
       <c r="D129" s="25" t="s">
-        <v>4875</v>
+        <v>4881</v>
       </c>
       <c r="E129" s="23" t="s">
-        <v>4876</v>
+        <v>4882</v>
       </c>
       <c r="F129" s="25" t="s">
-        <v>4877</v>
+        <v>4883</v>
       </c>
       <c r="G129" s="23" t="s">
-        <v>4878</v>
+        <v>4884</v>
       </c>
       <c r="H129" s="25" t="s">
-        <v>4879</v>
+        <v>4885</v>
       </c>
       <c r="I129" s="23" t="s">
-        <v>4880</v>
+        <v>4886</v>
       </c>
       <c r="J129" s="25" t="s">
-        <v>4881</v>
+        <v>4887</v>
       </c>
       <c r="K129" s="23" t="s">
-        <v>4882</v>
+        <v>4888</v>
       </c>
       <c r="L129" s="25" t="s">
-        <v>4883</v>
+        <v>4889</v>
       </c>
       <c r="M129" s="10"/>
       <c r="N129" s="10"/>
@@ -48741,10 +48775,10 @@
         <v>3488</v>
       </c>
       <c r="R129" s="10" t="s">
-        <v>4884</v>
+        <v>4890</v>
       </c>
       <c r="S129" s="10" t="s">
-        <v>4885</v>
+        <v>4891</v>
       </c>
     </row>
     <row r="130" ht="18.75" customHeight="1">
@@ -48752,34 +48786,34 @@
         <v>3604</v>
       </c>
       <c r="C130" s="23" t="s">
-        <v>4886</v>
+        <v>4892</v>
       </c>
       <c r="D130" s="25" t="s">
-        <v>4887</v>
+        <v>4893</v>
       </c>
       <c r="E130" s="23" t="s">
-        <v>4888</v>
+        <v>4894</v>
       </c>
       <c r="F130" s="25" t="s">
-        <v>4889</v>
+        <v>4895</v>
       </c>
       <c r="G130" s="23" t="s">
-        <v>4890</v>
+        <v>4896</v>
       </c>
       <c r="H130" s="25" t="s">
-        <v>4891</v>
+        <v>4897</v>
       </c>
       <c r="I130" s="23" t="s">
-        <v>4892</v>
+        <v>4898</v>
       </c>
       <c r="J130" s="25" t="s">
-        <v>4893</v>
+        <v>4899</v>
       </c>
       <c r="K130" s="23" t="s">
-        <v>4894</v>
+        <v>4900</v>
       </c>
       <c r="L130" s="25" t="s">
-        <v>4895</v>
+        <v>4901</v>
       </c>
       <c r="M130" s="10"/>
       <c r="N130" s="10"/>
@@ -48788,10 +48822,10 @@
         <v>3604</v>
       </c>
       <c r="R130" s="10" t="s">
-        <v>4896</v>
+        <v>4902</v>
       </c>
       <c r="S130" s="10" t="s">
-        <v>4897</v>
+        <v>4903</v>
       </c>
     </row>
     <row r="131" ht="18.75" customHeight="1">
@@ -48799,34 +48833,34 @@
         <v>4373</v>
       </c>
       <c r="C131" s="23" t="s">
-        <v>4898</v>
+        <v>4904</v>
       </c>
       <c r="D131" s="25" t="s">
-        <v>4899</v>
+        <v>4905</v>
       </c>
       <c r="E131" s="23" t="s">
-        <v>4900</v>
+        <v>4906</v>
       </c>
       <c r="F131" s="25" t="s">
-        <v>4901</v>
+        <v>4907</v>
       </c>
       <c r="G131" s="23" t="s">
-        <v>4902</v>
+        <v>4908</v>
       </c>
       <c r="H131" s="25" t="s">
-        <v>4903</v>
+        <v>4909</v>
       </c>
       <c r="I131" s="23" t="s">
-        <v>4904</v>
+        <v>4910</v>
       </c>
       <c r="J131" s="25" t="s">
-        <v>4905</v>
+        <v>4911</v>
       </c>
       <c r="K131" s="36" t="s">
-        <v>4906</v>
+        <v>4912</v>
       </c>
       <c r="L131" s="28" t="s">
-        <v>4907</v>
+        <v>4913</v>
       </c>
       <c r="M131" s="10"/>
       <c r="N131" s="10"/>
@@ -48835,10 +48869,10 @@
         <v>4373</v>
       </c>
       <c r="R131" s="10" t="s">
-        <v>4908</v>
+        <v>4914</v>
       </c>
       <c r="S131" s="10" t="s">
-        <v>4909</v>
+        <v>4915</v>
       </c>
     </row>
     <row r="132" ht="18.75" customHeight="1">
@@ -48888,28 +48922,28 @@
         <v>644</v>
       </c>
       <c r="C133" s="23" t="s">
-        <v>4910</v>
+        <v>4916</v>
       </c>
       <c r="D133" s="25" t="s">
-        <v>4911</v>
+        <v>4917</v>
       </c>
       <c r="E133" s="23" t="s">
-        <v>4912</v>
+        <v>4918</v>
       </c>
       <c r="F133" s="25" t="s">
-        <v>4913</v>
+        <v>4919</v>
       </c>
       <c r="G133" s="23" t="s">
-        <v>4914</v>
+        <v>4920</v>
       </c>
       <c r="H133" s="25" t="s">
-        <v>4915</v>
+        <v>4921</v>
       </c>
       <c r="I133" s="23" t="s">
-        <v>4916</v>
+        <v>4922</v>
       </c>
       <c r="J133" s="25" t="s">
-        <v>4917</v>
+        <v>4923</v>
       </c>
       <c r="K133" s="23"/>
       <c r="L133" s="10"/>
@@ -48975,28 +49009,28 @@
         <v>3488</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>4918</v>
+        <v>4924</v>
       </c>
       <c r="D136" s="25" t="s">
-        <v>4919</v>
+        <v>4925</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>4920</v>
+        <v>4926</v>
       </c>
       <c r="F136" s="25" t="s">
-        <v>4921</v>
+        <v>4927</v>
       </c>
       <c r="G136" s="10" t="s">
-        <v>4922</v>
+        <v>4928</v>
       </c>
       <c r="H136" s="25" t="s">
-        <v>4923</v>
+        <v>4929</v>
       </c>
       <c r="I136" s="10" t="s">
-        <v>4924</v>
+        <v>4930</v>
       </c>
       <c r="J136" s="25" t="s">
-        <v>4925</v>
+        <v>4931</v>
       </c>
       <c r="K136" s="23"/>
       <c r="L136" s="10"/>
@@ -49014,28 +49048,28 @@
         <v>3604</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>4926</v>
+        <v>4932</v>
       </c>
       <c r="D137" s="25" t="s">
-        <v>4927</v>
+        <v>4933</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>4928</v>
+        <v>4934</v>
       </c>
       <c r="F137" s="25" t="s">
-        <v>4929</v>
+        <v>4935</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>4930</v>
+        <v>4936</v>
       </c>
       <c r="H137" s="25" t="s">
-        <v>4931</v>
+        <v>4937</v>
       </c>
       <c r="I137" s="10" t="s">
-        <v>4932</v>
+        <v>4938</v>
       </c>
       <c r="J137" s="25" t="s">
-        <v>4933</v>
+        <v>4939</v>
       </c>
       <c r="K137" s="23"/>
       <c r="L137" s="10"/>
@@ -49095,15 +49129,15 @@
       <c r="A140" s="10"/>
       <c r="B140" s="10"/>
       <c r="C140" s="18" t="s">
-        <v>4934</v>
+        <v>4940</v>
       </c>
       <c r="D140" s="19"/>
       <c r="E140" s="18" t="s">
-        <v>4935</v>
+        <v>4941</v>
       </c>
       <c r="F140" s="19"/>
       <c r="G140" s="18" t="s">
-        <v>4936</v>
+        <v>4942</v>
       </c>
       <c r="H140" s="19"/>
       <c r="I140" s="10"/>
@@ -49122,15 +49156,15 @@
       <c r="A141" s="10"/>
       <c r="B141" s="10"/>
       <c r="C141" s="23" t="s">
-        <v>4937</v>
+        <v>4943</v>
       </c>
       <c r="D141" s="22"/>
       <c r="E141" s="23" t="s">
-        <v>4938</v>
+        <v>4944</v>
       </c>
       <c r="F141" s="22"/>
       <c r="G141" s="23" t="s">
-        <v>4939</v>
+        <v>4945</v>
       </c>
       <c r="H141" s="22"/>
       <c r="I141" s="10"/>
@@ -49149,15 +49183,15 @@
       <c r="A142" s="10"/>
       <c r="B142" s="10"/>
       <c r="C142" s="23" t="s">
-        <v>4940</v>
+        <v>4946</v>
       </c>
       <c r="D142" s="22"/>
       <c r="E142" s="23" t="s">
-        <v>4941</v>
+        <v>4947</v>
       </c>
       <c r="F142" s="22"/>
       <c r="G142" s="23" t="s">
-        <v>4942</v>
+        <v>4948</v>
       </c>
       <c r="H142" s="22"/>
       <c r="I142" s="10"/>
@@ -49176,11 +49210,11 @@
       <c r="A143" s="10"/>
       <c r="B143" s="10"/>
       <c r="C143" s="23" t="s">
-        <v>4943</v>
+        <v>4949</v>
       </c>
       <c r="D143" s="22"/>
       <c r="E143" s="23" t="s">
-        <v>4944</v>
+        <v>4950</v>
       </c>
       <c r="F143" s="22"/>
       <c r="G143" s="23" t="s">
@@ -49236,22 +49270,22 @@
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="23" t="s">
-        <v>4945</v>
+        <v>4951</v>
       </c>
       <c r="D145" s="25" t="s">
-        <v>4946</v>
+        <v>4952</v>
       </c>
       <c r="E145" s="23" t="s">
-        <v>4947</v>
+        <v>4953</v>
       </c>
       <c r="F145" s="25" t="s">
-        <v>4948</v>
+        <v>4954</v>
       </c>
       <c r="G145" s="23" t="s">
-        <v>4949</v>
+        <v>4955</v>
       </c>
       <c r="H145" s="25" t="s">
-        <v>4950</v>
+        <v>4956</v>
       </c>
       <c r="I145" s="10"/>
       <c r="J145" s="10"/>
@@ -49269,22 +49303,22 @@
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
       <c r="C146" s="23" t="s">
-        <v>4951</v>
+        <v>4957</v>
       </c>
       <c r="D146" s="25" t="s">
-        <v>4952</v>
+        <v>4958</v>
       </c>
       <c r="E146" s="23" t="s">
-        <v>4953</v>
+        <v>4959</v>
       </c>
       <c r="F146" s="25" t="s">
-        <v>4954</v>
+        <v>4960</v>
       </c>
       <c r="G146" s="23" t="s">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="H146" s="25" t="s">
-        <v>4956</v>
+        <v>4962</v>
       </c>
       <c r="I146" s="10"/>
       <c r="J146" s="10"/>
@@ -49302,22 +49336,22 @@
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
       <c r="C147" s="23" t="s">
-        <v>4951</v>
+        <v>4957</v>
       </c>
       <c r="D147" s="25" t="s">
-        <v>4946</v>
+        <v>4952</v>
       </c>
       <c r="E147" s="23" t="s">
-        <v>4953</v>
+        <v>4959</v>
       </c>
       <c r="F147" s="25" t="s">
-        <v>4948</v>
+        <v>4954</v>
       </c>
       <c r="G147" s="23" t="s">
-        <v>4955</v>
+        <v>4961</v>
       </c>
       <c r="H147" s="25" t="s">
-        <v>4950</v>
+        <v>4956</v>
       </c>
       <c r="I147" s="10"/>
       <c r="J147" s="10"/>
@@ -49335,22 +49369,22 @@
       <c r="A148" s="10"/>
       <c r="B148" s="10"/>
       <c r="C148" s="23" t="s">
-        <v>4957</v>
+        <v>4963</v>
       </c>
       <c r="D148" s="25" t="s">
-        <v>4958</v>
+        <v>4964</v>
       </c>
       <c r="E148" s="23" t="s">
-        <v>4959</v>
+        <v>4965</v>
       </c>
       <c r="F148" s="25" t="s">
-        <v>4960</v>
+        <v>4966</v>
       </c>
       <c r="G148" s="23" t="s">
-        <v>4961</v>
+        <v>4967</v>
       </c>
       <c r="H148" s="25" t="s">
-        <v>4962</v>
+        <v>4968</v>
       </c>
       <c r="I148" s="10"/>
       <c r="J148" s="10"/>
@@ -49368,22 +49402,22 @@
       <c r="A149" s="10"/>
       <c r="B149" s="10"/>
       <c r="C149" s="23" t="s">
-        <v>4963</v>
+        <v>4969</v>
       </c>
       <c r="D149" s="25" t="s">
-        <v>4964</v>
+        <v>4970</v>
       </c>
       <c r="E149" s="23" t="s">
-        <v>4965</v>
+        <v>4971</v>
       </c>
       <c r="F149" s="25" t="s">
-        <v>4966</v>
+        <v>4972</v>
       </c>
       <c r="G149" s="23" t="s">
-        <v>4967</v>
+        <v>4973</v>
       </c>
       <c r="H149" s="25" t="s">
-        <v>4968</v>
+        <v>4974</v>
       </c>
       <c r="I149" s="10"/>
       <c r="J149" s="10"/>
@@ -49401,22 +49435,22 @@
       <c r="A150" s="10"/>
       <c r="B150" s="10"/>
       <c r="C150" s="36" t="s">
-        <v>4969</v>
+        <v>4975</v>
       </c>
       <c r="D150" s="28" t="s">
-        <v>4970</v>
+        <v>4976</v>
       </c>
       <c r="E150" s="36" t="s">
-        <v>4971</v>
+        <v>4977</v>
       </c>
       <c r="F150" s="28" t="s">
-        <v>4972</v>
+        <v>4978</v>
       </c>
       <c r="G150" s="36" t="s">
-        <v>4973</v>
+        <v>4979</v>
       </c>
       <c r="H150" s="28" t="s">
-        <v>4974</v>
+        <v>4980</v>
       </c>
       <c r="I150" s="10"/>
       <c r="J150" s="10"/>
@@ -49453,19 +49487,19 @@
     </row>
     <row r="152" ht="18.75" customHeight="1">
       <c r="A152" s="18" t="s">
-        <v>4975</v>
+        <v>4981</v>
       </c>
       <c r="B152" s="19"/>
       <c r="C152" s="18" t="s">
-        <v>4976</v>
+        <v>4982</v>
       </c>
       <c r="D152" s="19"/>
       <c r="E152" s="18" t="s">
-        <v>4977</v>
+        <v>4983</v>
       </c>
       <c r="F152" s="19"/>
       <c r="G152" s="18" t="s">
-        <v>4978</v>
+        <v>4984</v>
       </c>
       <c r="H152" s="19"/>
       <c r="J152" s="10"/>
@@ -49485,15 +49519,15 @@
       </c>
       <c r="B153" s="22"/>
       <c r="C153" s="23" t="s">
-        <v>4979</v>
+        <v>4985</v>
       </c>
       <c r="D153" s="22"/>
       <c r="E153" s="23" t="s">
-        <v>4980</v>
+        <v>4986</v>
       </c>
       <c r="F153" s="22"/>
       <c r="G153" s="23" t="s">
-        <v>4981</v>
+        <v>4987</v>
       </c>
       <c r="H153" s="22"/>
       <c r="J153" s="10"/>
@@ -49513,15 +49547,15 @@
       </c>
       <c r="B154" s="22"/>
       <c r="C154" s="23" t="s">
-        <v>4982</v>
+        <v>4988</v>
       </c>
       <c r="D154" s="22"/>
       <c r="E154" s="23" t="s">
-        <v>4983</v>
+        <v>4989</v>
       </c>
       <c r="F154" s="22"/>
       <c r="G154" s="23" t="s">
-        <v>4984</v>
+        <v>4990</v>
       </c>
       <c r="H154" s="22"/>
       <c r="J154" s="10"/>
@@ -49541,15 +49575,15 @@
       </c>
       <c r="B155" s="22"/>
       <c r="C155" s="23" t="s">
-        <v>4985</v>
+        <v>4991</v>
       </c>
       <c r="D155" s="22"/>
       <c r="E155" s="23" t="s">
-        <v>4986</v>
+        <v>4992</v>
       </c>
       <c r="F155" s="22"/>
       <c r="G155" s="23" t="s">
-        <v>4987</v>
+        <v>4993</v>
       </c>
       <c r="H155" s="22"/>
       <c r="J155" s="10"/>
@@ -49605,22 +49639,22 @@
         <v>644</v>
       </c>
       <c r="C157" s="23" t="s">
-        <v>4988</v>
+        <v>4994</v>
       </c>
       <c r="D157" s="25" t="s">
-        <v>4989</v>
+        <v>4995</v>
       </c>
       <c r="E157" s="23" t="s">
-        <v>4990</v>
+        <v>4996</v>
       </c>
       <c r="F157" s="25" t="s">
-        <v>4991</v>
+        <v>4997</v>
       </c>
       <c r="G157" s="23" t="s">
-        <v>4992</v>
+        <v>4998</v>
       </c>
       <c r="H157" s="25" t="s">
-        <v>4993</v>
+        <v>4999</v>
       </c>
       <c r="J157" s="10"/>
       <c r="K157" s="10"/>
@@ -49639,22 +49673,22 @@
         <v>3648</v>
       </c>
       <c r="C158" s="23" t="s">
-        <v>4994</v>
+        <v>5000</v>
       </c>
       <c r="D158" s="25" t="s">
-        <v>4995</v>
+        <v>5001</v>
       </c>
       <c r="E158" s="23" t="s">
-        <v>4996</v>
+        <v>5002</v>
       </c>
       <c r="F158" s="25" t="s">
-        <v>4997</v>
+        <v>5003</v>
       </c>
       <c r="G158" s="23" t="s">
-        <v>4998</v>
+        <v>5004</v>
       </c>
       <c r="H158" s="25" t="s">
-        <v>4999</v>
+        <v>5005</v>
       </c>
       <c r="J158" s="10"/>
       <c r="K158" s="10"/>
@@ -49673,22 +49707,22 @@
         <v>4348</v>
       </c>
       <c r="C159" s="23" t="s">
-        <v>4994</v>
+        <v>5000</v>
       </c>
       <c r="D159" s="25" t="s">
-        <v>4989</v>
+        <v>4995</v>
       </c>
       <c r="E159" s="23" t="s">
-        <v>4996</v>
+        <v>5002</v>
       </c>
       <c r="F159" s="25" t="s">
-        <v>4991</v>
+        <v>4997</v>
       </c>
       <c r="G159" s="23" t="s">
-        <v>4998</v>
+        <v>5004</v>
       </c>
       <c r="H159" s="25" t="s">
-        <v>4993</v>
+        <v>4999</v>
       </c>
       <c r="J159" s="10"/>
       <c r="K159" s="10"/>
@@ -49709,22 +49743,22 @@
         <v>3488</v>
       </c>
       <c r="C160" s="23" t="s">
-        <v>5000</v>
+        <v>5006</v>
       </c>
       <c r="D160" s="25" t="s">
-        <v>5001</v>
+        <v>5007</v>
       </c>
       <c r="E160" s="23" t="s">
-        <v>5002</v>
+        <v>5008</v>
       </c>
       <c r="F160" s="25" t="s">
-        <v>5003</v>
+        <v>5009</v>
       </c>
       <c r="G160" s="23" t="s">
-        <v>5004</v>
+        <v>5010</v>
       </c>
       <c r="H160" s="25" t="s">
-        <v>5005</v>
+        <v>5011</v>
       </c>
       <c r="J160" s="10"/>
       <c r="K160" s="10"/>
@@ -49742,22 +49776,22 @@
         <v>3604</v>
       </c>
       <c r="C161" s="23" t="s">
-        <v>5006</v>
+        <v>5012</v>
       </c>
       <c r="D161" s="25" t="s">
-        <v>5007</v>
+        <v>5013</v>
       </c>
       <c r="E161" s="23" t="s">
-        <v>5008</v>
+        <v>5014</v>
       </c>
       <c r="F161" s="25" t="s">
-        <v>5009</v>
+        <v>5015</v>
       </c>
       <c r="G161" s="23" t="s">
-        <v>5010</v>
+        <v>5016</v>
       </c>
       <c r="H161" s="25" t="s">
-        <v>5011</v>
+        <v>5017</v>
       </c>
       <c r="J161" s="10"/>
       <c r="K161" s="10"/>
@@ -49775,22 +49809,22 @@
         <v>4373</v>
       </c>
       <c r="C162" s="23" t="s">
-        <v>5012</v>
+        <v>5018</v>
       </c>
       <c r="D162" s="25" t="s">
-        <v>5013</v>
+        <v>5019</v>
       </c>
       <c r="E162" s="23" t="s">
-        <v>5014</v>
+        <v>5020</v>
       </c>
       <c r="F162" s="25" t="s">
-        <v>5015</v>
+        <v>5021</v>
       </c>
       <c r="G162" s="23" t="s">
-        <v>5016</v>
+        <v>5022</v>
       </c>
       <c r="H162" s="25" t="s">
-        <v>5017</v>
+        <v>5023</v>
       </c>
       <c r="J162" s="10"/>
       <c r="K162" s="10"/>
@@ -49838,10 +49872,10 @@
         <v>644</v>
       </c>
       <c r="C164" s="23" t="s">
-        <v>5018</v>
+        <v>5024</v>
       </c>
       <c r="D164" s="25" t="s">
-        <v>5019</v>
+        <v>5025</v>
       </c>
       <c r="E164" s="40"/>
       <c r="F164" s="40"/>
@@ -49913,10 +49947,10 @@
         <v>3488</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>5020</v>
+        <v>5026</v>
       </c>
       <c r="D167" s="25" t="s">
-        <v>5021</v>
+        <v>5027</v>
       </c>
       <c r="E167" s="40"/>
       <c r="F167" s="40"/>
@@ -49940,10 +49974,10 @@
         <v>3604</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>5022</v>
+        <v>5028</v>
       </c>
       <c r="D168" s="25" t="s">
-        <v>5023</v>
+        <v>5029</v>
       </c>
       <c r="E168" s="40"/>
       <c r="F168" s="40"/>
@@ -50007,19 +50041,19 @@
     </row>
     <row r="171" ht="18.75" customHeight="1">
       <c r="A171" s="18" t="s">
-        <v>5024</v>
+        <v>5030</v>
       </c>
       <c r="B171" s="19"/>
       <c r="C171" s="20" t="s">
-        <v>5025</v>
+        <v>5031</v>
       </c>
       <c r="D171" s="19"/>
       <c r="E171" s="20" t="s">
-        <v>5026</v>
+        <v>5032</v>
       </c>
       <c r="F171" s="19"/>
       <c r="G171" s="20" t="s">
-        <v>5027</v>
+        <v>5033</v>
       </c>
       <c r="H171" s="19"/>
       <c r="I171" s="10"/>
@@ -50040,15 +50074,15 @@
       </c>
       <c r="B172" s="22"/>
       <c r="C172" s="10" t="s">
-        <v>5028</v>
+        <v>5034</v>
       </c>
       <c r="D172" s="22"/>
       <c r="E172" s="10" t="s">
-        <v>4840</v>
+        <v>4846</v>
       </c>
       <c r="F172" s="22"/>
       <c r="G172" s="10" t="s">
-        <v>5029</v>
+        <v>5035</v>
       </c>
       <c r="H172" s="22"/>
       <c r="I172" s="10"/>
@@ -50069,15 +50103,15 @@
       </c>
       <c r="B173" s="22"/>
       <c r="C173" s="23" t="s">
-        <v>5030</v>
+        <v>5036</v>
       </c>
       <c r="D173" s="22"/>
       <c r="E173" s="23" t="s">
-        <v>4846</v>
+        <v>4852</v>
       </c>
       <c r="F173" s="22"/>
       <c r="G173" s="23" t="s">
-        <v>5031</v>
+        <v>5037</v>
       </c>
       <c r="H173" s="22"/>
       <c r="I173" s="10"/>
@@ -50098,15 +50132,15 @@
       </c>
       <c r="B174" s="22"/>
       <c r="C174" s="23" t="s">
-        <v>5032</v>
+        <v>5038</v>
       </c>
       <c r="D174" s="22"/>
       <c r="E174" s="23" t="s">
-        <v>4852</v>
+        <v>4858</v>
       </c>
       <c r="F174" s="22"/>
       <c r="G174" s="23" t="s">
-        <v>5033</v>
+        <v>5039</v>
       </c>
       <c r="H174" s="22"/>
       <c r="I174" s="10"/>
@@ -50164,22 +50198,22 @@
         <v>644</v>
       </c>
       <c r="C176" s="23" t="s">
-        <v>5034</v>
+        <v>5040</v>
       </c>
       <c r="D176" s="25" t="s">
-        <v>5035</v>
+        <v>5041</v>
       </c>
       <c r="E176" s="23" t="s">
-        <v>4861</v>
+        <v>4867</v>
       </c>
       <c r="F176" s="25" t="s">
-        <v>4862</v>
+        <v>4868</v>
       </c>
       <c r="G176" s="23" t="s">
-        <v>5036</v>
+        <v>5042</v>
       </c>
       <c r="H176" s="25" t="s">
-        <v>5037</v>
+        <v>5043</v>
       </c>
       <c r="I176" s="10"/>
       <c r="J176" s="10"/>
@@ -50199,22 +50233,22 @@
         <v>3648</v>
       </c>
       <c r="C177" s="23" t="s">
-        <v>5038</v>
+        <v>5044</v>
       </c>
       <c r="D177" s="25" t="s">
-        <v>5039</v>
+        <v>5045</v>
       </c>
       <c r="E177" s="23" t="s">
-        <v>4872</v>
+        <v>4878</v>
       </c>
       <c r="F177" s="25" t="s">
-        <v>4873</v>
+        <v>4879</v>
       </c>
       <c r="G177" s="23" t="s">
-        <v>5040</v>
+        <v>5046</v>
       </c>
       <c r="H177" s="25" t="s">
-        <v>5041</v>
+        <v>5047</v>
       </c>
       <c r="I177" s="10"/>
       <c r="J177" s="10"/>
@@ -50234,22 +50268,22 @@
         <v>4348</v>
       </c>
       <c r="C178" s="23" t="s">
-        <v>5038</v>
+        <v>5044</v>
       </c>
       <c r="D178" s="25" t="s">
-        <v>5035</v>
+        <v>5041</v>
       </c>
       <c r="E178" s="23" t="s">
-        <v>4872</v>
+        <v>4878</v>
       </c>
       <c r="F178" s="25" t="s">
-        <v>4862</v>
+        <v>4868</v>
       </c>
       <c r="G178" s="23" t="s">
-        <v>5040</v>
+        <v>5046</v>
       </c>
       <c r="H178" s="25" t="s">
-        <v>5037</v>
+        <v>5043</v>
       </c>
       <c r="I178" s="10"/>
       <c r="J178" s="10"/>
@@ -50271,22 +50305,22 @@
         <v>3488</v>
       </c>
       <c r="C179" s="23" t="s">
-        <v>5042</v>
+        <v>5048</v>
       </c>
       <c r="D179" s="25" t="s">
-        <v>5043</v>
+        <v>5049</v>
       </c>
       <c r="E179" s="23" t="s">
-        <v>4884</v>
+        <v>4890</v>
       </c>
       <c r="F179" s="25" t="s">
-        <v>4885</v>
+        <v>4891</v>
       </c>
       <c r="G179" s="23" t="s">
-        <v>5044</v>
+        <v>5050</v>
       </c>
       <c r="H179" s="25" t="s">
-        <v>5045</v>
+        <v>5051</v>
       </c>
       <c r="I179" s="10"/>
       <c r="J179" s="10"/>
@@ -50306,22 +50340,22 @@
         <v>3604</v>
       </c>
       <c r="C180" s="23" t="s">
-        <v>5046</v>
+        <v>5052</v>
       </c>
       <c r="D180" s="25" t="s">
-        <v>5047</v>
+        <v>5053</v>
       </c>
       <c r="E180" s="23" t="s">
-        <v>4896</v>
+        <v>4902</v>
       </c>
       <c r="F180" s="10" t="s">
-        <v>4897</v>
+        <v>4903</v>
       </c>
       <c r="G180" s="23" t="s">
-        <v>5048</v>
+        <v>5054</v>
       </c>
       <c r="H180" s="25" t="s">
-        <v>5049</v>
+        <v>5055</v>
       </c>
       <c r="I180" s="10"/>
       <c r="J180" s="10"/>
@@ -50341,22 +50375,22 @@
         <v>4373</v>
       </c>
       <c r="C181" s="36" t="s">
-        <v>5050</v>
+        <v>5056</v>
       </c>
       <c r="D181" s="28" t="s">
-        <v>5051</v>
+        <v>5057</v>
       </c>
       <c r="E181" s="36" t="s">
-        <v>4908</v>
+        <v>4914</v>
       </c>
       <c r="F181" s="28" t="s">
-        <v>4909</v>
+        <v>4915</v>
       </c>
       <c r="G181" s="36" t="s">
-        <v>5052</v>
+        <v>5058</v>
       </c>
       <c r="H181" s="28" t="s">
-        <v>5053</v>
+        <v>5059</v>
       </c>
       <c r="I181" s="10"/>
       <c r="J181" s="10"/>
@@ -50393,11 +50427,11 @@
     </row>
     <row r="183" ht="18.75" customHeight="1">
       <c r="A183" s="18" t="s">
-        <v>5054</v>
+        <v>5060</v>
       </c>
       <c r="B183" s="19"/>
       <c r="C183" s="18" t="s">
-        <v>5055</v>
+        <v>5061</v>
       </c>
       <c r="D183" s="19"/>
       <c r="E183" s="10"/>
@@ -50422,7 +50456,7 @@
       </c>
       <c r="B184" s="22"/>
       <c r="C184" s="23" t="s">
-        <v>5056</v>
+        <v>5062</v>
       </c>
       <c r="D184" s="22"/>
       <c r="E184" s="10"/>
@@ -50447,7 +50481,7 @@
       </c>
       <c r="B185" s="22"/>
       <c r="C185" s="23" t="s">
-        <v>5057</v>
+        <v>5063</v>
       </c>
       <c r="D185" s="22"/>
       <c r="E185" s="10"/>
@@ -50472,7 +50506,7 @@
       </c>
       <c r="B186" s="22"/>
       <c r="C186" s="23" t="s">
-        <v>5058</v>
+        <v>5064</v>
       </c>
       <c r="D186" s="22"/>
       <c r="E186" s="10"/>
@@ -50526,10 +50560,10 @@
         <v>644</v>
       </c>
       <c r="C188" s="23" t="s">
-        <v>5059</v>
+        <v>5065</v>
       </c>
       <c r="D188" s="25" t="s">
-        <v>5060</v>
+        <v>5066</v>
       </c>
       <c r="E188" s="10"/>
       <c r="F188" s="10"/>
@@ -50553,10 +50587,10 @@
         <v>3648</v>
       </c>
       <c r="C189" s="23" t="s">
-        <v>5061</v>
+        <v>5067</v>
       </c>
       <c r="D189" s="25" t="s">
-        <v>5062</v>
+        <v>5068</v>
       </c>
       <c r="E189" s="10"/>
       <c r="F189" s="10"/>
@@ -50580,10 +50614,10 @@
         <v>4348</v>
       </c>
       <c r="C190" s="23" t="s">
-        <v>5061</v>
+        <v>5067</v>
       </c>
       <c r="D190" s="25" t="s">
-        <v>5060</v>
+        <v>5066</v>
       </c>
       <c r="E190" s="10"/>
       <c r="F190" s="10"/>
@@ -50609,10 +50643,10 @@
         <v>3488</v>
       </c>
       <c r="C191" s="23" t="s">
-        <v>5063</v>
+        <v>5069</v>
       </c>
       <c r="D191" s="25" t="s">
-        <v>5064</v>
+        <v>5070</v>
       </c>
       <c r="E191" s="10"/>
       <c r="F191" s="10"/>
@@ -50635,10 +50669,10 @@
         <v>3604</v>
       </c>
       <c r="C192" s="23" t="s">
-        <v>5065</v>
+        <v>5071</v>
       </c>
       <c r="D192" s="25" t="s">
-        <v>5066</v>
+        <v>5072</v>
       </c>
       <c r="E192" s="10"/>
       <c r="F192" s="10"/>
@@ -50661,10 +50695,10 @@
         <v>4373</v>
       </c>
       <c r="C193" s="23" t="s">
-        <v>5067</v>
+        <v>5073</v>
       </c>
       <c r="D193" s="25" t="s">
-        <v>5068</v>
+        <v>5074</v>
       </c>
       <c r="E193" s="10"/>
       <c r="F193" s="10"/>
@@ -50717,10 +50751,10 @@
         <v>644</v>
       </c>
       <c r="C195" s="23" t="s">
-        <v>5069</v>
+        <v>5075</v>
       </c>
       <c r="D195" s="25" t="s">
-        <v>5070</v>
+        <v>5076</v>
       </c>
       <c r="E195" s="10"/>
       <c r="F195" s="10"/>
@@ -50792,10 +50826,10 @@
         <v>3488</v>
       </c>
       <c r="C198" s="23" t="s">
-        <v>5071</v>
+        <v>5077</v>
       </c>
       <c r="D198" s="25" t="s">
-        <v>5072</v>
+        <v>5078</v>
       </c>
       <c r="E198" s="10"/>
       <c r="F198" s="10"/>
@@ -50819,10 +50853,10 @@
         <v>3604</v>
       </c>
       <c r="C199" s="23" t="s">
-        <v>5073</v>
+        <v>5079</v>
       </c>
       <c r="D199" s="25" t="s">
-        <v>5074</v>
+        <v>5080</v>
       </c>
       <c r="E199" s="10"/>
       <c r="F199" s="10"/>
@@ -50886,11 +50920,11 @@
     </row>
     <row r="202" ht="18.75" customHeight="1">
       <c r="A202" s="18" t="s">
-        <v>5075</v>
+        <v>5081</v>
       </c>
       <c r="B202" s="19"/>
       <c r="C202" s="18" t="s">
-        <v>5076</v>
+        <v>5082</v>
       </c>
       <c r="D202" s="19"/>
       <c r="E202" s="10"/>
@@ -50915,7 +50949,7 @@
       </c>
       <c r="B203" s="22"/>
       <c r="C203" s="23" t="s">
-        <v>5077</v>
+        <v>5083</v>
       </c>
       <c r="D203" s="22"/>
       <c r="E203" s="10"/>
@@ -50940,7 +50974,7 @@
       </c>
       <c r="B204" s="22"/>
       <c r="C204" s="23" t="s">
-        <v>5078</v>
+        <v>5084</v>
       </c>
       <c r="D204" s="22"/>
       <c r="E204" s="10"/>
@@ -50965,7 +50999,7 @@
       </c>
       <c r="B205" s="22"/>
       <c r="C205" s="23" t="s">
-        <v>5079</v>
+        <v>5085</v>
       </c>
       <c r="D205" s="22"/>
       <c r="E205" s="10"/>
@@ -51019,10 +51053,10 @@
         <v>644</v>
       </c>
       <c r="C207" s="23" t="s">
-        <v>5080</v>
+        <v>5086</v>
       </c>
       <c r="D207" s="25" t="s">
-        <v>5081</v>
+        <v>5087</v>
       </c>
       <c r="E207" s="10"/>
       <c r="F207" s="10"/>
@@ -51046,10 +51080,10 @@
         <v>3648</v>
       </c>
       <c r="C208" s="23" t="s">
-        <v>5082</v>
+        <v>5088</v>
       </c>
       <c r="D208" s="25" t="s">
-        <v>5083</v>
+        <v>5089</v>
       </c>
       <c r="E208" s="10"/>
       <c r="F208" s="10"/>
@@ -51073,10 +51107,10 @@
         <v>4348</v>
       </c>
       <c r="C209" s="23" t="s">
-        <v>5082</v>
+        <v>5088</v>
       </c>
       <c r="D209" s="25" t="s">
-        <v>5081</v>
+        <v>5087</v>
       </c>
       <c r="E209" s="10"/>
       <c r="F209" s="10"/>
@@ -51102,10 +51136,10 @@
         <v>3488</v>
       </c>
       <c r="C210" s="23" t="s">
-        <v>5084</v>
+        <v>5090</v>
       </c>
       <c r="D210" s="25" t="s">
-        <v>5085</v>
+        <v>5091</v>
       </c>
       <c r="E210" s="10"/>
       <c r="F210" s="10"/>
@@ -51128,10 +51162,10 @@
         <v>3604</v>
       </c>
       <c r="C211" s="23" t="s">
-        <v>5086</v>
+        <v>5092</v>
       </c>
       <c r="D211" s="25" t="s">
-        <v>5087</v>
+        <v>5093</v>
       </c>
       <c r="E211" s="10"/>
       <c r="F211" s="10"/>
@@ -51154,10 +51188,10 @@
         <v>4373</v>
       </c>
       <c r="C212" s="23" t="s">
-        <v>5088</v>
+        <v>5094</v>
       </c>
       <c r="D212" s="25" t="s">
-        <v>5089</v>
+        <v>5095</v>
       </c>
       <c r="E212" s="10"/>
       <c r="F212" s="10"/>
@@ -51210,10 +51244,10 @@
         <v>644</v>
       </c>
       <c r="C214" s="23" t="s">
-        <v>5090</v>
+        <v>5096</v>
       </c>
       <c r="D214" s="25" t="s">
-        <v>5091</v>
+        <v>5097</v>
       </c>
       <c r="E214" s="10"/>
       <c r="F214" s="10"/>
@@ -51285,10 +51319,10 @@
         <v>3488</v>
       </c>
       <c r="C217" s="23" t="s">
-        <v>5092</v>
+        <v>5098</v>
       </c>
       <c r="D217" s="25" t="s">
-        <v>5093</v>
+        <v>5099</v>
       </c>
       <c r="E217" s="10"/>
       <c r="F217" s="10"/>
@@ -51312,10 +51346,10 @@
         <v>3604</v>
       </c>
       <c r="C218" s="23" t="s">
-        <v>5094</v>
+        <v>5100</v>
       </c>
       <c r="D218" s="25" t="s">
-        <v>5095</v>
+        <v>5101</v>
       </c>
       <c r="E218" s="10"/>
       <c r="F218" s="10"/>
@@ -51379,11 +51413,11 @@
     </row>
     <row r="221" ht="18.75" customHeight="1">
       <c r="A221" s="18" t="s">
-        <v>5096</v>
+        <v>5102</v>
       </c>
       <c r="B221" s="19"/>
       <c r="C221" s="18" t="s">
-        <v>5097</v>
+        <v>5103</v>
       </c>
       <c r="D221" s="19"/>
       <c r="E221" s="10"/>
@@ -51408,7 +51442,7 @@
       </c>
       <c r="B222" s="22"/>
       <c r="C222" s="23" t="s">
-        <v>5098</v>
+        <v>5104</v>
       </c>
       <c r="D222" s="22"/>
       <c r="E222" s="10"/>
@@ -51433,7 +51467,7 @@
       </c>
       <c r="B223" s="22"/>
       <c r="C223" s="23" t="s">
-        <v>5099</v>
+        <v>5105</v>
       </c>
       <c r="D223" s="22"/>
       <c r="E223" s="10"/>
@@ -51458,7 +51492,7 @@
       </c>
       <c r="B224" s="22"/>
       <c r="C224" s="23" t="s">
-        <v>5100</v>
+        <v>5106</v>
       </c>
       <c r="D224" s="22"/>
       <c r="E224" s="10"/>
@@ -51512,10 +51546,10 @@
         <v>644</v>
       </c>
       <c r="C226" s="23" t="s">
-        <v>5101</v>
+        <v>5107</v>
       </c>
       <c r="D226" s="25" t="s">
-        <v>5102</v>
+        <v>5108</v>
       </c>
       <c r="E226" s="10"/>
       <c r="F226" s="10"/>
@@ -51539,10 +51573,10 @@
         <v>3648</v>
       </c>
       <c r="C227" s="23" t="s">
-        <v>5103</v>
+        <v>5109</v>
       </c>
       <c r="D227" s="25" t="s">
-        <v>5104</v>
+        <v>5110</v>
       </c>
       <c r="E227" s="10"/>
       <c r="F227" s="10"/>
@@ -51566,10 +51600,10 @@
         <v>4348</v>
       </c>
       <c r="C228" s="23" t="s">
-        <v>5103</v>
+        <v>5109</v>
       </c>
       <c r="D228" s="25" t="s">
-        <v>5105</v>
+        <v>5111</v>
       </c>
       <c r="E228" s="10"/>
       <c r="F228" s="10"/>
@@ -51595,10 +51629,10 @@
         <v>3488</v>
       </c>
       <c r="C229" s="23" t="s">
-        <v>5106</v>
+        <v>5112</v>
       </c>
       <c r="D229" s="25" t="s">
-        <v>5107</v>
+        <v>5113</v>
       </c>
       <c r="E229" s="10"/>
       <c r="F229" s="10"/>
@@ -51622,10 +51656,10 @@
         <v>3604</v>
       </c>
       <c r="C230" s="23" t="s">
-        <v>5108</v>
+        <v>5114</v>
       </c>
       <c r="D230" s="25" t="s">
-        <v>5109</v>
+        <v>5115</v>
       </c>
       <c r="E230" s="10"/>
       <c r="F230" s="10"/>
@@ -51649,10 +51683,10 @@
         <v>4373</v>
       </c>
       <c r="C231" s="36" t="s">
-        <v>5110</v>
+        <v>5116</v>
       </c>
       <c r="D231" s="28" t="s">
-        <v>5111</v>
+        <v>5117</v>
       </c>
       <c r="E231" s="10"/>
       <c r="F231" s="10"/>
@@ -51693,11 +51727,11 @@
     </row>
     <row r="233" ht="18.75" customHeight="1">
       <c r="A233" s="18" t="s">
-        <v>5112</v>
+        <v>5118</v>
       </c>
       <c r="B233" s="19"/>
       <c r="C233" s="18" t="s">
-        <v>5113</v>
+        <v>5119</v>
       </c>
       <c r="D233" s="19"/>
       <c r="E233" s="10"/>
@@ -51722,7 +51756,7 @@
       </c>
       <c r="B234" s="22"/>
       <c r="C234" s="23" t="s">
-        <v>5114</v>
+        <v>5120</v>
       </c>
       <c r="D234" s="22"/>
       <c r="E234" s="10"/>
@@ -51747,7 +51781,7 @@
       </c>
       <c r="B235" s="22"/>
       <c r="C235" s="23" t="s">
-        <v>5115</v>
+        <v>5121</v>
       </c>
       <c r="D235" s="22"/>
       <c r="E235" s="10"/>
@@ -51772,7 +51806,7 @@
       </c>
       <c r="B236" s="22"/>
       <c r="C236" s="23" t="s">
-        <v>5116</v>
+        <v>5122</v>
       </c>
       <c r="D236" s="22"/>
       <c r="E236" s="10"/>
@@ -51826,10 +51860,10 @@
         <v>644</v>
       </c>
       <c r="C238" s="23" t="s">
-        <v>5117</v>
+        <v>5123</v>
       </c>
       <c r="D238" s="25" t="s">
-        <v>5118</v>
+        <v>5124</v>
       </c>
       <c r="E238" s="10"/>
       <c r="F238" s="10"/>
@@ -51853,10 +51887,10 @@
         <v>3648</v>
       </c>
       <c r="C239" s="23" t="s">
-        <v>5117</v>
+        <v>5123</v>
       </c>
       <c r="D239" s="25" t="s">
-        <v>5119</v>
+        <v>5125</v>
       </c>
       <c r="E239" s="10"/>
       <c r="F239" s="10"/>
@@ -51880,10 +51914,10 @@
         <v>4348</v>
       </c>
       <c r="C240" s="23" t="s">
-        <v>5117</v>
+        <v>5123</v>
       </c>
       <c r="D240" s="25" t="s">
-        <v>5120</v>
+        <v>5126</v>
       </c>
       <c r="E240" s="10"/>
       <c r="F240" s="10"/>
@@ -51909,10 +51943,10 @@
         <v>3488</v>
       </c>
       <c r="C241" s="23" t="s">
-        <v>5121</v>
+        <v>5127</v>
       </c>
       <c r="D241" s="25" t="s">
-        <v>5122</v>
+        <v>5128</v>
       </c>
       <c r="E241" s="10"/>
       <c r="F241" s="10"/>
@@ -51936,10 +51970,10 @@
         <v>3604</v>
       </c>
       <c r="C242" s="23" t="s">
-        <v>5123</v>
+        <v>5129</v>
       </c>
       <c r="D242" s="25" t="s">
-        <v>5124</v>
+        <v>5130</v>
       </c>
       <c r="E242" s="10"/>
       <c r="F242" s="10"/>
@@ -51963,10 +51997,10 @@
         <v>4373</v>
       </c>
       <c r="C243" s="36" t="s">
-        <v>5125</v>
+        <v>5131</v>
       </c>
       <c r="D243" s="28" t="s">
-        <v>5126</v>
+        <v>5132</v>
       </c>
       <c r="E243" s="10"/>
       <c r="F243" s="10"/>
@@ -52007,15 +52041,15 @@
     </row>
     <row r="245" ht="18.75" customHeight="1">
       <c r="A245" s="18" t="s">
-        <v>5127</v>
+        <v>5133</v>
       </c>
       <c r="B245" s="19"/>
       <c r="C245" s="18" t="s">
-        <v>5128</v>
+        <v>5134</v>
       </c>
       <c r="D245" s="19"/>
       <c r="E245" s="18" t="s">
-        <v>5129</v>
+        <v>5135</v>
       </c>
       <c r="F245" s="19"/>
       <c r="G245" s="10"/>
@@ -52071,16 +52105,16 @@
         <v>644</v>
       </c>
       <c r="C247" s="23" t="s">
-        <v>5130</v>
+        <v>5136</v>
       </c>
       <c r="D247" s="25" t="s">
-        <v>5131</v>
+        <v>5137</v>
       </c>
       <c r="E247" s="23" t="s">
-        <v>5132</v>
+        <v>5138</v>
       </c>
       <c r="F247" s="25" t="s">
-        <v>5133</v>
+        <v>5139</v>
       </c>
       <c r="G247" s="10"/>
       <c r="H247" s="10"/>
@@ -52102,16 +52136,16 @@
         <v>3648</v>
       </c>
       <c r="C248" s="23" t="s">
-        <v>5130</v>
+        <v>5136</v>
       </c>
       <c r="D248" s="25" t="s">
         <v>4430</v>
       </c>
       <c r="E248" s="23" t="s">
-        <v>4950</v>
+        <v>4956</v>
       </c>
       <c r="F248" s="25" t="s">
-        <v>5134</v>
+        <v>5140</v>
       </c>
       <c r="G248" s="10"/>
       <c r="H248" s="10"/>
@@ -52133,16 +52167,16 @@
         <v>4348</v>
       </c>
       <c r="C249" s="23" t="s">
-        <v>5130</v>
+        <v>5136</v>
       </c>
       <c r="D249" s="25" t="s">
         <v>4420</v>
       </c>
       <c r="E249" s="23" t="s">
-        <v>4950</v>
+        <v>4956</v>
       </c>
       <c r="F249" s="25" t="s">
-        <v>5135</v>
+        <v>5141</v>
       </c>
       <c r="G249" s="10"/>
       <c r="H249" s="10"/>
@@ -52166,16 +52200,16 @@
         <v>3488</v>
       </c>
       <c r="C250" s="23" t="s">
-        <v>5136</v>
+        <v>5142</v>
       </c>
       <c r="D250" s="25" t="s">
-        <v>5137</v>
+        <v>5143</v>
       </c>
       <c r="E250" s="23" t="s">
-        <v>5138</v>
+        <v>5144</v>
       </c>
       <c r="F250" s="25" t="s">
-        <v>5139</v>
+        <v>5145</v>
       </c>
       <c r="G250" s="10"/>
       <c r="H250" s="10"/>
@@ -52197,16 +52231,16 @@
         <v>3604</v>
       </c>
       <c r="C251" s="23" t="s">
-        <v>5140</v>
+        <v>5146</v>
       </c>
       <c r="D251" s="25" t="s">
-        <v>5141</v>
+        <v>5147</v>
       </c>
       <c r="E251" s="23" t="s">
-        <v>5142</v>
+        <v>5148</v>
       </c>
       <c r="F251" s="25" t="s">
-        <v>5143</v>
+        <v>5149</v>
       </c>
       <c r="G251" s="10"/>
       <c r="H251" s="10"/>
@@ -52231,13 +52265,13 @@
         <v>2063</v>
       </c>
       <c r="D252" s="28" t="s">
-        <v>5144</v>
+        <v>5150</v>
       </c>
       <c r="E252" s="36" t="s">
         <v>2746</v>
       </c>
       <c r="F252" s="28" t="s">
-        <v>5145</v>
+        <v>5151</v>
       </c>
       <c r="G252" s="10"/>
       <c r="H252" s="10"/>
@@ -52326,7 +52360,7 @@
       <c r="S256" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="366">
+  <mergeCells count="370">
     <mergeCell ref="A110:B110"/>
     <mergeCell ref="C110:D110"/>
     <mergeCell ref="E110:F110"/>
@@ -52613,6 +52647,8 @@
     <mergeCell ref="K54:L54"/>
     <mergeCell ref="E63:E65"/>
     <mergeCell ref="F63:F65"/>
+    <mergeCell ref="G63:G65"/>
+    <mergeCell ref="H63:H65"/>
     <mergeCell ref="C54:D54"/>
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="A55:B55"/>
@@ -52620,13 +52656,6 @@
     <mergeCell ref="A59:A61"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="A63:A65"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="E67:E68"/>
-    <mergeCell ref="F67:F68"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="G71:H71"/>
     <mergeCell ref="C73:D73"/>
     <mergeCell ref="E73:F73"/>
     <mergeCell ref="A74:B74"/>
@@ -52656,6 +52685,15 @@
     <mergeCell ref="L83:L85"/>
     <mergeCell ref="I87:I88"/>
     <mergeCell ref="L87:L88"/>
+    <mergeCell ref="G67:G68"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="E67:E68"/>
+    <mergeCell ref="F67:F68"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="G71:H71"/>
     <mergeCell ref="G122:H122"/>
     <mergeCell ref="I122:J122"/>
     <mergeCell ref="E121:F121"/>
@@ -52710,11 +52748,11 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="42" t="s">
-        <v>5146</v>
+        <v>5152</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="42" t="s">
-        <v>5147</v>
+        <v>5153</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
@@ -52722,14 +52760,14 @@
         <v>206</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>5148</v>
+        <v>5154</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="43" t="s">
-        <v>5149</v>
+        <v>5155</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>5150</v>
+        <v>5156</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
@@ -52737,14 +52775,14 @@
         <v>1248</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>5151</v>
+        <v>5157</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="43" t="s">
-        <v>5152</v>
+        <v>5158</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>5153</v>
+        <v>5159</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
@@ -52752,14 +52790,14 @@
         <v>1760</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>5154</v>
+        <v>5160</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="43" t="s">
-        <v>5155</v>
+        <v>5161</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>5156</v>
+        <v>5162</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
@@ -52767,14 +52805,14 @@
         <v>1800</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>5157</v>
+        <v>5163</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="43" t="s">
-        <v>5158</v>
+        <v>5164</v>
       </c>
       <c r="G5" s="43" t="s">
-        <v>5159</v>
+        <v>5165</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
@@ -52782,14 +52820,14 @@
         <v>1962</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>5160</v>
+        <v>5166</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="43" t="s">
-        <v>5161</v>
+        <v>5167</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>5162</v>
+        <v>5168</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
@@ -52797,14 +52835,14 @@
         <v>2063</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>5163</v>
+        <v>5169</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="43" t="s">
-        <v>5164</v>
+        <v>5170</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>5165</v>
+        <v>5171</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
@@ -52812,14 +52850,14 @@
         <v>2132</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>5166</v>
+        <v>5172</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="43" t="s">
-        <v>5167</v>
+        <v>5173</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>5168</v>
+        <v>5174</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
@@ -52827,14 +52865,14 @@
         <v>2746</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>5169</v>
+        <v>5175</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="43" t="s">
-        <v>5170</v>
+        <v>5176</v>
       </c>
       <c r="G9" s="43" t="s">
-        <v>5171</v>
+        <v>5177</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
@@ -52842,14 +52880,14 @@
         <v>2963</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>5172</v>
+        <v>5178</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="43" t="s">
-        <v>5173</v>
+        <v>5179</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>5174</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
@@ -52857,14 +52895,14 @@
         <v>3574</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>5175</v>
+        <v>5181</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="43" t="s">
-        <v>5176</v>
+        <v>5182</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>5177</v>
+        <v>5183</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
@@ -52873,10 +52911,10 @@
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
       <c r="E12" s="43" t="s">
-        <v>5178</v>
+        <v>5184</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>5179</v>
+        <v>5185</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
@@ -52885,10 +52923,10 @@
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
       <c r="E13" s="43" t="s">
-        <v>5180</v>
+        <v>5186</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>5181</v>
+        <v>5187</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
@@ -52897,113 +52935,113 @@
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="43" t="s">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>5183</v>
+        <v>5189</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="42" t="s">
-        <v>5184</v>
+        <v>5190</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>5185</v>
+        <v>5191</v>
       </c>
       <c r="G15" s="45" t="s">
-        <v>5186</v>
+        <v>5192</v>
       </c>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>5187</v>
+        <v>5193</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>5188</v>
+        <v>5194</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>5189</v>
+        <v>5195</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>5190</v>
+        <v>5196</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>5191</v>
+        <v>5197</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>5192</v>
+        <v>5198</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>5193</v>
+        <v>5199</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>5194</v>
+        <v>5200</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>5195</v>
+        <v>5201</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>5196</v>
+        <v>5202</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>5197</v>
+        <v>5203</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>5198</v>
+        <v>5204</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>5199</v>
+        <v>5205</v>
       </c>
       <c r="G19" s="43" t="s">
-        <v>5200</v>
+        <v>5206</v>
       </c>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>5201</v>
+        <v>5207</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>5203</v>
+        <v>5209</v>
       </c>
       <c r="G20" s="43" t="s">
-        <v>5204</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>5205</v>
+        <v>5211</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>5206</v>
+        <v>5212</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>5207</v>
+        <v>5213</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>5208</v>
+        <v>5214</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>5209</v>
+        <v>5215</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>5210</v>
+        <v>5216</v>
       </c>
       <c r="E22" s="46" t="s">
-        <v>5211</v>
+        <v>5217</v>
       </c>
       <c r="G22" s="46" t="s">
-        <v>5212</v>
+        <v>5218</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
@@ -53018,65 +53056,65 @@
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
       <c r="E24" s="43" t="s">
-        <v>5213</v>
+        <v>5219</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>5214</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="E25" s="43" t="s">
-        <v>5215</v>
+        <v>5221</v>
       </c>
       <c r="G25" s="43" t="s">
-        <v>5216</v>
+        <v>5222</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="42" t="s">
-        <v>5217</v>
+        <v>5223</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>5218</v>
+        <v>5224</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>5219</v>
+        <v>5225</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>5220</v>
+        <v>5226</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>5221</v>
+        <v>5227</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>5222</v>
+        <v>5228</v>
       </c>
       <c r="G27" s="43" t="s">
-        <v>5223</v>
+        <v>5229</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="43" t="s">
-        <v>5224</v>
+        <v>5230</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>5225</v>
+        <v>5231</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>5226</v>
+        <v>5232</v>
       </c>
       <c r="G28" s="43" t="s">
-        <v>5227</v>
+        <v>5233</v>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="43" t="s">
-        <v>5228</v>
+        <v>5234</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>5229</v>
+        <v>5235</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
@@ -53298,10 +53336,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="43" t="s">
-        <v>5230</v>
+        <v>5236</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>5231</v>
+        <v>5237</v>
       </c>
       <c r="C1" s="12"/>
     </row>
@@ -53310,34 +53348,34 @@
         <v>34</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>5232</v>
+        <v>5238</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>5233</v>
+        <v>5239</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>5234</v>
+        <v>5240</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>5235</v>
+        <v>5241</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>5236</v>
+        <v>5242</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>5237</v>
+        <v>5243</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>5238</v>
+        <v>5244</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -53346,61 +53384,61 @@
         <v>1462</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>5239</v>
+        <v>5245</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>5240</v>
+        <v>5246</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>5241</v>
+        <v>5247</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>5242</v>
+        <v>5248</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>5243</v>
+        <v>5249</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>5244</v>
+        <v>5250</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>5245</v>
+        <v>5251</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>5246</v>
+        <v>5252</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>5247</v>
+        <v>5253</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>5248</v>
+        <v>5254</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>5249</v>
+        <v>5255</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>5250</v>
+        <v>5256</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>5251</v>
+        <v>5257</v>
       </c>
       <c r="C12" s="12"/>
     </row>
@@ -53409,7 +53447,7 @@
         <v>4079</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>5252</v>
+        <v>5258</v>
       </c>
       <c r="C13" s="12"/>
     </row>
@@ -53420,10 +53458,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="43" t="s">
-        <v>5253</v>
+        <v>5259</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>5254</v>
+        <v>5260</v>
       </c>
       <c r="C15" s="12"/>
     </row>
@@ -53432,7 +53470,7 @@
         <v>712</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>5255</v>
+        <v>5261</v>
       </c>
       <c r="C16" s="12"/>
     </row>
@@ -53443,235 +53481,235 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>5256</v>
+        <v>5262</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>5257</v>
+        <v>5263</v>
       </c>
       <c r="C18" s="12"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>5258</v>
+        <v>5264</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>5259</v>
+        <v>5265</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>5260</v>
+        <v>5266</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>5261</v>
+        <v>5267</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>5262</v>
+        <v>5268</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>5263</v>
+        <v>5269</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>5264</v>
+        <v>5270</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>5265</v>
+        <v>5271</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>5266</v>
+        <v>5272</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>5267</v>
+        <v>5273</v>
       </c>
       <c r="C23" s="12"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="43" t="s">
-        <v>5268</v>
+        <v>5274</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>5269</v>
+        <v>5275</v>
       </c>
       <c r="C24" s="12"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="43" t="s">
-        <v>5270</v>
+        <v>5276</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>5271</v>
+        <v>5277</v>
       </c>
       <c r="C25" s="12"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="43" t="s">
-        <v>5272</v>
+        <v>5278</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>5273</v>
+        <v>5279</v>
       </c>
       <c r="C26" s="12"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>5274</v>
+        <v>5280</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>5275</v>
+        <v>5281</v>
       </c>
       <c r="C27" s="12"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="43" t="s">
-        <v>5276</v>
+        <v>5282</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>5277</v>
+        <v>5283</v>
       </c>
       <c r="C28" s="12"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="43" t="s">
-        <v>5278</v>
+        <v>5284</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>5279</v>
+        <v>5285</v>
       </c>
       <c r="C29" s="12"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="43" t="s">
-        <v>5280</v>
+        <v>5286</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>5281</v>
+        <v>5287</v>
       </c>
       <c r="C30" s="12"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="43" t="s">
-        <v>5282</v>
+        <v>5288</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>5283</v>
+        <v>5289</v>
       </c>
       <c r="C31" s="12"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="43" t="s">
-        <v>5284</v>
+        <v>5290</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>5285</v>
+        <v>5291</v>
       </c>
       <c r="C32" s="12"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="43" t="s">
-        <v>5286</v>
+        <v>5292</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>5287</v>
+        <v>5293</v>
       </c>
       <c r="C33" s="12"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="43" t="s">
-        <v>5288</v>
+        <v>5294</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>5289</v>
+        <v>5295</v>
       </c>
       <c r="C34" s="12"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="43" t="s">
-        <v>5290</v>
+        <v>5296</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>5291</v>
+        <v>5297</v>
       </c>
       <c r="C35" s="12"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="43" t="s">
-        <v>5292</v>
+        <v>5298</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>5293</v>
+        <v>5299</v>
       </c>
       <c r="C36" s="12"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="43" t="s">
-        <v>5294</v>
+        <v>5300</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>5295</v>
+        <v>5301</v>
       </c>
       <c r="C37" s="12"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="43" t="s">
-        <v>5296</v>
+        <v>5302</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>5297</v>
+        <v>5303</v>
       </c>
       <c r="C38" s="12"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="43" t="s">
-        <v>5298</v>
+        <v>5304</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>5299</v>
+        <v>5305</v>
       </c>
       <c r="C39" s="12"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="43" t="s">
-        <v>5300</v>
+        <v>5306</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>5301</v>
+        <v>5307</v>
       </c>
       <c r="C40" s="12"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="43" t="s">
-        <v>5302</v>
+        <v>5308</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>5303</v>
+        <v>5309</v>
       </c>
       <c r="C41" s="12"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="43" t="s">
-        <v>5304</v>
+        <v>5310</v>
       </c>
       <c r="B42" s="43" t="s">
-        <v>5305</v>
+        <v>5311</v>
       </c>
       <c r="C42" s="12"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="43" t="s">
-        <v>5306</v>
+        <v>5312</v>
       </c>
       <c r="B43" s="43" t="s">
-        <v>5307</v>
+        <v>5313</v>
       </c>
       <c r="C43" s="12"/>
     </row>
@@ -53680,34 +53718,34 @@
         <v>690</v>
       </c>
       <c r="B44" s="43" t="s">
-        <v>5308</v>
+        <v>5314</v>
       </c>
       <c r="C44" s="12"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="43" t="s">
-        <v>5309</v>
+        <v>5315</v>
       </c>
       <c r="B45" s="43" t="s">
-        <v>5310</v>
+        <v>5316</v>
       </c>
       <c r="C45" s="12"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="43" t="s">
-        <v>5311</v>
+        <v>5317</v>
       </c>
       <c r="B46" s="43" t="s">
-        <v>5312</v>
+        <v>5318</v>
       </c>
       <c r="C46" s="12"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="43" t="s">
-        <v>5313</v>
+        <v>5319</v>
       </c>
       <c r="B47" s="43" t="s">
-        <v>5314</v>
+        <v>5320</v>
       </c>
       <c r="C47" s="12"/>
     </row>
@@ -53730,22 +53768,22 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="47" t="s">
-        <v>5315</v>
+        <v>5321</v>
       </c>
       <c r="C1" s="12"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="47" t="s">
-        <v>5316</v>
+        <v>5322</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>5317</v>
+        <v>5323</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>5318</v>
+        <v>5324</v>
       </c>
       <c r="B3" s="43" t="s">
         <v>712</v>
@@ -53754,97 +53792,97 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>5319</v>
+        <v>5325</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>5244</v>
+        <v>5250</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>5320</v>
+        <v>5326</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>5321</v>
+        <v>5327</v>
       </c>
       <c r="C5" s="12"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="43" t="s">
-        <v>5322</v>
+        <v>5328</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>5323</v>
+        <v>5329</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>5324</v>
+        <v>5330</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>5325</v>
+        <v>5331</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>5326</v>
+        <v>5332</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>5327</v>
+        <v>5333</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>5328</v>
+        <v>5334</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>5329</v>
+        <v>5335</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>5330</v>
+        <v>5336</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>5331</v>
+        <v>5337</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>5332</v>
+        <v>5338</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>5333</v>
+        <v>5339</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>5334</v>
+        <v>5340</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>5335</v>
+        <v>5341</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>5336</v>
+        <v>5342</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>5337</v>
+        <v>5343</v>
       </c>
       <c r="C13" s="12"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="43" t="s">
-        <v>5338</v>
+        <v>5344</v>
       </c>
       <c r="B14" s="43" t="s">
         <v>3209</v>
@@ -53853,73 +53891,73 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="43" t="s">
-        <v>5339</v>
+        <v>5345</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>5340</v>
+        <v>5346</v>
       </c>
       <c r="C15" s="12"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>5341</v>
+        <v>5347</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>5342</v>
+        <v>5348</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>5343</v>
+        <v>5349</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>5344</v>
+        <v>5350</v>
       </c>
       <c r="C17" s="12"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>5345</v>
+        <v>5351</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>5346</v>
+        <v>5352</v>
       </c>
       <c r="C18" s="12"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>5347</v>
+        <v>5353</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>5348</v>
+        <v>5354</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>5349</v>
+        <v>5355</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>5350</v>
+        <v>5356</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>5351</v>
+        <v>5357</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>5352</v>
+        <v>5358</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>5353</v>
+        <v>5359</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>5354</v>
+        <v>5360</v>
       </c>
       <c r="C22" s="12"/>
     </row>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -7552,6 +7552,12 @@
     <t>sperm cell</t>
   </si>
   <si>
+    <t>sáðma</t>
+  </si>
+  <si>
+    <t>to ejaculate (semen) (intransitive)</t>
+  </si>
+  <si>
     <t>saðr</t>
   </si>
   <si>
@@ -8623,28 +8629,22 @@
     <t>to turn, to rotate (intransitive)</t>
   </si>
   <si>
-    <t>søðva</t>
-  </si>
-  <si>
-    <t>to ejaculate (semen) (intransitive)</t>
-  </si>
-  <si>
     <t>sófi</t>
   </si>
   <si>
     <t>sofa, couch</t>
   </si>
   <si>
+    <t>søggva</t>
+  </si>
+  <si>
+    <t>to sink down</t>
+  </si>
+  <si>
     <t>søk</t>
   </si>
   <si>
     <t>accusation, blaming; reason, cause</t>
-  </si>
-  <si>
-    <t>søkkva</t>
-  </si>
-  <si>
-    <t>to sink down</t>
   </si>
   <si>
     <t>sól</t>
@@ -31879,7 +31879,7 @@
         <v>2499</v>
       </c>
       <c r="B1234" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C1234" s="3" t="s">
         <v>2500</v>
@@ -31891,7 +31891,7 @@
         <v>2501</v>
       </c>
       <c r="B1235" s="4" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C1235" s="3" t="s">
         <v>2502</v>
@@ -31903,26 +31903,26 @@
         <v>2503</v>
       </c>
       <c r="B1236" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C1236" s="3" t="s">
         <v>2504</v>
       </c>
-      <c r="D1236" s="3" t="s">
-        <v>93</v>
-      </c>
+      <c r="D1236" s="3"/>
     </row>
     <row r="1237" ht="18.75" customHeight="1">
       <c r="A1237" s="3" t="s">
         <v>2505</v>
       </c>
       <c r="B1237" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C1237" s="3" t="s">
         <v>2506</v>
       </c>
-      <c r="D1237" s="3"/>
+      <c r="D1237" s="3" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="1238" ht="18.75" customHeight="1">
       <c r="A1238" s="3" t="s">
@@ -31934,28 +31934,28 @@
       <c r="C1238" s="3" t="s">
         <v>2508</v>
       </c>
-      <c r="D1238" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="D1238" s="3"/>
     </row>
     <row r="1239" ht="18.75" customHeight="1">
       <c r="A1239" s="3" t="s">
         <v>2509</v>
       </c>
       <c r="B1239" s="4" t="s">
-        <v>994</v>
+        <v>48</v>
       </c>
       <c r="C1239" s="3" t="s">
         <v>2510</v>
       </c>
-      <c r="D1239" s="3"/>
+      <c r="D1239" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="1240" ht="18.75" customHeight="1">
       <c r="A1240" s="3" t="s">
         <v>2511</v>
       </c>
       <c r="B1240" s="4" t="s">
-        <v>48</v>
+        <v>994</v>
       </c>
       <c r="C1240" s="3" t="s">
         <v>2512</v>
@@ -31967,7 +31967,7 @@
         <v>2513</v>
       </c>
       <c r="B1241" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C1241" s="3" t="s">
         <v>2514</v>
@@ -31979,7 +31979,7 @@
         <v>2515</v>
       </c>
       <c r="B1242" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C1242" s="3" t="s">
         <v>2516</v>
@@ -31991,62 +31991,62 @@
         <v>2517</v>
       </c>
       <c r="B1243" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C1243" s="3" t="s">
         <v>2518</v>
       </c>
-      <c r="D1243" s="5"/>
+      <c r="D1243" s="3"/>
     </row>
     <row r="1244" ht="18.75" customHeight="1">
       <c r="A1244" s="3" t="s">
         <v>2519</v>
       </c>
       <c r="B1244" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C1244" s="3" t="s">
         <v>2520</v>
       </c>
-      <c r="D1244" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="D1244" s="5"/>
     </row>
     <row r="1245" ht="18.75" customHeight="1">
       <c r="A1245" s="3" t="s">
         <v>2521</v>
       </c>
       <c r="B1245" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C1245" s="3" t="s">
         <v>2522</v>
       </c>
-      <c r="D1245" s="3"/>
+      <c r="D1245" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="1246" ht="18.75" customHeight="1">
       <c r="A1246" s="3" t="s">
         <v>2523</v>
       </c>
       <c r="B1246" s="4" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C1246" s="3" t="s">
         <v>2524</v>
       </c>
-      <c r="D1246" s="5"/>
+      <c r="D1246" s="3"/>
     </row>
     <row r="1247" ht="18.75" customHeight="1">
       <c r="A1247" s="3" t="s">
         <v>2525</v>
       </c>
       <c r="B1247" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1247" s="3" t="s">
         <v>2526</v>
       </c>
-      <c r="D1247" s="3"/>
+      <c r="D1247" s="5"/>
     </row>
     <row r="1248" ht="18.75" customHeight="1">
       <c r="A1248" s="3" t="s">
@@ -32065,7 +32065,7 @@
         <v>2529</v>
       </c>
       <c r="B1249" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C1249" s="3" t="s">
         <v>2530</v>
@@ -32077,7 +32077,7 @@
         <v>2531</v>
       </c>
       <c r="B1250" s="4" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C1250" s="3" t="s">
         <v>2532</v>
@@ -32092,16 +32092,16 @@
         <v>60</v>
       </c>
       <c r="C1251" s="3" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="D1251" s="3"/>
     </row>
     <row r="1252" ht="18.75" customHeight="1">
       <c r="A1252" s="3" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="B1252" s="4" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C1252" s="3" t="s">
         <v>2535</v>
@@ -32113,38 +32113,38 @@
         <v>2536</v>
       </c>
       <c r="B1253" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C1253" s="3" t="s">
         <v>2537</v>
       </c>
-      <c r="D1253" s="5"/>
+      <c r="D1253" s="3"/>
     </row>
     <row r="1254" ht="18.75" customHeight="1">
       <c r="A1254" s="3" t="s">
         <v>2538</v>
       </c>
       <c r="B1254" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C1254" s="3" t="s">
         <v>2539</v>
       </c>
-      <c r="D1254" s="3" t="s">
-        <v>2540</v>
-      </c>
+      <c r="D1254" s="5"/>
     </row>
     <row r="1255" ht="18.75" customHeight="1">
       <c r="A1255" s="3" t="s">
+        <v>2540</v>
+      </c>
+      <c r="B1255" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1255" s="3" t="s">
         <v>2541</v>
       </c>
-      <c r="B1255" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1255" s="3" t="s">
+      <c r="D1255" s="3" t="s">
         <v>2542</v>
       </c>
-      <c r="D1255" s="5"/>
     </row>
     <row r="1256" ht="18.75" customHeight="1">
       <c r="A1256" s="3" t="s">
@@ -32156,28 +32156,28 @@
       <c r="C1256" s="3" t="s">
         <v>2544</v>
       </c>
-      <c r="D1256" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="D1256" s="5"/>
     </row>
     <row r="1257" ht="18.75" customHeight="1">
       <c r="A1257" s="3" t="s">
         <v>2545</v>
       </c>
       <c r="B1257" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C1257" s="3" t="s">
         <v>2546</v>
       </c>
-      <c r="D1257" s="3"/>
+      <c r="D1257" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="1258" ht="18.75" customHeight="1">
       <c r="A1258" s="3" t="s">
         <v>2547</v>
       </c>
       <c r="B1258" s="4" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C1258" s="3" t="s">
         <v>2548</v>
@@ -32189,7 +32189,7 @@
         <v>2549</v>
       </c>
       <c r="B1259" s="4" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C1259" s="3" t="s">
         <v>2550</v>
@@ -32201,7 +32201,7 @@
         <v>2551</v>
       </c>
       <c r="B1260" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C1260" s="3" t="s">
         <v>2552</v>
@@ -32213,27 +32213,25 @@
         <v>2553</v>
       </c>
       <c r="B1261" s="4" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C1261" s="3" t="s">
         <v>2554</v>
       </c>
-      <c r="D1261" s="3" t="s">
-        <v>2555</v>
-      </c>
+      <c r="D1261" s="3"/>
     </row>
     <row r="1262" ht="18.75" customHeight="1">
       <c r="A1262" s="3" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="B1262" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C1262" s="3" t="s">
+        <v>2556</v>
+      </c>
+      <c r="D1262" s="3" t="s">
         <v>2557</v>
-      </c>
-      <c r="D1262" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="1263" ht="18.75" customHeight="1">
@@ -32241,95 +32239,97 @@
         <v>2558</v>
       </c>
       <c r="B1263" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C1263" s="3" t="s">
         <v>2559</v>
       </c>
-      <c r="D1263" s="3"/>
+      <c r="D1263" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="1264" ht="18.75" customHeight="1">
       <c r="A1264" s="3" t="s">
         <v>2560</v>
       </c>
       <c r="B1264" s="4" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C1264" s="3" t="s">
         <v>2561</v>
       </c>
-      <c r="D1264" s="3" t="s">
-        <v>282</v>
-      </c>
+      <c r="D1264" s="3"/>
     </row>
     <row r="1265" ht="18.75" customHeight="1">
       <c r="A1265" s="3" t="s">
         <v>2562</v>
       </c>
       <c r="B1265" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C1265" s="3" t="s">
         <v>2563</v>
       </c>
-      <c r="D1265" s="3"/>
+      <c r="D1265" s="3" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="1266" ht="18.75" customHeight="1">
       <c r="A1266" s="3" t="s">
         <v>2564</v>
       </c>
       <c r="B1266" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C1266" s="3" t="s">
         <v>2565</v>
       </c>
-      <c r="D1266" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="D1266" s="3"/>
     </row>
     <row r="1267" ht="18.75" customHeight="1">
       <c r="A1267" s="3" t="s">
         <v>2566</v>
       </c>
       <c r="B1267" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C1267" s="3" t="s">
         <v>2567</v>
       </c>
-      <c r="D1267" s="3"/>
+      <c r="D1267" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="1268" ht="18.75" customHeight="1">
       <c r="A1268" s="3" t="s">
         <v>2568</v>
       </c>
       <c r="B1268" s="4" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C1268" s="3" t="s">
         <v>2569</v>
       </c>
-      <c r="D1268" s="5"/>
+      <c r="D1268" s="3"/>
     </row>
     <row r="1269" ht="18.75" customHeight="1">
       <c r="A1269" s="3" t="s">
         <v>2570</v>
       </c>
       <c r="B1269" s="4" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C1269" s="3" t="s">
         <v>2571</v>
       </c>
-      <c r="D1269" s="3"/>
+      <c r="D1269" s="5"/>
     </row>
     <row r="1270" ht="18.75" customHeight="1">
       <c r="A1270" s="3" t="s">
         <v>2572</v>
       </c>
       <c r="B1270" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C1270" s="3" t="s">
         <v>2573</v>
@@ -32341,19 +32341,19 @@
         <v>2574</v>
       </c>
       <c r="B1271" s="4" t="s">
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="C1271" s="3" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="D1271" s="3"/>
     </row>
     <row r="1272" ht="18.75" customHeight="1">
       <c r="A1272" s="3" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="B1272" s="4" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="C1272" s="3" t="s">
         <v>2576</v>
@@ -32365,14 +32365,12 @@
         <v>2577</v>
       </c>
       <c r="B1273" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C1273" s="3" t="s">
         <v>2578</v>
       </c>
-      <c r="D1273" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="D1273" s="3"/>
     </row>
     <row r="1274" ht="18.75" customHeight="1">
       <c r="A1274" s="3" t="s">
@@ -32393,13 +32391,13 @@
         <v>2581</v>
       </c>
       <c r="B1275" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C1275" s="3" t="s">
         <v>2582</v>
       </c>
       <c r="D1275" s="3" t="s">
-        <v>267</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1276" ht="18.75" customHeight="1">
@@ -32407,19 +32405,21 @@
         <v>2583</v>
       </c>
       <c r="B1276" s="4" t="s">
-        <v>202</v>
+        <v>45</v>
       </c>
       <c r="C1276" s="3" t="s">
         <v>2584</v>
       </c>
-      <c r="D1276" s="3"/>
+      <c r="D1276" s="3" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="1277" ht="18.75" customHeight="1">
       <c r="A1277" s="3" t="s">
         <v>2585</v>
       </c>
       <c r="B1277" s="4" t="s">
-        <v>45</v>
+        <v>202</v>
       </c>
       <c r="C1277" s="3" t="s">
         <v>2586</v>
@@ -32443,7 +32443,7 @@
         <v>2589</v>
       </c>
       <c r="B1279" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C1279" s="3" t="s">
         <v>2590</v>
@@ -32455,31 +32455,31 @@
         <v>2591</v>
       </c>
       <c r="B1280" s="4" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C1280" s="3" t="s">
         <v>2592</v>
       </c>
-      <c r="D1280" s="5"/>
+      <c r="D1280" s="3"/>
     </row>
     <row r="1281" ht="18.75" customHeight="1">
       <c r="A1281" s="3" t="s">
         <v>2593</v>
       </c>
       <c r="B1281" s="4" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C1281" s="3" t="s">
         <v>2594</v>
       </c>
-      <c r="D1281" s="3"/>
+      <c r="D1281" s="5"/>
     </row>
     <row r="1282" ht="18.75" customHeight="1">
       <c r="A1282" s="3" t="s">
         <v>2595</v>
       </c>
       <c r="B1282" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C1282" s="3" t="s">
         <v>2596</v>
@@ -32491,33 +32491,33 @@
         <v>2597</v>
       </c>
       <c r="B1283" s="4" t="s">
-        <v>209</v>
+        <v>45</v>
       </c>
       <c r="C1283" s="3" t="s">
         <v>2598</v>
       </c>
-      <c r="D1283" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="D1283" s="3"/>
     </row>
     <row r="1284" ht="18.75" customHeight="1">
       <c r="A1284" s="3" t="s">
         <v>2599</v>
       </c>
       <c r="B1284" s="4" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="C1284" s="3" t="s">
         <v>2600</v>
       </c>
-      <c r="D1284" s="3"/>
+      <c r="D1284" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="1285" ht="18.75" customHeight="1">
       <c r="A1285" s="3" t="s">
         <v>2601</v>
       </c>
       <c r="B1285" s="4" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C1285" s="3" t="s">
         <v>2602</v>
@@ -32529,7 +32529,7 @@
         <v>2603</v>
       </c>
       <c r="B1286" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C1286" s="3" t="s">
         <v>2604</v>
@@ -32541,7 +32541,7 @@
         <v>2605</v>
       </c>
       <c r="B1287" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C1287" s="3" t="s">
         <v>2606</v>
@@ -32553,26 +32553,26 @@
         <v>2607</v>
       </c>
       <c r="B1288" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C1288" s="3" t="s">
         <v>2608</v>
       </c>
-      <c r="D1288" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="D1288" s="3"/>
     </row>
     <row r="1289" ht="18.75" customHeight="1">
       <c r="A1289" s="3" t="s">
         <v>2609</v>
       </c>
       <c r="B1289" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C1289" s="3" t="s">
         <v>2610</v>
       </c>
-      <c r="D1289" s="3"/>
+      <c r="D1289" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="1290" ht="18.75" customHeight="1">
       <c r="A1290" s="3" t="s">
@@ -32591,7 +32591,7 @@
         <v>2613</v>
       </c>
       <c r="B1291" s="4" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C1291" s="3" t="s">
         <v>2614</v>
@@ -32603,7 +32603,7 @@
         <v>2615</v>
       </c>
       <c r="B1292" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C1292" s="3" t="s">
         <v>2616</v>
@@ -32620,9 +32620,7 @@
       <c r="C1293" s="3" t="s">
         <v>2618</v>
       </c>
-      <c r="D1293" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="D1293" s="3"/>
     </row>
     <row r="1294" ht="18.75" customHeight="1">
       <c r="A1294" s="3" t="s">
@@ -32634,14 +32632,16 @@
       <c r="C1294" s="3" t="s">
         <v>2620</v>
       </c>
-      <c r="D1294" s="3"/>
+      <c r="D1294" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="1295" ht="18.75" customHeight="1">
       <c r="A1295" s="3" t="s">
         <v>2621</v>
       </c>
       <c r="B1295" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C1295" s="3" t="s">
         <v>2622</v>
@@ -32653,53 +32653,51 @@
         <v>2623</v>
       </c>
       <c r="B1296" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C1296" s="3" t="s">
         <v>2624</v>
       </c>
-      <c r="D1296" s="3" t="s">
-        <v>267</v>
-      </c>
+      <c r="D1296" s="3"/>
     </row>
     <row r="1297" ht="18.75" customHeight="1">
       <c r="A1297" s="3" t="s">
         <v>2625</v>
       </c>
       <c r="B1297" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C1297" s="3" t="s">
         <v>2626</v>
       </c>
-      <c r="D1297" s="3"/>
+      <c r="D1297" s="3" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="1298" ht="18.75" customHeight="1">
       <c r="A1298" s="3" t="s">
         <v>2627</v>
       </c>
       <c r="B1298" s="4" t="s">
-        <v>209</v>
+        <v>48</v>
       </c>
       <c r="C1298" s="3" t="s">
         <v>2628</v>
       </c>
-      <c r="D1298" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="D1298" s="3"/>
     </row>
     <row r="1299" ht="18.75" customHeight="1">
       <c r="A1299" s="3" t="s">
         <v>2629</v>
       </c>
       <c r="B1299" s="4" t="s">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c r="C1299" s="3" t="s">
         <v>2630</v>
       </c>
       <c r="D1299" s="3" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1300" ht="18.75" customHeight="1">
@@ -32721,19 +32719,21 @@
         <v>2633</v>
       </c>
       <c r="B1301" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C1301" s="3" t="s">
         <v>2634</v>
       </c>
-      <c r="D1301" s="3"/>
+      <c r="D1301" s="3" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="1302" ht="18.75" customHeight="1">
       <c r="A1302" s="3" t="s">
         <v>2635</v>
       </c>
       <c r="B1302" s="4" t="s">
-        <v>628</v>
+        <v>42</v>
       </c>
       <c r="C1302" s="3" t="s">
         <v>2636</v>
@@ -32745,14 +32745,12 @@
         <v>2637</v>
       </c>
       <c r="B1303" s="4" t="s">
-        <v>45</v>
+        <v>628</v>
       </c>
       <c r="C1303" s="3" t="s">
         <v>2638</v>
       </c>
-      <c r="D1303" s="3" t="s">
-        <v>843</v>
-      </c>
+      <c r="D1303" s="3"/>
     </row>
     <row r="1304" ht="18.75" customHeight="1">
       <c r="A1304" s="3" t="s">
@@ -32787,19 +32785,21 @@
         <v>2643</v>
       </c>
       <c r="B1306" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C1306" s="3" t="s">
         <v>2644</v>
       </c>
-      <c r="D1306" s="3"/>
+      <c r="D1306" s="3" t="s">
+        <v>843</v>
+      </c>
     </row>
     <row r="1307" ht="18.75" customHeight="1">
       <c r="A1307" s="3" t="s">
         <v>2645</v>
       </c>
       <c r="B1307" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C1307" s="3" t="s">
         <v>2646</v>
@@ -32811,7 +32811,7 @@
         <v>2647</v>
       </c>
       <c r="B1308" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C1308" s="3" t="s">
         <v>2648</v>
@@ -32823,7 +32823,7 @@
         <v>2649</v>
       </c>
       <c r="B1309" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C1309" s="3" t="s">
         <v>2650</v>
@@ -32835,7 +32835,7 @@
         <v>2651</v>
       </c>
       <c r="B1310" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C1310" s="3" t="s">
         <v>2652</v>
@@ -32859,14 +32859,12 @@
         <v>2655</v>
       </c>
       <c r="B1312" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C1312" s="3" t="s">
         <v>2656</v>
       </c>
-      <c r="D1312" s="3" t="s">
-        <v>882</v>
-      </c>
+      <c r="D1312" s="3"/>
     </row>
     <row r="1313" ht="18.75" customHeight="1">
       <c r="A1313" s="3" t="s">
@@ -32878,26 +32876,28 @@
       <c r="C1313" s="3" t="s">
         <v>2658</v>
       </c>
-      <c r="D1313" s="5"/>
+      <c r="D1313" s="3" t="s">
+        <v>882</v>
+      </c>
     </row>
     <row r="1314" ht="18.75" customHeight="1">
       <c r="A1314" s="3" t="s">
         <v>2659</v>
       </c>
       <c r="B1314" s="4" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C1314" s="3" t="s">
         <v>2660</v>
       </c>
-      <c r="D1314" s="3"/>
+      <c r="D1314" s="5"/>
     </row>
     <row r="1315" ht="18.75" customHeight="1">
       <c r="A1315" s="3" t="s">
         <v>2661</v>
       </c>
       <c r="B1315" s="4" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C1315" s="3" t="s">
         <v>2662</v>
@@ -32909,7 +32909,7 @@
         <v>2663</v>
       </c>
       <c r="B1316" s="4" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C1316" s="3" t="s">
         <v>2664</v>
@@ -32921,7 +32921,7 @@
         <v>2665</v>
       </c>
       <c r="B1317" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C1317" s="3" t="s">
         <v>2666</v>
@@ -32945,7 +32945,7 @@
         <v>2669</v>
       </c>
       <c r="B1319" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C1319" s="3" t="s">
         <v>2670</v>
@@ -32957,38 +32957,38 @@
         <v>2671</v>
       </c>
       <c r="B1320" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C1320" s="3" t="s">
         <v>2672</v>
       </c>
-      <c r="D1320" s="5"/>
+      <c r="D1320" s="3"/>
     </row>
     <row r="1321" ht="18.75" customHeight="1">
       <c r="A1321" s="3" t="s">
         <v>2673</v>
       </c>
       <c r="B1321" s="4" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C1321" s="3" t="s">
         <v>2674</v>
       </c>
-      <c r="D1321" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="D1321" s="5"/>
     </row>
     <row r="1322" ht="18.75" customHeight="1">
       <c r="A1322" s="3" t="s">
         <v>2675</v>
       </c>
       <c r="B1322" s="4" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C1322" s="3" t="s">
         <v>2676</v>
       </c>
-      <c r="D1322" s="3"/>
+      <c r="D1322" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="1323" ht="18.75" customHeight="1">
       <c r="A1323" s="3" t="s">
@@ -33007,7 +33007,7 @@
         <v>2679</v>
       </c>
       <c r="B1324" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1324" s="3" t="s">
         <v>2680</v>
@@ -33019,7 +33019,7 @@
         <v>2681</v>
       </c>
       <c r="B1325" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C1325" s="3" t="s">
         <v>2682</v>
@@ -33043,7 +33043,7 @@
         <v>2685</v>
       </c>
       <c r="B1327" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1327" s="3" t="s">
         <v>2686</v>
@@ -33079,7 +33079,7 @@
         <v>2691</v>
       </c>
       <c r="B1330" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C1330" s="3" t="s">
         <v>2692</v>
@@ -33091,14 +33091,12 @@
         <v>2693</v>
       </c>
       <c r="B1331" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C1331" s="3" t="s">
         <v>2694</v>
       </c>
-      <c r="D1331" s="3" t="s">
-        <v>267</v>
-      </c>
+      <c r="D1331" s="3"/>
     </row>
     <row r="1332" ht="18.75" customHeight="1">
       <c r="A1332" s="3" t="s">
@@ -33111,20 +33109,22 @@
         <v>2696</v>
       </c>
       <c r="D1332" s="3" t="s">
-        <v>2697</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1333" ht="18.75" customHeight="1">
       <c r="A1333" s="3" t="s">
+        <v>2697</v>
+      </c>
+      <c r="B1333" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1333" s="3" t="s">
         <v>2698</v>
       </c>
-      <c r="B1333" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1333" s="3" t="s">
+      <c r="D1333" s="3" t="s">
         <v>2699</v>
       </c>
-      <c r="D1333" s="3"/>
     </row>
     <row r="1334" ht="18.75" customHeight="1">
       <c r="A1334" s="3" t="s">
@@ -33136,47 +33136,45 @@
       <c r="C1334" s="3" t="s">
         <v>2701</v>
       </c>
-      <c r="D1334" s="5"/>
+      <c r="D1334" s="3"/>
     </row>
     <row r="1335" ht="18.75" customHeight="1">
       <c r="A1335" s="3" t="s">
         <v>2702</v>
       </c>
       <c r="B1335" s="4" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C1335" s="3" t="s">
         <v>2703</v>
       </c>
-      <c r="D1335" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="D1335" s="5"/>
     </row>
     <row r="1336" ht="18.75" customHeight="1">
       <c r="A1336" s="3" t="s">
         <v>2704</v>
       </c>
       <c r="B1336" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C1336" s="3" t="s">
         <v>2705</v>
       </c>
-      <c r="D1336" s="3"/>
+      <c r="D1336" s="3" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="1337" ht="18.75" customHeight="1">
       <c r="A1337" s="3" t="s">
         <v>2706</v>
       </c>
       <c r="B1337" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C1337" s="3" t="s">
         <v>2707</v>
       </c>
-      <c r="D1337" s="3" t="s">
-        <v>90</v>
-      </c>
+      <c r="D1337" s="3"/>
     </row>
     <row r="1338" ht="18.75" customHeight="1">
       <c r="A1338" s="3" t="s">
@@ -33189,7 +33187,7 @@
         <v>2709</v>
       </c>
       <c r="D1338" s="3" t="s">
-        <v>267</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1339" ht="18.75" customHeight="1">
@@ -33197,81 +33195,83 @@
         <v>2710</v>
       </c>
       <c r="B1339" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C1339" s="3" t="s">
         <v>2711</v>
       </c>
-      <c r="D1339" s="3"/>
+      <c r="D1339" s="3" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="1340" ht="18.75" customHeight="1">
       <c r="A1340" s="3" t="s">
         <v>2712</v>
       </c>
       <c r="B1340" s="4" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C1340" s="3" t="s">
         <v>2713</v>
       </c>
-      <c r="D1340" s="5"/>
+      <c r="D1340" s="3"/>
     </row>
     <row r="1341" ht="18.75" customHeight="1">
       <c r="A1341" s="3" t="s">
         <v>2714</v>
       </c>
       <c r="B1341" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C1341" s="3" t="s">
         <v>2715</v>
       </c>
-      <c r="D1341" s="3"/>
+      <c r="D1341" s="5"/>
     </row>
     <row r="1342" ht="18.75" customHeight="1">
       <c r="A1342" s="3" t="s">
         <v>2716</v>
       </c>
       <c r="B1342" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C1342" s="3" t="s">
         <v>2717</v>
       </c>
-      <c r="D1342" s="5"/>
+      <c r="D1342" s="3"/>
     </row>
     <row r="1343" ht="18.75" customHeight="1">
       <c r="A1343" s="3" t="s">
         <v>2718</v>
       </c>
       <c r="B1343" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C1343" s="3" t="s">
         <v>2719</v>
       </c>
-      <c r="D1343" s="3" t="s">
-        <v>843</v>
-      </c>
+      <c r="D1343" s="5"/>
     </row>
     <row r="1344" ht="18.75" customHeight="1">
       <c r="A1344" s="3" t="s">
         <v>2720</v>
       </c>
       <c r="B1344" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C1344" s="3" t="s">
         <v>2721</v>
       </c>
-      <c r="D1344" s="5"/>
+      <c r="D1344" s="3" t="s">
+        <v>843</v>
+      </c>
     </row>
     <row r="1345" ht="18.75" customHeight="1">
       <c r="A1345" s="3" t="s">
         <v>2722</v>
       </c>
       <c r="B1345" s="4" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C1345" s="3" t="s">
         <v>2723</v>
@@ -33283,7 +33283,7 @@
         <v>2724</v>
       </c>
       <c r="B1346" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C1346" s="3" t="s">
         <v>2725</v>
@@ -33300,14 +33300,14 @@
       <c r="C1347" s="3" t="s">
         <v>2727</v>
       </c>
-      <c r="D1347" s="3"/>
+      <c r="D1347" s="5"/>
     </row>
     <row r="1348" ht="18.75" customHeight="1">
       <c r="A1348" s="3" t="s">
         <v>2728</v>
       </c>
       <c r="B1348" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1348" s="3" t="s">
         <v>2729</v>
@@ -33319,7 +33319,7 @@
         <v>2730</v>
       </c>
       <c r="B1349" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C1349" s="3" t="s">
         <v>2731</v>
@@ -33331,7 +33331,7 @@
         <v>2732</v>
       </c>
       <c r="B1350" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C1350" s="3" t="s">
         <v>2733</v>
@@ -33343,7 +33343,7 @@
         <v>2734</v>
       </c>
       <c r="B1351" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C1351" s="3" t="s">
         <v>2735</v>
@@ -33355,19 +33355,19 @@
         <v>2736</v>
       </c>
       <c r="B1352" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C1352" s="3" t="s">
         <v>2737</v>
       </c>
-      <c r="D1352" s="5"/>
+      <c r="D1352" s="3"/>
     </row>
     <row r="1353" ht="18.75" customHeight="1">
       <c r="A1353" s="3" t="s">
         <v>2738</v>
       </c>
       <c r="B1353" s="4" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C1353" s="3" t="s">
         <v>2739</v>
@@ -33379,19 +33379,19 @@
         <v>2740</v>
       </c>
       <c r="B1354" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C1354" s="3" t="s">
         <v>2741</v>
       </c>
-      <c r="D1354" s="3"/>
+      <c r="D1354" s="5"/>
     </row>
     <row r="1355" ht="18.75" customHeight="1">
       <c r="A1355" s="3" t="s">
         <v>2742</v>
       </c>
       <c r="B1355" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C1355" s="3" t="s">
         <v>2743</v>
@@ -33403,7 +33403,7 @@
         <v>2744</v>
       </c>
       <c r="B1356" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C1356" s="3" t="s">
         <v>2745</v>
@@ -33415,7 +33415,7 @@
         <v>2746</v>
       </c>
       <c r="B1357" s="4" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C1357" s="3" t="s">
         <v>2747</v>
@@ -33439,31 +33439,31 @@
         <v>2750</v>
       </c>
       <c r="B1359" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C1359" s="3" t="s">
         <v>2751</v>
       </c>
-      <c r="D1359" s="5"/>
+      <c r="D1359" s="3"/>
     </row>
     <row r="1360" ht="18.75" customHeight="1">
       <c r="A1360" s="3" t="s">
         <v>2752</v>
       </c>
       <c r="B1360" s="4" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C1360" s="3" t="s">
         <v>2753</v>
       </c>
-      <c r="D1360" s="3"/>
+      <c r="D1360" s="5"/>
     </row>
     <row r="1361" ht="18.75" customHeight="1">
       <c r="A1361" s="3" t="s">
         <v>2754</v>
       </c>
       <c r="B1361" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C1361" s="3" t="s">
         <v>2755</v>
@@ -33475,7 +33475,7 @@
         <v>2756</v>
       </c>
       <c r="B1362" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C1362" s="3" t="s">
         <v>2757</v>
@@ -33487,7 +33487,7 @@
         <v>2758</v>
       </c>
       <c r="B1363" s="4" t="s">
-        <v>2076</v>
+        <v>48</v>
       </c>
       <c r="C1363" s="3" t="s">
         <v>2759</v>
@@ -33499,7 +33499,7 @@
         <v>2760</v>
       </c>
       <c r="B1364" s="4" t="s">
-        <v>45</v>
+        <v>2076</v>
       </c>
       <c r="C1364" s="3" t="s">
         <v>2761</v>
@@ -33511,24 +33511,24 @@
         <v>2762</v>
       </c>
       <c r="B1365" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C1365" s="3" t="s">
         <v>2763</v>
       </c>
-      <c r="D1365" s="5"/>
+      <c r="D1365" s="3"/>
     </row>
     <row r="1366" ht="18.75" customHeight="1">
       <c r="A1366" s="3" t="s">
         <v>2764</v>
       </c>
       <c r="B1366" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C1366" s="3" t="s">
         <v>2765</v>
       </c>
-      <c r="D1366" s="3"/>
+      <c r="D1366" s="5"/>
     </row>
     <row r="1367" ht="18.75" customHeight="1">
       <c r="A1367" s="3" t="s">
@@ -33540,28 +33540,28 @@
       <c r="C1367" s="3" t="s">
         <v>2767</v>
       </c>
-      <c r="D1367" s="3" t="s">
-        <v>1394</v>
-      </c>
+      <c r="D1367" s="3"/>
     </row>
     <row r="1368" ht="18.75" customHeight="1">
       <c r="A1368" s="3" t="s">
         <v>2768</v>
       </c>
       <c r="B1368" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C1368" s="3" t="s">
         <v>2769</v>
       </c>
-      <c r="D1368" s="3"/>
+      <c r="D1368" s="3" t="s">
+        <v>1394</v>
+      </c>
     </row>
     <row r="1369" ht="18.75" customHeight="1">
       <c r="A1369" s="3" t="s">
         <v>2770</v>
       </c>
       <c r="B1369" s="4" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C1369" s="3" t="s">
         <v>2771</v>
@@ -33573,7 +33573,7 @@
         <v>2772</v>
       </c>
       <c r="B1370" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C1370" s="3" t="s">
         <v>2773</v>
@@ -33585,57 +33585,57 @@
         <v>2774</v>
       </c>
       <c r="B1371" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1371" s="3" t="s">
         <v>2775</v>
       </c>
-      <c r="D1371" s="3" t="s">
-        <v>748</v>
-      </c>
+      <c r="D1371" s="3"/>
     </row>
     <row r="1372" ht="18.75" customHeight="1">
       <c r="A1372" s="3" t="s">
         <v>2776</v>
       </c>
       <c r="B1372" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C1372" s="3" t="s">
         <v>2777</v>
       </c>
-      <c r="D1372" s="3"/>
+      <c r="D1372" s="3" t="s">
+        <v>748</v>
+      </c>
     </row>
     <row r="1373" ht="18.75" customHeight="1">
       <c r="A1373" s="3" t="s">
         <v>2778</v>
       </c>
       <c r="B1373" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C1373" s="3" t="s">
         <v>2779</v>
       </c>
-      <c r="D1373" s="5"/>
+      <c r="D1373" s="3"/>
     </row>
     <row r="1374" ht="18.75" customHeight="1">
       <c r="A1374" s="3" t="s">
         <v>2780</v>
       </c>
       <c r="B1374" s="4" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C1374" s="3" t="s">
         <v>2781</v>
       </c>
-      <c r="D1374" s="3"/>
+      <c r="D1374" s="5"/>
     </row>
     <row r="1375" ht="18.75" customHeight="1">
       <c r="A1375" s="3" t="s">
         <v>2782</v>
       </c>
       <c r="B1375" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C1375" s="3" t="s">
         <v>2783</v>
@@ -33647,14 +33647,12 @@
         <v>2784</v>
       </c>
       <c r="B1376" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1376" s="3" t="s">
         <v>2785</v>
       </c>
-      <c r="D1376" s="3" t="s">
-        <v>2555</v>
-      </c>
+      <c r="D1376" s="3"/>
     </row>
     <row r="1377" ht="18.75" customHeight="1">
       <c r="A1377" s="3" t="s">
@@ -33666,7 +33664,9 @@
       <c r="C1377" s="3" t="s">
         <v>2787</v>
       </c>
-      <c r="D1377" s="3"/>
+      <c r="D1377" s="3" t="s">
+        <v>2557</v>
+      </c>
     </row>
     <row r="1378" ht="18.75" customHeight="1">
       <c r="A1378" s="3" t="s">
@@ -33685,7 +33685,7 @@
         <v>2790</v>
       </c>
       <c r="B1379" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C1379" s="3" t="s">
         <v>2791</v>
@@ -33697,7 +33697,7 @@
         <v>2792</v>
       </c>
       <c r="B1380" s="4" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C1380" s="3" t="s">
         <v>2793</v>
@@ -33709,7 +33709,7 @@
         <v>2794</v>
       </c>
       <c r="B1381" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C1381" s="3" t="s">
         <v>2795</v>
@@ -33721,7 +33721,7 @@
         <v>2796</v>
       </c>
       <c r="B1382" s="4" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C1382" s="3" t="s">
         <v>2797</v>
@@ -33745,14 +33745,12 @@
         <v>2800</v>
       </c>
       <c r="B1384" s="4" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C1384" s="3" t="s">
         <v>2801</v>
       </c>
-      <c r="D1384" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="D1384" s="3"/>
     </row>
     <row r="1385" ht="18.75" customHeight="1">
       <c r="A1385" s="3" t="s">
@@ -33764,7 +33762,9 @@
       <c r="C1385" s="3" t="s">
         <v>2803</v>
       </c>
-      <c r="D1385" s="3"/>
+      <c r="D1385" s="3" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="1386" ht="18.75" customHeight="1">
       <c r="A1386" s="3" t="s">
@@ -33807,7 +33807,7 @@
         <v>2810</v>
       </c>
       <c r="B1389" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C1389" s="3" t="s">
         <v>2811</v>
@@ -33819,7 +33819,7 @@
         <v>2812</v>
       </c>
       <c r="B1390" s="4" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C1390" s="3" t="s">
         <v>2813</v>
@@ -33831,7 +33831,7 @@
         <v>2814</v>
       </c>
       <c r="B1391" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C1391" s="3" t="s">
         <v>2815</v>
@@ -33855,7 +33855,7 @@
         <v>2818</v>
       </c>
       <c r="B1393" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C1393" s="3" t="s">
         <v>2819</v>
@@ -33867,36 +33867,36 @@
         <v>2820</v>
       </c>
       <c r="B1394" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C1394" s="3" t="s">
         <v>2821</v>
       </c>
-      <c r="D1394" s="5"/>
+      <c r="D1394" s="3"/>
     </row>
     <row r="1395" ht="18.75" customHeight="1">
       <c r="A1395" s="3" t="s">
         <v>2822</v>
       </c>
       <c r="B1395" s="4" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C1395" s="3" t="s">
         <v>2823</v>
       </c>
-      <c r="D1395" s="3"/>
+      <c r="D1395" s="5"/>
     </row>
     <row r="1396" ht="18.75" customHeight="1">
       <c r="A1396" s="3" t="s">
         <v>2824</v>
       </c>
       <c r="B1396" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C1396" s="3" t="s">
         <v>2825</v>
       </c>
-      <c r="D1396" s="5"/>
+      <c r="D1396" s="3"/>
     </row>
     <row r="1397" ht="18.75" customHeight="1">
       <c r="A1397" s="3" t="s">
@@ -33908,28 +33908,26 @@
       <c r="C1397" s="3" t="s">
         <v>2827</v>
       </c>
-      <c r="D1397" s="3"/>
+      <c r="D1397" s="5"/>
     </row>
     <row r="1398" ht="18.75" customHeight="1">
       <c r="A1398" s="3" t="s">
         <v>2828</v>
       </c>
       <c r="B1398" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C1398" s="3" t="s">
         <v>2829</v>
       </c>
-      <c r="D1398" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="D1398" s="3"/>
     </row>
     <row r="1399" ht="18.75" customHeight="1">
       <c r="A1399" s="3" t="s">
         <v>2830</v>
       </c>
       <c r="B1399" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C1399" s="3" t="s">
         <v>2831</v>
@@ -33948,14 +33946,16 @@
       <c r="C1400" s="3" t="s">
         <v>2833</v>
       </c>
-      <c r="D1400" s="3"/>
+      <c r="D1400" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="1401" ht="18.75" customHeight="1">
       <c r="A1401" s="3" t="s">
         <v>2834</v>
       </c>
       <c r="B1401" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C1401" s="3" t="s">
         <v>2835</v>
@@ -33967,7 +33967,7 @@
         <v>2836</v>
       </c>
       <c r="B1402" s="4" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C1402" s="3" t="s">
         <v>2837</v>
@@ -33979,7 +33979,7 @@
         <v>2838</v>
       </c>
       <c r="B1403" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C1403" s="3" t="s">
         <v>2839</v>
@@ -33991,7 +33991,7 @@
         <v>2840</v>
       </c>
       <c r="B1404" s="4" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C1404" s="3" t="s">
         <v>2841</v>
@@ -34003,7 +34003,7 @@
         <v>2842</v>
       </c>
       <c r="B1405" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C1405" s="3" t="s">
         <v>2843</v>
@@ -34015,7 +34015,7 @@
         <v>2844</v>
       </c>
       <c r="B1406" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C1406" s="3" t="s">
         <v>2845</v>
@@ -34032,19 +34032,19 @@
       <c r="C1407" s="3" t="s">
         <v>2847</v>
       </c>
-      <c r="D1407" s="5"/>
+      <c r="D1407" s="3"/>
     </row>
     <row r="1408" ht="18.75" customHeight="1">
       <c r="A1408" s="3" t="s">
         <v>2848</v>
       </c>
       <c r="B1408" s="4" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C1408" s="3" t="s">
         <v>2849</v>
       </c>
-      <c r="D1408" s="3"/>
+      <c r="D1408" s="5"/>
     </row>
     <row r="1409" ht="18.75" customHeight="1">
       <c r="A1409" s="3" t="s">
@@ -34063,14 +34063,12 @@
         <v>2852</v>
       </c>
       <c r="B1410" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C1410" s="3" t="s">
         <v>2853</v>
       </c>
-      <c r="D1410" s="3" t="s">
-        <v>451</v>
-      </c>
+      <c r="D1410" s="3"/>
     </row>
     <row r="1411" ht="18.75" customHeight="1">
       <c r="A1411" s="3" t="s">
@@ -34096,7 +34094,9 @@
       <c r="C1412" s="3" t="s">
         <v>2857</v>
       </c>
-      <c r="D1412" s="3"/>
+      <c r="D1412" s="3" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="1413" ht="18.75" customHeight="1">
       <c r="A1413" s="3" t="s">
@@ -34115,7 +34115,7 @@
         <v>2860</v>
       </c>
       <c r="B1414" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C1414" s="3" t="s">
         <v>2861</v>
@@ -34127,7 +34127,7 @@
         <v>2862</v>
       </c>
       <c r="B1415" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1415" s="3" t="s">
         <v>2863</v>
@@ -39359,7 +39359,7 @@
         <v>3708</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>2722</v>
+        <v>2724</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>3709</v>
@@ -40400,13 +40400,13 @@
         <v>3708</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>3882</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="Q31" s="10" t="s">
         <v>3883</v>
@@ -41007,10 +41007,10 @@
       </c>
       <c r="L50" s="9"/>
       <c r="M50" s="8" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
       <c r="N50" s="8" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="51" ht="18.75" customHeight="1">
@@ -41090,7 +41090,7 @@
         <v>3708</v>
       </c>
       <c r="N52" s="10" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
       <c r="O52" s="10" t="s">
         <v>3980</v>
@@ -42756,7 +42756,7 @@
         <v>3708</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>2635</v>
+        <v>2637</v>
       </c>
       <c r="M24" s="10" t="s">
         <v>4199</v>
@@ -43847,7 +43847,7 @@
         <v>3708</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>2820</v>
+        <v>2822</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>4277</v>
@@ -43860,7 +43860,7 @@
         <v>3708</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>2770</v>
+        <v>2772</v>
       </c>
       <c r="M31" s="16" t="s">
         <v>4279</v>
@@ -44906,7 +44906,7 @@
         <v>4356</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>2764</v>
+        <v>2766</v>
       </c>
       <c r="J6" s="25" t="s">
         <v>4357</v>
@@ -49406,7 +49406,7 @@
       </c>
       <c r="F143" s="22"/>
       <c r="G143" s="23" t="s">
-        <v>2710</v>
+        <v>2712</v>
       </c>
       <c r="H143" s="22"/>
       <c r="I143" s="10"/>
@@ -52456,7 +52456,7 @@
         <v>5170</v>
       </c>
       <c r="E252" s="36" t="s">
-        <v>2758</v>
+        <v>2760</v>
       </c>
       <c r="F252" s="28" t="s">
         <v>5171</v>
@@ -53050,7 +53050,7 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>2758</v>
+        <v>2760</v>
       </c>
       <c r="B9" s="43" t="s">
         <v>5195</v>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -8641,7 +8641,7 @@
     <t>sofa, couch</t>
   </si>
   <si>
-    <t>søggva</t>
+    <t>søkkva</t>
   </si>
   <si>
     <t>to sink down</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -2596,6 +2596,12 @@
     <t>strong verb f</t>
   </si>
   <si>
+    <t>fljút</t>
+  </si>
+  <si>
+    <t>river</t>
+  </si>
+  <si>
     <t>flotinn</t>
   </si>
   <si>
@@ -2612,12 +2618,6 @@
   </si>
   <si>
     <t>to fly</t>
-  </si>
-  <si>
-    <t>flýtr</t>
-  </si>
-  <si>
-    <t>river</t>
   </si>
   <si>
     <t>føður-lína</t>
@@ -21810,7 +21810,7 @@
         <v>847</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C410" s="3" t="s">
         <v>848</v>
@@ -21822,7 +21822,7 @@
         <v>849</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C411" s="3" t="s">
         <v>850</v>
@@ -21846,7 +21846,7 @@
         <v>853</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C413" s="3" t="s">
         <v>854</v>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -16146,10 +16146,10 @@
     <t>-apn</t>
   </si>
   <si>
-    <t>jó (in verbs)</t>
-  </si>
-  <si>
-    <t>jú</t>
+    <t>jó</t>
+  </si>
+  <si>
+    <t>jú or ý</t>
   </si>
   <si>
     <t>kn-</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8603" uniqueCount="5384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8604" uniqueCount="5384">
   <si>
     <t>Entry</t>
   </si>
@@ -3865,7 +3865,7 @@
     <t>thud, thump; a dull sound</t>
   </si>
   <si>
-    <t>hlébarði</t>
+    <t>hlebarði</t>
   </si>
   <si>
     <t>leopard</t>
@@ -3907,19 +3907,19 @@
     <t>rudder, helm, wheel (on a boat)</t>
   </si>
   <si>
-    <t>hljóð</t>
+    <t>hljúð</t>
   </si>
   <si>
     <t>sound, noise</t>
   </si>
   <si>
-    <t>hljóð-ligr</t>
+    <t>hljúð-ligr</t>
   </si>
   <si>
     <t>loud</t>
   </si>
   <si>
-    <t>hljóða</t>
+    <t>hljúða</t>
   </si>
   <si>
     <t>to louden, to make loud</t>
@@ -24505,7 +24505,9 @@
       <c r="C630" s="3" t="s">
         <v>1289</v>
       </c>
-      <c r="D630" s="3"/>
+      <c r="D630" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="631" ht="18.75" customHeight="1">
       <c r="A631" s="3" t="s">

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -7018,7 +7018,7 @@
     <t>shoulder; axle, axis</t>
   </si>
   <si>
-    <t>pap</t>
+    <t>papp</t>
   </si>
   <si>
     <t>paper</t>
@@ -8197,7 +8197,7 @@
     <t>skin, hide, fur, pelt</t>
   </si>
   <si>
-    <t>skinn-pap</t>
+    <t>skinn-papp</t>
   </si>
   <si>
     <t>vellum</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8616" uniqueCount="5392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8628" uniqueCount="5395">
   <si>
     <t>Entry</t>
   </si>
@@ -12672,6 +12672,15 @@
     <t>sjalft</t>
   </si>
   <si>
+    <t>einhvers</t>
+  </si>
+  <si>
+    <t>einhverjar</t>
+  </si>
+  <si>
+    <t>eithvers</t>
+  </si>
+  <si>
     <t>þína</t>
   </si>
   <si>
@@ -12681,30 +12690,27 @@
     <t>sjalfa</t>
   </si>
   <si>
+    <t>þinum</t>
+  </si>
+  <si>
+    <t>þíni</t>
+  </si>
+  <si>
+    <t>þinu</t>
+  </si>
+  <si>
+    <t>sjølfum</t>
+  </si>
+  <si>
+    <t>sjalfi</t>
+  </si>
+  <si>
+    <t>sjølfu</t>
+  </si>
+  <si>
     <t>einhverjir</t>
   </si>
   <si>
-    <t>einhverjar</t>
-  </si>
-  <si>
-    <t>þinum</t>
-  </si>
-  <si>
-    <t>þíni</t>
-  </si>
-  <si>
-    <t>þinu</t>
-  </si>
-  <si>
-    <t>sjølfum</t>
-  </si>
-  <si>
-    <t>sjalfi</t>
-  </si>
-  <si>
-    <t>sjølfu</t>
-  </si>
-  <si>
     <t>þins</t>
   </si>
   <si>
@@ -12747,10 +12753,13 @@
     <t>engu</t>
   </si>
   <si>
+    <t>enks</t>
+  </si>
+  <si>
+    <t>engar</t>
+  </si>
+  <si>
     <t>engir</t>
-  </si>
-  <si>
-    <t>engar</t>
   </si>
   <si>
     <t>form 1</t>
@@ -42843,112 +42852,118 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="8" t="s">
-        <v>4152</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>4167</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>4168</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>3720</v>
+        <v>3754</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>4205</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>4206</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>4207</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="8" t="s">
         <v>3735</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>4205</v>
+        <v>4208</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>3735</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>4206</v>
+        <v>4209</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>4207</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="8" t="s">
-        <v>3724</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>4208</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>4209</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>4196</v>
+        <v>4152</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>4167</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>4168</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>3720</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="8" t="s">
         <v>3742</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>4210</v>
+        <v>4211</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>4211</v>
+        <v>4212</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>4212</v>
+        <v>4213</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>3742</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>4213</v>
+        <v>4214</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>4214</v>
+        <v>4215</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>4215</v>
+        <v>4216</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="8" t="s">
-        <v>3735</v>
+        <v>3724</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>4198</v>
+        <v>4217</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>4206</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>4196</v>
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="8" t="s">
         <v>3754</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>4216</v>
+        <v>4218</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>4217</v>
+        <v>4219</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>4216</v>
+        <v>4218</v>
       </c>
       <c r="K27" s="8" t="s">
         <v>3754</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>4218</v>
+        <v>4220</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>4219</v>
+        <v>4221</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>4218</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="8" t="s">
-        <v>3742</v>
+        <v>3735</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>4199</v>
+        <v>4198</v>
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="8" t="s">
@@ -42977,15 +42992,21 @@
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
+      <c r="A29" s="8" t="s">
+        <v>3742</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>4199</v>
+      </c>
       <c r="E29" s="9"/>
       <c r="F29" s="8" t="s">
         <v>3724</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>4220</v>
+        <v>4222</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>4217</v>
+        <v>4219</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>4147</v>
@@ -42994,10 +43015,10 @@
         <v>3724</v>
       </c>
       <c r="L29" s="10" t="s">
+        <v>4223</v>
+      </c>
+      <c r="M29" s="10" t="s">
         <v>4221</v>
-      </c>
-      <c r="M29" s="10" t="s">
-        <v>4219</v>
       </c>
       <c r="N29" s="10" t="s">
         <v>4203</v>
@@ -43005,94 +43026,79 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="8" t="s">
-        <v>4128</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>4167</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>4168</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>3720</v>
+        <v>3754</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>4198</v>
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="8" t="s">
         <v>3735</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>4222</v>
+        <v>4224</v>
       </c>
       <c r="K30" s="8" t="s">
         <v>3735</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>4207</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="8" t="s">
-        <v>3724</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>697</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>4223</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>4224</v>
-      </c>
       <c r="E31" s="9"/>
       <c r="F31" s="8" t="s">
         <v>3742</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>4210</v>
+        <v>4211</v>
       </c>
       <c r="K31" s="8" t="s">
         <v>3742</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>4213</v>
+        <v>4214</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="8" t="s">
-        <v>3735</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>4225</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>4226</v>
+        <v>4128</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>4167</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>4168</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>3720</v>
       </c>
       <c r="E32" s="9"/>
       <c r="F32" s="8" t="s">
         <v>3754</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>4222</v>
+        <v>4224</v>
       </c>
       <c r="K32" s="8" t="s">
         <v>3754</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>4207</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="8" t="s">
-        <v>3742</v>
+        <v>3724</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>4227</v>
+        <v>697</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>4228</v>
+        <v>4225</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>4229</v>
+        <v>4226</v>
       </c>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
@@ -43100,16 +43106,13 @@
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="8" t="s">
-        <v>4152</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>4167</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>4168</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>3720</v>
+        <v>3735</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>4227</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>4228</v>
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
@@ -43117,16 +43120,16 @@
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="8" t="s">
-        <v>3724</v>
+        <v>3742</v>
       </c>
       <c r="B35" s="10" t="s">
+        <v>4229</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>4230</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="D35" s="10" t="s">
         <v>4231</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>4223</v>
       </c>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
@@ -43134,10 +43137,16 @@
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="8" t="s">
-        <v>3735</v>
+        <v>3742</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>4226</v>
+        <v>4232</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>4233</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>4232</v>
       </c>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
@@ -43145,22 +43154,90 @@
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="8" t="s">
-        <v>3742</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>4227</v>
+        <v>4152</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>4167</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>4168</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>3720</v>
       </c>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
+      <c r="A38" s="8" t="s">
+        <v>3724</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>4234</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>4233</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>4225</v>
+      </c>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
     </row>
+    <row r="39" ht="18.75" customHeight="1">
+      <c r="A39" s="8" t="s">
+        <v>3735</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>4228</v>
+      </c>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+    </row>
+    <row r="40" ht="18.75" customHeight="1">
+      <c r="A40" s="8" t="s">
+        <v>3742</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>4229</v>
+      </c>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+    </row>
+    <row r="41" ht="18.75" customHeight="1">
+      <c r="A41" s="8" t="s">
+        <v>3754</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>4228</v>
+      </c>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+    </row>
+    <row r="42" ht="18.75" customHeight="1">
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+    </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="43">
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="C38:C39"/>
     <mergeCell ref="G13:G14"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="L13:L14"/>
@@ -43187,21 +43264,11 @@
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="I24:I25"/>
     <mergeCell ref="N24:N25"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
     <mergeCell ref="H29:H30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="M29:M30"/>
-    <mergeCell ref="N29:N30"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -43219,10 +43286,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>4232</v>
+        <v>4235</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>4233</v>
+        <v>4236</v>
       </c>
       <c r="H1" s="12"/>
       <c r="I1" s="12"/>
@@ -43241,14 +43308,14 @@
       </c>
       <c r="H2" s="12"/>
       <c r="I2" s="8" t="s">
-        <v>4234</v>
+        <v>4237</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>4235</v>
+        <v>4238</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>4167</v>
@@ -43270,7 +43337,7 @@
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="8" t="s">
-        <v>4235</v>
+        <v>4238</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>4167</v>
@@ -43292,32 +43359,32 @@
         <v>2435</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>4236</v>
+        <v>4239</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>4237</v>
+        <v>4240</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>4238</v>
+        <v>4241</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>4239</v>
+        <v>4242</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>4239</v>
+        <v>4242</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="8" t="s">
         <v>3724</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>4240</v>
+        <v>4243</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>4241</v>
+        <v>4244</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>4242</v>
+        <v>4245</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
@@ -43327,23 +43394,23 @@
         <v>3735</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>4243</v>
+        <v>4246</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>4239</v>
+        <v>4242</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>4239</v>
+        <v>4242</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>4244</v>
+        <v>4247</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="8" t="s">
         <v>3735</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>4245</v>
+        <v>4248</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
@@ -43353,26 +43420,26 @@
         <v>3742</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>4246</v>
+        <v>4249</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>4238</v>
+        <v>4241</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>4244</v>
+        <v>4247</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="8" t="s">
         <v>3742</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>4247</v>
+        <v>4250</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>4248</v>
+        <v>4251</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>4249</v>
+        <v>4252</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
@@ -43382,33 +43449,33 @@
         <v>3754</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>4250</v>
+        <v>4253</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>4251</v>
+        <v>4254</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>4250</v>
+        <v>4253</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="8" t="s">
         <v>3754</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>4252</v>
+        <v>4255</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>4253</v>
+        <v>4256</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>4252</v>
+        <v>4255</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>4254</v>
+        <v>4257</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>4167</v>
@@ -43441,16 +43508,16 @@
         <v>3724</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>4255</v>
+        <v>4258</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>4251</v>
+        <v>4254</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>4236</v>
+        <v>4239</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>4244</v>
+        <v>4247</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -43465,7 +43532,7 @@
         <v>3735</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>4239</v>
+        <v>4242</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
@@ -43480,7 +43547,7 @@
         <v>3742</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>4246</v>
+        <v>4249</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
@@ -43495,7 +43562,7 @@
         <v>3754</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>4239</v>
+        <v>4242</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
@@ -43507,7 +43574,7 @@
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>4256</v>
+        <v>4259</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>4167</v>
@@ -43540,22 +43607,22 @@
         <v>3724</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>4257</v>
+        <v>4260</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>4258</v>
+        <v>4261</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>4259</v>
+        <v>4262</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>4260</v>
+        <v>4263</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>4261</v>
+        <v>4264</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>4261</v>
+        <v>4264</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
@@ -43570,16 +43637,16 @@
         <v>3735</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>4262</v>
+        <v>4265</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>4261</v>
+        <v>4264</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>4261</v>
+        <v>4264</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>4263</v>
+        <v>4266</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
@@ -43594,13 +43661,13 @@
         <v>3742</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>4264</v>
+        <v>4267</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>4260</v>
+        <v>4263</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>4263</v>
+        <v>4266</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
@@ -43615,13 +43682,13 @@
         <v>3754</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>4265</v>
+        <v>4268</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>4266</v>
+        <v>4269</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>4265</v>
+        <v>4268</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
@@ -43633,7 +43700,7 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>4267</v>
+        <v>4270</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>4167</v>
@@ -43666,16 +43733,16 @@
         <v>3724</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>4268</v>
+        <v>4271</v>
       </c>
       <c r="C19" s="10" t="s">
+        <v>4269</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>4261</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>4266</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>4258</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>4263</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
@@ -43690,7 +43757,7 @@
         <v>3735</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>4261</v>
+        <v>4264</v>
       </c>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
@@ -43705,7 +43772,7 @@
         <v>3742</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>4264</v>
+        <v>4267</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
@@ -43720,7 +43787,7 @@
         <v>3754</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>4261</v>
+        <v>4264</v>
       </c>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
@@ -43732,7 +43799,7 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="8" t="s">
-        <v>4269</v>
+        <v>4272</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>4167</v>
@@ -43757,13 +43824,13 @@
         <v>3724</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>4270</v>
+        <v>4273</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>4271</v>
+        <v>4274</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>4271</v>
+        <v>4274</v>
       </c>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
@@ -43775,13 +43842,13 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="8" t="s">
-        <v>4272</v>
+        <v>4275</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>4271</v>
+        <v>4274</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>4273</v>
+        <v>4276</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -43793,7 +43860,7 @@
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="8" t="s">
-        <v>4274</v>
+        <v>4277</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>4167</v>
@@ -43814,10 +43881,10 @@
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="8" t="s">
-        <v>4275</v>
+        <v>4278</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>4273</v>
+        <v>4276</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -43845,24 +43912,24 @@
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>4232</v>
+        <v>4235</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>4276</v>
+        <v>4279</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="8" t="s">
-        <v>4232</v>
+        <v>4235</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>4277</v>
+        <v>4280</v>
       </c>
       <c r="J29" s="9"/>
       <c r="K29" s="14" t="s">
-        <v>4232</v>
+        <v>4235</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>4278</v>
+        <v>4281</v>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1">
@@ -43913,10 +43980,10 @@
         <v>1566</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>4279</v>
+        <v>4282</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>4280</v>
+        <v>4283</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="8" t="s">
@@ -43926,10 +43993,10 @@
         <v>2838</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>4281</v>
+        <v>4284</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>4282</v>
+        <v>4285</v>
       </c>
       <c r="J31" s="9"/>
       <c r="K31" s="14" t="s">
@@ -43939,10 +44006,10 @@
         <v>2788</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>4283</v>
+        <v>4286</v>
       </c>
       <c r="N31" s="16" t="s">
-        <v>4284</v>
+        <v>4287</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
@@ -43950,30 +44017,30 @@
         <v>3735</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>4285</v>
+        <v>4288</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>4286</v>
+        <v>4289</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="8" t="s">
         <v>3735</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>4287</v>
+        <v>4290</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>4288</v>
+        <v>4291</v>
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="14" t="s">
         <v>3735</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>4289</v>
+        <v>4292</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>4290</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
@@ -43981,39 +44048,39 @@
         <v>3742</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>4291</v>
+        <v>4294</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>4292</v>
+        <v>4295</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>4293</v>
+        <v>4296</v>
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="8" t="s">
         <v>3742</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>4294</v>
+        <v>4297</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>4295</v>
+        <v>4298</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>4296</v>
+        <v>4299</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="14" t="s">
         <v>3742</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>4297</v>
+        <v>4300</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>4298</v>
+        <v>4301</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>4299</v>
+        <v>4302</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
@@ -44021,39 +44088,39 @@
         <v>3754</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>4300</v>
+        <v>4303</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>4301</v>
+        <v>4304</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>4300</v>
+        <v>4303</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="8" t="s">
         <v>3754</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>4302</v>
+        <v>4305</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>4303</v>
+        <v>4306</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>4302</v>
+        <v>4305</v>
       </c>
       <c r="J34" s="9"/>
       <c r="K34" s="14" t="s">
         <v>3754</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>4304</v>
+        <v>4307</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>4305</v>
+        <v>4308</v>
       </c>
       <c r="N34" s="16" t="s">
-        <v>4304</v>
+        <v>4307</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
@@ -44101,39 +44168,39 @@
         <v>3724</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>4306</v>
+        <v>4309</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>4301</v>
+        <v>4304</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>4279</v>
+        <v>4282</v>
       </c>
       <c r="E36" s="12"/>
       <c r="F36" s="8" t="s">
         <v>3724</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>4307</v>
+        <v>4310</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>4303</v>
+        <v>4306</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>4281</v>
+        <v>4284</v>
       </c>
       <c r="J36" s="9"/>
       <c r="K36" s="14" t="s">
         <v>3724</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>4308</v>
+        <v>4311</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>4290</v>
+        <v>4293</v>
       </c>
       <c r="N36" s="16" t="s">
-        <v>4283</v>
+        <v>4286</v>
       </c>
     </row>
     <row r="37" ht="18.75" customHeight="1">
@@ -44141,21 +44208,21 @@
         <v>3735</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>4286</v>
+        <v>4289</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="8" t="s">
         <v>3735</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>4288</v>
+        <v>4291</v>
       </c>
       <c r="J37" s="10"/>
       <c r="K37" s="17" t="s">
         <v>3735</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>4290</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
@@ -44163,21 +44230,21 @@
         <v>3742</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>4291</v>
+        <v>4294</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="8" t="s">
         <v>3742</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>4294</v>
+        <v>4297</v>
       </c>
       <c r="J38" s="10"/>
       <c r="K38" s="17" t="s">
         <v>3742</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>4297</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
@@ -44185,21 +44252,21 @@
         <v>3754</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>4286</v>
+        <v>4289</v>
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="8" t="s">
         <v>3754</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>4288</v>
+        <v>4291</v>
       </c>
       <c r="J39" s="10"/>
       <c r="K39" s="17" t="s">
         <v>3754</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>4290</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
@@ -44220,10 +44287,10 @@
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="8" t="s">
-        <v>4309</v>
+        <v>4312</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>4310</v>
+        <v>4313</v>
       </c>
       <c r="E41" s="12"/>
       <c r="F41" s="9"/>
@@ -44268,10 +44335,10 @@
         <v>776</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>4311</v>
+        <v>4314</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>4312</v>
+        <v>4315</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="9"/>
@@ -44289,7 +44356,7 @@
         <v>3735</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>4313</v>
+        <v>4316</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="9"/>
@@ -44307,13 +44374,13 @@
         <v>3742</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>4314</v>
+        <v>4317</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>4315</v>
+        <v>4318</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>4316</v>
+        <v>4319</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="9"/>
@@ -44331,13 +44398,13 @@
         <v>3754</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>4317</v>
+        <v>4320</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>4318</v>
+        <v>4321</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>4317</v>
+        <v>4320</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="9"/>
@@ -44379,13 +44446,13 @@
         <v>3724</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>4319</v>
+        <v>4322</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>4318</v>
+        <v>4321</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>4311</v>
+        <v>4314</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="9"/>
@@ -44403,7 +44470,7 @@
         <v>3735</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>4313</v>
+        <v>4316</v>
       </c>
       <c r="E49" s="12"/>
       <c r="F49" s="9"/>
@@ -44421,7 +44488,7 @@
         <v>3742</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>4314</v>
+        <v>4317</v>
       </c>
       <c r="E50" s="12"/>
       <c r="F50" s="9"/>
@@ -44439,7 +44506,7 @@
         <v>3754</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>4313</v>
+        <v>4316</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="9"/>
@@ -44470,10 +44537,10 @@
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>4320</v>
+        <v>4323</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>4321</v>
+        <v>4324</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="9"/>
@@ -44521,7 +44588,7 @@
         <v>871</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>4322</v>
+        <v>4325</v>
       </c>
       <c r="E55" s="12"/>
       <c r="F55" s="9"/>
@@ -44539,10 +44606,10 @@
         <v>3735</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>4323</v>
+        <v>4326</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>4324</v>
+        <v>4327</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="9"/>
@@ -44560,13 +44627,13 @@
         <v>3742</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>4325</v>
+        <v>4328</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>4326</v>
+        <v>4329</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>4327</v>
+        <v>4330</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="9"/>
@@ -44584,13 +44651,13 @@
         <v>3754</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>4328</v>
+        <v>4331</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>4329</v>
+        <v>4332</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>4328</v>
+        <v>4331</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="9"/>
@@ -44632,10 +44699,10 @@
         <v>3724</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>4330</v>
+        <v>4333</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>4329</v>
+        <v>4332</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>871</v>
@@ -44656,7 +44723,7 @@
         <v>3735</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>4324</v>
+        <v>4327</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="9"/>
@@ -44674,7 +44741,7 @@
         <v>3742</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>4325</v>
+        <v>4328</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="9"/>
@@ -44692,7 +44759,7 @@
         <v>3754</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>4324</v>
+        <v>4327</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="9"/>
@@ -44783,27 +44850,27 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="18" t="s">
-        <v>4331</v>
+        <v>4334</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="20" t="s">
-        <v>4332</v>
+        <v>4335</v>
       </c>
       <c r="D1" s="19"/>
       <c r="E1" s="18" t="s">
-        <v>4333</v>
+        <v>4336</v>
       </c>
       <c r="F1" s="19"/>
       <c r="G1" s="18" t="s">
-        <v>4334</v>
+        <v>4337</v>
       </c>
       <c r="H1" s="19"/>
       <c r="I1" s="18" t="s">
-        <v>4335</v>
+        <v>4338</v>
       </c>
       <c r="J1" s="19"/>
       <c r="K1" s="18" t="s">
-        <v>4336</v>
+        <v>4339</v>
       </c>
       <c r="L1" s="19"/>
       <c r="M1" s="10"/>
@@ -44816,27 +44883,27 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="21" t="s">
-        <v>4337</v>
+        <v>4340</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="10" t="s">
-        <v>4338</v>
+        <v>4341</v>
       </c>
       <c r="D2" s="22"/>
       <c r="E2" s="23" t="s">
-        <v>4339</v>
+        <v>4342</v>
       </c>
       <c r="F2" s="22"/>
       <c r="G2" s="23" t="s">
-        <v>4340</v>
+        <v>4343</v>
       </c>
       <c r="H2" s="22"/>
       <c r="I2" s="23" t="s">
-        <v>4341</v>
+        <v>4344</v>
       </c>
       <c r="J2" s="22"/>
       <c r="K2" s="23" t="s">
-        <v>4342</v>
+        <v>4345</v>
       </c>
       <c r="L2" s="22"/>
       <c r="M2" s="10"/>
@@ -44849,27 +44916,27 @@
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="21" t="s">
-        <v>4343</v>
+        <v>4346</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="10" t="s">
-        <v>4344</v>
+        <v>4347</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="23" t="s">
-        <v>4345</v>
+        <v>4348</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="23" t="s">
-        <v>4346</v>
+        <v>4349</v>
       </c>
       <c r="H3" s="22"/>
       <c r="I3" s="23" t="s">
-        <v>4347</v>
+        <v>4350</v>
       </c>
       <c r="J3" s="22"/>
       <c r="K3" s="23" t="s">
-        <v>4348</v>
+        <v>4351</v>
       </c>
       <c r="L3" s="22"/>
       <c r="M3" s="10"/>
@@ -44882,27 +44949,27 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="21" t="s">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="10" t="s">
-        <v>4350</v>
+        <v>4353</v>
       </c>
       <c r="D4" s="22"/>
       <c r="E4" s="23" t="s">
-        <v>4351</v>
+        <v>4354</v>
       </c>
       <c r="F4" s="22"/>
       <c r="G4" s="23" t="s">
-        <v>4352</v>
+        <v>4355</v>
       </c>
       <c r="H4" s="22"/>
       <c r="I4" s="23" t="s">
-        <v>4353</v>
+        <v>4356</v>
       </c>
       <c r="J4" s="22"/>
       <c r="K4" s="23" t="s">
-        <v>4354</v>
+        <v>4357</v>
       </c>
       <c r="L4" s="22"/>
       <c r="M4" s="10"/>
@@ -44915,38 +44982,38 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>4355</v>
+        <v>4358</v>
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="L5" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
@@ -44961,37 +45028,37 @@
         <v>4128</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>665</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>4359</v>
+        <v>4362</v>
       </c>
       <c r="E6" s="23" t="s">
         <v>957</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>4360</v>
+        <v>4363</v>
       </c>
       <c r="G6" s="23" t="s">
         <v>1640</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="I6" s="23" t="s">
         <v>2782</v>
       </c>
       <c r="J6" s="25" t="s">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="K6" s="23" t="s">
         <v>2979</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>4363</v>
+        <v>4366</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
@@ -45007,34 +45074,34 @@
         <v>3684</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>4364</v>
+        <v>4367</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>4365</v>
+        <v>4368</v>
       </c>
       <c r="E7" s="23" t="s">
         <v>4095</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>4366</v>
+        <v>4369</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>4367</v>
+        <v>4370</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>4368</v>
+        <v>4371</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>4369</v>
+        <v>4372</v>
       </c>
       <c r="J7" s="25" t="s">
-        <v>4370</v>
+        <v>4373</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>4371</v>
+        <v>4374</v>
       </c>
       <c r="L7" s="25" t="s">
-        <v>4372</v>
+        <v>4375</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
@@ -45047,37 +45114,37 @@
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="26"/>
       <c r="B8" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>4364</v>
+        <v>4367</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>4374</v>
+        <v>4377</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>4095</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>4375</v>
+        <v>4378</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>4367</v>
+        <v>4370</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>4376</v>
+        <v>4379</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>4369</v>
+        <v>4372</v>
       </c>
       <c r="J8" s="25" t="s">
-        <v>4377</v>
+        <v>4380</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>4371</v>
+        <v>4374</v>
       </c>
       <c r="L8" s="25" t="s">
-        <v>4378</v>
+        <v>4381</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
@@ -45095,34 +45162,34 @@
         <v>3524</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>4379</v>
+        <v>4382</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>4380</v>
+        <v>4383</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>4109</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>4381</v>
+        <v>4384</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>4382</v>
+        <v>4385</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>4383</v>
+        <v>4386</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>4384</v>
+        <v>4387</v>
       </c>
       <c r="J9" s="25" t="s">
-        <v>4385</v>
+        <v>4388</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>4386</v>
+        <v>4389</v>
       </c>
       <c r="L9" s="25" t="s">
-        <v>4387</v>
+        <v>4390</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
@@ -45138,34 +45205,34 @@
         <v>3638</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>4388</v>
+        <v>4391</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>4389</v>
+        <v>4392</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>4390</v>
+        <v>4393</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>4391</v>
+        <v>4394</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>4392</v>
+        <v>4395</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>4393</v>
+        <v>4396</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>4394</v>
+        <v>4397</v>
       </c>
       <c r="J10" s="25" t="s">
-        <v>4395</v>
+        <v>4398</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>4396</v>
+        <v>4399</v>
       </c>
       <c r="L10" s="25" t="s">
-        <v>4397</v>
+        <v>4400</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
@@ -45178,37 +45245,37 @@
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="26"/>
       <c r="B11" s="24" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>4399</v>
+        <v>4402</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>4400</v>
+        <v>4403</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>4401</v>
+        <v>4404</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>4402</v>
+        <v>4405</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>4403</v>
+        <v>4406</v>
       </c>
       <c r="H11" s="25" t="s">
-        <v>4404</v>
+        <v>4407</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>4405</v>
+        <v>4408</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>4406</v>
+        <v>4409</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>4407</v>
+        <v>4410</v>
       </c>
       <c r="L11" s="28" t="s">
-        <v>4408</v>
+        <v>4411</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
@@ -45220,14 +45287,14 @@
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="21" t="s">
-        <v>4409</v>
+        <v>4412</v>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E12" s="29"/>
       <c r="F12" s="30"/>
@@ -45250,13 +45317,13 @@
         <v>4128</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>4410</v>
+        <v>4413</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>4411</v>
+        <v>4414</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="10"/>
@@ -45300,7 +45367,7 @@
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="26"/>
       <c r="B15" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C15" s="26"/>
       <c r="D15" s="22"/>
@@ -45328,10 +45395,10 @@
         <v>3524</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>4412</v>
+        <v>4415</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>4413</v>
+        <v>4416</v>
       </c>
       <c r="E16" s="23"/>
       <c r="F16" s="10"/>
@@ -45355,10 +45422,10 @@
         <v>3638</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>4414</v>
+        <v>4417</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>4415</v>
+        <v>4418</v>
       </c>
       <c r="E17" s="23"/>
       <c r="F17" s="10"/>
@@ -45379,7 +45446,7 @@
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="31"/>
       <c r="B18" s="32" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C18" s="33"/>
       <c r="D18" s="34"/>
@@ -45422,27 +45489,27 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>4416</v>
+        <v>4419</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="20" t="s">
-        <v>4417</v>
+        <v>4420</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="18" t="s">
-        <v>4418</v>
+        <v>4421</v>
       </c>
       <c r="F20" s="19"/>
       <c r="G20" s="18" t="s">
-        <v>4419</v>
+        <v>4422</v>
       </c>
       <c r="H20" s="19"/>
       <c r="I20" s="18" t="s">
-        <v>4420</v>
+        <v>4423</v>
       </c>
       <c r="J20" s="19"/>
       <c r="K20" s="18" t="s">
-        <v>4421</v>
+        <v>4424</v>
       </c>
       <c r="L20" s="19"/>
       <c r="M20" s="10"/>
@@ -45455,27 +45522,27 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="21" t="s">
-        <v>4337</v>
+        <v>4340</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="10" t="s">
-        <v>4422</v>
+        <v>4425</v>
       </c>
       <c r="D21" s="22"/>
       <c r="E21" s="23" t="s">
-        <v>4423</v>
+        <v>4426</v>
       </c>
       <c r="F21" s="22"/>
       <c r="G21" s="23" t="s">
-        <v>4424</v>
+        <v>4427</v>
       </c>
       <c r="H21" s="22"/>
       <c r="I21" s="23" t="s">
-        <v>4425</v>
+        <v>4428</v>
       </c>
       <c r="J21" s="22"/>
       <c r="K21" s="23" t="s">
-        <v>4426</v>
+        <v>4429</v>
       </c>
       <c r="L21" s="22"/>
       <c r="M21" s="10"/>
@@ -45488,27 +45555,27 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="21" t="s">
-        <v>4343</v>
+        <v>4346</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="10" t="s">
-        <v>4427</v>
+        <v>4430</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="23" t="s">
-        <v>4428</v>
+        <v>4431</v>
       </c>
       <c r="F22" s="22"/>
       <c r="G22" s="23" t="s">
-        <v>4429</v>
+        <v>4432</v>
       </c>
       <c r="H22" s="22"/>
       <c r="I22" s="23" t="s">
-        <v>4430</v>
+        <v>4433</v>
       </c>
       <c r="J22" s="22"/>
       <c r="K22" s="23" t="s">
-        <v>4431</v>
+        <v>4434</v>
       </c>
       <c r="L22" s="22"/>
       <c r="M22" s="10"/>
@@ -45521,27 +45588,27 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="10" t="s">
-        <v>4432</v>
+        <v>4435</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="23" t="s">
-        <v>4433</v>
+        <v>4436</v>
       </c>
       <c r="F23" s="22"/>
       <c r="G23" s="23" t="s">
-        <v>4434</v>
+        <v>4437</v>
       </c>
       <c r="H23" s="22"/>
       <c r="I23" s="23" t="s">
-        <v>4435</v>
+        <v>4438</v>
       </c>
       <c r="J23" s="22"/>
       <c r="K23" s="23" t="s">
-        <v>4436</v>
+        <v>4439</v>
       </c>
       <c r="L23" s="22"/>
       <c r="M23" s="10"/>
@@ -45554,38 +45621,38 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>4355</v>
+        <v>4358</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="I24" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="J24" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="K24" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="L24" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
@@ -45600,37 +45667,37 @@
         <v>4128</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>4437</v>
+        <v>4440</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>4438</v>
+        <v>4441</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>4439</v>
+        <v>4442</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>4440</v>
+        <v>4443</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>4441</v>
+        <v>4444</v>
       </c>
       <c r="H25" s="25" t="s">
-        <v>4442</v>
+        <v>4445</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>4443</v>
+        <v>4446</v>
       </c>
       <c r="J25" s="25" t="s">
-        <v>4444</v>
+        <v>4447</v>
       </c>
       <c r="K25" s="23" t="s">
-        <v>4445</v>
+        <v>4448</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>4446</v>
+        <v>4449</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
@@ -45646,34 +45713,34 @@
         <v>3684</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>4447</v>
+        <v>4450</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>4448</v>
+        <v>4451</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>4449</v>
+        <v>4452</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>4450</v>
+        <v>4453</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>4451</v>
+        <v>4454</v>
       </c>
       <c r="H26" s="25" t="s">
-        <v>4452</v>
+        <v>4455</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>4453</v>
+        <v>4456</v>
       </c>
       <c r="J26" s="25" t="s">
-        <v>4454</v>
+        <v>4457</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>4455</v>
+        <v>4458</v>
       </c>
       <c r="L26" s="25" t="s">
-        <v>4456</v>
+        <v>4459</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10"/>
@@ -45686,37 +45753,37 @@
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="26"/>
       <c r="B27" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>4447</v>
+        <v>4450</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>4457</v>
+        <v>4460</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>4449</v>
+        <v>4452</v>
       </c>
       <c r="F27" s="25" t="s">
+        <v>4461</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>4454</v>
+      </c>
+      <c r="H27" s="25" t="s">
+        <v>4462</v>
+      </c>
+      <c r="I27" s="23" t="s">
+        <v>4456</v>
+      </c>
+      <c r="J27" s="25" t="s">
+        <v>4463</v>
+      </c>
+      <c r="K27" s="23" t="s">
         <v>4458</v>
       </c>
-      <c r="G27" s="23" t="s">
-        <v>4451</v>
-      </c>
-      <c r="H27" s="25" t="s">
-        <v>4459</v>
-      </c>
-      <c r="I27" s="23" t="s">
-        <v>4453</v>
-      </c>
-      <c r="J27" s="25" t="s">
-        <v>4460</v>
-      </c>
-      <c r="K27" s="23" t="s">
-        <v>4455</v>
-      </c>
       <c r="L27" s="25" t="s">
-        <v>4461</v>
+        <v>4464</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
@@ -45734,34 +45801,34 @@
         <v>3524</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>4462</v>
+        <v>4465</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>4463</v>
+        <v>4466</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>4464</v>
+        <v>4467</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>4465</v>
+        <v>4468</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>4466</v>
+        <v>4469</v>
       </c>
       <c r="H28" s="25" t="s">
-        <v>4467</v>
+        <v>4470</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>4468</v>
+        <v>4471</v>
       </c>
       <c r="J28" s="25" t="s">
-        <v>4469</v>
+        <v>4472</v>
       </c>
       <c r="K28" s="23" t="s">
-        <v>4470</v>
+        <v>4473</v>
       </c>
       <c r="L28" s="25" t="s">
-        <v>4471</v>
+        <v>4474</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
@@ -45776,34 +45843,34 @@
         <v>3638</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>4472</v>
+        <v>4475</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>4473</v>
+        <v>4476</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>4474</v>
+        <v>4477</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>4475</v>
+        <v>4478</v>
       </c>
       <c r="G29" s="23" t="s">
-        <v>4476</v>
+        <v>4479</v>
       </c>
       <c r="H29" s="25" t="s">
-        <v>4477</v>
+        <v>4480</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>4478</v>
+        <v>4481</v>
       </c>
       <c r="J29" s="25" t="s">
-        <v>4479</v>
+        <v>4482</v>
       </c>
       <c r="K29" s="23" t="s">
-        <v>4480</v>
+        <v>4483</v>
       </c>
       <c r="L29" s="25" t="s">
-        <v>4481</v>
+        <v>4484</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
@@ -45815,37 +45882,37 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="B30" s="24" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>4482</v>
+        <v>4485</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>4483</v>
+        <v>4486</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>4484</v>
+        <v>4487</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>4485</v>
+        <v>4488</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>4486</v>
+        <v>4489</v>
       </c>
       <c r="H30" s="25" t="s">
-        <v>4487</v>
+        <v>4490</v>
       </c>
       <c r="I30" s="23" t="s">
-        <v>4488</v>
+        <v>4491</v>
       </c>
       <c r="J30" s="25" t="s">
-        <v>4489</v>
+        <v>4492</v>
       </c>
       <c r="K30" s="23" t="s">
-        <v>4490</v>
+        <v>4493</v>
       </c>
       <c r="L30" s="25" t="s">
-        <v>4491</v>
+        <v>4494</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
@@ -45857,7 +45924,7 @@
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="21" t="s">
-        <v>4409</v>
+        <v>4412</v>
       </c>
       <c r="B31" s="22"/>
       <c r="C31" s="29"/>
@@ -45869,10 +45936,10 @@
       <c r="I31" s="30"/>
       <c r="J31" s="35"/>
       <c r="K31" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="L31" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
@@ -45887,7 +45954,7 @@
         <v>4128</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C32" s="23"/>
       <c r="D32" s="10"/>
@@ -45898,10 +45965,10 @@
       <c r="I32" s="10"/>
       <c r="J32" s="25"/>
       <c r="K32" s="10" t="s">
-        <v>4492</v>
+        <v>4495</v>
       </c>
       <c r="L32" s="25" t="s">
-        <v>4493</v>
+        <v>4496</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
@@ -45936,7 +46003,7 @@
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="26"/>
       <c r="B34" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C34" s="23"/>
       <c r="D34" s="10"/>
@@ -45971,10 +46038,10 @@
       <c r="I35" s="10"/>
       <c r="J35" s="25"/>
       <c r="K35" s="10" t="s">
-        <v>4494</v>
+        <v>4497</v>
       </c>
       <c r="L35" s="25" t="s">
-        <v>4495</v>
+        <v>4498</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
@@ -45998,10 +46065,10 @@
       <c r="I36" s="10"/>
       <c r="J36" s="25"/>
       <c r="K36" s="10" t="s">
-        <v>4496</v>
+        <v>4499</v>
       </c>
       <c r="L36" s="25" t="s">
-        <v>4497</v>
+        <v>4500</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10"/>
@@ -46014,7 +46081,7 @@
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="31"/>
       <c r="B37" s="32" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C37" s="23"/>
       <c r="D37" s="10"/>
@@ -46059,15 +46126,15 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="18" t="s">
-        <v>4498</v>
+        <v>4501</v>
       </c>
       <c r="D39" s="19"/>
       <c r="E39" s="18" t="s">
-        <v>4499</v>
+        <v>4502</v>
       </c>
       <c r="F39" s="19"/>
       <c r="G39" s="18" t="s">
-        <v>4500</v>
+        <v>4503</v>
       </c>
       <c r="H39" s="19"/>
       <c r="I39" s="10"/>
@@ -46086,15 +46153,15 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="23" t="s">
-        <v>4501</v>
+        <v>4504</v>
       </c>
       <c r="D40" s="22"/>
       <c r="E40" s="23" t="s">
-        <v>4502</v>
+        <v>4505</v>
       </c>
       <c r="F40" s="22"/>
       <c r="G40" s="23" t="s">
-        <v>4503</v>
+        <v>4506</v>
       </c>
       <c r="H40" s="22"/>
       <c r="I40" s="10"/>
@@ -46113,15 +46180,15 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="23" t="s">
-        <v>4504</v>
+        <v>4507</v>
       </c>
       <c r="D41" s="22"/>
       <c r="E41" s="23" t="s">
-        <v>4505</v>
+        <v>4508</v>
       </c>
       <c r="F41" s="22"/>
       <c r="G41" s="23" t="s">
-        <v>4506</v>
+        <v>4509</v>
       </c>
       <c r="H41" s="22"/>
       <c r="I41" s="10"/>
@@ -46140,15 +46207,15 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="23" t="s">
-        <v>4507</v>
+        <v>4510</v>
       </c>
       <c r="D42" s="22"/>
       <c r="E42" s="23" t="s">
-        <v>4508</v>
+        <v>4511</v>
       </c>
       <c r="F42" s="22"/>
       <c r="G42" s="23" t="s">
-        <v>4509</v>
+        <v>4512</v>
       </c>
       <c r="H42" s="22"/>
       <c r="I42" s="10"/>
@@ -46167,22 +46234,22 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E43" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="G43" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>
@@ -46200,22 +46267,22 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="23" t="s">
-        <v>4510</v>
+        <v>4513</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>4511</v>
+        <v>4514</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>4512</v>
+        <v>4515</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>4513</v>
+        <v>4516</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>4514</v>
+        <v>4517</v>
       </c>
       <c r="H44" s="25" t="s">
-        <v>4515</v>
+        <v>4518</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" s="10"/>
@@ -46233,22 +46300,22 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="23" t="s">
-        <v>4516</v>
+        <v>4519</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>4517</v>
+        <v>4520</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>4518</v>
+        <v>4521</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>4519</v>
+        <v>4522</v>
       </c>
       <c r="G45" s="23" t="s">
-        <v>4520</v>
+        <v>4523</v>
       </c>
       <c r="H45" s="25" t="s">
-        <v>4521</v>
+        <v>4524</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
@@ -46266,22 +46333,22 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="23" t="s">
-        <v>4516</v>
+        <v>4519</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>4522</v>
+        <v>4525</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>4518</v>
+        <v>4521</v>
       </c>
       <c r="F46" s="25" t="s">
+        <v>4526</v>
+      </c>
+      <c r="G46" s="23" t="s">
         <v>4523</v>
       </c>
-      <c r="G46" s="23" t="s">
-        <v>4520</v>
-      </c>
       <c r="H46" s="25" t="s">
-        <v>4524</v>
+        <v>4527</v>
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
@@ -46299,22 +46366,22 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="23" t="s">
-        <v>4525</v>
+        <v>4528</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>4526</v>
+        <v>4529</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>4527</v>
+        <v>4530</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>4528</v>
+        <v>4531</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>4529</v>
+        <v>4532</v>
       </c>
       <c r="H47" s="25" t="s">
-        <v>4530</v>
+        <v>4533</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
@@ -46332,22 +46399,22 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="23" t="s">
-        <v>4531</v>
+        <v>4534</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>4532</v>
+        <v>4535</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>4533</v>
+        <v>4536</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>4534</v>
+        <v>4537</v>
       </c>
       <c r="G48" s="23" t="s">
-        <v>4535</v>
+        <v>4538</v>
       </c>
       <c r="H48" s="25" t="s">
-        <v>4536</v>
+        <v>4539</v>
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
@@ -46365,22 +46432,22 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="36" t="s">
-        <v>4537</v>
+        <v>4540</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>4538</v>
+        <v>4541</v>
       </c>
       <c r="E49" s="36" t="s">
-        <v>4539</v>
+        <v>4542</v>
       </c>
       <c r="F49" s="28" t="s">
-        <v>4540</v>
+        <v>4543</v>
       </c>
       <c r="G49" s="36" t="s">
-        <v>4541</v>
+        <v>4544</v>
       </c>
       <c r="H49" s="28" t="s">
-        <v>4542</v>
+        <v>4545</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
@@ -46421,23 +46488,23 @@
       </c>
       <c r="B51" s="19"/>
       <c r="C51" s="18" t="s">
-        <v>4543</v>
+        <v>4546</v>
       </c>
       <c r="D51" s="19"/>
       <c r="E51" s="20" t="s">
-        <v>4544</v>
+        <v>4547</v>
       </c>
       <c r="F51" s="19"/>
       <c r="G51" s="18" t="s">
-        <v>4545</v>
+        <v>4548</v>
       </c>
       <c r="H51" s="19"/>
       <c r="I51" s="18" t="s">
-        <v>4546</v>
+        <v>4549</v>
       </c>
       <c r="J51" s="19"/>
       <c r="K51" s="18" t="s">
-        <v>4547</v>
+        <v>4550</v>
       </c>
       <c r="L51" s="19"/>
       <c r="M51" s="10"/>
@@ -46450,27 +46517,27 @@
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" s="21" t="s">
-        <v>4337</v>
+        <v>4340</v>
       </c>
       <c r="B52" s="22"/>
       <c r="C52" s="10" t="s">
-        <v>4548</v>
+        <v>4551</v>
       </c>
       <c r="D52" s="22"/>
       <c r="E52" s="10" t="s">
-        <v>4549</v>
+        <v>4552</v>
       </c>
       <c r="F52" s="22"/>
       <c r="G52" s="23" t="s">
-        <v>4550</v>
+        <v>4553</v>
       </c>
       <c r="H52" s="22"/>
       <c r="I52" s="23" t="s">
-        <v>4551</v>
+        <v>4554</v>
       </c>
       <c r="J52" s="22"/>
       <c r="K52" s="23" t="s">
-        <v>4552</v>
+        <v>4555</v>
       </c>
       <c r="L52" s="22"/>
       <c r="M52" s="10"/>
@@ -46483,27 +46550,27 @@
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" s="21" t="s">
-        <v>4343</v>
+        <v>4346</v>
       </c>
       <c r="B53" s="22"/>
       <c r="C53" s="10" t="s">
-        <v>4553</v>
+        <v>4556</v>
       </c>
       <c r="D53" s="22"/>
       <c r="E53" s="10" t="s">
-        <v>4554</v>
+        <v>4557</v>
       </c>
       <c r="F53" s="22"/>
       <c r="G53" s="23" t="s">
-        <v>4555</v>
+        <v>4558</v>
       </c>
       <c r="H53" s="22"/>
       <c r="I53" s="23" t="s">
-        <v>4556</v>
+        <v>4559</v>
       </c>
       <c r="J53" s="22"/>
       <c r="K53" s="23" t="s">
-        <v>4557</v>
+        <v>4560</v>
       </c>
       <c r="L53" s="22"/>
       <c r="M53" s="10"/>
@@ -46516,27 +46583,27 @@
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" s="21" t="s">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="B54" s="22"/>
       <c r="C54" s="10" t="s">
-        <v>4558</v>
+        <v>4561</v>
       </c>
       <c r="D54" s="22"/>
       <c r="E54" s="10" t="s">
-        <v>4559</v>
+        <v>4562</v>
       </c>
       <c r="F54" s="22"/>
       <c r="G54" s="23" t="s">
-        <v>4560</v>
+        <v>4563</v>
       </c>
       <c r="H54" s="22"/>
       <c r="I54" s="23" t="s">
-        <v>4561</v>
+        <v>4564</v>
       </c>
       <c r="J54" s="22"/>
       <c r="K54" s="23" t="s">
-        <v>4562</v>
+        <v>4565</v>
       </c>
       <c r="L54" s="22"/>
       <c r="M54" s="10"/>
@@ -46549,38 +46616,38 @@
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" s="21" t="s">
-        <v>4355</v>
+        <v>4358</v>
       </c>
       <c r="B55" s="22"/>
       <c r="C55" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D55" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="F55" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="G55" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="I55" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="J55" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="K55" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="L55" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10"/>
@@ -46595,37 +46662,37 @@
         <v>4128</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>4563</v>
+        <v>4566</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>4564</v>
+        <v>4567</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>4565</v>
+        <v>4568</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>4566</v>
+        <v>4569</v>
       </c>
       <c r="G56" s="23" t="s">
-        <v>4567</v>
+        <v>4570</v>
       </c>
       <c r="H56" s="25" t="s">
-        <v>4568</v>
+        <v>4571</v>
       </c>
       <c r="I56" s="23" t="s">
-        <v>4569</v>
+        <v>4572</v>
       </c>
       <c r="J56" s="25" t="s">
-        <v>4570</v>
+        <v>4573</v>
       </c>
       <c r="K56" s="23" t="s">
-        <v>4571</v>
+        <v>4574</v>
       </c>
       <c r="L56" s="25" t="s">
-        <v>4572</v>
+        <v>4575</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10"/>
@@ -46641,34 +46708,34 @@
         <v>3684</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>4573</v>
+        <v>4576</v>
       </c>
       <c r="D57" s="25" t="s">
-        <v>4574</v>
+        <v>4577</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>4575</v>
+        <v>4578</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>4576</v>
+        <v>4579</v>
       </c>
       <c r="G57" s="23" t="s">
-        <v>4577</v>
+        <v>4580</v>
       </c>
       <c r="H57" s="25" t="s">
-        <v>4578</v>
+        <v>4581</v>
       </c>
       <c r="I57" s="23" t="s">
-        <v>4579</v>
+        <v>4582</v>
       </c>
       <c r="J57" s="25" t="s">
-        <v>4580</v>
+        <v>4583</v>
       </c>
       <c r="K57" s="23" t="s">
-        <v>4581</v>
+        <v>4584</v>
       </c>
       <c r="L57" s="25" t="s">
-        <v>4582</v>
+        <v>4585</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10"/>
@@ -46681,37 +46748,37 @@
     <row r="58" ht="18.75" customHeight="1">
       <c r="A58" s="26"/>
       <c r="B58" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>4573</v>
+        <v>4576</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>4583</v>
+        <v>4586</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>4575</v>
+        <v>4578</v>
       </c>
       <c r="F58" s="25" t="s">
+        <v>4587</v>
+      </c>
+      <c r="G58" s="23" t="s">
+        <v>4580</v>
+      </c>
+      <c r="H58" s="25" t="s">
+        <v>4588</v>
+      </c>
+      <c r="I58" s="23" t="s">
+        <v>4582</v>
+      </c>
+      <c r="J58" s="25" t="s">
+        <v>4589</v>
+      </c>
+      <c r="K58" s="23" t="s">
         <v>4584</v>
       </c>
-      <c r="G58" s="23" t="s">
-        <v>4577</v>
-      </c>
-      <c r="H58" s="25" t="s">
-        <v>4585</v>
-      </c>
-      <c r="I58" s="23" t="s">
-        <v>4579</v>
-      </c>
-      <c r="J58" s="25" t="s">
-        <v>4586</v>
-      </c>
-      <c r="K58" s="23" t="s">
-        <v>4581</v>
-      </c>
       <c r="L58" s="25" t="s">
-        <v>4587</v>
+        <v>4590</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10"/>
@@ -46729,34 +46796,34 @@
         <v>3524</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>4588</v>
+        <v>4591</v>
       </c>
       <c r="D59" s="25" t="s">
         <v>3031</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>4589</v>
+        <v>4592</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>4590</v>
+        <v>4593</v>
       </c>
       <c r="G59" s="23" t="s">
-        <v>4591</v>
+        <v>4594</v>
       </c>
       <c r="H59" s="25" t="s">
-        <v>4592</v>
+        <v>4595</v>
       </c>
       <c r="I59" s="23" t="s">
-        <v>4593</v>
+        <v>4596</v>
       </c>
       <c r="J59" s="25" t="s">
-        <v>4594</v>
+        <v>4597</v>
       </c>
       <c r="K59" s="23" t="s">
-        <v>4595</v>
+        <v>4598</v>
       </c>
       <c r="L59" s="25" t="s">
-        <v>4596</v>
+        <v>4599</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10"/>
@@ -46771,34 +46838,34 @@
         <v>3638</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>4597</v>
+        <v>4600</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>4598</v>
+        <v>4601</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>4599</v>
+        <v>4602</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>4600</v>
+        <v>4603</v>
       </c>
       <c r="G60" s="23" t="s">
-        <v>4601</v>
+        <v>4604</v>
       </c>
       <c r="H60" s="25" t="s">
-        <v>4602</v>
+        <v>4605</v>
       </c>
       <c r="I60" s="23" t="s">
-        <v>4603</v>
+        <v>4606</v>
       </c>
       <c r="J60" s="25" t="s">
-        <v>4604</v>
+        <v>4607</v>
       </c>
       <c r="K60" s="23" t="s">
-        <v>4605</v>
+        <v>4608</v>
       </c>
       <c r="L60" s="25" t="s">
-        <v>4606</v>
+        <v>4609</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10"/>
@@ -46810,37 +46877,37 @@
     </row>
     <row r="61" ht="18.75" customHeight="1">
       <c r="B61" s="24" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>4607</v>
+        <v>4610</v>
       </c>
       <c r="D61" s="25" t="s">
-        <v>4608</v>
+        <v>4611</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>4609</v>
+        <v>4612</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>4610</v>
+        <v>4613</v>
       </c>
       <c r="G61" s="23" t="s">
-        <v>4611</v>
+        <v>4614</v>
       </c>
       <c r="H61" s="25" t="s">
-        <v>4612</v>
+        <v>4615</v>
       </c>
       <c r="I61" s="23" t="s">
-        <v>4613</v>
+        <v>4616</v>
       </c>
       <c r="J61" s="25" t="s">
-        <v>4614</v>
+        <v>4617</v>
       </c>
       <c r="K61" s="23" t="s">
-        <v>4615</v>
+        <v>4618</v>
       </c>
       <c r="L61" s="25" t="s">
-        <v>4616</v>
+        <v>4619</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10"/>
@@ -46852,22 +46919,22 @@
     </row>
     <row r="62" ht="18.75" customHeight="1">
       <c r="A62" s="21" t="s">
-        <v>4409</v>
+        <v>4412</v>
       </c>
       <c r="B62" s="22"/>
       <c r="C62" s="37"/>
       <c r="D62" s="35"/>
       <c r="E62" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="I62" s="30"/>
       <c r="J62" s="38"/>
@@ -46886,21 +46953,21 @@
         <v>4128</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C63" s="39"/>
       <c r="D63" s="25"/>
       <c r="E63" s="23" t="s">
-        <v>4617</v>
+        <v>4620</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>4618</v>
+        <v>4621</v>
       </c>
       <c r="G63" s="23" t="s">
-        <v>4619</v>
+        <v>4622</v>
       </c>
       <c r="H63" s="25" t="s">
-        <v>4620</v>
+        <v>4623</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="40"/>
@@ -46940,7 +47007,7 @@
     <row r="65" ht="18.75" customHeight="1">
       <c r="A65" s="26"/>
       <c r="B65" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C65" s="39"/>
       <c r="D65" s="25"/>
@@ -46970,16 +47037,16 @@
       <c r="C66" s="39"/>
       <c r="D66" s="25"/>
       <c r="E66" s="10" t="s">
-        <v>4621</v>
+        <v>4624</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>4622</v>
+        <v>4625</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>4623</v>
+        <v>4626</v>
       </c>
       <c r="H66" s="25" t="s">
-        <v>4624</v>
+        <v>4627</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="40"/>
@@ -47001,16 +47068,16 @@
       <c r="C67" s="39"/>
       <c r="D67" s="25"/>
       <c r="E67" s="10" t="s">
-        <v>4625</v>
+        <v>4628</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>4626</v>
+        <v>4629</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>4627</v>
+        <v>4630</v>
       </c>
       <c r="H67" s="25" t="s">
-        <v>4628</v>
+        <v>4631</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="40"/>
@@ -47027,7 +47094,7 @@
     <row r="68" ht="18.75" customHeight="1">
       <c r="A68" s="31"/>
       <c r="B68" s="32" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C68" s="39"/>
       <c r="D68" s="25"/>
@@ -47091,139 +47158,139 @@
     </row>
     <row r="71" ht="18.75" customHeight="1">
       <c r="A71" s="18" t="s">
-        <v>4629</v>
+        <v>4632</v>
       </c>
       <c r="B71" s="19"/>
       <c r="C71" s="20" t="s">
-        <v>4630</v>
+        <v>4633</v>
       </c>
       <c r="D71" s="19"/>
       <c r="E71" s="18" t="s">
-        <v>4631</v>
+        <v>4634</v>
       </c>
       <c r="F71" s="41"/>
       <c r="G71" s="18" t="s">
-        <v>4632</v>
+        <v>4635</v>
       </c>
       <c r="H71" s="41"/>
       <c r="I71" s="18" t="s">
-        <v>4633</v>
+        <v>4636</v>
       </c>
       <c r="J71" s="19"/>
       <c r="K71" s="18" t="s">
-        <v>4634</v>
+        <v>4637</v>
       </c>
       <c r="L71" s="19"/>
     </row>
     <row r="72" ht="18.75" customHeight="1">
       <c r="A72" s="21" t="s">
-        <v>4337</v>
+        <v>4340</v>
       </c>
       <c r="B72" s="22"/>
       <c r="C72" s="10" t="s">
-        <v>4635</v>
+        <v>4638</v>
       </c>
       <c r="D72" s="22"/>
       <c r="E72" s="10" t="s">
-        <v>4636</v>
+        <v>4639</v>
       </c>
       <c r="F72" s="22"/>
       <c r="G72" s="10" t="s">
-        <v>4637</v>
+        <v>4640</v>
       </c>
       <c r="I72" s="23" t="s">
-        <v>4638</v>
+        <v>4641</v>
       </c>
       <c r="J72" s="22"/>
       <c r="K72" s="23" t="s">
-        <v>4639</v>
+        <v>4642</v>
       </c>
       <c r="L72" s="22"/>
     </row>
     <row r="73" ht="18.75" customHeight="1">
       <c r="A73" s="21" t="s">
-        <v>4343</v>
+        <v>4346</v>
       </c>
       <c r="B73" s="22"/>
       <c r="C73" s="10" t="s">
-        <v>4640</v>
+        <v>4643</v>
       </c>
       <c r="D73" s="22"/>
       <c r="E73" s="10" t="s">
-        <v>4641</v>
+        <v>4644</v>
       </c>
       <c r="F73" s="22"/>
       <c r="G73" s="10" t="s">
-        <v>4642</v>
+        <v>4645</v>
       </c>
       <c r="I73" s="23" t="s">
-        <v>4643</v>
+        <v>4646</v>
       </c>
       <c r="J73" s="22"/>
       <c r="K73" s="23" t="s">
-        <v>4644</v>
+        <v>4647</v>
       </c>
       <c r="L73" s="22"/>
     </row>
     <row r="74" ht="18.75" customHeight="1">
       <c r="A74" s="21" t="s">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="B74" s="22"/>
       <c r="C74" s="10" t="s">
-        <v>4645</v>
+        <v>4648</v>
       </c>
       <c r="D74" s="22"/>
       <c r="E74" s="10" t="s">
-        <v>4646</v>
+        <v>4649</v>
       </c>
       <c r="F74" s="22"/>
       <c r="G74" s="10" t="s">
-        <v>4647</v>
+        <v>4650</v>
       </c>
       <c r="I74" s="23" t="s">
-        <v>4648</v>
+        <v>4651</v>
       </c>
       <c r="J74" s="22"/>
       <c r="K74" s="23" t="s">
-        <v>4649</v>
+        <v>4652</v>
       </c>
       <c r="L74" s="22"/>
     </row>
     <row r="75" ht="18.75" customHeight="1">
       <c r="A75" s="21" t="s">
-        <v>4355</v>
+        <v>4358</v>
       </c>
       <c r="B75" s="22"/>
       <c r="C75" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D75" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="F75" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="I75" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="J75" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="K75" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="L75" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
     </row>
     <row r="76" ht="18.75" customHeight="1">
@@ -47231,37 +47298,37 @@
         <v>4128</v>
       </c>
       <c r="B76" s="24" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>4650</v>
+        <v>4653</v>
       </c>
       <c r="D76" s="25" t="s">
         <v>3360</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>4651</v>
+        <v>4654</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>4652</v>
+        <v>4655</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>4653</v>
+        <v>4656</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>4654</v>
+        <v>4657</v>
       </c>
       <c r="I76" s="23" t="s">
-        <v>4655</v>
+        <v>4658</v>
       </c>
       <c r="J76" s="25" t="s">
-        <v>4656</v>
+        <v>4659</v>
       </c>
       <c r="K76" s="23" t="s">
-        <v>4657</v>
+        <v>4660</v>
       </c>
       <c r="L76" s="25" t="s">
-        <v>4658</v>
+        <v>4661</v>
       </c>
     </row>
     <row r="77" ht="18.75" customHeight="1">
@@ -47270,70 +47337,70 @@
         <v>3684</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>4659</v>
+        <v>4662</v>
       </c>
       <c r="D77" s="25" t="s">
-        <v>4660</v>
+        <v>4663</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>4661</v>
+        <v>4664</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>4662</v>
+        <v>4665</v>
       </c>
       <c r="G77" s="10" t="s">
         <v>4145</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>4663</v>
+        <v>4666</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>4664</v>
+        <v>4667</v>
       </c>
       <c r="J77" s="25" t="s">
-        <v>4665</v>
+        <v>4668</v>
       </c>
       <c r="K77" s="23" t="s">
-        <v>4666</v>
+        <v>4669</v>
       </c>
       <c r="L77" s="25" t="s">
-        <v>4667</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="78" ht="18.75" customHeight="1">
       <c r="A78" s="26"/>
       <c r="B78" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>4650</v>
+        <v>4653</v>
       </c>
       <c r="D78" s="25" t="s">
         <v>3360</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>4651</v>
+        <v>4654</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>4652</v>
+        <v>4655</v>
       </c>
       <c r="G78" s="10" t="s">
         <v>4145</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>4654</v>
+        <v>4657</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>4664</v>
+        <v>4667</v>
       </c>
       <c r="J78" s="25" t="s">
-        <v>4656</v>
+        <v>4659</v>
       </c>
       <c r="K78" s="23" t="s">
-        <v>4666</v>
+        <v>4669</v>
       </c>
       <c r="L78" s="25" t="s">
-        <v>4668</v>
+        <v>4671</v>
       </c>
     </row>
     <row r="79" ht="18.75" customHeight="1">
@@ -47344,34 +47411,34 @@
         <v>3524</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>4669</v>
+        <v>4672</v>
       </c>
       <c r="D79" s="25" t="s">
-        <v>4670</v>
+        <v>4673</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>4671</v>
+        <v>4674</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>4672</v>
+        <v>4675</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>4673</v>
+        <v>4676</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>4674</v>
+        <v>4677</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>4675</v>
+        <v>4678</v>
       </c>
       <c r="J79" s="25" t="s">
-        <v>4676</v>
+        <v>4679</v>
       </c>
       <c r="K79" s="23" t="s">
-        <v>4677</v>
+        <v>4680</v>
       </c>
       <c r="L79" s="25" t="s">
-        <v>4678</v>
+        <v>4681</v>
       </c>
     </row>
     <row r="80" ht="18.75" customHeight="1">
@@ -47380,70 +47447,70 @@
         <v>3638</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>4679</v>
+        <v>4682</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>4680</v>
+        <v>4683</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>4681</v>
+        <v>4684</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>4682</v>
+        <v>4685</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>4683</v>
+        <v>4686</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>4684</v>
+        <v>4687</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>4685</v>
+        <v>4688</v>
       </c>
       <c r="J80" s="25" t="s">
-        <v>4686</v>
+        <v>4689</v>
       </c>
       <c r="K80" s="23" t="s">
-        <v>4687</v>
+        <v>4690</v>
       </c>
       <c r="L80" s="25" t="s">
-        <v>4688</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="81" ht="18.75" customHeight="1">
       <c r="A81" s="31"/>
       <c r="B81" s="32" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C81" s="27" t="s">
-        <v>4689</v>
+        <v>4692</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>4690</v>
+        <v>4693</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>4691</v>
+        <v>4694</v>
       </c>
       <c r="F81" s="28" t="s">
-        <v>4692</v>
+        <v>4695</v>
       </c>
       <c r="G81" s="27" t="s">
-        <v>4693</v>
+        <v>4696</v>
       </c>
       <c r="H81" s="27" t="s">
-        <v>4694</v>
+        <v>4697</v>
       </c>
       <c r="I81" s="23" t="s">
-        <v>4695</v>
+        <v>4698</v>
       </c>
       <c r="J81" s="25" t="s">
-        <v>4696</v>
+        <v>4699</v>
       </c>
       <c r="K81" s="23" t="s">
-        <v>4697</v>
+        <v>4700</v>
       </c>
       <c r="L81" s="25" t="s">
-        <v>4698</v>
+        <v>4701</v>
       </c>
     </row>
     <row r="82" ht="18.75" customHeight="1">
@@ -47456,16 +47523,16 @@
       <c r="G82" s="10"/>
       <c r="H82" s="10"/>
       <c r="I82" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="J82" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="K82" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="L82" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10"/>
@@ -47485,16 +47552,16 @@
       <c r="G83" s="10"/>
       <c r="H83" s="10"/>
       <c r="I83" s="23" t="s">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="J83" s="25" t="s">
-        <v>4700</v>
+        <v>4703</v>
       </c>
       <c r="K83" s="23" t="s">
-        <v>4701</v>
+        <v>4704</v>
       </c>
       <c r="L83" s="25" t="s">
-        <v>4702</v>
+        <v>4705</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10"/>
@@ -47556,16 +47623,16 @@
       <c r="G86" s="10"/>
       <c r="H86" s="10"/>
       <c r="I86" s="23" t="s">
-        <v>4703</v>
+        <v>4706</v>
       </c>
       <c r="J86" s="25" t="s">
-        <v>4704</v>
+        <v>4707</v>
       </c>
       <c r="K86" s="23" t="s">
-        <v>4705</v>
+        <v>4708</v>
       </c>
       <c r="L86" s="25" t="s">
-        <v>4706</v>
+        <v>4709</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10"/>
@@ -47585,16 +47652,16 @@
       <c r="G87" s="10"/>
       <c r="H87" s="10"/>
       <c r="I87" s="23" t="s">
-        <v>4707</v>
+        <v>4710</v>
       </c>
       <c r="J87" s="25" t="s">
-        <v>4708</v>
+        <v>4711</v>
       </c>
       <c r="K87" s="23" t="s">
-        <v>4709</v>
+        <v>4712</v>
       </c>
       <c r="L87" s="25" t="s">
-        <v>4710</v>
+        <v>4713</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10"/>
@@ -47648,27 +47715,27 @@
     </row>
     <row r="90" ht="18.75" customHeight="1">
       <c r="A90" s="18" t="s">
-        <v>4711</v>
+        <v>4714</v>
       </c>
       <c r="B90" s="19"/>
       <c r="C90" s="18" t="s">
-        <v>4712</v>
+        <v>4715</v>
       </c>
       <c r="D90" s="19"/>
       <c r="E90" s="18" t="s">
-        <v>4713</v>
+        <v>4716</v>
       </c>
       <c r="F90" s="19"/>
       <c r="G90" s="18" t="s">
-        <v>4714</v>
+        <v>4717</v>
       </c>
       <c r="H90" s="19"/>
       <c r="I90" s="18" t="s">
-        <v>4715</v>
+        <v>4718</v>
       </c>
       <c r="J90" s="19"/>
       <c r="K90" s="18" t="s">
-        <v>4716</v>
+        <v>4719</v>
       </c>
       <c r="L90" s="19"/>
       <c r="M90" s="10"/>
@@ -47681,27 +47748,27 @@
     </row>
     <row r="91" ht="18.75" customHeight="1">
       <c r="A91" s="23" t="s">
-        <v>4717</v>
+        <v>4720</v>
       </c>
       <c r="B91" s="22"/>
       <c r="C91" s="23" t="s">
-        <v>4718</v>
+        <v>4721</v>
       </c>
       <c r="D91" s="22"/>
       <c r="E91" s="23" t="s">
-        <v>4719</v>
+        <v>4722</v>
       </c>
       <c r="F91" s="22"/>
       <c r="G91" s="23" t="s">
-        <v>4720</v>
+        <v>4723</v>
       </c>
       <c r="H91" s="22"/>
       <c r="I91" s="23" t="s">
-        <v>4721</v>
+        <v>4724</v>
       </c>
       <c r="J91" s="22"/>
       <c r="K91" s="23" t="s">
-        <v>4722</v>
+        <v>4725</v>
       </c>
       <c r="L91" s="22"/>
       <c r="M91" s="10"/>
@@ -47714,27 +47781,27 @@
     </row>
     <row r="92" ht="18.75" customHeight="1">
       <c r="A92" s="23" t="s">
-        <v>4723</v>
+        <v>4726</v>
       </c>
       <c r="B92" s="22"/>
       <c r="C92" s="23" t="s">
-        <v>4724</v>
+        <v>4727</v>
       </c>
       <c r="D92" s="22"/>
       <c r="E92" s="23" t="s">
-        <v>4725</v>
+        <v>4728</v>
       </c>
       <c r="F92" s="22"/>
       <c r="G92" s="23" t="s">
-        <v>4726</v>
+        <v>4729</v>
       </c>
       <c r="H92" s="22"/>
       <c r="I92" s="23" t="s">
-        <v>4727</v>
+        <v>4730</v>
       </c>
       <c r="J92" s="22"/>
       <c r="K92" s="23" t="s">
-        <v>4728</v>
+        <v>4731</v>
       </c>
       <c r="L92" s="22"/>
       <c r="M92" s="10"/>
@@ -47747,27 +47814,27 @@
     </row>
     <row r="93" ht="18.75" customHeight="1">
       <c r="A93" s="23" t="s">
-        <v>4729</v>
+        <v>4732</v>
       </c>
       <c r="B93" s="22"/>
       <c r="C93" s="23" t="s">
-        <v>4729</v>
+        <v>4732</v>
       </c>
       <c r="D93" s="22"/>
       <c r="E93" s="23" t="s">
-        <v>4730</v>
+        <v>4733</v>
       </c>
       <c r="F93" s="22"/>
       <c r="G93" s="23" t="s">
-        <v>4731</v>
+        <v>4734</v>
       </c>
       <c r="H93" s="22"/>
       <c r="I93" s="23" t="s">
-        <v>4732</v>
+        <v>4735</v>
       </c>
       <c r="J93" s="22"/>
       <c r="K93" s="23" t="s">
-        <v>4733</v>
+        <v>4736</v>
       </c>
       <c r="L93" s="22"/>
       <c r="M93" s="10"/>
@@ -47780,40 +47847,40 @@
     </row>
     <row r="94" ht="18.75" customHeight="1">
       <c r="A94" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="B94" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D94" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E94" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="F94" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="G94" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="I94" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="J94" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="K94" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="L94" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="M94" s="10"/>
       <c r="N94" s="10"/>
@@ -47825,40 +47892,40 @@
     </row>
     <row r="95" ht="18.75" customHeight="1">
       <c r="A95" s="23" t="s">
-        <v>4734</v>
+        <v>4737</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>4735</v>
+        <v>4738</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>4736</v>
+        <v>4739</v>
       </c>
       <c r="D95" s="25" t="s">
-        <v>4737</v>
+        <v>4740</v>
       </c>
       <c r="E95" s="23" t="s">
-        <v>4738</v>
+        <v>4741</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>4739</v>
+        <v>4742</v>
       </c>
       <c r="G95" s="23" t="s">
-        <v>4740</v>
+        <v>4743</v>
       </c>
       <c r="H95" s="25" t="s">
-        <v>4741</v>
+        <v>4744</v>
       </c>
       <c r="I95" s="23" t="s">
-        <v>4742</v>
+        <v>4745</v>
       </c>
       <c r="J95" s="25" t="s">
-        <v>4743</v>
+        <v>4746</v>
       </c>
       <c r="K95" s="23" t="s">
-        <v>4744</v>
+        <v>4747</v>
       </c>
       <c r="L95" s="25" t="s">
-        <v>4745</v>
+        <v>4748</v>
       </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10"/>
@@ -47870,40 +47937,40 @@
     </row>
     <row r="96" ht="18.75" customHeight="1">
       <c r="A96" s="23" t="s">
-        <v>4746</v>
+        <v>4749</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>4747</v>
+        <v>4750</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>4748</v>
+        <v>4751</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>4749</v>
+        <v>4752</v>
       </c>
       <c r="E96" s="23" t="s">
-        <v>4750</v>
+        <v>4753</v>
       </c>
       <c r="F96" s="25" t="s">
-        <v>4751</v>
+        <v>4754</v>
       </c>
       <c r="G96" s="23" t="s">
-        <v>4752</v>
+        <v>4755</v>
       </c>
       <c r="H96" s="25" t="s">
-        <v>4753</v>
+        <v>4756</v>
       </c>
       <c r="I96" s="23" t="s">
         <v>1782</v>
       </c>
       <c r="J96" s="25" t="s">
-        <v>4754</v>
+        <v>4757</v>
       </c>
       <c r="K96" s="23" t="s">
-        <v>4755</v>
+        <v>4758</v>
       </c>
       <c r="L96" s="25" t="s">
-        <v>4756</v>
+        <v>4759</v>
       </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10"/>
@@ -47915,40 +47982,40 @@
     </row>
     <row r="97" ht="18.75" customHeight="1">
       <c r="A97" s="23" t="s">
-        <v>4746</v>
+        <v>4749</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>4757</v>
+        <v>4760</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>4748</v>
+        <v>4751</v>
       </c>
       <c r="D97" s="25" t="s">
-        <v>4758</v>
+        <v>4761</v>
       </c>
       <c r="E97" s="23" t="s">
-        <v>4750</v>
+        <v>4753</v>
       </c>
       <c r="F97" s="25" t="s">
-        <v>4739</v>
+        <v>4742</v>
       </c>
       <c r="G97" s="23" t="s">
-        <v>4740</v>
+        <v>4743</v>
       </c>
       <c r="H97" s="25" t="s">
-        <v>4759</v>
+        <v>4762</v>
       </c>
       <c r="I97" s="23" t="s">
         <v>1782</v>
       </c>
       <c r="J97" s="25" t="s">
-        <v>4760</v>
+        <v>4763</v>
       </c>
       <c r="K97" s="23" t="s">
-        <v>4755</v>
+        <v>4758</v>
       </c>
       <c r="L97" s="25" t="s">
-        <v>4745</v>
+        <v>4748</v>
       </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10"/>
@@ -47960,40 +48027,40 @@
     </row>
     <row r="98" ht="18.75" customHeight="1">
       <c r="A98" s="23" t="s">
-        <v>4761</v>
+        <v>4764</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>4762</v>
+        <v>4765</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>4763</v>
+        <v>4766</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>4764</v>
+        <v>4767</v>
       </c>
       <c r="E98" s="23" t="s">
-        <v>4765</v>
+        <v>4768</v>
       </c>
       <c r="F98" s="25" t="s">
-        <v>4766</v>
+        <v>4769</v>
       </c>
       <c r="G98" s="23" t="s">
-        <v>4767</v>
+        <v>4770</v>
       </c>
       <c r="H98" s="25" t="s">
-        <v>4768</v>
+        <v>4771</v>
       </c>
       <c r="I98" s="23" t="s">
-        <v>4769</v>
+        <v>4772</v>
       </c>
       <c r="J98" s="25" t="s">
-        <v>4770</v>
+        <v>4773</v>
       </c>
       <c r="K98" s="23" t="s">
-        <v>4771</v>
+        <v>4774</v>
       </c>
       <c r="L98" s="25" t="s">
-        <v>4772</v>
+        <v>4775</v>
       </c>
       <c r="M98" s="10"/>
       <c r="N98" s="10"/>
@@ -48005,40 +48072,40 @@
     </row>
     <row r="99" ht="18.75" customHeight="1">
       <c r="A99" s="23" t="s">
-        <v>4773</v>
+        <v>4776</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>4774</v>
+        <v>4777</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>4775</v>
+        <v>4778</v>
       </c>
       <c r="D99" s="25" t="s">
-        <v>4776</v>
+        <v>4779</v>
       </c>
       <c r="E99" s="23" t="s">
-        <v>4777</v>
+        <v>4780</v>
       </c>
       <c r="F99" s="25" t="s">
-        <v>4778</v>
+        <v>4781</v>
       </c>
       <c r="G99" s="23" t="s">
-        <v>4779</v>
+        <v>4782</v>
       </c>
       <c r="H99" s="25" t="s">
-        <v>4780</v>
+        <v>4783</v>
       </c>
       <c r="I99" s="23" t="s">
-        <v>4781</v>
+        <v>4784</v>
       </c>
       <c r="J99" s="25" t="s">
-        <v>4782</v>
+        <v>4785</v>
       </c>
       <c r="K99" s="23" t="s">
-        <v>4783</v>
+        <v>4786</v>
       </c>
       <c r="L99" s="25" t="s">
-        <v>4784</v>
+        <v>4787</v>
       </c>
       <c r="M99" s="10"/>
       <c r="N99" s="10"/>
@@ -48050,40 +48117,40 @@
     </row>
     <row r="100" ht="18.75" customHeight="1">
       <c r="A100" s="36" t="s">
-        <v>4785</v>
+        <v>4788</v>
       </c>
       <c r="B100" s="28" t="s">
-        <v>4786</v>
+        <v>4789</v>
       </c>
       <c r="C100" s="36" t="s">
-        <v>4787</v>
+        <v>4790</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>4788</v>
+        <v>4791</v>
       </c>
       <c r="E100" s="23" t="s">
-        <v>4789</v>
+        <v>4792</v>
       </c>
       <c r="F100" s="25" t="s">
-        <v>4790</v>
+        <v>4793</v>
       </c>
       <c r="G100" s="36" t="s">
-        <v>4791</v>
+        <v>4794</v>
       </c>
       <c r="H100" s="28" t="s">
-        <v>4792</v>
+        <v>4795</v>
       </c>
       <c r="I100" s="36" t="s">
-        <v>4793</v>
+        <v>4796</v>
       </c>
       <c r="J100" s="28" t="s">
-        <v>4794</v>
+        <v>4797</v>
       </c>
       <c r="K100" s="36" t="s">
-        <v>4795</v>
+        <v>4798</v>
       </c>
       <c r="L100" s="28" t="s">
-        <v>4796</v>
+        <v>4799</v>
       </c>
       <c r="M100" s="10"/>
       <c r="N100" s="10"/>
@@ -48097,10 +48164,10 @@
       <c r="A101" s="10"/>
       <c r="B101" s="10"/>
       <c r="E101" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="F101" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="G101" s="10"/>
       <c r="H101" s="10"/>
@@ -48120,10 +48187,10 @@
       <c r="A102" s="10"/>
       <c r="B102" s="10"/>
       <c r="E102" s="23" t="s">
-        <v>4797</v>
+        <v>4800</v>
       </c>
       <c r="F102" s="25" t="s">
-        <v>4798</v>
+        <v>4801</v>
       </c>
       <c r="G102" s="10"/>
       <c r="H102" s="10"/>
@@ -48181,10 +48248,10 @@
       <c r="A105" s="10"/>
       <c r="B105" s="10"/>
       <c r="E105" s="23" t="s">
-        <v>4799</v>
+        <v>4802</v>
       </c>
       <c r="F105" s="25" t="s">
-        <v>4800</v>
+        <v>4803</v>
       </c>
       <c r="G105" s="10"/>
       <c r="H105" s="10"/>
@@ -48204,10 +48271,10 @@
       <c r="A106" s="10"/>
       <c r="B106" s="10"/>
       <c r="E106" s="23" t="s">
-        <v>4801</v>
+        <v>4804</v>
       </c>
       <c r="F106" s="25" t="s">
-        <v>4802</v>
+        <v>4805</v>
       </c>
       <c r="G106" s="10"/>
       <c r="H106" s="10"/>
@@ -48265,19 +48332,19 @@
     </row>
     <row r="109" ht="18.75" customHeight="1">
       <c r="A109" s="18" t="s">
-        <v>4803</v>
+        <v>4806</v>
       </c>
       <c r="B109" s="19"/>
       <c r="C109" s="18" t="s">
-        <v>4804</v>
+        <v>4807</v>
       </c>
       <c r="D109" s="19"/>
       <c r="E109" s="18" t="s">
-        <v>4805</v>
+        <v>4808</v>
       </c>
       <c r="F109" s="19"/>
       <c r="G109" s="18" t="s">
-        <v>4806</v>
+        <v>4809</v>
       </c>
       <c r="H109" s="19"/>
       <c r="I109" s="10"/>
@@ -48294,19 +48361,19 @@
     </row>
     <row r="110" ht="18.75" customHeight="1">
       <c r="A110" s="23" t="s">
-        <v>4807</v>
+        <v>4810</v>
       </c>
       <c r="B110" s="22"/>
       <c r="C110" s="23" t="s">
-        <v>4808</v>
+        <v>4811</v>
       </c>
       <c r="D110" s="22"/>
       <c r="E110" s="23" t="s">
-        <v>4809</v>
+        <v>4812</v>
       </c>
       <c r="F110" s="22"/>
       <c r="G110" s="23" t="s">
-        <v>4810</v>
+        <v>4813</v>
       </c>
       <c r="H110" s="22"/>
       <c r="I110" s="10"/>
@@ -48323,19 +48390,19 @@
     </row>
     <row r="111" ht="18.75" customHeight="1">
       <c r="A111" s="23" t="s">
-        <v>4811</v>
+        <v>4814</v>
       </c>
       <c r="B111" s="22"/>
       <c r="C111" s="23" t="s">
-        <v>4812</v>
+        <v>4815</v>
       </c>
       <c r="D111" s="22"/>
       <c r="E111" s="23" t="s">
-        <v>4813</v>
+        <v>4816</v>
       </c>
       <c r="F111" s="22"/>
       <c r="G111" s="23" t="s">
-        <v>4814</v>
+        <v>4817</v>
       </c>
       <c r="H111" s="22"/>
       <c r="I111" s="10"/>
@@ -48352,19 +48419,19 @@
     </row>
     <row r="112" ht="18.75" customHeight="1">
       <c r="A112" s="23" t="s">
-        <v>4815</v>
+        <v>4818</v>
       </c>
       <c r="B112" s="22"/>
       <c r="C112" s="23" t="s">
-        <v>4816</v>
+        <v>4819</v>
       </c>
       <c r="D112" s="22"/>
       <c r="E112" s="23" t="s">
-        <v>4817</v>
+        <v>4820</v>
       </c>
       <c r="F112" s="22"/>
       <c r="G112" s="23" t="s">
-        <v>4818</v>
+        <v>4821</v>
       </c>
       <c r="H112" s="22"/>
       <c r="I112" s="10"/>
@@ -48381,28 +48448,28 @@
     </row>
     <row r="113" ht="18.75" customHeight="1">
       <c r="A113" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="B113" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="C113" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D113" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E113" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="F113" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="G113" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="H113" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="10"/>
@@ -48418,28 +48485,28 @@
     </row>
     <row r="114" ht="18.75" customHeight="1">
       <c r="A114" s="23" t="s">
-        <v>4819</v>
+        <v>4822</v>
       </c>
       <c r="B114" s="25" t="s">
         <v>4067</v>
       </c>
       <c r="C114" s="23" t="s">
-        <v>4820</v>
+        <v>4823</v>
       </c>
       <c r="D114" s="25" t="s">
-        <v>4821</v>
+        <v>4824</v>
       </c>
       <c r="E114" s="23" t="s">
-        <v>4822</v>
+        <v>4825</v>
       </c>
       <c r="F114" s="25" t="s">
-        <v>4823</v>
+        <v>4826</v>
       </c>
       <c r="G114" s="23" t="s">
-        <v>4824</v>
+        <v>4827</v>
       </c>
       <c r="H114" s="25" t="s">
-        <v>4825</v>
+        <v>4828</v>
       </c>
       <c r="I114" s="10"/>
       <c r="J114" s="10"/>
@@ -48455,28 +48522,28 @@
     </row>
     <row r="115" ht="18.75" customHeight="1">
       <c r="A115" s="23" t="s">
-        <v>4826</v>
+        <v>4829</v>
       </c>
       <c r="B115" s="25" t="s">
-        <v>4827</v>
+        <v>4830</v>
       </c>
       <c r="C115" s="23" t="s">
-        <v>4828</v>
+        <v>4831</v>
       </c>
       <c r="D115" s="25" t="s">
-        <v>4829</v>
+        <v>4832</v>
       </c>
       <c r="E115" s="23" t="s">
-        <v>4830</v>
+        <v>4833</v>
       </c>
       <c r="F115" s="25" t="s">
-        <v>4831</v>
+        <v>4834</v>
       </c>
       <c r="G115" s="23" t="s">
-        <v>4832</v>
+        <v>4835</v>
       </c>
       <c r="H115" s="25" t="s">
-        <v>4833</v>
+        <v>4836</v>
       </c>
       <c r="I115" s="10"/>
       <c r="J115" s="10"/>
@@ -48492,28 +48559,28 @@
     </row>
     <row r="116" ht="18.75" customHeight="1">
       <c r="A116" s="23" t="s">
-        <v>4826</v>
+        <v>4829</v>
       </c>
       <c r="B116" s="25" t="s">
         <v>4067</v>
       </c>
       <c r="C116" s="23" t="s">
-        <v>4828</v>
+        <v>4831</v>
       </c>
       <c r="D116" s="25" t="s">
-        <v>4821</v>
+        <v>4824</v>
       </c>
       <c r="E116" s="23" t="s">
-        <v>4830</v>
+        <v>4833</v>
       </c>
       <c r="F116" s="25" t="s">
-        <v>4823</v>
+        <v>4826</v>
       </c>
       <c r="G116" s="23" t="s">
-        <v>4832</v>
+        <v>4835</v>
       </c>
       <c r="H116" s="25" t="s">
-        <v>4834</v>
+        <v>4837</v>
       </c>
       <c r="I116" s="10"/>
       <c r="J116" s="10"/>
@@ -48529,28 +48596,28 @@
     </row>
     <row r="117" ht="18.75" customHeight="1">
       <c r="A117" s="23" t="s">
-        <v>4835</v>
+        <v>4838</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>4836</v>
+        <v>4839</v>
       </c>
       <c r="C117" s="23" t="s">
-        <v>4837</v>
+        <v>4840</v>
       </c>
       <c r="D117" s="25" t="s">
-        <v>4838</v>
+        <v>4841</v>
       </c>
       <c r="E117" s="23" t="s">
-        <v>4839</v>
+        <v>4842</v>
       </c>
       <c r="F117" s="25" t="s">
-        <v>4840</v>
+        <v>4843</v>
       </c>
       <c r="G117" s="23" t="s">
-        <v>4841</v>
+        <v>4844</v>
       </c>
       <c r="H117" s="25" t="s">
-        <v>4842</v>
+        <v>4845</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="10"/>
@@ -48566,28 +48633,28 @@
     </row>
     <row r="118" ht="18.75" customHeight="1">
       <c r="A118" s="23" t="s">
-        <v>4843</v>
+        <v>4846</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>4844</v>
+        <v>4847</v>
       </c>
       <c r="C118" s="23" t="s">
-        <v>4845</v>
+        <v>4848</v>
       </c>
       <c r="D118" s="25" t="s">
-        <v>4846</v>
+        <v>4849</v>
       </c>
       <c r="E118" s="23" t="s">
-        <v>4847</v>
+        <v>4850</v>
       </c>
       <c r="F118" s="25" t="s">
-        <v>4848</v>
+        <v>4851</v>
       </c>
       <c r="G118" s="23" t="s">
-        <v>4849</v>
+        <v>4852</v>
       </c>
       <c r="H118" s="25" t="s">
-        <v>4850</v>
+        <v>4853</v>
       </c>
       <c r="I118" s="10"/>
       <c r="J118" s="10"/>
@@ -48603,28 +48670,28 @@
     </row>
     <row r="119" ht="18.75" customHeight="1">
       <c r="A119" s="36" t="s">
-        <v>4851</v>
+        <v>4854</v>
       </c>
       <c r="B119" s="28" t="s">
-        <v>4852</v>
+        <v>4855</v>
       </c>
       <c r="C119" s="36" t="s">
-        <v>4853</v>
+        <v>4856</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>4854</v>
+        <v>4857</v>
       </c>
       <c r="E119" s="36" t="s">
-        <v>4855</v>
+        <v>4858</v>
       </c>
       <c r="F119" s="28" t="s">
-        <v>4856</v>
+        <v>4859</v>
       </c>
       <c r="G119" s="36" t="s">
-        <v>4857</v>
+        <v>4860</v>
       </c>
       <c r="H119" s="28" t="s">
-        <v>4858</v>
+        <v>4861</v>
       </c>
       <c r="I119" s="10"/>
       <c r="J119" s="10"/>
@@ -48661,175 +48728,175 @@
     </row>
     <row r="121" ht="18.75" customHeight="1">
       <c r="A121" s="18" t="s">
-        <v>4859</v>
+        <v>4862</v>
       </c>
       <c r="B121" s="19"/>
       <c r="C121" s="18" t="s">
-        <v>4860</v>
+        <v>4863</v>
       </c>
       <c r="D121" s="19"/>
       <c r="E121" s="18" t="s">
-        <v>4861</v>
+        <v>4864</v>
       </c>
       <c r="F121" s="19"/>
       <c r="G121" s="18" t="s">
-        <v>4862</v>
+        <v>4865</v>
       </c>
       <c r="H121" s="19"/>
       <c r="I121" s="18" t="s">
-        <v>4863</v>
+        <v>4866</v>
       </c>
       <c r="J121" s="19"/>
       <c r="K121" s="18" t="s">
-        <v>4864</v>
+        <v>4867</v>
       </c>
       <c r="L121" s="19"/>
       <c r="M121" s="10"/>
       <c r="N121" s="10"/>
       <c r="O121" s="10"/>
       <c r="P121" s="8" t="s">
-        <v>4865</v>
+        <v>4868</v>
       </c>
     </row>
     <row r="122" ht="18.75" customHeight="1">
       <c r="A122" s="21" t="s">
-        <v>4337</v>
+        <v>4340</v>
       </c>
       <c r="B122" s="22"/>
       <c r="C122" s="23" t="s">
-        <v>4866</v>
+        <v>4869</v>
       </c>
       <c r="D122" s="22"/>
       <c r="E122" s="23" t="s">
-        <v>4867</v>
+        <v>4870</v>
       </c>
       <c r="F122" s="22"/>
       <c r="G122" s="23" t="s">
-        <v>4868</v>
+        <v>4871</v>
       </c>
       <c r="H122" s="22"/>
       <c r="I122" s="23" t="s">
-        <v>4869</v>
+        <v>4872</v>
       </c>
       <c r="J122" s="22"/>
       <c r="K122" s="23" t="s">
-        <v>4870</v>
+        <v>4873</v>
       </c>
       <c r="L122" s="22"/>
       <c r="M122" s="10"/>
       <c r="N122" s="10"/>
       <c r="O122" s="10"/>
       <c r="P122" s="8" t="s">
-        <v>4337</v>
+        <v>4340</v>
       </c>
       <c r="Q122" s="10" t="s">
-        <v>4871</v>
+        <v>4874</v>
       </c>
     </row>
     <row r="123" ht="18.75" customHeight="1">
       <c r="A123" s="21" t="s">
-        <v>4343</v>
+        <v>4346</v>
       </c>
       <c r="B123" s="22"/>
       <c r="C123" s="23" t="s">
-        <v>4872</v>
+        <v>4875</v>
       </c>
       <c r="D123" s="22"/>
       <c r="E123" s="23" t="s">
-        <v>4873</v>
+        <v>4876</v>
       </c>
       <c r="F123" s="22"/>
       <c r="G123" s="23" t="s">
-        <v>4874</v>
+        <v>4877</v>
       </c>
       <c r="H123" s="22"/>
       <c r="I123" s="23" t="s">
-        <v>4875</v>
+        <v>4878</v>
       </c>
       <c r="J123" s="22"/>
       <c r="K123" s="23" t="s">
-        <v>4876</v>
+        <v>4879</v>
       </c>
       <c r="L123" s="22"/>
       <c r="M123" s="10"/>
       <c r="N123" s="10"/>
       <c r="O123" s="10"/>
       <c r="P123" s="8" t="s">
-        <v>4343</v>
+        <v>4346</v>
       </c>
       <c r="Q123" s="10" t="s">
-        <v>4877</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="124" ht="18.75" customHeight="1">
       <c r="A124" s="21" t="s">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="B124" s="22"/>
       <c r="C124" s="23" t="s">
-        <v>4878</v>
+        <v>4881</v>
       </c>
       <c r="D124" s="22"/>
       <c r="E124" s="23" t="s">
-        <v>4879</v>
+        <v>4882</v>
       </c>
       <c r="F124" s="22"/>
       <c r="G124" s="23" t="s">
-        <v>4880</v>
+        <v>4883</v>
       </c>
       <c r="H124" s="22"/>
       <c r="I124" s="23" t="s">
-        <v>4881</v>
+        <v>4884</v>
       </c>
       <c r="J124" s="22"/>
       <c r="K124" s="23" t="s">
-        <v>4882</v>
+        <v>4885</v>
       </c>
       <c r="L124" s="22"/>
       <c r="M124" s="10"/>
       <c r="N124" s="10"/>
       <c r="O124" s="10"/>
       <c r="P124" s="8" t="s">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="Q124" s="10" t="s">
-        <v>4883</v>
+        <v>4886</v>
       </c>
     </row>
     <row r="125" ht="18.75" customHeight="1">
       <c r="A125" s="21" t="s">
-        <v>4355</v>
+        <v>4358</v>
       </c>
       <c r="B125" s="22"/>
       <c r="C125" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D125" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E125" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="F125" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="G125" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="H125" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="I125" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="J125" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="K125" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="L125" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="M125" s="10"/>
       <c r="N125" s="10"/>
@@ -48837,10 +48904,10 @@
       <c r="P125" s="8"/>
       <c r="Q125" s="8"/>
       <c r="R125" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="S125" s="8" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
     </row>
     <row r="126" ht="18.75" customHeight="1">
@@ -48848,34 +48915,34 @@
         <v>4128</v>
       </c>
       <c r="B126" s="24" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C126" s="23" t="s">
         <v>778</v>
       </c>
       <c r="D126" s="25" t="s">
-        <v>4884</v>
+        <v>4887</v>
       </c>
       <c r="E126" s="23" t="s">
-        <v>4885</v>
+        <v>4888</v>
       </c>
       <c r="F126" s="25" t="s">
-        <v>4886</v>
+        <v>4889</v>
       </c>
       <c r="G126" s="23" t="s">
-        <v>4887</v>
+        <v>4890</v>
       </c>
       <c r="H126" s="25" t="s">
-        <v>4888</v>
+        <v>4891</v>
       </c>
       <c r="I126" s="23" t="s">
-        <v>4889</v>
+        <v>4892</v>
       </c>
       <c r="J126" s="25" t="s">
-        <v>4890</v>
+        <v>4893</v>
       </c>
       <c r="K126" s="23" t="s">
-        <v>4891</v>
+        <v>4894</v>
       </c>
       <c r="L126" s="25" t="s">
         <v>3386</v>
@@ -48887,13 +48954,13 @@
         <v>4128</v>
       </c>
       <c r="Q126" s="8" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="R126" s="10" t="s">
-        <v>4892</v>
+        <v>4895</v>
       </c>
       <c r="S126" s="10" t="s">
-        <v>4893</v>
+        <v>4896</v>
       </c>
     </row>
     <row r="127" ht="18.75" customHeight="1">
@@ -48902,34 +48969,34 @@
         <v>3684</v>
       </c>
       <c r="C127" s="23" t="s">
-        <v>4894</v>
+        <v>4897</v>
       </c>
       <c r="D127" s="25" t="s">
-        <v>4895</v>
+        <v>4898</v>
       </c>
       <c r="E127" s="23" t="s">
-        <v>4896</v>
+        <v>4899</v>
       </c>
       <c r="F127" s="25" t="s">
-        <v>4897</v>
+        <v>4900</v>
       </c>
       <c r="G127" s="23" t="s">
         <v>3442</v>
       </c>
       <c r="H127" s="25" t="s">
-        <v>4898</v>
+        <v>4901</v>
       </c>
       <c r="I127" s="23" t="s">
-        <v>4899</v>
+        <v>4902</v>
       </c>
       <c r="J127" s="25" t="s">
-        <v>4900</v>
+        <v>4903</v>
       </c>
       <c r="K127" s="23" t="s">
-        <v>4901</v>
+        <v>4904</v>
       </c>
       <c r="L127" s="25" t="s">
-        <v>4902</v>
+        <v>4905</v>
       </c>
       <c r="M127" s="10"/>
       <c r="N127" s="10"/>
@@ -48938,43 +49005,43 @@
         <v>3684</v>
       </c>
       <c r="R127" s="10" t="s">
-        <v>4903</v>
+        <v>4906</v>
       </c>
       <c r="S127" s="10" t="s">
-        <v>4904</v>
+        <v>4907</v>
       </c>
     </row>
     <row r="128" ht="18.75" customHeight="1">
       <c r="A128" s="26"/>
       <c r="B128" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C128" s="23" t="s">
-        <v>4894</v>
+        <v>4897</v>
       </c>
       <c r="D128" s="25" t="s">
-        <v>4884</v>
+        <v>4887</v>
       </c>
       <c r="E128" s="23" t="s">
-        <v>4896</v>
+        <v>4899</v>
       </c>
       <c r="F128" s="25" t="s">
-        <v>4886</v>
+        <v>4889</v>
       </c>
       <c r="G128" s="23" t="s">
         <v>3442</v>
       </c>
       <c r="H128" s="25" t="s">
-        <v>4888</v>
+        <v>4891</v>
       </c>
       <c r="I128" s="23" t="s">
-        <v>4899</v>
+        <v>4902</v>
       </c>
       <c r="J128" s="25" t="s">
-        <v>4890</v>
+        <v>4893</v>
       </c>
       <c r="K128" s="23" t="s">
-        <v>4901</v>
+        <v>4904</v>
       </c>
       <c r="L128" s="25" t="s">
         <v>3386</v>
@@ -48983,13 +49050,13 @@
       <c r="N128" s="10"/>
       <c r="O128" s="10"/>
       <c r="Q128" s="8" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="R128" s="10" t="s">
-        <v>4903</v>
+        <v>4906</v>
       </c>
       <c r="S128" s="10" t="s">
-        <v>4893</v>
+        <v>4896</v>
       </c>
     </row>
     <row r="129" ht="18.75" customHeight="1">
@@ -49000,34 +49067,34 @@
         <v>3524</v>
       </c>
       <c r="C129" s="23" t="s">
-        <v>4905</v>
+        <v>4908</v>
       </c>
       <c r="D129" s="25" t="s">
-        <v>4906</v>
+        <v>4909</v>
       </c>
       <c r="E129" s="23" t="s">
-        <v>4907</v>
+        <v>4910</v>
       </c>
       <c r="F129" s="25" t="s">
-        <v>4908</v>
+        <v>4911</v>
       </c>
       <c r="G129" s="23" t="s">
-        <v>4909</v>
+        <v>4912</v>
       </c>
       <c r="H129" s="25" t="s">
-        <v>4910</v>
+        <v>4913</v>
       </c>
       <c r="I129" s="23" t="s">
-        <v>4911</v>
+        <v>4914</v>
       </c>
       <c r="J129" s="25" t="s">
-        <v>4912</v>
+        <v>4915</v>
       </c>
       <c r="K129" s="23" t="s">
-        <v>4913</v>
+        <v>4916</v>
       </c>
       <c r="L129" s="25" t="s">
-        <v>4914</v>
+        <v>4917</v>
       </c>
       <c r="M129" s="10"/>
       <c r="N129" s="10"/>
@@ -49039,10 +49106,10 @@
         <v>3524</v>
       </c>
       <c r="R129" s="10" t="s">
-        <v>4915</v>
+        <v>4918</v>
       </c>
       <c r="S129" s="10" t="s">
-        <v>4916</v>
+        <v>4919</v>
       </c>
     </row>
     <row r="130" ht="18.75" customHeight="1">
@@ -49050,34 +49117,34 @@
         <v>3638</v>
       </c>
       <c r="C130" s="23" t="s">
-        <v>4917</v>
+        <v>4920</v>
       </c>
       <c r="D130" s="25" t="s">
-        <v>4918</v>
+        <v>4921</v>
       </c>
       <c r="E130" s="23" t="s">
-        <v>4919</v>
+        <v>4922</v>
       </c>
       <c r="F130" s="25" t="s">
-        <v>4920</v>
+        <v>4923</v>
       </c>
       <c r="G130" s="23" t="s">
-        <v>4921</v>
+        <v>4924</v>
       </c>
       <c r="H130" s="25" t="s">
-        <v>4922</v>
+        <v>4925</v>
       </c>
       <c r="I130" s="23" t="s">
-        <v>4923</v>
+        <v>4926</v>
       </c>
       <c r="J130" s="25" t="s">
-        <v>4924</v>
+        <v>4927</v>
       </c>
       <c r="K130" s="23" t="s">
-        <v>4925</v>
+        <v>4928</v>
       </c>
       <c r="L130" s="25" t="s">
-        <v>4926</v>
+        <v>4929</v>
       </c>
       <c r="M130" s="10"/>
       <c r="N130" s="10"/>
@@ -49086,87 +49153,87 @@
         <v>3638</v>
       </c>
       <c r="R130" s="10" t="s">
-        <v>4927</v>
+        <v>4930</v>
       </c>
       <c r="S130" s="10" t="s">
-        <v>4928</v>
+        <v>4931</v>
       </c>
     </row>
     <row r="131" ht="18.75" customHeight="1">
       <c r="B131" s="24" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C131" s="23" t="s">
-        <v>4929</v>
+        <v>4932</v>
       </c>
       <c r="D131" s="25" t="s">
-        <v>4930</v>
+        <v>4933</v>
       </c>
       <c r="E131" s="23" t="s">
-        <v>4931</v>
+        <v>4934</v>
       </c>
       <c r="F131" s="25" t="s">
-        <v>4932</v>
+        <v>4935</v>
       </c>
       <c r="G131" s="23" t="s">
-        <v>4933</v>
+        <v>4936</v>
       </c>
       <c r="H131" s="25" t="s">
-        <v>4934</v>
+        <v>4937</v>
       </c>
       <c r="I131" s="23" t="s">
-        <v>4935</v>
+        <v>4938</v>
       </c>
       <c r="J131" s="25" t="s">
-        <v>4936</v>
+        <v>4939</v>
       </c>
       <c r="K131" s="36" t="s">
-        <v>4937</v>
+        <v>4940</v>
       </c>
       <c r="L131" s="28" t="s">
-        <v>4938</v>
+        <v>4941</v>
       </c>
       <c r="M131" s="10"/>
       <c r="N131" s="10"/>
       <c r="O131" s="10"/>
       <c r="Q131" s="8" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="R131" s="10" t="s">
-        <v>4939</v>
+        <v>4942</v>
       </c>
       <c r="S131" s="10" t="s">
-        <v>4940</v>
+        <v>4943</v>
       </c>
     </row>
     <row r="132" ht="18.75" customHeight="1">
       <c r="A132" s="21" t="s">
-        <v>4409</v>
+        <v>4412</v>
       </c>
       <c r="B132" s="22"/>
       <c r="C132" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D132" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="F132" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="H132" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="J132" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="K132" s="10"/>
       <c r="L132" s="10"/>
@@ -49183,31 +49250,31 @@
         <v>4128</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C133" s="23" t="s">
-        <v>4941</v>
+        <v>4944</v>
       </c>
       <c r="D133" s="25" t="s">
-        <v>4942</v>
+        <v>4945</v>
       </c>
       <c r="E133" s="23" t="s">
-        <v>4943</v>
+        <v>4946</v>
       </c>
       <c r="F133" s="25" t="s">
-        <v>4944</v>
+        <v>4947</v>
       </c>
       <c r="G133" s="23" t="s">
-        <v>4945</v>
+        <v>4948</v>
       </c>
       <c r="H133" s="25" t="s">
-        <v>4946</v>
+        <v>4949</v>
       </c>
       <c r="I133" s="23" t="s">
-        <v>4947</v>
+        <v>4950</v>
       </c>
       <c r="J133" s="25" t="s">
-        <v>4948</v>
+        <v>4951</v>
       </c>
       <c r="K133" s="23"/>
       <c r="L133" s="10"/>
@@ -49245,7 +49312,7 @@
     <row r="135" ht="18.75" customHeight="1">
       <c r="A135" s="26"/>
       <c r="B135" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C135" s="26"/>
       <c r="D135" s="22"/>
@@ -49273,28 +49340,28 @@
         <v>3524</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>4949</v>
+        <v>4952</v>
       </c>
       <c r="D136" s="25" t="s">
-        <v>4950</v>
+        <v>4953</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>4951</v>
+        <v>4954</v>
       </c>
       <c r="F136" s="25" t="s">
-        <v>4952</v>
+        <v>4955</v>
       </c>
       <c r="G136" s="10" t="s">
-        <v>4953</v>
+        <v>4956</v>
       </c>
       <c r="H136" s="25" t="s">
-        <v>4954</v>
+        <v>4957</v>
       </c>
       <c r="I136" s="10" t="s">
-        <v>4955</v>
+        <v>4958</v>
       </c>
       <c r="J136" s="25" t="s">
-        <v>4956</v>
+        <v>4959</v>
       </c>
       <c r="K136" s="23"/>
       <c r="L136" s="10"/>
@@ -49312,28 +49379,28 @@
         <v>3638</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>4957</v>
+        <v>4960</v>
       </c>
       <c r="D137" s="25" t="s">
-        <v>4958</v>
+        <v>4961</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>4959</v>
+        <v>4962</v>
       </c>
       <c r="F137" s="25" t="s">
-        <v>4960</v>
+        <v>4963</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>4961</v>
+        <v>4964</v>
       </c>
       <c r="H137" s="25" t="s">
-        <v>4962</v>
+        <v>4965</v>
       </c>
       <c r="I137" s="10" t="s">
-        <v>4963</v>
+        <v>4966</v>
       </c>
       <c r="J137" s="25" t="s">
-        <v>4964</v>
+        <v>4967</v>
       </c>
       <c r="K137" s="23"/>
       <c r="L137" s="10"/>
@@ -49348,7 +49415,7 @@
     <row r="138" ht="18.75" customHeight="1">
       <c r="A138" s="31"/>
       <c r="B138" s="32" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C138" s="33"/>
       <c r="D138" s="34"/>
@@ -49393,15 +49460,15 @@
       <c r="A140" s="10"/>
       <c r="B140" s="10"/>
       <c r="C140" s="18" t="s">
-        <v>4965</v>
+        <v>4968</v>
       </c>
       <c r="D140" s="19"/>
       <c r="E140" s="18" t="s">
-        <v>4966</v>
+        <v>4969</v>
       </c>
       <c r="F140" s="19"/>
       <c r="G140" s="18" t="s">
-        <v>4967</v>
+        <v>4970</v>
       </c>
       <c r="H140" s="19"/>
       <c r="I140" s="10"/>
@@ -49420,15 +49487,15 @@
       <c r="A141" s="10"/>
       <c r="B141" s="10"/>
       <c r="C141" s="23" t="s">
-        <v>4968</v>
+        <v>4971</v>
       </c>
       <c r="D141" s="22"/>
       <c r="E141" s="23" t="s">
-        <v>4969</v>
+        <v>4972</v>
       </c>
       <c r="F141" s="22"/>
       <c r="G141" s="23" t="s">
-        <v>4970</v>
+        <v>4973</v>
       </c>
       <c r="H141" s="22"/>
       <c r="I141" s="10"/>
@@ -49447,15 +49514,15 @@
       <c r="A142" s="10"/>
       <c r="B142" s="10"/>
       <c r="C142" s="23" t="s">
-        <v>4971</v>
+        <v>4974</v>
       </c>
       <c r="D142" s="22"/>
       <c r="E142" s="23" t="s">
-        <v>4972</v>
+        <v>4975</v>
       </c>
       <c r="F142" s="22"/>
       <c r="G142" s="23" t="s">
-        <v>4973</v>
+        <v>4976</v>
       </c>
       <c r="H142" s="22"/>
       <c r="I142" s="10"/>
@@ -49474,11 +49541,11 @@
       <c r="A143" s="10"/>
       <c r="B143" s="10"/>
       <c r="C143" s="23" t="s">
-        <v>4974</v>
+        <v>4977</v>
       </c>
       <c r="D143" s="22"/>
       <c r="E143" s="23" t="s">
-        <v>4975</v>
+        <v>4978</v>
       </c>
       <c r="F143" s="22"/>
       <c r="G143" s="23" t="s">
@@ -49501,22 +49568,22 @@
       <c r="A144" s="10"/>
       <c r="B144" s="10"/>
       <c r="C144" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D144" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E144" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="F144" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="G144" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="H144" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="I144" s="10"/>
       <c r="J144" s="10"/>
@@ -49534,22 +49601,22 @@
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="23" t="s">
-        <v>4976</v>
+        <v>4979</v>
       </c>
       <c r="D145" s="25" t="s">
-        <v>4977</v>
+        <v>4980</v>
       </c>
       <c r="E145" s="23" t="s">
-        <v>4978</v>
+        <v>4981</v>
       </c>
       <c r="F145" s="25" t="s">
-        <v>4979</v>
+        <v>4982</v>
       </c>
       <c r="G145" s="23" t="s">
-        <v>4980</v>
+        <v>4983</v>
       </c>
       <c r="H145" s="25" t="s">
-        <v>4981</v>
+        <v>4984</v>
       </c>
       <c r="I145" s="10"/>
       <c r="J145" s="10"/>
@@ -49567,22 +49634,22 @@
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
       <c r="C146" s="23" t="s">
-        <v>4982</v>
+        <v>4985</v>
       </c>
       <c r="D146" s="25" t="s">
-        <v>4983</v>
+        <v>4986</v>
       </c>
       <c r="E146" s="23" t="s">
-        <v>4984</v>
+        <v>4987</v>
       </c>
       <c r="F146" s="25" t="s">
-        <v>4985</v>
+        <v>4988</v>
       </c>
       <c r="G146" s="23" t="s">
-        <v>4986</v>
+        <v>4989</v>
       </c>
       <c r="H146" s="25" t="s">
-        <v>4987</v>
+        <v>4990</v>
       </c>
       <c r="I146" s="10"/>
       <c r="J146" s="10"/>
@@ -49600,22 +49667,22 @@
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
       <c r="C147" s="23" t="s">
+        <v>4985</v>
+      </c>
+      <c r="D147" s="25" t="s">
+        <v>4980</v>
+      </c>
+      <c r="E147" s="23" t="s">
+        <v>4987</v>
+      </c>
+      <c r="F147" s="25" t="s">
         <v>4982</v>
       </c>
-      <c r="D147" s="25" t="s">
-        <v>4977</v>
-      </c>
-      <c r="E147" s="23" t="s">
+      <c r="G147" s="23" t="s">
+        <v>4989</v>
+      </c>
+      <c r="H147" s="25" t="s">
         <v>4984</v>
-      </c>
-      <c r="F147" s="25" t="s">
-        <v>4979</v>
-      </c>
-      <c r="G147" s="23" t="s">
-        <v>4986</v>
-      </c>
-      <c r="H147" s="25" t="s">
-        <v>4981</v>
       </c>
       <c r="I147" s="10"/>
       <c r="J147" s="10"/>
@@ -49633,22 +49700,22 @@
       <c r="A148" s="10"/>
       <c r="B148" s="10"/>
       <c r="C148" s="23" t="s">
-        <v>4988</v>
+        <v>4991</v>
       </c>
       <c r="D148" s="25" t="s">
-        <v>4989</v>
+        <v>4992</v>
       </c>
       <c r="E148" s="23" t="s">
-        <v>4990</v>
+        <v>4993</v>
       </c>
       <c r="F148" s="25" t="s">
-        <v>4991</v>
+        <v>4994</v>
       </c>
       <c r="G148" s="23" t="s">
-        <v>4992</v>
+        <v>4995</v>
       </c>
       <c r="H148" s="25" t="s">
-        <v>4993</v>
+        <v>4996</v>
       </c>
       <c r="I148" s="10"/>
       <c r="J148" s="10"/>
@@ -49666,22 +49733,22 @@
       <c r="A149" s="10"/>
       <c r="B149" s="10"/>
       <c r="C149" s="23" t="s">
-        <v>4994</v>
+        <v>4997</v>
       </c>
       <c r="D149" s="25" t="s">
-        <v>4995</v>
+        <v>4998</v>
       </c>
       <c r="E149" s="23" t="s">
-        <v>4996</v>
+        <v>4999</v>
       </c>
       <c r="F149" s="25" t="s">
-        <v>4997</v>
+        <v>5000</v>
       </c>
       <c r="G149" s="23" t="s">
-        <v>4998</v>
+        <v>5001</v>
       </c>
       <c r="H149" s="25" t="s">
-        <v>4999</v>
+        <v>5002</v>
       </c>
       <c r="I149" s="10"/>
       <c r="J149" s="10"/>
@@ -49699,22 +49766,22 @@
       <c r="A150" s="10"/>
       <c r="B150" s="10"/>
       <c r="C150" s="36" t="s">
-        <v>5000</v>
+        <v>5003</v>
       </c>
       <c r="D150" s="28" t="s">
-        <v>5001</v>
+        <v>5004</v>
       </c>
       <c r="E150" s="36" t="s">
-        <v>5002</v>
+        <v>5005</v>
       </c>
       <c r="F150" s="28" t="s">
-        <v>5003</v>
+        <v>5006</v>
       </c>
       <c r="G150" s="36" t="s">
-        <v>5004</v>
+        <v>5007</v>
       </c>
       <c r="H150" s="28" t="s">
-        <v>5005</v>
+        <v>5008</v>
       </c>
       <c r="I150" s="10"/>
       <c r="J150" s="10"/>
@@ -49751,19 +49818,19 @@
     </row>
     <row r="152" ht="18.75" customHeight="1">
       <c r="A152" s="18" t="s">
-        <v>5006</v>
+        <v>5009</v>
       </c>
       <c r="B152" s="19"/>
       <c r="C152" s="18" t="s">
-        <v>5007</v>
+        <v>5010</v>
       </c>
       <c r="D152" s="19"/>
       <c r="E152" s="18" t="s">
-        <v>5008</v>
+        <v>5011</v>
       </c>
       <c r="F152" s="19"/>
       <c r="G152" s="18" t="s">
-        <v>5009</v>
+        <v>5012</v>
       </c>
       <c r="H152" s="19"/>
       <c r="J152" s="10"/>
@@ -49779,19 +49846,19 @@
     </row>
     <row r="153" ht="18.75" customHeight="1">
       <c r="A153" s="21" t="s">
-        <v>4337</v>
+        <v>4340</v>
       </c>
       <c r="B153" s="22"/>
       <c r="C153" s="23" t="s">
-        <v>5010</v>
+        <v>5013</v>
       </c>
       <c r="D153" s="22"/>
       <c r="E153" s="23" t="s">
-        <v>5011</v>
+        <v>5014</v>
       </c>
       <c r="F153" s="22"/>
       <c r="G153" s="23" t="s">
-        <v>5012</v>
+        <v>5015</v>
       </c>
       <c r="H153" s="22"/>
       <c r="J153" s="10"/>
@@ -49807,19 +49874,19 @@
     </row>
     <row r="154" ht="18.75" customHeight="1">
       <c r="A154" s="21" t="s">
-        <v>4343</v>
+        <v>4346</v>
       </c>
       <c r="B154" s="22"/>
       <c r="C154" s="23" t="s">
-        <v>5013</v>
+        <v>5016</v>
       </c>
       <c r="D154" s="22"/>
       <c r="E154" s="23" t="s">
-        <v>5014</v>
+        <v>5017</v>
       </c>
       <c r="F154" s="22"/>
       <c r="G154" s="23" t="s">
-        <v>5015</v>
+        <v>5018</v>
       </c>
       <c r="H154" s="22"/>
       <c r="J154" s="10"/>
@@ -49835,19 +49902,19 @@
     </row>
     <row r="155" ht="18.75" customHeight="1">
       <c r="A155" s="21" t="s">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="B155" s="22"/>
       <c r="C155" s="23" t="s">
-        <v>5016</v>
+        <v>5019</v>
       </c>
       <c r="D155" s="22"/>
       <c r="E155" s="23" t="s">
-        <v>5017</v>
+        <v>5020</v>
       </c>
       <c r="F155" s="22"/>
       <c r="G155" s="23" t="s">
-        <v>5018</v>
+        <v>5021</v>
       </c>
       <c r="H155" s="22"/>
       <c r="J155" s="10"/>
@@ -49863,26 +49930,26 @@
     </row>
     <row r="156" ht="18.75" customHeight="1">
       <c r="A156" s="21" t="s">
-        <v>4355</v>
+        <v>4358</v>
       </c>
       <c r="B156" s="22"/>
       <c r="C156" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D156" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E156" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="F156" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="G156" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="H156" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="J156" s="10"/>
       <c r="K156" s="10"/>
@@ -49900,25 +49967,25 @@
         <v>4128</v>
       </c>
       <c r="B157" s="24" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C157" s="23" t="s">
-        <v>5019</v>
+        <v>5022</v>
       </c>
       <c r="D157" s="25" t="s">
-        <v>5020</v>
+        <v>5023</v>
       </c>
       <c r="E157" s="23" t="s">
-        <v>5021</v>
+        <v>5024</v>
       </c>
       <c r="F157" s="25" t="s">
-        <v>5022</v>
+        <v>5025</v>
       </c>
       <c r="G157" s="23" t="s">
-        <v>5023</v>
+        <v>5026</v>
       </c>
       <c r="H157" s="25" t="s">
-        <v>5024</v>
+        <v>5027</v>
       </c>
       <c r="J157" s="10"/>
       <c r="K157" s="10"/>
@@ -49937,22 +50004,22 @@
         <v>3684</v>
       </c>
       <c r="C158" s="23" t="s">
-        <v>5025</v>
+        <v>5028</v>
       </c>
       <c r="D158" s="25" t="s">
-        <v>5026</v>
+        <v>5029</v>
       </c>
       <c r="E158" s="23" t="s">
-        <v>5027</v>
+        <v>5030</v>
       </c>
       <c r="F158" s="25" t="s">
-        <v>5028</v>
+        <v>5031</v>
       </c>
       <c r="G158" s="23" t="s">
-        <v>5029</v>
+        <v>5032</v>
       </c>
       <c r="H158" s="25" t="s">
-        <v>5030</v>
+        <v>5033</v>
       </c>
       <c r="J158" s="10"/>
       <c r="K158" s="10"/>
@@ -49968,25 +50035,25 @@
     <row r="159" ht="18.75" customHeight="1">
       <c r="A159" s="26"/>
       <c r="B159" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C159" s="23" t="s">
+        <v>5028</v>
+      </c>
+      <c r="D159" s="25" t="s">
+        <v>5023</v>
+      </c>
+      <c r="E159" s="23" t="s">
+        <v>5030</v>
+      </c>
+      <c r="F159" s="25" t="s">
         <v>5025</v>
       </c>
-      <c r="D159" s="25" t="s">
-        <v>5020</v>
-      </c>
-      <c r="E159" s="23" t="s">
+      <c r="G159" s="23" t="s">
+        <v>5032</v>
+      </c>
+      <c r="H159" s="25" t="s">
         <v>5027</v>
-      </c>
-      <c r="F159" s="25" t="s">
-        <v>5022</v>
-      </c>
-      <c r="G159" s="23" t="s">
-        <v>5029</v>
-      </c>
-      <c r="H159" s="25" t="s">
-        <v>5024</v>
       </c>
       <c r="J159" s="10"/>
       <c r="K159" s="10"/>
@@ -50007,22 +50074,22 @@
         <v>3524</v>
       </c>
       <c r="C160" s="23" t="s">
-        <v>5031</v>
+        <v>5034</v>
       </c>
       <c r="D160" s="25" t="s">
-        <v>5032</v>
+        <v>5035</v>
       </c>
       <c r="E160" s="23" t="s">
-        <v>5033</v>
+        <v>5036</v>
       </c>
       <c r="F160" s="25" t="s">
-        <v>5034</v>
+        <v>5037</v>
       </c>
       <c r="G160" s="23" t="s">
-        <v>5035</v>
+        <v>5038</v>
       </c>
       <c r="H160" s="25" t="s">
-        <v>5036</v>
+        <v>5039</v>
       </c>
       <c r="J160" s="10"/>
       <c r="K160" s="10"/>
@@ -50040,22 +50107,22 @@
         <v>3638</v>
       </c>
       <c r="C161" s="23" t="s">
-        <v>5037</v>
+        <v>5040</v>
       </c>
       <c r="D161" s="25" t="s">
-        <v>5038</v>
+        <v>5041</v>
       </c>
       <c r="E161" s="23" t="s">
-        <v>5039</v>
+        <v>5042</v>
       </c>
       <c r="F161" s="25" t="s">
-        <v>5040</v>
+        <v>5043</v>
       </c>
       <c r="G161" s="23" t="s">
-        <v>5041</v>
+        <v>5044</v>
       </c>
       <c r="H161" s="25" t="s">
-        <v>5042</v>
+        <v>5045</v>
       </c>
       <c r="J161" s="10"/>
       <c r="K161" s="10"/>
@@ -50070,25 +50137,25 @@
     </row>
     <row r="162" ht="18.75" customHeight="1">
       <c r="B162" s="24" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C162" s="23" t="s">
-        <v>5043</v>
+        <v>5046</v>
       </c>
       <c r="D162" s="25" t="s">
-        <v>5044</v>
+        <v>5047</v>
       </c>
       <c r="E162" s="23" t="s">
-        <v>5045</v>
+        <v>5048</v>
       </c>
       <c r="F162" s="25" t="s">
-        <v>5046</v>
+        <v>5049</v>
       </c>
       <c r="G162" s="23" t="s">
-        <v>5047</v>
+        <v>5050</v>
       </c>
       <c r="H162" s="25" t="s">
-        <v>5048</v>
+        <v>5051</v>
       </c>
       <c r="J162" s="10"/>
       <c r="K162" s="10"/>
@@ -50103,14 +50170,14 @@
     </row>
     <row r="163" ht="18.75" customHeight="1">
       <c r="A163" s="21" t="s">
-        <v>4409</v>
+        <v>4412</v>
       </c>
       <c r="B163" s="22"/>
       <c r="C163" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D163" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E163" s="38"/>
       <c r="F163" s="38"/>
@@ -50133,13 +50200,13 @@
         <v>4128</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C164" s="23" t="s">
-        <v>5049</v>
+        <v>5052</v>
       </c>
       <c r="D164" s="25" t="s">
-        <v>5050</v>
+        <v>5053</v>
       </c>
       <c r="E164" s="40"/>
       <c r="F164" s="40"/>
@@ -50183,7 +50250,7 @@
     <row r="166" ht="18.75" customHeight="1">
       <c r="A166" s="26"/>
       <c r="B166" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C166" s="26"/>
       <c r="D166" s="22"/>
@@ -50211,10 +50278,10 @@
         <v>3524</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>5051</v>
+        <v>5054</v>
       </c>
       <c r="D167" s="25" t="s">
-        <v>5052</v>
+        <v>5055</v>
       </c>
       <c r="E167" s="40"/>
       <c r="F167" s="40"/>
@@ -50238,10 +50305,10 @@
         <v>3638</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>5053</v>
+        <v>5056</v>
       </c>
       <c r="D168" s="25" t="s">
-        <v>5054</v>
+        <v>5057</v>
       </c>
       <c r="E168" s="40"/>
       <c r="F168" s="40"/>
@@ -50262,7 +50329,7 @@
     <row r="169" ht="18.75" customHeight="1">
       <c r="A169" s="31"/>
       <c r="B169" s="32" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C169" s="33"/>
       <c r="D169" s="34"/>
@@ -50305,19 +50372,19 @@
     </row>
     <row r="171" ht="18.75" customHeight="1">
       <c r="A171" s="18" t="s">
-        <v>5055</v>
+        <v>5058</v>
       </c>
       <c r="B171" s="19"/>
       <c r="C171" s="20" t="s">
-        <v>5056</v>
+        <v>5059</v>
       </c>
       <c r="D171" s="19"/>
       <c r="E171" s="20" t="s">
-        <v>5057</v>
+        <v>5060</v>
       </c>
       <c r="F171" s="19"/>
       <c r="G171" s="20" t="s">
-        <v>5058</v>
+        <v>5061</v>
       </c>
       <c r="H171" s="19"/>
       <c r="I171" s="10"/>
@@ -50334,19 +50401,19 @@
     </row>
     <row r="172" ht="18.75" customHeight="1">
       <c r="A172" s="21" t="s">
-        <v>4337</v>
+        <v>4340</v>
       </c>
       <c r="B172" s="22"/>
       <c r="C172" s="10" t="s">
-        <v>5059</v>
+        <v>5062</v>
       </c>
       <c r="D172" s="22"/>
       <c r="E172" s="10" t="s">
-        <v>4871</v>
+        <v>4874</v>
       </c>
       <c r="F172" s="22"/>
       <c r="G172" s="10" t="s">
-        <v>5060</v>
+        <v>5063</v>
       </c>
       <c r="H172" s="22"/>
       <c r="I172" s="10"/>
@@ -50363,19 +50430,19 @@
     </row>
     <row r="173" ht="18.75" customHeight="1">
       <c r="A173" s="21" t="s">
-        <v>4343</v>
+        <v>4346</v>
       </c>
       <c r="B173" s="22"/>
       <c r="C173" s="23" t="s">
-        <v>5061</v>
+        <v>5064</v>
       </c>
       <c r="D173" s="22"/>
       <c r="E173" s="23" t="s">
-        <v>4877</v>
+        <v>4880</v>
       </c>
       <c r="F173" s="22"/>
       <c r="G173" s="23" t="s">
-        <v>5062</v>
+        <v>5065</v>
       </c>
       <c r="H173" s="22"/>
       <c r="I173" s="10"/>
@@ -50392,19 +50459,19 @@
     </row>
     <row r="174" ht="18.75" customHeight="1">
       <c r="A174" s="21" t="s">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="B174" s="22"/>
       <c r="C174" s="23" t="s">
-        <v>5063</v>
+        <v>5066</v>
       </c>
       <c r="D174" s="22"/>
       <c r="E174" s="23" t="s">
-        <v>4883</v>
+        <v>4886</v>
       </c>
       <c r="F174" s="22"/>
       <c r="G174" s="23" t="s">
-        <v>5064</v>
+        <v>5067</v>
       </c>
       <c r="H174" s="22"/>
       <c r="I174" s="10"/>
@@ -50421,26 +50488,26 @@
     </row>
     <row r="175" ht="18.75" customHeight="1">
       <c r="A175" s="21" t="s">
-        <v>4355</v>
+        <v>4358</v>
       </c>
       <c r="B175" s="22"/>
       <c r="C175" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D175" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E175" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="F175" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="G175" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="H175" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="I175" s="10"/>
       <c r="J175" s="10"/>
@@ -50459,25 +50526,25 @@
         <v>4128</v>
       </c>
       <c r="B176" s="24" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C176" s="23" t="s">
-        <v>5065</v>
+        <v>5068</v>
       </c>
       <c r="D176" s="25" t="s">
-        <v>5066</v>
+        <v>5069</v>
       </c>
       <c r="E176" s="23" t="s">
-        <v>4892</v>
+        <v>4895</v>
       </c>
       <c r="F176" s="25" t="s">
-        <v>4893</v>
+        <v>4896</v>
       </c>
       <c r="G176" s="23" t="s">
-        <v>5067</v>
+        <v>5070</v>
       </c>
       <c r="H176" s="25" t="s">
-        <v>5068</v>
+        <v>5071</v>
       </c>
       <c r="I176" s="10"/>
       <c r="J176" s="10"/>
@@ -50497,22 +50564,22 @@
         <v>3684</v>
       </c>
       <c r="C177" s="23" t="s">
-        <v>5069</v>
+        <v>5072</v>
       </c>
       <c r="D177" s="25" t="s">
-        <v>5070</v>
+        <v>5073</v>
       </c>
       <c r="E177" s="23" t="s">
-        <v>4903</v>
+        <v>4906</v>
       </c>
       <c r="F177" s="25" t="s">
-        <v>4904</v>
+        <v>4907</v>
       </c>
       <c r="G177" s="23" t="s">
-        <v>5071</v>
+        <v>5074</v>
       </c>
       <c r="H177" s="25" t="s">
-        <v>5072</v>
+        <v>5075</v>
       </c>
       <c r="I177" s="10"/>
       <c r="J177" s="10"/>
@@ -50529,25 +50596,25 @@
     <row r="178" ht="18.75" customHeight="1">
       <c r="A178" s="26"/>
       <c r="B178" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C178" s="23" t="s">
+        <v>5072</v>
+      </c>
+      <c r="D178" s="25" t="s">
         <v>5069</v>
       </c>
-      <c r="D178" s="25" t="s">
-        <v>5066</v>
-      </c>
       <c r="E178" s="23" t="s">
-        <v>4903</v>
+        <v>4906</v>
       </c>
       <c r="F178" s="25" t="s">
-        <v>4893</v>
+        <v>4896</v>
       </c>
       <c r="G178" s="23" t="s">
+        <v>5074</v>
+      </c>
+      <c r="H178" s="25" t="s">
         <v>5071</v>
-      </c>
-      <c r="H178" s="25" t="s">
-        <v>5068</v>
       </c>
       <c r="I178" s="10"/>
       <c r="J178" s="10"/>
@@ -50569,22 +50636,22 @@
         <v>3524</v>
       </c>
       <c r="C179" s="23" t="s">
-        <v>5073</v>
+        <v>5076</v>
       </c>
       <c r="D179" s="25" t="s">
-        <v>5074</v>
+        <v>5077</v>
       </c>
       <c r="E179" s="23" t="s">
-        <v>4915</v>
+        <v>4918</v>
       </c>
       <c r="F179" s="25" t="s">
-        <v>4916</v>
+        <v>4919</v>
       </c>
       <c r="G179" s="23" t="s">
-        <v>5075</v>
+        <v>5078</v>
       </c>
       <c r="H179" s="25" t="s">
-        <v>5076</v>
+        <v>5079</v>
       </c>
       <c r="I179" s="10"/>
       <c r="J179" s="10"/>
@@ -50604,22 +50671,22 @@
         <v>3638</v>
       </c>
       <c r="C180" s="23" t="s">
-        <v>5077</v>
+        <v>5080</v>
       </c>
       <c r="D180" s="25" t="s">
-        <v>5078</v>
+        <v>5081</v>
       </c>
       <c r="E180" s="23" t="s">
-        <v>4927</v>
+        <v>4930</v>
       </c>
       <c r="F180" s="10" t="s">
-        <v>4928</v>
+        <v>4931</v>
       </c>
       <c r="G180" s="23" t="s">
-        <v>5079</v>
+        <v>5082</v>
       </c>
       <c r="H180" s="25" t="s">
-        <v>5080</v>
+        <v>5083</v>
       </c>
       <c r="I180" s="10"/>
       <c r="J180" s="10"/>
@@ -50636,25 +50703,25 @@
     <row r="181" ht="18.75" customHeight="1">
       <c r="A181" s="31"/>
       <c r="B181" s="32" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C181" s="36" t="s">
-        <v>5081</v>
+        <v>5084</v>
       </c>
       <c r="D181" s="28" t="s">
-        <v>5082</v>
+        <v>5085</v>
       </c>
       <c r="E181" s="36" t="s">
-        <v>4939</v>
+        <v>4942</v>
       </c>
       <c r="F181" s="28" t="s">
-        <v>4940</v>
+        <v>4943</v>
       </c>
       <c r="G181" s="36" t="s">
-        <v>5083</v>
+        <v>5086</v>
       </c>
       <c r="H181" s="28" t="s">
-        <v>5084</v>
+        <v>5087</v>
       </c>
       <c r="I181" s="10"/>
       <c r="J181" s="10"/>
@@ -50691,11 +50758,11 @@
     </row>
     <row r="183" ht="18.75" customHeight="1">
       <c r="A183" s="18" t="s">
-        <v>5085</v>
+        <v>5088</v>
       </c>
       <c r="B183" s="19"/>
       <c r="C183" s="18" t="s">
-        <v>5086</v>
+        <v>5089</v>
       </c>
       <c r="D183" s="19"/>
       <c r="E183" s="10"/>
@@ -50716,11 +50783,11 @@
     </row>
     <row r="184" ht="18.75" customHeight="1">
       <c r="A184" s="21" t="s">
-        <v>4337</v>
+        <v>4340</v>
       </c>
       <c r="B184" s="22"/>
       <c r="C184" s="23" t="s">
-        <v>5087</v>
+        <v>5090</v>
       </c>
       <c r="D184" s="22"/>
       <c r="E184" s="10"/>
@@ -50741,11 +50808,11 @@
     </row>
     <row r="185" ht="18.75" customHeight="1">
       <c r="A185" s="21" t="s">
-        <v>4343</v>
+        <v>4346</v>
       </c>
       <c r="B185" s="22"/>
       <c r="C185" s="23" t="s">
-        <v>5088</v>
+        <v>5091</v>
       </c>
       <c r="D185" s="22"/>
       <c r="E185" s="10"/>
@@ -50766,11 +50833,11 @@
     </row>
     <row r="186" ht="18.75" customHeight="1">
       <c r="A186" s="21" t="s">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="B186" s="22"/>
       <c r="C186" s="23" t="s">
-        <v>5089</v>
+        <v>5092</v>
       </c>
       <c r="D186" s="22"/>
       <c r="E186" s="10"/>
@@ -50791,14 +50858,14 @@
     </row>
     <row r="187" ht="18.75" customHeight="1">
       <c r="A187" s="21" t="s">
-        <v>4355</v>
+        <v>4358</v>
       </c>
       <c r="B187" s="22"/>
       <c r="C187" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D187" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E187" s="10"/>
       <c r="F187" s="10"/>
@@ -50821,13 +50888,13 @@
         <v>4128</v>
       </c>
       <c r="B188" s="24" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C188" s="23" t="s">
-        <v>5090</v>
+        <v>5093</v>
       </c>
       <c r="D188" s="25" t="s">
-        <v>5091</v>
+        <v>5094</v>
       </c>
       <c r="E188" s="10"/>
       <c r="F188" s="10"/>
@@ -50851,10 +50918,10 @@
         <v>3684</v>
       </c>
       <c r="C189" s="23" t="s">
-        <v>5092</v>
+        <v>5095</v>
       </c>
       <c r="D189" s="25" t="s">
-        <v>5093</v>
+        <v>5096</v>
       </c>
       <c r="E189" s="10"/>
       <c r="F189" s="10"/>
@@ -50875,13 +50942,13 @@
     <row r="190" ht="18.75" customHeight="1">
       <c r="A190" s="26"/>
       <c r="B190" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C190" s="23" t="s">
-        <v>5092</v>
+        <v>5095</v>
       </c>
       <c r="D190" s="25" t="s">
-        <v>5091</v>
+        <v>5094</v>
       </c>
       <c r="E190" s="10"/>
       <c r="F190" s="10"/>
@@ -50907,10 +50974,10 @@
         <v>3524</v>
       </c>
       <c r="C191" s="23" t="s">
-        <v>5094</v>
+        <v>5097</v>
       </c>
       <c r="D191" s="25" t="s">
-        <v>5095</v>
+        <v>5098</v>
       </c>
       <c r="E191" s="10"/>
       <c r="F191" s="10"/>
@@ -50933,10 +51000,10 @@
         <v>3638</v>
       </c>
       <c r="C192" s="23" t="s">
-        <v>5096</v>
+        <v>5099</v>
       </c>
       <c r="D192" s="25" t="s">
-        <v>5097</v>
+        <v>5100</v>
       </c>
       <c r="E192" s="10"/>
       <c r="F192" s="10"/>
@@ -50956,13 +51023,13 @@
     </row>
     <row r="193" ht="18.75" customHeight="1">
       <c r="B193" s="24" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C193" s="23" t="s">
-        <v>5098</v>
+        <v>5101</v>
       </c>
       <c r="D193" s="25" t="s">
-        <v>5099</v>
+        <v>5102</v>
       </c>
       <c r="E193" s="10"/>
       <c r="F193" s="10"/>
@@ -50982,14 +51049,14 @@
     </row>
     <row r="194" ht="18.75" customHeight="1">
       <c r="A194" s="21" t="s">
-        <v>4409</v>
+        <v>4412</v>
       </c>
       <c r="B194" s="22"/>
       <c r="C194" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D194" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E194" s="10"/>
       <c r="F194" s="10"/>
@@ -51012,13 +51079,13 @@
         <v>4128</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C195" s="23" t="s">
-        <v>5100</v>
+        <v>5103</v>
       </c>
       <c r="D195" s="25" t="s">
-        <v>5101</v>
+        <v>5104</v>
       </c>
       <c r="E195" s="10"/>
       <c r="F195" s="10"/>
@@ -51062,7 +51129,7 @@
     <row r="197" ht="18.75" customHeight="1">
       <c r="A197" s="26"/>
       <c r="B197" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C197" s="26"/>
       <c r="D197" s="22"/>
@@ -51090,10 +51157,10 @@
         <v>3524</v>
       </c>
       <c r="C198" s="23" t="s">
-        <v>5102</v>
+        <v>5105</v>
       </c>
       <c r="D198" s="25" t="s">
-        <v>5103</v>
+        <v>5106</v>
       </c>
       <c r="E198" s="10"/>
       <c r="F198" s="10"/>
@@ -51117,10 +51184,10 @@
         <v>3638</v>
       </c>
       <c r="C199" s="23" t="s">
-        <v>5104</v>
+        <v>5107</v>
       </c>
       <c r="D199" s="25" t="s">
-        <v>5105</v>
+        <v>5108</v>
       </c>
       <c r="E199" s="10"/>
       <c r="F199" s="10"/>
@@ -51141,7 +51208,7 @@
     <row r="200" ht="18.75" customHeight="1">
       <c r="A200" s="31"/>
       <c r="B200" s="32" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C200" s="31"/>
       <c r="D200" s="34"/>
@@ -51184,11 +51251,11 @@
     </row>
     <row r="202" ht="18.75" customHeight="1">
       <c r="A202" s="18" t="s">
-        <v>5106</v>
+        <v>5109</v>
       </c>
       <c r="B202" s="19"/>
       <c r="C202" s="18" t="s">
-        <v>5107</v>
+        <v>5110</v>
       </c>
       <c r="D202" s="19"/>
       <c r="E202" s="10"/>
@@ -51209,11 +51276,11 @@
     </row>
     <row r="203" ht="18.75" customHeight="1">
       <c r="A203" s="21" t="s">
-        <v>4337</v>
+        <v>4340</v>
       </c>
       <c r="B203" s="22"/>
       <c r="C203" s="23" t="s">
-        <v>5108</v>
+        <v>5111</v>
       </c>
       <c r="D203" s="22"/>
       <c r="E203" s="10"/>
@@ -51234,11 +51301,11 @@
     </row>
     <row r="204" ht="18.75" customHeight="1">
       <c r="A204" s="21" t="s">
-        <v>4343</v>
+        <v>4346</v>
       </c>
       <c r="B204" s="22"/>
       <c r="C204" s="23" t="s">
-        <v>5109</v>
+        <v>5112</v>
       </c>
       <c r="D204" s="22"/>
       <c r="E204" s="10"/>
@@ -51259,11 +51326,11 @@
     </row>
     <row r="205" ht="18.75" customHeight="1">
       <c r="A205" s="21" t="s">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="B205" s="22"/>
       <c r="C205" s="23" t="s">
-        <v>5110</v>
+        <v>5113</v>
       </c>
       <c r="D205" s="22"/>
       <c r="E205" s="10"/>
@@ -51284,14 +51351,14 @@
     </row>
     <row r="206" ht="18.75" customHeight="1">
       <c r="A206" s="21" t="s">
-        <v>4355</v>
+        <v>4358</v>
       </c>
       <c r="B206" s="22"/>
       <c r="C206" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D206" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E206" s="10"/>
       <c r="F206" s="10"/>
@@ -51314,13 +51381,13 @@
         <v>4128</v>
       </c>
       <c r="B207" s="24" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C207" s="23" t="s">
-        <v>5111</v>
+        <v>5114</v>
       </c>
       <c r="D207" s="25" t="s">
-        <v>5112</v>
+        <v>5115</v>
       </c>
       <c r="E207" s="10"/>
       <c r="F207" s="10"/>
@@ -51344,10 +51411,10 @@
         <v>3684</v>
       </c>
       <c r="C208" s="23" t="s">
-        <v>5113</v>
+        <v>5116</v>
       </c>
       <c r="D208" s="25" t="s">
-        <v>5114</v>
+        <v>5117</v>
       </c>
       <c r="E208" s="10"/>
       <c r="F208" s="10"/>
@@ -51368,13 +51435,13 @@
     <row r="209" ht="18.75" customHeight="1">
       <c r="A209" s="26"/>
       <c r="B209" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C209" s="23" t="s">
-        <v>5113</v>
+        <v>5116</v>
       </c>
       <c r="D209" s="25" t="s">
-        <v>5112</v>
+        <v>5115</v>
       </c>
       <c r="E209" s="10"/>
       <c r="F209" s="10"/>
@@ -51400,10 +51467,10 @@
         <v>3524</v>
       </c>
       <c r="C210" s="23" t="s">
-        <v>5115</v>
+        <v>5118</v>
       </c>
       <c r="D210" s="25" t="s">
-        <v>5116</v>
+        <v>5119</v>
       </c>
       <c r="E210" s="10"/>
       <c r="F210" s="10"/>
@@ -51426,10 +51493,10 @@
         <v>3638</v>
       </c>
       <c r="C211" s="23" t="s">
-        <v>5117</v>
+        <v>5120</v>
       </c>
       <c r="D211" s="25" t="s">
-        <v>5118</v>
+        <v>5121</v>
       </c>
       <c r="E211" s="10"/>
       <c r="F211" s="10"/>
@@ -51449,13 +51516,13 @@
     </row>
     <row r="212" ht="18.75" customHeight="1">
       <c r="B212" s="24" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C212" s="23" t="s">
-        <v>5119</v>
+        <v>5122</v>
       </c>
       <c r="D212" s="25" t="s">
-        <v>5120</v>
+        <v>5123</v>
       </c>
       <c r="E212" s="10"/>
       <c r="F212" s="10"/>
@@ -51475,14 +51542,14 @@
     </row>
     <row r="213" ht="18.75" customHeight="1">
       <c r="A213" s="21" t="s">
-        <v>4409</v>
+        <v>4412</v>
       </c>
       <c r="B213" s="22"/>
       <c r="C213" s="8" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D213" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E213" s="10"/>
       <c r="F213" s="10"/>
@@ -51505,13 +51572,13 @@
         <v>4128</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C214" s="23" t="s">
-        <v>5121</v>
+        <v>5124</v>
       </c>
       <c r="D214" s="25" t="s">
-        <v>5122</v>
+        <v>5125</v>
       </c>
       <c r="E214" s="10"/>
       <c r="F214" s="10"/>
@@ -51555,7 +51622,7 @@
     <row r="216" ht="18.75" customHeight="1">
       <c r="A216" s="26"/>
       <c r="B216" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C216" s="26"/>
       <c r="D216" s="22"/>
@@ -51583,10 +51650,10 @@
         <v>3524</v>
       </c>
       <c r="C217" s="23" t="s">
-        <v>5123</v>
+        <v>5126</v>
       </c>
       <c r="D217" s="25" t="s">
-        <v>5124</v>
+        <v>5127</v>
       </c>
       <c r="E217" s="10"/>
       <c r="F217" s="10"/>
@@ -51610,10 +51677,10 @@
         <v>3638</v>
       </c>
       <c r="C218" s="23" t="s">
-        <v>5125</v>
+        <v>5128</v>
       </c>
       <c r="D218" s="25" t="s">
-        <v>5126</v>
+        <v>5129</v>
       </c>
       <c r="E218" s="10"/>
       <c r="F218" s="10"/>
@@ -51634,7 +51701,7 @@
     <row r="219" ht="18.75" customHeight="1">
       <c r="A219" s="31"/>
       <c r="B219" s="32" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C219" s="31"/>
       <c r="D219" s="34"/>
@@ -51677,11 +51744,11 @@
     </row>
     <row r="221" ht="18.75" customHeight="1">
       <c r="A221" s="18" t="s">
-        <v>5127</v>
+        <v>5130</v>
       </c>
       <c r="B221" s="19"/>
       <c r="C221" s="18" t="s">
-        <v>5128</v>
+        <v>5131</v>
       </c>
       <c r="D221" s="19"/>
       <c r="E221" s="10"/>
@@ -51702,11 +51769,11 @@
     </row>
     <row r="222" ht="18.75" customHeight="1">
       <c r="A222" s="21" t="s">
-        <v>4337</v>
+        <v>4340</v>
       </c>
       <c r="B222" s="22"/>
       <c r="C222" s="23" t="s">
-        <v>5129</v>
+        <v>5132</v>
       </c>
       <c r="D222" s="22"/>
       <c r="E222" s="10"/>
@@ -51727,11 +51794,11 @@
     </row>
     <row r="223" ht="18.75" customHeight="1">
       <c r="A223" s="21" t="s">
-        <v>4343</v>
+        <v>4346</v>
       </c>
       <c r="B223" s="22"/>
       <c r="C223" s="23" t="s">
-        <v>5130</v>
+        <v>5133</v>
       </c>
       <c r="D223" s="22"/>
       <c r="E223" s="10"/>
@@ -51752,11 +51819,11 @@
     </row>
     <row r="224" ht="18.75" customHeight="1">
       <c r="A224" s="21" t="s">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="B224" s="22"/>
       <c r="C224" s="23" t="s">
-        <v>5131</v>
+        <v>5134</v>
       </c>
       <c r="D224" s="22"/>
       <c r="E224" s="10"/>
@@ -51777,14 +51844,14 @@
     </row>
     <row r="225" ht="18.75" customHeight="1">
       <c r="A225" s="21" t="s">
-        <v>4355</v>
+        <v>4358</v>
       </c>
       <c r="B225" s="22"/>
       <c r="C225" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D225" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E225" s="10"/>
       <c r="F225" s="10"/>
@@ -51807,13 +51874,13 @@
         <v>4128</v>
       </c>
       <c r="B226" s="24" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C226" s="23" t="s">
-        <v>5132</v>
+        <v>5135</v>
       </c>
       <c r="D226" s="25" t="s">
-        <v>5133</v>
+        <v>5136</v>
       </c>
       <c r="E226" s="10"/>
       <c r="F226" s="10"/>
@@ -51837,10 +51904,10 @@
         <v>3684</v>
       </c>
       <c r="C227" s="23" t="s">
-        <v>5134</v>
+        <v>5137</v>
       </c>
       <c r="D227" s="25" t="s">
-        <v>5135</v>
+        <v>5138</v>
       </c>
       <c r="E227" s="10"/>
       <c r="F227" s="10"/>
@@ -51861,13 +51928,13 @@
     <row r="228" ht="18.75" customHeight="1">
       <c r="A228" s="26"/>
       <c r="B228" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C228" s="23" t="s">
-        <v>5134</v>
+        <v>5137</v>
       </c>
       <c r="D228" s="25" t="s">
-        <v>5136</v>
+        <v>5139</v>
       </c>
       <c r="E228" s="10"/>
       <c r="F228" s="10"/>
@@ -51893,10 +51960,10 @@
         <v>3524</v>
       </c>
       <c r="C229" s="23" t="s">
-        <v>5137</v>
+        <v>5140</v>
       </c>
       <c r="D229" s="25" t="s">
-        <v>5138</v>
+        <v>5141</v>
       </c>
       <c r="E229" s="10"/>
       <c r="F229" s="10"/>
@@ -51920,10 +51987,10 @@
         <v>3638</v>
       </c>
       <c r="C230" s="23" t="s">
-        <v>5139</v>
+        <v>5142</v>
       </c>
       <c r="D230" s="25" t="s">
-        <v>5140</v>
+        <v>5143</v>
       </c>
       <c r="E230" s="10"/>
       <c r="F230" s="10"/>
@@ -51944,13 +52011,13 @@
     <row r="231" ht="18.75" customHeight="1">
       <c r="A231" s="31"/>
       <c r="B231" s="32" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C231" s="36" t="s">
-        <v>5141</v>
+        <v>5144</v>
       </c>
       <c r="D231" s="28" t="s">
-        <v>5142</v>
+        <v>5145</v>
       </c>
       <c r="E231" s="10"/>
       <c r="F231" s="10"/>
@@ -51991,11 +52058,11 @@
     </row>
     <row r="233" ht="18.75" customHeight="1">
       <c r="A233" s="18" t="s">
-        <v>5143</v>
+        <v>5146</v>
       </c>
       <c r="B233" s="19"/>
       <c r="C233" s="18" t="s">
-        <v>5144</v>
+        <v>5147</v>
       </c>
       <c r="D233" s="19"/>
       <c r="E233" s="10"/>
@@ -52016,11 +52083,11 @@
     </row>
     <row r="234" ht="18.75" customHeight="1">
       <c r="A234" s="21" t="s">
-        <v>4337</v>
+        <v>4340</v>
       </c>
       <c r="B234" s="22"/>
       <c r="C234" s="23" t="s">
-        <v>5145</v>
+        <v>5148</v>
       </c>
       <c r="D234" s="22"/>
       <c r="E234" s="10"/>
@@ -52041,11 +52108,11 @@
     </row>
     <row r="235" ht="18.75" customHeight="1">
       <c r="A235" s="21" t="s">
-        <v>4343</v>
+        <v>4346</v>
       </c>
       <c r="B235" s="22"/>
       <c r="C235" s="23" t="s">
-        <v>5146</v>
+        <v>5149</v>
       </c>
       <c r="D235" s="22"/>
       <c r="E235" s="10"/>
@@ -52066,11 +52133,11 @@
     </row>
     <row r="236" ht="18.75" customHeight="1">
       <c r="A236" s="21" t="s">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="B236" s="22"/>
       <c r="C236" s="23" t="s">
-        <v>5147</v>
+        <v>5150</v>
       </c>
       <c r="D236" s="22"/>
       <c r="E236" s="10"/>
@@ -52091,14 +52158,14 @@
     </row>
     <row r="237" ht="18.75" customHeight="1">
       <c r="A237" s="21" t="s">
-        <v>4355</v>
+        <v>4358</v>
       </c>
       <c r="B237" s="22"/>
       <c r="C237" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D237" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E237" s="10"/>
       <c r="F237" s="10"/>
@@ -52121,13 +52188,13 @@
         <v>4128</v>
       </c>
       <c r="B238" s="24" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C238" s="23" t="s">
-        <v>5148</v>
+        <v>5151</v>
       </c>
       <c r="D238" s="25" t="s">
-        <v>5149</v>
+        <v>5152</v>
       </c>
       <c r="E238" s="10"/>
       <c r="F238" s="10"/>
@@ -52151,10 +52218,10 @@
         <v>3684</v>
       </c>
       <c r="C239" s="23" t="s">
-        <v>5148</v>
+        <v>5151</v>
       </c>
       <c r="D239" s="25" t="s">
-        <v>5150</v>
+        <v>5153</v>
       </c>
       <c r="E239" s="10"/>
       <c r="F239" s="10"/>
@@ -52175,13 +52242,13 @@
     <row r="240" ht="18.75" customHeight="1">
       <c r="A240" s="26"/>
       <c r="B240" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C240" s="23" t="s">
-        <v>5148</v>
+        <v>5151</v>
       </c>
       <c r="D240" s="25" t="s">
-        <v>5151</v>
+        <v>5154</v>
       </c>
       <c r="E240" s="10"/>
       <c r="F240" s="10"/>
@@ -52207,10 +52274,10 @@
         <v>3524</v>
       </c>
       <c r="C241" s="23" t="s">
-        <v>5152</v>
+        <v>5155</v>
       </c>
       <c r="D241" s="25" t="s">
-        <v>5153</v>
+        <v>5156</v>
       </c>
       <c r="E241" s="10"/>
       <c r="F241" s="10"/>
@@ -52234,10 +52301,10 @@
         <v>3638</v>
       </c>
       <c r="C242" s="23" t="s">
-        <v>5154</v>
+        <v>5157</v>
       </c>
       <c r="D242" s="25" t="s">
-        <v>5155</v>
+        <v>5158</v>
       </c>
       <c r="E242" s="10"/>
       <c r="F242" s="10"/>
@@ -52258,13 +52325,13 @@
     <row r="243" ht="18.75" customHeight="1">
       <c r="A243" s="31"/>
       <c r="B243" s="32" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C243" s="36" t="s">
-        <v>5156</v>
+        <v>5159</v>
       </c>
       <c r="D243" s="28" t="s">
-        <v>5157</v>
+        <v>5160</v>
       </c>
       <c r="E243" s="10"/>
       <c r="F243" s="10"/>
@@ -52305,15 +52372,15 @@
     </row>
     <row r="245" ht="18.75" customHeight="1">
       <c r="A245" s="18" t="s">
-        <v>5158</v>
+        <v>5161</v>
       </c>
       <c r="B245" s="19"/>
       <c r="C245" s="18" t="s">
-        <v>5159</v>
+        <v>5162</v>
       </c>
       <c r="D245" s="19"/>
       <c r="E245" s="18" t="s">
-        <v>5160</v>
+        <v>5163</v>
       </c>
       <c r="F245" s="19"/>
       <c r="G245" s="10"/>
@@ -52332,20 +52399,20 @@
     </row>
     <row r="246" ht="18.75" customHeight="1">
       <c r="A246" s="21" t="s">
-        <v>4355</v>
+        <v>4358</v>
       </c>
       <c r="B246" s="22"/>
       <c r="C246" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="D246" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="E246" s="21" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="F246" s="24" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="G246" s="10"/>
       <c r="H246" s="10"/>
@@ -52366,19 +52433,19 @@
         <v>4128</v>
       </c>
       <c r="B247" s="24" t="s">
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="C247" s="23" t="s">
-        <v>5161</v>
+        <v>5164</v>
       </c>
       <c r="D247" s="25" t="s">
-        <v>5162</v>
+        <v>5165</v>
       </c>
       <c r="E247" s="23" t="s">
-        <v>5163</v>
+        <v>5166</v>
       </c>
       <c r="F247" s="25" t="s">
-        <v>5164</v>
+        <v>5167</v>
       </c>
       <c r="G247" s="10"/>
       <c r="H247" s="10"/>
@@ -52400,16 +52467,16 @@
         <v>3684</v>
       </c>
       <c r="C248" s="23" t="s">
-        <v>5161</v>
+        <v>5164</v>
       </c>
       <c r="D248" s="25" t="s">
-        <v>4455</v>
+        <v>4458</v>
       </c>
       <c r="E248" s="23" t="s">
-        <v>4981</v>
+        <v>4984</v>
       </c>
       <c r="F248" s="25" t="s">
-        <v>5165</v>
+        <v>5168</v>
       </c>
       <c r="G248" s="10"/>
       <c r="H248" s="10"/>
@@ -52428,19 +52495,19 @@
     <row r="249" ht="18.75" customHeight="1">
       <c r="A249" s="26"/>
       <c r="B249" s="24" t="s">
-        <v>4373</v>
+        <v>4376</v>
       </c>
       <c r="C249" s="23" t="s">
-        <v>5161</v>
+        <v>5164</v>
       </c>
       <c r="D249" s="25" t="s">
-        <v>4445</v>
+        <v>4448</v>
       </c>
       <c r="E249" s="23" t="s">
-        <v>4981</v>
+        <v>4984</v>
       </c>
       <c r="F249" s="25" t="s">
-        <v>5166</v>
+        <v>5169</v>
       </c>
       <c r="G249" s="10"/>
       <c r="H249" s="10"/>
@@ -52464,16 +52531,16 @@
         <v>3524</v>
       </c>
       <c r="C250" s="23" t="s">
-        <v>5167</v>
+        <v>5170</v>
       </c>
       <c r="D250" s="25" t="s">
-        <v>5168</v>
+        <v>5171</v>
       </c>
       <c r="E250" s="23" t="s">
-        <v>5169</v>
+        <v>5172</v>
       </c>
       <c r="F250" s="25" t="s">
-        <v>5170</v>
+        <v>5173</v>
       </c>
       <c r="G250" s="10"/>
       <c r="H250" s="10"/>
@@ -52495,16 +52562,16 @@
         <v>3638</v>
       </c>
       <c r="C251" s="23" t="s">
-        <v>5171</v>
+        <v>5174</v>
       </c>
       <c r="D251" s="25" t="s">
-        <v>5172</v>
+        <v>5175</v>
       </c>
       <c r="E251" s="23" t="s">
-        <v>5173</v>
+        <v>5176</v>
       </c>
       <c r="F251" s="25" t="s">
-        <v>5174</v>
+        <v>5177</v>
       </c>
       <c r="G251" s="10"/>
       <c r="H251" s="10"/>
@@ -52523,19 +52590,19 @@
     <row r="252" ht="18.75" customHeight="1">
       <c r="A252" s="31"/>
       <c r="B252" s="32" t="s">
-        <v>4398</v>
+        <v>4401</v>
       </c>
       <c r="C252" s="36" t="s">
         <v>2075</v>
       </c>
       <c r="D252" s="28" t="s">
-        <v>5175</v>
+        <v>5178</v>
       </c>
       <c r="E252" s="36" t="s">
         <v>2776</v>
       </c>
       <c r="F252" s="28" t="s">
-        <v>5176</v>
+        <v>5179</v>
       </c>
       <c r="G252" s="10"/>
       <c r="H252" s="10"/>
@@ -53012,11 +53079,11 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="42" t="s">
-        <v>5177</v>
+        <v>5180</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="42" t="s">
-        <v>5178</v>
+        <v>5181</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
@@ -53024,14 +53091,14 @@
         <v>206</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="43" t="s">
-        <v>5180</v>
+        <v>5183</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>5181</v>
+        <v>5184</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
@@ -53039,14 +53106,14 @@
         <v>1254</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>5182</v>
+        <v>5185</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="43" t="s">
-        <v>5183</v>
+        <v>5186</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>5184</v>
+        <v>5187</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
@@ -53054,14 +53121,14 @@
         <v>1770</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>5185</v>
+        <v>5188</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="43" t="s">
-        <v>5186</v>
+        <v>5189</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>5187</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
@@ -53069,14 +53136,14 @@
         <v>1866</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>5188</v>
+        <v>5191</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="43" t="s">
-        <v>5189</v>
+        <v>5192</v>
       </c>
       <c r="G5" s="43" t="s">
-        <v>5190</v>
+        <v>5193</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
@@ -53084,14 +53151,14 @@
         <v>1976</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>5191</v>
+        <v>5194</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="43" t="s">
-        <v>5192</v>
+        <v>5195</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>5193</v>
+        <v>5196</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
@@ -53099,14 +53166,14 @@
         <v>2075</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>5194</v>
+        <v>5197</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="43" t="s">
-        <v>5195</v>
+        <v>5198</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>5196</v>
+        <v>5199</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
@@ -53114,14 +53181,14 @@
         <v>2146</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>5197</v>
+        <v>5200</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="43" t="s">
-        <v>5198</v>
+        <v>5201</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>5199</v>
+        <v>5202</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
@@ -53129,14 +53196,14 @@
         <v>2776</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>5200</v>
+        <v>5203</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="43" t="s">
-        <v>5201</v>
+        <v>5204</v>
       </c>
       <c r="G9" s="43" t="s">
-        <v>5202</v>
+        <v>5205</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
@@ -53144,14 +53211,14 @@
         <v>2995</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>5203</v>
+        <v>5206</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="43" t="s">
-        <v>5204</v>
+        <v>5207</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>5205</v>
+        <v>5208</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
@@ -53159,14 +53226,14 @@
         <v>3610</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>5206</v>
+        <v>5209</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="43" t="s">
-        <v>5207</v>
+        <v>5210</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>5208</v>
+        <v>5211</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
@@ -53175,10 +53242,10 @@
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
       <c r="E12" s="43" t="s">
-        <v>5209</v>
+        <v>5212</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>5210</v>
+        <v>5213</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
@@ -53187,10 +53254,10 @@
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
       <c r="E13" s="43" t="s">
-        <v>5211</v>
+        <v>5214</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>5212</v>
+        <v>5215</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
@@ -53199,113 +53266,113 @@
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="43" t="s">
-        <v>5213</v>
+        <v>5216</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>5214</v>
+        <v>5217</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="42" t="s">
-        <v>5215</v>
+        <v>5218</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>5216</v>
+        <v>5219</v>
       </c>
       <c r="G15" s="45" t="s">
-        <v>5217</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>5218</v>
+        <v>5221</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>5219</v>
+        <v>5222</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>5220</v>
+        <v>5223</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>5221</v>
+        <v>5224</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>5222</v>
+        <v>5225</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>5223</v>
+        <v>5226</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>5224</v>
+        <v>5227</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>5225</v>
+        <v>5228</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>5226</v>
+        <v>5229</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>5227</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>5228</v>
+        <v>5231</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>5229</v>
+        <v>5232</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>5230</v>
+        <v>5233</v>
       </c>
       <c r="G19" s="43" t="s">
-        <v>5231</v>
+        <v>5234</v>
       </c>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>5232</v>
+        <v>5235</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>5233</v>
+        <v>5236</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>5234</v>
+        <v>5237</v>
       </c>
       <c r="G20" s="43" t="s">
-        <v>5235</v>
+        <v>5238</v>
       </c>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>5236</v>
+        <v>5239</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>5237</v>
+        <v>5240</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>5238</v>
+        <v>5241</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>5239</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>5240</v>
+        <v>5243</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>5241</v>
+        <v>5244</v>
       </c>
       <c r="E22" s="46" t="s">
-        <v>5242</v>
+        <v>5245</v>
       </c>
       <c r="G22" s="46" t="s">
-        <v>5243</v>
+        <v>5246</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
@@ -53320,71 +53387,71 @@
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
       <c r="E24" s="43" t="s">
-        <v>5244</v>
+        <v>5247</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>5245</v>
+        <v>5248</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="E25" s="43" t="s">
-        <v>5246</v>
+        <v>5249</v>
       </c>
       <c r="G25" s="43" t="s">
-        <v>5247</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="42" t="s">
-        <v>5248</v>
+        <v>5251</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>5249</v>
+        <v>5252</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>5250</v>
+        <v>5253</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>5251</v>
+        <v>5254</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>5252</v>
+        <v>5255</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>5253</v>
+        <v>5256</v>
       </c>
       <c r="G27" s="43" t="s">
-        <v>5254</v>
+        <v>5257</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="43" t="s">
-        <v>5255</v>
+        <v>5258</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>5256</v>
+        <v>5259</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>5257</v>
+        <v>5260</v>
       </c>
       <c r="G28" s="43" t="s">
-        <v>5258</v>
+        <v>5261</v>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="43" t="s">
-        <v>5259</v>
+        <v>5262</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>5260</v>
+        <v>5263</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>5261</v>
+        <v>5264</v>
       </c>
       <c r="G29" s="43" t="s">
-        <v>5262</v>
+        <v>5265</v>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1">
@@ -53604,10 +53671,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="43" t="s">
-        <v>5263</v>
+        <v>5266</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>5264</v>
+        <v>5267</v>
       </c>
       <c r="C1" s="12"/>
     </row>
@@ -53616,34 +53683,34 @@
         <v>34</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>5265</v>
+        <v>5268</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>5266</v>
+        <v>5269</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>5267</v>
+        <v>5270</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>5268</v>
+        <v>5271</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>5269</v>
+        <v>5272</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>5270</v>
+        <v>5273</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>5271</v>
+        <v>5274</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -53652,70 +53719,70 @@
         <v>1470</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>5272</v>
+        <v>5275</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>5273</v>
+        <v>5276</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>5274</v>
+        <v>5277</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>5275</v>
+        <v>5278</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>5276</v>
+        <v>5279</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>5277</v>
+        <v>5280</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>5278</v>
+        <v>5281</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>5279</v>
+        <v>5282</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>5280</v>
+        <v>5283</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>5281</v>
+        <v>5284</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>5282</v>
+        <v>5285</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>5283</v>
+        <v>5286</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>5284</v>
+        <v>5287</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>5285</v>
+        <v>5288</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>5286</v>
+        <v>5289</v>
       </c>
       <c r="C13" s="12"/>
     </row>
@@ -53724,7 +53791,7 @@
         <v>4103</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>5287</v>
+        <v>5290</v>
       </c>
       <c r="C14" s="12"/>
     </row>
@@ -53735,19 +53802,19 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>5288</v>
+        <v>5291</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>5289</v>
+        <v>5292</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>5290</v>
+        <v>5293</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>5291</v>
+        <v>5294</v>
       </c>
       <c r="C17" s="12"/>
     </row>
@@ -53758,235 +53825,235 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>5292</v>
+        <v>5295</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>5293</v>
+        <v>5296</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>5294</v>
+        <v>5297</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>5295</v>
+        <v>5298</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>5296</v>
+        <v>5299</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>5297</v>
+        <v>5300</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>5298</v>
+        <v>5301</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>5299</v>
+        <v>5302</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>5300</v>
+        <v>5303</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>5301</v>
+        <v>5304</v>
       </c>
       <c r="C23" s="12"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="43" t="s">
-        <v>5302</v>
+        <v>5305</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>5303</v>
+        <v>5306</v>
       </c>
       <c r="C24" s="12"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="43" t="s">
-        <v>5304</v>
+        <v>5307</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>5305</v>
+        <v>5308</v>
       </c>
       <c r="C25" s="12"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="43" t="s">
-        <v>5306</v>
+        <v>5309</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>5307</v>
+        <v>5310</v>
       </c>
       <c r="C26" s="12"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>5308</v>
+        <v>5311</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>5309</v>
+        <v>5312</v>
       </c>
       <c r="C27" s="12"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="43" t="s">
-        <v>5310</v>
+        <v>5313</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>5311</v>
+        <v>5314</v>
       </c>
       <c r="C28" s="12"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="43" t="s">
-        <v>5312</v>
+        <v>5315</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>5313</v>
+        <v>5316</v>
       </c>
       <c r="C29" s="12"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="43" t="s">
-        <v>5314</v>
+        <v>5317</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>5315</v>
+        <v>5318</v>
       </c>
       <c r="C30" s="12"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="43" t="s">
-        <v>5316</v>
+        <v>5319</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>5317</v>
+        <v>5320</v>
       </c>
       <c r="C31" s="12"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="43" t="s">
-        <v>5318</v>
+        <v>5321</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>5319</v>
+        <v>5322</v>
       </c>
       <c r="C32" s="12"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="43" t="s">
-        <v>5320</v>
+        <v>5323</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>5321</v>
+        <v>5324</v>
       </c>
       <c r="C33" s="12"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="43" t="s">
-        <v>5322</v>
+        <v>5325</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>5323</v>
+        <v>5326</v>
       </c>
       <c r="C34" s="12"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="43" t="s">
-        <v>5324</v>
+        <v>5327</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>5325</v>
+        <v>5328</v>
       </c>
       <c r="C35" s="12"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="43" t="s">
-        <v>5326</v>
+        <v>5329</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>5327</v>
+        <v>5330</v>
       </c>
       <c r="C36" s="12"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="43" t="s">
-        <v>5328</v>
+        <v>5331</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>5329</v>
+        <v>5332</v>
       </c>
       <c r="C37" s="12"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="43" t="s">
-        <v>5330</v>
+        <v>5333</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>5331</v>
+        <v>5334</v>
       </c>
       <c r="C38" s="12"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="43" t="s">
-        <v>5332</v>
+        <v>5335</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>5333</v>
+        <v>5336</v>
       </c>
       <c r="C39" s="12"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="43" t="s">
-        <v>5334</v>
+        <v>5337</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>5335</v>
+        <v>5338</v>
       </c>
       <c r="C40" s="12"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="43" t="s">
-        <v>5336</v>
+        <v>5339</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>5337</v>
+        <v>5340</v>
       </c>
       <c r="C41" s="12"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="43" t="s">
-        <v>5338</v>
+        <v>5341</v>
       </c>
       <c r="B42" s="43" t="s">
-        <v>5339</v>
+        <v>5342</v>
       </c>
       <c r="C42" s="12"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="43" t="s">
-        <v>5340</v>
+        <v>5343</v>
       </c>
       <c r="B43" s="43" t="s">
-        <v>5341</v>
+        <v>5344</v>
       </c>
       <c r="C43" s="12"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" s="43" t="s">
-        <v>5342</v>
+        <v>5345</v>
       </c>
       <c r="B44" s="43" t="s">
-        <v>5343</v>
+        <v>5346</v>
       </c>
       <c r="C44" s="12"/>
     </row>
@@ -53995,34 +54062,34 @@
         <v>693</v>
       </c>
       <c r="B45" s="43" t="s">
-        <v>5344</v>
+        <v>5347</v>
       </c>
       <c r="C45" s="12"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="43" t="s">
-        <v>5345</v>
+        <v>5348</v>
       </c>
       <c r="B46" s="43" t="s">
-        <v>5346</v>
+        <v>5349</v>
       </c>
       <c r="C46" s="12"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="43" t="s">
-        <v>5347</v>
+        <v>5350</v>
       </c>
       <c r="B47" s="43" t="s">
-        <v>5348</v>
+        <v>5351</v>
       </c>
       <c r="C47" s="12"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="43" t="s">
-        <v>5349</v>
+        <v>5352</v>
       </c>
       <c r="B48" s="43" t="s">
-        <v>5350</v>
+        <v>5353</v>
       </c>
       <c r="C48" s="12"/>
     </row>
@@ -54045,130 +54112,130 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="47" t="s">
-        <v>5351</v>
+        <v>5354</v>
       </c>
       <c r="C1" s="12"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="47" t="s">
-        <v>5352</v>
+        <v>5355</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>5353</v>
+        <v>5356</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>5354</v>
+        <v>5357</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>5290</v>
+        <v>5293</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>5290</v>
+        <v>5293</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>5355</v>
+        <v>5358</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>5356</v>
+        <v>5359</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>5279</v>
+        <v>5282</v>
       </c>
       <c r="C5" s="12"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="43" t="s">
-        <v>5357</v>
+        <v>5360</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>5358</v>
+        <v>5361</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>5359</v>
+        <v>5362</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>5360</v>
+        <v>5363</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>5361</v>
+        <v>5364</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>5362</v>
+        <v>5365</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>5363</v>
+        <v>5366</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>5364</v>
+        <v>5367</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>5365</v>
+        <v>5368</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>5366</v>
+        <v>5369</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>5367</v>
+        <v>5370</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>5368</v>
+        <v>5371</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>5369</v>
+        <v>5372</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>5370</v>
+        <v>5373</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>5371</v>
+        <v>5374</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>5372</v>
+        <v>5375</v>
       </c>
       <c r="C13" s="12"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="43" t="s">
-        <v>5373</v>
+        <v>5376</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>5374</v>
+        <v>5377</v>
       </c>
       <c r="C14" s="12"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="43" t="s">
-        <v>5375</v>
+        <v>5378</v>
       </c>
       <c r="B15" s="43" t="s">
         <v>3243</v>
@@ -54177,73 +54244,73 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>5376</v>
+        <v>5379</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>5377</v>
+        <v>5380</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>5378</v>
+        <v>5381</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>5379</v>
+        <v>5382</v>
       </c>
       <c r="C17" s="12"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>5380</v>
+        <v>5383</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>5381</v>
+        <v>5384</v>
       </c>
       <c r="C18" s="12"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>5382</v>
+        <v>5385</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>5383</v>
+        <v>5386</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>5384</v>
+        <v>5387</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>5385</v>
+        <v>5388</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>5386</v>
+        <v>5389</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>5387</v>
+        <v>5390</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>5388</v>
+        <v>5391</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>5389</v>
+        <v>5392</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>5390</v>
+        <v>5393</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>5391</v>
+        <v>5394</v>
       </c>
       <c r="C23" s="12"/>
     </row>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -1975,18 +1975,18 @@
     <t>to drown</t>
   </si>
   <si>
+    <t>drukkr</t>
+  </si>
+  <si>
+    <t>drink, beverage, liquid; potion, concoction, draught</t>
+  </si>
+  <si>
     <t>drumbr</t>
   </si>
   <si>
     <t>a log of dry or rotten wood</t>
   </si>
   <si>
-    <t>drykkr</t>
-  </si>
-  <si>
-    <t>drink, beverage, liquid; potion, concoction, draught</t>
-  </si>
-  <si>
     <t>drymba</t>
   </si>
   <si>
@@ -4780,18 +4780,18 @@
     <t>horse, steed</t>
   </si>
   <si>
+    <t>hruggr</t>
+  </si>
+  <si>
+    <t>spine</t>
+  </si>
+  <si>
     <t>hrútr</t>
   </si>
   <si>
     <t>ram (male sheep)</t>
   </si>
   <si>
-    <t>hryggr</t>
-  </si>
-  <si>
-    <t>spine</t>
-  </si>
-  <si>
     <t>hrynja</t>
   </si>
   <si>
@@ -5761,6 +5761,12 @@
     <t>coldness</t>
   </si>
   <si>
+    <t>kurr</t>
+  </si>
+  <si>
+    <t>peace, stillness, tranquility, serenity; silence</t>
+  </si>
+  <si>
     <t>kvæði</t>
   </si>
   <si>
@@ -5863,12 +5869,6 @@
     <t>to sing loudly (intransitive)</t>
   </si>
   <si>
-    <t>kyrr</t>
-  </si>
-  <si>
-    <t>peace, stillness, tranquility, serenity; silence</t>
-  </si>
-  <si>
     <t>kyrtill</t>
   </si>
   <si>
@@ -10834,13 +10834,13 @@
     <t>verb group e</t>
   </si>
   <si>
-    <t>tryggð</t>
+    <t>truggð</t>
   </si>
   <si>
     <t>trustworthiness</t>
   </si>
   <si>
-    <t>tryggr</t>
+    <t>truggr</t>
   </si>
   <si>
     <t>trusty, trustworthy</t>
@@ -29528,7 +29528,7 @@
         <v>1902</v>
       </c>
       <c r="B936" s="4" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C936" s="3" t="s">
         <v>1903</v>
@@ -29540,40 +29540,38 @@
         <v>1904</v>
       </c>
       <c r="B937" s="4" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C937" s="3" t="s">
         <v>1905</v>
       </c>
-      <c r="D937" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="D937" s="3"/>
     </row>
     <row r="938" ht="18.75" customHeight="1">
       <c r="A938" s="3" t="s">
         <v>1906</v>
       </c>
       <c r="B938" s="4" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C938" s="3" t="s">
         <v>1907</v>
       </c>
-      <c r="D938" s="5"/>
+      <c r="D938" s="3" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="939" ht="18.75" customHeight="1">
       <c r="A939" s="3" t="s">
         <v>1908</v>
       </c>
       <c r="B939" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C939" s="3" t="s">
         <v>1909</v>
       </c>
-      <c r="D939" s="3" t="s">
-        <v>185</v>
-      </c>
+      <c r="D939" s="5"/>
     </row>
     <row r="940" ht="18.75" customHeight="1">
       <c r="A940" s="3" t="s">
@@ -29585,7 +29583,9 @@
       <c r="C940" s="3" t="s">
         <v>1911</v>
       </c>
-      <c r="D940" s="3"/>
+      <c r="D940" s="3" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="941" ht="18.75" customHeight="1">
       <c r="A941" s="3" t="s">
@@ -29616,26 +29616,24 @@
         <v>1916</v>
       </c>
       <c r="B943" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C943" s="3" t="s">
         <v>1917</v>
       </c>
-      <c r="D943" s="5"/>
+      <c r="D943" s="3"/>
     </row>
     <row r="944" ht="18.75" customHeight="1">
       <c r="A944" s="3" t="s">
         <v>1918</v>
       </c>
       <c r="B944" s="4" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C944" s="3" t="s">
         <v>1919</v>
       </c>
-      <c r="D944" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="D944" s="5"/>
     </row>
     <row r="945" ht="18.75" customHeight="1">
       <c r="A945" s="3" t="s">
@@ -29647,14 +29645,16 @@
       <c r="C945" s="3" t="s">
         <v>1921</v>
       </c>
-      <c r="D945" s="3"/>
+      <c r="D945" s="3" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="946" ht="18.75" customHeight="1">
       <c r="A946" s="3" t="s">
         <v>1922</v>
       </c>
       <c r="B946" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C946" s="3" t="s">
         <v>1923</v>
@@ -29666,7 +29666,7 @@
         <v>1924</v>
       </c>
       <c r="B947" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C947" s="3" t="s">
         <v>1925</v>
@@ -29678,7 +29678,7 @@
         <v>1926</v>
       </c>
       <c r="B948" s="4" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C948" s="3" t="s">
         <v>1927</v>
@@ -29702,7 +29702,7 @@
         <v>1930</v>
       </c>
       <c r="B950" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C950" s="3" t="s">
         <v>1931</v>
@@ -29714,14 +29714,12 @@
         <v>1932</v>
       </c>
       <c r="B951" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C951" s="3" t="s">
         <v>1933</v>
       </c>
-      <c r="D951" s="3" t="s">
-        <v>310</v>
-      </c>
+      <c r="D951" s="3"/>
     </row>
     <row r="952" ht="18.75" customHeight="1">
       <c r="A952" s="3" t="s">
@@ -29734,7 +29732,7 @@
         <v>1935</v>
       </c>
       <c r="D952" s="3" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
     </row>
     <row r="953" ht="18.75" customHeight="1">
@@ -29742,12 +29740,14 @@
         <v>1936</v>
       </c>
       <c r="B953" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C953" s="3" t="s">
         <v>1937</v>
       </c>
-      <c r="D953" s="3"/>
+      <c r="D953" s="3" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="954" ht="18.75" customHeight="1">
       <c r="A954" s="3" t="s">
@@ -43210,7 +43210,7 @@
         <v>4117</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="O3" s="10" t="s">
         <v>4125</v>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -1963,16 +1963,16 @@
     <t>to drip, to leak (with dative)</t>
   </si>
   <si>
+    <t>drokkna</t>
+  </si>
+  <si>
+    <t>to drown</t>
+  </si>
+  <si>
     <t>dróttning</t>
   </si>
   <si>
     <t>queen</t>
-  </si>
-  <si>
-    <t>drukkna</t>
-  </si>
-  <si>
-    <t>to drown</t>
   </si>
   <si>
     <t>drukkr</t>
@@ -21804,7 +21804,7 @@
         <v>636</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C308" s="3" t="s">
         <v>637</v>
@@ -21816,7 +21816,7 @@
         <v>638</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C309" s="3" t="s">
         <v>639</v>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -3463,7 +3463,7 @@
     <t>gera óførvandi</t>
   </si>
   <si>
-    <t>to incapacitate, to disable, to cripple (with accusative)</t>
+    <t>to incapacitate, to disable, to cripple (with accusative + óførvandi)</t>
   </si>
   <si>
     <t>gera vándamál</t>
@@ -3751,7 +3751,7 @@
     <t>grafa undir jørð</t>
   </si>
   <si>
-    <t>to bury</t>
+    <t>to bury (with accusative + undir jørð)</t>
   </si>
   <si>
     <t>gramr</t>
@@ -4093,7 +4093,7 @@
     <t>hamla á lærbaki</t>
   </si>
   <si>
-    <t>to hamstring, to disable someone by cutting the back of their thigh (with accusative)</t>
+    <t>to hamstring, to disable someone by cutting the back of their thigh (with accusative + á lærbaki)</t>
   </si>
   <si>
     <t>hand-</t>
@@ -4114,7 +4114,7 @@
     <t>handa í hendi</t>
   </si>
   <si>
-    <t>to hold someone's hand (with dative)</t>
+    <t>to hold someone's hand (with dative + í hendi)</t>
   </si>
   <si>
     <t>handari</t>
@@ -6577,7 +6577,7 @@
     <t>lóga af</t>
   </si>
   <si>
-    <t>to destroy, to remove (with accusative)</t>
+    <t>to destroy, to remove (with accusative + af)</t>
   </si>
   <si>
     <t>loka</t>
@@ -9004,7 +9004,7 @@
     <t>setja burt</t>
   </si>
   <si>
-    <t>to put away (with accusative)</t>
+    <t>to put away (with accusative + burt)</t>
   </si>
   <si>
     <t>sex</t>
@@ -10087,7 +10087,7 @@
     <t>spýta út</t>
   </si>
   <si>
-    <t>to spit out (with dative "what")</t>
+    <t>to spit out (with dative "what" + út)</t>
   </si>
   <si>
     <t>staðr</t>
@@ -10747,7 +10747,7 @@
     <t>taka fram</t>
   </si>
   <si>
-    <t>to take out, to present forwards (with accusative)</t>
+    <t>to take out, to present forwards (with accusative + fram)</t>
   </si>
   <si>
     <t>taka með</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -17532,7 +17532,7 @@
     <t>one cannot normally jump over a tree</t>
   </si>
   <si>
-    <t>maðr getr eigi hleypt yfir tre</t>
+    <t>maðr getr venjuliga eigi hleypt yfir tre</t>
   </si>
   <si>
     <t>a</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9711" uniqueCount="6080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9712" uniqueCount="6080">
   <si>
     <t>Entry</t>
   </si>
@@ -40289,7 +40289,9 @@
       <c r="C1744" s="3" t="s">
         <v>3524</v>
       </c>
-      <c r="D1744" s="3"/>
+      <c r="D1744" s="3" t="s">
+        <v>899</v>
+      </c>
     </row>
     <row r="1745" ht="18.75" customHeight="1">
       <c r="A1745" s="3" t="s">

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -1531,7 +1531,7 @@
     <t>borð</t>
   </si>
   <si>
-    <t>table</t>
+    <t>table; board, plank</t>
   </si>
   <si>
     <t>borg</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -18207,7 +18207,7 @@
     <t>he could have been busy</t>
   </si>
   <si>
-    <t>afallinn villans atlar eigi at vera svindlað af menni</t>
+    <t>afallinn villans atlar eigi at vera svindlað af manni</t>
   </si>
   <si>
     <t>the forces of nature are not to be trifled with</t>
@@ -40901,7 +40901,7 @@
         <v>3575</v>
       </c>
       <c r="D1769" s="3" t="s">
-        <v>201</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1770" ht="18.75" customHeight="1">
@@ -40915,7 +40915,7 @@
         <v>3577</v>
       </c>
       <c r="D1770" s="3" t="s">
-        <v>201</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1771" ht="18.75" customHeight="1">

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -13,7 +13,7 @@
     <sheet state="visible" name="Evolution Rules" sheetId="8" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Lexicon!$A$1:$D$2200</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Lexicon!$A$1:$D$2201</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9875" uniqueCount="6183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9913" uniqueCount="6210">
   <si>
     <t>Entry</t>
   </si>
@@ -11830,7 +11830,7 @@
     <t>unna</t>
   </si>
   <si>
-    <t>to adore (ann/annr/annr = sg present, unna/unnir/unni = sg past, ynndr = past participle)</t>
+    <t>to adore, to love (ann/annr/annr = sg present, unna/unnir/unni = sg past, ynndr = past participle)</t>
   </si>
   <si>
     <t>upp</t>
@@ -16752,6 +16752,9 @@
     <t>example: eiga</t>
   </si>
   <si>
+    <t>example: standa</t>
+  </si>
+  <si>
     <t>at syngja</t>
   </si>
   <si>
@@ -16767,6 +16770,9 @@
     <t>at eiga</t>
   </si>
   <si>
+    <t>at standa</t>
+  </si>
+  <si>
     <t>songið (songinn)</t>
   </si>
   <si>
@@ -16782,6 +16788,9 @@
     <t>eigið (eiginn)</t>
   </si>
   <si>
+    <t>standið (standinn)</t>
+  </si>
+  <si>
     <t>syngjandi</t>
   </si>
   <si>
@@ -16797,6 +16806,9 @@
     <t>eigandi</t>
   </si>
   <si>
+    <t>standandi</t>
+  </si>
+  <si>
     <t>syng</t>
   </si>
   <si>
@@ -16821,6 +16833,12 @@
     <t>átta</t>
   </si>
   <si>
+    <t>stend</t>
+  </si>
+  <si>
+    <t>stóð</t>
+  </si>
+  <si>
     <t>syngr</t>
   </si>
   <si>
@@ -16851,6 +16869,12 @@
     <t>áttir</t>
   </si>
   <si>
+    <t>stendr</t>
+  </si>
+  <si>
+    <t>stóðst</t>
+  </si>
+  <si>
     <t>ýtti</t>
   </si>
   <si>
@@ -16887,6 +16911,12 @@
     <t>áttum</t>
   </si>
   <si>
+    <t>stendum</t>
+  </si>
+  <si>
+    <t>stóðum</t>
+  </si>
+  <si>
     <t>syngjuð</t>
   </si>
   <si>
@@ -16917,6 +16947,12 @@
     <t>áttuð</t>
   </si>
   <si>
+    <t>stenduð</t>
+  </si>
+  <si>
+    <t>stóðuð</t>
+  </si>
+  <si>
     <t>syngju</t>
   </si>
   <si>
@@ -16945,6 +16981,51 @@
   </si>
   <si>
     <t>áttu</t>
+  </si>
+  <si>
+    <t>stendu</t>
+  </si>
+  <si>
+    <t>stóðu</t>
+  </si>
+  <si>
+    <t>example: høggva</t>
+  </si>
+  <si>
+    <t>at høggva</t>
+  </si>
+  <si>
+    <t>høggvið (høggvinn)</t>
+  </si>
+  <si>
+    <t>høggvandi</t>
+  </si>
+  <si>
+    <t>hjó</t>
+  </si>
+  <si>
+    <t>høggr</t>
+  </si>
+  <si>
+    <t>hjóst</t>
+  </si>
+  <si>
+    <t>høggvum</t>
+  </si>
+  <si>
+    <t>hjóum</t>
+  </si>
+  <si>
+    <t>høggvuð</t>
+  </si>
+  <si>
+    <t>hjóuð</t>
+  </si>
+  <si>
+    <t>høggvu</t>
+  </si>
+  <si>
+    <t>hjóu</t>
   </si>
   <si>
     <t>strong verb b (e-a)</t>
@@ -18945,8 +19026,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D2200" displayName="Lexicon" name="Lexicon" id="1">
-  <autoFilter ref="$A$1:$D$2200"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D2201" displayName="Lexicon" name="Lexicon" id="1">
+  <autoFilter ref="$A$1:$D$2201"/>
   <tableColumns count="4">
     <tableColumn name="Entry" id="1"/>
     <tableColumn name="Part of Speech" id="2"/>
@@ -31900,7 +31981,9 @@
       <c r="C1037" s="3" t="s">
         <v>2108</v>
       </c>
-      <c r="D1037" s="3"/>
+      <c r="D1037" s="3" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="1038" ht="18.75" customHeight="1">
       <c r="A1038" s="3" t="s">
@@ -40695,7 +40778,7 @@
         <v>3542</v>
       </c>
       <c r="B1753" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C1753" s="3" t="s">
         <v>3543</v>
@@ -46126,7 +46209,9 @@
       <c r="C2192" s="3" t="s">
         <v>4420</v>
       </c>
-      <c r="D2192" s="5"/>
+      <c r="D2192" s="3" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="2193" ht="18.75" customHeight="1">
       <c r="A2193" s="3" t="s">
@@ -46228,9 +46313,15 @@
       </c>
       <c r="D2200" s="3"/>
     </row>
+    <row r="2201" ht="18.75" customHeight="1">
+      <c r="A2201" s="3"/>
+      <c r="B2201" s="4"/>
+      <c r="C2201" s="3"/>
+      <c r="D2201" s="3"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B2200">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B2201">
       <formula1>"adjective,adverb,pronoun,masculine noun,feminine noun,neuter noun,number,preposition,phrase,verb,auxiliary,suffix,prefix,conjunction,question word,determiner"</formula1>
     </dataValidation>
   </dataValidations>
@@ -55403,8 +55494,10 @@
         <v>5564</v>
       </c>
       <c r="J109" s="19"/>
-      <c r="K109" s="10"/>
-      <c r="L109" s="10"/>
+      <c r="K109" s="18" t="s">
+        <v>5565</v>
+      </c>
+      <c r="L109" s="19"/>
       <c r="M109" s="10"/>
       <c r="N109" s="10"/>
       <c r="O109" s="10"/>
@@ -55415,27 +55508,29 @@
     </row>
     <row r="110" ht="18.75" customHeight="1">
       <c r="A110" s="23" t="s">
-        <v>5565</v>
+        <v>5566</v>
       </c>
       <c r="B110" s="22"/>
       <c r="C110" s="23" t="s">
-        <v>5566</v>
+        <v>5567</v>
       </c>
       <c r="D110" s="22"/>
       <c r="E110" s="23" t="s">
-        <v>5567</v>
+        <v>5568</v>
       </c>
       <c r="F110" s="22"/>
       <c r="G110" s="23" t="s">
-        <v>5568</v>
+        <v>5569</v>
       </c>
       <c r="H110" s="22"/>
       <c r="I110" s="23" t="s">
-        <v>5569</v>
+        <v>5570</v>
       </c>
       <c r="J110" s="22"/>
-      <c r="K110" s="10"/>
-      <c r="L110" s="10"/>
+      <c r="K110" s="23" t="s">
+        <v>5571</v>
+      </c>
+      <c r="L110" s="22"/>
       <c r="M110" s="10"/>
       <c r="N110" s="10"/>
       <c r="O110" s="10"/>
@@ -55446,27 +55541,29 @@
     </row>
     <row r="111" ht="18.75" customHeight="1">
       <c r="A111" s="23" t="s">
-        <v>5570</v>
+        <v>5572</v>
       </c>
       <c r="B111" s="22"/>
       <c r="C111" s="23" t="s">
-        <v>5571</v>
+        <v>5573</v>
       </c>
       <c r="D111" s="22"/>
       <c r="E111" s="23" t="s">
-        <v>5572</v>
+        <v>5574</v>
       </c>
       <c r="F111" s="22"/>
       <c r="G111" s="23" t="s">
-        <v>5573</v>
+        <v>5575</v>
       </c>
       <c r="H111" s="22"/>
       <c r="I111" s="23" t="s">
-        <v>5574</v>
+        <v>5576</v>
       </c>
       <c r="J111" s="22"/>
-      <c r="K111" s="10"/>
-      <c r="L111" s="10"/>
+      <c r="K111" s="23" t="s">
+        <v>5577</v>
+      </c>
+      <c r="L111" s="22"/>
       <c r="M111" s="10"/>
       <c r="N111" s="10"/>
       <c r="O111" s="10"/>
@@ -55477,27 +55574,29 @@
     </row>
     <row r="112" ht="18.75" customHeight="1">
       <c r="A112" s="23" t="s">
-        <v>5575</v>
+        <v>5578</v>
       </c>
       <c r="B112" s="22"/>
       <c r="C112" s="23" t="s">
-        <v>5576</v>
+        <v>5579</v>
       </c>
       <c r="D112" s="22"/>
       <c r="E112" s="23" t="s">
-        <v>5577</v>
+        <v>5580</v>
       </c>
       <c r="F112" s="22"/>
       <c r="G112" s="23" t="s">
-        <v>5578</v>
+        <v>5581</v>
       </c>
       <c r="H112" s="22"/>
       <c r="I112" s="23" t="s">
-        <v>5579</v>
+        <v>5582</v>
       </c>
       <c r="J112" s="22"/>
-      <c r="K112" s="10"/>
-      <c r="L112" s="10"/>
+      <c r="K112" s="23" t="s">
+        <v>5583</v>
+      </c>
+      <c r="L112" s="22"/>
       <c r="M112" s="10"/>
       <c r="N112" s="10"/>
       <c r="O112" s="10"/>
@@ -55537,8 +55636,12 @@
       <c r="J113" s="24" t="s">
         <v>5098</v>
       </c>
-      <c r="K113" s="10"/>
-      <c r="L113" s="10"/>
+      <c r="K113" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="L113" s="24" t="s">
+        <v>5098</v>
+      </c>
       <c r="M113" s="10"/>
       <c r="N113" s="10"/>
       <c r="O113" s="10"/>
@@ -55549,37 +55652,41 @@
     </row>
     <row r="114" ht="18.75" customHeight="1">
       <c r="A114" s="23" t="s">
-        <v>5580</v>
+        <v>5584</v>
       </c>
       <c r="B114" s="25" t="s">
         <v>4790</v>
       </c>
       <c r="C114" s="23" t="s">
-        <v>5581</v>
+        <v>5585</v>
       </c>
       <c r="D114" s="25" t="s">
-        <v>5582</v>
+        <v>5586</v>
       </c>
       <c r="E114" s="23" t="s">
-        <v>5583</v>
+        <v>5587</v>
       </c>
       <c r="F114" s="25" t="s">
-        <v>5584</v>
+        <v>5588</v>
       </c>
       <c r="G114" s="23" t="s">
-        <v>5585</v>
+        <v>5589</v>
       </c>
       <c r="H114" s="25" t="s">
-        <v>5586</v>
+        <v>5590</v>
       </c>
       <c r="I114" s="23" t="s">
         <v>792</v>
       </c>
       <c r="J114" s="25" t="s">
-        <v>5587</v>
-      </c>
-      <c r="K114" s="10"/>
-      <c r="L114" s="10"/>
+        <v>5591</v>
+      </c>
+      <c r="K114" s="23" t="s">
+        <v>5592</v>
+      </c>
+      <c r="L114" s="25" t="s">
+        <v>5593</v>
+      </c>
       <c r="M114" s="10"/>
       <c r="N114" s="10"/>
       <c r="O114" s="10"/>
@@ -55590,37 +55697,41 @@
     </row>
     <row r="115" ht="18.75" customHeight="1">
       <c r="A115" s="23" t="s">
-        <v>5588</v>
+        <v>5594</v>
       </c>
       <c r="B115" s="25" t="s">
-        <v>5589</v>
+        <v>5595</v>
       </c>
       <c r="C115" s="23" t="s">
-        <v>5590</v>
+        <v>5596</v>
       </c>
       <c r="D115" s="25" t="s">
-        <v>5591</v>
+        <v>5597</v>
       </c>
       <c r="E115" s="23" t="s">
-        <v>5592</v>
+        <v>5598</v>
       </c>
       <c r="F115" s="25" t="s">
-        <v>5593</v>
+        <v>5599</v>
       </c>
       <c r="G115" s="23" t="s">
-        <v>5594</v>
+        <v>5600</v>
       </c>
       <c r="H115" s="25" t="s">
-        <v>5595</v>
+        <v>5601</v>
       </c>
       <c r="I115" s="23" t="s">
-        <v>5596</v>
+        <v>5602</v>
       </c>
       <c r="J115" s="25" t="s">
-        <v>5597</v>
-      </c>
-      <c r="K115" s="10"/>
-      <c r="L115" s="10"/>
+        <v>5603</v>
+      </c>
+      <c r="K115" s="23" t="s">
+        <v>5604</v>
+      </c>
+      <c r="L115" s="25" t="s">
+        <v>5605</v>
+      </c>
       <c r="M115" s="10"/>
       <c r="N115" s="10"/>
       <c r="O115" s="10"/>
@@ -55631,37 +55742,41 @@
     </row>
     <row r="116" ht="18.75" customHeight="1">
       <c r="A116" s="23" t="s">
-        <v>5588</v>
+        <v>5594</v>
       </c>
       <c r="B116" s="25" t="s">
         <v>4790</v>
       </c>
       <c r="C116" s="23" t="s">
-        <v>5590</v>
+        <v>5596</v>
       </c>
       <c r="D116" s="25" t="s">
-        <v>5582</v>
+        <v>5586</v>
       </c>
       <c r="E116" s="23" t="s">
-        <v>5592</v>
+        <v>5598</v>
       </c>
       <c r="F116" s="25" t="s">
-        <v>5584</v>
+        <v>5588</v>
       </c>
       <c r="G116" s="23" t="s">
-        <v>5594</v>
+        <v>5600</v>
       </c>
       <c r="H116" s="25" t="s">
-        <v>5598</v>
+        <v>5606</v>
       </c>
       <c r="I116" s="23" t="s">
-        <v>5596</v>
+        <v>5602</v>
       </c>
       <c r="J116" s="25" t="s">
-        <v>5599</v>
-      </c>
-      <c r="K116" s="10"/>
-      <c r="L116" s="10"/>
+        <v>5607</v>
+      </c>
+      <c r="K116" s="23" t="s">
+        <v>5604</v>
+      </c>
+      <c r="L116" s="25" t="s">
+        <v>5593</v>
+      </c>
       <c r="M116" s="10"/>
       <c r="N116" s="10"/>
       <c r="O116" s="10"/>
@@ -55672,37 +55787,41 @@
     </row>
     <row r="117" ht="18.75" customHeight="1">
       <c r="A117" s="23" t="s">
-        <v>5600</v>
+        <v>5608</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>5601</v>
+        <v>5609</v>
       </c>
       <c r="C117" s="23" t="s">
-        <v>5602</v>
+        <v>5610</v>
       </c>
       <c r="D117" s="25" t="s">
-        <v>5603</v>
+        <v>5611</v>
       </c>
       <c r="E117" s="23" t="s">
-        <v>5604</v>
+        <v>5612</v>
       </c>
       <c r="F117" s="25" t="s">
-        <v>5605</v>
+        <v>5613</v>
       </c>
       <c r="G117" s="23" t="s">
-        <v>5606</v>
+        <v>5614</v>
       </c>
       <c r="H117" s="25" t="s">
-        <v>5607</v>
+        <v>5615</v>
       </c>
       <c r="I117" s="23" t="s">
-        <v>5608</v>
+        <v>5616</v>
       </c>
       <c r="J117" s="25" t="s">
-        <v>5609</v>
-      </c>
-      <c r="K117" s="10"/>
-      <c r="L117" s="10"/>
+        <v>5617</v>
+      </c>
+      <c r="K117" s="23" t="s">
+        <v>5618</v>
+      </c>
+      <c r="L117" s="25" t="s">
+        <v>5619</v>
+      </c>
       <c r="M117" s="10"/>
       <c r="N117" s="10"/>
       <c r="O117" s="10"/>
@@ -55713,37 +55832,41 @@
     </row>
     <row r="118" ht="18.75" customHeight="1">
       <c r="A118" s="23" t="s">
-        <v>5610</v>
+        <v>5620</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>5611</v>
+        <v>5621</v>
       </c>
       <c r="C118" s="23" t="s">
-        <v>5612</v>
+        <v>5622</v>
       </c>
       <c r="D118" s="25" t="s">
-        <v>5613</v>
+        <v>5623</v>
       </c>
       <c r="E118" s="23" t="s">
-        <v>5614</v>
+        <v>5624</v>
       </c>
       <c r="F118" s="25" t="s">
-        <v>5615</v>
+        <v>5625</v>
       </c>
       <c r="G118" s="23" t="s">
-        <v>5616</v>
+        <v>5626</v>
       </c>
       <c r="H118" s="25" t="s">
-        <v>5617</v>
+        <v>5627</v>
       </c>
       <c r="I118" s="23" t="s">
-        <v>5618</v>
+        <v>5628</v>
       </c>
       <c r="J118" s="25" t="s">
-        <v>5619</v>
-      </c>
-      <c r="K118" s="10"/>
-      <c r="L118" s="10"/>
+        <v>5629</v>
+      </c>
+      <c r="K118" s="23" t="s">
+        <v>5630</v>
+      </c>
+      <c r="L118" s="25" t="s">
+        <v>5631</v>
+      </c>
       <c r="M118" s="10"/>
       <c r="N118" s="10"/>
       <c r="O118" s="10"/>
@@ -55754,37 +55877,41 @@
     </row>
     <row r="119" ht="18.75" customHeight="1">
       <c r="A119" s="36" t="s">
-        <v>5620</v>
+        <v>5632</v>
       </c>
       <c r="B119" s="28" t="s">
-        <v>5621</v>
+        <v>5633</v>
       </c>
       <c r="C119" s="36" t="s">
-        <v>5622</v>
+        <v>5634</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>5623</v>
+        <v>5635</v>
       </c>
       <c r="E119" s="36" t="s">
-        <v>5624</v>
+        <v>5636</v>
       </c>
       <c r="F119" s="28" t="s">
-        <v>5625</v>
+        <v>5637</v>
       </c>
       <c r="G119" s="36" t="s">
-        <v>5626</v>
+        <v>5638</v>
       </c>
       <c r="H119" s="28" t="s">
-        <v>5627</v>
+        <v>5639</v>
       </c>
       <c r="I119" s="36" t="s">
-        <v>5628</v>
+        <v>5640</v>
       </c>
       <c r="J119" s="28" t="s">
-        <v>5629</v>
-      </c>
-      <c r="K119" s="10"/>
-      <c r="L119" s="10"/>
+        <v>5641</v>
+      </c>
+      <c r="K119" s="36" t="s">
+        <v>5642</v>
+      </c>
+      <c r="L119" s="28" t="s">
+        <v>5643</v>
+      </c>
       <c r="M119" s="10"/>
       <c r="N119" s="10"/>
       <c r="O119" s="10"/>
@@ -55816,513 +55943,282 @@
     </row>
     <row r="121" ht="18.75" customHeight="1">
       <c r="A121" s="18" t="s">
-        <v>5630</v>
+        <v>5644</v>
       </c>
       <c r="B121" s="19"/>
-      <c r="C121" s="18" t="s">
-        <v>5631</v>
-      </c>
-      <c r="D121" s="19"/>
-      <c r="E121" s="18" t="s">
-        <v>5632</v>
-      </c>
-      <c r="F121" s="19"/>
-      <c r="G121" s="18" t="s">
-        <v>5633</v>
-      </c>
-      <c r="H121" s="19"/>
-      <c r="I121" s="18" t="s">
-        <v>5634</v>
-      </c>
-      <c r="J121" s="19"/>
-      <c r="K121" s="18" t="s">
-        <v>5635</v>
-      </c>
-      <c r="L121" s="19"/>
+      <c r="C121" s="10"/>
+      <c r="D121" s="10"/>
+      <c r="E121" s="10"/>
+      <c r="F121" s="10"/>
+      <c r="G121" s="10"/>
+      <c r="H121" s="10"/>
+      <c r="I121" s="10"/>
+      <c r="J121" s="10"/>
+      <c r="K121" s="10"/>
+      <c r="L121" s="10"/>
       <c r="M121" s="10"/>
       <c r="N121" s="10"/>
       <c r="O121" s="10"/>
-      <c r="P121" s="8" t="s">
-        <v>5636</v>
-      </c>
+      <c r="P121" s="10"/>
+      <c r="Q121" s="10"/>
+      <c r="R121" s="10"/>
+      <c r="S121" s="10"/>
     </row>
     <row r="122" ht="18.75" customHeight="1">
-      <c r="A122" s="21" t="s">
-        <v>5078</v>
+      <c r="A122" s="23" t="s">
+        <v>5645</v>
       </c>
       <c r="B122" s="22"/>
-      <c r="C122" s="23" t="s">
-        <v>5637</v>
-      </c>
-      <c r="D122" s="22"/>
-      <c r="E122" s="23" t="s">
-        <v>5638</v>
-      </c>
-      <c r="F122" s="22"/>
-      <c r="G122" s="23" t="s">
-        <v>5639</v>
-      </c>
-      <c r="H122" s="22"/>
-      <c r="I122" s="23" t="s">
-        <v>5640</v>
-      </c>
-      <c r="J122" s="22"/>
-      <c r="K122" s="23" t="s">
-        <v>5641</v>
-      </c>
-      <c r="L122" s="22"/>
+      <c r="C122" s="10"/>
+      <c r="D122" s="10"/>
+      <c r="E122" s="10"/>
+      <c r="F122" s="10"/>
+      <c r="G122" s="10"/>
+      <c r="H122" s="10"/>
+      <c r="I122" s="10"/>
+      <c r="J122" s="10"/>
+      <c r="K122" s="10"/>
+      <c r="L122" s="10"/>
       <c r="M122" s="10"/>
       <c r="N122" s="10"/>
       <c r="O122" s="10"/>
-      <c r="P122" s="8" t="s">
-        <v>5078</v>
-      </c>
-      <c r="Q122" s="10" t="s">
-        <v>5642</v>
-      </c>
+      <c r="P122" s="10"/>
+      <c r="Q122" s="10"/>
+      <c r="R122" s="10"/>
+      <c r="S122" s="10"/>
     </row>
     <row r="123" ht="18.75" customHeight="1">
-      <c r="A123" s="21" t="s">
-        <v>5084</v>
+      <c r="A123" s="23" t="s">
+        <v>5646</v>
       </c>
       <c r="B123" s="22"/>
-      <c r="C123" s="23" t="s">
-        <v>5643</v>
-      </c>
-      <c r="D123" s="22"/>
-      <c r="E123" s="23" t="s">
-        <v>5644</v>
-      </c>
-      <c r="F123" s="22"/>
-      <c r="G123" s="23" t="s">
-        <v>5645</v>
-      </c>
-      <c r="H123" s="22"/>
-      <c r="I123" s="23" t="s">
-        <v>5646</v>
-      </c>
-      <c r="J123" s="22"/>
-      <c r="K123" s="23" t="s">
-        <v>5647</v>
-      </c>
-      <c r="L123" s="22"/>
+      <c r="C123" s="10"/>
+      <c r="D123" s="10"/>
+      <c r="E123" s="10"/>
+      <c r="F123" s="10"/>
+      <c r="G123" s="10"/>
+      <c r="H123" s="10"/>
+      <c r="I123" s="10"/>
+      <c r="J123" s="10"/>
+      <c r="K123" s="10"/>
+      <c r="L123" s="10"/>
       <c r="M123" s="10"/>
       <c r="N123" s="10"/>
       <c r="O123" s="10"/>
-      <c r="P123" s="8" t="s">
-        <v>5084</v>
-      </c>
-      <c r="Q123" s="10" t="s">
-        <v>5648</v>
-      </c>
+      <c r="P123" s="10"/>
+      <c r="Q123" s="10"/>
+      <c r="R123" s="10"/>
+      <c r="S123" s="10"/>
     </row>
     <row r="124" ht="18.75" customHeight="1">
-      <c r="A124" s="21" t="s">
-        <v>5090</v>
+      <c r="A124" s="23" t="s">
+        <v>5647</v>
       </c>
       <c r="B124" s="22"/>
-      <c r="C124" s="23" t="s">
-        <v>5649</v>
-      </c>
-      <c r="D124" s="22"/>
-      <c r="E124" s="23" t="s">
-        <v>5650</v>
-      </c>
-      <c r="F124" s="22"/>
-      <c r="G124" s="23" t="s">
-        <v>5651</v>
-      </c>
-      <c r="H124" s="22"/>
-      <c r="I124" s="23" t="s">
-        <v>5652</v>
-      </c>
-      <c r="J124" s="22"/>
-      <c r="K124" s="23" t="s">
-        <v>5653</v>
-      </c>
-      <c r="L124" s="22"/>
+      <c r="C124" s="10"/>
+      <c r="D124" s="10"/>
+      <c r="E124" s="10"/>
+      <c r="F124" s="10"/>
+      <c r="G124" s="10"/>
+      <c r="H124" s="10"/>
+      <c r="I124" s="10"/>
+      <c r="J124" s="10"/>
+      <c r="K124" s="10"/>
+      <c r="L124" s="10"/>
       <c r="M124" s="10"/>
       <c r="N124" s="10"/>
       <c r="O124" s="10"/>
-      <c r="P124" s="8" t="s">
-        <v>5090</v>
-      </c>
-      <c r="Q124" s="10" t="s">
-        <v>5654</v>
-      </c>
+      <c r="P124" s="10"/>
+      <c r="Q124" s="10"/>
+      <c r="R124" s="10"/>
+      <c r="S124" s="10"/>
     </row>
     <row r="125" ht="18.75" customHeight="1">
       <c r="A125" s="21" t="s">
-        <v>5096</v>
-      </c>
-      <c r="B125" s="22"/>
-      <c r="C125" s="21" t="s">
         <v>5097</v>
       </c>
-      <c r="D125" s="24" t="s">
+      <c r="B125" s="24" t="s">
         <v>5098</v>
       </c>
-      <c r="E125" s="21" t="s">
-        <v>5097</v>
-      </c>
-      <c r="F125" s="24" t="s">
-        <v>5098</v>
-      </c>
-      <c r="G125" s="21" t="s">
-        <v>5097</v>
-      </c>
-      <c r="H125" s="24" t="s">
-        <v>5098</v>
-      </c>
-      <c r="I125" s="21" t="s">
-        <v>5097</v>
-      </c>
-      <c r="J125" s="24" t="s">
-        <v>5098</v>
-      </c>
-      <c r="K125" s="21" t="s">
-        <v>5097</v>
-      </c>
-      <c r="L125" s="24" t="s">
-        <v>5098</v>
-      </c>
+      <c r="C125" s="10"/>
+      <c r="D125" s="10"/>
+      <c r="E125" s="10"/>
+      <c r="F125" s="10"/>
+      <c r="G125" s="10"/>
+      <c r="H125" s="10"/>
+      <c r="I125" s="10"/>
+      <c r="J125" s="10"/>
+      <c r="K125" s="10"/>
+      <c r="L125" s="10"/>
       <c r="M125" s="10"/>
       <c r="N125" s="10"/>
       <c r="O125" s="10"/>
-      <c r="P125" s="8"/>
-      <c r="Q125" s="8"/>
-      <c r="R125" s="8" t="s">
-        <v>5097</v>
-      </c>
-      <c r="S125" s="8" t="s">
-        <v>5098</v>
-      </c>
+      <c r="P125" s="10"/>
+      <c r="Q125" s="10"/>
+      <c r="R125" s="10"/>
+      <c r="S125" s="10"/>
     </row>
     <row r="126" ht="18.75" customHeight="1">
-      <c r="A126" s="21" t="s">
-        <v>4862</v>
-      </c>
-      <c r="B126" s="24" t="s">
-        <v>5099</v>
-      </c>
-      <c r="C126" s="23" t="s">
-        <v>983</v>
-      </c>
-      <c r="D126" s="25" t="s">
-        <v>5655</v>
-      </c>
-      <c r="E126" s="23" t="s">
-        <v>5656</v>
-      </c>
-      <c r="F126" s="25" t="s">
-        <v>5657</v>
-      </c>
-      <c r="G126" s="23" t="s">
-        <v>5658</v>
-      </c>
-      <c r="H126" s="25" t="s">
-        <v>5659</v>
-      </c>
-      <c r="I126" s="23" t="s">
-        <v>5660</v>
-      </c>
-      <c r="J126" s="25" t="s">
-        <v>5661</v>
-      </c>
-      <c r="K126" s="23" t="s">
-        <v>5662</v>
-      </c>
-      <c r="L126" s="25" t="s">
-        <v>4066</v>
-      </c>
+      <c r="A126" s="23" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B126" s="25" t="s">
+        <v>5648</v>
+      </c>
+      <c r="C126" s="10"/>
+      <c r="D126" s="10"/>
+      <c r="E126" s="10"/>
+      <c r="F126" s="10"/>
+      <c r="G126" s="10"/>
+      <c r="H126" s="10"/>
+      <c r="I126" s="10"/>
+      <c r="J126" s="10"/>
+      <c r="K126" s="10"/>
+      <c r="L126" s="10"/>
       <c r="M126" s="10"/>
       <c r="N126" s="10"/>
       <c r="O126" s="10"/>
-      <c r="P126" s="8" t="s">
-        <v>4862</v>
-      </c>
-      <c r="Q126" s="8" t="s">
-        <v>5099</v>
-      </c>
-      <c r="R126" s="10" t="s">
-        <v>5663</v>
-      </c>
-      <c r="S126" s="10" t="s">
-        <v>5664</v>
-      </c>
+      <c r="P126" s="10"/>
+      <c r="Q126" s="10"/>
+      <c r="R126" s="10"/>
+      <c r="S126" s="10"/>
     </row>
     <row r="127" ht="18.75" customHeight="1">
-      <c r="A127" s="26"/>
-      <c r="B127" s="24" t="s">
-        <v>4401</v>
-      </c>
-      <c r="C127" s="23" t="s">
-        <v>5665</v>
-      </c>
-      <c r="D127" s="25" t="s">
-        <v>5666</v>
-      </c>
-      <c r="E127" s="23" t="s">
-        <v>5667</v>
-      </c>
-      <c r="F127" s="25" t="s">
-        <v>5668</v>
-      </c>
-      <c r="G127" s="23" t="s">
-        <v>4132</v>
-      </c>
-      <c r="H127" s="25" t="s">
-        <v>5669</v>
-      </c>
-      <c r="I127" s="23" t="s">
-        <v>5670</v>
-      </c>
-      <c r="J127" s="25" t="s">
-        <v>5671</v>
-      </c>
-      <c r="K127" s="23" t="s">
-        <v>5672</v>
-      </c>
-      <c r="L127" s="25" t="s">
-        <v>5673</v>
-      </c>
+      <c r="A127" s="23" t="s">
+        <v>5649</v>
+      </c>
+      <c r="B127" s="25" t="s">
+        <v>5650</v>
+      </c>
+      <c r="C127" s="10"/>
+      <c r="D127" s="10"/>
+      <c r="E127" s="10"/>
+      <c r="F127" s="10"/>
+      <c r="G127" s="10"/>
+      <c r="H127" s="10"/>
+      <c r="I127" s="10"/>
+      <c r="J127" s="10"/>
+      <c r="K127" s="10"/>
+      <c r="L127" s="10"/>
       <c r="M127" s="10"/>
       <c r="N127" s="10"/>
       <c r="O127" s="10"/>
-      <c r="Q127" s="8" t="s">
-        <v>4401</v>
-      </c>
-      <c r="R127" s="10" t="s">
-        <v>5674</v>
-      </c>
-      <c r="S127" s="10" t="s">
-        <v>5675</v>
-      </c>
+      <c r="P127" s="10"/>
+      <c r="Q127" s="10"/>
+      <c r="R127" s="10"/>
+      <c r="S127" s="10"/>
     </row>
     <row r="128" ht="18.75" customHeight="1">
-      <c r="A128" s="26"/>
-      <c r="B128" s="24" t="s">
-        <v>5114</v>
-      </c>
-      <c r="C128" s="23" t="s">
-        <v>5665</v>
-      </c>
-      <c r="D128" s="25" t="s">
-        <v>5655</v>
-      </c>
-      <c r="E128" s="23" t="s">
-        <v>5667</v>
-      </c>
-      <c r="F128" s="25" t="s">
-        <v>5657</v>
-      </c>
-      <c r="G128" s="23" t="s">
-        <v>4132</v>
-      </c>
-      <c r="H128" s="25" t="s">
-        <v>5659</v>
-      </c>
-      <c r="I128" s="23" t="s">
-        <v>5670</v>
-      </c>
-      <c r="J128" s="25" t="s">
-        <v>5661</v>
-      </c>
-      <c r="K128" s="23" t="s">
-        <v>5672</v>
-      </c>
-      <c r="L128" s="25" t="s">
-        <v>4066</v>
-      </c>
+      <c r="A128" s="23" t="s">
+        <v>5649</v>
+      </c>
+      <c r="B128" s="25" t="s">
+        <v>5648</v>
+      </c>
+      <c r="C128" s="10"/>
+      <c r="D128" s="10"/>
+      <c r="E128" s="10"/>
+      <c r="F128" s="10"/>
+      <c r="G128" s="10"/>
+      <c r="H128" s="10"/>
+      <c r="I128" s="10"/>
+      <c r="J128" s="10"/>
+      <c r="K128" s="10"/>
+      <c r="L128" s="10"/>
       <c r="M128" s="10"/>
       <c r="N128" s="10"/>
       <c r="O128" s="10"/>
-      <c r="Q128" s="8" t="s">
-        <v>5114</v>
-      </c>
-      <c r="R128" s="10" t="s">
-        <v>5674</v>
-      </c>
-      <c r="S128" s="10" t="s">
-        <v>5664</v>
-      </c>
+      <c r="P128" s="10"/>
+      <c r="Q128" s="10"/>
+      <c r="R128" s="10"/>
+      <c r="S128" s="10"/>
     </row>
     <row r="129" ht="18.75" customHeight="1">
-      <c r="A129" s="8" t="s">
-        <v>4886</v>
-      </c>
-      <c r="B129" s="24" t="s">
-        <v>4230</v>
-      </c>
-      <c r="C129" s="23" t="s">
-        <v>5676</v>
-      </c>
-      <c r="D129" s="25" t="s">
-        <v>5677</v>
-      </c>
-      <c r="E129" s="23" t="s">
-        <v>5678</v>
-      </c>
-      <c r="F129" s="25" t="s">
-        <v>5679</v>
-      </c>
-      <c r="G129" s="23" t="s">
-        <v>5680</v>
-      </c>
-      <c r="H129" s="25" t="s">
-        <v>5681</v>
-      </c>
-      <c r="I129" s="23" t="s">
-        <v>5682</v>
-      </c>
-      <c r="J129" s="25" t="s">
-        <v>5683</v>
-      </c>
-      <c r="K129" s="23" t="s">
-        <v>5684</v>
-      </c>
-      <c r="L129" s="25" t="s">
-        <v>5685</v>
-      </c>
+      <c r="A129" s="23" t="s">
+        <v>5651</v>
+      </c>
+      <c r="B129" s="25" t="s">
+        <v>5652</v>
+      </c>
+      <c r="C129" s="10"/>
+      <c r="D129" s="10"/>
+      <c r="E129" s="10"/>
+      <c r="F129" s="10"/>
+      <c r="G129" s="10"/>
+      <c r="H129" s="10"/>
+      <c r="I129" s="10"/>
+      <c r="J129" s="10"/>
+      <c r="K129" s="10"/>
+      <c r="L129" s="10"/>
       <c r="M129" s="10"/>
       <c r="N129" s="10"/>
       <c r="O129" s="10"/>
-      <c r="P129" s="8" t="s">
-        <v>4886</v>
-      </c>
-      <c r="Q129" s="8" t="s">
-        <v>4230</v>
-      </c>
-      <c r="R129" s="10" t="s">
-        <v>5686</v>
-      </c>
-      <c r="S129" s="10" t="s">
-        <v>5687</v>
-      </c>
+      <c r="P129" s="10"/>
+      <c r="Q129" s="10"/>
+      <c r="R129" s="10"/>
+      <c r="S129" s="10"/>
     </row>
     <row r="130" ht="18.75" customHeight="1">
-      <c r="B130" s="24" t="s">
-        <v>4351</v>
-      </c>
-      <c r="C130" s="23" t="s">
-        <v>5688</v>
-      </c>
-      <c r="D130" s="25" t="s">
-        <v>5689</v>
-      </c>
-      <c r="E130" s="23" t="s">
-        <v>5690</v>
-      </c>
-      <c r="F130" s="25" t="s">
-        <v>5691</v>
-      </c>
-      <c r="G130" s="23" t="s">
-        <v>5692</v>
-      </c>
-      <c r="H130" s="25" t="s">
-        <v>5693</v>
-      </c>
-      <c r="I130" s="23" t="s">
-        <v>5694</v>
-      </c>
-      <c r="J130" s="25" t="s">
-        <v>5695</v>
-      </c>
-      <c r="K130" s="23" t="s">
-        <v>5696</v>
-      </c>
-      <c r="L130" s="25" t="s">
-        <v>5697</v>
-      </c>
+      <c r="A130" s="23" t="s">
+        <v>5653</v>
+      </c>
+      <c r="B130" s="25" t="s">
+        <v>5654</v>
+      </c>
+      <c r="C130" s="10"/>
+      <c r="D130" s="10"/>
+      <c r="E130" s="10"/>
+      <c r="F130" s="10"/>
+      <c r="G130" s="10"/>
+      <c r="H130" s="10"/>
+      <c r="I130" s="10"/>
+      <c r="J130" s="10"/>
+      <c r="K130" s="10"/>
+      <c r="L130" s="10"/>
       <c r="M130" s="10"/>
       <c r="N130" s="10"/>
       <c r="O130" s="10"/>
-      <c r="Q130" s="8" t="s">
-        <v>4351</v>
-      </c>
-      <c r="R130" s="10" t="s">
-        <v>5698</v>
-      </c>
-      <c r="S130" s="10" t="s">
-        <v>5699</v>
-      </c>
+      <c r="P130" s="10"/>
+      <c r="Q130" s="10"/>
+      <c r="R130" s="10"/>
+      <c r="S130" s="10"/>
     </row>
     <row r="131" ht="18.75" customHeight="1">
-      <c r="B131" s="24" t="s">
-        <v>5139</v>
-      </c>
-      <c r="C131" s="23" t="s">
-        <v>5700</v>
-      </c>
-      <c r="D131" s="25" t="s">
-        <v>5701</v>
-      </c>
-      <c r="E131" s="23" t="s">
-        <v>5702</v>
-      </c>
-      <c r="F131" s="25" t="s">
-        <v>5703</v>
-      </c>
-      <c r="G131" s="23" t="s">
-        <v>5704</v>
-      </c>
-      <c r="H131" s="25" t="s">
-        <v>5705</v>
-      </c>
-      <c r="I131" s="23" t="s">
-        <v>5706</v>
-      </c>
-      <c r="J131" s="25" t="s">
-        <v>5707</v>
-      </c>
-      <c r="K131" s="36" t="s">
-        <v>5708</v>
-      </c>
-      <c r="L131" s="28" t="s">
-        <v>5709</v>
-      </c>
+      <c r="A131" s="36" t="s">
+        <v>5655</v>
+      </c>
+      <c r="B131" s="28" t="s">
+        <v>5656</v>
+      </c>
+      <c r="C131" s="10"/>
+      <c r="D131" s="10"/>
+      <c r="E131" s="10"/>
+      <c r="F131" s="10"/>
+      <c r="G131" s="10"/>
+      <c r="H131" s="10"/>
+      <c r="I131" s="10"/>
+      <c r="J131" s="10"/>
+      <c r="K131" s="10"/>
+      <c r="L131" s="10"/>
       <c r="M131" s="10"/>
       <c r="N131" s="10"/>
       <c r="O131" s="10"/>
-      <c r="Q131" s="8" t="s">
-        <v>5139</v>
-      </c>
-      <c r="R131" s="10" t="s">
-        <v>5710</v>
-      </c>
-      <c r="S131" s="10" t="s">
-        <v>5711</v>
-      </c>
+      <c r="P131" s="10"/>
+      <c r="Q131" s="10"/>
+      <c r="R131" s="10"/>
+      <c r="S131" s="10"/>
     </row>
     <row r="132" ht="18.75" customHeight="1">
-      <c r="A132" s="21" t="s">
-        <v>5150</v>
-      </c>
-      <c r="B132" s="22"/>
-      <c r="C132" s="8" t="s">
-        <v>5097</v>
-      </c>
-      <c r="D132" s="24" t="s">
-        <v>5098</v>
-      </c>
-      <c r="E132" s="8" t="s">
-        <v>5097</v>
-      </c>
-      <c r="F132" s="24" t="s">
-        <v>5098</v>
-      </c>
-      <c r="G132" s="8" t="s">
-        <v>5097</v>
-      </c>
-      <c r="H132" s="24" t="s">
-        <v>5098</v>
-      </c>
-      <c r="I132" s="8" t="s">
-        <v>5097</v>
-      </c>
-      <c r="J132" s="24" t="s">
-        <v>5098</v>
-      </c>
+      <c r="A132" s="10"/>
+      <c r="B132" s="10"/>
+      <c r="C132" s="10"/>
+      <c r="D132" s="10"/>
+      <c r="E132" s="10"/>
+      <c r="F132" s="10"/>
+      <c r="G132" s="10"/>
+      <c r="H132" s="10"/>
+      <c r="I132" s="10"/>
+      <c r="J132" s="10"/>
       <c r="K132" s="10"/>
       <c r="L132" s="10"/>
       <c r="M132" s="10"/>
@@ -56334,347 +56230,514 @@
       <c r="S132" s="10"/>
     </row>
     <row r="133" ht="18.75" customHeight="1">
-      <c r="A133" s="21" t="s">
-        <v>4862</v>
-      </c>
-      <c r="B133" s="8" t="s">
-        <v>5099</v>
-      </c>
-      <c r="C133" s="23" t="s">
-        <v>5712</v>
-      </c>
-      <c r="D133" s="25" t="s">
-        <v>5713</v>
-      </c>
-      <c r="E133" s="23" t="s">
-        <v>5714</v>
-      </c>
-      <c r="F133" s="25" t="s">
-        <v>5715</v>
-      </c>
-      <c r="G133" s="23" t="s">
-        <v>5716</v>
-      </c>
-      <c r="H133" s="25" t="s">
-        <v>5717</v>
-      </c>
-      <c r="I133" s="23" t="s">
-        <v>5718</v>
-      </c>
-      <c r="J133" s="25" t="s">
-        <v>5719</v>
-      </c>
-      <c r="K133" s="23"/>
-      <c r="L133" s="10"/>
+      <c r="A133" s="18" t="s">
+        <v>5657</v>
+      </c>
+      <c r="B133" s="19"/>
+      <c r="C133" s="18" t="s">
+        <v>5658</v>
+      </c>
+      <c r="D133" s="19"/>
+      <c r="E133" s="18" t="s">
+        <v>5659</v>
+      </c>
+      <c r="F133" s="19"/>
+      <c r="G133" s="18" t="s">
+        <v>5660</v>
+      </c>
+      <c r="H133" s="19"/>
+      <c r="I133" s="18" t="s">
+        <v>5661</v>
+      </c>
+      <c r="J133" s="19"/>
+      <c r="K133" s="18" t="s">
+        <v>5662</v>
+      </c>
+      <c r="L133" s="19"/>
       <c r="M133" s="10"/>
       <c r="N133" s="10"/>
       <c r="O133" s="10"/>
-      <c r="P133" s="10"/>
-      <c r="Q133" s="10"/>
-      <c r="R133" s="10"/>
-      <c r="S133" s="10"/>
+      <c r="P133" s="8" t="s">
+        <v>5663</v>
+      </c>
     </row>
     <row r="134" ht="18.75" customHeight="1">
-      <c r="A134" s="26"/>
-      <c r="B134" s="8" t="s">
-        <v>4401</v>
-      </c>
-      <c r="C134" s="26"/>
+      <c r="A134" s="21" t="s">
+        <v>5078</v>
+      </c>
+      <c r="B134" s="22"/>
+      <c r="C134" s="23" t="s">
+        <v>5664</v>
+      </c>
       <c r="D134" s="22"/>
-      <c r="E134" s="26"/>
+      <c r="E134" s="23" t="s">
+        <v>5665</v>
+      </c>
       <c r="F134" s="22"/>
-      <c r="G134" s="26"/>
+      <c r="G134" s="23" t="s">
+        <v>5666</v>
+      </c>
       <c r="H134" s="22"/>
-      <c r="I134" s="26"/>
+      <c r="I134" s="23" t="s">
+        <v>5667</v>
+      </c>
       <c r="J134" s="22"/>
-      <c r="K134" s="23"/>
-      <c r="L134" s="10"/>
+      <c r="K134" s="23" t="s">
+        <v>5668</v>
+      </c>
+      <c r="L134" s="22"/>
       <c r="M134" s="10"/>
       <c r="N134" s="10"/>
       <c r="O134" s="10"/>
-      <c r="P134" s="10"/>
-      <c r="Q134" s="10"/>
-      <c r="R134" s="10"/>
-      <c r="S134" s="10"/>
+      <c r="P134" s="8" t="s">
+        <v>5078</v>
+      </c>
+      <c r="Q134" s="10" t="s">
+        <v>5669</v>
+      </c>
     </row>
     <row r="135" ht="18.75" customHeight="1">
-      <c r="A135" s="26"/>
-      <c r="B135" s="24" t="s">
-        <v>5114</v>
-      </c>
-      <c r="C135" s="26"/>
+      <c r="A135" s="21" t="s">
+        <v>5084</v>
+      </c>
+      <c r="B135" s="22"/>
+      <c r="C135" s="23" t="s">
+        <v>5670</v>
+      </c>
       <c r="D135" s="22"/>
-      <c r="E135" s="26"/>
+      <c r="E135" s="23" t="s">
+        <v>5671</v>
+      </c>
       <c r="F135" s="22"/>
-      <c r="G135" s="26"/>
+      <c r="G135" s="23" t="s">
+        <v>5672</v>
+      </c>
       <c r="H135" s="22"/>
-      <c r="I135" s="26"/>
+      <c r="I135" s="23" t="s">
+        <v>5673</v>
+      </c>
       <c r="J135" s="22"/>
-      <c r="K135" s="23"/>
-      <c r="L135" s="10"/>
+      <c r="K135" s="23" t="s">
+        <v>5674</v>
+      </c>
+      <c r="L135" s="22"/>
       <c r="M135" s="10"/>
       <c r="N135" s="10"/>
       <c r="O135" s="10"/>
-      <c r="P135" s="10"/>
-      <c r="Q135" s="10"/>
-      <c r="R135" s="10"/>
-      <c r="S135" s="10"/>
+      <c r="P135" s="8" t="s">
+        <v>5084</v>
+      </c>
+      <c r="Q135" s="10" t="s">
+        <v>5675</v>
+      </c>
     </row>
     <row r="136" ht="18.75" customHeight="1">
       <c r="A136" s="21" t="s">
-        <v>4886</v>
-      </c>
-      <c r="B136" s="24" t="s">
-        <v>4230</v>
-      </c>
-      <c r="C136" s="10" t="s">
-        <v>5720</v>
-      </c>
-      <c r="D136" s="25" t="s">
-        <v>5721</v>
-      </c>
-      <c r="E136" s="10" t="s">
-        <v>5722</v>
-      </c>
-      <c r="F136" s="25" t="s">
-        <v>5723</v>
-      </c>
-      <c r="G136" s="10" t="s">
-        <v>5724</v>
-      </c>
-      <c r="H136" s="25" t="s">
-        <v>5725</v>
-      </c>
-      <c r="I136" s="10" t="s">
-        <v>5726</v>
-      </c>
-      <c r="J136" s="25" t="s">
-        <v>5727</v>
-      </c>
-      <c r="K136" s="23"/>
-      <c r="L136" s="10"/>
+        <v>5090</v>
+      </c>
+      <c r="B136" s="22"/>
+      <c r="C136" s="23" t="s">
+        <v>5676</v>
+      </c>
+      <c r="D136" s="22"/>
+      <c r="E136" s="23" t="s">
+        <v>5677</v>
+      </c>
+      <c r="F136" s="22"/>
+      <c r="G136" s="23" t="s">
+        <v>5678</v>
+      </c>
+      <c r="H136" s="22"/>
+      <c r="I136" s="23" t="s">
+        <v>5679</v>
+      </c>
+      <c r="J136" s="22"/>
+      <c r="K136" s="23" t="s">
+        <v>5680</v>
+      </c>
+      <c r="L136" s="22"/>
       <c r="M136" s="10"/>
       <c r="N136" s="10"/>
       <c r="O136" s="10"/>
-      <c r="P136" s="10"/>
-      <c r="Q136" s="10"/>
-      <c r="R136" s="10"/>
-      <c r="S136" s="10"/>
+      <c r="P136" s="8" t="s">
+        <v>5090</v>
+      </c>
+      <c r="Q136" s="10" t="s">
+        <v>5681</v>
+      </c>
     </row>
     <row r="137" ht="18.75" customHeight="1">
-      <c r="A137" s="26"/>
-      <c r="B137" s="24" t="s">
-        <v>4351</v>
-      </c>
-      <c r="C137" s="10" t="s">
-        <v>5728</v>
-      </c>
-      <c r="D137" s="25" t="s">
-        <v>5729</v>
-      </c>
-      <c r="E137" s="10" t="s">
-        <v>5730</v>
-      </c>
-      <c r="F137" s="25" t="s">
-        <v>5731</v>
-      </c>
-      <c r="G137" s="10" t="s">
-        <v>5732</v>
-      </c>
-      <c r="H137" s="25" t="s">
-        <v>5733</v>
-      </c>
-      <c r="I137" s="10" t="s">
-        <v>5734</v>
-      </c>
-      <c r="J137" s="25" t="s">
-        <v>5735</v>
-      </c>
-      <c r="K137" s="23"/>
-      <c r="L137" s="10"/>
+      <c r="A137" s="21" t="s">
+        <v>5096</v>
+      </c>
+      <c r="B137" s="22"/>
+      <c r="C137" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="D137" s="24" t="s">
+        <v>5098</v>
+      </c>
+      <c r="E137" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="F137" s="24" t="s">
+        <v>5098</v>
+      </c>
+      <c r="G137" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="H137" s="24" t="s">
+        <v>5098</v>
+      </c>
+      <c r="I137" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="J137" s="24" t="s">
+        <v>5098</v>
+      </c>
+      <c r="K137" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="L137" s="24" t="s">
+        <v>5098</v>
+      </c>
       <c r="M137" s="10"/>
       <c r="N137" s="10"/>
       <c r="O137" s="10"/>
-      <c r="P137" s="10"/>
-      <c r="Q137" s="10"/>
-      <c r="R137" s="10"/>
-      <c r="S137" s="10"/>
+      <c r="P137" s="8"/>
+      <c r="Q137" s="8"/>
+      <c r="R137" s="8" t="s">
+        <v>5097</v>
+      </c>
+      <c r="S137" s="8" t="s">
+        <v>5098</v>
+      </c>
     </row>
     <row r="138" ht="18.75" customHeight="1">
-      <c r="A138" s="31"/>
-      <c r="B138" s="32" t="s">
-        <v>5139</v>
-      </c>
-      <c r="C138" s="33"/>
-      <c r="D138" s="34"/>
-      <c r="E138" s="33"/>
-      <c r="F138" s="34"/>
-      <c r="G138" s="33"/>
-      <c r="H138" s="34"/>
-      <c r="I138" s="33"/>
-      <c r="J138" s="34"/>
-      <c r="K138" s="23"/>
-      <c r="L138" s="10"/>
+      <c r="A138" s="21" t="s">
+        <v>4862</v>
+      </c>
+      <c r="B138" s="24" t="s">
+        <v>5099</v>
+      </c>
+      <c r="C138" s="23" t="s">
+        <v>983</v>
+      </c>
+      <c r="D138" s="25" t="s">
+        <v>5682</v>
+      </c>
+      <c r="E138" s="23" t="s">
+        <v>5683</v>
+      </c>
+      <c r="F138" s="25" t="s">
+        <v>5684</v>
+      </c>
+      <c r="G138" s="23" t="s">
+        <v>5685</v>
+      </c>
+      <c r="H138" s="25" t="s">
+        <v>5686</v>
+      </c>
+      <c r="I138" s="23" t="s">
+        <v>5687</v>
+      </c>
+      <c r="J138" s="25" t="s">
+        <v>5688</v>
+      </c>
+      <c r="K138" s="23" t="s">
+        <v>5689</v>
+      </c>
+      <c r="L138" s="25" t="s">
+        <v>4066</v>
+      </c>
       <c r="M138" s="10"/>
       <c r="N138" s="10"/>
       <c r="O138" s="10"/>
-      <c r="P138" s="10"/>
-      <c r="Q138" s="10"/>
-      <c r="R138" s="10"/>
-      <c r="S138" s="10"/>
+      <c r="P138" s="8" t="s">
+        <v>4862</v>
+      </c>
+      <c r="Q138" s="8" t="s">
+        <v>5099</v>
+      </c>
+      <c r="R138" s="10" t="s">
+        <v>5690</v>
+      </c>
+      <c r="S138" s="10" t="s">
+        <v>5691</v>
+      </c>
     </row>
     <row r="139" ht="18.75" customHeight="1">
-      <c r="A139" s="10"/>
-      <c r="B139" s="10"/>
-      <c r="C139" s="10"/>
-      <c r="D139" s="10"/>
-      <c r="E139" s="10"/>
-      <c r="F139" s="10"/>
-      <c r="G139" s="10"/>
-      <c r="H139" s="10"/>
-      <c r="I139" s="10"/>
-      <c r="J139" s="10"/>
-      <c r="K139" s="10"/>
-      <c r="L139" s="10"/>
+      <c r="A139" s="26"/>
+      <c r="B139" s="24" t="s">
+        <v>4401</v>
+      </c>
+      <c r="C139" s="23" t="s">
+        <v>5692</v>
+      </c>
+      <c r="D139" s="25" t="s">
+        <v>5693</v>
+      </c>
+      <c r="E139" s="23" t="s">
+        <v>5694</v>
+      </c>
+      <c r="F139" s="25" t="s">
+        <v>5695</v>
+      </c>
+      <c r="G139" s="23" t="s">
+        <v>4132</v>
+      </c>
+      <c r="H139" s="25" t="s">
+        <v>5696</v>
+      </c>
+      <c r="I139" s="23" t="s">
+        <v>5697</v>
+      </c>
+      <c r="J139" s="25" t="s">
+        <v>5698</v>
+      </c>
+      <c r="K139" s="23" t="s">
+        <v>5699</v>
+      </c>
+      <c r="L139" s="25" t="s">
+        <v>5700</v>
+      </c>
       <c r="M139" s="10"/>
       <c r="N139" s="10"/>
       <c r="O139" s="10"/>
-      <c r="P139" s="10"/>
-      <c r="Q139" s="10"/>
-      <c r="R139" s="10"/>
-      <c r="S139" s="10"/>
+      <c r="Q139" s="8" t="s">
+        <v>4401</v>
+      </c>
+      <c r="R139" s="10" t="s">
+        <v>5701</v>
+      </c>
+      <c r="S139" s="10" t="s">
+        <v>5702</v>
+      </c>
     </row>
     <row r="140" ht="18.75" customHeight="1">
-      <c r="A140" s="10"/>
-      <c r="B140" s="10"/>
-      <c r="C140" s="18" t="s">
-        <v>5736</v>
-      </c>
-      <c r="D140" s="19"/>
-      <c r="E140" s="18" t="s">
-        <v>5737</v>
-      </c>
-      <c r="F140" s="19"/>
-      <c r="G140" s="18" t="s">
-        <v>5738</v>
-      </c>
-      <c r="H140" s="19"/>
-      <c r="I140" s="10"/>
-      <c r="J140" s="10"/>
-      <c r="K140" s="10"/>
-      <c r="L140" s="10"/>
+      <c r="A140" s="26"/>
+      <c r="B140" s="24" t="s">
+        <v>5114</v>
+      </c>
+      <c r="C140" s="23" t="s">
+        <v>5692</v>
+      </c>
+      <c r="D140" s="25" t="s">
+        <v>5682</v>
+      </c>
+      <c r="E140" s="23" t="s">
+        <v>5694</v>
+      </c>
+      <c r="F140" s="25" t="s">
+        <v>5684</v>
+      </c>
+      <c r="G140" s="23" t="s">
+        <v>4132</v>
+      </c>
+      <c r="H140" s="25" t="s">
+        <v>5686</v>
+      </c>
+      <c r="I140" s="23" t="s">
+        <v>5697</v>
+      </c>
+      <c r="J140" s="25" t="s">
+        <v>5688</v>
+      </c>
+      <c r="K140" s="23" t="s">
+        <v>5699</v>
+      </c>
+      <c r="L140" s="25" t="s">
+        <v>4066</v>
+      </c>
       <c r="M140" s="10"/>
       <c r="N140" s="10"/>
       <c r="O140" s="10"/>
-      <c r="P140" s="10"/>
-      <c r="Q140" s="10"/>
-      <c r="R140" s="10"/>
-      <c r="S140" s="10"/>
+      <c r="Q140" s="8" t="s">
+        <v>5114</v>
+      </c>
+      <c r="R140" s="10" t="s">
+        <v>5701</v>
+      </c>
+      <c r="S140" s="10" t="s">
+        <v>5691</v>
+      </c>
     </row>
     <row r="141" ht="18.75" customHeight="1">
-      <c r="A141" s="10"/>
-      <c r="B141" s="10"/>
+      <c r="A141" s="8" t="s">
+        <v>4886</v>
+      </c>
+      <c r="B141" s="24" t="s">
+        <v>4230</v>
+      </c>
       <c r="C141" s="23" t="s">
-        <v>5739</v>
-      </c>
-      <c r="D141" s="22"/>
+        <v>5703</v>
+      </c>
+      <c r="D141" s="25" t="s">
+        <v>5704</v>
+      </c>
       <c r="E141" s="23" t="s">
-        <v>5740</v>
-      </c>
-      <c r="F141" s="22"/>
+        <v>5705</v>
+      </c>
+      <c r="F141" s="25" t="s">
+        <v>5706</v>
+      </c>
       <c r="G141" s="23" t="s">
-        <v>5741</v>
-      </c>
-      <c r="H141" s="22"/>
-      <c r="I141" s="10"/>
-      <c r="J141" s="10"/>
-      <c r="K141" s="10"/>
-      <c r="L141" s="10"/>
+        <v>5707</v>
+      </c>
+      <c r="H141" s="25" t="s">
+        <v>5708</v>
+      </c>
+      <c r="I141" s="23" t="s">
+        <v>5709</v>
+      </c>
+      <c r="J141" s="25" t="s">
+        <v>5710</v>
+      </c>
+      <c r="K141" s="23" t="s">
+        <v>5711</v>
+      </c>
+      <c r="L141" s="25" t="s">
+        <v>5712</v>
+      </c>
       <c r="M141" s="10"/>
       <c r="N141" s="10"/>
       <c r="O141" s="10"/>
-      <c r="P141" s="10"/>
-      <c r="Q141" s="10"/>
-      <c r="R141" s="10"/>
-      <c r="S141" s="10"/>
+      <c r="P141" s="8" t="s">
+        <v>4886</v>
+      </c>
+      <c r="Q141" s="8" t="s">
+        <v>4230</v>
+      </c>
+      <c r="R141" s="10" t="s">
+        <v>5713</v>
+      </c>
+      <c r="S141" s="10" t="s">
+        <v>5714</v>
+      </c>
     </row>
     <row r="142" ht="18.75" customHeight="1">
-      <c r="A142" s="10"/>
-      <c r="B142" s="10"/>
+      <c r="B142" s="24" t="s">
+        <v>4351</v>
+      </c>
       <c r="C142" s="23" t="s">
-        <v>5742</v>
-      </c>
-      <c r="D142" s="22"/>
+        <v>5715</v>
+      </c>
+      <c r="D142" s="25" t="s">
+        <v>5716</v>
+      </c>
       <c r="E142" s="23" t="s">
-        <v>5743</v>
-      </c>
-      <c r="F142" s="22"/>
+        <v>5717</v>
+      </c>
+      <c r="F142" s="25" t="s">
+        <v>5718</v>
+      </c>
       <c r="G142" s="23" t="s">
-        <v>5744</v>
-      </c>
-      <c r="H142" s="22"/>
-      <c r="I142" s="10"/>
-      <c r="J142" s="10"/>
-      <c r="K142" s="10"/>
-      <c r="L142" s="10"/>
+        <v>5719</v>
+      </c>
+      <c r="H142" s="25" t="s">
+        <v>5720</v>
+      </c>
+      <c r="I142" s="23" t="s">
+        <v>5721</v>
+      </c>
+      <c r="J142" s="25" t="s">
+        <v>5722</v>
+      </c>
+      <c r="K142" s="23" t="s">
+        <v>5723</v>
+      </c>
+      <c r="L142" s="25" t="s">
+        <v>5724</v>
+      </c>
       <c r="M142" s="10"/>
       <c r="N142" s="10"/>
       <c r="O142" s="10"/>
-      <c r="P142" s="10"/>
-      <c r="Q142" s="10"/>
-      <c r="R142" s="10"/>
-      <c r="S142" s="10"/>
+      <c r="Q142" s="8" t="s">
+        <v>4351</v>
+      </c>
+      <c r="R142" s="10" t="s">
+        <v>5725</v>
+      </c>
+      <c r="S142" s="10" t="s">
+        <v>5726</v>
+      </c>
     </row>
     <row r="143" ht="18.75" customHeight="1">
-      <c r="A143" s="10"/>
-      <c r="B143" s="10"/>
+      <c r="B143" s="24" t="s">
+        <v>5139</v>
+      </c>
       <c r="C143" s="23" t="s">
-        <v>5745</v>
-      </c>
-      <c r="D143" s="22"/>
+        <v>5727</v>
+      </c>
+      <c r="D143" s="25" t="s">
+        <v>5728</v>
+      </c>
       <c r="E143" s="23" t="s">
-        <v>5746</v>
-      </c>
-      <c r="F143" s="22"/>
+        <v>5729</v>
+      </c>
+      <c r="F143" s="25" t="s">
+        <v>5730</v>
+      </c>
       <c r="G143" s="23" t="s">
-        <v>3304</v>
-      </c>
-      <c r="H143" s="22"/>
-      <c r="I143" s="10"/>
-      <c r="J143" s="10"/>
-      <c r="K143" s="10"/>
-      <c r="L143" s="10"/>
+        <v>5731</v>
+      </c>
+      <c r="H143" s="25" t="s">
+        <v>5732</v>
+      </c>
+      <c r="I143" s="23" t="s">
+        <v>5733</v>
+      </c>
+      <c r="J143" s="25" t="s">
+        <v>5734</v>
+      </c>
+      <c r="K143" s="36" t="s">
+        <v>5735</v>
+      </c>
+      <c r="L143" s="28" t="s">
+        <v>5736</v>
+      </c>
       <c r="M143" s="10"/>
       <c r="N143" s="10"/>
       <c r="O143" s="10"/>
-      <c r="P143" s="10"/>
-      <c r="Q143" s="10"/>
-      <c r="R143" s="10"/>
-      <c r="S143" s="10"/>
+      <c r="Q143" s="8" t="s">
+        <v>5139</v>
+      </c>
+      <c r="R143" s="10" t="s">
+        <v>5737</v>
+      </c>
+      <c r="S143" s="10" t="s">
+        <v>5738</v>
+      </c>
     </row>
     <row r="144" ht="18.75" customHeight="1">
-      <c r="A144" s="10"/>
-      <c r="B144" s="10"/>
-      <c r="C144" s="21" t="s">
+      <c r="A144" s="21" t="s">
+        <v>5150</v>
+      </c>
+      <c r="B144" s="22"/>
+      <c r="C144" s="8" t="s">
         <v>5097</v>
       </c>
       <c r="D144" s="24" t="s">
         <v>5098</v>
       </c>
-      <c r="E144" s="21" t="s">
+      <c r="E144" s="8" t="s">
         <v>5097</v>
       </c>
       <c r="F144" s="24" t="s">
         <v>5098</v>
       </c>
-      <c r="G144" s="21" t="s">
+      <c r="G144" s="8" t="s">
         <v>5097</v>
       </c>
       <c r="H144" s="24" t="s">
         <v>5098</v>
       </c>
-      <c r="I144" s="10"/>
-      <c r="J144" s="10"/>
+      <c r="I144" s="8" t="s">
+        <v>5097</v>
+      </c>
+      <c r="J144" s="24" t="s">
+        <v>5098</v>
+      </c>
       <c r="K144" s="10"/>
       <c r="L144" s="10"/>
       <c r="M144" s="10"/>
@@ -56686,29 +56749,37 @@
       <c r="S144" s="10"/>
     </row>
     <row r="145" ht="18.75" customHeight="1">
-      <c r="A145" s="10"/>
-      <c r="B145" s="10"/>
+      <c r="A145" s="21" t="s">
+        <v>4862</v>
+      </c>
+      <c r="B145" s="8" t="s">
+        <v>5099</v>
+      </c>
       <c r="C145" s="23" t="s">
-        <v>5747</v>
+        <v>5739</v>
       </c>
       <c r="D145" s="25" t="s">
-        <v>5748</v>
+        <v>5740</v>
       </c>
       <c r="E145" s="23" t="s">
-        <v>5749</v>
+        <v>5741</v>
       </c>
       <c r="F145" s="25" t="s">
-        <v>5750</v>
+        <v>5742</v>
       </c>
       <c r="G145" s="23" t="s">
-        <v>5751</v>
+        <v>5743</v>
       </c>
       <c r="H145" s="25" t="s">
-        <v>5752</v>
-      </c>
-      <c r="I145" s="10"/>
-      <c r="J145" s="10"/>
-      <c r="K145" s="10"/>
+        <v>5744</v>
+      </c>
+      <c r="I145" s="23" t="s">
+        <v>5745</v>
+      </c>
+      <c r="J145" s="25" t="s">
+        <v>5746</v>
+      </c>
+      <c r="K145" s="23"/>
       <c r="L145" s="10"/>
       <c r="M145" s="10"/>
       <c r="N145" s="10"/>
@@ -56719,29 +56790,19 @@
       <c r="S145" s="10"/>
     </row>
     <row r="146" ht="18.75" customHeight="1">
-      <c r="A146" s="10"/>
-      <c r="B146" s="10"/>
-      <c r="C146" s="23" t="s">
-        <v>5753</v>
-      </c>
-      <c r="D146" s="25" t="s">
-        <v>5754</v>
-      </c>
-      <c r="E146" s="23" t="s">
-        <v>5755</v>
-      </c>
-      <c r="F146" s="25" t="s">
-        <v>5756</v>
-      </c>
-      <c r="G146" s="23" t="s">
-        <v>5757</v>
-      </c>
-      <c r="H146" s="25" t="s">
-        <v>5758</v>
-      </c>
-      <c r="I146" s="10"/>
-      <c r="J146" s="10"/>
-      <c r="K146" s="10"/>
+      <c r="A146" s="26"/>
+      <c r="B146" s="8" t="s">
+        <v>4401</v>
+      </c>
+      <c r="C146" s="26"/>
+      <c r="D146" s="22"/>
+      <c r="E146" s="26"/>
+      <c r="F146" s="22"/>
+      <c r="G146" s="26"/>
+      <c r="H146" s="22"/>
+      <c r="I146" s="26"/>
+      <c r="J146" s="22"/>
+      <c r="K146" s="23"/>
       <c r="L146" s="10"/>
       <c r="M146" s="10"/>
       <c r="N146" s="10"/>
@@ -56752,29 +56813,19 @@
       <c r="S146" s="10"/>
     </row>
     <row r="147" ht="18.75" customHeight="1">
-      <c r="A147" s="10"/>
-      <c r="B147" s="10"/>
-      <c r="C147" s="23" t="s">
-        <v>5753</v>
-      </c>
-      <c r="D147" s="25" t="s">
-        <v>5748</v>
-      </c>
-      <c r="E147" s="23" t="s">
-        <v>5755</v>
-      </c>
-      <c r="F147" s="25" t="s">
-        <v>5750</v>
-      </c>
-      <c r="G147" s="23" t="s">
-        <v>5757</v>
-      </c>
-      <c r="H147" s="25" t="s">
-        <v>5752</v>
-      </c>
-      <c r="I147" s="10"/>
-      <c r="J147" s="10"/>
-      <c r="K147" s="10"/>
+      <c r="A147" s="26"/>
+      <c r="B147" s="24" t="s">
+        <v>5114</v>
+      </c>
+      <c r="C147" s="26"/>
+      <c r="D147" s="22"/>
+      <c r="E147" s="26"/>
+      <c r="F147" s="22"/>
+      <c r="G147" s="26"/>
+      <c r="H147" s="22"/>
+      <c r="I147" s="26"/>
+      <c r="J147" s="22"/>
+      <c r="K147" s="23"/>
       <c r="L147" s="10"/>
       <c r="M147" s="10"/>
       <c r="N147" s="10"/>
@@ -56785,29 +56836,37 @@
       <c r="S147" s="10"/>
     </row>
     <row r="148" ht="18.75" customHeight="1">
-      <c r="A148" s="10"/>
-      <c r="B148" s="10"/>
-      <c r="C148" s="23" t="s">
-        <v>5759</v>
+      <c r="A148" s="21" t="s">
+        <v>4886</v>
+      </c>
+      <c r="B148" s="24" t="s">
+        <v>4230</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>5747</v>
       </c>
       <c r="D148" s="25" t="s">
-        <v>5760</v>
-      </c>
-      <c r="E148" s="23" t="s">
-        <v>5761</v>
+        <v>5748</v>
+      </c>
+      <c r="E148" s="10" t="s">
+        <v>5749</v>
       </c>
       <c r="F148" s="25" t="s">
-        <v>5762</v>
-      </c>
-      <c r="G148" s="23" t="s">
-        <v>5763</v>
+        <v>5750</v>
+      </c>
+      <c r="G148" s="10" t="s">
+        <v>5751</v>
       </c>
       <c r="H148" s="25" t="s">
-        <v>5764</v>
-      </c>
-      <c r="I148" s="10"/>
-      <c r="J148" s="10"/>
-      <c r="K148" s="10"/>
+        <v>5752</v>
+      </c>
+      <c r="I148" s="10" t="s">
+        <v>5753</v>
+      </c>
+      <c r="J148" s="25" t="s">
+        <v>5754</v>
+      </c>
+      <c r="K148" s="23"/>
       <c r="L148" s="10"/>
       <c r="M148" s="10"/>
       <c r="N148" s="10"/>
@@ -56818,29 +56877,35 @@
       <c r="S148" s="10"/>
     </row>
     <row r="149" ht="18.75" customHeight="1">
-      <c r="A149" s="10"/>
-      <c r="B149" s="10"/>
-      <c r="C149" s="23" t="s">
-        <v>5765</v>
+      <c r="A149" s="26"/>
+      <c r="B149" s="24" t="s">
+        <v>4351</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>5755</v>
       </c>
       <c r="D149" s="25" t="s">
-        <v>5766</v>
-      </c>
-      <c r="E149" s="23" t="s">
-        <v>5767</v>
+        <v>5756</v>
+      </c>
+      <c r="E149" s="10" t="s">
+        <v>5757</v>
       </c>
       <c r="F149" s="25" t="s">
-        <v>5768</v>
-      </c>
-      <c r="G149" s="23" t="s">
-        <v>5769</v>
+        <v>5758</v>
+      </c>
+      <c r="G149" s="10" t="s">
+        <v>5759</v>
       </c>
       <c r="H149" s="25" t="s">
-        <v>5770</v>
-      </c>
-      <c r="I149" s="10"/>
-      <c r="J149" s="10"/>
-      <c r="K149" s="10"/>
+        <v>5760</v>
+      </c>
+      <c r="I149" s="10" t="s">
+        <v>5761</v>
+      </c>
+      <c r="J149" s="25" t="s">
+        <v>5762</v>
+      </c>
+      <c r="K149" s="23"/>
       <c r="L149" s="10"/>
       <c r="M149" s="10"/>
       <c r="N149" s="10"/>
@@ -56851,29 +56916,19 @@
       <c r="S149" s="10"/>
     </row>
     <row r="150" ht="18.75" customHeight="1">
-      <c r="A150" s="10"/>
-      <c r="B150" s="10"/>
-      <c r="C150" s="36" t="s">
-        <v>5771</v>
-      </c>
-      <c r="D150" s="28" t="s">
-        <v>5772</v>
-      </c>
-      <c r="E150" s="36" t="s">
-        <v>5773</v>
-      </c>
-      <c r="F150" s="28" t="s">
-        <v>5774</v>
-      </c>
-      <c r="G150" s="36" t="s">
-        <v>5775</v>
-      </c>
-      <c r="H150" s="28" t="s">
-        <v>5776</v>
-      </c>
-      <c r="I150" s="10"/>
-      <c r="J150" s="10"/>
-      <c r="K150" s="10"/>
+      <c r="A150" s="31"/>
+      <c r="B150" s="32" t="s">
+        <v>5139</v>
+      </c>
+      <c r="C150" s="33"/>
+      <c r="D150" s="34"/>
+      <c r="E150" s="33"/>
+      <c r="F150" s="34"/>
+      <c r="G150" s="33"/>
+      <c r="H150" s="34"/>
+      <c r="I150" s="33"/>
+      <c r="J150" s="34"/>
+      <c r="K150" s="23"/>
       <c r="L150" s="10"/>
       <c r="M150" s="10"/>
       <c r="N150" s="10"/>
@@ -56905,22 +56960,21 @@
       <c r="S151" s="10"/>
     </row>
     <row r="152" ht="18.75" customHeight="1">
-      <c r="A152" s="18" t="s">
-        <v>5777</v>
-      </c>
-      <c r="B152" s="19"/>
+      <c r="A152" s="10"/>
+      <c r="B152" s="10"/>
       <c r="C152" s="18" t="s">
-        <v>5778</v>
+        <v>5763</v>
       </c>
       <c r="D152" s="19"/>
       <c r="E152" s="18" t="s">
-        <v>5779</v>
+        <v>5764</v>
       </c>
       <c r="F152" s="19"/>
       <c r="G152" s="18" t="s">
-        <v>5780</v>
+        <v>5765</v>
       </c>
       <c r="H152" s="19"/>
+      <c r="I152" s="10"/>
       <c r="J152" s="10"/>
       <c r="K152" s="10"/>
       <c r="L152" s="10"/>
@@ -56933,22 +56987,21 @@
       <c r="S152" s="10"/>
     </row>
     <row r="153" ht="18.75" customHeight="1">
-      <c r="A153" s="21" t="s">
-        <v>5078</v>
-      </c>
-      <c r="B153" s="22"/>
+      <c r="A153" s="10"/>
+      <c r="B153" s="10"/>
       <c r="C153" s="23" t="s">
-        <v>5781</v>
+        <v>5766</v>
       </c>
       <c r="D153" s="22"/>
       <c r="E153" s="23" t="s">
-        <v>5782</v>
+        <v>5767</v>
       </c>
       <c r="F153" s="22"/>
       <c r="G153" s="23" t="s">
-        <v>5783</v>
+        <v>5768</v>
       </c>
       <c r="H153" s="22"/>
+      <c r="I153" s="10"/>
       <c r="J153" s="10"/>
       <c r="K153" s="10"/>
       <c r="L153" s="10"/>
@@ -56961,22 +57014,21 @@
       <c r="S153" s="10"/>
     </row>
     <row r="154" ht="18.75" customHeight="1">
-      <c r="A154" s="21" t="s">
-        <v>5084</v>
-      </c>
-      <c r="B154" s="22"/>
+      <c r="A154" s="10"/>
+      <c r="B154" s="10"/>
       <c r="C154" s="23" t="s">
-        <v>5784</v>
+        <v>5769</v>
       </c>
       <c r="D154" s="22"/>
       <c r="E154" s="23" t="s">
-        <v>5785</v>
+        <v>5770</v>
       </c>
       <c r="F154" s="22"/>
       <c r="G154" s="23" t="s">
-        <v>5786</v>
+        <v>5771</v>
       </c>
       <c r="H154" s="22"/>
+      <c r="I154" s="10"/>
       <c r="J154" s="10"/>
       <c r="K154" s="10"/>
       <c r="L154" s="10"/>
@@ -56989,22 +57041,21 @@
       <c r="S154" s="10"/>
     </row>
     <row r="155" ht="18.75" customHeight="1">
-      <c r="A155" s="21" t="s">
-        <v>5090</v>
-      </c>
-      <c r="B155" s="22"/>
+      <c r="A155" s="10"/>
+      <c r="B155" s="10"/>
       <c r="C155" s="23" t="s">
-        <v>5787</v>
+        <v>5772</v>
       </c>
       <c r="D155" s="22"/>
       <c r="E155" s="23" t="s">
-        <v>5788</v>
+        <v>5773</v>
       </c>
       <c r="F155" s="22"/>
       <c r="G155" s="23" t="s">
-        <v>5789</v>
+        <v>3304</v>
       </c>
       <c r="H155" s="22"/>
+      <c r="I155" s="10"/>
       <c r="J155" s="10"/>
       <c r="K155" s="10"/>
       <c r="L155" s="10"/>
@@ -57017,10 +57068,8 @@
       <c r="S155" s="10"/>
     </row>
     <row r="156" ht="18.75" customHeight="1">
-      <c r="A156" s="21" t="s">
-        <v>5096</v>
-      </c>
-      <c r="B156" s="22"/>
+      <c r="A156" s="10"/>
+      <c r="B156" s="10"/>
       <c r="C156" s="21" t="s">
         <v>5097</v>
       </c>
@@ -57039,6 +57088,7 @@
       <c r="H156" s="24" t="s">
         <v>5098</v>
       </c>
+      <c r="I156" s="10"/>
       <c r="J156" s="10"/>
       <c r="K156" s="10"/>
       <c r="L156" s="10"/>
@@ -57051,30 +57101,27 @@
       <c r="S156" s="10"/>
     </row>
     <row r="157" ht="18.75" customHeight="1">
-      <c r="A157" s="21" t="s">
-        <v>4862</v>
-      </c>
-      <c r="B157" s="24" t="s">
-        <v>5099</v>
-      </c>
+      <c r="A157" s="10"/>
+      <c r="B157" s="10"/>
       <c r="C157" s="23" t="s">
-        <v>5790</v>
+        <v>5774</v>
       </c>
       <c r="D157" s="25" t="s">
-        <v>5791</v>
+        <v>5775</v>
       </c>
       <c r="E157" s="23" t="s">
-        <v>5792</v>
+        <v>5776</v>
       </c>
       <c r="F157" s="25" t="s">
-        <v>5793</v>
+        <v>5777</v>
       </c>
       <c r="G157" s="23" t="s">
-        <v>5794</v>
+        <v>5778</v>
       </c>
       <c r="H157" s="25" t="s">
-        <v>5795</v>
-      </c>
+        <v>5779</v>
+      </c>
+      <c r="I157" s="10"/>
       <c r="J157" s="10"/>
       <c r="K157" s="10"/>
       <c r="L157" s="10"/>
@@ -57087,28 +57134,27 @@
       <c r="S157" s="10"/>
     </row>
     <row r="158" ht="18.75" customHeight="1">
-      <c r="A158" s="26"/>
-      <c r="B158" s="24" t="s">
-        <v>4401</v>
-      </c>
+      <c r="A158" s="10"/>
+      <c r="B158" s="10"/>
       <c r="C158" s="23" t="s">
-        <v>5796</v>
+        <v>5780</v>
       </c>
       <c r="D158" s="25" t="s">
-        <v>5797</v>
+        <v>5781</v>
       </c>
       <c r="E158" s="23" t="s">
-        <v>5798</v>
+        <v>5782</v>
       </c>
       <c r="F158" s="25" t="s">
-        <v>5799</v>
+        <v>5783</v>
       </c>
       <c r="G158" s="23" t="s">
-        <v>5800</v>
+        <v>5784</v>
       </c>
       <c r="H158" s="25" t="s">
-        <v>5801</v>
-      </c>
+        <v>5785</v>
+      </c>
+      <c r="I158" s="10"/>
       <c r="J158" s="10"/>
       <c r="K158" s="10"/>
       <c r="L158" s="10"/>
@@ -57121,28 +57167,27 @@
       <c r="S158" s="10"/>
     </row>
     <row r="159" ht="18.75" customHeight="1">
-      <c r="A159" s="26"/>
-      <c r="B159" s="24" t="s">
-        <v>5114</v>
-      </c>
+      <c r="A159" s="10"/>
+      <c r="B159" s="10"/>
       <c r="C159" s="23" t="s">
-        <v>5796</v>
+        <v>5780</v>
       </c>
       <c r="D159" s="25" t="s">
-        <v>5791</v>
+        <v>5775</v>
       </c>
       <c r="E159" s="23" t="s">
-        <v>5798</v>
+        <v>5782</v>
       </c>
       <c r="F159" s="25" t="s">
-        <v>5793</v>
+        <v>5777</v>
       </c>
       <c r="G159" s="23" t="s">
-        <v>5800</v>
+        <v>5784</v>
       </c>
       <c r="H159" s="25" t="s">
-        <v>5795</v>
-      </c>
+        <v>5779</v>
+      </c>
+      <c r="I159" s="10"/>
       <c r="J159" s="10"/>
       <c r="K159" s="10"/>
       <c r="L159" s="10"/>
@@ -57155,30 +57200,27 @@
       <c r="S159" s="10"/>
     </row>
     <row r="160" ht="18.75" customHeight="1">
-      <c r="A160" s="8" t="s">
-        <v>4886</v>
-      </c>
-      <c r="B160" s="24" t="s">
-        <v>4230</v>
-      </c>
+      <c r="A160" s="10"/>
+      <c r="B160" s="10"/>
       <c r="C160" s="23" t="s">
-        <v>5802</v>
+        <v>5786</v>
       </c>
       <c r="D160" s="25" t="s">
-        <v>5803</v>
+        <v>5787</v>
       </c>
       <c r="E160" s="23" t="s">
-        <v>5804</v>
+        <v>5788</v>
       </c>
       <c r="F160" s="25" t="s">
-        <v>5805</v>
+        <v>5789</v>
       </c>
       <c r="G160" s="23" t="s">
-        <v>5806</v>
+        <v>5790</v>
       </c>
       <c r="H160" s="25" t="s">
-        <v>5807</v>
-      </c>
+        <v>5791</v>
+      </c>
+      <c r="I160" s="10"/>
       <c r="J160" s="10"/>
       <c r="K160" s="10"/>
       <c r="L160" s="10"/>
@@ -57191,27 +57233,27 @@
       <c r="S160" s="10"/>
     </row>
     <row r="161" ht="18.75" customHeight="1">
-      <c r="B161" s="24" t="s">
-        <v>4351</v>
-      </c>
+      <c r="A161" s="10"/>
+      <c r="B161" s="10"/>
       <c r="C161" s="23" t="s">
-        <v>5808</v>
+        <v>5792</v>
       </c>
       <c r="D161" s="25" t="s">
-        <v>5809</v>
+        <v>5793</v>
       </c>
       <c r="E161" s="23" t="s">
-        <v>5810</v>
+        <v>5794</v>
       </c>
       <c r="F161" s="25" t="s">
-        <v>5811</v>
+        <v>5795</v>
       </c>
       <c r="G161" s="23" t="s">
-        <v>5812</v>
+        <v>5796</v>
       </c>
       <c r="H161" s="25" t="s">
-        <v>5813</v>
-      </c>
+        <v>5797</v>
+      </c>
+      <c r="I161" s="10"/>
       <c r="J161" s="10"/>
       <c r="K161" s="10"/>
       <c r="L161" s="10"/>
@@ -57224,27 +57266,27 @@
       <c r="S161" s="10"/>
     </row>
     <row r="162" ht="18.75" customHeight="1">
-      <c r="B162" s="24" t="s">
-        <v>5139</v>
-      </c>
-      <c r="C162" s="23" t="s">
-        <v>5814</v>
-      </c>
-      <c r="D162" s="25" t="s">
-        <v>5815</v>
-      </c>
-      <c r="E162" s="23" t="s">
-        <v>5816</v>
-      </c>
-      <c r="F162" s="25" t="s">
-        <v>5817</v>
-      </c>
-      <c r="G162" s="23" t="s">
-        <v>5818</v>
-      </c>
-      <c r="H162" s="25" t="s">
-        <v>5819</v>
-      </c>
+      <c r="A162" s="10"/>
+      <c r="B162" s="10"/>
+      <c r="C162" s="36" t="s">
+        <v>5798</v>
+      </c>
+      <c r="D162" s="28" t="s">
+        <v>5799</v>
+      </c>
+      <c r="E162" s="36" t="s">
+        <v>5800</v>
+      </c>
+      <c r="F162" s="28" t="s">
+        <v>5801</v>
+      </c>
+      <c r="G162" s="36" t="s">
+        <v>5802</v>
+      </c>
+      <c r="H162" s="28" t="s">
+        <v>5803</v>
+      </c>
+      <c r="I162" s="10"/>
       <c r="J162" s="10"/>
       <c r="K162" s="10"/>
       <c r="L162" s="10"/>
@@ -57257,20 +57299,14 @@
       <c r="S162" s="10"/>
     </row>
     <row r="163" ht="18.75" customHeight="1">
-      <c r="A163" s="21" t="s">
-        <v>5150</v>
-      </c>
-      <c r="B163" s="22"/>
-      <c r="C163" s="8" t="s">
-        <v>5097</v>
-      </c>
-      <c r="D163" s="24" t="s">
-        <v>5098</v>
-      </c>
-      <c r="E163" s="38"/>
-      <c r="F163" s="38"/>
-      <c r="G163" s="30"/>
-      <c r="H163" s="30"/>
+      <c r="A163" s="10"/>
+      <c r="B163" s="10"/>
+      <c r="C163" s="10"/>
+      <c r="D163" s="10"/>
+      <c r="E163" s="10"/>
+      <c r="F163" s="10"/>
+      <c r="G163" s="10"/>
+      <c r="H163" s="10"/>
       <c r="I163" s="10"/>
       <c r="J163" s="10"/>
       <c r="K163" s="10"/>
@@ -57284,23 +57320,22 @@
       <c r="S163" s="10"/>
     </row>
     <row r="164" ht="18.75" customHeight="1">
-      <c r="A164" s="21" t="s">
-        <v>4862</v>
-      </c>
-      <c r="B164" s="8" t="s">
-        <v>5099</v>
-      </c>
-      <c r="C164" s="23" t="s">
-        <v>5820</v>
-      </c>
-      <c r="D164" s="25" t="s">
-        <v>5821</v>
-      </c>
-      <c r="E164" s="40"/>
-      <c r="F164" s="40"/>
-      <c r="G164" s="10"/>
-      <c r="H164" s="10"/>
-      <c r="I164" s="10"/>
+      <c r="A164" s="18" t="s">
+        <v>5804</v>
+      </c>
+      <c r="B164" s="19"/>
+      <c r="C164" s="18" t="s">
+        <v>5805</v>
+      </c>
+      <c r="D164" s="19"/>
+      <c r="E164" s="18" t="s">
+        <v>5806</v>
+      </c>
+      <c r="F164" s="19"/>
+      <c r="G164" s="18" t="s">
+        <v>5807</v>
+      </c>
+      <c r="H164" s="19"/>
       <c r="J164" s="10"/>
       <c r="K164" s="10"/>
       <c r="L164" s="10"/>
@@ -57313,17 +57348,22 @@
       <c r="S164" s="10"/>
     </row>
     <row r="165" ht="18.75" customHeight="1">
-      <c r="A165" s="26"/>
-      <c r="B165" s="8" t="s">
-        <v>4401</v>
-      </c>
-      <c r="C165" s="26"/>
+      <c r="A165" s="21" t="s">
+        <v>5078</v>
+      </c>
+      <c r="B165" s="22"/>
+      <c r="C165" s="23" t="s">
+        <v>5808</v>
+      </c>
       <c r="D165" s="22"/>
-      <c r="E165" s="40"/>
-      <c r="F165" s="40"/>
-      <c r="G165" s="10"/>
-      <c r="H165" s="10"/>
-      <c r="I165" s="10"/>
+      <c r="E165" s="23" t="s">
+        <v>5809</v>
+      </c>
+      <c r="F165" s="22"/>
+      <c r="G165" s="23" t="s">
+        <v>5810</v>
+      </c>
+      <c r="H165" s="22"/>
       <c r="J165" s="10"/>
       <c r="K165" s="10"/>
       <c r="L165" s="10"/>
@@ -57336,17 +57376,22 @@
       <c r="S165" s="10"/>
     </row>
     <row r="166" ht="18.75" customHeight="1">
-      <c r="A166" s="26"/>
-      <c r="B166" s="24" t="s">
-        <v>5114</v>
-      </c>
-      <c r="C166" s="26"/>
+      <c r="A166" s="21" t="s">
+        <v>5084</v>
+      </c>
+      <c r="B166" s="22"/>
+      <c r="C166" s="23" t="s">
+        <v>5811</v>
+      </c>
       <c r="D166" s="22"/>
-      <c r="E166" s="40"/>
-      <c r="F166" s="40"/>
-      <c r="G166" s="10"/>
-      <c r="H166" s="10"/>
-      <c r="I166" s="10"/>
+      <c r="E166" s="23" t="s">
+        <v>5812</v>
+      </c>
+      <c r="F166" s="22"/>
+      <c r="G166" s="23" t="s">
+        <v>5813</v>
+      </c>
+      <c r="H166" s="22"/>
       <c r="J166" s="10"/>
       <c r="K166" s="10"/>
       <c r="L166" s="10"/>
@@ -57360,22 +57405,21 @@
     </row>
     <row r="167" ht="18.75" customHeight="1">
       <c r="A167" s="21" t="s">
-        <v>4886</v>
-      </c>
-      <c r="B167" s="24" t="s">
-        <v>4230</v>
-      </c>
-      <c r="C167" s="10" t="s">
-        <v>5822</v>
-      </c>
-      <c r="D167" s="25" t="s">
-        <v>5823</v>
-      </c>
-      <c r="E167" s="40"/>
-      <c r="F167" s="40"/>
-      <c r="G167" s="10"/>
-      <c r="H167" s="10"/>
-      <c r="I167" s="10"/>
+        <v>5090</v>
+      </c>
+      <c r="B167" s="22"/>
+      <c r="C167" s="23" t="s">
+        <v>5814</v>
+      </c>
+      <c r="D167" s="22"/>
+      <c r="E167" s="23" t="s">
+        <v>5815</v>
+      </c>
+      <c r="F167" s="22"/>
+      <c r="G167" s="23" t="s">
+        <v>5816</v>
+      </c>
+      <c r="H167" s="22"/>
       <c r="J167" s="10"/>
       <c r="K167" s="10"/>
       <c r="L167" s="10"/>
@@ -57388,21 +57432,28 @@
       <c r="S167" s="10"/>
     </row>
     <row r="168" ht="18.75" customHeight="1">
-      <c r="A168" s="26"/>
-      <c r="B168" s="24" t="s">
-        <v>4351</v>
-      </c>
-      <c r="C168" s="10" t="s">
-        <v>5824</v>
-      </c>
-      <c r="D168" s="25" t="s">
-        <v>5825</v>
-      </c>
-      <c r="E168" s="40"/>
-      <c r="F168" s="40"/>
-      <c r="G168" s="10"/>
-      <c r="H168" s="10"/>
-      <c r="I168" s="10"/>
+      <c r="A168" s="21" t="s">
+        <v>5096</v>
+      </c>
+      <c r="B168" s="22"/>
+      <c r="C168" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="D168" s="24" t="s">
+        <v>5098</v>
+      </c>
+      <c r="E168" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="F168" s="24" t="s">
+        <v>5098</v>
+      </c>
+      <c r="G168" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="H168" s="24" t="s">
+        <v>5098</v>
+      </c>
       <c r="J168" s="10"/>
       <c r="K168" s="10"/>
       <c r="L168" s="10"/>
@@ -57415,17 +57466,30 @@
       <c r="S168" s="10"/>
     </row>
     <row r="169" ht="18.75" customHeight="1">
-      <c r="A169" s="31"/>
-      <c r="B169" s="32" t="s">
-        <v>5139</v>
-      </c>
-      <c r="C169" s="33"/>
-      <c r="D169" s="34"/>
-      <c r="E169" s="40"/>
-      <c r="F169" s="40"/>
-      <c r="G169" s="10"/>
-      <c r="H169" s="10"/>
-      <c r="I169" s="10"/>
+      <c r="A169" s="21" t="s">
+        <v>4862</v>
+      </c>
+      <c r="B169" s="24" t="s">
+        <v>5099</v>
+      </c>
+      <c r="C169" s="23" t="s">
+        <v>5817</v>
+      </c>
+      <c r="D169" s="25" t="s">
+        <v>5818</v>
+      </c>
+      <c r="E169" s="23" t="s">
+        <v>5819</v>
+      </c>
+      <c r="F169" s="25" t="s">
+        <v>5820</v>
+      </c>
+      <c r="G169" s="23" t="s">
+        <v>5821</v>
+      </c>
+      <c r="H169" s="25" t="s">
+        <v>5822</v>
+      </c>
       <c r="J169" s="10"/>
       <c r="K169" s="10"/>
       <c r="L169" s="10"/>
@@ -57438,15 +57502,28 @@
       <c r="S169" s="10"/>
     </row>
     <row r="170" ht="18.75" customHeight="1">
-      <c r="A170" s="10"/>
-      <c r="B170" s="10"/>
-      <c r="C170" s="10"/>
-      <c r="D170" s="10"/>
-      <c r="E170" s="10"/>
-      <c r="F170" s="10"/>
-      <c r="G170" s="10"/>
-      <c r="H170" s="10"/>
-      <c r="I170" s="10"/>
+      <c r="A170" s="26"/>
+      <c r="B170" s="24" t="s">
+        <v>4401</v>
+      </c>
+      <c r="C170" s="23" t="s">
+        <v>5823</v>
+      </c>
+      <c r="D170" s="25" t="s">
+        <v>5824</v>
+      </c>
+      <c r="E170" s="23" t="s">
+        <v>5825</v>
+      </c>
+      <c r="F170" s="25" t="s">
+        <v>5826</v>
+      </c>
+      <c r="G170" s="23" t="s">
+        <v>5827</v>
+      </c>
+      <c r="H170" s="25" t="s">
+        <v>5828</v>
+      </c>
       <c r="J170" s="10"/>
       <c r="K170" s="10"/>
       <c r="L170" s="10"/>
@@ -57459,23 +57536,28 @@
       <c r="S170" s="10"/>
     </row>
     <row r="171" ht="18.75" customHeight="1">
-      <c r="A171" s="18" t="s">
-        <v>5826</v>
-      </c>
-      <c r="B171" s="19"/>
-      <c r="C171" s="20" t="s">
+      <c r="A171" s="26"/>
+      <c r="B171" s="24" t="s">
+        <v>5114</v>
+      </c>
+      <c r="C171" s="23" t="s">
+        <v>5823</v>
+      </c>
+      <c r="D171" s="25" t="s">
+        <v>5818</v>
+      </c>
+      <c r="E171" s="23" t="s">
+        <v>5825</v>
+      </c>
+      <c r="F171" s="25" t="s">
+        <v>5820</v>
+      </c>
+      <c r="G171" s="23" t="s">
         <v>5827</v>
       </c>
-      <c r="D171" s="19"/>
-      <c r="E171" s="20" t="s">
-        <v>5828</v>
-      </c>
-      <c r="F171" s="19"/>
-      <c r="G171" s="20" t="s">
-        <v>5829</v>
-      </c>
-      <c r="H171" s="19"/>
-      <c r="I171" s="10"/>
+      <c r="H171" s="25" t="s">
+        <v>5822</v>
+      </c>
       <c r="J171" s="10"/>
       <c r="K171" s="10"/>
       <c r="L171" s="10"/>
@@ -57488,23 +57570,30 @@
       <c r="S171" s="10"/>
     </row>
     <row r="172" ht="18.75" customHeight="1">
-      <c r="A172" s="21" t="s">
-        <v>5078</v>
-      </c>
-      <c r="B172" s="22"/>
-      <c r="C172" s="10" t="s">
+      <c r="A172" s="8" t="s">
+        <v>4886</v>
+      </c>
+      <c r="B172" s="24" t="s">
+        <v>4230</v>
+      </c>
+      <c r="C172" s="23" t="s">
+        <v>5829</v>
+      </c>
+      <c r="D172" s="25" t="s">
         <v>5830</v>
       </c>
-      <c r="D172" s="22"/>
-      <c r="E172" s="10" t="s">
-        <v>5642</v>
-      </c>
-      <c r="F172" s="22"/>
-      <c r="G172" s="10" t="s">
+      <c r="E172" s="23" t="s">
         <v>5831</v>
       </c>
-      <c r="H172" s="22"/>
-      <c r="I172" s="10"/>
+      <c r="F172" s="25" t="s">
+        <v>5832</v>
+      </c>
+      <c r="G172" s="23" t="s">
+        <v>5833</v>
+      </c>
+      <c r="H172" s="25" t="s">
+        <v>5834</v>
+      </c>
       <c r="J172" s="10"/>
       <c r="K172" s="10"/>
       <c r="L172" s="10"/>
@@ -57517,23 +57606,27 @@
       <c r="S172" s="10"/>
     </row>
     <row r="173" ht="18.75" customHeight="1">
-      <c r="A173" s="21" t="s">
-        <v>5084</v>
-      </c>
-      <c r="B173" s="22"/>
+      <c r="B173" s="24" t="s">
+        <v>4351</v>
+      </c>
       <c r="C173" s="23" t="s">
-        <v>5832</v>
-      </c>
-      <c r="D173" s="22"/>
+        <v>5835</v>
+      </c>
+      <c r="D173" s="25" t="s">
+        <v>5836</v>
+      </c>
       <c r="E173" s="23" t="s">
-        <v>5648</v>
-      </c>
-      <c r="F173" s="22"/>
+        <v>5837</v>
+      </c>
+      <c r="F173" s="25" t="s">
+        <v>5838</v>
+      </c>
       <c r="G173" s="23" t="s">
-        <v>5833</v>
-      </c>
-      <c r="H173" s="22"/>
-      <c r="I173" s="10"/>
+        <v>5839</v>
+      </c>
+      <c r="H173" s="25" t="s">
+        <v>5840</v>
+      </c>
       <c r="J173" s="10"/>
       <c r="K173" s="10"/>
       <c r="L173" s="10"/>
@@ -57546,23 +57639,27 @@
       <c r="S173" s="10"/>
     </row>
     <row r="174" ht="18.75" customHeight="1">
-      <c r="A174" s="21" t="s">
-        <v>5090</v>
-      </c>
-      <c r="B174" s="22"/>
+      <c r="B174" s="24" t="s">
+        <v>5139</v>
+      </c>
       <c r="C174" s="23" t="s">
-        <v>5834</v>
-      </c>
-      <c r="D174" s="22"/>
+        <v>5841</v>
+      </c>
+      <c r="D174" s="25" t="s">
+        <v>5842</v>
+      </c>
       <c r="E174" s="23" t="s">
-        <v>5654</v>
-      </c>
-      <c r="F174" s="22"/>
+        <v>5843</v>
+      </c>
+      <c r="F174" s="25" t="s">
+        <v>5844</v>
+      </c>
       <c r="G174" s="23" t="s">
-        <v>5835</v>
-      </c>
-      <c r="H174" s="22"/>
-      <c r="I174" s="10"/>
+        <v>5845</v>
+      </c>
+      <c r="H174" s="25" t="s">
+        <v>5846</v>
+      </c>
       <c r="J174" s="10"/>
       <c r="K174" s="10"/>
       <c r="L174" s="10"/>
@@ -57576,27 +57673,19 @@
     </row>
     <row r="175" ht="18.75" customHeight="1">
       <c r="A175" s="21" t="s">
-        <v>5096</v>
+        <v>5150</v>
       </c>
       <c r="B175" s="22"/>
-      <c r="C175" s="21" t="s">
+      <c r="C175" s="8" t="s">
         <v>5097</v>
       </c>
       <c r="D175" s="24" t="s">
         <v>5098</v>
       </c>
-      <c r="E175" s="21" t="s">
-        <v>5097</v>
-      </c>
-      <c r="F175" s="24" t="s">
-        <v>5098</v>
-      </c>
-      <c r="G175" s="21" t="s">
-        <v>5097</v>
-      </c>
-      <c r="H175" s="24" t="s">
-        <v>5098</v>
-      </c>
+      <c r="E175" s="38"/>
+      <c r="F175" s="38"/>
+      <c r="G175" s="30"/>
+      <c r="H175" s="30"/>
       <c r="I175" s="10"/>
       <c r="J175" s="10"/>
       <c r="K175" s="10"/>
@@ -57613,27 +57702,19 @@
       <c r="A176" s="21" t="s">
         <v>4862</v>
       </c>
-      <c r="B176" s="24" t="s">
+      <c r="B176" s="8" t="s">
         <v>5099</v>
       </c>
       <c r="C176" s="23" t="s">
-        <v>5836</v>
+        <v>5847</v>
       </c>
       <c r="D176" s="25" t="s">
-        <v>5837</v>
-      </c>
-      <c r="E176" s="23" t="s">
-        <v>5663</v>
-      </c>
-      <c r="F176" s="25" t="s">
-        <v>5664</v>
-      </c>
-      <c r="G176" s="23" t="s">
-        <v>5838</v>
-      </c>
-      <c r="H176" s="25" t="s">
-        <v>5839</v>
-      </c>
+        <v>5848</v>
+      </c>
+      <c r="E176" s="40"/>
+      <c r="F176" s="40"/>
+      <c r="G176" s="10"/>
+      <c r="H176" s="10"/>
       <c r="I176" s="10"/>
       <c r="J176" s="10"/>
       <c r="K176" s="10"/>
@@ -57648,27 +57729,15 @@
     </row>
     <row r="177" ht="18.75" customHeight="1">
       <c r="A177" s="26"/>
-      <c r="B177" s="24" t="s">
+      <c r="B177" s="8" t="s">
         <v>4401</v>
       </c>
-      <c r="C177" s="23" t="s">
-        <v>5840</v>
-      </c>
-      <c r="D177" s="25" t="s">
-        <v>5841</v>
-      </c>
-      <c r="E177" s="23" t="s">
-        <v>5674</v>
-      </c>
-      <c r="F177" s="25" t="s">
-        <v>5675</v>
-      </c>
-      <c r="G177" s="23" t="s">
-        <v>5842</v>
-      </c>
-      <c r="H177" s="25" t="s">
-        <v>5843</v>
-      </c>
+      <c r="C177" s="26"/>
+      <c r="D177" s="22"/>
+      <c r="E177" s="40"/>
+      <c r="F177" s="40"/>
+      <c r="G177" s="10"/>
+      <c r="H177" s="10"/>
       <c r="I177" s="10"/>
       <c r="J177" s="10"/>
       <c r="K177" s="10"/>
@@ -57686,24 +57755,12 @@
       <c r="B178" s="24" t="s">
         <v>5114</v>
       </c>
-      <c r="C178" s="23" t="s">
-        <v>5840</v>
-      </c>
-      <c r="D178" s="25" t="s">
-        <v>5837</v>
-      </c>
-      <c r="E178" s="23" t="s">
-        <v>5674</v>
-      </c>
-      <c r="F178" s="25" t="s">
-        <v>5664</v>
-      </c>
-      <c r="G178" s="23" t="s">
-        <v>5842</v>
-      </c>
-      <c r="H178" s="25" t="s">
-        <v>5839</v>
-      </c>
+      <c r="C178" s="26"/>
+      <c r="D178" s="22"/>
+      <c r="E178" s="40"/>
+      <c r="F178" s="40"/>
+      <c r="G178" s="10"/>
+      <c r="H178" s="10"/>
       <c r="I178" s="10"/>
       <c r="J178" s="10"/>
       <c r="K178" s="10"/>
@@ -57723,24 +57780,16 @@
       <c r="B179" s="24" t="s">
         <v>4230</v>
       </c>
-      <c r="C179" s="23" t="s">
-        <v>5844</v>
+      <c r="C179" s="10" t="s">
+        <v>5849</v>
       </c>
       <c r="D179" s="25" t="s">
-        <v>5845</v>
-      </c>
-      <c r="E179" s="23" t="s">
-        <v>5686</v>
-      </c>
-      <c r="F179" s="25" t="s">
-        <v>5687</v>
-      </c>
-      <c r="G179" s="23" t="s">
-        <v>5846</v>
-      </c>
-      <c r="H179" s="25" t="s">
-        <v>5847</v>
-      </c>
+        <v>5850</v>
+      </c>
+      <c r="E179" s="40"/>
+      <c r="F179" s="40"/>
+      <c r="G179" s="10"/>
+      <c r="H179" s="10"/>
       <c r="I179" s="10"/>
       <c r="J179" s="10"/>
       <c r="K179" s="10"/>
@@ -57758,24 +57807,16 @@
       <c r="B180" s="24" t="s">
         <v>4351</v>
       </c>
-      <c r="C180" s="23" t="s">
-        <v>5848</v>
+      <c r="C180" s="10" t="s">
+        <v>5851</v>
       </c>
       <c r="D180" s="25" t="s">
-        <v>5849</v>
-      </c>
-      <c r="E180" s="23" t="s">
-        <v>5698</v>
-      </c>
-      <c r="F180" s="10" t="s">
-        <v>5699</v>
-      </c>
-      <c r="G180" s="23" t="s">
-        <v>5850</v>
-      </c>
-      <c r="H180" s="25" t="s">
-        <v>5851</v>
-      </c>
+        <v>5852</v>
+      </c>
+      <c r="E180" s="40"/>
+      <c r="F180" s="40"/>
+      <c r="G180" s="10"/>
+      <c r="H180" s="10"/>
       <c r="I180" s="10"/>
       <c r="J180" s="10"/>
       <c r="K180" s="10"/>
@@ -57793,24 +57834,12 @@
       <c r="B181" s="32" t="s">
         <v>5139</v>
       </c>
-      <c r="C181" s="36" t="s">
-        <v>5852</v>
-      </c>
-      <c r="D181" s="28" t="s">
-        <v>5853</v>
-      </c>
-      <c r="E181" s="36" t="s">
-        <v>5710</v>
-      </c>
-      <c r="F181" s="28" t="s">
-        <v>5711</v>
-      </c>
-      <c r="G181" s="36" t="s">
-        <v>5854</v>
-      </c>
-      <c r="H181" s="28" t="s">
-        <v>5855</v>
-      </c>
+      <c r="C181" s="33"/>
+      <c r="D181" s="34"/>
+      <c r="E181" s="40"/>
+      <c r="F181" s="40"/>
+      <c r="G181" s="10"/>
+      <c r="H181" s="10"/>
       <c r="I181" s="10"/>
       <c r="J181" s="10"/>
       <c r="K181" s="10"/>
@@ -57846,17 +57875,21 @@
     </row>
     <row r="183" ht="18.75" customHeight="1">
       <c r="A183" s="18" t="s">
+        <v>5853</v>
+      </c>
+      <c r="B183" s="19"/>
+      <c r="C183" s="20" t="s">
+        <v>5854</v>
+      </c>
+      <c r="D183" s="19"/>
+      <c r="E183" s="20" t="s">
+        <v>5855</v>
+      </c>
+      <c r="F183" s="19"/>
+      <c r="G183" s="20" t="s">
         <v>5856</v>
       </c>
-      <c r="B183" s="19"/>
-      <c r="C183" s="18" t="s">
-        <v>5857</v>
-      </c>
-      <c r="D183" s="19"/>
-      <c r="E183" s="10"/>
-      <c r="F183" s="10"/>
-      <c r="G183" s="10"/>
-      <c r="H183" s="10"/>
+      <c r="H183" s="19"/>
       <c r="I183" s="10"/>
       <c r="J183" s="10"/>
       <c r="K183" s="10"/>
@@ -57874,14 +57907,18 @@
         <v>5078</v>
       </c>
       <c r="B184" s="22"/>
-      <c r="C184" s="23" t="s">
+      <c r="C184" s="10" t="s">
+        <v>5857</v>
+      </c>
+      <c r="D184" s="22"/>
+      <c r="E184" s="10" t="s">
+        <v>5669</v>
+      </c>
+      <c r="F184" s="22"/>
+      <c r="G184" s="10" t="s">
         <v>5858</v>
       </c>
-      <c r="D184" s="22"/>
-      <c r="E184" s="10"/>
-      <c r="F184" s="10"/>
-      <c r="G184" s="10"/>
-      <c r="H184" s="10"/>
+      <c r="H184" s="22"/>
       <c r="I184" s="10"/>
       <c r="J184" s="10"/>
       <c r="K184" s="10"/>
@@ -57903,10 +57940,14 @@
         <v>5859</v>
       </c>
       <c r="D185" s="22"/>
-      <c r="E185" s="10"/>
-      <c r="F185" s="10"/>
-      <c r="G185" s="10"/>
-      <c r="H185" s="10"/>
+      <c r="E185" s="23" t="s">
+        <v>5675</v>
+      </c>
+      <c r="F185" s="22"/>
+      <c r="G185" s="23" t="s">
+        <v>5860</v>
+      </c>
+      <c r="H185" s="22"/>
       <c r="I185" s="10"/>
       <c r="J185" s="10"/>
       <c r="K185" s="10"/>
@@ -57925,13 +57966,17 @@
       </c>
       <c r="B186" s="22"/>
       <c r="C186" s="23" t="s">
-        <v>5860</v>
+        <v>5861</v>
       </c>
       <c r="D186" s="22"/>
-      <c r="E186" s="10"/>
-      <c r="F186" s="10"/>
-      <c r="G186" s="10"/>
-      <c r="H186" s="10"/>
+      <c r="E186" s="23" t="s">
+        <v>5681</v>
+      </c>
+      <c r="F186" s="22"/>
+      <c r="G186" s="23" t="s">
+        <v>5862</v>
+      </c>
+      <c r="H186" s="22"/>
       <c r="I186" s="10"/>
       <c r="J186" s="10"/>
       <c r="K186" s="10"/>
@@ -57955,10 +58000,18 @@
       <c r="D187" s="24" t="s">
         <v>5098</v>
       </c>
-      <c r="E187" s="10"/>
-      <c r="F187" s="10"/>
-      <c r="G187" s="10"/>
-      <c r="H187" s="10"/>
+      <c r="E187" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="F187" s="24" t="s">
+        <v>5098</v>
+      </c>
+      <c r="G187" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="H187" s="24" t="s">
+        <v>5098</v>
+      </c>
       <c r="I187" s="10"/>
       <c r="J187" s="10"/>
       <c r="K187" s="10"/>
@@ -57979,15 +58032,23 @@
         <v>5099</v>
       </c>
       <c r="C188" s="23" t="s">
-        <v>5861</v>
+        <v>5863</v>
       </c>
       <c r="D188" s="25" t="s">
-        <v>5862</v>
-      </c>
-      <c r="E188" s="10"/>
-      <c r="F188" s="10"/>
-      <c r="G188" s="10"/>
-      <c r="H188" s="10"/>
+        <v>5864</v>
+      </c>
+      <c r="E188" s="23" t="s">
+        <v>5690</v>
+      </c>
+      <c r="F188" s="25" t="s">
+        <v>5691</v>
+      </c>
+      <c r="G188" s="23" t="s">
+        <v>5865</v>
+      </c>
+      <c r="H188" s="25" t="s">
+        <v>5866</v>
+      </c>
       <c r="I188" s="10"/>
       <c r="J188" s="10"/>
       <c r="K188" s="10"/>
@@ -58006,15 +58067,23 @@
         <v>4401</v>
       </c>
       <c r="C189" s="23" t="s">
-        <v>5863</v>
+        <v>5867</v>
       </c>
       <c r="D189" s="25" t="s">
-        <v>5864</v>
-      </c>
-      <c r="E189" s="10"/>
-      <c r="F189" s="10"/>
-      <c r="G189" s="10"/>
-      <c r="H189" s="10"/>
+        <v>5868</v>
+      </c>
+      <c r="E189" s="23" t="s">
+        <v>5701</v>
+      </c>
+      <c r="F189" s="25" t="s">
+        <v>5702</v>
+      </c>
+      <c r="G189" s="23" t="s">
+        <v>5869</v>
+      </c>
+      <c r="H189" s="25" t="s">
+        <v>5870</v>
+      </c>
       <c r="I189" s="10"/>
       <c r="J189" s="10"/>
       <c r="K189" s="10"/>
@@ -58033,15 +58102,23 @@
         <v>5114</v>
       </c>
       <c r="C190" s="23" t="s">
-        <v>5863</v>
+        <v>5867</v>
       </c>
       <c r="D190" s="25" t="s">
-        <v>5862</v>
-      </c>
-      <c r="E190" s="10"/>
-      <c r="F190" s="10"/>
-      <c r="G190" s="10"/>
-      <c r="H190" s="10"/>
+        <v>5864</v>
+      </c>
+      <c r="E190" s="23" t="s">
+        <v>5701</v>
+      </c>
+      <c r="F190" s="25" t="s">
+        <v>5691</v>
+      </c>
+      <c r="G190" s="23" t="s">
+        <v>5869</v>
+      </c>
+      <c r="H190" s="25" t="s">
+        <v>5866</v>
+      </c>
       <c r="I190" s="10"/>
       <c r="J190" s="10"/>
       <c r="K190" s="10"/>
@@ -58055,22 +58132,30 @@
       <c r="S190" s="10"/>
     </row>
     <row r="191" ht="18.75" customHeight="1">
-      <c r="A191" s="8" t="s">
+      <c r="A191" s="21" t="s">
         <v>4886</v>
       </c>
       <c r="B191" s="24" t="s">
         <v>4230</v>
       </c>
       <c r="C191" s="23" t="s">
-        <v>5865</v>
+        <v>5871</v>
       </c>
       <c r="D191" s="25" t="s">
-        <v>5866</v>
-      </c>
-      <c r="E191" s="10"/>
-      <c r="F191" s="10"/>
-      <c r="G191" s="10"/>
-      <c r="H191" s="10"/>
+        <v>5872</v>
+      </c>
+      <c r="E191" s="23" t="s">
+        <v>5713</v>
+      </c>
+      <c r="F191" s="25" t="s">
+        <v>5714</v>
+      </c>
+      <c r="G191" s="23" t="s">
+        <v>5873</v>
+      </c>
+      <c r="H191" s="25" t="s">
+        <v>5874</v>
+      </c>
       <c r="I191" s="10"/>
       <c r="J191" s="10"/>
       <c r="K191" s="10"/>
@@ -58084,19 +58169,28 @@
       <c r="S191" s="10"/>
     </row>
     <row r="192" ht="18.75" customHeight="1">
+      <c r="A192" s="26"/>
       <c r="B192" s="24" t="s">
         <v>4351</v>
       </c>
       <c r="C192" s="23" t="s">
-        <v>5867</v>
+        <v>5875</v>
       </c>
       <c r="D192" s="25" t="s">
-        <v>5868</v>
-      </c>
-      <c r="E192" s="10"/>
-      <c r="F192" s="10"/>
-      <c r="G192" s="10"/>
-      <c r="H192" s="10"/>
+        <v>5876</v>
+      </c>
+      <c r="E192" s="23" t="s">
+        <v>5725</v>
+      </c>
+      <c r="F192" s="10" t="s">
+        <v>5726</v>
+      </c>
+      <c r="G192" s="23" t="s">
+        <v>5877</v>
+      </c>
+      <c r="H192" s="25" t="s">
+        <v>5878</v>
+      </c>
       <c r="I192" s="10"/>
       <c r="J192" s="10"/>
       <c r="K192" s="10"/>
@@ -58110,19 +58204,28 @@
       <c r="S192" s="10"/>
     </row>
     <row r="193" ht="18.75" customHeight="1">
-      <c r="B193" s="24" t="s">
+      <c r="A193" s="31"/>
+      <c r="B193" s="32" t="s">
         <v>5139</v>
       </c>
-      <c r="C193" s="23" t="s">
-        <v>5869</v>
-      </c>
-      <c r="D193" s="25" t="s">
-        <v>5870</v>
-      </c>
-      <c r="E193" s="10"/>
-      <c r="F193" s="10"/>
-      <c r="G193" s="10"/>
-      <c r="H193" s="10"/>
+      <c r="C193" s="36" t="s">
+        <v>5879</v>
+      </c>
+      <c r="D193" s="28" t="s">
+        <v>5880</v>
+      </c>
+      <c r="E193" s="36" t="s">
+        <v>5737</v>
+      </c>
+      <c r="F193" s="28" t="s">
+        <v>5738</v>
+      </c>
+      <c r="G193" s="36" t="s">
+        <v>5881</v>
+      </c>
+      <c r="H193" s="28" t="s">
+        <v>5882</v>
+      </c>
       <c r="I193" s="10"/>
       <c r="J193" s="10"/>
       <c r="K193" s="10"/>
@@ -58136,16 +58239,10 @@
       <c r="S193" s="10"/>
     </row>
     <row r="194" ht="18.75" customHeight="1">
-      <c r="A194" s="21" t="s">
-        <v>5150</v>
-      </c>
-      <c r="B194" s="22"/>
-      <c r="C194" s="8" t="s">
-        <v>5097</v>
-      </c>
-      <c r="D194" s="24" t="s">
-        <v>5098</v>
-      </c>
+      <c r="A194" s="10"/>
+      <c r="B194" s="10"/>
+      <c r="C194" s="10"/>
+      <c r="D194" s="10"/>
       <c r="E194" s="10"/>
       <c r="F194" s="10"/>
       <c r="G194" s="10"/>
@@ -58163,18 +58260,14 @@
       <c r="S194" s="10"/>
     </row>
     <row r="195" ht="18.75" customHeight="1">
-      <c r="A195" s="21" t="s">
-        <v>4862</v>
-      </c>
-      <c r="B195" s="8" t="s">
-        <v>5099</v>
-      </c>
-      <c r="C195" s="23" t="s">
-        <v>5871</v>
-      </c>
-      <c r="D195" s="25" t="s">
-        <v>5872</v>
-      </c>
+      <c r="A195" s="18" t="s">
+        <v>5883</v>
+      </c>
+      <c r="B195" s="19"/>
+      <c r="C195" s="18" t="s">
+        <v>5884</v>
+      </c>
+      <c r="D195" s="19"/>
       <c r="E195" s="10"/>
       <c r="F195" s="10"/>
       <c r="G195" s="10"/>
@@ -58192,11 +58285,13 @@
       <c r="S195" s="10"/>
     </row>
     <row r="196" ht="18.75" customHeight="1">
-      <c r="A196" s="26"/>
-      <c r="B196" s="8" t="s">
-        <v>4401</v>
-      </c>
-      <c r="C196" s="26"/>
+      <c r="A196" s="21" t="s">
+        <v>5078</v>
+      </c>
+      <c r="B196" s="22"/>
+      <c r="C196" s="23" t="s">
+        <v>5885</v>
+      </c>
       <c r="D196" s="22"/>
       <c r="E196" s="10"/>
       <c r="F196" s="10"/>
@@ -58215,11 +58310,13 @@
       <c r="S196" s="10"/>
     </row>
     <row r="197" ht="18.75" customHeight="1">
-      <c r="A197" s="26"/>
-      <c r="B197" s="24" t="s">
-        <v>5114</v>
-      </c>
-      <c r="C197" s="26"/>
+      <c r="A197" s="21" t="s">
+        <v>5084</v>
+      </c>
+      <c r="B197" s="22"/>
+      <c r="C197" s="23" t="s">
+        <v>5886</v>
+      </c>
       <c r="D197" s="22"/>
       <c r="E197" s="10"/>
       <c r="F197" s="10"/>
@@ -58239,17 +58336,13 @@
     </row>
     <row r="198" ht="18.75" customHeight="1">
       <c r="A198" s="21" t="s">
-        <v>4886</v>
-      </c>
-      <c r="B198" s="24" t="s">
-        <v>4230</v>
-      </c>
+        <v>5090</v>
+      </c>
+      <c r="B198" s="22"/>
       <c r="C198" s="23" t="s">
-        <v>5873</v>
-      </c>
-      <c r="D198" s="25" t="s">
-        <v>5874</v>
-      </c>
+        <v>5887</v>
+      </c>
+      <c r="D198" s="22"/>
       <c r="E198" s="10"/>
       <c r="F198" s="10"/>
       <c r="G198" s="10"/>
@@ -58267,15 +58360,15 @@
       <c r="S198" s="10"/>
     </row>
     <row r="199" ht="18.75" customHeight="1">
-      <c r="A199" s="26"/>
-      <c r="B199" s="24" t="s">
-        <v>4351</v>
-      </c>
-      <c r="C199" s="23" t="s">
-        <v>5875</v>
-      </c>
-      <c r="D199" s="25" t="s">
-        <v>5876</v>
+      <c r="A199" s="21" t="s">
+        <v>5096</v>
+      </c>
+      <c r="B199" s="22"/>
+      <c r="C199" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="D199" s="24" t="s">
+        <v>5098</v>
       </c>
       <c r="E199" s="10"/>
       <c r="F199" s="10"/>
@@ -58294,12 +58387,18 @@
       <c r="S199" s="10"/>
     </row>
     <row r="200" ht="18.75" customHeight="1">
-      <c r="A200" s="31"/>
-      <c r="B200" s="32" t="s">
-        <v>5139</v>
-      </c>
-      <c r="C200" s="31"/>
-      <c r="D200" s="34"/>
+      <c r="A200" s="21" t="s">
+        <v>4862</v>
+      </c>
+      <c r="B200" s="24" t="s">
+        <v>5099</v>
+      </c>
+      <c r="C200" s="23" t="s">
+        <v>5888</v>
+      </c>
+      <c r="D200" s="25" t="s">
+        <v>5889</v>
+      </c>
       <c r="E200" s="10"/>
       <c r="F200" s="10"/>
       <c r="G200" s="10"/>
@@ -58317,10 +58416,16 @@
       <c r="S200" s="10"/>
     </row>
     <row r="201" ht="18.75" customHeight="1">
-      <c r="A201" s="10"/>
-      <c r="B201" s="10"/>
-      <c r="C201" s="10"/>
-      <c r="D201" s="10"/>
+      <c r="A201" s="26"/>
+      <c r="B201" s="24" t="s">
+        <v>4401</v>
+      </c>
+      <c r="C201" s="23" t="s">
+        <v>5890</v>
+      </c>
+      <c r="D201" s="25" t="s">
+        <v>5891</v>
+      </c>
       <c r="E201" s="10"/>
       <c r="F201" s="10"/>
       <c r="G201" s="10"/>
@@ -58338,14 +58443,16 @@
       <c r="S201" s="10"/>
     </row>
     <row r="202" ht="18.75" customHeight="1">
-      <c r="A202" s="18" t="s">
-        <v>5877</v>
-      </c>
-      <c r="B202" s="19"/>
-      <c r="C202" s="18" t="s">
-        <v>5878</v>
-      </c>
-      <c r="D202" s="19"/>
+      <c r="A202" s="26"/>
+      <c r="B202" s="24" t="s">
+        <v>5114</v>
+      </c>
+      <c r="C202" s="23" t="s">
+        <v>5890</v>
+      </c>
+      <c r="D202" s="25" t="s">
+        <v>5889</v>
+      </c>
       <c r="E202" s="10"/>
       <c r="F202" s="10"/>
       <c r="G202" s="10"/>
@@ -58363,14 +58470,18 @@
       <c r="S202" s="10"/>
     </row>
     <row r="203" ht="18.75" customHeight="1">
-      <c r="A203" s="21" t="s">
-        <v>5078</v>
-      </c>
-      <c r="B203" s="22"/>
+      <c r="A203" s="8" t="s">
+        <v>4886</v>
+      </c>
+      <c r="B203" s="24" t="s">
+        <v>4230</v>
+      </c>
       <c r="C203" s="23" t="s">
-        <v>5879</v>
-      </c>
-      <c r="D203" s="22"/>
+        <v>5892</v>
+      </c>
+      <c r="D203" s="25" t="s">
+        <v>5893</v>
+      </c>
       <c r="E203" s="10"/>
       <c r="F203" s="10"/>
       <c r="G203" s="10"/>
@@ -58388,14 +58499,15 @@
       <c r="S203" s="10"/>
     </row>
     <row r="204" ht="18.75" customHeight="1">
-      <c r="A204" s="21" t="s">
-        <v>5084</v>
-      </c>
-      <c r="B204" s="22"/>
+      <c r="B204" s="24" t="s">
+        <v>4351</v>
+      </c>
       <c r="C204" s="23" t="s">
-        <v>5880</v>
-      </c>
-      <c r="D204" s="22"/>
+        <v>5894</v>
+      </c>
+      <c r="D204" s="25" t="s">
+        <v>5895</v>
+      </c>
       <c r="E204" s="10"/>
       <c r="F204" s="10"/>
       <c r="G204" s="10"/>
@@ -58413,14 +58525,15 @@
       <c r="S204" s="10"/>
     </row>
     <row r="205" ht="18.75" customHeight="1">
-      <c r="A205" s="21" t="s">
-        <v>5090</v>
-      </c>
-      <c r="B205" s="22"/>
+      <c r="B205" s="24" t="s">
+        <v>5139</v>
+      </c>
       <c r="C205" s="23" t="s">
-        <v>5881</v>
-      </c>
-      <c r="D205" s="22"/>
+        <v>5896</v>
+      </c>
+      <c r="D205" s="25" t="s">
+        <v>5897</v>
+      </c>
       <c r="E205" s="10"/>
       <c r="F205" s="10"/>
       <c r="G205" s="10"/>
@@ -58439,10 +58552,10 @@
     </row>
     <row r="206" ht="18.75" customHeight="1">
       <c r="A206" s="21" t="s">
-        <v>5096</v>
+        <v>5150</v>
       </c>
       <c r="B206" s="22"/>
-      <c r="C206" s="21" t="s">
+      <c r="C206" s="8" t="s">
         <v>5097</v>
       </c>
       <c r="D206" s="24" t="s">
@@ -58468,14 +58581,14 @@
       <c r="A207" s="21" t="s">
         <v>4862</v>
       </c>
-      <c r="B207" s="24" t="s">
+      <c r="B207" s="8" t="s">
         <v>5099</v>
       </c>
       <c r="C207" s="23" t="s">
-        <v>5882</v>
+        <v>5898</v>
       </c>
       <c r="D207" s="25" t="s">
-        <v>5883</v>
+        <v>5899</v>
       </c>
       <c r="E207" s="10"/>
       <c r="F207" s="10"/>
@@ -58495,15 +58608,11 @@
     </row>
     <row r="208" ht="18.75" customHeight="1">
       <c r="A208" s="26"/>
-      <c r="B208" s="24" t="s">
+      <c r="B208" s="8" t="s">
         <v>4401</v>
       </c>
-      <c r="C208" s="23" t="s">
-        <v>5884</v>
-      </c>
-      <c r="D208" s="25" t="s">
-        <v>5885</v>
-      </c>
+      <c r="C208" s="26"/>
+      <c r="D208" s="22"/>
       <c r="E208" s="10"/>
       <c r="F208" s="10"/>
       <c r="G208" s="10"/>
@@ -58525,12 +58634,8 @@
       <c r="B209" s="24" t="s">
         <v>5114</v>
       </c>
-      <c r="C209" s="23" t="s">
-        <v>5884</v>
-      </c>
-      <c r="D209" s="25" t="s">
-        <v>5883</v>
-      </c>
+      <c r="C209" s="26"/>
+      <c r="D209" s="22"/>
       <c r="E209" s="10"/>
       <c r="F209" s="10"/>
       <c r="G209" s="10"/>
@@ -58548,17 +58653,17 @@
       <c r="S209" s="10"/>
     </row>
     <row r="210" ht="18.75" customHeight="1">
-      <c r="A210" s="8" t="s">
+      <c r="A210" s="21" t="s">
         <v>4886</v>
       </c>
       <c r="B210" s="24" t="s">
         <v>4230</v>
       </c>
       <c r="C210" s="23" t="s">
-        <v>5886</v>
+        <v>5900</v>
       </c>
       <c r="D210" s="25" t="s">
-        <v>5887</v>
+        <v>5901</v>
       </c>
       <c r="E210" s="10"/>
       <c r="F210" s="10"/>
@@ -58577,14 +58682,15 @@
       <c r="S210" s="10"/>
     </row>
     <row r="211" ht="18.75" customHeight="1">
+      <c r="A211" s="26"/>
       <c r="B211" s="24" t="s">
         <v>4351</v>
       </c>
       <c r="C211" s="23" t="s">
-        <v>5888</v>
+        <v>5902</v>
       </c>
       <c r="D211" s="25" t="s">
-        <v>5889</v>
+        <v>5903</v>
       </c>
       <c r="E211" s="10"/>
       <c r="F211" s="10"/>
@@ -58603,15 +58709,12 @@
       <c r="S211" s="10"/>
     </row>
     <row r="212" ht="18.75" customHeight="1">
-      <c r="B212" s="24" t="s">
+      <c r="A212" s="31"/>
+      <c r="B212" s="32" t="s">
         <v>5139</v>
       </c>
-      <c r="C212" s="23" t="s">
-        <v>5890</v>
-      </c>
-      <c r="D212" s="25" t="s">
-        <v>5891</v>
-      </c>
+      <c r="C212" s="31"/>
+      <c r="D212" s="34"/>
       <c r="E212" s="10"/>
       <c r="F212" s="10"/>
       <c r="G212" s="10"/>
@@ -58629,16 +58732,10 @@
       <c r="S212" s="10"/>
     </row>
     <row r="213" ht="18.75" customHeight="1">
-      <c r="A213" s="21" t="s">
-        <v>5150</v>
-      </c>
-      <c r="B213" s="22"/>
-      <c r="C213" s="8" t="s">
-        <v>5097</v>
-      </c>
-      <c r="D213" s="24" t="s">
-        <v>5098</v>
-      </c>
+      <c r="A213" s="10"/>
+      <c r="B213" s="10"/>
+      <c r="C213" s="10"/>
+      <c r="D213" s="10"/>
       <c r="E213" s="10"/>
       <c r="F213" s="10"/>
       <c r="G213" s="10"/>
@@ -58656,18 +58753,14 @@
       <c r="S213" s="10"/>
     </row>
     <row r="214" ht="18.75" customHeight="1">
-      <c r="A214" s="21" t="s">
-        <v>4862</v>
-      </c>
-      <c r="B214" s="8" t="s">
-        <v>5099</v>
-      </c>
-      <c r="C214" s="23" t="s">
-        <v>5892</v>
-      </c>
-      <c r="D214" s="25" t="s">
-        <v>5893</v>
-      </c>
+      <c r="A214" s="18" t="s">
+        <v>5904</v>
+      </c>
+      <c r="B214" s="19"/>
+      <c r="C214" s="18" t="s">
+        <v>5905</v>
+      </c>
+      <c r="D214" s="19"/>
       <c r="E214" s="10"/>
       <c r="F214" s="10"/>
       <c r="G214" s="10"/>
@@ -58685,11 +58778,13 @@
       <c r="S214" s="10"/>
     </row>
     <row r="215" ht="18.75" customHeight="1">
-      <c r="A215" s="26"/>
-      <c r="B215" s="8" t="s">
-        <v>4401</v>
-      </c>
-      <c r="C215" s="26"/>
+      <c r="A215" s="21" t="s">
+        <v>5078</v>
+      </c>
+      <c r="B215" s="22"/>
+      <c r="C215" s="23" t="s">
+        <v>5906</v>
+      </c>
       <c r="D215" s="22"/>
       <c r="E215" s="10"/>
       <c r="F215" s="10"/>
@@ -58708,11 +58803,13 @@
       <c r="S215" s="10"/>
     </row>
     <row r="216" ht="18.75" customHeight="1">
-      <c r="A216" s="26"/>
-      <c r="B216" s="24" t="s">
-        <v>5114</v>
-      </c>
-      <c r="C216" s="26"/>
+      <c r="A216" s="21" t="s">
+        <v>5084</v>
+      </c>
+      <c r="B216" s="22"/>
+      <c r="C216" s="23" t="s">
+        <v>5907</v>
+      </c>
       <c r="D216" s="22"/>
       <c r="E216" s="10"/>
       <c r="F216" s="10"/>
@@ -58732,17 +58829,13 @@
     </row>
     <row r="217" ht="18.75" customHeight="1">
       <c r="A217" s="21" t="s">
-        <v>4886</v>
-      </c>
-      <c r="B217" s="24" t="s">
-        <v>4230</v>
-      </c>
+        <v>5090</v>
+      </c>
+      <c r="B217" s="22"/>
       <c r="C217" s="23" t="s">
-        <v>5894</v>
-      </c>
-      <c r="D217" s="25" t="s">
-        <v>5895</v>
-      </c>
+        <v>5908</v>
+      </c>
+      <c r="D217" s="22"/>
       <c r="E217" s="10"/>
       <c r="F217" s="10"/>
       <c r="G217" s="10"/>
@@ -58760,15 +58853,15 @@
       <c r="S217" s="10"/>
     </row>
     <row r="218" ht="18.75" customHeight="1">
-      <c r="A218" s="26"/>
-      <c r="B218" s="24" t="s">
-        <v>4351</v>
-      </c>
-      <c r="C218" s="23" t="s">
-        <v>5896</v>
-      </c>
-      <c r="D218" s="25" t="s">
-        <v>5897</v>
+      <c r="A218" s="21" t="s">
+        <v>5096</v>
+      </c>
+      <c r="B218" s="22"/>
+      <c r="C218" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="D218" s="24" t="s">
+        <v>5098</v>
       </c>
       <c r="E218" s="10"/>
       <c r="F218" s="10"/>
@@ -58787,12 +58880,18 @@
       <c r="S218" s="10"/>
     </row>
     <row r="219" ht="18.75" customHeight="1">
-      <c r="A219" s="31"/>
-      <c r="B219" s="32" t="s">
-        <v>5139</v>
-      </c>
-      <c r="C219" s="31"/>
-      <c r="D219" s="34"/>
+      <c r="A219" s="21" t="s">
+        <v>4862</v>
+      </c>
+      <c r="B219" s="24" t="s">
+        <v>5099</v>
+      </c>
+      <c r="C219" s="23" t="s">
+        <v>5909</v>
+      </c>
+      <c r="D219" s="25" t="s">
+        <v>5910</v>
+      </c>
       <c r="E219" s="10"/>
       <c r="F219" s="10"/>
       <c r="G219" s="10"/>
@@ -58810,10 +58909,16 @@
       <c r="S219" s="10"/>
     </row>
     <row r="220" ht="18.75" customHeight="1">
-      <c r="A220" s="10"/>
-      <c r="B220" s="10"/>
-      <c r="C220" s="10"/>
-      <c r="D220" s="10"/>
+      <c r="A220" s="26"/>
+      <c r="B220" s="24" t="s">
+        <v>4401</v>
+      </c>
+      <c r="C220" s="23" t="s">
+        <v>5911</v>
+      </c>
+      <c r="D220" s="25" t="s">
+        <v>5912</v>
+      </c>
       <c r="E220" s="10"/>
       <c r="F220" s="10"/>
       <c r="G220" s="10"/>
@@ -58831,14 +58936,16 @@
       <c r="S220" s="10"/>
     </row>
     <row r="221" ht="18.75" customHeight="1">
-      <c r="A221" s="18" t="s">
-        <v>5898</v>
-      </c>
-      <c r="B221" s="19"/>
-      <c r="C221" s="18" t="s">
-        <v>5899</v>
-      </c>
-      <c r="D221" s="19"/>
+      <c r="A221" s="26"/>
+      <c r="B221" s="24" t="s">
+        <v>5114</v>
+      </c>
+      <c r="C221" s="23" t="s">
+        <v>5911</v>
+      </c>
+      <c r="D221" s="25" t="s">
+        <v>5910</v>
+      </c>
       <c r="E221" s="10"/>
       <c r="F221" s="10"/>
       <c r="G221" s="10"/>
@@ -58856,14 +58963,18 @@
       <c r="S221" s="10"/>
     </row>
     <row r="222" ht="18.75" customHeight="1">
-      <c r="A222" s="21" t="s">
-        <v>5078</v>
-      </c>
-      <c r="B222" s="22"/>
+      <c r="A222" s="8" t="s">
+        <v>4886</v>
+      </c>
+      <c r="B222" s="24" t="s">
+        <v>4230</v>
+      </c>
       <c r="C222" s="23" t="s">
-        <v>5900</v>
-      </c>
-      <c r="D222" s="22"/>
+        <v>5913</v>
+      </c>
+      <c r="D222" s="25" t="s">
+        <v>5914</v>
+      </c>
       <c r="E222" s="10"/>
       <c r="F222" s="10"/>
       <c r="G222" s="10"/>
@@ -58881,14 +58992,15 @@
       <c r="S222" s="10"/>
     </row>
     <row r="223" ht="18.75" customHeight="1">
-      <c r="A223" s="21" t="s">
-        <v>5084</v>
-      </c>
-      <c r="B223" s="22"/>
+      <c r="B223" s="24" t="s">
+        <v>4351</v>
+      </c>
       <c r="C223" s="23" t="s">
-        <v>5901</v>
-      </c>
-      <c r="D223" s="22"/>
+        <v>5915</v>
+      </c>
+      <c r="D223" s="25" t="s">
+        <v>5916</v>
+      </c>
       <c r="E223" s="10"/>
       <c r="F223" s="10"/>
       <c r="G223" s="10"/>
@@ -58906,14 +59018,15 @@
       <c r="S223" s="10"/>
     </row>
     <row r="224" ht="18.75" customHeight="1">
-      <c r="A224" s="21" t="s">
-        <v>5090</v>
-      </c>
-      <c r="B224" s="22"/>
+      <c r="B224" s="24" t="s">
+        <v>5139</v>
+      </c>
       <c r="C224" s="23" t="s">
-        <v>5902</v>
-      </c>
-      <c r="D224" s="22"/>
+        <v>5917</v>
+      </c>
+      <c r="D224" s="25" t="s">
+        <v>5918</v>
+      </c>
       <c r="E224" s="10"/>
       <c r="F224" s="10"/>
       <c r="G224" s="10"/>
@@ -58932,10 +59045,10 @@
     </row>
     <row r="225" ht="18.75" customHeight="1">
       <c r="A225" s="21" t="s">
-        <v>5096</v>
+        <v>5150</v>
       </c>
       <c r="B225" s="22"/>
-      <c r="C225" s="21" t="s">
+      <c r="C225" s="8" t="s">
         <v>5097</v>
       </c>
       <c r="D225" s="24" t="s">
@@ -58961,14 +59074,14 @@
       <c r="A226" s="21" t="s">
         <v>4862</v>
       </c>
-      <c r="B226" s="24" t="s">
+      <c r="B226" s="8" t="s">
         <v>5099</v>
       </c>
       <c r="C226" s="23" t="s">
-        <v>5903</v>
+        <v>5919</v>
       </c>
       <c r="D226" s="25" t="s">
-        <v>5904</v>
+        <v>5920</v>
       </c>
       <c r="E226" s="10"/>
       <c r="F226" s="10"/>
@@ -58988,15 +59101,11 @@
     </row>
     <row r="227" ht="18.75" customHeight="1">
       <c r="A227" s="26"/>
-      <c r="B227" s="24" t="s">
+      <c r="B227" s="8" t="s">
         <v>4401</v>
       </c>
-      <c r="C227" s="23" t="s">
-        <v>5905</v>
-      </c>
-      <c r="D227" s="25" t="s">
-        <v>5906</v>
-      </c>
+      <c r="C227" s="26"/>
+      <c r="D227" s="22"/>
       <c r="E227" s="10"/>
       <c r="F227" s="10"/>
       <c r="G227" s="10"/>
@@ -59018,12 +59127,8 @@
       <c r="B228" s="24" t="s">
         <v>5114</v>
       </c>
-      <c r="C228" s="23" t="s">
-        <v>5905</v>
-      </c>
-      <c r="D228" s="25" t="s">
-        <v>5907</v>
-      </c>
+      <c r="C228" s="26"/>
+      <c r="D228" s="22"/>
       <c r="E228" s="10"/>
       <c r="F228" s="10"/>
       <c r="G228" s="10"/>
@@ -59048,10 +59153,10 @@
         <v>4230</v>
       </c>
       <c r="C229" s="23" t="s">
-        <v>5908</v>
+        <v>5921</v>
       </c>
       <c r="D229" s="25" t="s">
-        <v>5909</v>
+        <v>5922</v>
       </c>
       <c r="E229" s="10"/>
       <c r="F229" s="10"/>
@@ -59075,10 +59180,10 @@
         <v>4351</v>
       </c>
       <c r="C230" s="23" t="s">
-        <v>5910</v>
+        <v>5923</v>
       </c>
       <c r="D230" s="25" t="s">
-        <v>5911</v>
+        <v>5924</v>
       </c>
       <c r="E230" s="10"/>
       <c r="F230" s="10"/>
@@ -59101,12 +59206,8 @@
       <c r="B231" s="32" t="s">
         <v>5139</v>
       </c>
-      <c r="C231" s="36" t="s">
-        <v>5912</v>
-      </c>
-      <c r="D231" s="28" t="s">
-        <v>5913</v>
-      </c>
+      <c r="C231" s="31"/>
+      <c r="D231" s="34"/>
       <c r="E231" s="10"/>
       <c r="F231" s="10"/>
       <c r="G231" s="10"/>
@@ -59146,11 +59247,11 @@
     </row>
     <row r="233" ht="18.75" customHeight="1">
       <c r="A233" s="18" t="s">
-        <v>5914</v>
+        <v>5925</v>
       </c>
       <c r="B233" s="19"/>
       <c r="C233" s="18" t="s">
-        <v>5915</v>
+        <v>5926</v>
       </c>
       <c r="D233" s="19"/>
       <c r="E233" s="10"/>
@@ -59175,7 +59276,7 @@
       </c>
       <c r="B234" s="22"/>
       <c r="C234" s="23" t="s">
-        <v>5916</v>
+        <v>5927</v>
       </c>
       <c r="D234" s="22"/>
       <c r="E234" s="10"/>
@@ -59200,7 +59301,7 @@
       </c>
       <c r="B235" s="22"/>
       <c r="C235" s="23" t="s">
-        <v>5917</v>
+        <v>5928</v>
       </c>
       <c r="D235" s="22"/>
       <c r="E235" s="10"/>
@@ -59225,7 +59326,7 @@
       </c>
       <c r="B236" s="22"/>
       <c r="C236" s="23" t="s">
-        <v>5918</v>
+        <v>5929</v>
       </c>
       <c r="D236" s="22"/>
       <c r="E236" s="10"/>
@@ -59279,10 +59380,10 @@
         <v>5099</v>
       </c>
       <c r="C238" s="23" t="s">
-        <v>5919</v>
+        <v>5930</v>
       </c>
       <c r="D238" s="25" t="s">
-        <v>5920</v>
+        <v>5931</v>
       </c>
       <c r="E238" s="10"/>
       <c r="F238" s="10"/>
@@ -59306,10 +59407,10 @@
         <v>4401</v>
       </c>
       <c r="C239" s="23" t="s">
-        <v>5919</v>
+        <v>5932</v>
       </c>
       <c r="D239" s="25" t="s">
-        <v>5921</v>
+        <v>5933</v>
       </c>
       <c r="E239" s="10"/>
       <c r="F239" s="10"/>
@@ -59333,10 +59434,10 @@
         <v>5114</v>
       </c>
       <c r="C240" s="23" t="s">
-        <v>5919</v>
+        <v>5932</v>
       </c>
       <c r="D240" s="25" t="s">
-        <v>5922</v>
+        <v>5934</v>
       </c>
       <c r="E240" s="10"/>
       <c r="F240" s="10"/>
@@ -59362,10 +59463,10 @@
         <v>4230</v>
       </c>
       <c r="C241" s="23" t="s">
-        <v>5923</v>
+        <v>5935</v>
       </c>
       <c r="D241" s="25" t="s">
-        <v>5924</v>
+        <v>5936</v>
       </c>
       <c r="E241" s="10"/>
       <c r="F241" s="10"/>
@@ -59389,10 +59490,10 @@
         <v>4351</v>
       </c>
       <c r="C242" s="23" t="s">
-        <v>5925</v>
+        <v>5937</v>
       </c>
       <c r="D242" s="25" t="s">
-        <v>5926</v>
+        <v>5938</v>
       </c>
       <c r="E242" s="10"/>
       <c r="F242" s="10"/>
@@ -59416,10 +59517,10 @@
         <v>5139</v>
       </c>
       <c r="C243" s="36" t="s">
-        <v>5927</v>
+        <v>5939</v>
       </c>
       <c r="D243" s="28" t="s">
-        <v>5928</v>
+        <v>5940</v>
       </c>
       <c r="E243" s="10"/>
       <c r="F243" s="10"/>
@@ -59460,17 +59561,15 @@
     </row>
     <row r="245" ht="18.75" customHeight="1">
       <c r="A245" s="18" t="s">
-        <v>5929</v>
+        <v>5941</v>
       </c>
       <c r="B245" s="19"/>
       <c r="C245" s="18" t="s">
-        <v>5930</v>
+        <v>5942</v>
       </c>
       <c r="D245" s="19"/>
-      <c r="E245" s="18" t="s">
-        <v>5931</v>
-      </c>
-      <c r="F245" s="19"/>
+      <c r="E245" s="10"/>
+      <c r="F245" s="10"/>
       <c r="G245" s="10"/>
       <c r="H245" s="10"/>
       <c r="I245" s="10"/>
@@ -59487,21 +59586,15 @@
     </row>
     <row r="246" ht="18.75" customHeight="1">
       <c r="A246" s="21" t="s">
-        <v>5096</v>
+        <v>5078</v>
       </c>
       <c r="B246" s="22"/>
-      <c r="C246" s="21" t="s">
-        <v>5097</v>
-      </c>
-      <c r="D246" s="24" t="s">
-        <v>5098</v>
-      </c>
-      <c r="E246" s="21" t="s">
-        <v>5097</v>
-      </c>
-      <c r="F246" s="24" t="s">
-        <v>5098</v>
-      </c>
+      <c r="C246" s="23" t="s">
+        <v>5943</v>
+      </c>
+      <c r="D246" s="22"/>
+      <c r="E246" s="10"/>
+      <c r="F246" s="10"/>
       <c r="G246" s="10"/>
       <c r="H246" s="10"/>
       <c r="I246" s="10"/>
@@ -59518,23 +59611,15 @@
     </row>
     <row r="247" ht="18.75" customHeight="1">
       <c r="A247" s="21" t="s">
-        <v>4862</v>
-      </c>
-      <c r="B247" s="24" t="s">
-        <v>5099</v>
-      </c>
+        <v>5084</v>
+      </c>
+      <c r="B247" s="22"/>
       <c r="C247" s="23" t="s">
-        <v>5932</v>
-      </c>
-      <c r="D247" s="25" t="s">
-        <v>5933</v>
-      </c>
-      <c r="E247" s="23" t="s">
-        <v>5934</v>
-      </c>
-      <c r="F247" s="25" t="s">
-        <v>5935</v>
-      </c>
+        <v>5944</v>
+      </c>
+      <c r="D247" s="22"/>
+      <c r="E247" s="10"/>
+      <c r="F247" s="10"/>
       <c r="G247" s="10"/>
       <c r="H247" s="10"/>
       <c r="I247" s="10"/>
@@ -59550,22 +59635,16 @@
       <c r="S247" s="10"/>
     </row>
     <row r="248" ht="18.75" customHeight="1">
-      <c r="A248" s="26"/>
-      <c r="B248" s="24" t="s">
-        <v>4401</v>
-      </c>
+      <c r="A248" s="21" t="s">
+        <v>5090</v>
+      </c>
+      <c r="B248" s="22"/>
       <c r="C248" s="23" t="s">
-        <v>5932</v>
-      </c>
-      <c r="D248" s="25" t="s">
-        <v>5196</v>
-      </c>
-      <c r="E248" s="23" t="s">
-        <v>5752</v>
-      </c>
-      <c r="F248" s="25" t="s">
-        <v>5936</v>
-      </c>
+        <v>5945</v>
+      </c>
+      <c r="D248" s="22"/>
+      <c r="E248" s="10"/>
+      <c r="F248" s="10"/>
       <c r="G248" s="10"/>
       <c r="H248" s="10"/>
       <c r="I248" s="10"/>
@@ -59581,22 +59660,18 @@
       <c r="S248" s="10"/>
     </row>
     <row r="249" ht="18.75" customHeight="1">
-      <c r="A249" s="26"/>
-      <c r="B249" s="24" t="s">
-        <v>5114</v>
-      </c>
-      <c r="C249" s="23" t="s">
-        <v>5932</v>
-      </c>
-      <c r="D249" s="25" t="s">
-        <v>5186</v>
-      </c>
-      <c r="E249" s="23" t="s">
-        <v>5752</v>
-      </c>
-      <c r="F249" s="25" t="s">
-        <v>5937</v>
-      </c>
+      <c r="A249" s="21" t="s">
+        <v>5096</v>
+      </c>
+      <c r="B249" s="22"/>
+      <c r="C249" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="D249" s="24" t="s">
+        <v>5098</v>
+      </c>
+      <c r="E249" s="10"/>
+      <c r="F249" s="10"/>
       <c r="G249" s="10"/>
       <c r="H249" s="10"/>
       <c r="I249" s="10"/>
@@ -59613,23 +59688,19 @@
     </row>
     <row r="250" ht="18.75" customHeight="1">
       <c r="A250" s="21" t="s">
-        <v>4886</v>
+        <v>4862</v>
       </c>
       <c r="B250" s="24" t="s">
-        <v>4230</v>
+        <v>5099</v>
       </c>
       <c r="C250" s="23" t="s">
-        <v>5938</v>
+        <v>5946</v>
       </c>
       <c r="D250" s="25" t="s">
-        <v>5939</v>
-      </c>
-      <c r="E250" s="23" t="s">
-        <v>5940</v>
-      </c>
-      <c r="F250" s="25" t="s">
-        <v>5941</v>
-      </c>
+        <v>5947</v>
+      </c>
+      <c r="E250" s="10"/>
+      <c r="F250" s="10"/>
       <c r="G250" s="10"/>
       <c r="H250" s="10"/>
       <c r="I250" s="10"/>
@@ -59647,20 +59718,16 @@
     <row r="251" ht="18.75" customHeight="1">
       <c r="A251" s="26"/>
       <c r="B251" s="24" t="s">
-        <v>4351</v>
+        <v>4401</v>
       </c>
       <c r="C251" s="23" t="s">
-        <v>5942</v>
+        <v>5946</v>
       </c>
       <c r="D251" s="25" t="s">
-        <v>5943</v>
-      </c>
-      <c r="E251" s="23" t="s">
-        <v>5944</v>
-      </c>
-      <c r="F251" s="25" t="s">
-        <v>5945</v>
-      </c>
+        <v>5948</v>
+      </c>
+      <c r="E251" s="10"/>
+      <c r="F251" s="10"/>
       <c r="G251" s="10"/>
       <c r="H251" s="10"/>
       <c r="I251" s="10"/>
@@ -59676,22 +59743,18 @@
       <c r="S251" s="10"/>
     </row>
     <row r="252" ht="18.75" customHeight="1">
-      <c r="A252" s="31"/>
-      <c r="B252" s="32" t="s">
-        <v>5139</v>
-      </c>
-      <c r="C252" s="36" t="s">
-        <v>2544</v>
-      </c>
-      <c r="D252" s="28" t="s">
+      <c r="A252" s="26"/>
+      <c r="B252" s="24" t="s">
+        <v>5114</v>
+      </c>
+      <c r="C252" s="23" t="s">
         <v>5946</v>
       </c>
-      <c r="E252" s="36" t="s">
-        <v>3356</v>
-      </c>
-      <c r="F252" s="28" t="s">
-        <v>5947</v>
-      </c>
+      <c r="D252" s="25" t="s">
+        <v>5949</v>
+      </c>
+      <c r="E252" s="10"/>
+      <c r="F252" s="10"/>
       <c r="G252" s="10"/>
       <c r="H252" s="10"/>
       <c r="I252" s="10"/>
@@ -59707,6 +59770,18 @@
       <c r="S252" s="10"/>
     </row>
     <row r="253" ht="18.75" customHeight="1">
+      <c r="A253" s="21" t="s">
+        <v>4886</v>
+      </c>
+      <c r="B253" s="24" t="s">
+        <v>4230</v>
+      </c>
+      <c r="C253" s="23" t="s">
+        <v>5950</v>
+      </c>
+      <c r="D253" s="25" t="s">
+        <v>5951</v>
+      </c>
       <c r="E253" s="10"/>
       <c r="F253" s="10"/>
       <c r="G253" s="10"/>
@@ -59724,6 +59799,16 @@
       <c r="S253" s="10"/>
     </row>
     <row r="254" ht="18.75" customHeight="1">
+      <c r="A254" s="26"/>
+      <c r="B254" s="24" t="s">
+        <v>4351</v>
+      </c>
+      <c r="C254" s="23" t="s">
+        <v>5952</v>
+      </c>
+      <c r="D254" s="25" t="s">
+        <v>5953</v>
+      </c>
       <c r="E254" s="10"/>
       <c r="F254" s="10"/>
       <c r="G254" s="10"/>
@@ -59741,6 +59826,16 @@
       <c r="S254" s="10"/>
     </row>
     <row r="255" ht="18.75" customHeight="1">
+      <c r="A255" s="31"/>
+      <c r="B255" s="32" t="s">
+        <v>5139</v>
+      </c>
+      <c r="C255" s="36" t="s">
+        <v>5954</v>
+      </c>
+      <c r="D255" s="28" t="s">
+        <v>5955</v>
+      </c>
       <c r="E255" s="10"/>
       <c r="F255" s="10"/>
       <c r="G255" s="10"/>
@@ -59778,8 +59873,328 @@
       <c r="R256" s="10"/>
       <c r="S256" s="10"/>
     </row>
+    <row r="257" ht="18.75" customHeight="1">
+      <c r="A257" s="18" t="s">
+        <v>5956</v>
+      </c>
+      <c r="B257" s="19"/>
+      <c r="C257" s="18" t="s">
+        <v>5957</v>
+      </c>
+      <c r="D257" s="19"/>
+      <c r="E257" s="18" t="s">
+        <v>5958</v>
+      </c>
+      <c r="F257" s="19"/>
+      <c r="G257" s="10"/>
+      <c r="H257" s="10"/>
+      <c r="I257" s="10"/>
+      <c r="J257" s="10"/>
+      <c r="K257" s="10"/>
+      <c r="L257" s="10"/>
+      <c r="M257" s="10"/>
+      <c r="N257" s="10"/>
+      <c r="O257" s="10"/>
+      <c r="P257" s="10"/>
+      <c r="Q257" s="10"/>
+      <c r="R257" s="10"/>
+      <c r="S257" s="10"/>
+    </row>
+    <row r="258" ht="18.75" customHeight="1">
+      <c r="A258" s="21" t="s">
+        <v>5096</v>
+      </c>
+      <c r="B258" s="22"/>
+      <c r="C258" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="D258" s="24" t="s">
+        <v>5098</v>
+      </c>
+      <c r="E258" s="21" t="s">
+        <v>5097</v>
+      </c>
+      <c r="F258" s="24" t="s">
+        <v>5098</v>
+      </c>
+      <c r="G258" s="10"/>
+      <c r="H258" s="10"/>
+      <c r="I258" s="10"/>
+      <c r="J258" s="10"/>
+      <c r="K258" s="10"/>
+      <c r="L258" s="10"/>
+      <c r="M258" s="10"/>
+      <c r="N258" s="10"/>
+      <c r="O258" s="10"/>
+      <c r="P258" s="10"/>
+      <c r="Q258" s="10"/>
+      <c r="R258" s="10"/>
+      <c r="S258" s="10"/>
+    </row>
+    <row r="259" ht="18.75" customHeight="1">
+      <c r="A259" s="21" t="s">
+        <v>4862</v>
+      </c>
+      <c r="B259" s="24" t="s">
+        <v>5099</v>
+      </c>
+      <c r="C259" s="23" t="s">
+        <v>5959</v>
+      </c>
+      <c r="D259" s="25" t="s">
+        <v>5960</v>
+      </c>
+      <c r="E259" s="23" t="s">
+        <v>5961</v>
+      </c>
+      <c r="F259" s="25" t="s">
+        <v>5962</v>
+      </c>
+      <c r="G259" s="10"/>
+      <c r="H259" s="10"/>
+      <c r="I259" s="10"/>
+      <c r="J259" s="10"/>
+      <c r="K259" s="10"/>
+      <c r="L259" s="10"/>
+      <c r="M259" s="10"/>
+      <c r="N259" s="10"/>
+      <c r="O259" s="10"/>
+      <c r="P259" s="10"/>
+      <c r="Q259" s="10"/>
+      <c r="R259" s="10"/>
+      <c r="S259" s="10"/>
+    </row>
+    <row r="260" ht="18.75" customHeight="1">
+      <c r="A260" s="26"/>
+      <c r="B260" s="24" t="s">
+        <v>4401</v>
+      </c>
+      <c r="C260" s="23" t="s">
+        <v>5959</v>
+      </c>
+      <c r="D260" s="25" t="s">
+        <v>5196</v>
+      </c>
+      <c r="E260" s="23" t="s">
+        <v>5779</v>
+      </c>
+      <c r="F260" s="25" t="s">
+        <v>5963</v>
+      </c>
+      <c r="G260" s="10"/>
+      <c r="H260" s="10"/>
+      <c r="I260" s="10"/>
+      <c r="J260" s="10"/>
+      <c r="K260" s="10"/>
+      <c r="L260" s="10"/>
+      <c r="M260" s="10"/>
+      <c r="N260" s="10"/>
+      <c r="O260" s="10"/>
+      <c r="P260" s="10"/>
+      <c r="Q260" s="10"/>
+      <c r="R260" s="10"/>
+      <c r="S260" s="10"/>
+    </row>
+    <row r="261" ht="18.75" customHeight="1">
+      <c r="A261" s="26"/>
+      <c r="B261" s="24" t="s">
+        <v>5114</v>
+      </c>
+      <c r="C261" s="23" t="s">
+        <v>5959</v>
+      </c>
+      <c r="D261" s="25" t="s">
+        <v>5186</v>
+      </c>
+      <c r="E261" s="23" t="s">
+        <v>5779</v>
+      </c>
+      <c r="F261" s="25" t="s">
+        <v>5964</v>
+      </c>
+      <c r="G261" s="10"/>
+      <c r="H261" s="10"/>
+      <c r="I261" s="10"/>
+      <c r="J261" s="10"/>
+      <c r="K261" s="10"/>
+      <c r="L261" s="10"/>
+      <c r="M261" s="10"/>
+      <c r="N261" s="10"/>
+      <c r="O261" s="10"/>
+      <c r="P261" s="10"/>
+      <c r="Q261" s="10"/>
+      <c r="R261" s="10"/>
+      <c r="S261" s="10"/>
+    </row>
+    <row r="262" ht="18.75" customHeight="1">
+      <c r="A262" s="21" t="s">
+        <v>4886</v>
+      </c>
+      <c r="B262" s="24" t="s">
+        <v>4230</v>
+      </c>
+      <c r="C262" s="23" t="s">
+        <v>5965</v>
+      </c>
+      <c r="D262" s="25" t="s">
+        <v>5966</v>
+      </c>
+      <c r="E262" s="23" t="s">
+        <v>5967</v>
+      </c>
+      <c r="F262" s="25" t="s">
+        <v>5968</v>
+      </c>
+      <c r="G262" s="10"/>
+      <c r="H262" s="10"/>
+      <c r="I262" s="10"/>
+      <c r="J262" s="10"/>
+      <c r="K262" s="10"/>
+      <c r="L262" s="10"/>
+      <c r="M262" s="10"/>
+      <c r="N262" s="10"/>
+      <c r="O262" s="10"/>
+      <c r="P262" s="10"/>
+      <c r="Q262" s="10"/>
+      <c r="R262" s="10"/>
+      <c r="S262" s="10"/>
+    </row>
+    <row r="263" ht="18.75" customHeight="1">
+      <c r="A263" s="26"/>
+      <c r="B263" s="24" t="s">
+        <v>4351</v>
+      </c>
+      <c r="C263" s="23" t="s">
+        <v>5969</v>
+      </c>
+      <c r="D263" s="25" t="s">
+        <v>5970</v>
+      </c>
+      <c r="E263" s="23" t="s">
+        <v>5971</v>
+      </c>
+      <c r="F263" s="25" t="s">
+        <v>5972</v>
+      </c>
+      <c r="G263" s="10"/>
+      <c r="H263" s="10"/>
+      <c r="I263" s="10"/>
+      <c r="J263" s="10"/>
+      <c r="K263" s="10"/>
+      <c r="L263" s="10"/>
+      <c r="M263" s="10"/>
+      <c r="N263" s="10"/>
+      <c r="O263" s="10"/>
+      <c r="P263" s="10"/>
+      <c r="Q263" s="10"/>
+      <c r="R263" s="10"/>
+      <c r="S263" s="10"/>
+    </row>
+    <row r="264" ht="18.75" customHeight="1">
+      <c r="A264" s="31"/>
+      <c r="B264" s="32" t="s">
+        <v>5139</v>
+      </c>
+      <c r="C264" s="36" t="s">
+        <v>2544</v>
+      </c>
+      <c r="D264" s="28" t="s">
+        <v>5973</v>
+      </c>
+      <c r="E264" s="36" t="s">
+        <v>3356</v>
+      </c>
+      <c r="F264" s="28" t="s">
+        <v>5974</v>
+      </c>
+      <c r="G264" s="10"/>
+      <c r="H264" s="10"/>
+      <c r="I264" s="10"/>
+      <c r="J264" s="10"/>
+      <c r="K264" s="10"/>
+      <c r="L264" s="10"/>
+      <c r="M264" s="10"/>
+      <c r="N264" s="10"/>
+      <c r="O264" s="10"/>
+      <c r="P264" s="10"/>
+      <c r="Q264" s="10"/>
+      <c r="R264" s="10"/>
+      <c r="S264" s="10"/>
+    </row>
+    <row r="265" ht="18.75" customHeight="1">
+      <c r="E265" s="10"/>
+      <c r="F265" s="10"/>
+      <c r="G265" s="10"/>
+      <c r="H265" s="10"/>
+      <c r="I265" s="10"/>
+      <c r="J265" s="10"/>
+      <c r="K265" s="10"/>
+      <c r="L265" s="10"/>
+      <c r="M265" s="10"/>
+      <c r="N265" s="10"/>
+      <c r="O265" s="10"/>
+      <c r="P265" s="10"/>
+      <c r="Q265" s="10"/>
+      <c r="R265" s="10"/>
+      <c r="S265" s="10"/>
+    </row>
+    <row r="266" ht="18.75" customHeight="1">
+      <c r="E266" s="10"/>
+      <c r="F266" s="10"/>
+      <c r="G266" s="10"/>
+      <c r="H266" s="10"/>
+      <c r="I266" s="10"/>
+      <c r="J266" s="10"/>
+      <c r="K266" s="10"/>
+      <c r="L266" s="10"/>
+      <c r="M266" s="10"/>
+      <c r="N266" s="10"/>
+      <c r="O266" s="10"/>
+      <c r="P266" s="10"/>
+      <c r="Q266" s="10"/>
+      <c r="R266" s="10"/>
+      <c r="S266" s="10"/>
+    </row>
+    <row r="267" ht="18.75" customHeight="1">
+      <c r="E267" s="10"/>
+      <c r="F267" s="10"/>
+      <c r="G267" s="10"/>
+      <c r="H267" s="10"/>
+      <c r="I267" s="10"/>
+      <c r="J267" s="10"/>
+      <c r="K267" s="10"/>
+      <c r="L267" s="10"/>
+      <c r="M267" s="10"/>
+      <c r="N267" s="10"/>
+      <c r="O267" s="10"/>
+      <c r="P267" s="10"/>
+      <c r="Q267" s="10"/>
+      <c r="R267" s="10"/>
+      <c r="S267" s="10"/>
+    </row>
+    <row r="268" ht="18.75" customHeight="1">
+      <c r="A268" s="10"/>
+      <c r="B268" s="10"/>
+      <c r="C268" s="10"/>
+      <c r="D268" s="10"/>
+      <c r="E268" s="10"/>
+      <c r="F268" s="10"/>
+      <c r="G268" s="10"/>
+      <c r="H268" s="10"/>
+      <c r="I268" s="10"/>
+      <c r="J268" s="10"/>
+      <c r="K268" s="10"/>
+      <c r="L268" s="10"/>
+      <c r="M268" s="10"/>
+      <c r="N268" s="10"/>
+      <c r="O268" s="10"/>
+      <c r="P268" s="10"/>
+      <c r="Q268" s="10"/>
+      <c r="R268" s="10"/>
+      <c r="S268" s="10"/>
+    </row>
   </sheetData>
-  <mergeCells count="378">
+  <mergeCells count="386">
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="C21:D21"/>
@@ -59897,11 +60312,6 @@
     <mergeCell ref="C72:D72"/>
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="G91:H91"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="K91:L91"/>
     <mergeCell ref="J87:J88"/>
     <mergeCell ref="K87:K88"/>
     <mergeCell ref="C90:D90"/>
@@ -59909,6 +60319,19 @@
     <mergeCell ref="G90:H90"/>
     <mergeCell ref="I90:J90"/>
     <mergeCell ref="K90:L90"/>
+    <mergeCell ref="K110:L110"/>
+    <mergeCell ref="K109:L109"/>
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="K91:L91"/>
+    <mergeCell ref="K111:L111"/>
+    <mergeCell ref="K112:L112"/>
     <mergeCell ref="C53:D53"/>
     <mergeCell ref="E53:F53"/>
     <mergeCell ref="A54:B54"/>
@@ -59950,83 +60373,83 @@
     <mergeCell ref="K83:K85"/>
     <mergeCell ref="L83:L85"/>
     <mergeCell ref="L87:L88"/>
-    <mergeCell ref="A121:B121"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="E122:F122"/>
-    <mergeCell ref="G122:H122"/>
-    <mergeCell ref="I122:J122"/>
-    <mergeCell ref="K122:L122"/>
-    <mergeCell ref="Q122:S122"/>
-    <mergeCell ref="A122:B122"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="E123:F123"/>
-    <mergeCell ref="G123:H123"/>
-    <mergeCell ref="I123:J123"/>
-    <mergeCell ref="K123:L123"/>
-    <mergeCell ref="Q123:S123"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:B221"/>
-    <mergeCell ref="A222:B222"/>
-    <mergeCell ref="A210:A212"/>
-    <mergeCell ref="A213:B213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="C214:C216"/>
-    <mergeCell ref="D214:D216"/>
-    <mergeCell ref="C218:C219"/>
-    <mergeCell ref="D218:D219"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="C186:D186"/>
-    <mergeCell ref="A174:B174"/>
-    <mergeCell ref="A175:B175"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A183:B183"/>
-    <mergeCell ref="C183:D183"/>
-    <mergeCell ref="C184:D184"/>
-    <mergeCell ref="A184:B184"/>
-    <mergeCell ref="A185:B185"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="G134:H134"/>
+    <mergeCell ref="I134:J134"/>
+    <mergeCell ref="K134:L134"/>
+    <mergeCell ref="Q134:S134"/>
+    <mergeCell ref="A134:B134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="G135:H135"/>
+    <mergeCell ref="I135:J135"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="Q135:S135"/>
+    <mergeCell ref="A229:A231"/>
+    <mergeCell ref="A233:B233"/>
+    <mergeCell ref="A234:B234"/>
+    <mergeCell ref="A222:A224"/>
+    <mergeCell ref="A225:B225"/>
+    <mergeCell ref="A226:A228"/>
+    <mergeCell ref="C226:C228"/>
+    <mergeCell ref="D226:D228"/>
+    <mergeCell ref="C230:C231"/>
+    <mergeCell ref="D230:D231"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="C198:D198"/>
     <mergeCell ref="A186:B186"/>
     <mergeCell ref="A187:B187"/>
     <mergeCell ref="A188:A190"/>
     <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A194:B194"/>
-    <mergeCell ref="C204:D204"/>
-    <mergeCell ref="C205:D205"/>
-    <mergeCell ref="A195:A197"/>
-    <mergeCell ref="C195:C197"/>
-    <mergeCell ref="D195:D197"/>
-    <mergeCell ref="C199:C200"/>
-    <mergeCell ref="D199:D200"/>
-    <mergeCell ref="C202:D202"/>
-    <mergeCell ref="C203:D203"/>
-    <mergeCell ref="A198:A200"/>
-    <mergeCell ref="A202:B202"/>
-    <mergeCell ref="A203:B203"/>
-    <mergeCell ref="A204:B204"/>
-    <mergeCell ref="A205:B205"/>
+    <mergeCell ref="A195:B195"/>
+    <mergeCell ref="C195:D195"/>
+    <mergeCell ref="C196:D196"/>
+    <mergeCell ref="A196:B196"/>
+    <mergeCell ref="A197:B197"/>
+    <mergeCell ref="A198:B198"/>
+    <mergeCell ref="A199:B199"/>
+    <mergeCell ref="A200:A202"/>
+    <mergeCell ref="A203:A205"/>
     <mergeCell ref="A206:B206"/>
+    <mergeCell ref="C216:D216"/>
+    <mergeCell ref="C217:D217"/>
     <mergeCell ref="A207:A209"/>
-    <mergeCell ref="C221:D221"/>
-    <mergeCell ref="C222:D222"/>
-    <mergeCell ref="A223:B223"/>
-    <mergeCell ref="C223:D223"/>
-    <mergeCell ref="A224:B224"/>
-    <mergeCell ref="C224:D224"/>
-    <mergeCell ref="A225:B225"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="C124:D124"/>
-    <mergeCell ref="E124:F124"/>
-    <mergeCell ref="G124:H124"/>
-    <mergeCell ref="I124:J124"/>
-    <mergeCell ref="K124:L124"/>
-    <mergeCell ref="Q124:S124"/>
-    <mergeCell ref="A124:B124"/>
-    <mergeCell ref="A125:B125"/>
-    <mergeCell ref="A126:A128"/>
-    <mergeCell ref="P126:P128"/>
-    <mergeCell ref="A129:A131"/>
-    <mergeCell ref="P129:P131"/>
-    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="C207:C209"/>
+    <mergeCell ref="D207:D209"/>
+    <mergeCell ref="C211:C212"/>
+    <mergeCell ref="D211:D212"/>
+    <mergeCell ref="C214:D214"/>
+    <mergeCell ref="C215:D215"/>
+    <mergeCell ref="A210:A212"/>
+    <mergeCell ref="A214:B214"/>
+    <mergeCell ref="A215:B215"/>
+    <mergeCell ref="A216:B216"/>
+    <mergeCell ref="A217:B217"/>
+    <mergeCell ref="A218:B218"/>
+    <mergeCell ref="A219:A221"/>
+    <mergeCell ref="C233:D233"/>
+    <mergeCell ref="C234:D234"/>
+    <mergeCell ref="A235:B235"/>
+    <mergeCell ref="C235:D235"/>
+    <mergeCell ref="A236:B236"/>
+    <mergeCell ref="C236:D236"/>
+    <mergeCell ref="A237:B237"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="G136:H136"/>
+    <mergeCell ref="I136:J136"/>
+    <mergeCell ref="K136:L136"/>
+    <mergeCell ref="Q136:S136"/>
+    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="A137:B137"/>
+    <mergeCell ref="A138:A140"/>
+    <mergeCell ref="P138:P140"/>
+    <mergeCell ref="A141:A143"/>
+    <mergeCell ref="P141:P143"/>
+    <mergeCell ref="A144:B144"/>
     <mergeCell ref="A75:B75"/>
     <mergeCell ref="A76:A78"/>
     <mergeCell ref="A79:A81"/>
@@ -60062,102 +60485,102 @@
     <mergeCell ref="C112:D112"/>
     <mergeCell ref="E112:F112"/>
     <mergeCell ref="A112:B112"/>
-    <mergeCell ref="C121:D121"/>
-    <mergeCell ref="E121:F121"/>
-    <mergeCell ref="G121:H121"/>
-    <mergeCell ref="I121:J121"/>
-    <mergeCell ref="K121:L121"/>
-    <mergeCell ref="P121:S121"/>
-    <mergeCell ref="I133:I135"/>
-    <mergeCell ref="J133:J135"/>
-    <mergeCell ref="C133:C135"/>
-    <mergeCell ref="C137:C138"/>
-    <mergeCell ref="A152:B152"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="G133:H133"/>
+    <mergeCell ref="I133:J133"/>
+    <mergeCell ref="K133:L133"/>
+    <mergeCell ref="P133:S133"/>
+    <mergeCell ref="I145:I147"/>
+    <mergeCell ref="J145:J147"/>
+    <mergeCell ref="C145:C147"/>
+    <mergeCell ref="C149:C150"/>
+    <mergeCell ref="A164:B164"/>
+    <mergeCell ref="C164:D164"/>
+    <mergeCell ref="E164:F164"/>
+    <mergeCell ref="G164:H164"/>
+    <mergeCell ref="G165:H165"/>
+    <mergeCell ref="A165:B165"/>
+    <mergeCell ref="A166:B166"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="E166:F166"/>
+    <mergeCell ref="G166:H166"/>
+    <mergeCell ref="A167:B167"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="C176:C178"/>
+    <mergeCell ref="C180:C181"/>
+    <mergeCell ref="A168:B168"/>
+    <mergeCell ref="A169:A171"/>
+    <mergeCell ref="A172:A174"/>
+    <mergeCell ref="A175:B175"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="D176:D178"/>
+    <mergeCell ref="D180:D181"/>
+    <mergeCell ref="E184:F184"/>
+    <mergeCell ref="G184:H184"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A183:B183"/>
+    <mergeCell ref="C183:D183"/>
+    <mergeCell ref="E183:F183"/>
+    <mergeCell ref="G183:H183"/>
+    <mergeCell ref="A184:B184"/>
+    <mergeCell ref="C184:D184"/>
+    <mergeCell ref="F149:F150"/>
+    <mergeCell ref="G149:G150"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="J149:J150"/>
+    <mergeCell ref="A145:A147"/>
+    <mergeCell ref="D145:D147"/>
+    <mergeCell ref="E145:E147"/>
+    <mergeCell ref="F145:F147"/>
+    <mergeCell ref="G145:G147"/>
+    <mergeCell ref="H145:H147"/>
+    <mergeCell ref="A148:A150"/>
+    <mergeCell ref="H149:H150"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="G154:H154"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="E155:F155"/>
+    <mergeCell ref="G155:H155"/>
+    <mergeCell ref="D149:D150"/>
+    <mergeCell ref="E149:E150"/>
     <mergeCell ref="C152:D152"/>
     <mergeCell ref="E152:F152"/>
     <mergeCell ref="G152:H152"/>
+    <mergeCell ref="E153:F153"/>
     <mergeCell ref="G153:H153"/>
-    <mergeCell ref="A153:B153"/>
-    <mergeCell ref="A154:B154"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="E154:F154"/>
-    <mergeCell ref="G154:H154"/>
-    <mergeCell ref="A155:B155"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C164:C166"/>
-    <mergeCell ref="C168:C169"/>
-    <mergeCell ref="A156:B156"/>
-    <mergeCell ref="A157:A159"/>
-    <mergeCell ref="A160:A162"/>
-    <mergeCell ref="A163:B163"/>
-    <mergeCell ref="A164:A166"/>
-    <mergeCell ref="D164:D166"/>
-    <mergeCell ref="D168:D169"/>
-    <mergeCell ref="E172:F172"/>
-    <mergeCell ref="G172:H172"/>
-    <mergeCell ref="A167:A169"/>
-    <mergeCell ref="A171:B171"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="E171:F171"/>
-    <mergeCell ref="G171:H171"/>
-    <mergeCell ref="A172:B172"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="F137:F138"/>
-    <mergeCell ref="G137:G138"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="J137:J138"/>
-    <mergeCell ref="A133:A135"/>
-    <mergeCell ref="D133:D135"/>
-    <mergeCell ref="E133:E135"/>
-    <mergeCell ref="F133:F135"/>
-    <mergeCell ref="G133:G135"/>
-    <mergeCell ref="H133:H135"/>
-    <mergeCell ref="A136:A138"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="E142:F142"/>
-    <mergeCell ref="G142:H142"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="E143:F143"/>
-    <mergeCell ref="G143:H143"/>
-    <mergeCell ref="D137:D138"/>
-    <mergeCell ref="E137:E138"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="E140:F140"/>
-    <mergeCell ref="G140:H140"/>
-    <mergeCell ref="E141:F141"/>
-    <mergeCell ref="G141:H141"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="E153:F153"/>
-    <mergeCell ref="E155:F155"/>
-    <mergeCell ref="G155:H155"/>
-    <mergeCell ref="A173:B173"/>
-    <mergeCell ref="C173:D173"/>
-    <mergeCell ref="E173:F173"/>
-    <mergeCell ref="G173:H173"/>
-    <mergeCell ref="C174:D174"/>
-    <mergeCell ref="E174:F174"/>
-    <mergeCell ref="G174:H174"/>
-    <mergeCell ref="A226:A228"/>
-    <mergeCell ref="A229:A231"/>
-    <mergeCell ref="A233:B233"/>
-    <mergeCell ref="C233:D233"/>
-    <mergeCell ref="A234:B234"/>
-    <mergeCell ref="C234:D234"/>
-    <mergeCell ref="C235:D235"/>
-    <mergeCell ref="C236:D236"/>
-    <mergeCell ref="A245:B245"/>
-    <mergeCell ref="A246:B246"/>
-    <mergeCell ref="A247:A249"/>
-    <mergeCell ref="A250:A252"/>
-    <mergeCell ref="A235:B235"/>
-    <mergeCell ref="A236:B236"/>
-    <mergeCell ref="A237:B237"/>
+    <mergeCell ref="C165:D165"/>
+    <mergeCell ref="E165:F165"/>
+    <mergeCell ref="E167:F167"/>
+    <mergeCell ref="G167:H167"/>
+    <mergeCell ref="A185:B185"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="E185:F185"/>
+    <mergeCell ref="G185:H185"/>
+    <mergeCell ref="C186:D186"/>
+    <mergeCell ref="E186:F186"/>
+    <mergeCell ref="G186:H186"/>
     <mergeCell ref="A238:A240"/>
     <mergeCell ref="A241:A243"/>
+    <mergeCell ref="A245:B245"/>
     <mergeCell ref="C245:D245"/>
-    <mergeCell ref="E245:F245"/>
+    <mergeCell ref="A246:B246"/>
+    <mergeCell ref="C246:D246"/>
+    <mergeCell ref="C247:D247"/>
+    <mergeCell ref="C248:D248"/>
+    <mergeCell ref="A257:B257"/>
+    <mergeCell ref="A258:B258"/>
+    <mergeCell ref="A259:A261"/>
+    <mergeCell ref="A262:A264"/>
+    <mergeCell ref="A247:B247"/>
+    <mergeCell ref="A248:B248"/>
+    <mergeCell ref="A249:B249"/>
+    <mergeCell ref="A250:A252"/>
+    <mergeCell ref="A253:A255"/>
+    <mergeCell ref="C257:D257"/>
+    <mergeCell ref="E257:F257"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -60175,11 +60598,11 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="42" t="s">
-        <v>5948</v>
+        <v>5975</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="42" t="s">
-        <v>5949</v>
+        <v>5976</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
@@ -60187,14 +60610,14 @@
         <v>253</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>5950</v>
+        <v>5977</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="43" t="s">
-        <v>5951</v>
+        <v>5978</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>5952</v>
+        <v>5979</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
@@ -60202,14 +60625,14 @@
         <v>1583</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>5953</v>
+        <v>5980</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="43" t="s">
-        <v>5954</v>
+        <v>5981</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>5955</v>
+        <v>5982</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
@@ -60217,14 +60640,14 @@
         <v>2181</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>5956</v>
+        <v>5983</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="43" t="s">
-        <v>5957</v>
+        <v>5984</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>5958</v>
+        <v>5985</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
@@ -60232,14 +60655,14 @@
         <v>2297</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>5959</v>
+        <v>5986</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="43" t="s">
-        <v>5960</v>
+        <v>5987</v>
       </c>
       <c r="G5" s="43" t="s">
-        <v>5961</v>
+        <v>5988</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
@@ -60247,14 +60670,14 @@
         <v>2437</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>5962</v>
+        <v>5989</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="43" t="s">
-        <v>5963</v>
+        <v>5990</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>5964</v>
+        <v>5991</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
@@ -60262,14 +60685,14 @@
         <v>2544</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>5965</v>
+        <v>5992</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="43" t="s">
-        <v>5966</v>
+        <v>5993</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>5967</v>
+        <v>5994</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
@@ -60277,14 +60700,14 @@
         <v>2631</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>5968</v>
+        <v>5995</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="43" t="s">
-        <v>5969</v>
+        <v>5996</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>5970</v>
+        <v>5997</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
@@ -60292,14 +60715,14 @@
         <v>3356</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>5971</v>
+        <v>5998</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="43" t="s">
-        <v>5972</v>
+        <v>5999</v>
       </c>
       <c r="G9" s="43" t="s">
-        <v>5973</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
@@ -60307,14 +60730,14 @@
         <v>3628</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>5974</v>
+        <v>6001</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="43" t="s">
-        <v>5975</v>
+        <v>6002</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>5976</v>
+        <v>6003</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
@@ -60322,14 +60745,14 @@
         <v>4323</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>5977</v>
+        <v>6004</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="43" t="s">
-        <v>5978</v>
+        <v>6005</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>5979</v>
+        <v>6006</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
@@ -60338,10 +60761,10 @@
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
       <c r="E12" s="43" t="s">
-        <v>5980</v>
+        <v>6007</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>5981</v>
+        <v>6008</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
@@ -60350,10 +60773,10 @@
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
       <c r="E13" s="43" t="s">
-        <v>5982</v>
+        <v>6009</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>5983</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
@@ -60362,113 +60785,113 @@
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="43" t="s">
-        <v>5984</v>
+        <v>6011</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>5985</v>
+        <v>6012</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="42" t="s">
-        <v>5986</v>
+        <v>6013</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>5987</v>
+        <v>6014</v>
       </c>
       <c r="G15" s="45" t="s">
-        <v>5988</v>
+        <v>6015</v>
       </c>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>5989</v>
+        <v>6016</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>5990</v>
+        <v>6017</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>5991</v>
+        <v>6018</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>5992</v>
+        <v>6019</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>5993</v>
+        <v>6020</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>5994</v>
+        <v>6021</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>5995</v>
+        <v>6022</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>5996</v>
+        <v>6023</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>5997</v>
+        <v>6024</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>5998</v>
+        <v>6025</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>5999</v>
+        <v>6026</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>6000</v>
+        <v>6027</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>6001</v>
+        <v>6028</v>
       </c>
       <c r="G19" s="43" t="s">
-        <v>6002</v>
+        <v>6029</v>
       </c>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6003</v>
+        <v>6030</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>6004</v>
+        <v>6031</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>6005</v>
+        <v>6032</v>
       </c>
       <c r="G20" s="43" t="s">
-        <v>6006</v>
+        <v>6033</v>
       </c>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6007</v>
+        <v>6034</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>6008</v>
+        <v>6035</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>6009</v>
+        <v>6036</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>6010</v>
+        <v>6037</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6011</v>
+        <v>6038</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>6012</v>
+        <v>6039</v>
       </c>
       <c r="E22" s="46" t="s">
-        <v>6013</v>
+        <v>6040</v>
       </c>
       <c r="G22" s="46" t="s">
-        <v>6014</v>
+        <v>6041</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
@@ -60483,71 +60906,71 @@
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
       <c r="E24" s="43" t="s">
-        <v>6015</v>
+        <v>6042</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>6016</v>
+        <v>6043</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="E25" s="43" t="s">
-        <v>6017</v>
+        <v>6044</v>
       </c>
       <c r="G25" s="43" t="s">
-        <v>6018</v>
+        <v>6045</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="42" t="s">
-        <v>6019</v>
+        <v>6046</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>6020</v>
+        <v>6047</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>6021</v>
+        <v>6048</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>6022</v>
+        <v>6049</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>6023</v>
+        <v>6050</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>6024</v>
+        <v>6051</v>
       </c>
       <c r="G27" s="43" t="s">
-        <v>6025</v>
+        <v>6052</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="43" t="s">
-        <v>6026</v>
+        <v>6053</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>6027</v>
+        <v>6054</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>6028</v>
+        <v>6055</v>
       </c>
       <c r="G28" s="43" t="s">
-        <v>6029</v>
+        <v>6056</v>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="43" t="s">
-        <v>6030</v>
+        <v>6057</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>6031</v>
+        <v>6058</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>6032</v>
+        <v>6059</v>
       </c>
       <c r="G29" s="43" t="s">
-        <v>6033</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1">
@@ -60556,10 +60979,10 @@
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
       <c r="E30" s="43" t="s">
-        <v>6034</v>
+        <v>6061</v>
       </c>
       <c r="G30" s="43" t="s">
-        <v>6035</v>
+        <v>6062</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
@@ -60568,10 +60991,10 @@
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
       <c r="E31" s="43" t="s">
-        <v>6036</v>
+        <v>6063</v>
       </c>
       <c r="G31" s="43" t="s">
-        <v>6037</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
@@ -60580,10 +61003,10 @@
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
       <c r="E32" s="43" t="s">
-        <v>6038</v>
+        <v>6065</v>
       </c>
       <c r="G32" s="43" t="s">
-        <v>6039</v>
+        <v>6066</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
@@ -60592,10 +61015,10 @@
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
       <c r="E33" s="43" t="s">
-        <v>6040</v>
+        <v>6067</v>
       </c>
       <c r="G33" s="43" t="s">
-        <v>6041</v>
+        <v>6068</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
@@ -60604,10 +61027,10 @@
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
       <c r="E34" s="43" t="s">
-        <v>6042</v>
+        <v>6069</v>
       </c>
       <c r="G34" s="43" t="s">
-        <v>6043</v>
+        <v>6070</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
@@ -60616,10 +61039,10 @@
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
       <c r="E35" s="45" t="s">
-        <v>6044</v>
+        <v>6071</v>
       </c>
       <c r="G35" s="45" t="s">
-        <v>6045</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1">
@@ -60634,10 +61057,10 @@
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
       <c r="E37" s="43" t="s">
-        <v>6046</v>
+        <v>6073</v>
       </c>
       <c r="G37" s="43" t="s">
-        <v>6047</v>
+        <v>6074</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
@@ -60646,10 +61069,10 @@
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
       <c r="E38" s="43" t="s">
-        <v>6048</v>
+        <v>6075</v>
       </c>
       <c r="G38" s="43" t="s">
-        <v>6049</v>
+        <v>6076</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
@@ -60658,10 +61081,10 @@
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
       <c r="E39" s="45" t="s">
-        <v>6050</v>
+        <v>6077</v>
       </c>
       <c r="G39" s="45" t="s">
-        <v>6051</v>
+        <v>6078</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
@@ -60676,10 +61099,10 @@
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
       <c r="E41" s="45" t="s">
-        <v>6052</v>
+        <v>6079</v>
       </c>
       <c r="G41" s="45" t="s">
-        <v>6053</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1">
@@ -60897,10 +61320,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="43" t="s">
-        <v>6054</v>
+        <v>6081</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>6055</v>
+        <v>6082</v>
       </c>
       <c r="C1" s="12"/>
     </row>
@@ -60909,34 +61332,34 @@
         <v>38</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>6056</v>
+        <v>6083</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>6057</v>
+        <v>6084</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6058</v>
+        <v>6085</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>6059</v>
+        <v>6086</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6060</v>
+        <v>6087</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>6061</v>
+        <v>6088</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>6062</v>
+        <v>6089</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -60945,70 +61368,70 @@
         <v>1831</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6063</v>
+        <v>6090</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>6064</v>
+        <v>6091</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6065</v>
+        <v>6092</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>6066</v>
+        <v>6093</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6067</v>
+        <v>6094</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>6068</v>
+        <v>6095</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6069</v>
+        <v>6096</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>6070</v>
+        <v>6097</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6071</v>
+        <v>6098</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>6072</v>
+        <v>6099</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6073</v>
+        <v>6100</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>6074</v>
+        <v>6101</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>6075</v>
+        <v>6102</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>6076</v>
+        <v>6103</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>6077</v>
+        <v>6104</v>
       </c>
       <c r="C13" s="12"/>
     </row>
@@ -61017,7 +61440,7 @@
         <v>4826</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>6078</v>
+        <v>6105</v>
       </c>
       <c r="C14" s="12"/>
     </row>
@@ -61028,19 +61451,19 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6079</v>
+        <v>6106</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>6080</v>
+        <v>6107</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6081</v>
+        <v>6108</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>6082</v>
+        <v>6109</v>
       </c>
       <c r="C17" s="12"/>
     </row>
@@ -61051,235 +61474,235 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6083</v>
+        <v>6110</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>6084</v>
+        <v>6111</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6085</v>
+        <v>6112</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>6086</v>
+        <v>6113</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6087</v>
+        <v>6114</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>6088</v>
+        <v>6115</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6089</v>
+        <v>6116</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>6090</v>
+        <v>6117</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>6091</v>
+        <v>6118</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>6092</v>
+        <v>6119</v>
       </c>
       <c r="C23" s="12"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="43" t="s">
-        <v>6093</v>
+        <v>6120</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>6094</v>
+        <v>6121</v>
       </c>
       <c r="C24" s="12"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="43" t="s">
-        <v>6095</v>
+        <v>6122</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>6096</v>
+        <v>6123</v>
       </c>
       <c r="C25" s="12"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="43" t="s">
-        <v>6097</v>
+        <v>6124</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>6098</v>
+        <v>6125</v>
       </c>
       <c r="C26" s="12"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>6099</v>
+        <v>6126</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>6100</v>
+        <v>6127</v>
       </c>
       <c r="C27" s="12"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="43" t="s">
-        <v>6101</v>
+        <v>6128</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>6102</v>
+        <v>6129</v>
       </c>
       <c r="C28" s="12"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="43" t="s">
-        <v>6103</v>
+        <v>6130</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>6104</v>
+        <v>6131</v>
       </c>
       <c r="C29" s="12"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="43" t="s">
-        <v>6105</v>
+        <v>6132</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>6106</v>
+        <v>6133</v>
       </c>
       <c r="C30" s="12"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="43" t="s">
-        <v>6107</v>
+        <v>6134</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>6108</v>
+        <v>6135</v>
       </c>
       <c r="C31" s="12"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="43" t="s">
-        <v>6109</v>
+        <v>6136</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>6110</v>
+        <v>6137</v>
       </c>
       <c r="C32" s="12"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="43" t="s">
-        <v>6111</v>
+        <v>6138</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>6112</v>
+        <v>6139</v>
       </c>
       <c r="C33" s="12"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="43" t="s">
-        <v>6113</v>
+        <v>6140</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>6114</v>
+        <v>6141</v>
       </c>
       <c r="C34" s="12"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="43" t="s">
-        <v>6115</v>
+        <v>6142</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>6116</v>
+        <v>6143</v>
       </c>
       <c r="C35" s="12"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="43" t="s">
-        <v>6117</v>
+        <v>6144</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>6118</v>
+        <v>6145</v>
       </c>
       <c r="C36" s="12"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="43" t="s">
-        <v>6119</v>
+        <v>6146</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>6120</v>
+        <v>6147</v>
       </c>
       <c r="C37" s="12"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="43" t="s">
-        <v>6121</v>
+        <v>6148</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>6122</v>
+        <v>6149</v>
       </c>
       <c r="C38" s="12"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="43" t="s">
-        <v>6123</v>
+        <v>6150</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>6124</v>
+        <v>6151</v>
       </c>
       <c r="C39" s="12"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="43" t="s">
-        <v>6125</v>
+        <v>6152</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>6126</v>
+        <v>6153</v>
       </c>
       <c r="C40" s="12"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="43" t="s">
-        <v>6127</v>
+        <v>6154</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>6128</v>
+        <v>6155</v>
       </c>
       <c r="C41" s="12"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="43" t="s">
-        <v>6129</v>
+        <v>6156</v>
       </c>
       <c r="B42" s="43" t="s">
-        <v>6130</v>
+        <v>6157</v>
       </c>
       <c r="C42" s="12"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="43" t="s">
-        <v>6131</v>
+        <v>6158</v>
       </c>
       <c r="B43" s="43" t="s">
-        <v>6132</v>
+        <v>6159</v>
       </c>
       <c r="C43" s="12"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" s="43" t="s">
-        <v>6133</v>
+        <v>6160</v>
       </c>
       <c r="B44" s="43" t="s">
-        <v>6134</v>
+        <v>6161</v>
       </c>
       <c r="C44" s="12"/>
     </row>
@@ -61288,34 +61711,34 @@
         <v>888</v>
       </c>
       <c r="B45" s="43" t="s">
-        <v>6135</v>
+        <v>6162</v>
       </c>
       <c r="C45" s="12"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="43" t="s">
-        <v>6136</v>
+        <v>6163</v>
       </c>
       <c r="B46" s="43" t="s">
-        <v>6137</v>
+        <v>6164</v>
       </c>
       <c r="C46" s="12"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="43" t="s">
-        <v>6138</v>
+        <v>6165</v>
       </c>
       <c r="B47" s="43" t="s">
-        <v>6139</v>
+        <v>6166</v>
       </c>
       <c r="C47" s="12"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="43" t="s">
-        <v>6140</v>
+        <v>6167</v>
       </c>
       <c r="B48" s="43" t="s">
-        <v>6141</v>
+        <v>6168</v>
       </c>
       <c r="C48" s="12"/>
     </row>
@@ -61338,130 +61761,130 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="47" t="s">
-        <v>6142</v>
+        <v>6169</v>
       </c>
       <c r="C1" s="12"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="47" t="s">
-        <v>6143</v>
+        <v>6170</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>6144</v>
+        <v>6171</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>6145</v>
+        <v>6172</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6081</v>
+        <v>6108</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>6081</v>
+        <v>6108</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6146</v>
+        <v>6173</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>6147</v>
+        <v>6174</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>6070</v>
+        <v>6097</v>
       </c>
       <c r="C5" s="12"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="43" t="s">
-        <v>6148</v>
+        <v>6175</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6149</v>
+        <v>6176</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>6150</v>
+        <v>6177</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6151</v>
+        <v>6178</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>6152</v>
+        <v>6179</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6153</v>
+        <v>6180</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>6154</v>
+        <v>6181</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6155</v>
+        <v>6182</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>6156</v>
+        <v>6183</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6157</v>
+        <v>6184</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>6158</v>
+        <v>6185</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6159</v>
+        <v>6186</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>6160</v>
+        <v>6187</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>6161</v>
+        <v>6188</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>6162</v>
+        <v>6189</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>6163</v>
+        <v>6190</v>
       </c>
       <c r="C13" s="12"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="43" t="s">
-        <v>6164</v>
+        <v>6191</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>6165</v>
+        <v>6192</v>
       </c>
       <c r="C14" s="12"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="43" t="s">
-        <v>6166</v>
+        <v>6193</v>
       </c>
       <c r="B15" s="43" t="s">
         <v>3897</v>
@@ -61470,73 +61893,73 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6167</v>
+        <v>6194</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>6168</v>
+        <v>6195</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6169</v>
+        <v>6196</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>6170</v>
+        <v>6197</v>
       </c>
       <c r="C17" s="12"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>6171</v>
+        <v>6198</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>6172</v>
+        <v>6199</v>
       </c>
       <c r="C18" s="12"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6173</v>
+        <v>6200</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>6174</v>
+        <v>6201</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6175</v>
+        <v>6202</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>6176</v>
+        <v>6203</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6177</v>
+        <v>6204</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>6178</v>
+        <v>6205</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6179</v>
+        <v>6206</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>6180</v>
+        <v>6207</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>6181</v>
+        <v>6208</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>6182</v>
+        <v>6209</v>
       </c>
       <c r="C23" s="12"/>
     </row>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -10378,7 +10378,7 @@
     <t>smarta</t>
   </si>
   <si>
-    <t>to smite, to strike, to bash</t>
+    <t>to hurt, to feel painful (intransitive)</t>
   </si>
   <si>
     <t>smíða</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -18483,7 +18483,7 @@
     <t>h</t>
   </si>
   <si>
-    <t>/x/</t>
+    <t>/h/</t>
   </si>
   <si>
     <t>j</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9945" uniqueCount="6231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9945" uniqueCount="6230">
   <si>
     <t>Entry</t>
   </si>
@@ -18405,10 +18405,10 @@
     <t>/ouː/</t>
   </si>
   <si>
-    <t>œ, œi</t>
-  </si>
-  <si>
-    <t>/oiː/</t>
+    <t>œ</t>
+  </si>
+  <si>
+    <t>/ɤiː/</t>
   </si>
   <si>
     <t>ø</t>
@@ -18447,7 +18447,7 @@
     <t>ey</t>
   </si>
   <si>
-    <t>/ɛyː/, /œyː/</t>
+    <t>/eyː/</t>
   </si>
   <si>
     <t>b</t>
@@ -18637,9 +18637,6 @@
   </si>
   <si>
     <t>au</t>
-  </si>
-  <si>
-    <t>œ</t>
   </si>
   <si>
     <t>ǫ, ø, œ</t>
@@ -61963,13 +61960,13 @@
         <v>6129</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6194</v>
+        <v>6116</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>6195</v>
+        <v>6194</v>
       </c>
       <c r="B5" s="43" t="s">
         <v>6118</v>
@@ -61978,88 +61975,88 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="43" t="s">
+        <v>6195</v>
+      </c>
+      <c r="B6" s="43" t="s">
         <v>6196</v>
-      </c>
-      <c r="B6" s="43" t="s">
-        <v>6197</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
+        <v>6197</v>
+      </c>
+      <c r="B7" s="43" t="s">
         <v>6198</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>6199</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
+        <v>6199</v>
+      </c>
+      <c r="B8" s="43" t="s">
         <v>6200</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>6201</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
+        <v>6201</v>
+      </c>
+      <c r="B9" s="43" t="s">
         <v>6202</v>
-      </c>
-      <c r="B9" s="43" t="s">
-        <v>6203</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
+        <v>6203</v>
+      </c>
+      <c r="B10" s="43" t="s">
         <v>6204</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>6205</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
+        <v>6205</v>
+      </c>
+      <c r="B11" s="43" t="s">
         <v>6206</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>6207</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
+        <v>6207</v>
+      </c>
+      <c r="B12" s="43" t="s">
         <v>6208</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>6209</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
+        <v>6209</v>
+      </c>
+      <c r="B13" s="43" t="s">
         <v>6210</v>
-      </c>
-      <c r="B13" s="43" t="s">
-        <v>6211</v>
       </c>
       <c r="C13" s="12"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="43" t="s">
+        <v>6211</v>
+      </c>
+      <c r="B14" s="43" t="s">
         <v>6212</v>
-      </c>
-      <c r="B14" s="43" t="s">
-        <v>6213</v>
       </c>
       <c r="C14" s="12"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="43" t="s">
-        <v>6214</v>
+        <v>6213</v>
       </c>
       <c r="B15" s="43" t="s">
         <v>3914</v>
@@ -62068,73 +62065,73 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
+        <v>6214</v>
+      </c>
+      <c r="B16" s="43" t="s">
         <v>6215</v>
-      </c>
-      <c r="B16" s="43" t="s">
-        <v>6216</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
+        <v>6216</v>
+      </c>
+      <c r="B17" s="43" t="s">
         <v>6217</v>
-      </c>
-      <c r="B17" s="43" t="s">
-        <v>6218</v>
       </c>
       <c r="C17" s="12"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
+        <v>6218</v>
+      </c>
+      <c r="B18" s="43" t="s">
         <v>6219</v>
-      </c>
-      <c r="B18" s="43" t="s">
-        <v>6220</v>
       </c>
       <c r="C18" s="12"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
+        <v>6220</v>
+      </c>
+      <c r="B19" s="43" t="s">
         <v>6221</v>
-      </c>
-      <c r="B19" s="43" t="s">
-        <v>6222</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
+        <v>6222</v>
+      </c>
+      <c r="B20" s="43" t="s">
         <v>6223</v>
-      </c>
-      <c r="B20" s="43" t="s">
-        <v>6224</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
+        <v>6224</v>
+      </c>
+      <c r="B21" s="43" t="s">
         <v>6225</v>
-      </c>
-      <c r="B21" s="43" t="s">
-        <v>6226</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
+        <v>6226</v>
+      </c>
+      <c r="B22" s="43" t="s">
         <v>6227</v>
-      </c>
-      <c r="B22" s="43" t="s">
-        <v>6228</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
+        <v>6228</v>
+      </c>
+      <c r="B23" s="43" t="s">
         <v>6229</v>
-      </c>
-      <c r="B23" s="43" t="s">
-        <v>6230</v>
       </c>
       <c r="C23" s="12"/>
     </row>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9945" uniqueCount="6230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9959" uniqueCount="6245">
   <si>
     <t>Entry</t>
   </si>
@@ -14790,7 +14790,7 @@
     <t>þá</t>
   </si>
   <si>
-    <t>sei</t>
+    <t>sá</t>
   </si>
   <si>
     <t>oss</t>
@@ -18480,6 +18480,12 @@
     <t>/g/ at the start or when doubled, /ɣ/ in the middle</t>
   </si>
   <si>
+    <t>gj</t>
+  </si>
+  <si>
+    <t>/c/</t>
+  </si>
+  <si>
     <t>h</t>
   </si>
   <si>
@@ -18492,6 +18498,12 @@
     <t>/j/</t>
   </si>
   <si>
+    <t>hj</t>
+  </si>
+  <si>
+    <t>/j̊/</t>
+  </si>
+  <si>
     <t>k</t>
   </si>
   <si>
@@ -18522,12 +18534,24 @@
     <t>/m/</t>
   </si>
   <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>/mː/</t>
+  </si>
+  <si>
     <t>n</t>
   </si>
   <si>
     <t>/n/</t>
   </si>
   <si>
+    <t>nn</t>
+  </si>
+  <si>
+    <t>/nː/</t>
+  </si>
+  <si>
     <t>hn</t>
   </si>
   <si>
@@ -18552,12 +18576,24 @@
     <t>/r/</t>
   </si>
   <si>
+    <t>rr</t>
+  </si>
+  <si>
+    <t>/rː/</t>
+  </si>
+  <si>
     <t>s</t>
   </si>
   <si>
     <t>/s/</t>
   </si>
   <si>
+    <t>ss</t>
+  </si>
+  <si>
+    <t>/ʃː/</t>
+  </si>
+  <si>
     <t>t</t>
   </si>
   <si>
@@ -18600,31 +18636,40 @@
     <t>/ð/</t>
   </si>
   <si>
-    <t>ang</t>
-  </si>
-  <si>
-    <t>/aŋk/</t>
-  </si>
-  <si>
-    <t>/eiŋk/</t>
-  </si>
-  <si>
-    <t>ing</t>
-  </si>
-  <si>
-    <t>/iŋk/</t>
-  </si>
-  <si>
-    <t>ung</t>
-  </si>
-  <si>
-    <t>/uŋk/</t>
-  </si>
-  <si>
-    <t>yng</t>
-  </si>
-  <si>
-    <t>/yŋk/</t>
+    <t>ang, angr</t>
+  </si>
+  <si>
+    <t>/aŋk/, /aŋgr/</t>
+  </si>
+  <si>
+    <t>eng, engr</t>
+  </si>
+  <si>
+    <t>/eiŋk/, /eiŋgr/</t>
+  </si>
+  <si>
+    <t>ing, ingr</t>
+  </si>
+  <si>
+    <t>/iŋk/, /iŋgr/</t>
+  </si>
+  <si>
+    <t>ung, ungr</t>
+  </si>
+  <si>
+    <t>/uŋk/, /uŋgr/</t>
+  </si>
+  <si>
+    <t>yng, yngr</t>
+  </si>
+  <si>
+    <t>/yŋk/, /yŋgr/</t>
+  </si>
+  <si>
+    <t>m, n, r + k, p, t</t>
+  </si>
+  <si>
+    <t>m, n, r gets devoiced</t>
   </si>
   <si>
     <t>remember: there are exeptions, this list is just for general words</t>
@@ -50515,10 +50560,6 @@
     <mergeCell ref="C38:C39"/>
     <mergeCell ref="D38:D39"/>
     <mergeCell ref="G38:I38"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="N13:N14"/>
     <mergeCell ref="G20:I20"/>
     <mergeCell ref="L20:N20"/>
     <mergeCell ref="G21:I21"/>
@@ -50530,13 +50571,6 @@
     <mergeCell ref="M18:M19"/>
     <mergeCell ref="N18:N19"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D13:D14"/>
     <mergeCell ref="D22:D23"/>
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="I24:I25"/>
@@ -50548,6 +50582,17 @@
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B41:D41"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="N13:N14"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -61880,39 +61925,102 @@
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="43" t="s">
-        <v>890</v>
+        <v>6183</v>
       </c>
       <c r="B45" s="43" t="s">
-        <v>6183</v>
+        <v>6184</v>
       </c>
       <c r="C45" s="12"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="43" t="s">
-        <v>6184</v>
+        <v>6185</v>
       </c>
       <c r="B46" s="43" t="s">
-        <v>6185</v>
+        <v>6186</v>
       </c>
       <c r="C46" s="12"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="43" t="s">
-        <v>6186</v>
+        <v>6187</v>
       </c>
       <c r="B47" s="43" t="s">
-        <v>6187</v>
+        <v>6188</v>
       </c>
       <c r="C47" s="12"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="43" t="s">
-        <v>6188</v>
+        <v>6189</v>
       </c>
       <c r="B48" s="43" t="s">
-        <v>6189</v>
+        <v>6190</v>
       </c>
       <c r="C48" s="12"/>
+    </row>
+    <row r="49" ht="18.75" customHeight="1">
+      <c r="A49" s="43" t="s">
+        <v>6191</v>
+      </c>
+      <c r="B49" s="43" t="s">
+        <v>6192</v>
+      </c>
+      <c r="C49" s="12"/>
+    </row>
+    <row r="50" ht="18.75" customHeight="1">
+      <c r="A50" s="43" t="s">
+        <v>6193</v>
+      </c>
+      <c r="B50" s="43" t="s">
+        <v>6194</v>
+      </c>
+      <c r="C50" s="12"/>
+    </row>
+    <row r="51" ht="18.75" customHeight="1">
+      <c r="A51" s="43" t="s">
+        <v>6195</v>
+      </c>
+      <c r="B51" s="43" t="s">
+        <v>6196</v>
+      </c>
+      <c r="C51" s="12"/>
+    </row>
+    <row r="52" ht="18.75" customHeight="1">
+      <c r="A52" s="43" t="s">
+        <v>6197</v>
+      </c>
+      <c r="B52" s="43" t="s">
+        <v>6198</v>
+      </c>
+      <c r="C52" s="12"/>
+    </row>
+    <row r="53" ht="18.75" customHeight="1">
+      <c r="A53" s="43" t="s">
+        <v>6199</v>
+      </c>
+      <c r="B53" s="43" t="s">
+        <v>6200</v>
+      </c>
+      <c r="C53" s="12"/>
+    </row>
+    <row r="54" ht="18.75" customHeight="1">
+      <c r="A54" s="43" t="s">
+        <v>6201</v>
+      </c>
+      <c r="B54" s="43" t="s">
+        <v>6202</v>
+      </c>
+      <c r="C54" s="12"/>
+    </row>
+    <row r="55" ht="18.75" customHeight="1">
+      <c r="A55" s="43" t="s">
+        <v>6203</v>
+      </c>
+      <c r="B55" s="43" t="s">
+        <v>6204</v>
+      </c>
+      <c r="C55" s="12"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -61933,22 +62041,22 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="47" t="s">
-        <v>6190</v>
+        <v>6205</v>
       </c>
       <c r="C1" s="12"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="47" t="s">
-        <v>6191</v>
+        <v>6206</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>6192</v>
+        <v>6207</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>6193</v>
+        <v>6208</v>
       </c>
       <c r="B3" s="43" t="s">
         <v>6129</v>
@@ -61966,7 +62074,7 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>6194</v>
+        <v>6209</v>
       </c>
       <c r="B5" s="43" t="s">
         <v>6118</v>
@@ -61975,88 +62083,88 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="43" t="s">
-        <v>6195</v>
+        <v>6210</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6196</v>
+        <v>6211</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>6197</v>
+        <v>6212</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6198</v>
+        <v>6213</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>6199</v>
+        <v>6214</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6200</v>
+        <v>6215</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>6201</v>
+        <v>6216</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6202</v>
+        <v>6217</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>6203</v>
+        <v>6218</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6204</v>
+        <v>6219</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>6205</v>
+        <v>6220</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6206</v>
+        <v>6221</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>6207</v>
+        <v>6222</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>6208</v>
+        <v>6223</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>6209</v>
+        <v>6224</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>6210</v>
+        <v>6225</v>
       </c>
       <c r="C13" s="12"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="43" t="s">
-        <v>6211</v>
+        <v>6226</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>6212</v>
+        <v>6227</v>
       </c>
       <c r="C14" s="12"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="43" t="s">
-        <v>6213</v>
+        <v>6228</v>
       </c>
       <c r="B15" s="43" t="s">
         <v>3914</v>
@@ -62065,73 +62173,73 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6214</v>
+        <v>6229</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>6215</v>
+        <v>6230</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6216</v>
+        <v>6231</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>6217</v>
+        <v>6232</v>
       </c>
       <c r="C17" s="12"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>6218</v>
+        <v>6233</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>6219</v>
+        <v>6234</v>
       </c>
       <c r="C18" s="12"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6220</v>
+        <v>6235</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>6221</v>
+        <v>6236</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6222</v>
+        <v>6237</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>6223</v>
+        <v>6238</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6224</v>
+        <v>6239</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>6225</v>
+        <v>6240</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6226</v>
+        <v>6241</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>6227</v>
+        <v>6242</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>6228</v>
+        <v>6243</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>6229</v>
+        <v>6244</v>
       </c>
       <c r="C23" s="12"/>
     </row>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -2944,13 +2944,13 @@
     <t>to go to war</t>
   </si>
   <si>
-    <t>fara í kanningu</t>
+    <t>fara í kanning</t>
   </si>
   <si>
     <t>to go exploring</t>
   </si>
   <si>
-    <t>fara í víkingu</t>
+    <t>fara í víking</t>
   </si>
   <si>
     <t>to go viking</t>
@@ -3670,7 +3670,7 @@
     <t>ganga</t>
   </si>
   <si>
-    <t>to walk</t>
+    <t>to walk (intransitive); to join (with í + accusative)</t>
   </si>
   <si>
     <t>gangr</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9981" uniqueCount="6259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9981" uniqueCount="6260">
   <si>
     <t>Entry</t>
   </si>
@@ -12226,682 +12226,682 @@
     <t>weapon</t>
   </si>
   <si>
-    <t>var</t>
+    <t>vár</t>
+  </si>
+  <si>
+    <t>spring (season)</t>
+  </si>
+  <si>
+    <t>var-kárr</t>
+  </si>
+  <si>
+    <t>careful, cautious, wary</t>
+  </si>
+  <si>
+    <t>var-merki</t>
+  </si>
+  <si>
+    <t>info sign, notice sign, warning sign, placard</t>
+  </si>
+  <si>
+    <t>vara</t>
+  </si>
+  <si>
+    <t>to warn (with accusative)</t>
+  </si>
+  <si>
+    <t>varangr</t>
+  </si>
+  <si>
+    <t>Varangian</t>
+  </si>
+  <si>
+    <t>varða</t>
+  </si>
+  <si>
+    <t>to ward, to protect (with accusative "who/what" + frá + dative "from who/what")</t>
+  </si>
+  <si>
+    <t>varða-torn</t>
+  </si>
+  <si>
+    <t>watchtower</t>
+  </si>
+  <si>
+    <t>varðandi</t>
+  </si>
+  <si>
+    <t>protective</t>
+  </si>
+  <si>
+    <t>varma</t>
+  </si>
+  <si>
+    <t>to warm (with accusative)</t>
+  </si>
+  <si>
+    <t>varmr</t>
+  </si>
+  <si>
+    <t>warm</t>
+  </si>
+  <si>
+    <t>varpa</t>
+  </si>
+  <si>
+    <t>to shed, to take off, to cause to fall off</t>
+  </si>
+  <si>
+    <t>varr</t>
+  </si>
+  <si>
+    <t>wary (archaic)</t>
+  </si>
+  <si>
+    <t>varta</t>
+  </si>
+  <si>
+    <t>wart</t>
+  </si>
+  <si>
+    <t>vas</t>
+  </si>
+  <si>
+    <t>vase</t>
+  </si>
+  <si>
+    <t>Vatakonda</t>
+  </si>
+  <si>
+    <t>Vatakond (a kingdom in Myrkjørð)</t>
+  </si>
+  <si>
+    <t>vatn</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>vatns-gefari</t>
+  </si>
+  <si>
+    <t>tap, faucet</t>
+  </si>
+  <si>
+    <t>vatns-høld</t>
+  </si>
+  <si>
+    <t>water reservoir</t>
+  </si>
+  <si>
+    <t>vátr</t>
+  </si>
+  <si>
+    <t>wet</t>
+  </si>
+  <si>
+    <t>vax</t>
+  </si>
+  <si>
+    <t>wax</t>
+  </si>
+  <si>
+    <t>vaxa (1)</t>
+  </si>
+  <si>
+    <t>to grow, to age (intransitive)</t>
+  </si>
+  <si>
+    <t>vaxa (2)</t>
+  </si>
+  <si>
+    <t>to wax (with accusative)</t>
+  </si>
+  <si>
+    <t>veðr</t>
+  </si>
+  <si>
+    <t>weather</t>
+  </si>
+  <si>
+    <t>vefa</t>
+  </si>
+  <si>
+    <t>to weave, to knit, to tailor</t>
+  </si>
+  <si>
+    <t>vefr</t>
+  </si>
+  <si>
+    <t>web (of a spider); fishing net</t>
+  </si>
+  <si>
+    <t>veg-steinn</t>
+  </si>
+  <si>
+    <t>pavement, cobblestone; a symbol carved on a rock for good fortune; a vegvísir stone; a lucky charm</t>
+  </si>
+  <si>
+    <t>veg-streymr</t>
+  </si>
+  <si>
+    <t>traffic</t>
+  </si>
+  <si>
+    <t>vega</t>
+  </si>
+  <si>
+    <t>to travel, to navigate</t>
+  </si>
+  <si>
+    <t>vegna</t>
+  </si>
+  <si>
+    <t>because</t>
+  </si>
+  <si>
+    <t>vegr</t>
+  </si>
+  <si>
+    <t>road, street, path, way</t>
+  </si>
+  <si>
+    <t>veiða</t>
+  </si>
+  <si>
+    <t>to hunt, to fish (with accusative)</t>
+  </si>
+  <si>
+    <t>veifa</t>
+  </si>
+  <si>
+    <t>to swing, to wave (with accusative)</t>
+  </si>
+  <si>
+    <t>veiki</t>
+  </si>
+  <si>
+    <t>weakness; illness, sickness</t>
+  </si>
+  <si>
+    <t>veikja</t>
+  </si>
+  <si>
+    <t>to weaken</t>
+  </si>
+  <si>
+    <t>veikr</t>
+  </si>
+  <si>
+    <t>weak</t>
+  </si>
+  <si>
+    <t>veikr í hugi</t>
+  </si>
+  <si>
+    <t>sick in the head; crazy, out of one's mind</t>
+  </si>
+  <si>
+    <t>veira</t>
+  </si>
+  <si>
+    <t>virus (biology); malware, virus, trojan</t>
+  </si>
+  <si>
+    <t>vekja</t>
+  </si>
+  <si>
+    <t>to cause to wake (with accusative)</t>
+  </si>
+  <si>
+    <t>vel</t>
+  </si>
+  <si>
+    <t>well, good (velr = better, velst = best)</t>
+  </si>
+  <si>
+    <t>vel-eyðinn</t>
+  </si>
+  <si>
+    <t>successful</t>
+  </si>
+  <si>
+    <t>vel-kominn</t>
+  </si>
+  <si>
+    <t>welcomed, gladly received (not used as a phrase!)</t>
+  </si>
+  <si>
+    <t>Veldalfheimr</t>
+  </si>
+  <si>
+    <t>world of the fey</t>
+  </si>
+  <si>
+    <t>veldi</t>
+  </si>
+  <si>
+    <t>kingdom, realm, empire; power, reign</t>
+  </si>
+  <si>
+    <t>velja</t>
+  </si>
+  <si>
+    <t>to choose, to select</t>
+  </si>
+  <si>
+    <t>venja (1)</t>
+  </si>
+  <si>
+    <t>to teach, to train, to coach, to guide</t>
+  </si>
+  <si>
+    <t>venja (2)</t>
+  </si>
+  <si>
+    <t>teaching, guidance; habit, tendency</t>
+  </si>
+  <si>
+    <t>venju-liga</t>
+  </si>
+  <si>
+    <t>normally, usually</t>
+  </si>
+  <si>
+    <t>venju-ligr</t>
+  </si>
+  <si>
+    <t>normal, usual, ordinary, common</t>
+  </si>
+  <si>
+    <t>vera</t>
+  </si>
+  <si>
+    <t>to be (with nominative)</t>
+  </si>
+  <si>
+    <t>vera í eldi</t>
+  </si>
+  <si>
+    <t>to be on fire</t>
+  </si>
+  <si>
+    <t>vera varkárr</t>
+  </si>
+  <si>
+    <t>to be careful, to beware</t>
+  </si>
+  <si>
+    <t>verð-leyss</t>
+  </si>
+  <si>
+    <t>worthless, without value</t>
+  </si>
+  <si>
+    <t>verða</t>
+  </si>
+  <si>
+    <t>to become (with nominative); will be, will turn out (with nominative)</t>
+  </si>
+  <si>
+    <t>verðr</t>
+  </si>
+  <si>
+    <t>worthy, valueable; expensive</t>
+  </si>
+  <si>
+    <t>veri</t>
+  </si>
+  <si>
+    <t>creation, creature, animal, monster</t>
+  </si>
+  <si>
+    <t>verk</t>
+  </si>
+  <si>
+    <t>action, deed, doing</t>
+  </si>
+  <si>
+    <t>verk-mál</t>
+  </si>
+  <si>
+    <t>task, assignment, project</t>
+  </si>
+  <si>
+    <t>versa-lag</t>
+  </si>
+  <si>
+    <t>version, update</t>
+  </si>
+  <si>
+    <t>versi</t>
+  </si>
+  <si>
+    <t>verse, stanza</t>
+  </si>
+  <si>
+    <t>versla</t>
+  </si>
+  <si>
+    <t>to sell, to market, to advertise</t>
+  </si>
+  <si>
+    <t>verslu-kona</t>
+  </si>
+  <si>
+    <t>merchant woman</t>
+  </si>
+  <si>
+    <t>verslu-maðr</t>
+  </si>
+  <si>
+    <t>merchant</t>
+  </si>
+  <si>
+    <t>verslun</t>
+  </si>
+  <si>
+    <t>shop, store, emporium</t>
+  </si>
+  <si>
+    <t>vestr (1)</t>
+  </si>
+  <si>
+    <t>west</t>
+  </si>
+  <si>
+    <t>vestr (2)</t>
+  </si>
+  <si>
+    <t>westwards</t>
+  </si>
+  <si>
+    <t>vetr</t>
+  </si>
+  <si>
+    <t>winter (season)</t>
+  </si>
+  <si>
+    <t>við-list</t>
+  </si>
+  <si>
+    <t>woodwork, woodcarving</t>
+  </si>
+  <si>
+    <t>við-stafr</t>
+  </si>
+  <si>
+    <t>walking staff, fighting staff, quarterstaff</t>
+  </si>
+  <si>
+    <t>við-støttva</t>
+  </si>
+  <si>
+    <t>figurine, carving (of wood)</t>
+  </si>
+  <si>
+    <t>víðir</t>
+  </si>
+  <si>
+    <t>willow</t>
+  </si>
+  <si>
+    <t>viðr</t>
+  </si>
+  <si>
+    <t>wood, timber</t>
+  </si>
+  <si>
+    <t>víg</t>
+  </si>
+  <si>
+    <t>slaying, killing</t>
+  </si>
+  <si>
+    <t>víg-maðr</t>
+  </si>
+  <si>
+    <t>a slayer</t>
+  </si>
+  <si>
+    <t>víg-tøn</t>
+  </si>
+  <si>
+    <t>fang</t>
+  </si>
+  <si>
+    <t>vík</t>
+  </si>
+  <si>
+    <t>bay, cove, inlet</t>
+  </si>
+  <si>
+    <t>vika</t>
+  </si>
+  <si>
+    <t>week</t>
+  </si>
+  <si>
+    <t>víkja</t>
+  </si>
+  <si>
+    <t>to retreat</t>
+  </si>
+  <si>
+    <t>vilja</t>
+  </si>
+  <si>
+    <t>to want</t>
+  </si>
+  <si>
+    <t>villa-</t>
+  </si>
+  <si>
+    <t>wild-</t>
+  </si>
+  <si>
+    <t>villa-maðr</t>
+  </si>
+  <si>
+    <t>one who comes from the wilderness, one who lives in the wild</t>
+  </si>
+  <si>
+    <t>villa-mørk</t>
+  </si>
+  <si>
+    <t>nature, wilderness</t>
+  </si>
+  <si>
+    <t>villa-svín</t>
+  </si>
+  <si>
+    <t>wild boar</t>
+  </si>
+  <si>
+    <t>villi</t>
+  </si>
+  <si>
+    <t>nature, wilderness (poetic)</t>
+  </si>
+  <si>
+    <t>vín</t>
+  </si>
+  <si>
+    <t>wine</t>
+  </si>
+  <si>
+    <t>vín-kona</t>
+  </si>
+  <si>
+    <t>barmaid</t>
+  </si>
+  <si>
+    <t>vin-liga</t>
+  </si>
+  <si>
+    <t>please</t>
+  </si>
+  <si>
+    <t>vín-maðr</t>
+  </si>
+  <si>
+    <t>bartender, barkeep, barkeeper</t>
+  </si>
+  <si>
+    <t>vind-eyga</t>
+  </si>
+  <si>
+    <t>window</t>
+  </si>
+  <si>
+    <t>vindr</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>vinna</t>
+  </si>
+  <si>
+    <t>to win</t>
+  </si>
+  <si>
+    <t>vinr</t>
+  </si>
+  <si>
+    <t>friend</t>
+  </si>
+  <si>
+    <t>vinstra</t>
+  </si>
+  <si>
+    <t>left (direction)</t>
+  </si>
+  <si>
+    <t>vinstri</t>
+  </si>
+  <si>
+    <t>left (position)</t>
+  </si>
+  <si>
+    <t>virð-leiki</t>
+  </si>
+  <si>
+    <t>respect, manners, ettiquette</t>
+  </si>
+  <si>
+    <t>virða</t>
+  </si>
+  <si>
+    <t>to respect, to show respect, to pay respect (with til + genitive)</t>
+  </si>
+  <si>
+    <t>virka</t>
+  </si>
+  <si>
+    <t>to work, to labour</t>
+  </si>
+  <si>
+    <t>virka-hurð</t>
+  </si>
+  <si>
+    <t>gate, door</t>
+  </si>
+  <si>
+    <t>virkandi</t>
+  </si>
+  <si>
+    <t>working; busy, unavailable</t>
+  </si>
+  <si>
+    <t>virki</t>
+  </si>
+  <si>
+    <t>castle</t>
+  </si>
+  <si>
+    <t>virku-riffill</t>
+  </si>
+  <si>
+    <t>machine gun</t>
+  </si>
+  <si>
+    <t>vírr</t>
+  </si>
+  <si>
+    <t>wire</t>
+  </si>
+  <si>
+    <t>viskari</t>
+  </si>
+  <si>
+    <t>worker</t>
+  </si>
+  <si>
+    <t>víski</t>
+  </si>
+  <si>
+    <t>whiskey</t>
+  </si>
+  <si>
+    <t>vit</t>
+  </si>
+  <si>
+    <t>1st person plural</t>
+  </si>
+  <si>
+    <t>vit-leggja</t>
+  </si>
+  <si>
+    <t>to plan, to strategise, to scheme</t>
+  </si>
+  <si>
+    <t>vit-máll</t>
+  </si>
+  <si>
+    <t>wise in speech</t>
+  </si>
+  <si>
+    <t>vita</t>
+  </si>
+  <si>
+    <t>to know</t>
+  </si>
+  <si>
+    <t>vøðvi</t>
+  </si>
+  <si>
+    <t>muscle, flesh (of a person)</t>
+  </si>
+  <si>
+    <t>vøllr</t>
+  </si>
+  <si>
+    <t>field, flat ground, meadow</t>
+  </si>
+  <si>
+    <t>vølva</t>
+  </si>
+  <si>
+    <t>seeress (a woman who practises seiðr)</t>
+  </si>
+  <si>
+    <t>vømpur-ligr</t>
+  </si>
+  <si>
+    <t>vampiric</t>
+  </si>
+  <si>
+    <t>vøngr</t>
+  </si>
+  <si>
+    <t>wing</t>
+  </si>
+  <si>
+    <t>vør</t>
   </si>
   <si>
     <t>lip (lips) (usually used in plural)</t>
-  </si>
-  <si>
-    <t>var-kárr</t>
-  </si>
-  <si>
-    <t>careful, cautious, wary</t>
-  </si>
-  <si>
-    <t>var-merki</t>
-  </si>
-  <si>
-    <t>info sign, notice sign, warning sign, placard</t>
-  </si>
-  <si>
-    <t>vara</t>
-  </si>
-  <si>
-    <t>to warn (with accusative)</t>
-  </si>
-  <si>
-    <t>varangr</t>
-  </si>
-  <si>
-    <t>Varangian</t>
-  </si>
-  <si>
-    <t>varða</t>
-  </si>
-  <si>
-    <t>to ward, to protect (with accusative "who/what" + frá + dative "from who/what")</t>
-  </si>
-  <si>
-    <t>varða-torn</t>
-  </si>
-  <si>
-    <t>watchtower</t>
-  </si>
-  <si>
-    <t>varðandi</t>
-  </si>
-  <si>
-    <t>protective</t>
-  </si>
-  <si>
-    <t>varma</t>
-  </si>
-  <si>
-    <t>to warm (with accusative)</t>
-  </si>
-  <si>
-    <t>varmr</t>
-  </si>
-  <si>
-    <t>warm</t>
-  </si>
-  <si>
-    <t>varpa</t>
-  </si>
-  <si>
-    <t>to shed, to take off, to cause to fall off</t>
-  </si>
-  <si>
-    <t>varr</t>
-  </si>
-  <si>
-    <t>wary (archaic)</t>
-  </si>
-  <si>
-    <t>varta</t>
-  </si>
-  <si>
-    <t>wart</t>
-  </si>
-  <si>
-    <t>vas</t>
-  </si>
-  <si>
-    <t>vase</t>
-  </si>
-  <si>
-    <t>Vatakonda</t>
-  </si>
-  <si>
-    <t>Vatakond (a kingdom in Myrkjørð)</t>
-  </si>
-  <si>
-    <t>vatn</t>
-  </si>
-  <si>
-    <t>water</t>
-  </si>
-  <si>
-    <t>vatns-gefari</t>
-  </si>
-  <si>
-    <t>tap, faucet</t>
-  </si>
-  <si>
-    <t>vatns-høld</t>
-  </si>
-  <si>
-    <t>water reservoir</t>
-  </si>
-  <si>
-    <t>vátr</t>
-  </si>
-  <si>
-    <t>wet</t>
-  </si>
-  <si>
-    <t>vax</t>
-  </si>
-  <si>
-    <t>wax</t>
-  </si>
-  <si>
-    <t>vaxa (1)</t>
-  </si>
-  <si>
-    <t>to grow, to age (intransitive)</t>
-  </si>
-  <si>
-    <t>vaxa (2)</t>
-  </si>
-  <si>
-    <t>to wax (with accusative)</t>
-  </si>
-  <si>
-    <t>veðr</t>
-  </si>
-  <si>
-    <t>weather</t>
-  </si>
-  <si>
-    <t>vefa</t>
-  </si>
-  <si>
-    <t>to weave, to knit, to tailor</t>
-  </si>
-  <si>
-    <t>vefr</t>
-  </si>
-  <si>
-    <t>web (of a spider); fishing net</t>
-  </si>
-  <si>
-    <t>veg-steinn</t>
-  </si>
-  <si>
-    <t>pavement, cobblestone; a symbol carved on a rock for good fortune; a vegvísir stone; a lucky charm</t>
-  </si>
-  <si>
-    <t>veg-streymr</t>
-  </si>
-  <si>
-    <t>traffic</t>
-  </si>
-  <si>
-    <t>vega</t>
-  </si>
-  <si>
-    <t>to travel, to navigate</t>
-  </si>
-  <si>
-    <t>vegna</t>
-  </si>
-  <si>
-    <t>because</t>
-  </si>
-  <si>
-    <t>vegr</t>
-  </si>
-  <si>
-    <t>road, street, path, way</t>
-  </si>
-  <si>
-    <t>veiða</t>
-  </si>
-  <si>
-    <t>to hunt, to fish (with accusative)</t>
-  </si>
-  <si>
-    <t>veifa</t>
-  </si>
-  <si>
-    <t>to swing, to wave (with accusative)</t>
-  </si>
-  <si>
-    <t>veiki</t>
-  </si>
-  <si>
-    <t>weakness; illness, sickness</t>
-  </si>
-  <si>
-    <t>veikja</t>
-  </si>
-  <si>
-    <t>to weaken</t>
-  </si>
-  <si>
-    <t>veikr</t>
-  </si>
-  <si>
-    <t>weak</t>
-  </si>
-  <si>
-    <t>veikr í hugi</t>
-  </si>
-  <si>
-    <t>sick in the head; crazy, out of one's mind</t>
-  </si>
-  <si>
-    <t>veira</t>
-  </si>
-  <si>
-    <t>virus (biology); malware, virus, trojan</t>
-  </si>
-  <si>
-    <t>vekja</t>
-  </si>
-  <si>
-    <t>to cause to wake (with accusative)</t>
-  </si>
-  <si>
-    <t>vel</t>
-  </si>
-  <si>
-    <t>well, good (velr = better, velst = best)</t>
-  </si>
-  <si>
-    <t>vel-eyðinn</t>
-  </si>
-  <si>
-    <t>successful</t>
-  </si>
-  <si>
-    <t>vel-kominn</t>
-  </si>
-  <si>
-    <t>welcomed, gladly received (not used as a phrase!)</t>
-  </si>
-  <si>
-    <t>Veldalfheimr</t>
-  </si>
-  <si>
-    <t>world of the fey</t>
-  </si>
-  <si>
-    <t>veldi</t>
-  </si>
-  <si>
-    <t>kingdom, realm, empire; power, reign</t>
-  </si>
-  <si>
-    <t>velja</t>
-  </si>
-  <si>
-    <t>to choose, to select</t>
-  </si>
-  <si>
-    <t>venja (1)</t>
-  </si>
-  <si>
-    <t>to teach, to train, to coach, to guide</t>
-  </si>
-  <si>
-    <t>venja (2)</t>
-  </si>
-  <si>
-    <t>teaching, guidance; habit, tendency</t>
-  </si>
-  <si>
-    <t>venju-liga</t>
-  </si>
-  <si>
-    <t>normally, usually</t>
-  </si>
-  <si>
-    <t>venju-ligr</t>
-  </si>
-  <si>
-    <t>normal, usual, ordinary, common</t>
-  </si>
-  <si>
-    <t>vera</t>
-  </si>
-  <si>
-    <t>to be (with nominative)</t>
-  </si>
-  <si>
-    <t>vera í eldi</t>
-  </si>
-  <si>
-    <t>to be on fire</t>
-  </si>
-  <si>
-    <t>vera varkárr</t>
-  </si>
-  <si>
-    <t>to be careful, to beware</t>
-  </si>
-  <si>
-    <t>verð-leyss</t>
-  </si>
-  <si>
-    <t>worthless, without value</t>
-  </si>
-  <si>
-    <t>verða</t>
-  </si>
-  <si>
-    <t>to become (with nominative); will be, will turn out (with nominative)</t>
-  </si>
-  <si>
-    <t>verðr</t>
-  </si>
-  <si>
-    <t>worthy, valueable; expensive</t>
-  </si>
-  <si>
-    <t>veri</t>
-  </si>
-  <si>
-    <t>creation, creature, animal, monster</t>
-  </si>
-  <si>
-    <t>verk</t>
-  </si>
-  <si>
-    <t>action, deed, doing</t>
-  </si>
-  <si>
-    <t>verk-mál</t>
-  </si>
-  <si>
-    <t>task, assignment, project</t>
-  </si>
-  <si>
-    <t>versa-lag</t>
-  </si>
-  <si>
-    <t>version, update</t>
-  </si>
-  <si>
-    <t>versi</t>
-  </si>
-  <si>
-    <t>verse, stanza</t>
-  </si>
-  <si>
-    <t>versla</t>
-  </si>
-  <si>
-    <t>to sell, to market, to advertise</t>
-  </si>
-  <si>
-    <t>verslu-kona</t>
-  </si>
-  <si>
-    <t>merchant woman</t>
-  </si>
-  <si>
-    <t>verslu-maðr</t>
-  </si>
-  <si>
-    <t>merchant</t>
-  </si>
-  <si>
-    <t>verslun</t>
-  </si>
-  <si>
-    <t>shop, store, emporium</t>
-  </si>
-  <si>
-    <t>vestr (1)</t>
-  </si>
-  <si>
-    <t>west</t>
-  </si>
-  <si>
-    <t>vestr (2)</t>
-  </si>
-  <si>
-    <t>westwards</t>
-  </si>
-  <si>
-    <t>vetr</t>
-  </si>
-  <si>
-    <t>winter (season)</t>
-  </si>
-  <si>
-    <t>við-list</t>
-  </si>
-  <si>
-    <t>woodwork, woodcarving</t>
-  </si>
-  <si>
-    <t>við-stafr</t>
-  </si>
-  <si>
-    <t>walking staff, fighting staff, quarterstaff</t>
-  </si>
-  <si>
-    <t>við-støttva</t>
-  </si>
-  <si>
-    <t>figurine, carving (of wood)</t>
-  </si>
-  <si>
-    <t>víðir</t>
-  </si>
-  <si>
-    <t>willow</t>
-  </si>
-  <si>
-    <t>viðr</t>
-  </si>
-  <si>
-    <t>wood, timber</t>
-  </si>
-  <si>
-    <t>víg</t>
-  </si>
-  <si>
-    <t>slaying, killing</t>
-  </si>
-  <si>
-    <t>víg-maðr</t>
-  </si>
-  <si>
-    <t>a slayer</t>
-  </si>
-  <si>
-    <t>víg-tøn</t>
-  </si>
-  <si>
-    <t>fang</t>
-  </si>
-  <si>
-    <t>vík</t>
-  </si>
-  <si>
-    <t>bay, cove, inlet</t>
-  </si>
-  <si>
-    <t>vika</t>
-  </si>
-  <si>
-    <t>week</t>
-  </si>
-  <si>
-    <t>víkja</t>
-  </si>
-  <si>
-    <t>to retreat</t>
-  </si>
-  <si>
-    <t>vilja</t>
-  </si>
-  <si>
-    <t>to want</t>
-  </si>
-  <si>
-    <t>villa-</t>
-  </si>
-  <si>
-    <t>wild-</t>
-  </si>
-  <si>
-    <t>villa-maðr</t>
-  </si>
-  <si>
-    <t>one who comes from the wilderness, one who lives in the wild</t>
-  </si>
-  <si>
-    <t>villa-mørk</t>
-  </si>
-  <si>
-    <t>nature, wilderness</t>
-  </si>
-  <si>
-    <t>villa-svín</t>
-  </si>
-  <si>
-    <t>wild boar</t>
-  </si>
-  <si>
-    <t>villi</t>
-  </si>
-  <si>
-    <t>nature, wilderness (poetic)</t>
-  </si>
-  <si>
-    <t>vín</t>
-  </si>
-  <si>
-    <t>wine</t>
-  </si>
-  <si>
-    <t>vín-kona</t>
-  </si>
-  <si>
-    <t>barmaid</t>
-  </si>
-  <si>
-    <t>vin-liga</t>
-  </si>
-  <si>
-    <t>please</t>
-  </si>
-  <si>
-    <t>vín-maðr</t>
-  </si>
-  <si>
-    <t>bartender, barkeep, barkeeper</t>
-  </si>
-  <si>
-    <t>vind-eyga</t>
-  </si>
-  <si>
-    <t>window</t>
-  </si>
-  <si>
-    <t>vindr</t>
-  </si>
-  <si>
-    <t>wind</t>
-  </si>
-  <si>
-    <t>vinna</t>
-  </si>
-  <si>
-    <t>to win</t>
-  </si>
-  <si>
-    <t>vinr</t>
-  </si>
-  <si>
-    <t>friend</t>
-  </si>
-  <si>
-    <t>vinstra</t>
-  </si>
-  <si>
-    <t>left (direction)</t>
-  </si>
-  <si>
-    <t>vinstri</t>
-  </si>
-  <si>
-    <t>left (position)</t>
-  </si>
-  <si>
-    <t>virð-leiki</t>
-  </si>
-  <si>
-    <t>respect, manners, ettiquette</t>
-  </si>
-  <si>
-    <t>virða</t>
-  </si>
-  <si>
-    <t>to respect, to show respect, to pay respect (with til + genitive)</t>
-  </si>
-  <si>
-    <t>virka</t>
-  </si>
-  <si>
-    <t>to work, to labour</t>
-  </si>
-  <si>
-    <t>virka-hurð</t>
-  </si>
-  <si>
-    <t>gate, door</t>
-  </si>
-  <si>
-    <t>virkandi</t>
-  </si>
-  <si>
-    <t>working; busy, unavailable</t>
-  </si>
-  <si>
-    <t>virki</t>
-  </si>
-  <si>
-    <t>castle</t>
-  </si>
-  <si>
-    <t>virku-riffill</t>
-  </si>
-  <si>
-    <t>machine gun</t>
-  </si>
-  <si>
-    <t>vírr</t>
-  </si>
-  <si>
-    <t>wire</t>
-  </si>
-  <si>
-    <t>viskari</t>
-  </si>
-  <si>
-    <t>worker</t>
-  </si>
-  <si>
-    <t>víski</t>
-  </si>
-  <si>
-    <t>whiskey</t>
-  </si>
-  <si>
-    <t>vit</t>
-  </si>
-  <si>
-    <t>1st person plural</t>
-  </si>
-  <si>
-    <t>vit-leggja</t>
-  </si>
-  <si>
-    <t>to plan, to strategise, to scheme</t>
-  </si>
-  <si>
-    <t>vit-máll</t>
-  </si>
-  <si>
-    <t>wise in speech</t>
-  </si>
-  <si>
-    <t>vita</t>
-  </si>
-  <si>
-    <t>to know</t>
-  </si>
-  <si>
-    <t>vøðvi</t>
-  </si>
-  <si>
-    <t>muscle, flesh (of a person)</t>
-  </si>
-  <si>
-    <t>vøllr</t>
-  </si>
-  <si>
-    <t>field, flat ground, meadow</t>
-  </si>
-  <si>
-    <t>vølva</t>
-  </si>
-  <si>
-    <t>seeress (a woman who practises seiðr)</t>
-  </si>
-  <si>
-    <t>vømpur-ligr</t>
-  </si>
-  <si>
-    <t>vampiric</t>
-  </si>
-  <si>
-    <t>vøngr</t>
-  </si>
-  <si>
-    <t>wing</t>
-  </si>
-  <si>
-    <t>vør</t>
-  </si>
-  <si>
-    <t>spring (season)</t>
   </si>
   <si>
     <t>vørð</t>
@@ -16375,6 +16375,9 @@
   </si>
   <si>
     <t>er</t>
+  </si>
+  <si>
+    <t>var</t>
   </si>
   <si>
     <t>fer</t>
@@ -44098,7 +44101,7 @@
       <c r="C2010" s="3" t="s">
         <v>4058</v>
       </c>
-      <c r="D2010" s="3"/>
+      <c r="D2010" s="5"/>
     </row>
     <row r="2011" ht="18.75" customHeight="1">
       <c r="A2011" s="3" t="s">
@@ -45498,7 +45501,7 @@
       <c r="C2122" s="3" t="s">
         <v>4282</v>
       </c>
-      <c r="D2122" s="5"/>
+      <c r="D2122" s="3"/>
     </row>
     <row r="2123" ht="18.75" customHeight="1">
       <c r="A2123" s="3" t="s">
@@ -54792,31 +54795,31 @@
         <v>5439</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>4057</v>
+        <v>5440</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>5440</v>
+        <v>5441</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>5441</v>
+        <v>5442</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>5442</v>
+        <v>5443</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>5443</v>
+        <v>5444</v>
       </c>
       <c r="I76" s="23" t="s">
-        <v>5444</v>
+        <v>5445</v>
       </c>
       <c r="J76" s="25" t="s">
-        <v>5445</v>
+        <v>5446</v>
       </c>
       <c r="K76" s="23" t="s">
-        <v>5446</v>
+        <v>5447</v>
       </c>
       <c r="L76" s="25" t="s">
-        <v>5447</v>
+        <v>5448</v>
       </c>
     </row>
     <row r="77" ht="18.75" customHeight="1">
@@ -54825,34 +54828,34 @@
         <v>4434</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="D77" s="25" t="s">
-        <v>5449</v>
+        <v>5450</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>5450</v>
+        <v>5451</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>5451</v>
+        <v>5452</v>
       </c>
       <c r="G77" s="10" t="s">
         <v>4912</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>5452</v>
+        <v>5453</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>5453</v>
+        <v>5454</v>
       </c>
       <c r="J77" s="25" t="s">
-        <v>5454</v>
+        <v>5455</v>
       </c>
       <c r="K77" s="23" t="s">
-        <v>5455</v>
+        <v>5456</v>
       </c>
       <c r="L77" s="25" t="s">
-        <v>5456</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="78" ht="18.75" customHeight="1">
@@ -54864,31 +54867,31 @@
         <v>5439</v>
       </c>
       <c r="D78" s="25" t="s">
-        <v>4057</v>
+        <v>5440</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>5440</v>
+        <v>5441</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>5441</v>
+        <v>5442</v>
       </c>
       <c r="G78" s="10" t="s">
         <v>4912</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>5443</v>
+        <v>5444</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>5453</v>
+        <v>5454</v>
       </c>
       <c r="J78" s="25" t="s">
-        <v>5445</v>
+        <v>5446</v>
       </c>
       <c r="K78" s="23" t="s">
-        <v>5455</v>
+        <v>5456</v>
       </c>
       <c r="L78" s="25" t="s">
-        <v>5457</v>
+        <v>5458</v>
       </c>
     </row>
     <row r="79" ht="18.75" customHeight="1">
@@ -54899,34 +54902,34 @@
         <v>4263</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="D79" s="25" t="s">
-        <v>5459</v>
+        <v>5460</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>5460</v>
+        <v>5461</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>5461</v>
+        <v>5462</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>5462</v>
+        <v>5463</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>5463</v>
+        <v>5464</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>5464</v>
+        <v>5465</v>
       </c>
       <c r="J79" s="25" t="s">
-        <v>5465</v>
+        <v>5466</v>
       </c>
       <c r="K79" s="23" t="s">
-        <v>5466</v>
+        <v>5467</v>
       </c>
       <c r="L79" s="25" t="s">
-        <v>5467</v>
+        <v>5468</v>
       </c>
     </row>
     <row r="80" ht="18.75" customHeight="1">
@@ -54935,34 +54938,34 @@
         <v>4384</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>5469</v>
+        <v>5470</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>5470</v>
+        <v>5471</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>5471</v>
+        <v>5472</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>5472</v>
+        <v>5473</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>5473</v>
+        <v>5474</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>5474</v>
+        <v>5475</v>
       </c>
       <c r="J80" s="25" t="s">
-        <v>5475</v>
+        <v>5476</v>
       </c>
       <c r="K80" s="23" t="s">
-        <v>5476</v>
+        <v>5477</v>
       </c>
       <c r="L80" s="25" t="s">
-        <v>5477</v>
+        <v>5478</v>
       </c>
     </row>
     <row r="81" ht="18.75" customHeight="1">
@@ -54971,34 +54974,34 @@
         <v>5172</v>
       </c>
       <c r="C81" s="27" t="s">
-        <v>5478</v>
+        <v>5479</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>5479</v>
+        <v>5480</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>5480</v>
+        <v>5481</v>
       </c>
       <c r="F81" s="28" t="s">
-        <v>5481</v>
+        <v>5482</v>
       </c>
       <c r="G81" s="27" t="s">
-        <v>5482</v>
+        <v>5483</v>
       </c>
       <c r="H81" s="27" t="s">
-        <v>5483</v>
+        <v>5484</v>
       </c>
       <c r="I81" s="23" t="s">
-        <v>5484</v>
+        <v>5485</v>
       </c>
       <c r="J81" s="25" t="s">
-        <v>5485</v>
+        <v>5486</v>
       </c>
       <c r="K81" s="23" t="s">
-        <v>5486</v>
+        <v>5487</v>
       </c>
       <c r="L81" s="25" t="s">
-        <v>5487</v>
+        <v>5488</v>
       </c>
     </row>
     <row r="82" ht="18.75" customHeight="1">
@@ -55040,16 +55043,16 @@
       <c r="G83" s="10"/>
       <c r="H83" s="10"/>
       <c r="I83" s="23" t="s">
-        <v>5488</v>
+        <v>5489</v>
       </c>
       <c r="J83" s="25" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="K83" s="23" t="s">
-        <v>5490</v>
+        <v>5491</v>
       </c>
       <c r="L83" s="25" t="s">
-        <v>5491</v>
+        <v>5492</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10"/>
@@ -55111,16 +55114,16 @@
       <c r="G86" s="10"/>
       <c r="H86" s="10"/>
       <c r="I86" s="23" t="s">
-        <v>5492</v>
+        <v>5493</v>
       </c>
       <c r="J86" s="25" t="s">
-        <v>5493</v>
+        <v>5494</v>
       </c>
       <c r="K86" s="23" t="s">
-        <v>5494</v>
+        <v>5495</v>
       </c>
       <c r="L86" s="25" t="s">
-        <v>5495</v>
+        <v>5496</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10"/>
@@ -55140,16 +55143,16 @@
       <c r="G87" s="10"/>
       <c r="H87" s="10"/>
       <c r="I87" s="23" t="s">
-        <v>5496</v>
+        <v>5497</v>
       </c>
       <c r="J87" s="25" t="s">
-        <v>5497</v>
+        <v>5498</v>
       </c>
       <c r="K87" s="23" t="s">
-        <v>5498</v>
+        <v>5499</v>
       </c>
       <c r="L87" s="25" t="s">
-        <v>5499</v>
+        <v>5500</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10"/>
@@ -55203,27 +55206,27 @@
     </row>
     <row r="90" ht="18.75" customHeight="1">
       <c r="A90" s="18" t="s">
-        <v>5500</v>
+        <v>5501</v>
       </c>
       <c r="B90" s="19"/>
       <c r="C90" s="18" t="s">
-        <v>5501</v>
+        <v>5502</v>
       </c>
       <c r="D90" s="19"/>
       <c r="E90" s="18" t="s">
-        <v>5502</v>
+        <v>5503</v>
       </c>
       <c r="F90" s="19"/>
       <c r="G90" s="18" t="s">
-        <v>5503</v>
+        <v>5504</v>
       </c>
       <c r="H90" s="19"/>
       <c r="I90" s="18" t="s">
-        <v>5504</v>
+        <v>5505</v>
       </c>
       <c r="J90" s="19"/>
       <c r="K90" s="18" t="s">
-        <v>5505</v>
+        <v>5506</v>
       </c>
       <c r="L90" s="19"/>
       <c r="M90" s="10"/>
@@ -55236,27 +55239,27 @@
     </row>
     <row r="91" ht="18.75" customHeight="1">
       <c r="A91" s="23" t="s">
-        <v>5506</v>
+        <v>5507</v>
       </c>
       <c r="B91" s="22"/>
       <c r="C91" s="23" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="D91" s="22"/>
       <c r="E91" s="23" t="s">
-        <v>5508</v>
+        <v>5509</v>
       </c>
       <c r="F91" s="22"/>
       <c r="G91" s="23" t="s">
-        <v>5509</v>
+        <v>5510</v>
       </c>
       <c r="H91" s="22"/>
       <c r="I91" s="23" t="s">
-        <v>5510</v>
+        <v>5511</v>
       </c>
       <c r="J91" s="22"/>
       <c r="K91" s="23" t="s">
-        <v>5511</v>
+        <v>5512</v>
       </c>
       <c r="L91" s="22"/>
       <c r="M91" s="10"/>
@@ -55269,27 +55272,27 @@
     </row>
     <row r="92" ht="18.75" customHeight="1">
       <c r="A92" s="23" t="s">
-        <v>5512</v>
+        <v>5513</v>
       </c>
       <c r="B92" s="22"/>
       <c r="C92" s="23" t="s">
-        <v>5513</v>
+        <v>5514</v>
       </c>
       <c r="D92" s="22"/>
       <c r="E92" s="23" t="s">
-        <v>5514</v>
+        <v>5515</v>
       </c>
       <c r="F92" s="22"/>
       <c r="G92" s="23" t="s">
-        <v>5515</v>
+        <v>5516</v>
       </c>
       <c r="H92" s="22"/>
       <c r="I92" s="23" t="s">
-        <v>5516</v>
+        <v>5517</v>
       </c>
       <c r="J92" s="22"/>
       <c r="K92" s="23" t="s">
-        <v>5517</v>
+        <v>5518</v>
       </c>
       <c r="L92" s="22"/>
       <c r="M92" s="10"/>
@@ -55302,27 +55305,27 @@
     </row>
     <row r="93" ht="18.75" customHeight="1">
       <c r="A93" s="23" t="s">
-        <v>5518</v>
+        <v>5519</v>
       </c>
       <c r="B93" s="22"/>
       <c r="C93" s="23" t="s">
-        <v>5519</v>
+        <v>5520</v>
       </c>
       <c r="D93" s="22"/>
       <c r="E93" s="23" t="s">
-        <v>5520</v>
+        <v>5521</v>
       </c>
       <c r="F93" s="22"/>
       <c r="G93" s="23" t="s">
-        <v>5521</v>
+        <v>5522</v>
       </c>
       <c r="H93" s="22"/>
       <c r="I93" s="23" t="s">
-        <v>5522</v>
+        <v>5523</v>
       </c>
       <c r="J93" s="22"/>
       <c r="K93" s="23" t="s">
-        <v>5523</v>
+        <v>5524</v>
       </c>
       <c r="L93" s="22"/>
       <c r="M93" s="10"/>
@@ -55380,40 +55383,40 @@
     </row>
     <row r="95" ht="18.75" customHeight="1">
       <c r="A95" s="23" t="s">
-        <v>5524</v>
+        <v>5525</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>5525</v>
+        <v>5526</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>5526</v>
+        <v>5527</v>
       </c>
       <c r="D95" s="25" t="s">
-        <v>5527</v>
+        <v>5528</v>
       </c>
       <c r="E95" s="23" t="s">
-        <v>5528</v>
+        <v>5529</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>5529</v>
+        <v>5530</v>
       </c>
       <c r="G95" s="23" t="s">
-        <v>5530</v>
+        <v>5531</v>
       </c>
       <c r="H95" s="25" t="s">
-        <v>5531</v>
+        <v>5532</v>
       </c>
       <c r="I95" s="23" t="s">
-        <v>5532</v>
+        <v>5533</v>
       </c>
       <c r="J95" s="25" t="s">
-        <v>5533</v>
+        <v>5534</v>
       </c>
       <c r="K95" s="23" t="s">
-        <v>5534</v>
+        <v>5535</v>
       </c>
       <c r="L95" s="25" t="s">
-        <v>5535</v>
+        <v>5536</v>
       </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10"/>
@@ -55425,40 +55428,40 @@
     </row>
     <row r="96" ht="18.75" customHeight="1">
       <c r="A96" s="23" t="s">
-        <v>5536</v>
+        <v>5537</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>5537</v>
+        <v>5538</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>5538</v>
+        <v>5539</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>5539</v>
+        <v>5540</v>
       </c>
       <c r="E96" s="23" t="s">
-        <v>5540</v>
+        <v>5541</v>
       </c>
       <c r="F96" s="25" t="s">
-        <v>5541</v>
+        <v>5542</v>
       </c>
       <c r="G96" s="23" t="s">
-        <v>5542</v>
+        <v>5543</v>
       </c>
       <c r="H96" s="25" t="s">
-        <v>5543</v>
+        <v>5544</v>
       </c>
       <c r="I96" s="23" t="s">
         <v>2214</v>
       </c>
       <c r="J96" s="25" t="s">
-        <v>5544</v>
+        <v>5545</v>
       </c>
       <c r="K96" s="23" t="s">
-        <v>5545</v>
+        <v>5546</v>
       </c>
       <c r="L96" s="25" t="s">
-        <v>5546</v>
+        <v>5547</v>
       </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10"/>
@@ -55470,40 +55473,40 @@
     </row>
     <row r="97" ht="18.75" customHeight="1">
       <c r="A97" s="23" t="s">
-        <v>5536</v>
+        <v>5537</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>5547</v>
+        <v>5548</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>5538</v>
+        <v>5539</v>
       </c>
       <c r="D97" s="25" t="s">
-        <v>5548</v>
+        <v>5549</v>
       </c>
       <c r="E97" s="23" t="s">
-        <v>5540</v>
+        <v>5541</v>
       </c>
       <c r="F97" s="25" t="s">
-        <v>5529</v>
+        <v>5530</v>
       </c>
       <c r="G97" s="23" t="s">
-        <v>5530</v>
+        <v>5531</v>
       </c>
       <c r="H97" s="25" t="s">
-        <v>5549</v>
+        <v>5550</v>
       </c>
       <c r="I97" s="23" t="s">
         <v>2214</v>
       </c>
       <c r="J97" s="25" t="s">
-        <v>5550</v>
+        <v>5551</v>
       </c>
       <c r="K97" s="23" t="s">
-        <v>5545</v>
+        <v>5546</v>
       </c>
       <c r="L97" s="25" t="s">
-        <v>5535</v>
+        <v>5536</v>
       </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10"/>
@@ -55515,40 +55518,40 @@
     </row>
     <row r="98" ht="18.75" customHeight="1">
       <c r="A98" s="23" t="s">
-        <v>5551</v>
+        <v>5552</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>5552</v>
+        <v>5553</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>5553</v>
+        <v>5554</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>5554</v>
+        <v>5555</v>
       </c>
       <c r="E98" s="23" t="s">
-        <v>5555</v>
+        <v>5556</v>
       </c>
       <c r="F98" s="25" t="s">
-        <v>5556</v>
+        <v>5557</v>
       </c>
       <c r="G98" s="23" t="s">
-        <v>5557</v>
+        <v>5558</v>
       </c>
       <c r="H98" s="25" t="s">
-        <v>5558</v>
+        <v>5559</v>
       </c>
       <c r="I98" s="23" t="s">
-        <v>5559</v>
+        <v>5560</v>
       </c>
       <c r="J98" s="25" t="s">
-        <v>5560</v>
+        <v>5561</v>
       </c>
       <c r="K98" s="23" t="s">
-        <v>5561</v>
+        <v>5562</v>
       </c>
       <c r="L98" s="25" t="s">
-        <v>5562</v>
+        <v>5563</v>
       </c>
       <c r="M98" s="10"/>
       <c r="N98" s="10"/>
@@ -55560,40 +55563,40 @@
     </row>
     <row r="99" ht="18.75" customHeight="1">
       <c r="A99" s="23" t="s">
-        <v>5563</v>
+        <v>5564</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>5564</v>
+        <v>5565</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>5565</v>
+        <v>5566</v>
       </c>
       <c r="D99" s="25" t="s">
-        <v>5566</v>
+        <v>5567</v>
       </c>
       <c r="E99" s="23" t="s">
-        <v>5567</v>
+        <v>5568</v>
       </c>
       <c r="F99" s="25" t="s">
-        <v>5568</v>
+        <v>5569</v>
       </c>
       <c r="G99" s="23" t="s">
-        <v>5569</v>
+        <v>5570</v>
       </c>
       <c r="H99" s="25" t="s">
-        <v>5570</v>
+        <v>5571</v>
       </c>
       <c r="I99" s="23" t="s">
-        <v>5571</v>
+        <v>5572</v>
       </c>
       <c r="J99" s="25" t="s">
-        <v>5572</v>
+        <v>5573</v>
       </c>
       <c r="K99" s="23" t="s">
-        <v>5573</v>
+        <v>5574</v>
       </c>
       <c r="L99" s="25" t="s">
-        <v>5574</v>
+        <v>5575</v>
       </c>
       <c r="M99" s="10"/>
       <c r="N99" s="10"/>
@@ -55605,40 +55608,40 @@
     </row>
     <row r="100" ht="18.75" customHeight="1">
       <c r="A100" s="36" t="s">
-        <v>5575</v>
+        <v>5576</v>
       </c>
       <c r="B100" s="28" t="s">
-        <v>5576</v>
+        <v>5577</v>
       </c>
       <c r="C100" s="36" t="s">
-        <v>5577</v>
+        <v>5578</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>5578</v>
+        <v>5579</v>
       </c>
       <c r="E100" s="23" t="s">
-        <v>5579</v>
+        <v>5580</v>
       </c>
       <c r="F100" s="25" t="s">
-        <v>5580</v>
+        <v>5581</v>
       </c>
       <c r="G100" s="36" t="s">
-        <v>5581</v>
+        <v>5582</v>
       </c>
       <c r="H100" s="28" t="s">
-        <v>5582</v>
+        <v>5583</v>
       </c>
       <c r="I100" s="36" t="s">
-        <v>5583</v>
+        <v>5584</v>
       </c>
       <c r="J100" s="28" t="s">
-        <v>5584</v>
+        <v>5585</v>
       </c>
       <c r="K100" s="36" t="s">
-        <v>5585</v>
+        <v>5586</v>
       </c>
       <c r="L100" s="28" t="s">
-        <v>5586</v>
+        <v>5587</v>
       </c>
       <c r="M100" s="10"/>
       <c r="N100" s="10"/>
@@ -55675,10 +55678,10 @@
       <c r="A102" s="10"/>
       <c r="B102" s="10"/>
       <c r="E102" s="23" t="s">
-        <v>5587</v>
+        <v>5588</v>
       </c>
       <c r="F102" s="25" t="s">
-        <v>5588</v>
+        <v>5589</v>
       </c>
       <c r="G102" s="10"/>
       <c r="H102" s="10"/>
@@ -55736,10 +55739,10 @@
       <c r="A105" s="10"/>
       <c r="B105" s="10"/>
       <c r="E105" s="23" t="s">
-        <v>5589</v>
+        <v>5590</v>
       </c>
       <c r="F105" s="25" t="s">
-        <v>5590</v>
+        <v>5591</v>
       </c>
       <c r="G105" s="10"/>
       <c r="H105" s="10"/>
@@ -55759,10 +55762,10 @@
       <c r="A106" s="10"/>
       <c r="B106" s="10"/>
       <c r="E106" s="23" t="s">
-        <v>5591</v>
+        <v>5592</v>
       </c>
       <c r="F106" s="25" t="s">
-        <v>5592</v>
+        <v>5593</v>
       </c>
       <c r="G106" s="10"/>
       <c r="H106" s="10"/>
@@ -55820,27 +55823,27 @@
     </row>
     <row r="109" ht="18.75" customHeight="1">
       <c r="A109" s="18" t="s">
-        <v>5593</v>
+        <v>5594</v>
       </c>
       <c r="B109" s="19"/>
       <c r="C109" s="18" t="s">
-        <v>5594</v>
+        <v>5595</v>
       </c>
       <c r="D109" s="19"/>
       <c r="E109" s="18" t="s">
-        <v>5595</v>
+        <v>5596</v>
       </c>
       <c r="F109" s="19"/>
       <c r="G109" s="18" t="s">
-        <v>5596</v>
+        <v>5597</v>
       </c>
       <c r="H109" s="19"/>
       <c r="I109" s="18" t="s">
-        <v>5597</v>
+        <v>5598</v>
       </c>
       <c r="J109" s="19"/>
       <c r="K109" s="18" t="s">
-        <v>5598</v>
+        <v>5599</v>
       </c>
       <c r="L109" s="19"/>
       <c r="M109" s="10"/>
@@ -55853,27 +55856,27 @@
     </row>
     <row r="110" ht="18.75" customHeight="1">
       <c r="A110" s="23" t="s">
-        <v>5599</v>
+        <v>5600</v>
       </c>
       <c r="B110" s="22"/>
       <c r="C110" s="23" t="s">
-        <v>5600</v>
+        <v>5601</v>
       </c>
       <c r="D110" s="22"/>
       <c r="E110" s="23" t="s">
-        <v>5601</v>
+        <v>5602</v>
       </c>
       <c r="F110" s="22"/>
       <c r="G110" s="23" t="s">
-        <v>5602</v>
+        <v>5603</v>
       </c>
       <c r="H110" s="22"/>
       <c r="I110" s="23" t="s">
-        <v>5603</v>
+        <v>5604</v>
       </c>
       <c r="J110" s="22"/>
       <c r="K110" s="23" t="s">
-        <v>5604</v>
+        <v>5605</v>
       </c>
       <c r="L110" s="22"/>
       <c r="M110" s="10"/>
@@ -55886,27 +55889,27 @@
     </row>
     <row r="111" ht="18.75" customHeight="1">
       <c r="A111" s="23" t="s">
-        <v>5605</v>
+        <v>5606</v>
       </c>
       <c r="B111" s="22"/>
       <c r="C111" s="23" t="s">
-        <v>5606</v>
+        <v>5607</v>
       </c>
       <c r="D111" s="22"/>
       <c r="E111" s="23" t="s">
-        <v>5607</v>
+        <v>5608</v>
       </c>
       <c r="F111" s="22"/>
       <c r="G111" s="23" t="s">
-        <v>5608</v>
+        <v>5609</v>
       </c>
       <c r="H111" s="22"/>
       <c r="I111" s="23" t="s">
-        <v>5609</v>
+        <v>5610</v>
       </c>
       <c r="J111" s="22"/>
       <c r="K111" s="23" t="s">
-        <v>5610</v>
+        <v>5611</v>
       </c>
       <c r="L111" s="22"/>
       <c r="M111" s="10"/>
@@ -55919,27 +55922,27 @@
     </row>
     <row r="112" ht="18.75" customHeight="1">
       <c r="A112" s="23" t="s">
-        <v>5611</v>
+        <v>5612</v>
       </c>
       <c r="B112" s="22"/>
       <c r="C112" s="23" t="s">
-        <v>5612</v>
+        <v>5613</v>
       </c>
       <c r="D112" s="22"/>
       <c r="E112" s="23" t="s">
-        <v>5613</v>
+        <v>5614</v>
       </c>
       <c r="F112" s="22"/>
       <c r="G112" s="23" t="s">
-        <v>5614</v>
+        <v>5615</v>
       </c>
       <c r="H112" s="22"/>
       <c r="I112" s="23" t="s">
-        <v>5615</v>
+        <v>5616</v>
       </c>
       <c r="J112" s="22"/>
       <c r="K112" s="23" t="s">
-        <v>5616</v>
+        <v>5617</v>
       </c>
       <c r="L112" s="22"/>
       <c r="M112" s="10"/>
@@ -55997,40 +56000,40 @@
     </row>
     <row r="114" ht="18.75" customHeight="1">
       <c r="A114" s="23" t="s">
-        <v>5617</v>
+        <v>5618</v>
       </c>
       <c r="B114" s="25" t="s">
         <v>4823</v>
       </c>
       <c r="C114" s="23" t="s">
-        <v>5618</v>
+        <v>5619</v>
       </c>
       <c r="D114" s="25" t="s">
-        <v>5619</v>
+        <v>5620</v>
       </c>
       <c r="E114" s="23" t="s">
-        <v>5620</v>
+        <v>5621</v>
       </c>
       <c r="F114" s="25" t="s">
-        <v>5621</v>
+        <v>5622</v>
       </c>
       <c r="G114" s="23" t="s">
-        <v>5622</v>
+        <v>5623</v>
       </c>
       <c r="H114" s="25" t="s">
-        <v>5623</v>
+        <v>5624</v>
       </c>
       <c r="I114" s="23" t="s">
         <v>796</v>
       </c>
       <c r="J114" s="25" t="s">
-        <v>5624</v>
+        <v>5625</v>
       </c>
       <c r="K114" s="23" t="s">
-        <v>5625</v>
+        <v>5626</v>
       </c>
       <c r="L114" s="25" t="s">
-        <v>5626</v>
+        <v>5627</v>
       </c>
       <c r="M114" s="10"/>
       <c r="N114" s="10"/>
@@ -56042,40 +56045,40 @@
     </row>
     <row r="115" ht="18.75" customHeight="1">
       <c r="A115" s="23" t="s">
-        <v>5627</v>
+        <v>5628</v>
       </c>
       <c r="B115" s="25" t="s">
-        <v>5628</v>
+        <v>5629</v>
       </c>
       <c r="C115" s="23" t="s">
-        <v>5629</v>
+        <v>5630</v>
       </c>
       <c r="D115" s="25" t="s">
-        <v>5630</v>
+        <v>5631</v>
       </c>
       <c r="E115" s="23" t="s">
-        <v>5631</v>
+        <v>5632</v>
       </c>
       <c r="F115" s="25" t="s">
-        <v>5632</v>
+        <v>5633</v>
       </c>
       <c r="G115" s="23" t="s">
-        <v>5633</v>
+        <v>5634</v>
       </c>
       <c r="H115" s="25" t="s">
-        <v>5634</v>
+        <v>5635</v>
       </c>
       <c r="I115" s="23" t="s">
-        <v>5635</v>
+        <v>5636</v>
       </c>
       <c r="J115" s="25" t="s">
-        <v>5636</v>
+        <v>5637</v>
       </c>
       <c r="K115" s="23" t="s">
-        <v>5637</v>
+        <v>5638</v>
       </c>
       <c r="L115" s="25" t="s">
-        <v>5638</v>
+        <v>5639</v>
       </c>
       <c r="M115" s="10"/>
       <c r="N115" s="10"/>
@@ -56087,40 +56090,40 @@
     </row>
     <row r="116" ht="18.75" customHeight="1">
       <c r="A116" s="23" t="s">
-        <v>5627</v>
+        <v>5628</v>
       </c>
       <c r="B116" s="25" t="s">
         <v>4823</v>
       </c>
       <c r="C116" s="23" t="s">
-        <v>5629</v>
+        <v>5630</v>
       </c>
       <c r="D116" s="25" t="s">
-        <v>5619</v>
+        <v>5620</v>
       </c>
       <c r="E116" s="23" t="s">
-        <v>5631</v>
+        <v>5632</v>
       </c>
       <c r="F116" s="25" t="s">
-        <v>5621</v>
+        <v>5622</v>
       </c>
       <c r="G116" s="23" t="s">
-        <v>5633</v>
+        <v>5634</v>
       </c>
       <c r="H116" s="25" t="s">
-        <v>5639</v>
+        <v>5640</v>
       </c>
       <c r="I116" s="23" t="s">
-        <v>5635</v>
+        <v>5636</v>
       </c>
       <c r="J116" s="25" t="s">
-        <v>5640</v>
+        <v>5641</v>
       </c>
       <c r="K116" s="23" t="s">
-        <v>5637</v>
+        <v>5638</v>
       </c>
       <c r="L116" s="25" t="s">
-        <v>5626</v>
+        <v>5627</v>
       </c>
       <c r="M116" s="10"/>
       <c r="N116" s="10"/>
@@ -56132,40 +56135,40 @@
     </row>
     <row r="117" ht="18.75" customHeight="1">
       <c r="A117" s="23" t="s">
-        <v>5641</v>
+        <v>5642</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>5642</v>
+        <v>5643</v>
       </c>
       <c r="C117" s="23" t="s">
-        <v>5643</v>
+        <v>5644</v>
       </c>
       <c r="D117" s="25" t="s">
-        <v>5644</v>
+        <v>5645</v>
       </c>
       <c r="E117" s="23" t="s">
-        <v>5645</v>
+        <v>5646</v>
       </c>
       <c r="F117" s="25" t="s">
-        <v>5646</v>
+        <v>5647</v>
       </c>
       <c r="G117" s="23" t="s">
-        <v>5647</v>
+        <v>5648</v>
       </c>
       <c r="H117" s="25" t="s">
-        <v>5648</v>
+        <v>5649</v>
       </c>
       <c r="I117" s="23" t="s">
-        <v>5649</v>
+        <v>5650</v>
       </c>
       <c r="J117" s="25" t="s">
-        <v>5650</v>
+        <v>5651</v>
       </c>
       <c r="K117" s="23" t="s">
-        <v>5651</v>
+        <v>5652</v>
       </c>
       <c r="L117" s="25" t="s">
-        <v>5652</v>
+        <v>5653</v>
       </c>
       <c r="M117" s="10"/>
       <c r="N117" s="10"/>
@@ -56177,40 +56180,40 @@
     </row>
     <row r="118" ht="18.75" customHeight="1">
       <c r="A118" s="23" t="s">
-        <v>5653</v>
+        <v>5654</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>5654</v>
+        <v>5655</v>
       </c>
       <c r="C118" s="23" t="s">
-        <v>5655</v>
+        <v>5656</v>
       </c>
       <c r="D118" s="25" t="s">
-        <v>5656</v>
+        <v>5657</v>
       </c>
       <c r="E118" s="23" t="s">
-        <v>5657</v>
+        <v>5658</v>
       </c>
       <c r="F118" s="25" t="s">
-        <v>5658</v>
+        <v>5659</v>
       </c>
       <c r="G118" s="23" t="s">
-        <v>5659</v>
+        <v>5660</v>
       </c>
       <c r="H118" s="25" t="s">
-        <v>5660</v>
+        <v>5661</v>
       </c>
       <c r="I118" s="23" t="s">
-        <v>5661</v>
+        <v>5662</v>
       </c>
       <c r="J118" s="25" t="s">
-        <v>5662</v>
+        <v>5663</v>
       </c>
       <c r="K118" s="23" t="s">
-        <v>5663</v>
+        <v>5664</v>
       </c>
       <c r="L118" s="25" t="s">
-        <v>5664</v>
+        <v>5665</v>
       </c>
       <c r="M118" s="10"/>
       <c r="N118" s="10"/>
@@ -56222,40 +56225,40 @@
     </row>
     <row r="119" ht="18.75" customHeight="1">
       <c r="A119" s="36" t="s">
-        <v>5665</v>
+        <v>5666</v>
       </c>
       <c r="B119" s="28" t="s">
-        <v>5666</v>
+        <v>5667</v>
       </c>
       <c r="C119" s="36" t="s">
-        <v>5667</v>
+        <v>5668</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>5668</v>
+        <v>5669</v>
       </c>
       <c r="E119" s="36" t="s">
-        <v>5669</v>
+        <v>5670</v>
       </c>
       <c r="F119" s="28" t="s">
-        <v>5670</v>
+        <v>5671</v>
       </c>
       <c r="G119" s="36" t="s">
-        <v>5671</v>
+        <v>5672</v>
       </c>
       <c r="H119" s="28" t="s">
-        <v>5672</v>
+        <v>5673</v>
       </c>
       <c r="I119" s="36" t="s">
-        <v>5673</v>
+        <v>5674</v>
       </c>
       <c r="J119" s="28" t="s">
-        <v>5674</v>
+        <v>5675</v>
       </c>
       <c r="K119" s="36" t="s">
-        <v>5675</v>
+        <v>5676</v>
       </c>
       <c r="L119" s="28" t="s">
-        <v>5676</v>
+        <v>5677</v>
       </c>
       <c r="M119" s="10"/>
       <c r="N119" s="10"/>
@@ -56288,7 +56291,7 @@
     </row>
     <row r="121" ht="18.75" customHeight="1">
       <c r="A121" s="18" t="s">
-        <v>5677</v>
+        <v>5678</v>
       </c>
       <c r="B121" s="19"/>
       <c r="C121" s="10"/>
@@ -56311,7 +56314,7 @@
     </row>
     <row r="122" ht="18.75" customHeight="1">
       <c r="A122" s="23" t="s">
-        <v>5678</v>
+        <v>5679</v>
       </c>
       <c r="B122" s="22"/>
       <c r="C122" s="10"/>
@@ -56334,7 +56337,7 @@
     </row>
     <row r="123" ht="18.75" customHeight="1">
       <c r="A123" s="23" t="s">
-        <v>5679</v>
+        <v>5680</v>
       </c>
       <c r="B123" s="22"/>
       <c r="C123" s="10"/>
@@ -56357,7 +56360,7 @@
     </row>
     <row r="124" ht="18.75" customHeight="1">
       <c r="A124" s="23" t="s">
-        <v>5680</v>
+        <v>5681</v>
       </c>
       <c r="B124" s="22"/>
       <c r="C124" s="10"/>
@@ -56408,7 +56411,7 @@
         <v>1671</v>
       </c>
       <c r="B126" s="25" t="s">
-        <v>5681</v>
+        <v>5682</v>
       </c>
       <c r="C126" s="10"/>
       <c r="D126" s="10"/>
@@ -56430,10 +56433,10 @@
     </row>
     <row r="127" ht="18.75" customHeight="1">
       <c r="A127" s="23" t="s">
-        <v>5682</v>
+        <v>5683</v>
       </c>
       <c r="B127" s="25" t="s">
-        <v>5683</v>
+        <v>5684</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="10"/>
@@ -56455,10 +56458,10 @@
     </row>
     <row r="128" ht="18.75" customHeight="1">
       <c r="A128" s="23" t="s">
+        <v>5683</v>
+      </c>
+      <c r="B128" s="25" t="s">
         <v>5682</v>
-      </c>
-      <c r="B128" s="25" t="s">
-        <v>5681</v>
       </c>
       <c r="C128" s="10"/>
       <c r="D128" s="10"/>
@@ -56480,10 +56483,10 @@
     </row>
     <row r="129" ht="18.75" customHeight="1">
       <c r="A129" s="23" t="s">
-        <v>5684</v>
+        <v>5685</v>
       </c>
       <c r="B129" s="25" t="s">
-        <v>5685</v>
+        <v>5686</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="10"/>
@@ -56505,10 +56508,10 @@
     </row>
     <row r="130" ht="18.75" customHeight="1">
       <c r="A130" s="23" t="s">
-        <v>5686</v>
+        <v>5687</v>
       </c>
       <c r="B130" s="25" t="s">
-        <v>5687</v>
+        <v>5688</v>
       </c>
       <c r="C130" s="10"/>
       <c r="D130" s="10"/>
@@ -56530,10 +56533,10 @@
     </row>
     <row r="131" ht="18.75" customHeight="1">
       <c r="A131" s="36" t="s">
-        <v>5688</v>
+        <v>5689</v>
       </c>
       <c r="B131" s="28" t="s">
-        <v>5689</v>
+        <v>5690</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="10"/>
@@ -56576,34 +56579,34 @@
     </row>
     <row r="133" ht="18.75" customHeight="1">
       <c r="A133" s="18" t="s">
-        <v>5690</v>
+        <v>5691</v>
       </c>
       <c r="B133" s="19"/>
       <c r="C133" s="18" t="s">
-        <v>5691</v>
+        <v>5692</v>
       </c>
       <c r="D133" s="19"/>
       <c r="E133" s="18" t="s">
-        <v>5692</v>
+        <v>5693</v>
       </c>
       <c r="F133" s="19"/>
       <c r="G133" s="18" t="s">
-        <v>5693</v>
+        <v>5694</v>
       </c>
       <c r="H133" s="19"/>
       <c r="I133" s="18" t="s">
-        <v>5694</v>
+        <v>5695</v>
       </c>
       <c r="J133" s="19"/>
       <c r="K133" s="18" t="s">
-        <v>5695</v>
+        <v>5696</v>
       </c>
       <c r="L133" s="19"/>
       <c r="M133" s="10"/>
       <c r="N133" s="10"/>
       <c r="O133" s="10"/>
       <c r="P133" s="8" t="s">
-        <v>5696</v>
+        <v>5697</v>
       </c>
     </row>
     <row r="134" ht="18.75" customHeight="1">
@@ -56612,23 +56615,23 @@
       </c>
       <c r="B134" s="22"/>
       <c r="C134" s="23" t="s">
-        <v>5697</v>
+        <v>5698</v>
       </c>
       <c r="D134" s="22"/>
       <c r="E134" s="23" t="s">
-        <v>5698</v>
+        <v>5699</v>
       </c>
       <c r="F134" s="22"/>
       <c r="G134" s="23" t="s">
-        <v>5699</v>
+        <v>5700</v>
       </c>
       <c r="H134" s="22"/>
       <c r="I134" s="23" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="J134" s="22"/>
       <c r="K134" s="23" t="s">
-        <v>5701</v>
+        <v>5702</v>
       </c>
       <c r="L134" s="22"/>
       <c r="M134" s="10"/>
@@ -56638,7 +56641,7 @@
         <v>5111</v>
       </c>
       <c r="Q134" s="10" t="s">
-        <v>5702</v>
+        <v>5703</v>
       </c>
     </row>
     <row r="135" ht="18.75" customHeight="1">
@@ -56647,23 +56650,23 @@
       </c>
       <c r="B135" s="22"/>
       <c r="C135" s="23" t="s">
-        <v>5703</v>
+        <v>5704</v>
       </c>
       <c r="D135" s="22"/>
       <c r="E135" s="23" t="s">
-        <v>5704</v>
+        <v>5705</v>
       </c>
       <c r="F135" s="22"/>
       <c r="G135" s="23" t="s">
-        <v>5705</v>
+        <v>5706</v>
       </c>
       <c r="H135" s="22"/>
       <c r="I135" s="23" t="s">
-        <v>5706</v>
+        <v>5707</v>
       </c>
       <c r="J135" s="22"/>
       <c r="K135" s="23" t="s">
-        <v>5707</v>
+        <v>5708</v>
       </c>
       <c r="L135" s="22"/>
       <c r="M135" s="10"/>
@@ -56673,7 +56676,7 @@
         <v>5117</v>
       </c>
       <c r="Q135" s="10" t="s">
-        <v>5708</v>
+        <v>5709</v>
       </c>
     </row>
     <row r="136" ht="18.75" customHeight="1">
@@ -56682,23 +56685,23 @@
       </c>
       <c r="B136" s="22"/>
       <c r="C136" s="23" t="s">
-        <v>5709</v>
+        <v>5710</v>
       </c>
       <c r="D136" s="22"/>
       <c r="E136" s="23" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="F136" s="22"/>
       <c r="G136" s="23" t="s">
-        <v>5711</v>
+        <v>5712</v>
       </c>
       <c r="H136" s="22"/>
       <c r="I136" s="23" t="s">
-        <v>5712</v>
+        <v>5713</v>
       </c>
       <c r="J136" s="22"/>
       <c r="K136" s="23" t="s">
-        <v>5713</v>
+        <v>5714</v>
       </c>
       <c r="L136" s="22"/>
       <c r="M136" s="10"/>
@@ -56708,7 +56711,7 @@
         <v>5123</v>
       </c>
       <c r="Q136" s="10" t="s">
-        <v>5714</v>
+        <v>5715</v>
       </c>
     </row>
     <row r="137" ht="18.75" customHeight="1">
@@ -56769,28 +56772,28 @@
         <v>987</v>
       </c>
       <c r="D138" s="25" t="s">
-        <v>5715</v>
+        <v>5716</v>
       </c>
       <c r="E138" s="23" t="s">
-        <v>5716</v>
+        <v>5717</v>
       </c>
       <c r="F138" s="25" t="s">
-        <v>5717</v>
+        <v>5718</v>
       </c>
       <c r="G138" s="23" t="s">
-        <v>5718</v>
+        <v>5719</v>
       </c>
       <c r="H138" s="25" t="s">
-        <v>5719</v>
+        <v>5720</v>
       </c>
       <c r="I138" s="23" t="s">
-        <v>5720</v>
+        <v>5721</v>
       </c>
       <c r="J138" s="25" t="s">
-        <v>5721</v>
+        <v>5722</v>
       </c>
       <c r="K138" s="23" t="s">
-        <v>5722</v>
+        <v>5723</v>
       </c>
       <c r="L138" s="25" t="s">
         <v>4095</v>
@@ -56805,10 +56808,10 @@
         <v>5132</v>
       </c>
       <c r="R138" s="10" t="s">
-        <v>5723</v>
+        <v>5724</v>
       </c>
       <c r="S138" s="10" t="s">
-        <v>5724</v>
+        <v>5725</v>
       </c>
     </row>
     <row r="139" ht="18.75" customHeight="1">
@@ -56817,34 +56820,34 @@
         <v>4434</v>
       </c>
       <c r="C139" s="23" t="s">
-        <v>5725</v>
+        <v>5726</v>
       </c>
       <c r="D139" s="25" t="s">
-        <v>5726</v>
+        <v>5727</v>
       </c>
       <c r="E139" s="23" t="s">
-        <v>5727</v>
+        <v>5728</v>
       </c>
       <c r="F139" s="25" t="s">
-        <v>5728</v>
+        <v>5729</v>
       </c>
       <c r="G139" s="23" t="s">
         <v>4163</v>
       </c>
       <c r="H139" s="25" t="s">
-        <v>5729</v>
+        <v>5730</v>
       </c>
       <c r="I139" s="23" t="s">
-        <v>5730</v>
+        <v>5731</v>
       </c>
       <c r="J139" s="25" t="s">
-        <v>5731</v>
+        <v>5732</v>
       </c>
       <c r="K139" s="23" t="s">
-        <v>5732</v>
+        <v>5733</v>
       </c>
       <c r="L139" s="25" t="s">
-        <v>5733</v>
+        <v>5734</v>
       </c>
       <c r="M139" s="10"/>
       <c r="N139" s="10"/>
@@ -56853,10 +56856,10 @@
         <v>4434</v>
       </c>
       <c r="R139" s="10" t="s">
-        <v>5734</v>
+        <v>5735</v>
       </c>
       <c r="S139" s="10" t="s">
-        <v>5735</v>
+        <v>5736</v>
       </c>
     </row>
     <row r="140" ht="18.75" customHeight="1">
@@ -56865,31 +56868,31 @@
         <v>5147</v>
       </c>
       <c r="C140" s="23" t="s">
-        <v>5725</v>
+        <v>5726</v>
       </c>
       <c r="D140" s="25" t="s">
-        <v>5715</v>
+        <v>5716</v>
       </c>
       <c r="E140" s="23" t="s">
-        <v>5727</v>
+        <v>5728</v>
       </c>
       <c r="F140" s="25" t="s">
-        <v>5717</v>
+        <v>5718</v>
       </c>
       <c r="G140" s="23" t="s">
         <v>4163</v>
       </c>
       <c r="H140" s="25" t="s">
-        <v>5719</v>
+        <v>5720</v>
       </c>
       <c r="I140" s="23" t="s">
-        <v>5730</v>
+        <v>5731</v>
       </c>
       <c r="J140" s="25" t="s">
-        <v>5721</v>
+        <v>5722</v>
       </c>
       <c r="K140" s="23" t="s">
-        <v>5732</v>
+        <v>5733</v>
       </c>
       <c r="L140" s="25" t="s">
         <v>4095</v>
@@ -56901,10 +56904,10 @@
         <v>5147</v>
       </c>
       <c r="R140" s="10" t="s">
-        <v>5734</v>
+        <v>5735</v>
       </c>
       <c r="S140" s="10" t="s">
-        <v>5724</v>
+        <v>5725</v>
       </c>
     </row>
     <row r="141" ht="18.75" customHeight="1">
@@ -56915,34 +56918,34 @@
         <v>4263</v>
       </c>
       <c r="C141" s="23" t="s">
-        <v>5736</v>
+        <v>5737</v>
       </c>
       <c r="D141" s="25" t="s">
-        <v>5737</v>
+        <v>5738</v>
       </c>
       <c r="E141" s="23" t="s">
-        <v>5738</v>
+        <v>5739</v>
       </c>
       <c r="F141" s="25" t="s">
-        <v>5739</v>
+        <v>5740</v>
       </c>
       <c r="G141" s="23" t="s">
-        <v>5740</v>
+        <v>5741</v>
       </c>
       <c r="H141" s="25" t="s">
-        <v>5741</v>
+        <v>5742</v>
       </c>
       <c r="I141" s="23" t="s">
-        <v>5742</v>
+        <v>5743</v>
       </c>
       <c r="J141" s="25" t="s">
-        <v>5743</v>
+        <v>5744</v>
       </c>
       <c r="K141" s="23" t="s">
-        <v>5744</v>
+        <v>5745</v>
       </c>
       <c r="L141" s="25" t="s">
-        <v>5745</v>
+        <v>5746</v>
       </c>
       <c r="M141" s="10"/>
       <c r="N141" s="10"/>
@@ -56954,10 +56957,10 @@
         <v>4263</v>
       </c>
       <c r="R141" s="10" t="s">
-        <v>5746</v>
+        <v>5747</v>
       </c>
       <c r="S141" s="10" t="s">
-        <v>5747</v>
+        <v>5748</v>
       </c>
     </row>
     <row r="142" ht="18.75" customHeight="1">
@@ -56965,34 +56968,34 @@
         <v>4384</v>
       </c>
       <c r="C142" s="23" t="s">
-        <v>5748</v>
+        <v>5749</v>
       </c>
       <c r="D142" s="25" t="s">
-        <v>5749</v>
+        <v>5750</v>
       </c>
       <c r="E142" s="23" t="s">
-        <v>5750</v>
+        <v>5751</v>
       </c>
       <c r="F142" s="25" t="s">
-        <v>5751</v>
+        <v>5752</v>
       </c>
       <c r="G142" s="23" t="s">
-        <v>5752</v>
+        <v>5753</v>
       </c>
       <c r="H142" s="25" t="s">
-        <v>5753</v>
+        <v>5754</v>
       </c>
       <c r="I142" s="23" t="s">
-        <v>5754</v>
+        <v>5755</v>
       </c>
       <c r="J142" s="25" t="s">
-        <v>5755</v>
+        <v>5756</v>
       </c>
       <c r="K142" s="23" t="s">
-        <v>5756</v>
+        <v>5757</v>
       </c>
       <c r="L142" s="25" t="s">
-        <v>5757</v>
+        <v>5758</v>
       </c>
       <c r="M142" s="10"/>
       <c r="N142" s="10"/>
@@ -57001,10 +57004,10 @@
         <v>4384</v>
       </c>
       <c r="R142" s="10" t="s">
-        <v>5758</v>
+        <v>5759</v>
       </c>
       <c r="S142" s="10" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="143" ht="18.75" customHeight="1">
@@ -57012,34 +57015,34 @@
         <v>5172</v>
       </c>
       <c r="C143" s="23" t="s">
-        <v>5760</v>
+        <v>5761</v>
       </c>
       <c r="D143" s="25" t="s">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="E143" s="23" t="s">
-        <v>5762</v>
+        <v>5763</v>
       </c>
       <c r="F143" s="25" t="s">
-        <v>5763</v>
+        <v>5764</v>
       </c>
       <c r="G143" s="23" t="s">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="H143" s="25" t="s">
-        <v>5765</v>
+        <v>5766</v>
       </c>
       <c r="I143" s="23" t="s">
-        <v>5766</v>
+        <v>5767</v>
       </c>
       <c r="J143" s="25" t="s">
-        <v>5767</v>
+        <v>5768</v>
       </c>
       <c r="K143" s="36" t="s">
-        <v>5768</v>
+        <v>5769</v>
       </c>
       <c r="L143" s="28" t="s">
-        <v>5769</v>
+        <v>5770</v>
       </c>
       <c r="M143" s="10"/>
       <c r="N143" s="10"/>
@@ -57048,10 +57051,10 @@
         <v>5172</v>
       </c>
       <c r="R143" s="10" t="s">
-        <v>5770</v>
+        <v>5771</v>
       </c>
       <c r="S143" s="10" t="s">
-        <v>5771</v>
+        <v>5772</v>
       </c>
     </row>
     <row r="144" ht="18.75" customHeight="1">
@@ -57101,28 +57104,28 @@
         <v>5132</v>
       </c>
       <c r="C145" s="23" t="s">
-        <v>5772</v>
+        <v>5773</v>
       </c>
       <c r="D145" s="25" t="s">
-        <v>5773</v>
+        <v>5774</v>
       </c>
       <c r="E145" s="23" t="s">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="F145" s="25" t="s">
-        <v>5775</v>
+        <v>5776</v>
       </c>
       <c r="G145" s="23" t="s">
-        <v>5776</v>
+        <v>5777</v>
       </c>
       <c r="H145" s="25" t="s">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="I145" s="23" t="s">
-        <v>5778</v>
+        <v>5779</v>
       </c>
       <c r="J145" s="25" t="s">
-        <v>5779</v>
+        <v>5780</v>
       </c>
       <c r="K145" s="23"/>
       <c r="L145" s="10"/>
@@ -57188,28 +57191,28 @@
         <v>4263</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>5780</v>
+        <v>5781</v>
       </c>
       <c r="D148" s="25" t="s">
-        <v>5781</v>
+        <v>5782</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>5782</v>
+        <v>5783</v>
       </c>
       <c r="F148" s="25" t="s">
-        <v>5783</v>
+        <v>5784</v>
       </c>
       <c r="G148" s="10" t="s">
-        <v>5784</v>
+        <v>5785</v>
       </c>
       <c r="H148" s="25" t="s">
-        <v>5785</v>
+        <v>5786</v>
       </c>
       <c r="I148" s="10" t="s">
-        <v>5786</v>
+        <v>5787</v>
       </c>
       <c r="J148" s="25" t="s">
-        <v>5787</v>
+        <v>5788</v>
       </c>
       <c r="K148" s="23"/>
       <c r="L148" s="10"/>
@@ -57227,28 +57230,28 @@
         <v>4384</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>5788</v>
+        <v>5789</v>
       </c>
       <c r="D149" s="25" t="s">
-        <v>5789</v>
+        <v>5790</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>5790</v>
+        <v>5791</v>
       </c>
       <c r="F149" s="25" t="s">
-        <v>5791</v>
+        <v>5792</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>5792</v>
+        <v>5793</v>
       </c>
       <c r="H149" s="25" t="s">
-        <v>5793</v>
+        <v>5794</v>
       </c>
       <c r="I149" s="10" t="s">
-        <v>5794</v>
+        <v>5795</v>
       </c>
       <c r="J149" s="25" t="s">
-        <v>5795</v>
+        <v>5796</v>
       </c>
       <c r="K149" s="23"/>
       <c r="L149" s="10"/>
@@ -57308,15 +57311,15 @@
       <c r="A152" s="10"/>
       <c r="B152" s="10"/>
       <c r="C152" s="18" t="s">
-        <v>5796</v>
+        <v>5797</v>
       </c>
       <c r="D152" s="19"/>
       <c r="E152" s="18" t="s">
-        <v>5797</v>
+        <v>5798</v>
       </c>
       <c r="F152" s="19"/>
       <c r="G152" s="18" t="s">
-        <v>5798</v>
+        <v>5799</v>
       </c>
       <c r="H152" s="19"/>
       <c r="I152" s="10"/>
@@ -57335,15 +57338,15 @@
       <c r="A153" s="10"/>
       <c r="B153" s="10"/>
       <c r="C153" s="23" t="s">
-        <v>5799</v>
+        <v>5800</v>
       </c>
       <c r="D153" s="22"/>
       <c r="E153" s="23" t="s">
-        <v>5800</v>
+        <v>5801</v>
       </c>
       <c r="F153" s="22"/>
       <c r="G153" s="23" t="s">
-        <v>5801</v>
+        <v>5802</v>
       </c>
       <c r="H153" s="22"/>
       <c r="I153" s="10"/>
@@ -57362,15 +57365,15 @@
       <c r="A154" s="10"/>
       <c r="B154" s="10"/>
       <c r="C154" s="23" t="s">
-        <v>5802</v>
+        <v>5803</v>
       </c>
       <c r="D154" s="22"/>
       <c r="E154" s="23" t="s">
-        <v>5803</v>
+        <v>5804</v>
       </c>
       <c r="F154" s="22"/>
       <c r="G154" s="23" t="s">
-        <v>5804</v>
+        <v>5805</v>
       </c>
       <c r="H154" s="22"/>
       <c r="I154" s="10"/>
@@ -57389,11 +57392,11 @@
       <c r="A155" s="10"/>
       <c r="B155" s="10"/>
       <c r="C155" s="23" t="s">
-        <v>5805</v>
+        <v>5806</v>
       </c>
       <c r="D155" s="22"/>
       <c r="E155" s="23" t="s">
-        <v>5806</v>
+        <v>5807</v>
       </c>
       <c r="F155" s="22"/>
       <c r="G155" s="23" t="s">
@@ -57449,22 +57452,22 @@
       <c r="A157" s="10"/>
       <c r="B157" s="10"/>
       <c r="C157" s="23" t="s">
-        <v>5807</v>
+        <v>5808</v>
       </c>
       <c r="D157" s="25" t="s">
-        <v>5808</v>
+        <v>5809</v>
       </c>
       <c r="E157" s="23" t="s">
-        <v>5809</v>
+        <v>5810</v>
       </c>
       <c r="F157" s="25" t="s">
-        <v>5810</v>
+        <v>5811</v>
       </c>
       <c r="G157" s="23" t="s">
-        <v>5811</v>
+        <v>5812</v>
       </c>
       <c r="H157" s="25" t="s">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="I157" s="10"/>
       <c r="J157" s="10"/>
@@ -57482,22 +57485,22 @@
       <c r="A158" s="10"/>
       <c r="B158" s="10"/>
       <c r="C158" s="23" t="s">
-        <v>5813</v>
+        <v>5814</v>
       </c>
       <c r="D158" s="25" t="s">
-        <v>5814</v>
+        <v>5815</v>
       </c>
       <c r="E158" s="23" t="s">
-        <v>5815</v>
+        <v>5816</v>
       </c>
       <c r="F158" s="25" t="s">
-        <v>5816</v>
+        <v>5817</v>
       </c>
       <c r="G158" s="23" t="s">
-        <v>5817</v>
+        <v>5818</v>
       </c>
       <c r="H158" s="25" t="s">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="I158" s="10"/>
       <c r="J158" s="10"/>
@@ -57515,22 +57518,22 @@
       <c r="A159" s="10"/>
       <c r="B159" s="10"/>
       <c r="C159" s="23" t="s">
+        <v>5814</v>
+      </c>
+      <c r="D159" s="25" t="s">
+        <v>5809</v>
+      </c>
+      <c r="E159" s="23" t="s">
+        <v>5816</v>
+      </c>
+      <c r="F159" s="25" t="s">
+        <v>5811</v>
+      </c>
+      <c r="G159" s="23" t="s">
+        <v>5818</v>
+      </c>
+      <c r="H159" s="25" t="s">
         <v>5813</v>
-      </c>
-      <c r="D159" s="25" t="s">
-        <v>5808</v>
-      </c>
-      <c r="E159" s="23" t="s">
-        <v>5815</v>
-      </c>
-      <c r="F159" s="25" t="s">
-        <v>5810</v>
-      </c>
-      <c r="G159" s="23" t="s">
-        <v>5817</v>
-      </c>
-      <c r="H159" s="25" t="s">
-        <v>5812</v>
       </c>
       <c r="I159" s="10"/>
       <c r="J159" s="10"/>
@@ -57548,22 +57551,22 @@
       <c r="A160" s="10"/>
       <c r="B160" s="10"/>
       <c r="C160" s="23" t="s">
-        <v>5819</v>
+        <v>5820</v>
       </c>
       <c r="D160" s="25" t="s">
-        <v>5820</v>
+        <v>5821</v>
       </c>
       <c r="E160" s="23" t="s">
-        <v>5821</v>
+        <v>5822</v>
       </c>
       <c r="F160" s="25" t="s">
-        <v>5822</v>
+        <v>5823</v>
       </c>
       <c r="G160" s="23" t="s">
-        <v>5823</v>
+        <v>5824</v>
       </c>
       <c r="H160" s="25" t="s">
-        <v>5824</v>
+        <v>5825</v>
       </c>
       <c r="I160" s="10"/>
       <c r="J160" s="10"/>
@@ -57581,22 +57584,22 @@
       <c r="A161" s="10"/>
       <c r="B161" s="10"/>
       <c r="C161" s="23" t="s">
-        <v>5825</v>
+        <v>5826</v>
       </c>
       <c r="D161" s="25" t="s">
-        <v>5826</v>
+        <v>5827</v>
       </c>
       <c r="E161" s="23" t="s">
-        <v>5827</v>
+        <v>5828</v>
       </c>
       <c r="F161" s="25" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="G161" s="23" t="s">
-        <v>5829</v>
+        <v>5830</v>
       </c>
       <c r="H161" s="25" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="I161" s="10"/>
       <c r="J161" s="10"/>
@@ -57614,22 +57617,22 @@
       <c r="A162" s="10"/>
       <c r="B162" s="10"/>
       <c r="C162" s="36" t="s">
-        <v>5831</v>
+        <v>5832</v>
       </c>
       <c r="D162" s="28" t="s">
-        <v>5832</v>
+        <v>5833</v>
       </c>
       <c r="E162" s="36" t="s">
-        <v>5833</v>
+        <v>5834</v>
       </c>
       <c r="F162" s="28" t="s">
-        <v>5834</v>
+        <v>5835</v>
       </c>
       <c r="G162" s="36" t="s">
-        <v>5835</v>
+        <v>5836</v>
       </c>
       <c r="H162" s="28" t="s">
-        <v>5836</v>
+        <v>5837</v>
       </c>
       <c r="I162" s="10"/>
       <c r="J162" s="10"/>
@@ -57666,19 +57669,19 @@
     </row>
     <row r="164" ht="18.75" customHeight="1">
       <c r="A164" s="18" t="s">
-        <v>5837</v>
+        <v>5838</v>
       </c>
       <c r="B164" s="19"/>
       <c r="C164" s="18" t="s">
-        <v>5838</v>
+        <v>5839</v>
       </c>
       <c r="D164" s="19"/>
       <c r="E164" s="18" t="s">
-        <v>5839</v>
+        <v>5840</v>
       </c>
       <c r="F164" s="19"/>
       <c r="G164" s="18" t="s">
-        <v>5840</v>
+        <v>5841</v>
       </c>
       <c r="H164" s="19"/>
       <c r="J164" s="10"/>
@@ -57698,15 +57701,15 @@
       </c>
       <c r="B165" s="22"/>
       <c r="C165" s="23" t="s">
-        <v>5841</v>
+        <v>5842</v>
       </c>
       <c r="D165" s="22"/>
       <c r="E165" s="23" t="s">
-        <v>5842</v>
+        <v>5843</v>
       </c>
       <c r="F165" s="22"/>
       <c r="G165" s="23" t="s">
-        <v>5843</v>
+        <v>5844</v>
       </c>
       <c r="H165" s="22"/>
       <c r="J165" s="10"/>
@@ -57726,15 +57729,15 @@
       </c>
       <c r="B166" s="22"/>
       <c r="C166" s="23" t="s">
-        <v>5844</v>
+        <v>5845</v>
       </c>
       <c r="D166" s="22"/>
       <c r="E166" s="23" t="s">
-        <v>5845</v>
+        <v>5846</v>
       </c>
       <c r="F166" s="22"/>
       <c r="G166" s="23" t="s">
-        <v>5846</v>
+        <v>5847</v>
       </c>
       <c r="H166" s="22"/>
       <c r="J166" s="10"/>
@@ -57754,15 +57757,15 @@
       </c>
       <c r="B167" s="22"/>
       <c r="C167" s="23" t="s">
-        <v>5847</v>
+        <v>5848</v>
       </c>
       <c r="D167" s="22"/>
       <c r="E167" s="23" t="s">
-        <v>5848</v>
+        <v>5849</v>
       </c>
       <c r="F167" s="22"/>
       <c r="G167" s="23" t="s">
-        <v>5849</v>
+        <v>5850</v>
       </c>
       <c r="H167" s="22"/>
       <c r="J167" s="10"/>
@@ -57818,22 +57821,22 @@
         <v>5132</v>
       </c>
       <c r="C169" s="23" t="s">
-        <v>5850</v>
+        <v>5851</v>
       </c>
       <c r="D169" s="25" t="s">
-        <v>5851</v>
+        <v>5852</v>
       </c>
       <c r="E169" s="23" t="s">
-        <v>5852</v>
+        <v>5853</v>
       </c>
       <c r="F169" s="25" t="s">
-        <v>5853</v>
+        <v>5854</v>
       </c>
       <c r="G169" s="23" t="s">
-        <v>5854</v>
+        <v>5855</v>
       </c>
       <c r="H169" s="25" t="s">
-        <v>5855</v>
+        <v>5856</v>
       </c>
       <c r="J169" s="10"/>
       <c r="K169" s="10"/>
@@ -57852,22 +57855,22 @@
         <v>4434</v>
       </c>
       <c r="C170" s="23" t="s">
-        <v>5856</v>
+        <v>5857</v>
       </c>
       <c r="D170" s="25" t="s">
-        <v>5857</v>
+        <v>5858</v>
       </c>
       <c r="E170" s="23" t="s">
-        <v>5858</v>
+        <v>5859</v>
       </c>
       <c r="F170" s="25" t="s">
-        <v>5859</v>
+        <v>5860</v>
       </c>
       <c r="G170" s="23" t="s">
-        <v>5860</v>
+        <v>5861</v>
       </c>
       <c r="H170" s="25" t="s">
-        <v>5861</v>
+        <v>5862</v>
       </c>
       <c r="J170" s="10"/>
       <c r="K170" s="10"/>
@@ -57886,22 +57889,22 @@
         <v>5147</v>
       </c>
       <c r="C171" s="23" t="s">
+        <v>5857</v>
+      </c>
+      <c r="D171" s="25" t="s">
+        <v>5852</v>
+      </c>
+      <c r="E171" s="23" t="s">
+        <v>5859</v>
+      </c>
+      <c r="F171" s="25" t="s">
+        <v>5854</v>
+      </c>
+      <c r="G171" s="23" t="s">
+        <v>5861</v>
+      </c>
+      <c r="H171" s="25" t="s">
         <v>5856</v>
-      </c>
-      <c r="D171" s="25" t="s">
-        <v>5851</v>
-      </c>
-      <c r="E171" s="23" t="s">
-        <v>5858</v>
-      </c>
-      <c r="F171" s="25" t="s">
-        <v>5853</v>
-      </c>
-      <c r="G171" s="23" t="s">
-        <v>5860</v>
-      </c>
-      <c r="H171" s="25" t="s">
-        <v>5855</v>
       </c>
       <c r="J171" s="10"/>
       <c r="K171" s="10"/>
@@ -57922,22 +57925,22 @@
         <v>4263</v>
       </c>
       <c r="C172" s="23" t="s">
-        <v>5862</v>
+        <v>5863</v>
       </c>
       <c r="D172" s="25" t="s">
-        <v>5863</v>
+        <v>5864</v>
       </c>
       <c r="E172" s="23" t="s">
-        <v>5864</v>
+        <v>5865</v>
       </c>
       <c r="F172" s="25" t="s">
-        <v>5865</v>
+        <v>5866</v>
       </c>
       <c r="G172" s="23" t="s">
-        <v>5866</v>
+        <v>5867</v>
       </c>
       <c r="H172" s="25" t="s">
-        <v>5867</v>
+        <v>5868</v>
       </c>
       <c r="J172" s="10"/>
       <c r="K172" s="10"/>
@@ -57955,22 +57958,22 @@
         <v>4384</v>
       </c>
       <c r="C173" s="23" t="s">
-        <v>5868</v>
+        <v>5869</v>
       </c>
       <c r="D173" s="25" t="s">
-        <v>5869</v>
+        <v>5870</v>
       </c>
       <c r="E173" s="23" t="s">
-        <v>5870</v>
+        <v>5871</v>
       </c>
       <c r="F173" s="25" t="s">
-        <v>5871</v>
+        <v>5872</v>
       </c>
       <c r="G173" s="23" t="s">
-        <v>5872</v>
+        <v>5873</v>
       </c>
       <c r="H173" s="25" t="s">
-        <v>5873</v>
+        <v>5874</v>
       </c>
       <c r="J173" s="10"/>
       <c r="K173" s="10"/>
@@ -57988,22 +57991,22 @@
         <v>5172</v>
       </c>
       <c r="C174" s="23" t="s">
-        <v>5874</v>
+        <v>5875</v>
       </c>
       <c r="D174" s="25" t="s">
-        <v>5875</v>
+        <v>5876</v>
       </c>
       <c r="E174" s="23" t="s">
-        <v>5876</v>
+        <v>5877</v>
       </c>
       <c r="F174" s="25" t="s">
-        <v>5877</v>
+        <v>5878</v>
       </c>
       <c r="G174" s="23" t="s">
-        <v>5878</v>
+        <v>5879</v>
       </c>
       <c r="H174" s="25" t="s">
-        <v>5879</v>
+        <v>5880</v>
       </c>
       <c r="J174" s="10"/>
       <c r="K174" s="10"/>
@@ -58051,10 +58054,10 @@
         <v>5132</v>
       </c>
       <c r="C176" s="23" t="s">
-        <v>5880</v>
+        <v>5881</v>
       </c>
       <c r="D176" s="25" t="s">
-        <v>5881</v>
+        <v>5882</v>
       </c>
       <c r="E176" s="40"/>
       <c r="F176" s="40"/>
@@ -58126,10 +58129,10 @@
         <v>4263</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>5882</v>
+        <v>5883</v>
       </c>
       <c r="D179" s="25" t="s">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="E179" s="40"/>
       <c r="F179" s="40"/>
@@ -58153,10 +58156,10 @@
         <v>4384</v>
       </c>
       <c r="C180" s="10" t="s">
-        <v>5884</v>
+        <v>5885</v>
       </c>
       <c r="D180" s="25" t="s">
-        <v>5885</v>
+        <v>5886</v>
       </c>
       <c r="E180" s="40"/>
       <c r="F180" s="40"/>
@@ -58220,19 +58223,19 @@
     </row>
     <row r="183" ht="18.75" customHeight="1">
       <c r="A183" s="18" t="s">
-        <v>5886</v>
+        <v>5887</v>
       </c>
       <c r="B183" s="19"/>
       <c r="C183" s="20" t="s">
-        <v>5887</v>
+        <v>5888</v>
       </c>
       <c r="D183" s="19"/>
       <c r="E183" s="20" t="s">
-        <v>5888</v>
+        <v>5889</v>
       </c>
       <c r="F183" s="19"/>
       <c r="G183" s="20" t="s">
-        <v>5889</v>
+        <v>5890</v>
       </c>
       <c r="H183" s="19"/>
       <c r="I183" s="10"/>
@@ -58253,15 +58256,15 @@
       </c>
       <c r="B184" s="22"/>
       <c r="C184" s="10" t="s">
-        <v>5890</v>
+        <v>5891</v>
       </c>
       <c r="D184" s="22"/>
       <c r="E184" s="10" t="s">
-        <v>5702</v>
+        <v>5703</v>
       </c>
       <c r="F184" s="22"/>
       <c r="G184" s="10" t="s">
-        <v>5891</v>
+        <v>5892</v>
       </c>
       <c r="H184" s="22"/>
       <c r="I184" s="10"/>
@@ -58282,15 +58285,15 @@
       </c>
       <c r="B185" s="22"/>
       <c r="C185" s="23" t="s">
-        <v>5892</v>
+        <v>5893</v>
       </c>
       <c r="D185" s="22"/>
       <c r="E185" s="23" t="s">
-        <v>5708</v>
+        <v>5709</v>
       </c>
       <c r="F185" s="22"/>
       <c r="G185" s="23" t="s">
-        <v>5893</v>
+        <v>5894</v>
       </c>
       <c r="H185" s="22"/>
       <c r="I185" s="10"/>
@@ -58311,15 +58314,15 @@
       </c>
       <c r="B186" s="22"/>
       <c r="C186" s="23" t="s">
-        <v>5894</v>
+        <v>5895</v>
       </c>
       <c r="D186" s="22"/>
       <c r="E186" s="23" t="s">
-        <v>5714</v>
+        <v>5715</v>
       </c>
       <c r="F186" s="22"/>
       <c r="G186" s="23" t="s">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="H186" s="22"/>
       <c r="I186" s="10"/>
@@ -58377,22 +58380,22 @@
         <v>5132</v>
       </c>
       <c r="C188" s="23" t="s">
-        <v>5896</v>
+        <v>5897</v>
       </c>
       <c r="D188" s="25" t="s">
-        <v>5897</v>
+        <v>5898</v>
       </c>
       <c r="E188" s="23" t="s">
-        <v>5723</v>
+        <v>5724</v>
       </c>
       <c r="F188" s="25" t="s">
-        <v>5724</v>
+        <v>5725</v>
       </c>
       <c r="G188" s="23" t="s">
-        <v>5898</v>
+        <v>5899</v>
       </c>
       <c r="H188" s="25" t="s">
-        <v>5899</v>
+        <v>5900</v>
       </c>
       <c r="I188" s="10"/>
       <c r="J188" s="10"/>
@@ -58412,22 +58415,22 @@
         <v>4434</v>
       </c>
       <c r="C189" s="23" t="s">
-        <v>5900</v>
+        <v>5901</v>
       </c>
       <c r="D189" s="25" t="s">
-        <v>5901</v>
+        <v>5902</v>
       </c>
       <c r="E189" s="23" t="s">
-        <v>5734</v>
+        <v>5735</v>
       </c>
       <c r="F189" s="25" t="s">
-        <v>5735</v>
+        <v>5736</v>
       </c>
       <c r="G189" s="23" t="s">
-        <v>5902</v>
+        <v>5903</v>
       </c>
       <c r="H189" s="25" t="s">
-        <v>5903</v>
+        <v>5904</v>
       </c>
       <c r="I189" s="10"/>
       <c r="J189" s="10"/>
@@ -58447,22 +58450,22 @@
         <v>5147</v>
       </c>
       <c r="C190" s="23" t="s">
+        <v>5901</v>
+      </c>
+      <c r="D190" s="25" t="s">
+        <v>5898</v>
+      </c>
+      <c r="E190" s="23" t="s">
+        <v>5735</v>
+      </c>
+      <c r="F190" s="25" t="s">
+        <v>5725</v>
+      </c>
+      <c r="G190" s="23" t="s">
+        <v>5903</v>
+      </c>
+      <c r="H190" s="25" t="s">
         <v>5900</v>
-      </c>
-      <c r="D190" s="25" t="s">
-        <v>5897</v>
-      </c>
-      <c r="E190" s="23" t="s">
-        <v>5734</v>
-      </c>
-      <c r="F190" s="25" t="s">
-        <v>5724</v>
-      </c>
-      <c r="G190" s="23" t="s">
-        <v>5902</v>
-      </c>
-      <c r="H190" s="25" t="s">
-        <v>5899</v>
       </c>
       <c r="I190" s="10"/>
       <c r="J190" s="10"/>
@@ -58484,22 +58487,22 @@
         <v>4263</v>
       </c>
       <c r="C191" s="23" t="s">
-        <v>5904</v>
+        <v>5905</v>
       </c>
       <c r="D191" s="25" t="s">
-        <v>5905</v>
+        <v>5906</v>
       </c>
       <c r="E191" s="23" t="s">
-        <v>5746</v>
+        <v>5747</v>
       </c>
       <c r="F191" s="25" t="s">
-        <v>5747</v>
+        <v>5748</v>
       </c>
       <c r="G191" s="23" t="s">
-        <v>5906</v>
+        <v>5907</v>
       </c>
       <c r="H191" s="25" t="s">
-        <v>5907</v>
+        <v>5908</v>
       </c>
       <c r="I191" s="10"/>
       <c r="J191" s="10"/>
@@ -58519,22 +58522,22 @@
         <v>4384</v>
       </c>
       <c r="C192" s="23" t="s">
-        <v>5908</v>
+        <v>5909</v>
       </c>
       <c r="D192" s="25" t="s">
-        <v>5909</v>
+        <v>5910</v>
       </c>
       <c r="E192" s="23" t="s">
-        <v>5758</v>
+        <v>5759</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="G192" s="23" t="s">
-        <v>5910</v>
+        <v>5911</v>
       </c>
       <c r="H192" s="25" t="s">
-        <v>5911</v>
+        <v>5912</v>
       </c>
       <c r="I192" s="10"/>
       <c r="J192" s="10"/>
@@ -58554,22 +58557,22 @@
         <v>5172</v>
       </c>
       <c r="C193" s="36" t="s">
-        <v>5912</v>
+        <v>5913</v>
       </c>
       <c r="D193" s="28" t="s">
-        <v>5913</v>
+        <v>5914</v>
       </c>
       <c r="E193" s="36" t="s">
-        <v>5770</v>
+        <v>5771</v>
       </c>
       <c r="F193" s="28" t="s">
-        <v>5771</v>
+        <v>5772</v>
       </c>
       <c r="G193" s="36" t="s">
-        <v>5914</v>
+        <v>5915</v>
       </c>
       <c r="H193" s="28" t="s">
-        <v>5915</v>
+        <v>5916</v>
       </c>
       <c r="I193" s="10"/>
       <c r="J193" s="10"/>
@@ -58606,11 +58609,11 @@
     </row>
     <row r="195" ht="18.75" customHeight="1">
       <c r="A195" s="18" t="s">
-        <v>5916</v>
+        <v>5917</v>
       </c>
       <c r="B195" s="19"/>
       <c r="C195" s="18" t="s">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="D195" s="19"/>
       <c r="E195" s="10"/>
@@ -58635,7 +58638,7 @@
       </c>
       <c r="B196" s="22"/>
       <c r="C196" s="23" t="s">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="D196" s="22"/>
       <c r="E196" s="10"/>
@@ -58660,7 +58663,7 @@
       </c>
       <c r="B197" s="22"/>
       <c r="C197" s="23" t="s">
-        <v>5919</v>
+        <v>5920</v>
       </c>
       <c r="D197" s="22"/>
       <c r="E197" s="10"/>
@@ -58685,7 +58688,7 @@
       </c>
       <c r="B198" s="22"/>
       <c r="C198" s="23" t="s">
-        <v>5920</v>
+        <v>5921</v>
       </c>
       <c r="D198" s="22"/>
       <c r="E198" s="10"/>
@@ -58739,10 +58742,10 @@
         <v>5132</v>
       </c>
       <c r="C200" s="23" t="s">
-        <v>5921</v>
+        <v>5922</v>
       </c>
       <c r="D200" s="25" t="s">
-        <v>5922</v>
+        <v>5923</v>
       </c>
       <c r="E200" s="10"/>
       <c r="F200" s="10"/>
@@ -58766,10 +58769,10 @@
         <v>4434</v>
       </c>
       <c r="C201" s="23" t="s">
-        <v>5923</v>
+        <v>5924</v>
       </c>
       <c r="D201" s="25" t="s">
-        <v>5924</v>
+        <v>5925</v>
       </c>
       <c r="E201" s="10"/>
       <c r="F201" s="10"/>
@@ -58793,10 +58796,10 @@
         <v>5147</v>
       </c>
       <c r="C202" s="23" t="s">
+        <v>5924</v>
+      </c>
+      <c r="D202" s="25" t="s">
         <v>5923</v>
-      </c>
-      <c r="D202" s="25" t="s">
-        <v>5922</v>
       </c>
       <c r="E202" s="10"/>
       <c r="F202" s="10"/>
@@ -58822,10 +58825,10 @@
         <v>4263</v>
       </c>
       <c r="C203" s="23" t="s">
-        <v>5925</v>
+        <v>5926</v>
       </c>
       <c r="D203" s="25" t="s">
-        <v>5926</v>
+        <v>5927</v>
       </c>
       <c r="E203" s="10"/>
       <c r="F203" s="10"/>
@@ -58848,10 +58851,10 @@
         <v>4384</v>
       </c>
       <c r="C204" s="23" t="s">
-        <v>5927</v>
+        <v>5928</v>
       </c>
       <c r="D204" s="25" t="s">
-        <v>5928</v>
+        <v>5929</v>
       </c>
       <c r="E204" s="10"/>
       <c r="F204" s="10"/>
@@ -58874,10 +58877,10 @@
         <v>5172</v>
       </c>
       <c r="C205" s="23" t="s">
-        <v>5929</v>
+        <v>5930</v>
       </c>
       <c r="D205" s="25" t="s">
-        <v>5930</v>
+        <v>5931</v>
       </c>
       <c r="E205" s="10"/>
       <c r="F205" s="10"/>
@@ -58930,10 +58933,10 @@
         <v>5132</v>
       </c>
       <c r="C207" s="23" t="s">
-        <v>5931</v>
+        <v>5932</v>
       </c>
       <c r="D207" s="25" t="s">
-        <v>5932</v>
+        <v>5933</v>
       </c>
       <c r="E207" s="10"/>
       <c r="F207" s="10"/>
@@ -59005,10 +59008,10 @@
         <v>4263</v>
       </c>
       <c r="C210" s="23" t="s">
-        <v>5933</v>
+        <v>5934</v>
       </c>
       <c r="D210" s="25" t="s">
-        <v>5934</v>
+        <v>5935</v>
       </c>
       <c r="E210" s="10"/>
       <c r="F210" s="10"/>
@@ -59032,10 +59035,10 @@
         <v>4384</v>
       </c>
       <c r="C211" s="23" t="s">
-        <v>5935</v>
+        <v>5936</v>
       </c>
       <c r="D211" s="25" t="s">
-        <v>5936</v>
+        <v>5937</v>
       </c>
       <c r="E211" s="10"/>
       <c r="F211" s="10"/>
@@ -59099,11 +59102,11 @@
     </row>
     <row r="214" ht="18.75" customHeight="1">
       <c r="A214" s="18" t="s">
-        <v>5937</v>
+        <v>5938</v>
       </c>
       <c r="B214" s="19"/>
       <c r="C214" s="18" t="s">
-        <v>5938</v>
+        <v>5939</v>
       </c>
       <c r="D214" s="19"/>
       <c r="E214" s="10"/>
@@ -59128,7 +59131,7 @@
       </c>
       <c r="B215" s="22"/>
       <c r="C215" s="23" t="s">
-        <v>5939</v>
+        <v>5940</v>
       </c>
       <c r="D215" s="22"/>
       <c r="E215" s="10"/>
@@ -59153,7 +59156,7 @@
       </c>
       <c r="B216" s="22"/>
       <c r="C216" s="23" t="s">
-        <v>5940</v>
+        <v>5941</v>
       </c>
       <c r="D216" s="22"/>
       <c r="E216" s="10"/>
@@ -59178,7 +59181,7 @@
       </c>
       <c r="B217" s="22"/>
       <c r="C217" s="23" t="s">
-        <v>5941</v>
+        <v>5942</v>
       </c>
       <c r="D217" s="22"/>
       <c r="E217" s="10"/>
@@ -59232,10 +59235,10 @@
         <v>5132</v>
       </c>
       <c r="C219" s="23" t="s">
-        <v>5942</v>
+        <v>5943</v>
       </c>
       <c r="D219" s="25" t="s">
-        <v>5943</v>
+        <v>5944</v>
       </c>
       <c r="E219" s="10"/>
       <c r="F219" s="10"/>
@@ -59259,10 +59262,10 @@
         <v>4434</v>
       </c>
       <c r="C220" s="23" t="s">
-        <v>5944</v>
+        <v>5945</v>
       </c>
       <c r="D220" s="25" t="s">
-        <v>5945</v>
+        <v>5946</v>
       </c>
       <c r="E220" s="10"/>
       <c r="F220" s="10"/>
@@ -59286,10 +59289,10 @@
         <v>5147</v>
       </c>
       <c r="C221" s="23" t="s">
+        <v>5945</v>
+      </c>
+      <c r="D221" s="25" t="s">
         <v>5944</v>
-      </c>
-      <c r="D221" s="25" t="s">
-        <v>5943</v>
       </c>
       <c r="E221" s="10"/>
       <c r="F221" s="10"/>
@@ -59315,10 +59318,10 @@
         <v>4263</v>
       </c>
       <c r="C222" s="23" t="s">
-        <v>5946</v>
+        <v>5947</v>
       </c>
       <c r="D222" s="25" t="s">
-        <v>5947</v>
+        <v>5948</v>
       </c>
       <c r="E222" s="10"/>
       <c r="F222" s="10"/>
@@ -59341,10 +59344,10 @@
         <v>4384</v>
       </c>
       <c r="C223" s="23" t="s">
-        <v>5948</v>
+        <v>5949</v>
       </c>
       <c r="D223" s="25" t="s">
-        <v>5949</v>
+        <v>5950</v>
       </c>
       <c r="E223" s="10"/>
       <c r="F223" s="10"/>
@@ -59367,10 +59370,10 @@
         <v>5172</v>
       </c>
       <c r="C224" s="23" t="s">
-        <v>5950</v>
+        <v>5951</v>
       </c>
       <c r="D224" s="25" t="s">
-        <v>5951</v>
+        <v>5952</v>
       </c>
       <c r="E224" s="10"/>
       <c r="F224" s="10"/>
@@ -59423,10 +59426,10 @@
         <v>5132</v>
       </c>
       <c r="C226" s="23" t="s">
-        <v>5952</v>
+        <v>5953</v>
       </c>
       <c r="D226" s="25" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="E226" s="10"/>
       <c r="F226" s="10"/>
@@ -59498,10 +59501,10 @@
         <v>4263</v>
       </c>
       <c r="C229" s="23" t="s">
-        <v>5954</v>
+        <v>5955</v>
       </c>
       <c r="D229" s="25" t="s">
-        <v>5955</v>
+        <v>5956</v>
       </c>
       <c r="E229" s="10"/>
       <c r="F229" s="10"/>
@@ -59525,10 +59528,10 @@
         <v>4384</v>
       </c>
       <c r="C230" s="23" t="s">
-        <v>5956</v>
+        <v>5957</v>
       </c>
       <c r="D230" s="25" t="s">
-        <v>5957</v>
+        <v>5958</v>
       </c>
       <c r="E230" s="10"/>
       <c r="F230" s="10"/>
@@ -59592,11 +59595,11 @@
     </row>
     <row r="233" ht="18.75" customHeight="1">
       <c r="A233" s="18" t="s">
-        <v>5958</v>
+        <v>5959</v>
       </c>
       <c r="B233" s="19"/>
       <c r="C233" s="18" t="s">
-        <v>5959</v>
+        <v>5960</v>
       </c>
       <c r="D233" s="19"/>
       <c r="E233" s="10"/>
@@ -59621,7 +59624,7 @@
       </c>
       <c r="B234" s="22"/>
       <c r="C234" s="23" t="s">
-        <v>5960</v>
+        <v>5961</v>
       </c>
       <c r="D234" s="22"/>
       <c r="E234" s="10"/>
@@ -59646,7 +59649,7 @@
       </c>
       <c r="B235" s="22"/>
       <c r="C235" s="23" t="s">
-        <v>5961</v>
+        <v>5962</v>
       </c>
       <c r="D235" s="22"/>
       <c r="E235" s="10"/>
@@ -59671,7 +59674,7 @@
       </c>
       <c r="B236" s="22"/>
       <c r="C236" s="23" t="s">
-        <v>5962</v>
+        <v>5963</v>
       </c>
       <c r="D236" s="22"/>
       <c r="E236" s="10"/>
@@ -59725,10 +59728,10 @@
         <v>5132</v>
       </c>
       <c r="C238" s="23" t="s">
-        <v>5963</v>
+        <v>5964</v>
       </c>
       <c r="D238" s="25" t="s">
-        <v>5964</v>
+        <v>5965</v>
       </c>
       <c r="E238" s="10"/>
       <c r="F238" s="10"/>
@@ -59752,10 +59755,10 @@
         <v>4434</v>
       </c>
       <c r="C239" s="23" t="s">
-        <v>5965</v>
+        <v>5966</v>
       </c>
       <c r="D239" s="25" t="s">
-        <v>5966</v>
+        <v>5967</v>
       </c>
       <c r="E239" s="10"/>
       <c r="F239" s="10"/>
@@ -59779,10 +59782,10 @@
         <v>5147</v>
       </c>
       <c r="C240" s="23" t="s">
-        <v>5965</v>
+        <v>5966</v>
       </c>
       <c r="D240" s="25" t="s">
-        <v>5967</v>
+        <v>5968</v>
       </c>
       <c r="E240" s="10"/>
       <c r="F240" s="10"/>
@@ -59808,10 +59811,10 @@
         <v>4263</v>
       </c>
       <c r="C241" s="23" t="s">
-        <v>5968</v>
+        <v>5969</v>
       </c>
       <c r="D241" s="25" t="s">
-        <v>5969</v>
+        <v>5970</v>
       </c>
       <c r="E241" s="10"/>
       <c r="F241" s="10"/>
@@ -59835,10 +59838,10 @@
         <v>4384</v>
       </c>
       <c r="C242" s="23" t="s">
-        <v>5970</v>
+        <v>5971</v>
       </c>
       <c r="D242" s="25" t="s">
-        <v>5971</v>
+        <v>5972</v>
       </c>
       <c r="E242" s="10"/>
       <c r="F242" s="10"/>
@@ -59862,10 +59865,10 @@
         <v>5172</v>
       </c>
       <c r="C243" s="36" t="s">
-        <v>5972</v>
+        <v>5973</v>
       </c>
       <c r="D243" s="28" t="s">
-        <v>5973</v>
+        <v>5974</v>
       </c>
       <c r="E243" s="10"/>
       <c r="F243" s="10"/>
@@ -59906,11 +59909,11 @@
     </row>
     <row r="245" ht="18.75" customHeight="1">
       <c r="A245" s="18" t="s">
-        <v>5974</v>
+        <v>5975</v>
       </c>
       <c r="B245" s="19"/>
       <c r="C245" s="18" t="s">
-        <v>5975</v>
+        <v>5976</v>
       </c>
       <c r="D245" s="19"/>
       <c r="E245" s="10"/>
@@ -59935,7 +59938,7 @@
       </c>
       <c r="B246" s="22"/>
       <c r="C246" s="23" t="s">
-        <v>5976</v>
+        <v>5977</v>
       </c>
       <c r="D246" s="22"/>
       <c r="E246" s="10"/>
@@ -59960,7 +59963,7 @@
       </c>
       <c r="B247" s="22"/>
       <c r="C247" s="23" t="s">
-        <v>5977</v>
+        <v>5978</v>
       </c>
       <c r="D247" s="22"/>
       <c r="E247" s="10"/>
@@ -59985,7 +59988,7 @@
       </c>
       <c r="B248" s="22"/>
       <c r="C248" s="23" t="s">
-        <v>5978</v>
+        <v>5979</v>
       </c>
       <c r="D248" s="22"/>
       <c r="E248" s="10"/>
@@ -60039,10 +60042,10 @@
         <v>5132</v>
       </c>
       <c r="C250" s="23" t="s">
-        <v>5979</v>
+        <v>5980</v>
       </c>
       <c r="D250" s="25" t="s">
-        <v>5980</v>
+        <v>5981</v>
       </c>
       <c r="E250" s="10"/>
       <c r="F250" s="10"/>
@@ -60066,10 +60069,10 @@
         <v>4434</v>
       </c>
       <c r="C251" s="23" t="s">
-        <v>5981</v>
+        <v>5982</v>
       </c>
       <c r="D251" s="25" t="s">
-        <v>5982</v>
+        <v>5983</v>
       </c>
       <c r="E251" s="10"/>
       <c r="F251" s="10"/>
@@ -60093,10 +60096,10 @@
         <v>5147</v>
       </c>
       <c r="C252" s="23" t="s">
-        <v>5979</v>
+        <v>5980</v>
       </c>
       <c r="D252" s="25" t="s">
-        <v>5983</v>
+        <v>5984</v>
       </c>
       <c r="E252" s="10"/>
       <c r="F252" s="10"/>
@@ -60122,10 +60125,10 @@
         <v>4263</v>
       </c>
       <c r="C253" s="23" t="s">
-        <v>5984</v>
+        <v>5985</v>
       </c>
       <c r="D253" s="25" t="s">
-        <v>5985</v>
+        <v>5986</v>
       </c>
       <c r="E253" s="10"/>
       <c r="F253" s="10"/>
@@ -60149,10 +60152,10 @@
         <v>4384</v>
       </c>
       <c r="C254" s="23" t="s">
-        <v>5986</v>
+        <v>5987</v>
       </c>
       <c r="D254" s="25" t="s">
-        <v>5987</v>
+        <v>5988</v>
       </c>
       <c r="E254" s="10"/>
       <c r="F254" s="10"/>
@@ -60176,10 +60179,10 @@
         <v>5172</v>
       </c>
       <c r="C255" s="36" t="s">
-        <v>5988</v>
+        <v>5989</v>
       </c>
       <c r="D255" s="28" t="s">
-        <v>5989</v>
+        <v>5990</v>
       </c>
       <c r="E255" s="10"/>
       <c r="F255" s="10"/>
@@ -60220,15 +60223,15 @@
     </row>
     <row r="257" ht="18.75" customHeight="1">
       <c r="A257" s="18" t="s">
-        <v>5990</v>
+        <v>5991</v>
       </c>
       <c r="B257" s="19"/>
       <c r="C257" s="18" t="s">
-        <v>5991</v>
+        <v>5992</v>
       </c>
       <c r="D257" s="19"/>
       <c r="E257" s="18" t="s">
-        <v>5992</v>
+        <v>5993</v>
       </c>
       <c r="F257" s="19"/>
       <c r="G257" s="10"/>
@@ -60284,16 +60287,16 @@
         <v>5132</v>
       </c>
       <c r="C259" s="23" t="s">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="D259" s="25" t="s">
-        <v>5994</v>
+        <v>5995</v>
       </c>
       <c r="E259" s="23" t="s">
-        <v>5995</v>
+        <v>5996</v>
       </c>
       <c r="F259" s="25" t="s">
-        <v>5996</v>
+        <v>5997</v>
       </c>
       <c r="G259" s="10"/>
       <c r="H259" s="10"/>
@@ -60315,16 +60318,16 @@
         <v>4434</v>
       </c>
       <c r="C260" s="23" t="s">
-        <v>5997</v>
+        <v>5998</v>
       </c>
       <c r="D260" s="25" t="s">
         <v>5229</v>
       </c>
       <c r="E260" s="23" t="s">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="F260" s="25" t="s">
-        <v>5998</v>
+        <v>5999</v>
       </c>
       <c r="G260" s="10"/>
       <c r="H260" s="10"/>
@@ -60346,16 +60349,16 @@
         <v>5147</v>
       </c>
       <c r="C261" s="23" t="s">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="D261" s="25" t="s">
         <v>5219</v>
       </c>
       <c r="E261" s="23" t="s">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="F261" s="25" t="s">
-        <v>5999</v>
+        <v>6000</v>
       </c>
       <c r="G261" s="10"/>
       <c r="H261" s="10"/>
@@ -60379,16 +60382,16 @@
         <v>4263</v>
       </c>
       <c r="C262" s="23" t="s">
-        <v>6000</v>
+        <v>6001</v>
       </c>
       <c r="D262" s="25" t="s">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="E262" s="23" t="s">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="F262" s="25" t="s">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="G262" s="10"/>
       <c r="H262" s="10"/>
@@ -60410,16 +60413,16 @@
         <v>4384</v>
       </c>
       <c r="C263" s="23" t="s">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="D263" s="25" t="s">
-        <v>6005</v>
+        <v>6006</v>
       </c>
       <c r="E263" s="23" t="s">
-        <v>6006</v>
+        <v>6007</v>
       </c>
       <c r="F263" s="25" t="s">
-        <v>6007</v>
+        <v>6008</v>
       </c>
       <c r="G263" s="10"/>
       <c r="H263" s="10"/>
@@ -60444,13 +60447,13 @@
         <v>2565</v>
       </c>
       <c r="D264" s="28" t="s">
-        <v>6008</v>
+        <v>6009</v>
       </c>
       <c r="E264" s="36" t="s">
         <v>3383</v>
       </c>
       <c r="F264" s="28" t="s">
-        <v>6009</v>
+        <v>6010</v>
       </c>
       <c r="G264" s="10"/>
       <c r="H264" s="10"/>
@@ -60943,11 +60946,11 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="42" t="s">
-        <v>6010</v>
+        <v>6011</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="42" t="s">
-        <v>6011</v>
+        <v>6012</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
@@ -60955,14 +60958,14 @@
         <v>255</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>6012</v>
+        <v>6013</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="43" t="s">
-        <v>6013</v>
+        <v>6014</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>6014</v>
+        <v>6015</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
@@ -60970,14 +60973,14 @@
         <v>1593</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6015</v>
+        <v>6016</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="43" t="s">
-        <v>6016</v>
+        <v>6017</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>6017</v>
+        <v>6018</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
@@ -60985,14 +60988,14 @@
         <v>2198</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6018</v>
+        <v>6019</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="43" t="s">
-        <v>6019</v>
+        <v>6020</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>6020</v>
+        <v>6021</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
@@ -61000,14 +61003,14 @@
         <v>2316</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="43" t="s">
-        <v>6022</v>
+        <v>6023</v>
       </c>
       <c r="G5" s="43" t="s">
-        <v>6023</v>
+        <v>6024</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
@@ -61015,14 +61018,14 @@
         <v>2456</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6024</v>
+        <v>6025</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="43" t="s">
-        <v>6025</v>
+        <v>6026</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>6026</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
@@ -61030,14 +61033,14 @@
         <v>2565</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6027</v>
+        <v>6028</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="43" t="s">
-        <v>6028</v>
+        <v>6029</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>6029</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
@@ -61045,14 +61048,14 @@
         <v>2652</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6030</v>
+        <v>6031</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="43" t="s">
-        <v>6031</v>
+        <v>6032</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>6032</v>
+        <v>6033</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
@@ -61060,14 +61063,14 @@
         <v>3383</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6033</v>
+        <v>6034</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="43" t="s">
-        <v>6034</v>
+        <v>6035</v>
       </c>
       <c r="G9" s="43" t="s">
-        <v>6035</v>
+        <v>6036</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
@@ -61075,14 +61078,14 @@
         <v>3657</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6036</v>
+        <v>6037</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="43" t="s">
-        <v>6037</v>
+        <v>6038</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>6038</v>
+        <v>6039</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
@@ -61090,14 +61093,14 @@
         <v>4356</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6039</v>
+        <v>6040</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="43" t="s">
-        <v>6040</v>
+        <v>6041</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>6041</v>
+        <v>6042</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
@@ -61106,10 +61109,10 @@
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
       <c r="E12" s="43" t="s">
-        <v>6042</v>
+        <v>6043</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>6043</v>
+        <v>6044</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
@@ -61118,10 +61121,10 @@
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
       <c r="E13" s="43" t="s">
-        <v>6044</v>
+        <v>6045</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>6045</v>
+        <v>6046</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
@@ -61130,113 +61133,113 @@
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="43" t="s">
-        <v>6046</v>
+        <v>6047</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>6047</v>
+        <v>6048</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="42" t="s">
-        <v>6048</v>
+        <v>6049</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>6049</v>
+        <v>6050</v>
       </c>
       <c r="G15" s="45" t="s">
-        <v>6050</v>
+        <v>6051</v>
       </c>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6051</v>
+        <v>6052</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>6052</v>
+        <v>6053</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6053</v>
+        <v>6054</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>6054</v>
+        <v>6055</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>6055</v>
+        <v>6056</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>6056</v>
+        <v>6057</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>6057</v>
+        <v>6058</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>6058</v>
+        <v>6059</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>6059</v>
+        <v>6060</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>6060</v>
+        <v>6061</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6061</v>
+        <v>6062</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>6062</v>
+        <v>6063</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>6063</v>
+        <v>6064</v>
       </c>
       <c r="G19" s="43" t="s">
-        <v>6064</v>
+        <v>6065</v>
       </c>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6065</v>
+        <v>6066</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>6066</v>
+        <v>6067</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>6067</v>
+        <v>6068</v>
       </c>
       <c r="G20" s="43" t="s">
-        <v>6068</v>
+        <v>6069</v>
       </c>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6069</v>
+        <v>6070</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>6070</v>
+        <v>6071</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>6071</v>
+        <v>6072</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>6072</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6073</v>
+        <v>6074</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>6074</v>
+        <v>6075</v>
       </c>
       <c r="E22" s="46" t="s">
-        <v>6075</v>
+        <v>6076</v>
       </c>
       <c r="G22" s="46" t="s">
-        <v>6076</v>
+        <v>6077</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
@@ -61251,71 +61254,71 @@
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
       <c r="E24" s="43" t="s">
-        <v>6077</v>
+        <v>6078</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>6078</v>
+        <v>6079</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="E25" s="43" t="s">
-        <v>6079</v>
+        <v>6080</v>
       </c>
       <c r="G25" s="43" t="s">
-        <v>6080</v>
+        <v>6081</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="42" t="s">
-        <v>6081</v>
+        <v>6082</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>6082</v>
+        <v>6083</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>6083</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>6084</v>
+        <v>6085</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>6085</v>
+        <v>6086</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>6086</v>
+        <v>6087</v>
       </c>
       <c r="G27" s="43" t="s">
-        <v>6087</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="43" t="s">
-        <v>6088</v>
+        <v>6089</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>6089</v>
+        <v>6090</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>6090</v>
+        <v>6091</v>
       </c>
       <c r="G28" s="43" t="s">
-        <v>6091</v>
+        <v>6092</v>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="43" t="s">
-        <v>6092</v>
+        <v>6093</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>6093</v>
+        <v>6094</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>6094</v>
+        <v>6095</v>
       </c>
       <c r="G29" s="43" t="s">
-        <v>6095</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1">
@@ -61324,10 +61327,10 @@
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
       <c r="E30" s="43" t="s">
-        <v>6096</v>
+        <v>6097</v>
       </c>
       <c r="G30" s="43" t="s">
-        <v>6097</v>
+        <v>6098</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
@@ -61336,10 +61339,10 @@
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
       <c r="E31" s="43" t="s">
-        <v>6098</v>
+        <v>6099</v>
       </c>
       <c r="G31" s="43" t="s">
-        <v>6099</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
@@ -61348,10 +61351,10 @@
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
       <c r="E32" s="43" t="s">
-        <v>6100</v>
+        <v>6101</v>
       </c>
       <c r="G32" s="43" t="s">
-        <v>6101</v>
+        <v>6102</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
@@ -61360,10 +61363,10 @@
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
       <c r="E33" s="43" t="s">
-        <v>6102</v>
+        <v>6103</v>
       </c>
       <c r="G33" s="43" t="s">
-        <v>6103</v>
+        <v>6104</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
@@ -61372,10 +61375,10 @@
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
       <c r="E34" s="43" t="s">
-        <v>6104</v>
+        <v>6105</v>
       </c>
       <c r="G34" s="43" t="s">
-        <v>6105</v>
+        <v>6106</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
@@ -61384,10 +61387,10 @@
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
       <c r="E35" s="45" t="s">
-        <v>6106</v>
+        <v>6107</v>
       </c>
       <c r="G35" s="45" t="s">
-        <v>6107</v>
+        <v>6108</v>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1">
@@ -61402,10 +61405,10 @@
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
       <c r="E37" s="43" t="s">
-        <v>6108</v>
+        <v>6109</v>
       </c>
       <c r="G37" s="43" t="s">
-        <v>6109</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
@@ -61414,10 +61417,10 @@
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
       <c r="E38" s="43" t="s">
-        <v>6110</v>
+        <v>6111</v>
       </c>
       <c r="G38" s="43" t="s">
-        <v>6111</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
@@ -61426,10 +61429,10 @@
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
       <c r="E39" s="45" t="s">
-        <v>6112</v>
+        <v>6113</v>
       </c>
       <c r="G39" s="45" t="s">
-        <v>6113</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
@@ -61444,10 +61447,10 @@
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
       <c r="E41" s="45" t="s">
-        <v>6114</v>
+        <v>6115</v>
       </c>
       <c r="G41" s="45" t="s">
-        <v>6115</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1">
@@ -61665,10 +61668,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="43" t="s">
-        <v>6116</v>
+        <v>6117</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>6117</v>
+        <v>6118</v>
       </c>
       <c r="C1" s="12"/>
     </row>
@@ -61677,34 +61680,34 @@
         <v>38</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>6118</v>
+        <v>6119</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>6119</v>
+        <v>6120</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6120</v>
+        <v>6121</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>6121</v>
+        <v>6122</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6122</v>
+        <v>6123</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>6123</v>
+        <v>6124</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>6124</v>
+        <v>6125</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -61713,70 +61716,70 @@
         <v>1848</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6125</v>
+        <v>6126</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>6126</v>
+        <v>6127</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6127</v>
+        <v>6128</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>6128</v>
+        <v>6129</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6129</v>
+        <v>6130</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>6130</v>
+        <v>6131</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6131</v>
+        <v>6132</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>6132</v>
+        <v>6133</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6133</v>
+        <v>6134</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>6134</v>
+        <v>6135</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6135</v>
+        <v>6136</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>6136</v>
+        <v>6137</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>6137</v>
+        <v>6138</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>6138</v>
+        <v>6139</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>6139</v>
+        <v>6140</v>
       </c>
       <c r="C13" s="12"/>
     </row>
@@ -61785,7 +61788,7 @@
         <v>4859</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>6140</v>
+        <v>6141</v>
       </c>
       <c r="C14" s="12"/>
     </row>
@@ -61796,19 +61799,19 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6141</v>
+        <v>6142</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>6142</v>
+        <v>6143</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6143</v>
+        <v>6144</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>6144</v>
+        <v>6145</v>
       </c>
       <c r="C17" s="12"/>
     </row>
@@ -61819,334 +61822,334 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6145</v>
+        <v>6146</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>6146</v>
+        <v>6147</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6147</v>
+        <v>6148</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>6148</v>
+        <v>6149</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6149</v>
+        <v>6150</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>6150</v>
+        <v>6151</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6151</v>
+        <v>6152</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>6152</v>
+        <v>6153</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>6153</v>
+        <v>6154</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>6154</v>
+        <v>6155</v>
       </c>
       <c r="C23" s="12"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="43" t="s">
-        <v>6155</v>
+        <v>6156</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>6156</v>
+        <v>6157</v>
       </c>
       <c r="C24" s="12"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="43" t="s">
-        <v>6157</v>
+        <v>6158</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>6158</v>
+        <v>6159</v>
       </c>
       <c r="C25" s="12"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="43" t="s">
-        <v>6159</v>
+        <v>6160</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>6160</v>
+        <v>6161</v>
       </c>
       <c r="C26" s="12"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>6161</v>
+        <v>6162</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>6162</v>
+        <v>6163</v>
       </c>
       <c r="C27" s="12"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="43" t="s">
-        <v>6163</v>
+        <v>6164</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>6164</v>
+        <v>6165</v>
       </c>
       <c r="C28" s="12"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="43" t="s">
-        <v>6165</v>
+        <v>6166</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>6166</v>
+        <v>6167</v>
       </c>
       <c r="C29" s="12"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="43" t="s">
-        <v>6167</v>
+        <v>6168</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>6168</v>
+        <v>6169</v>
       </c>
       <c r="C30" s="12"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="43" t="s">
-        <v>6169</v>
+        <v>6170</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>6170</v>
+        <v>6171</v>
       </c>
       <c r="C31" s="12"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="43" t="s">
-        <v>6171</v>
+        <v>6172</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>6172</v>
+        <v>6173</v>
       </c>
       <c r="C32" s="12"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="43" t="s">
-        <v>6173</v>
+        <v>6174</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>6174</v>
+        <v>6175</v>
       </c>
       <c r="C33" s="12"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="43" t="s">
-        <v>6175</v>
+        <v>6176</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>6176</v>
+        <v>6177</v>
       </c>
       <c r="C34" s="12"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="43" t="s">
-        <v>6177</v>
+        <v>6178</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>6178</v>
+        <v>6179</v>
       </c>
       <c r="C35" s="12"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="43" t="s">
-        <v>6179</v>
+        <v>6180</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>6180</v>
+        <v>6181</v>
       </c>
       <c r="C36" s="12"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="43" t="s">
-        <v>6181</v>
+        <v>6182</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>6182</v>
+        <v>6183</v>
       </c>
       <c r="C37" s="12"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="43" t="s">
-        <v>6183</v>
+        <v>6184</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>6184</v>
+        <v>6185</v>
       </c>
       <c r="C38" s="12"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="43" t="s">
-        <v>6185</v>
+        <v>6186</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>6186</v>
+        <v>6187</v>
       </c>
       <c r="C39" s="12"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="43" t="s">
-        <v>6187</v>
+        <v>6188</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>6188</v>
+        <v>6189</v>
       </c>
       <c r="C40" s="12"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="43" t="s">
-        <v>6189</v>
+        <v>6190</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>6190</v>
+        <v>6191</v>
       </c>
       <c r="C41" s="12"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="43" t="s">
-        <v>6191</v>
+        <v>6192</v>
       </c>
       <c r="B42" s="43" t="s">
-        <v>6192</v>
+        <v>6193</v>
       </c>
       <c r="C42" s="12"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="43" t="s">
-        <v>6193</v>
+        <v>6194</v>
       </c>
       <c r="B43" s="43" t="s">
-        <v>6194</v>
+        <v>6195</v>
       </c>
       <c r="C43" s="12"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" s="43" t="s">
-        <v>6195</v>
+        <v>6196</v>
       </c>
       <c r="B44" s="43" t="s">
-        <v>6196</v>
+        <v>6197</v>
       </c>
       <c r="C44" s="12"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="43" t="s">
-        <v>6197</v>
+        <v>6198</v>
       </c>
       <c r="B45" s="43" t="s">
-        <v>6198</v>
+        <v>6199</v>
       </c>
       <c r="C45" s="12"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="43" t="s">
-        <v>6199</v>
+        <v>6200</v>
       </c>
       <c r="B46" s="43" t="s">
-        <v>6200</v>
+        <v>6201</v>
       </c>
       <c r="C46" s="12"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="43" t="s">
-        <v>6201</v>
+        <v>6202</v>
       </c>
       <c r="B47" s="43" t="s">
-        <v>6202</v>
+        <v>6203</v>
       </c>
       <c r="C47" s="12"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="43" t="s">
-        <v>6203</v>
+        <v>6204</v>
       </c>
       <c r="B48" s="43" t="s">
-        <v>6204</v>
+        <v>6205</v>
       </c>
       <c r="C48" s="12"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" s="43" t="s">
-        <v>6205</v>
+        <v>6206</v>
       </c>
       <c r="B49" s="43" t="s">
-        <v>6206</v>
+        <v>6207</v>
       </c>
       <c r="C49" s="12"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" s="43" t="s">
-        <v>6207</v>
+        <v>6208</v>
       </c>
       <c r="B50" s="43" t="s">
-        <v>6208</v>
+        <v>6209</v>
       </c>
       <c r="C50" s="12"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" s="43" t="s">
-        <v>6209</v>
+        <v>6210</v>
       </c>
       <c r="B51" s="43" t="s">
-        <v>6210</v>
+        <v>6211</v>
       </c>
       <c r="C51" s="12"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" s="43" t="s">
-        <v>6211</v>
+        <v>6212</v>
       </c>
       <c r="B52" s="43" t="s">
-        <v>6212</v>
+        <v>6213</v>
       </c>
       <c r="C52" s="12"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" s="43" t="s">
-        <v>6213</v>
+        <v>6214</v>
       </c>
       <c r="B53" s="43" t="s">
-        <v>6214</v>
+        <v>6215</v>
       </c>
       <c r="C53" s="12"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" s="43" t="s">
-        <v>6215</v>
+        <v>6216</v>
       </c>
       <c r="B54" s="43" t="s">
-        <v>6216</v>
+        <v>6217</v>
       </c>
       <c r="C54" s="12"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" s="43" t="s">
-        <v>6217</v>
+        <v>6218</v>
       </c>
       <c r="B55" s="43" t="s">
-        <v>6218</v>
+        <v>6219</v>
       </c>
       <c r="C55" s="12"/>
     </row>
@@ -62169,130 +62172,130 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="47" t="s">
-        <v>6219</v>
+        <v>6220</v>
       </c>
       <c r="C1" s="12"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="47" t="s">
-        <v>6220</v>
+        <v>6221</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>6221</v>
+        <v>6222</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>6222</v>
+        <v>6223</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6143</v>
+        <v>6144</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>6143</v>
+        <v>6144</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6130</v>
+        <v>6131</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>6223</v>
+        <v>6224</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>6132</v>
+        <v>6133</v>
       </c>
       <c r="C5" s="12"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="43" t="s">
-        <v>6224</v>
+        <v>6225</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6225</v>
+        <v>6226</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>6226</v>
+        <v>6227</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6227</v>
+        <v>6228</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>6228</v>
+        <v>6229</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6229</v>
+        <v>6230</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>6230</v>
+        <v>6231</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6231</v>
+        <v>6232</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>6232</v>
+        <v>6233</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6233</v>
+        <v>6234</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>6234</v>
+        <v>6235</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6235</v>
+        <v>6236</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>6236</v>
+        <v>6237</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>6237</v>
+        <v>6238</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>6238</v>
+        <v>6239</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>6239</v>
+        <v>6240</v>
       </c>
       <c r="C13" s="12"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="43" t="s">
-        <v>6240</v>
+        <v>6241</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>6241</v>
+        <v>6242</v>
       </c>
       <c r="C14" s="12"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="43" t="s">
-        <v>6242</v>
+        <v>6243</v>
       </c>
       <c r="B15" s="43" t="s">
         <v>3926</v>
@@ -62301,73 +62304,73 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6243</v>
+        <v>6244</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>6244</v>
+        <v>6245</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6245</v>
+        <v>6246</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="C17" s="12"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>6247</v>
+        <v>6248</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>6248</v>
+        <v>6249</v>
       </c>
       <c r="C18" s="12"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6249</v>
+        <v>6250</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>6250</v>
+        <v>6251</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6251</v>
+        <v>6252</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>6252</v>
+        <v>6253</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6253</v>
+        <v>6254</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>6254</v>
+        <v>6255</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6255</v>
+        <v>6256</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>6256</v>
+        <v>6257</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>6257</v>
+        <v>6258</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>6258</v>
+        <v>6259</v>
       </c>
       <c r="C23" s="12"/>
     </row>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10011" uniqueCount="6278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10006" uniqueCount="6278">
   <si>
     <t>Entry</t>
   </si>
@@ -18246,7 +18246,7 @@
     <t>that smells like fish</t>
   </si>
   <si>
-    <t>hann gar mek óførvandi</t>
+    <t>hann gerði mek óførvandi</t>
   </si>
   <si>
     <t>he incapacitated me</t>
@@ -18339,7 +18339,7 @@
     <t>im lost</t>
   </si>
   <si>
-    <t>Goð gar menn sem suma lítlan ok suma stóran, en gøru menn stál ok stál gar þá flata.</t>
+    <t>Goð gerði menn sem suma lítlan ok suma stóran, en gerðu menn stál ok stál gerði þá flata.</t>
   </si>
   <si>
     <t>God made some men small and some men big, but man made steel and steel made them equal.</t>
@@ -26819,9 +26819,7 @@
       <c r="C601" s="3" t="s">
         <v>1232</v>
       </c>
-      <c r="D601" s="3" t="s">
-        <v>200</v>
-      </c>
+      <c r="D601" s="3"/>
     </row>
     <row r="602" ht="18.75" customHeight="1">
       <c r="A602" s="3" t="s">
@@ -26833,9 +26831,7 @@
       <c r="C602" s="3" t="s">
         <v>1234</v>
       </c>
-      <c r="D602" s="3" t="s">
-        <v>200</v>
-      </c>
+      <c r="D602" s="3"/>
     </row>
     <row r="603" ht="18.75" customHeight="1">
       <c r="A603" s="3" t="s">
@@ -26847,9 +26843,7 @@
       <c r="C603" s="3" t="s">
         <v>1237</v>
       </c>
-      <c r="D603" s="3" t="s">
-        <v>200</v>
-      </c>
+      <c r="D603" s="3"/>
     </row>
     <row r="604" ht="18.75" customHeight="1">
       <c r="A604" s="3" t="s">
@@ -26861,9 +26855,7 @@
       <c r="C604" s="3" t="s">
         <v>1239</v>
       </c>
-      <c r="D604" s="3" t="s">
-        <v>200</v>
-      </c>
+      <c r="D604" s="3"/>
     </row>
     <row r="605" ht="18.75" customHeight="1">
       <c r="A605" s="3" t="s">
@@ -26875,9 +26867,7 @@
       <c r="C605" s="3" t="s">
         <v>1241</v>
       </c>
-      <c r="D605" s="3" t="s">
-        <v>200</v>
-      </c>
+      <c r="D605" s="3"/>
     </row>
     <row r="606" ht="18.75" customHeight="1">
       <c r="A606" s="3" t="s">

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -15178,6 +15178,15 @@
     <t>positive sg</t>
   </si>
   <si>
+    <t>einn</t>
+  </si>
+  <si>
+    <t>ein</t>
+  </si>
+  <si>
+    <t>eitt</t>
+  </si>
+  <si>
     <t>reyð</t>
   </si>
   <si>
@@ -15190,13 +15199,7 @@
     <t>reyða</t>
   </si>
   <si>
-    <t>einn</t>
-  </si>
-  <si>
-    <t>ein</t>
-  </si>
-  <si>
-    <t>eitt</t>
+    <t>eina</t>
   </si>
   <si>
     <t>reyðan</t>
@@ -15205,31 +15208,28 @@
     <t>reyðu</t>
   </si>
   <si>
-    <t>eina</t>
+    <t>einum</t>
+  </si>
+  <si>
+    <t>eini</t>
+  </si>
+  <si>
+    <t>einu</t>
   </si>
   <si>
     <t>reyðum</t>
   </si>
   <si>
-    <t>einum</t>
-  </si>
-  <si>
-    <t>eini</t>
-  </si>
-  <si>
-    <t>einu</t>
+    <t>eins</t>
+  </si>
+  <si>
+    <t>einar</t>
   </si>
   <si>
     <t>reyðs</t>
   </si>
   <si>
     <t>reyðar</t>
-  </si>
-  <si>
-    <t>eins</t>
-  </si>
-  <si>
-    <t>einar</t>
   </si>
   <si>
     <t>positive pl</t>
@@ -51042,10 +51042,9 @@
         <v>5037</v>
       </c>
       <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
+      <c r="I1" s="8" t="s">
+        <v>5038</v>
+      </c>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
     </row>
@@ -51058,10 +51057,19 @@
       </c>
       <c r="H2" s="12"/>
       <c r="I2" s="8" t="s">
-        <v>5038</v>
-      </c>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
+        <v>5039</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>4964</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>4965</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>4504</v>
+      </c>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="8" t="s">
@@ -51087,19 +51095,19 @@
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="8" t="s">
-        <v>5039</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>4964</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>4965</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>4504</v>
-      </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
+        <v>4508</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>5040</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>5041</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>5042</v>
+      </c>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="8" t="s">
@@ -51109,58 +51117,58 @@
         <v>3025</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>5040</v>
+        <v>5043</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>5041</v>
+        <v>5044</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>5042</v>
+        <v>5045</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>5043</v>
+        <v>5046</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>5043</v>
+        <v>5046</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="8" t="s">
-        <v>4508</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>5044</v>
+        <v>4519</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>5045</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>5046</v>
-      </c>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
+        <v>5047</v>
+      </c>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>4519</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>5047</v>
+        <v>5048</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>5043</v>
+        <v>5046</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>5043</v>
+        <v>5046</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>5048</v>
+        <v>5049</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="8" t="s">
-        <v>4519</v>
+        <v>4526</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>5050</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>5049</v>
+        <v>5051</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>5052</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
@@ -51170,26 +51178,26 @@
         <v>4526</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>5050</v>
+        <v>5053</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>5042</v>
+        <v>5045</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>5048</v>
+        <v>5049</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="8" t="s">
-        <v>4526</v>
+        <v>4538</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>5051</v>
+        <v>5054</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>5052</v>
+        <v>5055</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>5053</v>
+        <v>5054</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
@@ -51199,27 +51207,15 @@
         <v>4538</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>5054</v>
+        <v>5056</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>5055</v>
+        <v>5057</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>5054</v>
+        <v>5056</v>
       </c>
       <c r="H7" s="12"/>
-      <c r="I7" s="8" t="s">
-        <v>4538</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>5056</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>5057</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>5056</v>
-      </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
     </row>
@@ -51261,13 +51257,13 @@
         <v>5059</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>5055</v>
+        <v>5057</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>5040</v>
+        <v>5043</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>5048</v>
+        <v>5049</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -51282,7 +51278,7 @@
         <v>4519</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>5043</v>
+        <v>5046</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
@@ -51297,7 +51293,7 @@
         <v>4526</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>5050</v>
+        <v>5053</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
@@ -51312,7 +51308,7 @@
         <v>4538</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>5043</v>
+        <v>5046</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
@@ -52544,15 +52540,6 @@
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="B51:D51"/>
     <mergeCell ref="B53:D53"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="G4:G7"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="F5:F7"/>
     <mergeCell ref="C9:C10"/>
@@ -52583,6 +52570,15 @@
     <mergeCell ref="N36:N37"/>
     <mergeCell ref="G38:I38"/>
     <mergeCell ref="G39:I39"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10043" uniqueCount="6298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10102" uniqueCount="6321">
   <si>
     <t>Entry</t>
   </si>
@@ -15397,6 +15397,27 @@
     <t>skýir</t>
   </si>
   <si>
+    <t>comparative</t>
+  </si>
+  <si>
+    <t>kaldari</t>
+  </si>
+  <si>
+    <t>superlative</t>
+  </si>
+  <si>
+    <t>kaldastr</t>
+  </si>
+  <si>
+    <t>smæstr</t>
+  </si>
+  <si>
+    <t>skýjari</t>
+  </si>
+  <si>
+    <t>skýjastr</t>
+  </si>
+  <si>
     <t>form 2</t>
   </si>
   <si>
@@ -15430,6 +15451,12 @@
     <t>feimnir</t>
   </si>
   <si>
+    <t>feimnari</t>
+  </si>
+  <si>
+    <t>feimnastr</t>
+  </si>
+  <si>
     <t>form 3</t>
   </si>
   <si>
@@ -15463,6 +15490,54 @@
     <t>fornir</t>
   </si>
   <si>
+    <t>fornari</t>
+  </si>
+  <si>
+    <t>fornastr</t>
+  </si>
+  <si>
+    <t>form 4</t>
+  </si>
+  <si>
+    <t>example: seinn</t>
+  </si>
+  <si>
+    <t>sein</t>
+  </si>
+  <si>
+    <t>seint</t>
+  </si>
+  <si>
+    <t>seinan</t>
+  </si>
+  <si>
+    <t>seina</t>
+  </si>
+  <si>
+    <t>seinum</t>
+  </si>
+  <si>
+    <t>seini</t>
+  </si>
+  <si>
+    <t>seinu</t>
+  </si>
+  <si>
+    <t>seins</t>
+  </si>
+  <si>
+    <t>seinar</t>
+  </si>
+  <si>
+    <t>seinir</t>
+  </si>
+  <si>
+    <t>seinni</t>
+  </si>
+  <si>
+    <t>seinastr</t>
+  </si>
+  <si>
     <t>adverb a (none)</t>
   </si>
   <si>
@@ -15470,12 +15545,6 @@
   </si>
   <si>
     <t>positive</t>
-  </si>
-  <si>
-    <t>comparative</t>
-  </si>
-  <si>
-    <t>superlative</t>
   </si>
   <si>
     <t>adverb b</t>
@@ -52016,28 +52085,50 @@
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" s="12"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
+      <c r="A40" s="8" t="s">
+        <v>5113</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>5114</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>5115</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>5116</v>
+      </c>
       <c r="E40" s="12"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
+      <c r="F40" s="8" t="s">
+        <v>5113</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>3481</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>5115</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>5117</v>
+      </c>
+      <c r="J40" s="10"/>
+      <c r="K40" s="8" t="s">
+        <v>5113</v>
+      </c>
+      <c r="L40" s="10" t="s">
+        <v>5118</v>
+      </c>
+      <c r="M40" s="8" t="s">
+        <v>5115</v>
+      </c>
+      <c r="N40" s="10" t="s">
+        <v>5119</v>
+      </c>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" s="8" t="s">
-        <v>5113</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>5114</v>
-      </c>
+      <c r="A41" s="12"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
       <c r="E41" s="12"/>
       <c r="F41" s="9"/>
       <c r="G41" s="9"/>
@@ -52051,16 +52142,10 @@
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="8" t="s">
-        <v>4925</v>
+        <v>5120</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>4964</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>4965</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>4504</v>
+        <v>5121</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="9"/>
@@ -52075,16 +52160,16 @@
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="8" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>987</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>5115</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>5116</v>
+        <v>4925</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>4964</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>4965</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>4504</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="9"/>
@@ -52099,10 +52184,16 @@
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" s="8" t="s">
-        <v>4519</v>
+        <v>4508</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>987</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>5117</v>
+        <v>5122</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>5123</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="9"/>
@@ -52117,16 +52208,10 @@
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="8" t="s">
-        <v>4526</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>5118</v>
+        <v>4519</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>5119</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>5120</v>
+        <v>5124</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="9"/>
@@ -52141,16 +52226,16 @@
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="8" t="s">
-        <v>4538</v>
+        <v>4526</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>5121</v>
+        <v>5125</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>5122</v>
+        <v>5126</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>5121</v>
+        <v>5127</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="9"/>
@@ -52165,16 +52250,16 @@
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="8" t="s">
-        <v>4949</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>4964</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>4965</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>4504</v>
+        <v>4538</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>5128</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>5129</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>5128</v>
       </c>
       <c r="E47" s="12"/>
       <c r="F47" s="9"/>
@@ -52189,16 +52274,16 @@
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="8" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>5123</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>5122</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>5115</v>
+        <v>4949</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>4964</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>4965</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>4504</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="9"/>
@@ -52213,10 +52298,16 @@
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" s="8" t="s">
-        <v>4519</v>
+        <v>4508</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>5117</v>
+        <v>5130</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>5129</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>5122</v>
       </c>
       <c r="E49" s="12"/>
       <c r="F49" s="9"/>
@@ -52231,10 +52322,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" s="8" t="s">
-        <v>4526</v>
+        <v>4519</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>5118</v>
+        <v>5124</v>
       </c>
       <c r="E50" s="12"/>
       <c r="F50" s="9"/>
@@ -52249,10 +52340,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" s="8" t="s">
-        <v>4538</v>
+        <v>4526</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>5117</v>
+        <v>5125</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="9"/>
@@ -52266,10 +52357,12 @@
       <c r="N51" s="9"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
-      <c r="A52" s="12"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
+      <c r="A52" s="8" t="s">
+        <v>4538</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>5124</v>
+      </c>
       <c r="E52" s="12"/>
       <c r="F52" s="9"/>
       <c r="G52" s="9"/>
@@ -52283,10 +52376,16 @@
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>5124</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>5125</v>
+        <v>5113</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>5131</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>5115</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>5132</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="9"/>
@@ -52300,18 +52399,10 @@
       <c r="N53" s="9"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
-      <c r="A54" s="8" t="s">
-        <v>4925</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>4964</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>4965</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>4504</v>
-      </c>
+      <c r="A54" s="12"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
       <c r="E54" s="12"/>
       <c r="F54" s="9"/>
       <c r="G54" s="9"/>
@@ -52325,16 +52416,10 @@
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" s="8" t="s">
-        <v>4508</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>1100</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>5126</v>
+        <v>5133</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>5134</v>
       </c>
       <c r="E55" s="12"/>
       <c r="F55" s="9"/>
@@ -52349,13 +52434,16 @@
     </row>
     <row r="56" ht="18.75" customHeight="1">
       <c r="A56" s="8" t="s">
-        <v>4519</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>5127</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>5128</v>
+        <v>4925</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>4964</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>4965</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>4504</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="9"/>
@@ -52370,16 +52458,16 @@
     </row>
     <row r="57" ht="18.75" customHeight="1">
       <c r="A57" s="8" t="s">
-        <v>4526</v>
+        <v>4508</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>5129</v>
+        <v>1100</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>5130</v>
+        <v>1100</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>5131</v>
+        <v>5135</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="9"/>
@@ -52394,16 +52482,13 @@
     </row>
     <row r="58" ht="18.75" customHeight="1">
       <c r="A58" s="8" t="s">
-        <v>4538</v>
+        <v>4519</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>5132</v>
+        <v>5136</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>5133</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>5132</v>
+        <v>5137</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="9"/>
@@ -52418,16 +52503,16 @@
     </row>
     <row r="59" ht="18.75" customHeight="1">
       <c r="A59" s="8" t="s">
-        <v>4949</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>4964</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>4965</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>4504</v>
+        <v>4526</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>5138</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>5139</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>5140</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="9"/>
@@ -52442,16 +52527,16 @@
     </row>
     <row r="60" ht="18.75" customHeight="1">
       <c r="A60" s="8" t="s">
-        <v>4508</v>
+        <v>4538</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>5134</v>
+        <v>5141</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>5133</v>
+        <v>5142</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>1100</v>
+        <v>5141</v>
       </c>
       <c r="E60" s="12"/>
       <c r="F60" s="9"/>
@@ -52466,10 +52551,16 @@
     </row>
     <row r="61" ht="18.75" customHeight="1">
       <c r="A61" s="8" t="s">
-        <v>4519</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>5128</v>
+        <v>4949</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>4964</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>4965</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>4504</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="9"/>
@@ -52484,10 +52575,16 @@
     </row>
     <row r="62" ht="18.75" customHeight="1">
       <c r="A62" s="8" t="s">
-        <v>4526</v>
+        <v>4508</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>5129</v>
+        <v>5143</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>5142</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>1100</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="9"/>
@@ -52502,10 +52599,10 @@
     </row>
     <row r="63" ht="18.75" customHeight="1">
       <c r="A63" s="8" t="s">
-        <v>4538</v>
+        <v>4519</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>5128</v>
+        <v>5137</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="9"/>
@@ -52518,8 +52615,345 @@
       <c r="M63" s="9"/>
       <c r="N63" s="9"/>
     </row>
+    <row r="64" ht="18.75" customHeight="1">
+      <c r="A64" s="8" t="s">
+        <v>4526</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>5138</v>
+      </c>
+      <c r="E64" s="12"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="9"/>
+      <c r="K64" s="9"/>
+      <c r="L64" s="9"/>
+      <c r="M64" s="9"/>
+      <c r="N64" s="9"/>
+    </row>
+    <row r="65" ht="18.75" customHeight="1">
+      <c r="A65" s="8" t="s">
+        <v>4538</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>5137</v>
+      </c>
+      <c r="E65" s="12"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="9"/>
+      <c r="K65" s="9"/>
+      <c r="L65" s="9"/>
+      <c r="M65" s="9"/>
+      <c r="N65" s="9"/>
+    </row>
+    <row r="66" ht="18.75" customHeight="1">
+      <c r="A66" s="8" t="s">
+        <v>5113</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>5144</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>5115</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>5145</v>
+      </c>
+      <c r="E66" s="12"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
+      <c r="I66" s="9"/>
+      <c r="J66" s="9"/>
+      <c r="K66" s="9"/>
+      <c r="L66" s="9"/>
+      <c r="M66" s="9"/>
+      <c r="N66" s="9"/>
+    </row>
+    <row r="67" ht="18.75" customHeight="1">
+      <c r="A67" s="12"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="9"/>
+      <c r="I67" s="9"/>
+      <c r="J67" s="9"/>
+      <c r="K67" s="9"/>
+      <c r="L67" s="9"/>
+      <c r="M67" s="9"/>
+      <c r="N67" s="9"/>
+    </row>
+    <row r="68" ht="18.75" customHeight="1">
+      <c r="A68" s="8" t="s">
+        <v>5146</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>5147</v>
+      </c>
+      <c r="E68" s="12"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9"/>
+      <c r="I68" s="9"/>
+      <c r="J68" s="9"/>
+      <c r="K68" s="9"/>
+      <c r="L68" s="9"/>
+      <c r="M68" s="9"/>
+      <c r="N68" s="9"/>
+    </row>
+    <row r="69" ht="18.75" customHeight="1">
+      <c r="A69" s="8" t="s">
+        <v>4925</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>4964</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>4965</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>4504</v>
+      </c>
+      <c r="E69" s="12"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="9"/>
+      <c r="H69" s="9"/>
+      <c r="I69" s="9"/>
+      <c r="J69" s="9"/>
+      <c r="K69" s="9"/>
+      <c r="L69" s="9"/>
+      <c r="M69" s="9"/>
+      <c r="N69" s="9"/>
+    </row>
+    <row r="70" ht="18.75" customHeight="1">
+      <c r="A70" s="8" t="s">
+        <v>4508</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>3196</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>5148</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>5149</v>
+      </c>
+      <c r="E70" s="12"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="9"/>
+      <c r="I70" s="9"/>
+      <c r="J70" s="9"/>
+      <c r="K70" s="9"/>
+      <c r="L70" s="9"/>
+      <c r="M70" s="9"/>
+      <c r="N70" s="9"/>
+    </row>
+    <row r="71" ht="18.75" customHeight="1">
+      <c r="A71" s="8" t="s">
+        <v>4519</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>5150</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>5151</v>
+      </c>
+      <c r="E71" s="12"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="9"/>
+      <c r="I71" s="9"/>
+      <c r="J71" s="9"/>
+      <c r="K71" s="9"/>
+      <c r="L71" s="9"/>
+      <c r="M71" s="9"/>
+      <c r="N71" s="9"/>
+    </row>
+    <row r="72" ht="18.75" customHeight="1">
+      <c r="A72" s="8" t="s">
+        <v>4526</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>5152</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>5153</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>5154</v>
+      </c>
+      <c r="E72" s="12"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="9"/>
+      <c r="H72" s="9"/>
+      <c r="I72" s="9"/>
+      <c r="J72" s="9"/>
+      <c r="K72" s="9"/>
+      <c r="L72" s="9"/>
+      <c r="M72" s="9"/>
+      <c r="N72" s="9"/>
+    </row>
+    <row r="73" ht="18.75" customHeight="1">
+      <c r="A73" s="8" t="s">
+        <v>4538</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>5155</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>5156</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>5155</v>
+      </c>
+      <c r="E73" s="12"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="9"/>
+      <c r="H73" s="9"/>
+      <c r="I73" s="9"/>
+      <c r="J73" s="9"/>
+      <c r="K73" s="9"/>
+      <c r="L73" s="9"/>
+      <c r="M73" s="9"/>
+      <c r="N73" s="9"/>
+    </row>
+    <row r="74" ht="18.75" customHeight="1">
+      <c r="A74" s="8" t="s">
+        <v>4949</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>4964</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>4965</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>4504</v>
+      </c>
+      <c r="E74" s="12"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="9"/>
+      <c r="H74" s="9"/>
+      <c r="I74" s="9"/>
+      <c r="J74" s="9"/>
+      <c r="K74" s="9"/>
+      <c r="L74" s="9"/>
+      <c r="M74" s="9"/>
+      <c r="N74" s="9"/>
+    </row>
+    <row r="75" ht="18.75" customHeight="1">
+      <c r="A75" s="8" t="s">
+        <v>4508</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>5157</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>5156</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>5148</v>
+      </c>
+      <c r="E75" s="12"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9"/>
+      <c r="I75" s="9"/>
+      <c r="J75" s="9"/>
+      <c r="K75" s="9"/>
+      <c r="L75" s="9"/>
+      <c r="M75" s="9"/>
+      <c r="N75" s="9"/>
+    </row>
+    <row r="76" ht="18.75" customHeight="1">
+      <c r="A76" s="8" t="s">
+        <v>4519</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>5151</v>
+      </c>
+      <c r="E76" s="12"/>
+      <c r="F76" s="9"/>
+      <c r="G76" s="9"/>
+      <c r="H76" s="9"/>
+      <c r="I76" s="9"/>
+      <c r="J76" s="9"/>
+      <c r="K76" s="9"/>
+      <c r="L76" s="9"/>
+      <c r="M76" s="9"/>
+      <c r="N76" s="9"/>
+    </row>
+    <row r="77" ht="18.75" customHeight="1">
+      <c r="A77" s="8" t="s">
+        <v>4526</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>5152</v>
+      </c>
+      <c r="E77" s="12"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9"/>
+      <c r="L77" s="9"/>
+      <c r="M77" s="9"/>
+      <c r="N77" s="9"/>
+    </row>
+    <row r="78" ht="18.75" customHeight="1">
+      <c r="A78" s="8" t="s">
+        <v>4538</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>5151</v>
+      </c>
+      <c r="E78" s="12"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="9"/>
+      <c r="I78" s="9"/>
+      <c r="J78" s="9"/>
+      <c r="K78" s="9"/>
+      <c r="L78" s="9"/>
+      <c r="M78" s="9"/>
+      <c r="N78" s="9"/>
+    </row>
+    <row r="79" ht="18.75" customHeight="1">
+      <c r="A79" s="8" t="s">
+        <v>5113</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>5158</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>5115</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>5159</v>
+      </c>
+      <c r="E79" s="12"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="9"/>
+      <c r="H79" s="9"/>
+      <c r="I79" s="9"/>
+      <c r="J79" s="9"/>
+      <c r="K79" s="9"/>
+      <c r="L79" s="9"/>
+      <c r="M79" s="9"/>
+      <c r="N79" s="9"/>
+    </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="65">
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="D31:D32"/>
@@ -52527,19 +52961,25 @@
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B39:D39"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B68:D68"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="F5:F7"/>
     <mergeCell ref="C9:C10"/>
@@ -52596,10 +53036,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>5135</v>
+        <v>5160</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>5136</v>
+        <v>5161</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -52614,7 +53054,7 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="8" t="s">
-        <v>5137</v>
+        <v>5162</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>2811</v>
@@ -52632,7 +53072,7 @@
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>5138</v>
+        <v>5113</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>2813</v>
@@ -52650,7 +53090,7 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="8" t="s">
-        <v>5139</v>
+        <v>5115</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>2815</v>
@@ -52682,13 +53122,13 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>5140</v>
+        <v>5163</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>5141</v>
+        <v>5164</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>5142</v>
+        <v>5165</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -52702,7 +53142,7 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>5137</v>
+        <v>5162</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>2698</v>
@@ -52720,7 +53160,7 @@
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>5138</v>
+        <v>5113</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>2660</v>
@@ -52740,7 +53180,7 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>5139</v>
+        <v>5115</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>2662</v>
@@ -52907,27 +53347,27 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="18" t="s">
-        <v>5143</v>
+        <v>5166</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="20" t="s">
-        <v>5144</v>
+        <v>5167</v>
       </c>
       <c r="D1" s="19"/>
       <c r="E1" s="18" t="s">
-        <v>5145</v>
+        <v>5168</v>
       </c>
       <c r="F1" s="19"/>
       <c r="G1" s="18" t="s">
-        <v>5146</v>
+        <v>5169</v>
       </c>
       <c r="H1" s="19"/>
       <c r="I1" s="18" t="s">
-        <v>5147</v>
+        <v>5170</v>
       </c>
       <c r="J1" s="19"/>
       <c r="K1" s="18" t="s">
-        <v>5148</v>
+        <v>5171</v>
       </c>
       <c r="L1" s="19"/>
       <c r="M1" s="10"/>
@@ -52940,27 +53380,27 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="21" t="s">
-        <v>5149</v>
+        <v>5172</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="10" t="s">
-        <v>5150</v>
+        <v>5173</v>
       </c>
       <c r="D2" s="22"/>
       <c r="E2" s="23" t="s">
-        <v>5151</v>
+        <v>5174</v>
       </c>
       <c r="F2" s="22"/>
       <c r="G2" s="23" t="s">
-        <v>5152</v>
+        <v>5175</v>
       </c>
       <c r="H2" s="22"/>
       <c r="I2" s="23" t="s">
-        <v>5153</v>
+        <v>5176</v>
       </c>
       <c r="J2" s="22"/>
       <c r="K2" s="23" t="s">
-        <v>5154</v>
+        <v>5177</v>
       </c>
       <c r="L2" s="22"/>
       <c r="M2" s="10"/>
@@ -52973,27 +53413,27 @@
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="21" t="s">
-        <v>5155</v>
+        <v>5178</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="10" t="s">
-        <v>5156</v>
+        <v>5179</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="23" t="s">
-        <v>5157</v>
+        <v>5180</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="23" t="s">
-        <v>5158</v>
+        <v>5181</v>
       </c>
       <c r="H3" s="22"/>
       <c r="I3" s="23" t="s">
-        <v>5159</v>
+        <v>5182</v>
       </c>
       <c r="J3" s="22"/>
       <c r="K3" s="23" t="s">
-        <v>5160</v>
+        <v>5183</v>
       </c>
       <c r="L3" s="22"/>
       <c r="M3" s="10"/>
@@ -53006,27 +53446,27 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="21" t="s">
-        <v>5161</v>
+        <v>5184</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="10" t="s">
-        <v>5162</v>
+        <v>5185</v>
       </c>
       <c r="D4" s="22"/>
       <c r="E4" s="23" t="s">
-        <v>5163</v>
+        <v>5186</v>
       </c>
       <c r="F4" s="22"/>
       <c r="G4" s="23" t="s">
-        <v>5164</v>
+        <v>5187</v>
       </c>
       <c r="H4" s="22"/>
       <c r="I4" s="23" t="s">
-        <v>5165</v>
+        <v>5188</v>
       </c>
       <c r="J4" s="22"/>
       <c r="K4" s="23" t="s">
-        <v>5166</v>
+        <v>5189</v>
       </c>
       <c r="L4" s="22"/>
       <c r="M4" s="10"/>
@@ -53039,38 +53479,38 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>5167</v>
+        <v>5190</v>
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="L5" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
@@ -53085,37 +53525,37 @@
         <v>4925</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>862</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>5171</v>
+        <v>5194</v>
       </c>
       <c r="E6" s="23" t="s">
         <v>1200</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>5172</v>
+        <v>5195</v>
       </c>
       <c r="G6" s="23" t="s">
         <v>2057</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>5173</v>
+        <v>5196</v>
       </c>
       <c r="I6" s="23" t="s">
         <v>3415</v>
       </c>
       <c r="J6" s="25" t="s">
-        <v>5174</v>
+        <v>5197</v>
       </c>
       <c r="K6" s="23" t="s">
         <v>3667</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>5175</v>
+        <v>5198</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
@@ -53131,34 +53571,34 @@
         <v>4464</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>5176</v>
+        <v>5199</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>5177</v>
+        <v>5200</v>
       </c>
       <c r="E7" s="23" t="s">
         <v>4881</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>5178</v>
+        <v>5201</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>5179</v>
+        <v>5202</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>5180</v>
+        <v>5203</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>5181</v>
+        <v>5204</v>
       </c>
       <c r="J7" s="25" t="s">
-        <v>5182</v>
+        <v>5205</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>5183</v>
+        <v>5206</v>
       </c>
       <c r="L7" s="25" t="s">
-        <v>5184</v>
+        <v>5207</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
@@ -53171,37 +53611,37 @@
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="26"/>
       <c r="B8" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>5176</v>
+        <v>5199</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>5186</v>
+        <v>5209</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>4881</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>5187</v>
+        <v>5210</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>5179</v>
+        <v>5202</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>5188</v>
+        <v>5211</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>5181</v>
+        <v>5204</v>
       </c>
       <c r="J8" s="25" t="s">
-        <v>5189</v>
+        <v>5212</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>5183</v>
+        <v>5206</v>
       </c>
       <c r="L8" s="25" t="s">
-        <v>5190</v>
+        <v>5213</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
@@ -53219,34 +53659,34 @@
         <v>4293</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>5191</v>
+        <v>5214</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>5192</v>
+        <v>5215</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>4895</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>5193</v>
+        <v>5216</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>5194</v>
+        <v>5217</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>5195</v>
+        <v>5218</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>5196</v>
+        <v>5219</v>
       </c>
       <c r="J9" s="25" t="s">
-        <v>5197</v>
+        <v>5220</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>5198</v>
+        <v>5221</v>
       </c>
       <c r="L9" s="25" t="s">
-        <v>5199</v>
+        <v>5222</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
@@ -53262,34 +53702,34 @@
         <v>4414</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>5200</v>
+        <v>5223</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>5201</v>
+        <v>5224</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>5202</v>
+        <v>5225</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>5203</v>
+        <v>5226</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>5204</v>
+        <v>5227</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>5205</v>
+        <v>5228</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>5206</v>
+        <v>5229</v>
       </c>
       <c r="J10" s="25" t="s">
-        <v>5207</v>
+        <v>5230</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>5208</v>
+        <v>5231</v>
       </c>
       <c r="L10" s="25" t="s">
-        <v>5209</v>
+        <v>5232</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
@@ -53302,37 +53742,37 @@
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="26"/>
       <c r="B11" s="24" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>5211</v>
+        <v>5234</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>5212</v>
+        <v>5235</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>5213</v>
+        <v>5236</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>5214</v>
+        <v>5237</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>5215</v>
+        <v>5238</v>
       </c>
       <c r="H11" s="25" t="s">
-        <v>5216</v>
+        <v>5239</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>5217</v>
+        <v>5240</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>5218</v>
+        <v>5241</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>5219</v>
+        <v>5242</v>
       </c>
       <c r="L11" s="28" t="s">
-        <v>5220</v>
+        <v>5243</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
@@ -53344,14 +53784,14 @@
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="21" t="s">
-        <v>5221</v>
+        <v>5244</v>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E12" s="29"/>
       <c r="F12" s="30"/>
@@ -53374,13 +53814,13 @@
         <v>4925</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>5222</v>
+        <v>5245</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>5223</v>
+        <v>5246</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="10"/>
@@ -53424,7 +53864,7 @@
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="26"/>
       <c r="B15" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C15" s="26"/>
       <c r="D15" s="22"/>
@@ -53452,10 +53892,10 @@
         <v>4293</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>5224</v>
+        <v>5247</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>5225</v>
+        <v>5248</v>
       </c>
       <c r="E16" s="23"/>
       <c r="F16" s="10"/>
@@ -53479,10 +53919,10 @@
         <v>4414</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>5226</v>
+        <v>5249</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>5227</v>
+        <v>5250</v>
       </c>
       <c r="E17" s="23"/>
       <c r="F17" s="10"/>
@@ -53503,7 +53943,7 @@
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="31"/>
       <c r="B18" s="32" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C18" s="33"/>
       <c r="D18" s="34"/>
@@ -53546,27 +53986,27 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>5228</v>
+        <v>5251</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="20" t="s">
-        <v>5229</v>
+        <v>5252</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="18" t="s">
-        <v>5230</v>
+        <v>5253</v>
       </c>
       <c r="F20" s="19"/>
       <c r="G20" s="18" t="s">
-        <v>5231</v>
+        <v>5254</v>
       </c>
       <c r="H20" s="19"/>
       <c r="I20" s="18" t="s">
-        <v>5232</v>
+        <v>5255</v>
       </c>
       <c r="J20" s="19"/>
       <c r="K20" s="18" t="s">
-        <v>5233</v>
+        <v>5256</v>
       </c>
       <c r="L20" s="19"/>
       <c r="M20" s="10"/>
@@ -53579,27 +54019,27 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="21" t="s">
-        <v>5149</v>
+        <v>5172</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="10" t="s">
-        <v>5234</v>
+        <v>5257</v>
       </c>
       <c r="D21" s="22"/>
       <c r="E21" s="23" t="s">
-        <v>5235</v>
+        <v>5258</v>
       </c>
       <c r="F21" s="22"/>
       <c r="G21" s="23" t="s">
-        <v>5236</v>
+        <v>5259</v>
       </c>
       <c r="H21" s="22"/>
       <c r="I21" s="23" t="s">
-        <v>5237</v>
+        <v>5260</v>
       </c>
       <c r="J21" s="22"/>
       <c r="K21" s="23" t="s">
-        <v>5238</v>
+        <v>5261</v>
       </c>
       <c r="L21" s="22"/>
       <c r="M21" s="10"/>
@@ -53612,27 +54052,27 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="21" t="s">
-        <v>5155</v>
+        <v>5178</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="10" t="s">
-        <v>5239</v>
+        <v>5262</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="23" t="s">
-        <v>5240</v>
+        <v>5263</v>
       </c>
       <c r="F22" s="22"/>
       <c r="G22" s="23" t="s">
-        <v>5241</v>
+        <v>5264</v>
       </c>
       <c r="H22" s="22"/>
       <c r="I22" s="23" t="s">
-        <v>5242</v>
+        <v>5265</v>
       </c>
       <c r="J22" s="22"/>
       <c r="K22" s="23" t="s">
-        <v>5243</v>
+        <v>5266</v>
       </c>
       <c r="L22" s="22"/>
       <c r="M22" s="10"/>
@@ -53645,27 +54085,27 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>5161</v>
+        <v>5184</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="10" t="s">
-        <v>5244</v>
+        <v>5267</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="23" t="s">
-        <v>5245</v>
+        <v>5268</v>
       </c>
       <c r="F23" s="22"/>
       <c r="G23" s="23" t="s">
-        <v>5246</v>
+        <v>5269</v>
       </c>
       <c r="H23" s="22"/>
       <c r="I23" s="23" t="s">
-        <v>5247</v>
+        <v>5270</v>
       </c>
       <c r="J23" s="22"/>
       <c r="K23" s="23" t="s">
-        <v>5248</v>
+        <v>5271</v>
       </c>
       <c r="L23" s="22"/>
       <c r="M23" s="10"/>
@@ -53678,38 +54118,38 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>5167</v>
+        <v>5190</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="I24" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="J24" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="K24" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="L24" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
@@ -53724,37 +54164,37 @@
         <v>4925</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>5249</v>
+        <v>5272</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>5250</v>
+        <v>5273</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>5251</v>
+        <v>5274</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>5252</v>
+        <v>5275</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>5253</v>
+        <v>5276</v>
       </c>
       <c r="H25" s="25" t="s">
-        <v>5254</v>
+        <v>5277</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>5255</v>
+        <v>5278</v>
       </c>
       <c r="J25" s="25" t="s">
-        <v>5256</v>
+        <v>5279</v>
       </c>
       <c r="K25" s="23" t="s">
-        <v>5257</v>
+        <v>5280</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>5258</v>
+        <v>5281</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
@@ -53770,34 +54210,34 @@
         <v>4464</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>5259</v>
+        <v>5282</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>5260</v>
+        <v>5283</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>5261</v>
+        <v>5284</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>5262</v>
+        <v>5285</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>5263</v>
+        <v>5286</v>
       </c>
       <c r="H26" s="25" t="s">
-        <v>5264</v>
+        <v>5287</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>5265</v>
+        <v>5288</v>
       </c>
       <c r="J26" s="25" t="s">
-        <v>5266</v>
+        <v>5289</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>5267</v>
+        <v>5290</v>
       </c>
       <c r="L26" s="25" t="s">
-        <v>5268</v>
+        <v>5291</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10"/>
@@ -53810,37 +54250,37 @@
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="26"/>
       <c r="B27" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>5259</v>
+        <v>5282</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>5269</v>
+        <v>5292</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>5261</v>
+        <v>5284</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>5270</v>
+        <v>5293</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>5263</v>
+        <v>5286</v>
       </c>
       <c r="H27" s="25" t="s">
-        <v>5271</v>
+        <v>5294</v>
       </c>
       <c r="I27" s="23" t="s">
-        <v>5265</v>
+        <v>5288</v>
       </c>
       <c r="J27" s="25" t="s">
-        <v>5272</v>
+        <v>5295</v>
       </c>
       <c r="K27" s="23" t="s">
-        <v>5267</v>
+        <v>5290</v>
       </c>
       <c r="L27" s="25" t="s">
-        <v>5273</v>
+        <v>5296</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
@@ -53858,34 +54298,34 @@
         <v>4293</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>5274</v>
+        <v>5297</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>5275</v>
+        <v>5298</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>5276</v>
+        <v>5299</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>5277</v>
+        <v>5300</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>5278</v>
+        <v>5301</v>
       </c>
       <c r="H28" s="25" t="s">
-        <v>5279</v>
+        <v>5302</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>5280</v>
+        <v>5303</v>
       </c>
       <c r="J28" s="25" t="s">
-        <v>5281</v>
+        <v>5304</v>
       </c>
       <c r="K28" s="23" t="s">
-        <v>5282</v>
+        <v>5305</v>
       </c>
       <c r="L28" s="25" t="s">
-        <v>5283</v>
+        <v>5306</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
@@ -53900,34 +54340,34 @@
         <v>4414</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>5284</v>
+        <v>5307</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>5285</v>
+        <v>5308</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>5286</v>
+        <v>5309</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>5287</v>
+        <v>5310</v>
       </c>
       <c r="G29" s="23" t="s">
-        <v>5288</v>
+        <v>5311</v>
       </c>
       <c r="H29" s="25" t="s">
-        <v>5289</v>
+        <v>5312</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>5290</v>
+        <v>5313</v>
       </c>
       <c r="J29" s="25" t="s">
-        <v>5291</v>
+        <v>5314</v>
       </c>
       <c r="K29" s="23" t="s">
-        <v>5292</v>
+        <v>5315</v>
       </c>
       <c r="L29" s="25" t="s">
-        <v>5293</v>
+        <v>5316</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
@@ -53939,37 +54379,37 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="B30" s="24" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>5294</v>
+        <v>5317</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>5295</v>
+        <v>5318</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>5296</v>
+        <v>5319</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>5297</v>
+        <v>5320</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>5298</v>
+        <v>5321</v>
       </c>
       <c r="H30" s="25" t="s">
-        <v>5299</v>
+        <v>5322</v>
       </c>
       <c r="I30" s="23" t="s">
-        <v>5300</v>
+        <v>5323</v>
       </c>
       <c r="J30" s="25" t="s">
-        <v>5301</v>
+        <v>5324</v>
       </c>
       <c r="K30" s="23" t="s">
-        <v>5302</v>
+        <v>5325</v>
       </c>
       <c r="L30" s="25" t="s">
-        <v>5303</v>
+        <v>5326</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
@@ -53981,7 +54421,7 @@
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="21" t="s">
-        <v>5221</v>
+        <v>5244</v>
       </c>
       <c r="B31" s="22"/>
       <c r="C31" s="29"/>
@@ -53993,10 +54433,10 @@
       <c r="I31" s="30"/>
       <c r="J31" s="35"/>
       <c r="K31" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="L31" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
@@ -54011,7 +54451,7 @@
         <v>4925</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C32" s="23"/>
       <c r="D32" s="10"/>
@@ -54022,10 +54462,10 @@
       <c r="I32" s="10"/>
       <c r="J32" s="25"/>
       <c r="K32" s="10" t="s">
-        <v>5304</v>
+        <v>5327</v>
       </c>
       <c r="L32" s="25" t="s">
-        <v>5305</v>
+        <v>5328</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
@@ -54060,7 +54500,7 @@
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="26"/>
       <c r="B34" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C34" s="23"/>
       <c r="D34" s="10"/>
@@ -54095,10 +54535,10 @@
       <c r="I35" s="10"/>
       <c r="J35" s="25"/>
       <c r="K35" s="10" t="s">
-        <v>5306</v>
+        <v>5329</v>
       </c>
       <c r="L35" s="25" t="s">
-        <v>5307</v>
+        <v>5330</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
@@ -54122,10 +54562,10 @@
       <c r="I36" s="10"/>
       <c r="J36" s="25"/>
       <c r="K36" s="10" t="s">
-        <v>5308</v>
+        <v>5331</v>
       </c>
       <c r="L36" s="25" t="s">
-        <v>5309</v>
+        <v>5332</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10"/>
@@ -54138,7 +54578,7 @@
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="31"/>
       <c r="B37" s="32" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C37" s="23"/>
       <c r="D37" s="10"/>
@@ -54183,19 +54623,19 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="18" t="s">
-        <v>5310</v>
+        <v>5333</v>
       </c>
       <c r="D39" s="19"/>
       <c r="E39" s="18" t="s">
-        <v>5311</v>
+        <v>5334</v>
       </c>
       <c r="F39" s="19"/>
       <c r="G39" s="18" t="s">
-        <v>5312</v>
+        <v>5335</v>
       </c>
       <c r="H39" s="19"/>
       <c r="I39" s="18" t="s">
-        <v>5313</v>
+        <v>5336</v>
       </c>
       <c r="J39" s="19"/>
       <c r="K39" s="10"/>
@@ -54212,19 +54652,19 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="23" t="s">
-        <v>5314</v>
+        <v>5337</v>
       </c>
       <c r="D40" s="22"/>
       <c r="E40" s="23" t="s">
-        <v>5315</v>
+        <v>5338</v>
       </c>
       <c r="F40" s="22"/>
       <c r="G40" s="23" t="s">
-        <v>5316</v>
+        <v>5339</v>
       </c>
       <c r="H40" s="22"/>
       <c r="I40" s="23" t="s">
-        <v>5317</v>
+        <v>5340</v>
       </c>
       <c r="J40" s="22"/>
       <c r="K40" s="10"/>
@@ -54241,19 +54681,19 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="23" t="s">
-        <v>5318</v>
+        <v>5341</v>
       </c>
       <c r="D41" s="22"/>
       <c r="E41" s="23" t="s">
-        <v>5319</v>
+        <v>5342</v>
       </c>
       <c r="F41" s="22"/>
       <c r="G41" s="23" t="s">
-        <v>5320</v>
+        <v>5343</v>
       </c>
       <c r="H41" s="22"/>
       <c r="I41" s="23" t="s">
-        <v>5321</v>
+        <v>5344</v>
       </c>
       <c r="J41" s="22"/>
       <c r="K41" s="10"/>
@@ -54270,19 +54710,19 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="23" t="s">
-        <v>5322</v>
+        <v>5345</v>
       </c>
       <c r="D42" s="22"/>
       <c r="E42" s="23" t="s">
-        <v>5323</v>
+        <v>5346</v>
       </c>
       <c r="F42" s="22"/>
       <c r="G42" s="23" t="s">
-        <v>5324</v>
+        <v>5347</v>
       </c>
       <c r="H42" s="22"/>
       <c r="I42" s="23" t="s">
-        <v>5325</v>
+        <v>5348</v>
       </c>
       <c r="J42" s="22"/>
       <c r="K42" s="10"/>
@@ -54299,28 +54739,28 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E43" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="G43" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="I43" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="J43" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="K43" s="10"/>
       <c r="L43" s="10"/>
@@ -54336,28 +54776,28 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="23" t="s">
-        <v>5326</v>
+        <v>5349</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>5327</v>
+        <v>5350</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>5328</v>
+        <v>5351</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>5329</v>
+        <v>5352</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>5330</v>
+        <v>5353</v>
       </c>
       <c r="H44" s="25" t="s">
-        <v>5331</v>
+        <v>5354</v>
       </c>
       <c r="I44" s="23" t="s">
-        <v>5332</v>
+        <v>5355</v>
       </c>
       <c r="J44" s="25" t="s">
-        <v>5333</v>
+        <v>5356</v>
       </c>
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
@@ -54373,28 +54813,28 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="23" t="s">
-        <v>5334</v>
+        <v>5357</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>5335</v>
+        <v>5358</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>5336</v>
+        <v>5359</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>5337</v>
+        <v>5360</v>
       </c>
       <c r="G45" s="23" t="s">
-        <v>5338</v>
+        <v>5361</v>
       </c>
       <c r="H45" s="25" t="s">
-        <v>5339</v>
+        <v>5362</v>
       </c>
       <c r="I45" s="23" t="s">
-        <v>5340</v>
+        <v>5363</v>
       </c>
       <c r="J45" s="25" t="s">
-        <v>5341</v>
+        <v>5364</v>
       </c>
       <c r="K45" s="10"/>
       <c r="L45" s="10"/>
@@ -54410,28 +54850,28 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="23" t="s">
-        <v>5334</v>
+        <v>5357</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>5342</v>
+        <v>5365</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>5336</v>
+        <v>5359</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>5343</v>
+        <v>5366</v>
       </c>
       <c r="G46" s="23" t="s">
-        <v>5338</v>
+        <v>5361</v>
       </c>
       <c r="H46" s="25" t="s">
-        <v>5344</v>
+        <v>5367</v>
       </c>
       <c r="I46" s="23" t="s">
-        <v>5340</v>
+        <v>5363</v>
       </c>
       <c r="J46" s="25" t="s">
-        <v>5345</v>
+        <v>5368</v>
       </c>
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
@@ -54447,28 +54887,28 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="23" t="s">
-        <v>5346</v>
+        <v>5369</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>5347</v>
+        <v>5370</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>5348</v>
+        <v>5371</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>5349</v>
+        <v>5372</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>5350</v>
+        <v>5373</v>
       </c>
       <c r="H47" s="25" t="s">
-        <v>5351</v>
+        <v>5374</v>
       </c>
       <c r="I47" s="23" t="s">
-        <v>5352</v>
+        <v>5375</v>
       </c>
       <c r="J47" s="25" t="s">
-        <v>5353</v>
+        <v>5376</v>
       </c>
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
@@ -54484,28 +54924,28 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="23" t="s">
-        <v>5354</v>
+        <v>5377</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>5355</v>
+        <v>5378</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>5356</v>
+        <v>5379</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>5357</v>
+        <v>5380</v>
       </c>
       <c r="G48" s="23" t="s">
-        <v>5358</v>
+        <v>5381</v>
       </c>
       <c r="H48" s="25" t="s">
-        <v>5359</v>
+        <v>5382</v>
       </c>
       <c r="I48" s="23" t="s">
-        <v>5360</v>
+        <v>5383</v>
       </c>
       <c r="J48" s="25" t="s">
-        <v>5361</v>
+        <v>5384</v>
       </c>
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
@@ -54521,28 +54961,28 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="36" t="s">
-        <v>5362</v>
+        <v>5385</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>5363</v>
+        <v>5386</v>
       </c>
       <c r="E49" s="36" t="s">
-        <v>5364</v>
+        <v>5387</v>
       </c>
       <c r="F49" s="28" t="s">
-        <v>5365</v>
+        <v>5388</v>
       </c>
       <c r="G49" s="36" t="s">
-        <v>5366</v>
+        <v>5389</v>
       </c>
       <c r="H49" s="28" t="s">
-        <v>5367</v>
+        <v>5390</v>
       </c>
       <c r="I49" s="36" t="s">
-        <v>5368</v>
+        <v>5391</v>
       </c>
       <c r="J49" s="28" t="s">
-        <v>5369</v>
+        <v>5392</v>
       </c>
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
@@ -54581,23 +55021,23 @@
       </c>
       <c r="B51" s="19"/>
       <c r="C51" s="18" t="s">
-        <v>5370</v>
+        <v>5393</v>
       </c>
       <c r="D51" s="19"/>
       <c r="E51" s="20" t="s">
-        <v>5371</v>
+        <v>5394</v>
       </c>
       <c r="F51" s="19"/>
       <c r="G51" s="18" t="s">
-        <v>5372</v>
+        <v>5395</v>
       </c>
       <c r="H51" s="19"/>
       <c r="I51" s="18" t="s">
-        <v>5373</v>
+        <v>5396</v>
       </c>
       <c r="J51" s="19"/>
       <c r="K51" s="18" t="s">
-        <v>5374</v>
+        <v>5397</v>
       </c>
       <c r="L51" s="19"/>
       <c r="M51" s="10"/>
@@ -54610,27 +55050,27 @@
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" s="21" t="s">
-        <v>5149</v>
+        <v>5172</v>
       </c>
       <c r="B52" s="22"/>
       <c r="C52" s="10" t="s">
-        <v>5375</v>
+        <v>5398</v>
       </c>
       <c r="D52" s="22"/>
       <c r="E52" s="10" t="s">
-        <v>5376</v>
+        <v>5399</v>
       </c>
       <c r="F52" s="22"/>
       <c r="G52" s="23" t="s">
-        <v>5377</v>
+        <v>5400</v>
       </c>
       <c r="H52" s="22"/>
       <c r="I52" s="23" t="s">
-        <v>5378</v>
+        <v>5401</v>
       </c>
       <c r="J52" s="22"/>
       <c r="K52" s="23" t="s">
-        <v>5379</v>
+        <v>5402</v>
       </c>
       <c r="L52" s="22"/>
       <c r="M52" s="10"/>
@@ -54643,27 +55083,27 @@
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" s="21" t="s">
-        <v>5155</v>
+        <v>5178</v>
       </c>
       <c r="B53" s="22"/>
       <c r="C53" s="10" t="s">
-        <v>5380</v>
+        <v>5403</v>
       </c>
       <c r="D53" s="22"/>
       <c r="E53" s="10" t="s">
-        <v>5381</v>
+        <v>5404</v>
       </c>
       <c r="F53" s="22"/>
       <c r="G53" s="23" t="s">
-        <v>5382</v>
+        <v>5405</v>
       </c>
       <c r="H53" s="22"/>
       <c r="I53" s="23" t="s">
-        <v>5383</v>
+        <v>5406</v>
       </c>
       <c r="J53" s="22"/>
       <c r="K53" s="23" t="s">
-        <v>5384</v>
+        <v>5407</v>
       </c>
       <c r="L53" s="22"/>
       <c r="M53" s="10"/>
@@ -54676,27 +55116,27 @@
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" s="21" t="s">
-        <v>5161</v>
+        <v>5184</v>
       </c>
       <c r="B54" s="22"/>
       <c r="C54" s="10" t="s">
-        <v>5385</v>
+        <v>5408</v>
       </c>
       <c r="D54" s="22"/>
       <c r="E54" s="10" t="s">
-        <v>5386</v>
+        <v>5409</v>
       </c>
       <c r="F54" s="22"/>
       <c r="G54" s="23" t="s">
-        <v>5387</v>
+        <v>5410</v>
       </c>
       <c r="H54" s="22"/>
       <c r="I54" s="23" t="s">
-        <v>5388</v>
+        <v>5411</v>
       </c>
       <c r="J54" s="22"/>
       <c r="K54" s="23" t="s">
-        <v>5389</v>
+        <v>5412</v>
       </c>
       <c r="L54" s="22"/>
       <c r="M54" s="10"/>
@@ -54709,38 +55149,38 @@
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" s="21" t="s">
-        <v>5167</v>
+        <v>5190</v>
       </c>
       <c r="B55" s="22"/>
       <c r="C55" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D55" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="F55" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="G55" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="I55" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="J55" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="K55" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="L55" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10"/>
@@ -54755,37 +55195,37 @@
         <v>4925</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>5390</v>
+        <v>5413</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>5391</v>
+        <v>5414</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>5392</v>
+        <v>5415</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>5393</v>
+        <v>5416</v>
       </c>
       <c r="G56" s="23" t="s">
-        <v>5394</v>
+        <v>5417</v>
       </c>
       <c r="H56" s="25" t="s">
-        <v>5395</v>
+        <v>5418</v>
       </c>
       <c r="I56" s="23" t="s">
-        <v>5396</v>
+        <v>5419</v>
       </c>
       <c r="J56" s="25" t="s">
-        <v>5397</v>
+        <v>5420</v>
       </c>
       <c r="K56" s="23" t="s">
-        <v>5398</v>
+        <v>5421</v>
       </c>
       <c r="L56" s="25" t="s">
-        <v>5399</v>
+        <v>5422</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10"/>
@@ -54801,34 +55241,34 @@
         <v>4464</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>5400</v>
+        <v>5423</v>
       </c>
       <c r="D57" s="25" t="s">
-        <v>5401</v>
+        <v>5424</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>5402</v>
+        <v>5425</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>5403</v>
+        <v>5426</v>
       </c>
       <c r="G57" s="23" t="s">
-        <v>5404</v>
+        <v>5427</v>
       </c>
       <c r="H57" s="25" t="s">
-        <v>5405</v>
+        <v>5428</v>
       </c>
       <c r="I57" s="23" t="s">
-        <v>5406</v>
+        <v>5429</v>
       </c>
       <c r="J57" s="25" t="s">
-        <v>5407</v>
+        <v>5430</v>
       </c>
       <c r="K57" s="23" t="s">
-        <v>5408</v>
+        <v>5431</v>
       </c>
       <c r="L57" s="25" t="s">
-        <v>5409</v>
+        <v>5432</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10"/>
@@ -54841,37 +55281,37 @@
     <row r="58" ht="18.75" customHeight="1">
       <c r="A58" s="26"/>
       <c r="B58" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>5400</v>
+        <v>5423</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>5410</v>
+        <v>5433</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>5402</v>
+        <v>5425</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>5411</v>
+        <v>5434</v>
       </c>
       <c r="G58" s="23" t="s">
-        <v>5404</v>
+        <v>5427</v>
       </c>
       <c r="H58" s="25" t="s">
-        <v>5412</v>
+        <v>5435</v>
       </c>
       <c r="I58" s="23" t="s">
-        <v>5406</v>
+        <v>5429</v>
       </c>
       <c r="J58" s="25" t="s">
-        <v>5413</v>
+        <v>5436</v>
       </c>
       <c r="K58" s="23" t="s">
-        <v>5408</v>
+        <v>5431</v>
       </c>
       <c r="L58" s="25" t="s">
-        <v>5414</v>
+        <v>5437</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10"/>
@@ -54889,34 +55329,34 @@
         <v>4293</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>5415</v>
+        <v>5438</v>
       </c>
       <c r="D59" s="25" t="s">
         <v>3717</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>5416</v>
+        <v>5439</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>5417</v>
+        <v>5440</v>
       </c>
       <c r="G59" s="23" t="s">
-        <v>5418</v>
+        <v>5441</v>
       </c>
       <c r="H59" s="25" t="s">
-        <v>5419</v>
+        <v>5442</v>
       </c>
       <c r="I59" s="23" t="s">
-        <v>5420</v>
+        <v>5443</v>
       </c>
       <c r="J59" s="25" t="s">
-        <v>5421</v>
+        <v>5444</v>
       </c>
       <c r="K59" s="23" t="s">
-        <v>5422</v>
+        <v>5445</v>
       </c>
       <c r="L59" s="25" t="s">
-        <v>5423</v>
+        <v>5446</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10"/>
@@ -54931,34 +55371,34 @@
         <v>4414</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>5424</v>
+        <v>5447</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>5425</v>
+        <v>5448</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>5426</v>
+        <v>5449</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>5427</v>
+        <v>5450</v>
       </c>
       <c r="G60" s="23" t="s">
-        <v>5428</v>
+        <v>5451</v>
       </c>
       <c r="H60" s="25" t="s">
-        <v>5429</v>
+        <v>5452</v>
       </c>
       <c r="I60" s="23" t="s">
-        <v>5430</v>
+        <v>5453</v>
       </c>
       <c r="J60" s="25" t="s">
-        <v>5431</v>
+        <v>5454</v>
       </c>
       <c r="K60" s="23" t="s">
-        <v>5432</v>
+        <v>5455</v>
       </c>
       <c r="L60" s="25" t="s">
-        <v>5433</v>
+        <v>5456</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10"/>
@@ -54970,37 +55410,37 @@
     </row>
     <row r="61" ht="18.75" customHeight="1">
       <c r="B61" s="24" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>5434</v>
+        <v>5457</v>
       </c>
       <c r="D61" s="25" t="s">
-        <v>5435</v>
+        <v>5458</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>5436</v>
+        <v>5459</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>5437</v>
+        <v>5460</v>
       </c>
       <c r="G61" s="23" t="s">
-        <v>5438</v>
+        <v>5461</v>
       </c>
       <c r="H61" s="25" t="s">
-        <v>5439</v>
+        <v>5462</v>
       </c>
       <c r="I61" s="23" t="s">
-        <v>5440</v>
+        <v>5463</v>
       </c>
       <c r="J61" s="25" t="s">
-        <v>5441</v>
+        <v>5464</v>
       </c>
       <c r="K61" s="23" t="s">
-        <v>5442</v>
+        <v>5465</v>
       </c>
       <c r="L61" s="25" t="s">
-        <v>5443</v>
+        <v>5466</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10"/>
@@ -55012,22 +55452,22 @@
     </row>
     <row r="62" ht="18.75" customHeight="1">
       <c r="A62" s="21" t="s">
-        <v>5221</v>
+        <v>5244</v>
       </c>
       <c r="B62" s="22"/>
       <c r="C62" s="37"/>
       <c r="D62" s="35"/>
       <c r="E62" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="I62" s="30"/>
       <c r="J62" s="38"/>
@@ -55046,21 +55486,21 @@
         <v>4925</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C63" s="39"/>
       <c r="D63" s="25"/>
       <c r="E63" s="23" t="s">
-        <v>5444</v>
+        <v>5467</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>5445</v>
+        <v>5468</v>
       </c>
       <c r="G63" s="23" t="s">
-        <v>5446</v>
+        <v>5469</v>
       </c>
       <c r="H63" s="25" t="s">
-        <v>5447</v>
+        <v>5470</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="40"/>
@@ -55100,7 +55540,7 @@
     <row r="65" ht="18.75" customHeight="1">
       <c r="A65" s="26"/>
       <c r="B65" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C65" s="39"/>
       <c r="D65" s="25"/>
@@ -55130,16 +55570,16 @@
       <c r="C66" s="39"/>
       <c r="D66" s="25"/>
       <c r="E66" s="10" t="s">
-        <v>5448</v>
+        <v>5471</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>5449</v>
+        <v>5472</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>5450</v>
+        <v>5473</v>
       </c>
       <c r="H66" s="25" t="s">
-        <v>5451</v>
+        <v>5474</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="40"/>
@@ -55161,16 +55601,16 @@
       <c r="C67" s="39"/>
       <c r="D67" s="25"/>
       <c r="E67" s="10" t="s">
-        <v>5452</v>
+        <v>5475</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>5453</v>
+        <v>5476</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>5454</v>
+        <v>5477</v>
       </c>
       <c r="H67" s="25" t="s">
-        <v>5455</v>
+        <v>5478</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="40"/>
@@ -55187,7 +55627,7 @@
     <row r="68" ht="18.75" customHeight="1">
       <c r="A68" s="31"/>
       <c r="B68" s="32" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C68" s="39"/>
       <c r="D68" s="25"/>
@@ -55251,139 +55691,139 @@
     </row>
     <row r="71" ht="18.75" customHeight="1">
       <c r="A71" s="18" t="s">
-        <v>5456</v>
+        <v>5479</v>
       </c>
       <c r="B71" s="19"/>
       <c r="C71" s="20" t="s">
-        <v>5457</v>
+        <v>5480</v>
       </c>
       <c r="D71" s="19"/>
       <c r="E71" s="18" t="s">
-        <v>5458</v>
+        <v>5481</v>
       </c>
       <c r="F71" s="41"/>
       <c r="G71" s="18" t="s">
-        <v>5459</v>
+        <v>5482</v>
       </c>
       <c r="H71" s="41"/>
       <c r="I71" s="18" t="s">
-        <v>5460</v>
+        <v>5483</v>
       </c>
       <c r="J71" s="19"/>
       <c r="K71" s="18" t="s">
-        <v>5461</v>
+        <v>5484</v>
       </c>
       <c r="L71" s="19"/>
     </row>
     <row r="72" ht="18.75" customHeight="1">
       <c r="A72" s="21" t="s">
-        <v>5149</v>
+        <v>5172</v>
       </c>
       <c r="B72" s="22"/>
       <c r="C72" s="10" t="s">
-        <v>5462</v>
+        <v>5485</v>
       </c>
       <c r="D72" s="22"/>
       <c r="E72" s="10" t="s">
-        <v>5463</v>
+        <v>5486</v>
       </c>
       <c r="F72" s="22"/>
       <c r="G72" s="10" t="s">
-        <v>5464</v>
+        <v>5487</v>
       </c>
       <c r="I72" s="23" t="s">
-        <v>5465</v>
+        <v>5488</v>
       </c>
       <c r="J72" s="22"/>
       <c r="K72" s="23" t="s">
-        <v>5466</v>
+        <v>5489</v>
       </c>
       <c r="L72" s="22"/>
     </row>
     <row r="73" ht="18.75" customHeight="1">
       <c r="A73" s="21" t="s">
-        <v>5155</v>
+        <v>5178</v>
       </c>
       <c r="B73" s="22"/>
       <c r="C73" s="10" t="s">
-        <v>5467</v>
+        <v>5490</v>
       </c>
       <c r="D73" s="22"/>
       <c r="E73" s="10" t="s">
-        <v>5468</v>
+        <v>5491</v>
       </c>
       <c r="F73" s="22"/>
       <c r="G73" s="10" t="s">
-        <v>5469</v>
+        <v>5492</v>
       </c>
       <c r="I73" s="23" t="s">
-        <v>5470</v>
+        <v>5493</v>
       </c>
       <c r="J73" s="22"/>
       <c r="K73" s="23" t="s">
-        <v>5471</v>
+        <v>5494</v>
       </c>
       <c r="L73" s="22"/>
     </row>
     <row r="74" ht="18.75" customHeight="1">
       <c r="A74" s="21" t="s">
-        <v>5161</v>
+        <v>5184</v>
       </c>
       <c r="B74" s="22"/>
       <c r="C74" s="10" t="s">
-        <v>5472</v>
+        <v>5495</v>
       </c>
       <c r="D74" s="22"/>
       <c r="E74" s="10" t="s">
-        <v>5473</v>
+        <v>5496</v>
       </c>
       <c r="F74" s="22"/>
       <c r="G74" s="10" t="s">
-        <v>5474</v>
+        <v>5497</v>
       </c>
       <c r="I74" s="23" t="s">
-        <v>5475</v>
+        <v>5498</v>
       </c>
       <c r="J74" s="22"/>
       <c r="K74" s="23" t="s">
-        <v>5476</v>
+        <v>5499</v>
       </c>
       <c r="L74" s="22"/>
     </row>
     <row r="75" ht="18.75" customHeight="1">
       <c r="A75" s="21" t="s">
-        <v>5167</v>
+        <v>5190</v>
       </c>
       <c r="B75" s="22"/>
       <c r="C75" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D75" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="F75" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="I75" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="J75" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="K75" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="L75" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
     </row>
     <row r="76" ht="18.75" customHeight="1">
@@ -55391,37 +55831,37 @@
         <v>4925</v>
       </c>
       <c r="B76" s="24" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>5477</v>
+        <v>5500</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>5478</v>
+        <v>5501</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>5479</v>
+        <v>5502</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>5480</v>
+        <v>5503</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>5481</v>
+        <v>5504</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>5482</v>
+        <v>5505</v>
       </c>
       <c r="I76" s="23" t="s">
-        <v>5483</v>
+        <v>5506</v>
       </c>
       <c r="J76" s="25" t="s">
-        <v>5484</v>
+        <v>5507</v>
       </c>
       <c r="K76" s="23" t="s">
-        <v>5485</v>
+        <v>5508</v>
       </c>
       <c r="L76" s="25" t="s">
-        <v>5486</v>
+        <v>5509</v>
       </c>
     </row>
     <row r="77" ht="18.75" customHeight="1">
@@ -55430,70 +55870,70 @@
         <v>4464</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>5487</v>
+        <v>5510</v>
       </c>
       <c r="D77" s="25" t="s">
-        <v>5488</v>
+        <v>5511</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>5489</v>
+        <v>5512</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>5490</v>
+        <v>5513</v>
       </c>
       <c r="G77" s="10" t="s">
         <v>4942</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>5491</v>
+        <v>5514</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>5492</v>
+        <v>5515</v>
       </c>
       <c r="J77" s="25" t="s">
-        <v>5493</v>
+        <v>5516</v>
       </c>
       <c r="K77" s="23" t="s">
-        <v>5494</v>
+        <v>5517</v>
       </c>
       <c r="L77" s="25" t="s">
-        <v>5495</v>
+        <v>5518</v>
       </c>
     </row>
     <row r="78" ht="18.75" customHeight="1">
       <c r="A78" s="26"/>
       <c r="B78" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>5477</v>
+        <v>5500</v>
       </c>
       <c r="D78" s="25" t="s">
-        <v>5478</v>
+        <v>5501</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>5479</v>
+        <v>5502</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>5480</v>
+        <v>5503</v>
       </c>
       <c r="G78" s="10" t="s">
         <v>4942</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>5482</v>
+        <v>5505</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>5492</v>
+        <v>5515</v>
       </c>
       <c r="J78" s="25" t="s">
-        <v>5484</v>
+        <v>5507</v>
       </c>
       <c r="K78" s="23" t="s">
-        <v>5494</v>
+        <v>5517</v>
       </c>
       <c r="L78" s="25" t="s">
-        <v>5496</v>
+        <v>5519</v>
       </c>
     </row>
     <row r="79" ht="18.75" customHeight="1">
@@ -55504,34 +55944,34 @@
         <v>4293</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>5497</v>
+        <v>5520</v>
       </c>
       <c r="D79" s="25" t="s">
-        <v>5498</v>
+        <v>5521</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>5499</v>
+        <v>5522</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>5500</v>
+        <v>5523</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>5501</v>
+        <v>5524</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>5502</v>
+        <v>5525</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>5503</v>
+        <v>5526</v>
       </c>
       <c r="J79" s="25" t="s">
-        <v>5504</v>
+        <v>5527</v>
       </c>
       <c r="K79" s="23" t="s">
-        <v>5505</v>
+        <v>5528</v>
       </c>
       <c r="L79" s="25" t="s">
-        <v>5506</v>
+        <v>5529</v>
       </c>
     </row>
     <row r="80" ht="18.75" customHeight="1">
@@ -55540,70 +55980,70 @@
         <v>4414</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>5507</v>
+        <v>5530</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>5508</v>
+        <v>5531</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>5509</v>
+        <v>5532</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>5510</v>
+        <v>5533</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>5511</v>
+        <v>5534</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>5512</v>
+        <v>5535</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>5513</v>
+        <v>5536</v>
       </c>
       <c r="J80" s="25" t="s">
-        <v>5514</v>
+        <v>5537</v>
       </c>
       <c r="K80" s="23" t="s">
-        <v>5515</v>
+        <v>5538</v>
       </c>
       <c r="L80" s="25" t="s">
-        <v>5516</v>
+        <v>5539</v>
       </c>
     </row>
     <row r="81" ht="18.75" customHeight="1">
       <c r="A81" s="31"/>
       <c r="B81" s="32" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C81" s="27" t="s">
-        <v>5517</v>
+        <v>5540</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>5518</v>
+        <v>5541</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>5519</v>
+        <v>5542</v>
       </c>
       <c r="F81" s="28" t="s">
-        <v>5520</v>
+        <v>5543</v>
       </c>
       <c r="G81" s="27" t="s">
-        <v>5521</v>
+        <v>5544</v>
       </c>
       <c r="H81" s="27" t="s">
-        <v>5522</v>
+        <v>5545</v>
       </c>
       <c r="I81" s="23" t="s">
-        <v>5523</v>
+        <v>5546</v>
       </c>
       <c r="J81" s="25" t="s">
-        <v>5524</v>
+        <v>5547</v>
       </c>
       <c r="K81" s="23" t="s">
-        <v>5525</v>
+        <v>5548</v>
       </c>
       <c r="L81" s="25" t="s">
-        <v>5526</v>
+        <v>5549</v>
       </c>
     </row>
     <row r="82" ht="18.75" customHeight="1">
@@ -55616,16 +56056,16 @@
       <c r="G82" s="10"/>
       <c r="H82" s="10"/>
       <c r="I82" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="J82" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="K82" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="L82" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10"/>
@@ -55645,16 +56085,16 @@
       <c r="G83" s="10"/>
       <c r="H83" s="10"/>
       <c r="I83" s="23" t="s">
-        <v>5527</v>
+        <v>5550</v>
       </c>
       <c r="J83" s="25" t="s">
-        <v>5528</v>
+        <v>5551</v>
       </c>
       <c r="K83" s="23" t="s">
-        <v>5529</v>
+        <v>5552</v>
       </c>
       <c r="L83" s="25" t="s">
-        <v>5530</v>
+        <v>5553</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10"/>
@@ -55716,16 +56156,16 @@
       <c r="G86" s="10"/>
       <c r="H86" s="10"/>
       <c r="I86" s="23" t="s">
-        <v>5531</v>
+        <v>5554</v>
       </c>
       <c r="J86" s="25" t="s">
-        <v>5532</v>
+        <v>5555</v>
       </c>
       <c r="K86" s="23" t="s">
-        <v>5533</v>
+        <v>5556</v>
       </c>
       <c r="L86" s="25" t="s">
-        <v>5534</v>
+        <v>5557</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10"/>
@@ -55745,16 +56185,16 @@
       <c r="G87" s="10"/>
       <c r="H87" s="10"/>
       <c r="I87" s="23" t="s">
-        <v>5535</v>
+        <v>5558</v>
       </c>
       <c r="J87" s="25" t="s">
-        <v>5536</v>
+        <v>5559</v>
       </c>
       <c r="K87" s="23" t="s">
-        <v>5537</v>
+        <v>5560</v>
       </c>
       <c r="L87" s="25" t="s">
-        <v>5538</v>
+        <v>5561</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10"/>
@@ -55808,27 +56248,27 @@
     </row>
     <row r="90" ht="18.75" customHeight="1">
       <c r="A90" s="18" t="s">
-        <v>5539</v>
+        <v>5562</v>
       </c>
       <c r="B90" s="19"/>
       <c r="C90" s="18" t="s">
-        <v>5540</v>
+        <v>5563</v>
       </c>
       <c r="D90" s="19"/>
       <c r="E90" s="18" t="s">
-        <v>5541</v>
+        <v>5564</v>
       </c>
       <c r="F90" s="19"/>
       <c r="G90" s="18" t="s">
-        <v>5542</v>
+        <v>5565</v>
       </c>
       <c r="H90" s="19"/>
       <c r="I90" s="18" t="s">
-        <v>5543</v>
+        <v>5566</v>
       </c>
       <c r="J90" s="19"/>
       <c r="K90" s="18" t="s">
-        <v>5544</v>
+        <v>5567</v>
       </c>
       <c r="L90" s="19"/>
       <c r="M90" s="10"/>
@@ -55841,27 +56281,27 @@
     </row>
     <row r="91" ht="18.75" customHeight="1">
       <c r="A91" s="23" t="s">
-        <v>5545</v>
+        <v>5568</v>
       </c>
       <c r="B91" s="22"/>
       <c r="C91" s="23" t="s">
-        <v>5546</v>
+        <v>5569</v>
       </c>
       <c r="D91" s="22"/>
       <c r="E91" s="23" t="s">
-        <v>5547</v>
+        <v>5570</v>
       </c>
       <c r="F91" s="22"/>
       <c r="G91" s="23" t="s">
-        <v>5548</v>
+        <v>5571</v>
       </c>
       <c r="H91" s="22"/>
       <c r="I91" s="23" t="s">
-        <v>5549</v>
+        <v>5572</v>
       </c>
       <c r="J91" s="22"/>
       <c r="K91" s="23" t="s">
-        <v>5550</v>
+        <v>5573</v>
       </c>
       <c r="L91" s="22"/>
       <c r="M91" s="10"/>
@@ -55874,27 +56314,27 @@
     </row>
     <row r="92" ht="18.75" customHeight="1">
       <c r="A92" s="23" t="s">
-        <v>5551</v>
+        <v>5574</v>
       </c>
       <c r="B92" s="22"/>
       <c r="C92" s="23" t="s">
-        <v>5552</v>
+        <v>5575</v>
       </c>
       <c r="D92" s="22"/>
       <c r="E92" s="23" t="s">
-        <v>5553</v>
+        <v>5576</v>
       </c>
       <c r="F92" s="22"/>
       <c r="G92" s="23" t="s">
-        <v>5554</v>
+        <v>5577</v>
       </c>
       <c r="H92" s="22"/>
       <c r="I92" s="23" t="s">
-        <v>5555</v>
+        <v>5578</v>
       </c>
       <c r="J92" s="22"/>
       <c r="K92" s="23" t="s">
-        <v>5556</v>
+        <v>5579</v>
       </c>
       <c r="L92" s="22"/>
       <c r="M92" s="10"/>
@@ -55907,27 +56347,27 @@
     </row>
     <row r="93" ht="18.75" customHeight="1">
       <c r="A93" s="23" t="s">
-        <v>5557</v>
+        <v>5580</v>
       </c>
       <c r="B93" s="22"/>
       <c r="C93" s="23" t="s">
-        <v>5558</v>
+        <v>5581</v>
       </c>
       <c r="D93" s="22"/>
       <c r="E93" s="23" t="s">
-        <v>5559</v>
+        <v>5582</v>
       </c>
       <c r="F93" s="22"/>
       <c r="G93" s="23" t="s">
-        <v>5560</v>
+        <v>5583</v>
       </c>
       <c r="H93" s="22"/>
       <c r="I93" s="23" t="s">
-        <v>5561</v>
+        <v>5584</v>
       </c>
       <c r="J93" s="22"/>
       <c r="K93" s="23" t="s">
-        <v>5562</v>
+        <v>5585</v>
       </c>
       <c r="L93" s="22"/>
       <c r="M93" s="10"/>
@@ -55940,40 +56380,40 @@
     </row>
     <row r="94" ht="18.75" customHeight="1">
       <c r="A94" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="B94" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D94" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E94" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="F94" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="G94" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="I94" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="J94" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="K94" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="L94" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="M94" s="10"/>
       <c r="N94" s="10"/>
@@ -55985,40 +56425,40 @@
     </row>
     <row r="95" ht="18.75" customHeight="1">
       <c r="A95" s="23" t="s">
-        <v>5563</v>
+        <v>5586</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>5564</v>
+        <v>5587</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>5565</v>
+        <v>5588</v>
       </c>
       <c r="D95" s="25" t="s">
-        <v>5566</v>
+        <v>5589</v>
       </c>
       <c r="E95" s="23" t="s">
-        <v>5567</v>
+        <v>5590</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>5568</v>
+        <v>5591</v>
       </c>
       <c r="G95" s="23" t="s">
-        <v>5569</v>
+        <v>5592</v>
       </c>
       <c r="H95" s="25" t="s">
-        <v>5570</v>
+        <v>5593</v>
       </c>
       <c r="I95" s="23" t="s">
-        <v>5571</v>
+        <v>5594</v>
       </c>
       <c r="J95" s="25" t="s">
-        <v>5572</v>
+        <v>5595</v>
       </c>
       <c r="K95" s="23" t="s">
-        <v>5573</v>
+        <v>5596</v>
       </c>
       <c r="L95" s="25" t="s">
-        <v>5574</v>
+        <v>5597</v>
       </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10"/>
@@ -56030,40 +56470,40 @@
     </row>
     <row r="96" ht="18.75" customHeight="1">
       <c r="A96" s="23" t="s">
-        <v>5575</v>
+        <v>5598</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>5576</v>
+        <v>5599</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>5577</v>
+        <v>5600</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>5578</v>
+        <v>5601</v>
       </c>
       <c r="E96" s="23" t="s">
-        <v>5579</v>
+        <v>5602</v>
       </c>
       <c r="F96" s="25" t="s">
-        <v>5580</v>
+        <v>5603</v>
       </c>
       <c r="G96" s="23" t="s">
-        <v>5581</v>
+        <v>5604</v>
       </c>
       <c r="H96" s="25" t="s">
-        <v>5582</v>
+        <v>5605</v>
       </c>
       <c r="I96" s="23" t="s">
         <v>2224</v>
       </c>
       <c r="J96" s="25" t="s">
-        <v>5583</v>
+        <v>5606</v>
       </c>
       <c r="K96" s="23" t="s">
-        <v>5584</v>
+        <v>5607</v>
       </c>
       <c r="L96" s="25" t="s">
-        <v>5585</v>
+        <v>5608</v>
       </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10"/>
@@ -56075,40 +56515,40 @@
     </row>
     <row r="97" ht="18.75" customHeight="1">
       <c r="A97" s="23" t="s">
-        <v>5575</v>
+        <v>5598</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>5586</v>
+        <v>5609</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>5577</v>
+        <v>5600</v>
       </c>
       <c r="D97" s="25" t="s">
-        <v>5587</v>
+        <v>5610</v>
       </c>
       <c r="E97" s="23" t="s">
-        <v>5579</v>
+        <v>5602</v>
       </c>
       <c r="F97" s="25" t="s">
-        <v>5568</v>
+        <v>5591</v>
       </c>
       <c r="G97" s="23" t="s">
-        <v>5569</v>
+        <v>5592</v>
       </c>
       <c r="H97" s="25" t="s">
-        <v>5588</v>
+        <v>5611</v>
       </c>
       <c r="I97" s="23" t="s">
         <v>2224</v>
       </c>
       <c r="J97" s="25" t="s">
-        <v>5589</v>
+        <v>5612</v>
       </c>
       <c r="K97" s="23" t="s">
-        <v>5584</v>
+        <v>5607</v>
       </c>
       <c r="L97" s="25" t="s">
-        <v>5574</v>
+        <v>5597</v>
       </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10"/>
@@ -56120,40 +56560,40 @@
     </row>
     <row r="98" ht="18.75" customHeight="1">
       <c r="A98" s="23" t="s">
-        <v>5590</v>
+        <v>5613</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>5591</v>
+        <v>5614</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>5592</v>
+        <v>5615</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>5593</v>
+        <v>5616</v>
       </c>
       <c r="E98" s="23" t="s">
-        <v>5594</v>
+        <v>5617</v>
       </c>
       <c r="F98" s="25" t="s">
-        <v>5595</v>
+        <v>5618</v>
       </c>
       <c r="G98" s="23" t="s">
-        <v>5596</v>
+        <v>5619</v>
       </c>
       <c r="H98" s="25" t="s">
-        <v>5597</v>
+        <v>5620</v>
       </c>
       <c r="I98" s="23" t="s">
-        <v>5598</v>
+        <v>5621</v>
       </c>
       <c r="J98" s="25" t="s">
-        <v>5599</v>
+        <v>5622</v>
       </c>
       <c r="K98" s="23" t="s">
-        <v>5600</v>
+        <v>5623</v>
       </c>
       <c r="L98" s="25" t="s">
-        <v>5601</v>
+        <v>5624</v>
       </c>
       <c r="M98" s="10"/>
       <c r="N98" s="10"/>
@@ -56165,40 +56605,40 @@
     </row>
     <row r="99" ht="18.75" customHeight="1">
       <c r="A99" s="23" t="s">
-        <v>5602</v>
+        <v>5625</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>5603</v>
+        <v>5626</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>5604</v>
+        <v>5627</v>
       </c>
       <c r="D99" s="25" t="s">
-        <v>5605</v>
+        <v>5628</v>
       </c>
       <c r="E99" s="23" t="s">
-        <v>5606</v>
+        <v>5629</v>
       </c>
       <c r="F99" s="25" t="s">
-        <v>5607</v>
+        <v>5630</v>
       </c>
       <c r="G99" s="23" t="s">
-        <v>5608</v>
+        <v>5631</v>
       </c>
       <c r="H99" s="25" t="s">
-        <v>5609</v>
+        <v>5632</v>
       </c>
       <c r="I99" s="23" t="s">
-        <v>5610</v>
+        <v>5633</v>
       </c>
       <c r="J99" s="25" t="s">
-        <v>5611</v>
+        <v>5634</v>
       </c>
       <c r="K99" s="23" t="s">
-        <v>5612</v>
+        <v>5635</v>
       </c>
       <c r="L99" s="25" t="s">
-        <v>5613</v>
+        <v>5636</v>
       </c>
       <c r="M99" s="10"/>
       <c r="N99" s="10"/>
@@ -56210,40 +56650,40 @@
     </row>
     <row r="100" ht="18.75" customHeight="1">
       <c r="A100" s="36" t="s">
-        <v>5614</v>
+        <v>5637</v>
       </c>
       <c r="B100" s="28" t="s">
-        <v>5615</v>
+        <v>5638</v>
       </c>
       <c r="C100" s="36" t="s">
-        <v>5616</v>
+        <v>5639</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>5617</v>
+        <v>5640</v>
       </c>
       <c r="E100" s="23" t="s">
-        <v>5618</v>
+        <v>5641</v>
       </c>
       <c r="F100" s="25" t="s">
-        <v>5619</v>
+        <v>5642</v>
       </c>
       <c r="G100" s="36" t="s">
-        <v>5620</v>
+        <v>5643</v>
       </c>
       <c r="H100" s="28" t="s">
-        <v>5621</v>
+        <v>5644</v>
       </c>
       <c r="I100" s="36" t="s">
-        <v>5622</v>
+        <v>5645</v>
       </c>
       <c r="J100" s="28" t="s">
-        <v>5623</v>
+        <v>5646</v>
       </c>
       <c r="K100" s="36" t="s">
-        <v>5624</v>
+        <v>5647</v>
       </c>
       <c r="L100" s="28" t="s">
-        <v>5625</v>
+        <v>5648</v>
       </c>
       <c r="M100" s="10"/>
       <c r="N100" s="10"/>
@@ -56257,10 +56697,10 @@
       <c r="A101" s="10"/>
       <c r="B101" s="10"/>
       <c r="E101" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="F101" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="G101" s="10"/>
       <c r="H101" s="10"/>
@@ -56280,10 +56720,10 @@
       <c r="A102" s="10"/>
       <c r="B102" s="10"/>
       <c r="E102" s="23" t="s">
-        <v>5626</v>
+        <v>5649</v>
       </c>
       <c r="F102" s="25" t="s">
-        <v>5627</v>
+        <v>5650</v>
       </c>
       <c r="G102" s="10"/>
       <c r="H102" s="10"/>
@@ -56341,10 +56781,10 @@
       <c r="A105" s="10"/>
       <c r="B105" s="10"/>
       <c r="E105" s="23" t="s">
-        <v>5628</v>
+        <v>5651</v>
       </c>
       <c r="F105" s="25" t="s">
-        <v>5629</v>
+        <v>5652</v>
       </c>
       <c r="G105" s="10"/>
       <c r="H105" s="10"/>
@@ -56364,10 +56804,10 @@
       <c r="A106" s="10"/>
       <c r="B106" s="10"/>
       <c r="E106" s="23" t="s">
-        <v>5630</v>
+        <v>5653</v>
       </c>
       <c r="F106" s="25" t="s">
-        <v>5631</v>
+        <v>5654</v>
       </c>
       <c r="G106" s="10"/>
       <c r="H106" s="10"/>
@@ -56425,27 +56865,27 @@
     </row>
     <row r="109" ht="18.75" customHeight="1">
       <c r="A109" s="18" t="s">
-        <v>5632</v>
+        <v>5655</v>
       </c>
       <c r="B109" s="19"/>
       <c r="C109" s="18" t="s">
-        <v>5633</v>
+        <v>5656</v>
       </c>
       <c r="D109" s="19"/>
       <c r="E109" s="18" t="s">
-        <v>5634</v>
+        <v>5657</v>
       </c>
       <c r="F109" s="19"/>
       <c r="G109" s="18" t="s">
-        <v>5635</v>
+        <v>5658</v>
       </c>
       <c r="H109" s="19"/>
       <c r="I109" s="18" t="s">
-        <v>5636</v>
+        <v>5659</v>
       </c>
       <c r="J109" s="19"/>
       <c r="K109" s="18" t="s">
-        <v>5637</v>
+        <v>5660</v>
       </c>
       <c r="L109" s="19"/>
       <c r="M109" s="10"/>
@@ -56458,27 +56898,27 @@
     </row>
     <row r="110" ht="18.75" customHeight="1">
       <c r="A110" s="23" t="s">
-        <v>5638</v>
+        <v>5661</v>
       </c>
       <c r="B110" s="22"/>
       <c r="C110" s="23" t="s">
-        <v>5639</v>
+        <v>5662</v>
       </c>
       <c r="D110" s="22"/>
       <c r="E110" s="23" t="s">
-        <v>5640</v>
+        <v>5663</v>
       </c>
       <c r="F110" s="22"/>
       <c r="G110" s="23" t="s">
-        <v>5641</v>
+        <v>5664</v>
       </c>
       <c r="H110" s="22"/>
       <c r="I110" s="23" t="s">
-        <v>5642</v>
+        <v>5665</v>
       </c>
       <c r="J110" s="22"/>
       <c r="K110" s="23" t="s">
-        <v>5643</v>
+        <v>5666</v>
       </c>
       <c r="L110" s="22"/>
       <c r="M110" s="10"/>
@@ -56491,27 +56931,27 @@
     </row>
     <row r="111" ht="18.75" customHeight="1">
       <c r="A111" s="23" t="s">
-        <v>5644</v>
+        <v>5667</v>
       </c>
       <c r="B111" s="22"/>
       <c r="C111" s="23" t="s">
-        <v>5645</v>
+        <v>5668</v>
       </c>
       <c r="D111" s="22"/>
       <c r="E111" s="23" t="s">
-        <v>5646</v>
+        <v>5669</v>
       </c>
       <c r="F111" s="22"/>
       <c r="G111" s="23" t="s">
-        <v>5647</v>
+        <v>5670</v>
       </c>
       <c r="H111" s="22"/>
       <c r="I111" s="23" t="s">
-        <v>5648</v>
+        <v>5671</v>
       </c>
       <c r="J111" s="22"/>
       <c r="K111" s="23" t="s">
-        <v>5649</v>
+        <v>5672</v>
       </c>
       <c r="L111" s="22"/>
       <c r="M111" s="10"/>
@@ -56524,27 +56964,27 @@
     </row>
     <row r="112" ht="18.75" customHeight="1">
       <c r="A112" s="23" t="s">
-        <v>5650</v>
+        <v>5673</v>
       </c>
       <c r="B112" s="22"/>
       <c r="C112" s="23" t="s">
-        <v>5651</v>
+        <v>5674</v>
       </c>
       <c r="D112" s="22"/>
       <c r="E112" s="23" t="s">
-        <v>5652</v>
+        <v>5675</v>
       </c>
       <c r="F112" s="22"/>
       <c r="G112" s="23" t="s">
-        <v>5653</v>
+        <v>5676</v>
       </c>
       <c r="H112" s="22"/>
       <c r="I112" s="23" t="s">
-        <v>5654</v>
+        <v>5677</v>
       </c>
       <c r="J112" s="22"/>
       <c r="K112" s="23" t="s">
-        <v>5655</v>
+        <v>5678</v>
       </c>
       <c r="L112" s="22"/>
       <c r="M112" s="10"/>
@@ -56557,40 +56997,40 @@
     </row>
     <row r="113" ht="18.75" customHeight="1">
       <c r="A113" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="B113" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="C113" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D113" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E113" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="F113" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="G113" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="H113" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="I113" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="J113" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="K113" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="L113" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="M113" s="10"/>
       <c r="N113" s="10"/>
@@ -56602,40 +57042,40 @@
     </row>
     <row r="114" ht="18.75" customHeight="1">
       <c r="A114" s="23" t="s">
-        <v>5656</v>
+        <v>5679</v>
       </c>
       <c r="B114" s="25" t="s">
         <v>4853</v>
       </c>
       <c r="C114" s="23" t="s">
-        <v>5657</v>
+        <v>5680</v>
       </c>
       <c r="D114" s="25" t="s">
-        <v>5658</v>
+        <v>5681</v>
       </c>
       <c r="E114" s="23" t="s">
-        <v>5659</v>
+        <v>5682</v>
       </c>
       <c r="F114" s="25" t="s">
-        <v>5660</v>
+        <v>5683</v>
       </c>
       <c r="G114" s="23" t="s">
-        <v>5661</v>
+        <v>5684</v>
       </c>
       <c r="H114" s="25" t="s">
-        <v>5662</v>
+        <v>5685</v>
       </c>
       <c r="I114" s="23" t="s">
         <v>800</v>
       </c>
       <c r="J114" s="25" t="s">
-        <v>5663</v>
+        <v>5686</v>
       </c>
       <c r="K114" s="23" t="s">
-        <v>5664</v>
+        <v>5687</v>
       </c>
       <c r="L114" s="25" t="s">
-        <v>5665</v>
+        <v>5688</v>
       </c>
       <c r="M114" s="10"/>
       <c r="N114" s="10"/>
@@ -56647,40 +57087,40 @@
     </row>
     <row r="115" ht="18.75" customHeight="1">
       <c r="A115" s="23" t="s">
-        <v>5666</v>
+        <v>5689</v>
       </c>
       <c r="B115" s="25" t="s">
-        <v>5667</v>
+        <v>5690</v>
       </c>
       <c r="C115" s="23" t="s">
-        <v>5668</v>
+        <v>5691</v>
       </c>
       <c r="D115" s="25" t="s">
-        <v>5669</v>
+        <v>5692</v>
       </c>
       <c r="E115" s="23" t="s">
-        <v>5670</v>
+        <v>5693</v>
       </c>
       <c r="F115" s="25" t="s">
-        <v>5671</v>
+        <v>5694</v>
       </c>
       <c r="G115" s="23" t="s">
-        <v>5672</v>
+        <v>5695</v>
       </c>
       <c r="H115" s="25" t="s">
-        <v>5673</v>
+        <v>5696</v>
       </c>
       <c r="I115" s="23" t="s">
-        <v>5674</v>
+        <v>5697</v>
       </c>
       <c r="J115" s="25" t="s">
-        <v>5675</v>
+        <v>5698</v>
       </c>
       <c r="K115" s="23" t="s">
-        <v>5676</v>
+        <v>5699</v>
       </c>
       <c r="L115" s="25" t="s">
-        <v>5677</v>
+        <v>5700</v>
       </c>
       <c r="M115" s="10"/>
       <c r="N115" s="10"/>
@@ -56692,40 +57132,40 @@
     </row>
     <row r="116" ht="18.75" customHeight="1">
       <c r="A116" s="23" t="s">
-        <v>5666</v>
+        <v>5689</v>
       </c>
       <c r="B116" s="25" t="s">
         <v>4853</v>
       </c>
       <c r="C116" s="23" t="s">
-        <v>5668</v>
+        <v>5691</v>
       </c>
       <c r="D116" s="25" t="s">
-        <v>5658</v>
+        <v>5681</v>
       </c>
       <c r="E116" s="23" t="s">
-        <v>5670</v>
+        <v>5693</v>
       </c>
       <c r="F116" s="25" t="s">
-        <v>5660</v>
+        <v>5683</v>
       </c>
       <c r="G116" s="23" t="s">
-        <v>5672</v>
+        <v>5695</v>
       </c>
       <c r="H116" s="25" t="s">
-        <v>5678</v>
+        <v>5701</v>
       </c>
       <c r="I116" s="23" t="s">
-        <v>5674</v>
+        <v>5697</v>
       </c>
       <c r="J116" s="25" t="s">
-        <v>5679</v>
+        <v>5702</v>
       </c>
       <c r="K116" s="23" t="s">
-        <v>5676</v>
+        <v>5699</v>
       </c>
       <c r="L116" s="25" t="s">
-        <v>5665</v>
+        <v>5688</v>
       </c>
       <c r="M116" s="10"/>
       <c r="N116" s="10"/>
@@ -56737,40 +57177,40 @@
     </row>
     <row r="117" ht="18.75" customHeight="1">
       <c r="A117" s="23" t="s">
-        <v>5680</v>
+        <v>5703</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>5681</v>
+        <v>5704</v>
       </c>
       <c r="C117" s="23" t="s">
-        <v>5682</v>
+        <v>5705</v>
       </c>
       <c r="D117" s="25" t="s">
-        <v>5683</v>
+        <v>5706</v>
       </c>
       <c r="E117" s="23" t="s">
-        <v>5684</v>
+        <v>5707</v>
       </c>
       <c r="F117" s="25" t="s">
-        <v>5685</v>
+        <v>5708</v>
       </c>
       <c r="G117" s="23" t="s">
-        <v>5686</v>
+        <v>5709</v>
       </c>
       <c r="H117" s="25" t="s">
-        <v>5687</v>
+        <v>5710</v>
       </c>
       <c r="I117" s="23" t="s">
-        <v>5688</v>
+        <v>5711</v>
       </c>
       <c r="J117" s="25" t="s">
-        <v>5689</v>
+        <v>5712</v>
       </c>
       <c r="K117" s="23" t="s">
-        <v>5690</v>
+        <v>5713</v>
       </c>
       <c r="L117" s="25" t="s">
-        <v>5691</v>
+        <v>5714</v>
       </c>
       <c r="M117" s="10"/>
       <c r="N117" s="10"/>
@@ -56782,40 +57222,40 @@
     </row>
     <row r="118" ht="18.75" customHeight="1">
       <c r="A118" s="23" t="s">
-        <v>5692</v>
+        <v>5715</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>5693</v>
+        <v>5716</v>
       </c>
       <c r="C118" s="23" t="s">
-        <v>5694</v>
+        <v>5717</v>
       </c>
       <c r="D118" s="25" t="s">
-        <v>5695</v>
+        <v>5718</v>
       </c>
       <c r="E118" s="23" t="s">
-        <v>5696</v>
+        <v>5719</v>
       </c>
       <c r="F118" s="25" t="s">
-        <v>5697</v>
+        <v>5720</v>
       </c>
       <c r="G118" s="23" t="s">
-        <v>5698</v>
+        <v>5721</v>
       </c>
       <c r="H118" s="25" t="s">
-        <v>5699</v>
+        <v>5722</v>
       </c>
       <c r="I118" s="23" t="s">
-        <v>5700</v>
+        <v>5723</v>
       </c>
       <c r="J118" s="25" t="s">
-        <v>5701</v>
+        <v>5724</v>
       </c>
       <c r="K118" s="23" t="s">
-        <v>5702</v>
+        <v>5725</v>
       </c>
       <c r="L118" s="25" t="s">
-        <v>5703</v>
+        <v>5726</v>
       </c>
       <c r="M118" s="10"/>
       <c r="N118" s="10"/>
@@ -56827,40 +57267,40 @@
     </row>
     <row r="119" ht="18.75" customHeight="1">
       <c r="A119" s="36" t="s">
-        <v>5704</v>
+        <v>5727</v>
       </c>
       <c r="B119" s="28" t="s">
-        <v>5705</v>
+        <v>5728</v>
       </c>
       <c r="C119" s="36" t="s">
-        <v>5706</v>
+        <v>5729</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>5707</v>
+        <v>5730</v>
       </c>
       <c r="E119" s="36" t="s">
-        <v>5708</v>
+        <v>5731</v>
       </c>
       <c r="F119" s="28" t="s">
-        <v>5709</v>
+        <v>5732</v>
       </c>
       <c r="G119" s="36" t="s">
-        <v>5710</v>
+        <v>5733</v>
       </c>
       <c r="H119" s="28" t="s">
-        <v>5711</v>
+        <v>5734</v>
       </c>
       <c r="I119" s="36" t="s">
-        <v>5712</v>
+        <v>5735</v>
       </c>
       <c r="J119" s="28" t="s">
-        <v>5713</v>
+        <v>5736</v>
       </c>
       <c r="K119" s="36" t="s">
-        <v>5714</v>
+        <v>5737</v>
       </c>
       <c r="L119" s="28" t="s">
-        <v>5715</v>
+        <v>5738</v>
       </c>
       <c r="M119" s="10"/>
       <c r="N119" s="10"/>
@@ -56893,7 +57333,7 @@
     </row>
     <row r="121" ht="18.75" customHeight="1">
       <c r="A121" s="18" t="s">
-        <v>5716</v>
+        <v>5739</v>
       </c>
       <c r="B121" s="19"/>
       <c r="C121" s="10"/>
@@ -56916,7 +57356,7 @@
     </row>
     <row r="122" ht="18.75" customHeight="1">
       <c r="A122" s="23" t="s">
-        <v>5717</v>
+        <v>5740</v>
       </c>
       <c r="B122" s="22"/>
       <c r="C122" s="10"/>
@@ -56939,7 +57379,7 @@
     </row>
     <row r="123" ht="18.75" customHeight="1">
       <c r="A123" s="23" t="s">
-        <v>5718</v>
+        <v>5741</v>
       </c>
       <c r="B123" s="22"/>
       <c r="C123" s="10"/>
@@ -56962,7 +57402,7 @@
     </row>
     <row r="124" ht="18.75" customHeight="1">
       <c r="A124" s="23" t="s">
-        <v>5719</v>
+        <v>5742</v>
       </c>
       <c r="B124" s="22"/>
       <c r="C124" s="10"/>
@@ -56985,10 +57425,10 @@
     </row>
     <row r="125" ht="18.75" customHeight="1">
       <c r="A125" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="B125" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="10"/>
@@ -57013,7 +57453,7 @@
         <v>1681</v>
       </c>
       <c r="B126" s="25" t="s">
-        <v>5720</v>
+        <v>5743</v>
       </c>
       <c r="C126" s="10"/>
       <c r="D126" s="10"/>
@@ -57035,10 +57475,10 @@
     </row>
     <row r="127" ht="18.75" customHeight="1">
       <c r="A127" s="23" t="s">
-        <v>5721</v>
+        <v>5744</v>
       </c>
       <c r="B127" s="25" t="s">
-        <v>5722</v>
+        <v>5745</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="10"/>
@@ -57060,10 +57500,10 @@
     </row>
     <row r="128" ht="18.75" customHeight="1">
       <c r="A128" s="23" t="s">
-        <v>5721</v>
+        <v>5744</v>
       </c>
       <c r="B128" s="25" t="s">
-        <v>5720</v>
+        <v>5743</v>
       </c>
       <c r="C128" s="10"/>
       <c r="D128" s="10"/>
@@ -57085,10 +57525,10 @@
     </row>
     <row r="129" ht="18.75" customHeight="1">
       <c r="A129" s="23" t="s">
-        <v>5723</v>
+        <v>5746</v>
       </c>
       <c r="B129" s="25" t="s">
-        <v>5724</v>
+        <v>5747</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="10"/>
@@ -57110,10 +57550,10 @@
     </row>
     <row r="130" ht="18.75" customHeight="1">
       <c r="A130" s="23" t="s">
-        <v>5725</v>
+        <v>5748</v>
       </c>
       <c r="B130" s="25" t="s">
-        <v>5726</v>
+        <v>5749</v>
       </c>
       <c r="C130" s="10"/>
       <c r="D130" s="10"/>
@@ -57135,10 +57575,10 @@
     </row>
     <row r="131" ht="18.75" customHeight="1">
       <c r="A131" s="36" t="s">
-        <v>5727</v>
+        <v>5750</v>
       </c>
       <c r="B131" s="28" t="s">
-        <v>5728</v>
+        <v>5751</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="10"/>
@@ -57181,175 +57621,175 @@
     </row>
     <row r="133" ht="18.75" customHeight="1">
       <c r="A133" s="18" t="s">
-        <v>5729</v>
+        <v>5752</v>
       </c>
       <c r="B133" s="19"/>
       <c r="C133" s="18" t="s">
-        <v>5730</v>
+        <v>5753</v>
       </c>
       <c r="D133" s="19"/>
       <c r="E133" s="18" t="s">
-        <v>5731</v>
+        <v>5754</v>
       </c>
       <c r="F133" s="19"/>
       <c r="G133" s="18" t="s">
-        <v>5732</v>
+        <v>5755</v>
       </c>
       <c r="H133" s="19"/>
       <c r="I133" s="18" t="s">
-        <v>5733</v>
+        <v>5756</v>
       </c>
       <c r="J133" s="19"/>
       <c r="K133" s="18" t="s">
-        <v>5734</v>
+        <v>5757</v>
       </c>
       <c r="L133" s="19"/>
       <c r="M133" s="10"/>
       <c r="N133" s="10"/>
       <c r="O133" s="10"/>
       <c r="P133" s="8" t="s">
-        <v>5735</v>
+        <v>5758</v>
       </c>
     </row>
     <row r="134" ht="18.75" customHeight="1">
       <c r="A134" s="21" t="s">
-        <v>5149</v>
+        <v>5172</v>
       </c>
       <c r="B134" s="22"/>
       <c r="C134" s="23" t="s">
-        <v>5736</v>
+        <v>5759</v>
       </c>
       <c r="D134" s="22"/>
       <c r="E134" s="23" t="s">
-        <v>5737</v>
+        <v>5760</v>
       </c>
       <c r="F134" s="22"/>
       <c r="G134" s="23" t="s">
-        <v>5738</v>
+        <v>5761</v>
       </c>
       <c r="H134" s="22"/>
       <c r="I134" s="23" t="s">
-        <v>5739</v>
+        <v>5762</v>
       </c>
       <c r="J134" s="22"/>
       <c r="K134" s="23" t="s">
-        <v>5740</v>
+        <v>5763</v>
       </c>
       <c r="L134" s="22"/>
       <c r="M134" s="10"/>
       <c r="N134" s="10"/>
       <c r="O134" s="10"/>
       <c r="P134" s="8" t="s">
-        <v>5149</v>
+        <v>5172</v>
       </c>
       <c r="Q134" s="10" t="s">
-        <v>5741</v>
+        <v>5764</v>
       </c>
     </row>
     <row r="135" ht="18.75" customHeight="1">
       <c r="A135" s="21" t="s">
-        <v>5155</v>
+        <v>5178</v>
       </c>
       <c r="B135" s="22"/>
       <c r="C135" s="23" t="s">
-        <v>5742</v>
+        <v>5765</v>
       </c>
       <c r="D135" s="22"/>
       <c r="E135" s="23" t="s">
-        <v>5743</v>
+        <v>5766</v>
       </c>
       <c r="F135" s="22"/>
       <c r="G135" s="23" t="s">
-        <v>5744</v>
+        <v>5767</v>
       </c>
       <c r="H135" s="22"/>
       <c r="I135" s="23" t="s">
-        <v>5745</v>
+        <v>5768</v>
       </c>
       <c r="J135" s="22"/>
       <c r="K135" s="23" t="s">
-        <v>5746</v>
+        <v>5769</v>
       </c>
       <c r="L135" s="22"/>
       <c r="M135" s="10"/>
       <c r="N135" s="10"/>
       <c r="O135" s="10"/>
       <c r="P135" s="8" t="s">
-        <v>5155</v>
+        <v>5178</v>
       </c>
       <c r="Q135" s="10" t="s">
-        <v>5747</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="136" ht="18.75" customHeight="1">
       <c r="A136" s="21" t="s">
-        <v>5161</v>
+        <v>5184</v>
       </c>
       <c r="B136" s="22"/>
       <c r="C136" s="23" t="s">
-        <v>5748</v>
+        <v>5771</v>
       </c>
       <c r="D136" s="22"/>
       <c r="E136" s="23" t="s">
-        <v>5749</v>
+        <v>5772</v>
       </c>
       <c r="F136" s="22"/>
       <c r="G136" s="23" t="s">
-        <v>5750</v>
+        <v>5773</v>
       </c>
       <c r="H136" s="22"/>
       <c r="I136" s="23" t="s">
-        <v>5751</v>
+        <v>5774</v>
       </c>
       <c r="J136" s="22"/>
       <c r="K136" s="23" t="s">
-        <v>5752</v>
+        <v>5775</v>
       </c>
       <c r="L136" s="22"/>
       <c r="M136" s="10"/>
       <c r="N136" s="10"/>
       <c r="O136" s="10"/>
       <c r="P136" s="8" t="s">
-        <v>5161</v>
+        <v>5184</v>
       </c>
       <c r="Q136" s="10" t="s">
-        <v>5753</v>
+        <v>5776</v>
       </c>
     </row>
     <row r="137" ht="18.75" customHeight="1">
       <c r="A137" s="21" t="s">
-        <v>5167</v>
+        <v>5190</v>
       </c>
       <c r="B137" s="22"/>
       <c r="C137" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D137" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E137" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="F137" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="G137" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="H137" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="I137" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="J137" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="K137" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="L137" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="M137" s="10"/>
       <c r="N137" s="10"/>
@@ -57357,10 +57797,10 @@
       <c r="P137" s="8"/>
       <c r="Q137" s="8"/>
       <c r="R137" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="S137" s="8" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
     </row>
     <row r="138" ht="18.75" customHeight="1">
@@ -57368,34 +57808,34 @@
         <v>4925</v>
       </c>
       <c r="B138" s="24" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C138" s="23" t="s">
         <v>991</v>
       </c>
       <c r="D138" s="25" t="s">
-        <v>5754</v>
+        <v>5777</v>
       </c>
       <c r="E138" s="23" t="s">
-        <v>5755</v>
+        <v>5778</v>
       </c>
       <c r="F138" s="25" t="s">
-        <v>5756</v>
+        <v>5779</v>
       </c>
       <c r="G138" s="23" t="s">
-        <v>5757</v>
+        <v>5780</v>
       </c>
       <c r="H138" s="25" t="s">
-        <v>5758</v>
+        <v>5781</v>
       </c>
       <c r="I138" s="23" t="s">
-        <v>5759</v>
+        <v>5782</v>
       </c>
       <c r="J138" s="25" t="s">
-        <v>5760</v>
+        <v>5783</v>
       </c>
       <c r="K138" s="23" t="s">
-        <v>5761</v>
+        <v>5784</v>
       </c>
       <c r="L138" s="25" t="s">
         <v>4123</v>
@@ -57407,13 +57847,13 @@
         <v>4925</v>
       </c>
       <c r="Q138" s="8" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="R138" s="10" t="s">
-        <v>5762</v>
+        <v>5785</v>
       </c>
       <c r="S138" s="10" t="s">
-        <v>5763</v>
+        <v>5786</v>
       </c>
     </row>
     <row r="139" ht="18.75" customHeight="1">
@@ -57422,34 +57862,34 @@
         <v>4464</v>
       </c>
       <c r="C139" s="23" t="s">
-        <v>5764</v>
+        <v>5787</v>
       </c>
       <c r="D139" s="25" t="s">
-        <v>5765</v>
+        <v>5788</v>
       </c>
       <c r="E139" s="23" t="s">
-        <v>5766</v>
+        <v>5789</v>
       </c>
       <c r="F139" s="25" t="s">
-        <v>5767</v>
+        <v>5790</v>
       </c>
       <c r="G139" s="23" t="s">
         <v>4191</v>
       </c>
       <c r="H139" s="25" t="s">
-        <v>5768</v>
+        <v>5791</v>
       </c>
       <c r="I139" s="23" t="s">
-        <v>5769</v>
+        <v>5792</v>
       </c>
       <c r="J139" s="25" t="s">
-        <v>5770</v>
+        <v>5793</v>
       </c>
       <c r="K139" s="23" t="s">
-        <v>5771</v>
+        <v>5794</v>
       </c>
       <c r="L139" s="25" t="s">
-        <v>5772</v>
+        <v>5795</v>
       </c>
       <c r="M139" s="10"/>
       <c r="N139" s="10"/>
@@ -57458,43 +57898,43 @@
         <v>4464</v>
       </c>
       <c r="R139" s="10" t="s">
-        <v>5773</v>
+        <v>5796</v>
       </c>
       <c r="S139" s="10" t="s">
-        <v>5774</v>
+        <v>5797</v>
       </c>
     </row>
     <row r="140" ht="18.75" customHeight="1">
       <c r="A140" s="26"/>
       <c r="B140" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C140" s="23" t="s">
-        <v>5764</v>
+        <v>5787</v>
       </c>
       <c r="D140" s="25" t="s">
-        <v>5754</v>
+        <v>5777</v>
       </c>
       <c r="E140" s="23" t="s">
-        <v>5766</v>
+        <v>5789</v>
       </c>
       <c r="F140" s="25" t="s">
-        <v>5756</v>
+        <v>5779</v>
       </c>
       <c r="G140" s="23" t="s">
         <v>4191</v>
       </c>
       <c r="H140" s="25" t="s">
-        <v>5758</v>
+        <v>5781</v>
       </c>
       <c r="I140" s="23" t="s">
-        <v>5769</v>
+        <v>5792</v>
       </c>
       <c r="J140" s="25" t="s">
-        <v>5760</v>
+        <v>5783</v>
       </c>
       <c r="K140" s="23" t="s">
-        <v>5771</v>
+        <v>5794</v>
       </c>
       <c r="L140" s="25" t="s">
         <v>4123</v>
@@ -57503,13 +57943,13 @@
       <c r="N140" s="10"/>
       <c r="O140" s="10"/>
       <c r="Q140" s="8" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="R140" s="10" t="s">
-        <v>5773</v>
+        <v>5796</v>
       </c>
       <c r="S140" s="10" t="s">
-        <v>5763</v>
+        <v>5786</v>
       </c>
     </row>
     <row r="141" ht="18.75" customHeight="1">
@@ -57520,34 +57960,34 @@
         <v>4293</v>
       </c>
       <c r="C141" s="23" t="s">
-        <v>5775</v>
+        <v>5798</v>
       </c>
       <c r="D141" s="25" t="s">
-        <v>5776</v>
+        <v>5799</v>
       </c>
       <c r="E141" s="23" t="s">
-        <v>5777</v>
+        <v>5800</v>
       </c>
       <c r="F141" s="25" t="s">
-        <v>5778</v>
+        <v>5801</v>
       </c>
       <c r="G141" s="23" t="s">
-        <v>5779</v>
+        <v>5802</v>
       </c>
       <c r="H141" s="25" t="s">
-        <v>5780</v>
+        <v>5803</v>
       </c>
       <c r="I141" s="23" t="s">
-        <v>5781</v>
+        <v>5804</v>
       </c>
       <c r="J141" s="25" t="s">
-        <v>5782</v>
+        <v>5805</v>
       </c>
       <c r="K141" s="23" t="s">
-        <v>5783</v>
+        <v>5806</v>
       </c>
       <c r="L141" s="25" t="s">
-        <v>5784</v>
+        <v>5807</v>
       </c>
       <c r="M141" s="10"/>
       <c r="N141" s="10"/>
@@ -57559,10 +57999,10 @@
         <v>4293</v>
       </c>
       <c r="R141" s="10" t="s">
-        <v>5785</v>
+        <v>5808</v>
       </c>
       <c r="S141" s="10" t="s">
-        <v>5786</v>
+        <v>5809</v>
       </c>
     </row>
     <row r="142" ht="18.75" customHeight="1">
@@ -57570,34 +58010,34 @@
         <v>4414</v>
       </c>
       <c r="C142" s="23" t="s">
-        <v>5787</v>
+        <v>5810</v>
       </c>
       <c r="D142" s="25" t="s">
-        <v>5788</v>
+        <v>5811</v>
       </c>
       <c r="E142" s="23" t="s">
-        <v>5789</v>
+        <v>5812</v>
       </c>
       <c r="F142" s="25" t="s">
-        <v>5790</v>
+        <v>5813</v>
       </c>
       <c r="G142" s="23" t="s">
-        <v>5791</v>
+        <v>5814</v>
       </c>
       <c r="H142" s="25" t="s">
-        <v>5792</v>
+        <v>5815</v>
       </c>
       <c r="I142" s="23" t="s">
-        <v>5793</v>
+        <v>5816</v>
       </c>
       <c r="J142" s="25" t="s">
-        <v>5794</v>
+        <v>5817</v>
       </c>
       <c r="K142" s="23" t="s">
-        <v>5795</v>
+        <v>5818</v>
       </c>
       <c r="L142" s="25" t="s">
-        <v>5796</v>
+        <v>5819</v>
       </c>
       <c r="M142" s="10"/>
       <c r="N142" s="10"/>
@@ -57606,87 +58046,87 @@
         <v>4414</v>
       </c>
       <c r="R142" s="10" t="s">
-        <v>5797</v>
+        <v>5820</v>
       </c>
       <c r="S142" s="10" t="s">
-        <v>5798</v>
+        <v>5821</v>
       </c>
     </row>
     <row r="143" ht="18.75" customHeight="1">
       <c r="B143" s="24" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C143" s="23" t="s">
-        <v>5799</v>
+        <v>5822</v>
       </c>
       <c r="D143" s="25" t="s">
-        <v>5800</v>
+        <v>5823</v>
       </c>
       <c r="E143" s="23" t="s">
-        <v>5801</v>
+        <v>5824</v>
       </c>
       <c r="F143" s="25" t="s">
-        <v>5802</v>
+        <v>5825</v>
       </c>
       <c r="G143" s="23" t="s">
-        <v>5803</v>
+        <v>5826</v>
       </c>
       <c r="H143" s="25" t="s">
-        <v>5804</v>
+        <v>5827</v>
       </c>
       <c r="I143" s="23" t="s">
-        <v>5805</v>
+        <v>5828</v>
       </c>
       <c r="J143" s="25" t="s">
-        <v>5806</v>
+        <v>5829</v>
       </c>
       <c r="K143" s="36" t="s">
-        <v>5807</v>
+        <v>5830</v>
       </c>
       <c r="L143" s="28" t="s">
-        <v>5808</v>
+        <v>5831</v>
       </c>
       <c r="M143" s="10"/>
       <c r="N143" s="10"/>
       <c r="O143" s="10"/>
       <c r="Q143" s="8" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="R143" s="10" t="s">
-        <v>5809</v>
+        <v>5832</v>
       </c>
       <c r="S143" s="10" t="s">
-        <v>5810</v>
+        <v>5833</v>
       </c>
     </row>
     <row r="144" ht="18.75" customHeight="1">
       <c r="A144" s="21" t="s">
-        <v>5221</v>
+        <v>5244</v>
       </c>
       <c r="B144" s="22"/>
       <c r="C144" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D144" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="F144" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="H144" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="I144" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="J144" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="K144" s="10"/>
       <c r="L144" s="10"/>
@@ -57703,31 +58143,31 @@
         <v>4925</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C145" s="23" t="s">
-        <v>5811</v>
+        <v>5834</v>
       </c>
       <c r="D145" s="25" t="s">
-        <v>5812</v>
+        <v>5835</v>
       </c>
       <c r="E145" s="23" t="s">
-        <v>5813</v>
+        <v>5836</v>
       </c>
       <c r="F145" s="25" t="s">
-        <v>5814</v>
+        <v>5837</v>
       </c>
       <c r="G145" s="23" t="s">
-        <v>5815</v>
+        <v>5838</v>
       </c>
       <c r="H145" s="25" t="s">
-        <v>5816</v>
+        <v>5839</v>
       </c>
       <c r="I145" s="23" t="s">
-        <v>5817</v>
+        <v>5840</v>
       </c>
       <c r="J145" s="25" t="s">
-        <v>5818</v>
+        <v>5841</v>
       </c>
       <c r="K145" s="23"/>
       <c r="L145" s="10"/>
@@ -57765,7 +58205,7 @@
     <row r="147" ht="18.75" customHeight="1">
       <c r="A147" s="26"/>
       <c r="B147" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C147" s="26"/>
       <c r="D147" s="22"/>
@@ -57793,28 +58233,28 @@
         <v>4293</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>5819</v>
+        <v>5842</v>
       </c>
       <c r="D148" s="25" t="s">
-        <v>5820</v>
+        <v>5843</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>5821</v>
+        <v>5844</v>
       </c>
       <c r="F148" s="25" t="s">
-        <v>5822</v>
+        <v>5845</v>
       </c>
       <c r="G148" s="10" t="s">
-        <v>5823</v>
+        <v>5846</v>
       </c>
       <c r="H148" s="25" t="s">
-        <v>5824</v>
+        <v>5847</v>
       </c>
       <c r="I148" s="10" t="s">
-        <v>5825</v>
+        <v>5848</v>
       </c>
       <c r="J148" s="25" t="s">
-        <v>5826</v>
+        <v>5849</v>
       </c>
       <c r="K148" s="23"/>
       <c r="L148" s="10"/>
@@ -57832,28 +58272,28 @@
         <v>4414</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>5827</v>
+        <v>5850</v>
       </c>
       <c r="D149" s="25" t="s">
-        <v>5828</v>
+        <v>5851</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>5829</v>
+        <v>5852</v>
       </c>
       <c r="F149" s="25" t="s">
-        <v>5830</v>
+        <v>5853</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>5831</v>
+        <v>5854</v>
       </c>
       <c r="H149" s="25" t="s">
-        <v>5832</v>
+        <v>5855</v>
       </c>
       <c r="I149" s="10" t="s">
-        <v>5833</v>
+        <v>5856</v>
       </c>
       <c r="J149" s="25" t="s">
-        <v>5834</v>
+        <v>5857</v>
       </c>
       <c r="K149" s="23"/>
       <c r="L149" s="10"/>
@@ -57868,7 +58308,7 @@
     <row r="150" ht="18.75" customHeight="1">
       <c r="A150" s="31"/>
       <c r="B150" s="32" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C150" s="33"/>
       <c r="D150" s="34"/>
@@ -57913,15 +58353,15 @@
       <c r="A152" s="10"/>
       <c r="B152" s="10"/>
       <c r="C152" s="18" t="s">
-        <v>5835</v>
+        <v>5858</v>
       </c>
       <c r="D152" s="19"/>
       <c r="E152" s="18" t="s">
-        <v>5836</v>
+        <v>5859</v>
       </c>
       <c r="F152" s="19"/>
       <c r="G152" s="18" t="s">
-        <v>5837</v>
+        <v>5860</v>
       </c>
       <c r="H152" s="19"/>
       <c r="I152" s="10"/>
@@ -57940,15 +58380,15 @@
       <c r="A153" s="10"/>
       <c r="B153" s="10"/>
       <c r="C153" s="23" t="s">
-        <v>5838</v>
+        <v>5861</v>
       </c>
       <c r="D153" s="22"/>
       <c r="E153" s="23" t="s">
-        <v>5839</v>
+        <v>5862</v>
       </c>
       <c r="F153" s="22"/>
       <c r="G153" s="23" t="s">
-        <v>5840</v>
+        <v>5863</v>
       </c>
       <c r="H153" s="22"/>
       <c r="I153" s="10"/>
@@ -57967,15 +58407,15 @@
       <c r="A154" s="10"/>
       <c r="B154" s="10"/>
       <c r="C154" s="23" t="s">
-        <v>5841</v>
+        <v>5864</v>
       </c>
       <c r="D154" s="22"/>
       <c r="E154" s="23" t="s">
-        <v>5842</v>
+        <v>5865</v>
       </c>
       <c r="F154" s="22"/>
       <c r="G154" s="23" t="s">
-        <v>5843</v>
+        <v>5866</v>
       </c>
       <c r="H154" s="22"/>
       <c r="I154" s="10"/>
@@ -57994,11 +58434,11 @@
       <c r="A155" s="10"/>
       <c r="B155" s="10"/>
       <c r="C155" s="23" t="s">
-        <v>5844</v>
+        <v>5867</v>
       </c>
       <c r="D155" s="22"/>
       <c r="E155" s="23" t="s">
-        <v>5845</v>
+        <v>5868</v>
       </c>
       <c r="F155" s="22"/>
       <c r="G155" s="23" t="s">
@@ -58021,22 +58461,22 @@
       <c r="A156" s="10"/>
       <c r="B156" s="10"/>
       <c r="C156" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D156" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E156" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="F156" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="G156" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="H156" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="I156" s="10"/>
       <c r="J156" s="10"/>
@@ -58054,22 +58494,22 @@
       <c r="A157" s="10"/>
       <c r="B157" s="10"/>
       <c r="C157" s="23" t="s">
-        <v>5846</v>
+        <v>5869</v>
       </c>
       <c r="D157" s="25" t="s">
-        <v>5847</v>
+        <v>5870</v>
       </c>
       <c r="E157" s="23" t="s">
-        <v>5848</v>
+        <v>5871</v>
       </c>
       <c r="F157" s="25" t="s">
-        <v>5849</v>
+        <v>5872</v>
       </c>
       <c r="G157" s="23" t="s">
-        <v>5850</v>
+        <v>5873</v>
       </c>
       <c r="H157" s="25" t="s">
-        <v>5851</v>
+        <v>5874</v>
       </c>
       <c r="I157" s="10"/>
       <c r="J157" s="10"/>
@@ -58087,22 +58527,22 @@
       <c r="A158" s="10"/>
       <c r="B158" s="10"/>
       <c r="C158" s="23" t="s">
-        <v>5852</v>
+        <v>5875</v>
       </c>
       <c r="D158" s="25" t="s">
-        <v>5853</v>
+        <v>5876</v>
       </c>
       <c r="E158" s="23" t="s">
-        <v>5854</v>
+        <v>5877</v>
       </c>
       <c r="F158" s="25" t="s">
-        <v>5855</v>
+        <v>5878</v>
       </c>
       <c r="G158" s="23" t="s">
-        <v>5856</v>
+        <v>5879</v>
       </c>
       <c r="H158" s="25" t="s">
-        <v>5857</v>
+        <v>5880</v>
       </c>
       <c r="I158" s="10"/>
       <c r="J158" s="10"/>
@@ -58120,22 +58560,22 @@
       <c r="A159" s="10"/>
       <c r="B159" s="10"/>
       <c r="C159" s="23" t="s">
-        <v>5852</v>
+        <v>5875</v>
       </c>
       <c r="D159" s="25" t="s">
-        <v>5847</v>
+        <v>5870</v>
       </c>
       <c r="E159" s="23" t="s">
-        <v>5854</v>
+        <v>5877</v>
       </c>
       <c r="F159" s="25" t="s">
-        <v>5849</v>
+        <v>5872</v>
       </c>
       <c r="G159" s="23" t="s">
-        <v>5856</v>
+        <v>5879</v>
       </c>
       <c r="H159" s="25" t="s">
-        <v>5851</v>
+        <v>5874</v>
       </c>
       <c r="I159" s="10"/>
       <c r="J159" s="10"/>
@@ -58153,22 +58593,22 @@
       <c r="A160" s="10"/>
       <c r="B160" s="10"/>
       <c r="C160" s="23" t="s">
-        <v>5858</v>
+        <v>5881</v>
       </c>
       <c r="D160" s="25" t="s">
-        <v>5859</v>
+        <v>5882</v>
       </c>
       <c r="E160" s="23" t="s">
-        <v>5860</v>
+        <v>5883</v>
       </c>
       <c r="F160" s="25" t="s">
-        <v>5861</v>
+        <v>5884</v>
       </c>
       <c r="G160" s="23" t="s">
-        <v>5862</v>
+        <v>5885</v>
       </c>
       <c r="H160" s="25" t="s">
-        <v>5863</v>
+        <v>5886</v>
       </c>
       <c r="I160" s="10"/>
       <c r="J160" s="10"/>
@@ -58186,22 +58626,22 @@
       <c r="A161" s="10"/>
       <c r="B161" s="10"/>
       <c r="C161" s="23" t="s">
-        <v>5864</v>
+        <v>5887</v>
       </c>
       <c r="D161" s="25" t="s">
-        <v>5865</v>
+        <v>5888</v>
       </c>
       <c r="E161" s="23" t="s">
-        <v>5866</v>
+        <v>5889</v>
       </c>
       <c r="F161" s="25" t="s">
-        <v>5867</v>
+        <v>5890</v>
       </c>
       <c r="G161" s="23" t="s">
-        <v>5868</v>
+        <v>5891</v>
       </c>
       <c r="H161" s="25" t="s">
-        <v>5869</v>
+        <v>5892</v>
       </c>
       <c r="I161" s="10"/>
       <c r="J161" s="10"/>
@@ -58219,22 +58659,22 @@
       <c r="A162" s="10"/>
       <c r="B162" s="10"/>
       <c r="C162" s="36" t="s">
-        <v>5870</v>
+        <v>5893</v>
       </c>
       <c r="D162" s="28" t="s">
-        <v>5871</v>
+        <v>5894</v>
       </c>
       <c r="E162" s="36" t="s">
-        <v>5872</v>
+        <v>5895</v>
       </c>
       <c r="F162" s="28" t="s">
-        <v>5873</v>
+        <v>5896</v>
       </c>
       <c r="G162" s="36" t="s">
-        <v>5874</v>
+        <v>5897</v>
       </c>
       <c r="H162" s="28" t="s">
-        <v>5875</v>
+        <v>5898</v>
       </c>
       <c r="I162" s="10"/>
       <c r="J162" s="10"/>
@@ -58271,19 +58711,19 @@
     </row>
     <row r="164" ht="18.75" customHeight="1">
       <c r="A164" s="18" t="s">
-        <v>5876</v>
+        <v>5899</v>
       </c>
       <c r="B164" s="19"/>
       <c r="C164" s="18" t="s">
-        <v>5877</v>
+        <v>5900</v>
       </c>
       <c r="D164" s="19"/>
       <c r="E164" s="18" t="s">
-        <v>5878</v>
+        <v>5901</v>
       </c>
       <c r="F164" s="19"/>
       <c r="G164" s="18" t="s">
-        <v>5879</v>
+        <v>5902</v>
       </c>
       <c r="H164" s="19"/>
       <c r="J164" s="10"/>
@@ -58299,19 +58739,19 @@
     </row>
     <row r="165" ht="18.75" customHeight="1">
       <c r="A165" s="21" t="s">
-        <v>5149</v>
+        <v>5172</v>
       </c>
       <c r="B165" s="22"/>
       <c r="C165" s="23" t="s">
-        <v>5880</v>
+        <v>5903</v>
       </c>
       <c r="D165" s="22"/>
       <c r="E165" s="23" t="s">
-        <v>5881</v>
+        <v>5904</v>
       </c>
       <c r="F165" s="22"/>
       <c r="G165" s="23" t="s">
-        <v>5882</v>
+        <v>5905</v>
       </c>
       <c r="H165" s="22"/>
       <c r="J165" s="10"/>
@@ -58327,19 +58767,19 @@
     </row>
     <row r="166" ht="18.75" customHeight="1">
       <c r="A166" s="21" t="s">
-        <v>5155</v>
+        <v>5178</v>
       </c>
       <c r="B166" s="22"/>
       <c r="C166" s="23" t="s">
-        <v>5883</v>
+        <v>5906</v>
       </c>
       <c r="D166" s="22"/>
       <c r="E166" s="23" t="s">
-        <v>5884</v>
+        <v>5907</v>
       </c>
       <c r="F166" s="22"/>
       <c r="G166" s="23" t="s">
-        <v>5885</v>
+        <v>5908</v>
       </c>
       <c r="H166" s="22"/>
       <c r="J166" s="10"/>
@@ -58355,19 +58795,19 @@
     </row>
     <row r="167" ht="18.75" customHeight="1">
       <c r="A167" s="21" t="s">
-        <v>5161</v>
+        <v>5184</v>
       </c>
       <c r="B167" s="22"/>
       <c r="C167" s="23" t="s">
-        <v>5886</v>
+        <v>5909</v>
       </c>
       <c r="D167" s="22"/>
       <c r="E167" s="23" t="s">
-        <v>5887</v>
+        <v>5910</v>
       </c>
       <c r="F167" s="22"/>
       <c r="G167" s="23" t="s">
-        <v>5888</v>
+        <v>5911</v>
       </c>
       <c r="H167" s="22"/>
       <c r="J167" s="10"/>
@@ -58383,26 +58823,26 @@
     </row>
     <row r="168" ht="18.75" customHeight="1">
       <c r="A168" s="21" t="s">
-        <v>5167</v>
+        <v>5190</v>
       </c>
       <c r="B168" s="22"/>
       <c r="C168" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D168" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E168" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="F168" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="G168" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="H168" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="J168" s="10"/>
       <c r="K168" s="10"/>
@@ -58420,25 +58860,25 @@
         <v>4925</v>
       </c>
       <c r="B169" s="24" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C169" s="23" t="s">
-        <v>5889</v>
+        <v>5912</v>
       </c>
       <c r="D169" s="25" t="s">
-        <v>5890</v>
+        <v>5913</v>
       </c>
       <c r="E169" s="23" t="s">
-        <v>5891</v>
+        <v>5914</v>
       </c>
       <c r="F169" s="25" t="s">
-        <v>5892</v>
+        <v>5915</v>
       </c>
       <c r="G169" s="23" t="s">
-        <v>5893</v>
+        <v>5916</v>
       </c>
       <c r="H169" s="25" t="s">
-        <v>5894</v>
+        <v>5917</v>
       </c>
       <c r="J169" s="10"/>
       <c r="K169" s="10"/>
@@ -58457,22 +58897,22 @@
         <v>4464</v>
       </c>
       <c r="C170" s="23" t="s">
-        <v>5895</v>
+        <v>5918</v>
       </c>
       <c r="D170" s="25" t="s">
-        <v>5896</v>
+        <v>5919</v>
       </c>
       <c r="E170" s="23" t="s">
-        <v>5897</v>
+        <v>5920</v>
       </c>
       <c r="F170" s="25" t="s">
-        <v>5898</v>
+        <v>5921</v>
       </c>
       <c r="G170" s="23" t="s">
-        <v>5899</v>
+        <v>5922</v>
       </c>
       <c r="H170" s="25" t="s">
-        <v>5900</v>
+        <v>5923</v>
       </c>
       <c r="J170" s="10"/>
       <c r="K170" s="10"/>
@@ -58488,25 +58928,25 @@
     <row r="171" ht="18.75" customHeight="1">
       <c r="A171" s="26"/>
       <c r="B171" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C171" s="23" t="s">
-        <v>5895</v>
+        <v>5918</v>
       </c>
       <c r="D171" s="25" t="s">
-        <v>5890</v>
+        <v>5913</v>
       </c>
       <c r="E171" s="23" t="s">
-        <v>5897</v>
+        <v>5920</v>
       </c>
       <c r="F171" s="25" t="s">
-        <v>5892</v>
+        <v>5915</v>
       </c>
       <c r="G171" s="23" t="s">
-        <v>5899</v>
+        <v>5922</v>
       </c>
       <c r="H171" s="25" t="s">
-        <v>5894</v>
+        <v>5917</v>
       </c>
       <c r="J171" s="10"/>
       <c r="K171" s="10"/>
@@ -58527,22 +58967,22 @@
         <v>4293</v>
       </c>
       <c r="C172" s="23" t="s">
-        <v>5901</v>
+        <v>5924</v>
       </c>
       <c r="D172" s="25" t="s">
-        <v>5902</v>
+        <v>5925</v>
       </c>
       <c r="E172" s="23" t="s">
-        <v>5903</v>
+        <v>5926</v>
       </c>
       <c r="F172" s="25" t="s">
-        <v>5904</v>
+        <v>5927</v>
       </c>
       <c r="G172" s="23" t="s">
-        <v>5905</v>
+        <v>5928</v>
       </c>
       <c r="H172" s="25" t="s">
-        <v>5906</v>
+        <v>5929</v>
       </c>
       <c r="J172" s="10"/>
       <c r="K172" s="10"/>
@@ -58560,22 +59000,22 @@
         <v>4414</v>
       </c>
       <c r="C173" s="23" t="s">
-        <v>5907</v>
+        <v>5930</v>
       </c>
       <c r="D173" s="25" t="s">
-        <v>5908</v>
+        <v>5931</v>
       </c>
       <c r="E173" s="23" t="s">
-        <v>5909</v>
+        <v>5932</v>
       </c>
       <c r="F173" s="25" t="s">
-        <v>5910</v>
+        <v>5933</v>
       </c>
       <c r="G173" s="23" t="s">
-        <v>5911</v>
+        <v>5934</v>
       </c>
       <c r="H173" s="25" t="s">
-        <v>5912</v>
+        <v>5935</v>
       </c>
       <c r="J173" s="10"/>
       <c r="K173" s="10"/>
@@ -58590,25 +59030,25 @@
     </row>
     <row r="174" ht="18.75" customHeight="1">
       <c r="B174" s="24" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C174" s="23" t="s">
-        <v>5913</v>
+        <v>5936</v>
       </c>
       <c r="D174" s="25" t="s">
-        <v>5914</v>
+        <v>5937</v>
       </c>
       <c r="E174" s="23" t="s">
-        <v>5915</v>
+        <v>5938</v>
       </c>
       <c r="F174" s="25" t="s">
-        <v>5916</v>
+        <v>5939</v>
       </c>
       <c r="G174" s="23" t="s">
-        <v>5917</v>
+        <v>5940</v>
       </c>
       <c r="H174" s="25" t="s">
-        <v>5918</v>
+        <v>5941</v>
       </c>
       <c r="J174" s="10"/>
       <c r="K174" s="10"/>
@@ -58623,14 +59063,14 @@
     </row>
     <row r="175" ht="18.75" customHeight="1">
       <c r="A175" s="21" t="s">
-        <v>5221</v>
+        <v>5244</v>
       </c>
       <c r="B175" s="22"/>
       <c r="C175" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D175" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E175" s="38"/>
       <c r="F175" s="38"/>
@@ -58653,13 +59093,13 @@
         <v>4925</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C176" s="23" t="s">
-        <v>5919</v>
+        <v>5942</v>
       </c>
       <c r="D176" s="25" t="s">
-        <v>5920</v>
+        <v>5943</v>
       </c>
       <c r="E176" s="40"/>
       <c r="F176" s="40"/>
@@ -58703,7 +59143,7 @@
     <row r="178" ht="18.75" customHeight="1">
       <c r="A178" s="26"/>
       <c r="B178" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C178" s="26"/>
       <c r="D178" s="22"/>
@@ -58731,10 +59171,10 @@
         <v>4293</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>5921</v>
+        <v>5944</v>
       </c>
       <c r="D179" s="25" t="s">
-        <v>5922</v>
+        <v>5945</v>
       </c>
       <c r="E179" s="40"/>
       <c r="F179" s="40"/>
@@ -58758,10 +59198,10 @@
         <v>4414</v>
       </c>
       <c r="C180" s="10" t="s">
-        <v>5923</v>
+        <v>5946</v>
       </c>
       <c r="D180" s="25" t="s">
-        <v>5924</v>
+        <v>5947</v>
       </c>
       <c r="E180" s="40"/>
       <c r="F180" s="40"/>
@@ -58782,7 +59222,7 @@
     <row r="181" ht="18.75" customHeight="1">
       <c r="A181" s="31"/>
       <c r="B181" s="32" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C181" s="33"/>
       <c r="D181" s="34"/>
@@ -58825,19 +59265,19 @@
     </row>
     <row r="183" ht="18.75" customHeight="1">
       <c r="A183" s="18" t="s">
-        <v>5925</v>
+        <v>5948</v>
       </c>
       <c r="B183" s="19"/>
       <c r="C183" s="20" t="s">
-        <v>5926</v>
+        <v>5949</v>
       </c>
       <c r="D183" s="19"/>
       <c r="E183" s="20" t="s">
-        <v>5927</v>
+        <v>5950</v>
       </c>
       <c r="F183" s="19"/>
       <c r="G183" s="20" t="s">
-        <v>5928</v>
+        <v>5951</v>
       </c>
       <c r="H183" s="19"/>
       <c r="I183" s="10"/>
@@ -58854,19 +59294,19 @@
     </row>
     <row r="184" ht="18.75" customHeight="1">
       <c r="A184" s="21" t="s">
-        <v>5149</v>
+        <v>5172</v>
       </c>
       <c r="B184" s="22"/>
       <c r="C184" s="10" t="s">
-        <v>5929</v>
+        <v>5952</v>
       </c>
       <c r="D184" s="22"/>
       <c r="E184" s="10" t="s">
-        <v>5741</v>
+        <v>5764</v>
       </c>
       <c r="F184" s="22"/>
       <c r="G184" s="10" t="s">
-        <v>5930</v>
+        <v>5953</v>
       </c>
       <c r="H184" s="22"/>
       <c r="I184" s="10"/>
@@ -58883,19 +59323,19 @@
     </row>
     <row r="185" ht="18.75" customHeight="1">
       <c r="A185" s="21" t="s">
-        <v>5155</v>
+        <v>5178</v>
       </c>
       <c r="B185" s="22"/>
       <c r="C185" s="23" t="s">
-        <v>5931</v>
+        <v>5954</v>
       </c>
       <c r="D185" s="22"/>
       <c r="E185" s="23" t="s">
-        <v>5747</v>
+        <v>5770</v>
       </c>
       <c r="F185" s="22"/>
       <c r="G185" s="23" t="s">
-        <v>5932</v>
+        <v>5955</v>
       </c>
       <c r="H185" s="22"/>
       <c r="I185" s="10"/>
@@ -58912,19 +59352,19 @@
     </row>
     <row r="186" ht="18.75" customHeight="1">
       <c r="A186" s="21" t="s">
-        <v>5161</v>
+        <v>5184</v>
       </c>
       <c r="B186" s="22"/>
       <c r="C186" s="23" t="s">
-        <v>5933</v>
+        <v>5956</v>
       </c>
       <c r="D186" s="22"/>
       <c r="E186" s="23" t="s">
-        <v>5753</v>
+        <v>5776</v>
       </c>
       <c r="F186" s="22"/>
       <c r="G186" s="23" t="s">
-        <v>5934</v>
+        <v>5957</v>
       </c>
       <c r="H186" s="22"/>
       <c r="I186" s="10"/>
@@ -58941,26 +59381,26 @@
     </row>
     <row r="187" ht="18.75" customHeight="1">
       <c r="A187" s="21" t="s">
-        <v>5167</v>
+        <v>5190</v>
       </c>
       <c r="B187" s="22"/>
       <c r="C187" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D187" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E187" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="F187" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="G187" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="H187" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="I187" s="10"/>
       <c r="J187" s="10"/>
@@ -58979,25 +59419,25 @@
         <v>4925</v>
       </c>
       <c r="B188" s="24" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C188" s="23" t="s">
-        <v>5935</v>
+        <v>5958</v>
       </c>
       <c r="D188" s="25" t="s">
-        <v>5936</v>
+        <v>5959</v>
       </c>
       <c r="E188" s="23" t="s">
-        <v>5762</v>
+        <v>5785</v>
       </c>
       <c r="F188" s="25" t="s">
-        <v>5763</v>
+        <v>5786</v>
       </c>
       <c r="G188" s="23" t="s">
-        <v>5937</v>
+        <v>5960</v>
       </c>
       <c r="H188" s="25" t="s">
-        <v>5938</v>
+        <v>5961</v>
       </c>
       <c r="I188" s="10"/>
       <c r="J188" s="10"/>
@@ -59017,22 +59457,22 @@
         <v>4464</v>
       </c>
       <c r="C189" s="23" t="s">
-        <v>5939</v>
+        <v>5962</v>
       </c>
       <c r="D189" s="25" t="s">
-        <v>5940</v>
+        <v>5963</v>
       </c>
       <c r="E189" s="23" t="s">
-        <v>5773</v>
+        <v>5796</v>
       </c>
       <c r="F189" s="25" t="s">
-        <v>5774</v>
+        <v>5797</v>
       </c>
       <c r="G189" s="23" t="s">
-        <v>5941</v>
+        <v>5964</v>
       </c>
       <c r="H189" s="25" t="s">
-        <v>5942</v>
+        <v>5965</v>
       </c>
       <c r="I189" s="10"/>
       <c r="J189" s="10"/>
@@ -59049,25 +59489,25 @@
     <row r="190" ht="18.75" customHeight="1">
       <c r="A190" s="26"/>
       <c r="B190" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C190" s="23" t="s">
-        <v>5939</v>
+        <v>5962</v>
       </c>
       <c r="D190" s="25" t="s">
-        <v>5936</v>
+        <v>5959</v>
       </c>
       <c r="E190" s="23" t="s">
-        <v>5773</v>
+        <v>5796</v>
       </c>
       <c r="F190" s="25" t="s">
-        <v>5763</v>
+        <v>5786</v>
       </c>
       <c r="G190" s="23" t="s">
-        <v>5941</v>
+        <v>5964</v>
       </c>
       <c r="H190" s="25" t="s">
-        <v>5938</v>
+        <v>5961</v>
       </c>
       <c r="I190" s="10"/>
       <c r="J190" s="10"/>
@@ -59089,22 +59529,22 @@
         <v>4293</v>
       </c>
       <c r="C191" s="23" t="s">
-        <v>5943</v>
+        <v>5966</v>
       </c>
       <c r="D191" s="25" t="s">
-        <v>5944</v>
+        <v>5967</v>
       </c>
       <c r="E191" s="23" t="s">
-        <v>5785</v>
+        <v>5808</v>
       </c>
       <c r="F191" s="25" t="s">
-        <v>5786</v>
+        <v>5809</v>
       </c>
       <c r="G191" s="23" t="s">
-        <v>5945</v>
+        <v>5968</v>
       </c>
       <c r="H191" s="25" t="s">
-        <v>5946</v>
+        <v>5969</v>
       </c>
       <c r="I191" s="10"/>
       <c r="J191" s="10"/>
@@ -59124,22 +59564,22 @@
         <v>4414</v>
       </c>
       <c r="C192" s="23" t="s">
-        <v>5947</v>
+        <v>5970</v>
       </c>
       <c r="D192" s="25" t="s">
-        <v>5948</v>
+        <v>5971</v>
       </c>
       <c r="E192" s="23" t="s">
-        <v>5797</v>
+        <v>5820</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>5798</v>
+        <v>5821</v>
       </c>
       <c r="G192" s="23" t="s">
-        <v>5949</v>
+        <v>5972</v>
       </c>
       <c r="H192" s="25" t="s">
-        <v>5950</v>
+        <v>5973</v>
       </c>
       <c r="I192" s="10"/>
       <c r="J192" s="10"/>
@@ -59156,25 +59596,25 @@
     <row r="193" ht="18.75" customHeight="1">
       <c r="A193" s="31"/>
       <c r="B193" s="32" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C193" s="36" t="s">
-        <v>5951</v>
+        <v>5974</v>
       </c>
       <c r="D193" s="28" t="s">
-        <v>5952</v>
+        <v>5975</v>
       </c>
       <c r="E193" s="36" t="s">
-        <v>5809</v>
+        <v>5832</v>
       </c>
       <c r="F193" s="28" t="s">
-        <v>5810</v>
+        <v>5833</v>
       </c>
       <c r="G193" s="36" t="s">
-        <v>5953</v>
+        <v>5976</v>
       </c>
       <c r="H193" s="28" t="s">
-        <v>5954</v>
+        <v>5977</v>
       </c>
       <c r="I193" s="10"/>
       <c r="J193" s="10"/>
@@ -59211,11 +59651,11 @@
     </row>
     <row r="195" ht="18.75" customHeight="1">
       <c r="A195" s="18" t="s">
-        <v>5955</v>
+        <v>5978</v>
       </c>
       <c r="B195" s="19"/>
       <c r="C195" s="18" t="s">
-        <v>5956</v>
+        <v>5979</v>
       </c>
       <c r="D195" s="19"/>
       <c r="E195" s="10"/>
@@ -59236,11 +59676,11 @@
     </row>
     <row r="196" ht="18.75" customHeight="1">
       <c r="A196" s="21" t="s">
-        <v>5149</v>
+        <v>5172</v>
       </c>
       <c r="B196" s="22"/>
       <c r="C196" s="23" t="s">
-        <v>5957</v>
+        <v>5980</v>
       </c>
       <c r="D196" s="22"/>
       <c r="E196" s="10"/>
@@ -59261,11 +59701,11 @@
     </row>
     <row r="197" ht="18.75" customHeight="1">
       <c r="A197" s="21" t="s">
-        <v>5155</v>
+        <v>5178</v>
       </c>
       <c r="B197" s="22"/>
       <c r="C197" s="23" t="s">
-        <v>5958</v>
+        <v>5981</v>
       </c>
       <c r="D197" s="22"/>
       <c r="E197" s="10"/>
@@ -59286,11 +59726,11 @@
     </row>
     <row r="198" ht="18.75" customHeight="1">
       <c r="A198" s="21" t="s">
-        <v>5161</v>
+        <v>5184</v>
       </c>
       <c r="B198" s="22"/>
       <c r="C198" s="23" t="s">
-        <v>5959</v>
+        <v>5982</v>
       </c>
       <c r="D198" s="22"/>
       <c r="E198" s="10"/>
@@ -59311,14 +59751,14 @@
     </row>
     <row r="199" ht="18.75" customHeight="1">
       <c r="A199" s="21" t="s">
-        <v>5167</v>
+        <v>5190</v>
       </c>
       <c r="B199" s="22"/>
       <c r="C199" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D199" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E199" s="10"/>
       <c r="F199" s="10"/>
@@ -59341,13 +59781,13 @@
         <v>4925</v>
       </c>
       <c r="B200" s="24" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C200" s="23" t="s">
-        <v>5960</v>
+        <v>5983</v>
       </c>
       <c r="D200" s="25" t="s">
-        <v>5961</v>
+        <v>5984</v>
       </c>
       <c r="E200" s="10"/>
       <c r="F200" s="10"/>
@@ -59371,10 +59811,10 @@
         <v>4464</v>
       </c>
       <c r="C201" s="23" t="s">
-        <v>5962</v>
+        <v>5985</v>
       </c>
       <c r="D201" s="25" t="s">
-        <v>5963</v>
+        <v>5986</v>
       </c>
       <c r="E201" s="10"/>
       <c r="F201" s="10"/>
@@ -59395,13 +59835,13 @@
     <row r="202" ht="18.75" customHeight="1">
       <c r="A202" s="26"/>
       <c r="B202" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C202" s="23" t="s">
-        <v>5962</v>
+        <v>5985</v>
       </c>
       <c r="D202" s="25" t="s">
-        <v>5961</v>
+        <v>5984</v>
       </c>
       <c r="E202" s="10"/>
       <c r="F202" s="10"/>
@@ -59427,10 +59867,10 @@
         <v>4293</v>
       </c>
       <c r="C203" s="23" t="s">
-        <v>5964</v>
+        <v>5987</v>
       </c>
       <c r="D203" s="25" t="s">
-        <v>5965</v>
+        <v>5988</v>
       </c>
       <c r="E203" s="10"/>
       <c r="F203" s="10"/>
@@ -59453,10 +59893,10 @@
         <v>4414</v>
       </c>
       <c r="C204" s="23" t="s">
-        <v>5966</v>
+        <v>5989</v>
       </c>
       <c r="D204" s="25" t="s">
-        <v>5967</v>
+        <v>5990</v>
       </c>
       <c r="E204" s="10"/>
       <c r="F204" s="10"/>
@@ -59476,13 +59916,13 @@
     </row>
     <row r="205" ht="18.75" customHeight="1">
       <c r="B205" s="24" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C205" s="23" t="s">
-        <v>5968</v>
+        <v>5991</v>
       </c>
       <c r="D205" s="25" t="s">
-        <v>5969</v>
+        <v>5992</v>
       </c>
       <c r="E205" s="10"/>
       <c r="F205" s="10"/>
@@ -59502,14 +59942,14 @@
     </row>
     <row r="206" ht="18.75" customHeight="1">
       <c r="A206" s="21" t="s">
-        <v>5221</v>
+        <v>5244</v>
       </c>
       <c r="B206" s="22"/>
       <c r="C206" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D206" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E206" s="10"/>
       <c r="F206" s="10"/>
@@ -59532,13 +59972,13 @@
         <v>4925</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C207" s="23" t="s">
-        <v>5970</v>
+        <v>5993</v>
       </c>
       <c r="D207" s="25" t="s">
-        <v>5971</v>
+        <v>5994</v>
       </c>
       <c r="E207" s="10"/>
       <c r="F207" s="10"/>
@@ -59582,7 +60022,7 @@
     <row r="209" ht="18.75" customHeight="1">
       <c r="A209" s="26"/>
       <c r="B209" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C209" s="26"/>
       <c r="D209" s="22"/>
@@ -59610,10 +60050,10 @@
         <v>4293</v>
       </c>
       <c r="C210" s="23" t="s">
-        <v>5972</v>
+        <v>5995</v>
       </c>
       <c r="D210" s="25" t="s">
-        <v>5973</v>
+        <v>5996</v>
       </c>
       <c r="E210" s="10"/>
       <c r="F210" s="10"/>
@@ -59637,10 +60077,10 @@
         <v>4414</v>
       </c>
       <c r="C211" s="23" t="s">
-        <v>5974</v>
+        <v>5997</v>
       </c>
       <c r="D211" s="25" t="s">
-        <v>5975</v>
+        <v>5998</v>
       </c>
       <c r="E211" s="10"/>
       <c r="F211" s="10"/>
@@ -59661,7 +60101,7 @@
     <row r="212" ht="18.75" customHeight="1">
       <c r="A212" s="31"/>
       <c r="B212" s="32" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C212" s="31"/>
       <c r="D212" s="34"/>
@@ -59704,11 +60144,11 @@
     </row>
     <row r="214" ht="18.75" customHeight="1">
       <c r="A214" s="18" t="s">
-        <v>5976</v>
+        <v>5999</v>
       </c>
       <c r="B214" s="19"/>
       <c r="C214" s="18" t="s">
-        <v>5977</v>
+        <v>6000</v>
       </c>
       <c r="D214" s="19"/>
       <c r="E214" s="10"/>
@@ -59729,11 +60169,11 @@
     </row>
     <row r="215" ht="18.75" customHeight="1">
       <c r="A215" s="21" t="s">
-        <v>5149</v>
+        <v>5172</v>
       </c>
       <c r="B215" s="22"/>
       <c r="C215" s="23" t="s">
-        <v>5978</v>
+        <v>6001</v>
       </c>
       <c r="D215" s="22"/>
       <c r="E215" s="10"/>
@@ -59754,11 +60194,11 @@
     </row>
     <row r="216" ht="18.75" customHeight="1">
       <c r="A216" s="21" t="s">
-        <v>5155</v>
+        <v>5178</v>
       </c>
       <c r="B216" s="22"/>
       <c r="C216" s="23" t="s">
-        <v>5979</v>
+        <v>6002</v>
       </c>
       <c r="D216" s="22"/>
       <c r="E216" s="10"/>
@@ -59779,11 +60219,11 @@
     </row>
     <row r="217" ht="18.75" customHeight="1">
       <c r="A217" s="21" t="s">
-        <v>5161</v>
+        <v>5184</v>
       </c>
       <c r="B217" s="22"/>
       <c r="C217" s="23" t="s">
-        <v>5980</v>
+        <v>6003</v>
       </c>
       <c r="D217" s="22"/>
       <c r="E217" s="10"/>
@@ -59804,14 +60244,14 @@
     </row>
     <row r="218" ht="18.75" customHeight="1">
       <c r="A218" s="21" t="s">
-        <v>5167</v>
+        <v>5190</v>
       </c>
       <c r="B218" s="22"/>
       <c r="C218" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D218" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E218" s="10"/>
       <c r="F218" s="10"/>
@@ -59834,13 +60274,13 @@
         <v>4925</v>
       </c>
       <c r="B219" s="24" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C219" s="23" t="s">
-        <v>5981</v>
+        <v>6004</v>
       </c>
       <c r="D219" s="25" t="s">
-        <v>5982</v>
+        <v>6005</v>
       </c>
       <c r="E219" s="10"/>
       <c r="F219" s="10"/>
@@ -59864,10 +60304,10 @@
         <v>4464</v>
       </c>
       <c r="C220" s="23" t="s">
-        <v>5983</v>
+        <v>6006</v>
       </c>
       <c r="D220" s="25" t="s">
-        <v>5984</v>
+        <v>6007</v>
       </c>
       <c r="E220" s="10"/>
       <c r="F220" s="10"/>
@@ -59888,13 +60328,13 @@
     <row r="221" ht="18.75" customHeight="1">
       <c r="A221" s="26"/>
       <c r="B221" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C221" s="23" t="s">
-        <v>5983</v>
+        <v>6006</v>
       </c>
       <c r="D221" s="25" t="s">
-        <v>5982</v>
+        <v>6005</v>
       </c>
       <c r="E221" s="10"/>
       <c r="F221" s="10"/>
@@ -59920,10 +60360,10 @@
         <v>4293</v>
       </c>
       <c r="C222" s="23" t="s">
-        <v>5985</v>
+        <v>6008</v>
       </c>
       <c r="D222" s="25" t="s">
-        <v>5986</v>
+        <v>6009</v>
       </c>
       <c r="E222" s="10"/>
       <c r="F222" s="10"/>
@@ -59946,10 +60386,10 @@
         <v>4414</v>
       </c>
       <c r="C223" s="23" t="s">
-        <v>5987</v>
+        <v>6010</v>
       </c>
       <c r="D223" s="25" t="s">
-        <v>5988</v>
+        <v>6011</v>
       </c>
       <c r="E223" s="10"/>
       <c r="F223" s="10"/>
@@ -59969,13 +60409,13 @@
     </row>
     <row r="224" ht="18.75" customHeight="1">
       <c r="B224" s="24" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C224" s="23" t="s">
-        <v>5989</v>
+        <v>6012</v>
       </c>
       <c r="D224" s="25" t="s">
-        <v>5990</v>
+        <v>6013</v>
       </c>
       <c r="E224" s="10"/>
       <c r="F224" s="10"/>
@@ -59995,14 +60435,14 @@
     </row>
     <row r="225" ht="18.75" customHeight="1">
       <c r="A225" s="21" t="s">
-        <v>5221</v>
+        <v>5244</v>
       </c>
       <c r="B225" s="22"/>
       <c r="C225" s="8" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D225" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E225" s="10"/>
       <c r="F225" s="10"/>
@@ -60025,13 +60465,13 @@
         <v>4925</v>
       </c>
       <c r="B226" s="8" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C226" s="23" t="s">
-        <v>5991</v>
+        <v>6014</v>
       </c>
       <c r="D226" s="25" t="s">
-        <v>5992</v>
+        <v>6015</v>
       </c>
       <c r="E226" s="10"/>
       <c r="F226" s="10"/>
@@ -60075,7 +60515,7 @@
     <row r="228" ht="18.75" customHeight="1">
       <c r="A228" s="26"/>
       <c r="B228" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C228" s="26"/>
       <c r="D228" s="22"/>
@@ -60103,10 +60543,10 @@
         <v>4293</v>
       </c>
       <c r="C229" s="23" t="s">
-        <v>5993</v>
+        <v>6016</v>
       </c>
       <c r="D229" s="25" t="s">
-        <v>5994</v>
+        <v>6017</v>
       </c>
       <c r="E229" s="10"/>
       <c r="F229" s="10"/>
@@ -60130,10 +60570,10 @@
         <v>4414</v>
       </c>
       <c r="C230" s="23" t="s">
-        <v>5995</v>
+        <v>6018</v>
       </c>
       <c r="D230" s="25" t="s">
-        <v>5996</v>
+        <v>6019</v>
       </c>
       <c r="E230" s="10"/>
       <c r="F230" s="10"/>
@@ -60154,7 +60594,7 @@
     <row r="231" ht="18.75" customHeight="1">
       <c r="A231" s="31"/>
       <c r="B231" s="32" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C231" s="31"/>
       <c r="D231" s="34"/>
@@ -60197,11 +60637,11 @@
     </row>
     <row r="233" ht="18.75" customHeight="1">
       <c r="A233" s="18" t="s">
-        <v>5997</v>
+        <v>6020</v>
       </c>
       <c r="B233" s="19"/>
       <c r="C233" s="18" t="s">
-        <v>5998</v>
+        <v>6021</v>
       </c>
       <c r="D233" s="19"/>
       <c r="E233" s="10"/>
@@ -60222,11 +60662,11 @@
     </row>
     <row r="234" ht="18.75" customHeight="1">
       <c r="A234" s="21" t="s">
-        <v>5149</v>
+        <v>5172</v>
       </c>
       <c r="B234" s="22"/>
       <c r="C234" s="23" t="s">
-        <v>5999</v>
+        <v>6022</v>
       </c>
       <c r="D234" s="22"/>
       <c r="E234" s="10"/>
@@ -60247,11 +60687,11 @@
     </row>
     <row r="235" ht="18.75" customHeight="1">
       <c r="A235" s="21" t="s">
-        <v>5155</v>
+        <v>5178</v>
       </c>
       <c r="B235" s="22"/>
       <c r="C235" s="23" t="s">
-        <v>6000</v>
+        <v>6023</v>
       </c>
       <c r="D235" s="22"/>
       <c r="E235" s="10"/>
@@ -60272,11 +60712,11 @@
     </row>
     <row r="236" ht="18.75" customHeight="1">
       <c r="A236" s="21" t="s">
-        <v>5161</v>
+        <v>5184</v>
       </c>
       <c r="B236" s="22"/>
       <c r="C236" s="23" t="s">
-        <v>6001</v>
+        <v>6024</v>
       </c>
       <c r="D236" s="22"/>
       <c r="E236" s="10"/>
@@ -60297,14 +60737,14 @@
     </row>
     <row r="237" ht="18.75" customHeight="1">
       <c r="A237" s="21" t="s">
-        <v>5167</v>
+        <v>5190</v>
       </c>
       <c r="B237" s="22"/>
       <c r="C237" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D237" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E237" s="10"/>
       <c r="F237" s="10"/>
@@ -60327,13 +60767,13 @@
         <v>4925</v>
       </c>
       <c r="B238" s="24" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C238" s="23" t="s">
-        <v>6002</v>
+        <v>6025</v>
       </c>
       <c r="D238" s="25" t="s">
-        <v>6003</v>
+        <v>6026</v>
       </c>
       <c r="E238" s="10"/>
       <c r="F238" s="10"/>
@@ -60357,10 +60797,10 @@
         <v>4464</v>
       </c>
       <c r="C239" s="23" t="s">
-        <v>6004</v>
+        <v>6027</v>
       </c>
       <c r="D239" s="25" t="s">
-        <v>6005</v>
+        <v>6028</v>
       </c>
       <c r="E239" s="10"/>
       <c r="F239" s="10"/>
@@ -60381,13 +60821,13 @@
     <row r="240" ht="18.75" customHeight="1">
       <c r="A240" s="26"/>
       <c r="B240" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C240" s="23" t="s">
-        <v>6004</v>
+        <v>6027</v>
       </c>
       <c r="D240" s="25" t="s">
-        <v>6006</v>
+        <v>6029</v>
       </c>
       <c r="E240" s="10"/>
       <c r="F240" s="10"/>
@@ -60413,10 +60853,10 @@
         <v>4293</v>
       </c>
       <c r="C241" s="23" t="s">
-        <v>6007</v>
+        <v>6030</v>
       </c>
       <c r="D241" s="25" t="s">
-        <v>6008</v>
+        <v>6031</v>
       </c>
       <c r="E241" s="10"/>
       <c r="F241" s="10"/>
@@ -60440,10 +60880,10 @@
         <v>4414</v>
       </c>
       <c r="C242" s="23" t="s">
-        <v>6009</v>
+        <v>6032</v>
       </c>
       <c r="D242" s="25" t="s">
-        <v>6010</v>
+        <v>6033</v>
       </c>
       <c r="E242" s="10"/>
       <c r="F242" s="10"/>
@@ -60464,13 +60904,13 @@
     <row r="243" ht="18.75" customHeight="1">
       <c r="A243" s="31"/>
       <c r="B243" s="32" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C243" s="36" t="s">
-        <v>6011</v>
+        <v>6034</v>
       </c>
       <c r="D243" s="28" t="s">
-        <v>6012</v>
+        <v>6035</v>
       </c>
       <c r="E243" s="10"/>
       <c r="F243" s="10"/>
@@ -60511,11 +60951,11 @@
     </row>
     <row r="245" ht="18.75" customHeight="1">
       <c r="A245" s="18" t="s">
-        <v>6013</v>
+        <v>6036</v>
       </c>
       <c r="B245" s="19"/>
       <c r="C245" s="18" t="s">
-        <v>6014</v>
+        <v>6037</v>
       </c>
       <c r="D245" s="19"/>
       <c r="E245" s="10"/>
@@ -60536,11 +60976,11 @@
     </row>
     <row r="246" ht="18.75" customHeight="1">
       <c r="A246" s="21" t="s">
-        <v>5149</v>
+        <v>5172</v>
       </c>
       <c r="B246" s="22"/>
       <c r="C246" s="23" t="s">
-        <v>6015</v>
+        <v>6038</v>
       </c>
       <c r="D246" s="22"/>
       <c r="E246" s="10"/>
@@ -60561,11 +61001,11 @@
     </row>
     <row r="247" ht="18.75" customHeight="1">
       <c r="A247" s="21" t="s">
-        <v>5155</v>
+        <v>5178</v>
       </c>
       <c r="B247" s="22"/>
       <c r="C247" s="23" t="s">
-        <v>6016</v>
+        <v>6039</v>
       </c>
       <c r="D247" s="22"/>
       <c r="E247" s="10"/>
@@ -60586,11 +61026,11 @@
     </row>
     <row r="248" ht="18.75" customHeight="1">
       <c r="A248" s="21" t="s">
-        <v>5161</v>
+        <v>5184</v>
       </c>
       <c r="B248" s="22"/>
       <c r="C248" s="23" t="s">
-        <v>6017</v>
+        <v>6040</v>
       </c>
       <c r="D248" s="22"/>
       <c r="E248" s="10"/>
@@ -60611,14 +61051,14 @@
     </row>
     <row r="249" ht="18.75" customHeight="1">
       <c r="A249" s="21" t="s">
-        <v>5167</v>
+        <v>5190</v>
       </c>
       <c r="B249" s="22"/>
       <c r="C249" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D249" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E249" s="10"/>
       <c r="F249" s="10"/>
@@ -60641,13 +61081,13 @@
         <v>4925</v>
       </c>
       <c r="B250" s="24" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C250" s="23" t="s">
-        <v>6018</v>
+        <v>6041</v>
       </c>
       <c r="D250" s="25" t="s">
-        <v>6019</v>
+        <v>6042</v>
       </c>
       <c r="E250" s="10"/>
       <c r="F250" s="10"/>
@@ -60671,10 +61111,10 @@
         <v>4464</v>
       </c>
       <c r="C251" s="23" t="s">
-        <v>6020</v>
+        <v>6043</v>
       </c>
       <c r="D251" s="25" t="s">
-        <v>6021</v>
+        <v>6044</v>
       </c>
       <c r="E251" s="10"/>
       <c r="F251" s="10"/>
@@ -60695,13 +61135,13 @@
     <row r="252" ht="18.75" customHeight="1">
       <c r="A252" s="26"/>
       <c r="B252" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C252" s="23" t="s">
-        <v>6018</v>
+        <v>6041</v>
       </c>
       <c r="D252" s="25" t="s">
-        <v>6022</v>
+        <v>6045</v>
       </c>
       <c r="E252" s="10"/>
       <c r="F252" s="10"/>
@@ -60727,10 +61167,10 @@
         <v>4293</v>
       </c>
       <c r="C253" s="23" t="s">
-        <v>6023</v>
+        <v>6046</v>
       </c>
       <c r="D253" s="25" t="s">
-        <v>6024</v>
+        <v>6047</v>
       </c>
       <c r="E253" s="10"/>
       <c r="F253" s="10"/>
@@ -60754,10 +61194,10 @@
         <v>4414</v>
       </c>
       <c r="C254" s="23" t="s">
-        <v>6025</v>
+        <v>6048</v>
       </c>
       <c r="D254" s="25" t="s">
-        <v>6026</v>
+        <v>6049</v>
       </c>
       <c r="E254" s="10"/>
       <c r="F254" s="10"/>
@@ -60778,13 +61218,13 @@
     <row r="255" ht="18.75" customHeight="1">
       <c r="A255" s="31"/>
       <c r="B255" s="32" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C255" s="36" t="s">
-        <v>6027</v>
+        <v>6050</v>
       </c>
       <c r="D255" s="28" t="s">
-        <v>6028</v>
+        <v>6051</v>
       </c>
       <c r="E255" s="10"/>
       <c r="F255" s="10"/>
@@ -60825,15 +61265,15 @@
     </row>
     <row r="257" ht="18.75" customHeight="1">
       <c r="A257" s="18" t="s">
-        <v>6029</v>
+        <v>6052</v>
       </c>
       <c r="B257" s="19"/>
       <c r="C257" s="18" t="s">
-        <v>6030</v>
+        <v>6053</v>
       </c>
       <c r="D257" s="19"/>
       <c r="E257" s="18" t="s">
-        <v>6031</v>
+        <v>6054</v>
       </c>
       <c r="F257" s="19"/>
       <c r="G257" s="10"/>
@@ -60852,20 +61292,20 @@
     </row>
     <row r="258" ht="18.75" customHeight="1">
       <c r="A258" s="21" t="s">
-        <v>5167</v>
+        <v>5190</v>
       </c>
       <c r="B258" s="22"/>
       <c r="C258" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="D258" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="E258" s="21" t="s">
-        <v>5168</v>
+        <v>5191</v>
       </c>
       <c r="F258" s="24" t="s">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="G258" s="10"/>
       <c r="H258" s="10"/>
@@ -60886,19 +61326,19 @@
         <v>4925</v>
       </c>
       <c r="B259" s="24" t="s">
-        <v>5170</v>
+        <v>5193</v>
       </c>
       <c r="C259" s="23" t="s">
-        <v>6032</v>
+        <v>6055</v>
       </c>
       <c r="D259" s="25" t="s">
-        <v>6033</v>
+        <v>6056</v>
       </c>
       <c r="E259" s="23" t="s">
-        <v>6034</v>
+        <v>6057</v>
       </c>
       <c r="F259" s="25" t="s">
-        <v>6035</v>
+        <v>6058</v>
       </c>
       <c r="G259" s="10"/>
       <c r="H259" s="10"/>
@@ -60920,16 +61360,16 @@
         <v>4464</v>
       </c>
       <c r="C260" s="23" t="s">
-        <v>6036</v>
+        <v>6059</v>
       </c>
       <c r="D260" s="25" t="s">
-        <v>5267</v>
+        <v>5290</v>
       </c>
       <c r="E260" s="23" t="s">
-        <v>5851</v>
+        <v>5874</v>
       </c>
       <c r="F260" s="25" t="s">
-        <v>6037</v>
+        <v>6060</v>
       </c>
       <c r="G260" s="10"/>
       <c r="H260" s="10"/>
@@ -60948,19 +61388,19 @@
     <row r="261" ht="18.75" customHeight="1">
       <c r="A261" s="26"/>
       <c r="B261" s="24" t="s">
-        <v>5185</v>
+        <v>5208</v>
       </c>
       <c r="C261" s="23" t="s">
-        <v>6032</v>
+        <v>6055</v>
       </c>
       <c r="D261" s="25" t="s">
-        <v>5257</v>
+        <v>5280</v>
       </c>
       <c r="E261" s="23" t="s">
-        <v>5851</v>
+        <v>5874</v>
       </c>
       <c r="F261" s="25" t="s">
-        <v>6038</v>
+        <v>6061</v>
       </c>
       <c r="G261" s="10"/>
       <c r="H261" s="10"/>
@@ -60984,16 +61424,16 @@
         <v>4293</v>
       </c>
       <c r="C262" s="23" t="s">
-        <v>6039</v>
+        <v>6062</v>
       </c>
       <c r="D262" s="25" t="s">
-        <v>6040</v>
+        <v>6063</v>
       </c>
       <c r="E262" s="23" t="s">
-        <v>6041</v>
+        <v>6064</v>
       </c>
       <c r="F262" s="25" t="s">
-        <v>6042</v>
+        <v>6065</v>
       </c>
       <c r="G262" s="10"/>
       <c r="H262" s="10"/>
@@ -61015,16 +61455,16 @@
         <v>4414</v>
       </c>
       <c r="C263" s="23" t="s">
-        <v>6043</v>
+        <v>6066</v>
       </c>
       <c r="D263" s="25" t="s">
-        <v>6044</v>
+        <v>6067</v>
       </c>
       <c r="E263" s="23" t="s">
-        <v>6045</v>
+        <v>6068</v>
       </c>
       <c r="F263" s="25" t="s">
-        <v>6046</v>
+        <v>6069</v>
       </c>
       <c r="G263" s="10"/>
       <c r="H263" s="10"/>
@@ -61043,19 +61483,19 @@
     <row r="264" ht="18.75" customHeight="1">
       <c r="A264" s="31"/>
       <c r="B264" s="32" t="s">
-        <v>5210</v>
+        <v>5233</v>
       </c>
       <c r="C264" s="36" t="s">
         <v>2577</v>
       </c>
       <c r="D264" s="28" t="s">
-        <v>6047</v>
+        <v>6070</v>
       </c>
       <c r="E264" s="36" t="s">
         <v>3409</v>
       </c>
       <c r="F264" s="28" t="s">
-        <v>6048</v>
+        <v>6071</v>
       </c>
       <c r="G264" s="10"/>
       <c r="H264" s="10"/>
@@ -61548,11 +61988,11 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="42" t="s">
-        <v>6049</v>
+        <v>6072</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="42" t="s">
-        <v>6050</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
@@ -61560,14 +62000,14 @@
         <v>254</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>6051</v>
+        <v>6074</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="43" t="s">
-        <v>6052</v>
+        <v>6075</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>6053</v>
+        <v>6076</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
@@ -61575,14 +62015,14 @@
         <v>1603</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6054</v>
+        <v>6077</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="43" t="s">
-        <v>6055</v>
+        <v>6078</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>6056</v>
+        <v>6079</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
@@ -61590,14 +62030,14 @@
         <v>2208</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6057</v>
+        <v>6080</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="43" t="s">
-        <v>6058</v>
+        <v>6081</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>6059</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
@@ -61605,14 +62045,14 @@
         <v>2326</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>6060</v>
+        <v>6083</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="43" t="s">
-        <v>6061</v>
+        <v>6084</v>
       </c>
       <c r="G5" s="43" t="s">
-        <v>6062</v>
+        <v>6085</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
@@ -61620,14 +62060,14 @@
         <v>2468</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6063</v>
+        <v>6086</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="43" t="s">
-        <v>6064</v>
+        <v>6087</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>6065</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
@@ -61635,14 +62075,14 @@
         <v>2577</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6066</v>
+        <v>6089</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="43" t="s">
-        <v>6067</v>
+        <v>6090</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>6068</v>
+        <v>6091</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
@@ -61650,14 +62090,14 @@
         <v>2664</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6069</v>
+        <v>6092</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="43" t="s">
-        <v>6070</v>
+        <v>6093</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>6071</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
@@ -61665,14 +62105,14 @@
         <v>3409</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6072</v>
+        <v>6095</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="43" t="s">
-        <v>6073</v>
+        <v>6096</v>
       </c>
       <c r="G9" s="43" t="s">
-        <v>6074</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
@@ -61680,14 +62120,14 @@
         <v>3683</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6075</v>
+        <v>6098</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="43" t="s">
-        <v>6076</v>
+        <v>6099</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>6077</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
@@ -61695,14 +62135,14 @@
         <v>4386</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6078</v>
+        <v>6101</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="43" t="s">
-        <v>6079</v>
+        <v>6102</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>6080</v>
+        <v>6103</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
@@ -61711,10 +62151,10 @@
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
       <c r="E12" s="43" t="s">
-        <v>6081</v>
+        <v>6104</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>6082</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
@@ -61723,10 +62163,10 @@
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
       <c r="E13" s="43" t="s">
-        <v>6083</v>
+        <v>6106</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>6084</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
@@ -61735,113 +62175,113 @@
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="43" t="s">
-        <v>6085</v>
+        <v>6108</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>6086</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="42" t="s">
-        <v>6087</v>
+        <v>6110</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>6088</v>
+        <v>6111</v>
       </c>
       <c r="G15" s="45" t="s">
-        <v>6089</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6090</v>
+        <v>6113</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>6091</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6092</v>
+        <v>6115</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>6093</v>
+        <v>6116</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>6094</v>
+        <v>6117</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>6095</v>
+        <v>6118</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>6096</v>
+        <v>6119</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>6097</v>
+        <v>6120</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>6098</v>
+        <v>6121</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>6099</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6100</v>
+        <v>6123</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>6101</v>
+        <v>6124</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>6102</v>
+        <v>6125</v>
       </c>
       <c r="G19" s="43" t="s">
-        <v>6103</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6104</v>
+        <v>6127</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>6105</v>
+        <v>6128</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>6106</v>
+        <v>6129</v>
       </c>
       <c r="G20" s="43" t="s">
-        <v>6107</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6108</v>
+        <v>6131</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>6109</v>
+        <v>6132</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>6110</v>
+        <v>6133</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>6111</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6112</v>
+        <v>6135</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>6113</v>
+        <v>6136</v>
       </c>
       <c r="E22" s="46" t="s">
-        <v>6114</v>
+        <v>6137</v>
       </c>
       <c r="G22" s="46" t="s">
-        <v>6115</v>
+        <v>6138</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
@@ -61856,71 +62296,71 @@
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
       <c r="E24" s="43" t="s">
-        <v>6116</v>
+        <v>6139</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>6117</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="E25" s="43" t="s">
-        <v>6118</v>
+        <v>6141</v>
       </c>
       <c r="G25" s="43" t="s">
-        <v>6119</v>
+        <v>6142</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="42" t="s">
-        <v>6120</v>
+        <v>6143</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>6121</v>
+        <v>6144</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>6122</v>
+        <v>6145</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>6123</v>
+        <v>6146</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>6124</v>
+        <v>6147</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>6125</v>
+        <v>6148</v>
       </c>
       <c r="G27" s="43" t="s">
-        <v>6126</v>
+        <v>6149</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="43" t="s">
-        <v>6127</v>
+        <v>6150</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>6128</v>
+        <v>6151</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>6129</v>
+        <v>6152</v>
       </c>
       <c r="G28" s="43" t="s">
-        <v>6130</v>
+        <v>6153</v>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="43" t="s">
-        <v>6131</v>
+        <v>6154</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>6132</v>
+        <v>6155</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>6133</v>
+        <v>6156</v>
       </c>
       <c r="G29" s="43" t="s">
-        <v>6134</v>
+        <v>6157</v>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1">
@@ -61929,10 +62369,10 @@
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
       <c r="E30" s="43" t="s">
-        <v>6135</v>
+        <v>6158</v>
       </c>
       <c r="G30" s="43" t="s">
-        <v>6136</v>
+        <v>6159</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
@@ -61941,10 +62381,10 @@
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
       <c r="E31" s="43" t="s">
-        <v>6137</v>
+        <v>6160</v>
       </c>
       <c r="G31" s="43" t="s">
-        <v>6138</v>
+        <v>6161</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
@@ -61953,10 +62393,10 @@
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
       <c r="E32" s="43" t="s">
-        <v>6139</v>
+        <v>6162</v>
       </c>
       <c r="G32" s="43" t="s">
-        <v>6140</v>
+        <v>6163</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
@@ -61965,10 +62405,10 @@
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
       <c r="E33" s="43" t="s">
-        <v>6141</v>
+        <v>6164</v>
       </c>
       <c r="G33" s="43" t="s">
-        <v>6142</v>
+        <v>6165</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
@@ -61977,10 +62417,10 @@
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
       <c r="E34" s="43" t="s">
-        <v>6143</v>
+        <v>6166</v>
       </c>
       <c r="G34" s="43" t="s">
-        <v>6144</v>
+        <v>6167</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
@@ -61989,10 +62429,10 @@
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
       <c r="E35" s="45" t="s">
-        <v>6145</v>
+        <v>6168</v>
       </c>
       <c r="G35" s="45" t="s">
-        <v>6146</v>
+        <v>6169</v>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1">
@@ -62007,10 +62447,10 @@
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
       <c r="E37" s="43" t="s">
-        <v>6147</v>
+        <v>6170</v>
       </c>
       <c r="G37" s="43" t="s">
-        <v>6148</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
@@ -62019,10 +62459,10 @@
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
       <c r="E38" s="43" t="s">
-        <v>6149</v>
+        <v>6172</v>
       </c>
       <c r="G38" s="43" t="s">
-        <v>6150</v>
+        <v>6173</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
@@ -62031,10 +62471,10 @@
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
       <c r="E39" s="45" t="s">
-        <v>6151</v>
+        <v>6174</v>
       </c>
       <c r="G39" s="45" t="s">
-        <v>6152</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
@@ -62049,10 +62489,10 @@
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
       <c r="E41" s="45" t="s">
-        <v>6153</v>
+        <v>6176</v>
       </c>
       <c r="G41" s="45" t="s">
-        <v>6154</v>
+        <v>6177</v>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1">
@@ -62270,10 +62710,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="43" t="s">
-        <v>6155</v>
+        <v>6178</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>6156</v>
+        <v>6179</v>
       </c>
       <c r="C1" s="12"/>
     </row>
@@ -62282,34 +62722,34 @@
         <v>38</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>6157</v>
+        <v>6180</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>6158</v>
+        <v>6181</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6159</v>
+        <v>6182</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>6160</v>
+        <v>6183</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6161</v>
+        <v>6184</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>6162</v>
+        <v>6185</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>6163</v>
+        <v>6186</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -62318,70 +62758,70 @@
         <v>1858</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6164</v>
+        <v>6187</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>6165</v>
+        <v>6188</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6166</v>
+        <v>6189</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>6167</v>
+        <v>6190</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6168</v>
+        <v>6191</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>6169</v>
+        <v>6192</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6170</v>
+        <v>6193</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>6171</v>
+        <v>6194</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6172</v>
+        <v>6195</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>6173</v>
+        <v>6196</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6174</v>
+        <v>6197</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>6175</v>
+        <v>6198</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>6176</v>
+        <v>6199</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>6177</v>
+        <v>6200</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>6178</v>
+        <v>6201</v>
       </c>
       <c r="C13" s="12"/>
     </row>
@@ -62390,7 +62830,7 @@
         <v>4889</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>6179</v>
+        <v>6202</v>
       </c>
       <c r="C14" s="12"/>
     </row>
@@ -62401,19 +62841,19 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6180</v>
+        <v>6203</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>6181</v>
+        <v>6204</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6182</v>
+        <v>6205</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>6183</v>
+        <v>6206</v>
       </c>
       <c r="C17" s="12"/>
     </row>
@@ -62424,334 +62864,334 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6184</v>
+        <v>6207</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>6185</v>
+        <v>6208</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6186</v>
+        <v>6209</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>6187</v>
+        <v>6210</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6188</v>
+        <v>6211</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>6189</v>
+        <v>6212</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6190</v>
+        <v>6213</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>6191</v>
+        <v>6214</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>6192</v>
+        <v>6215</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>6193</v>
+        <v>6216</v>
       </c>
       <c r="C23" s="12"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="43" t="s">
-        <v>6194</v>
+        <v>6217</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>6195</v>
+        <v>6218</v>
       </c>
       <c r="C24" s="12"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="43" t="s">
-        <v>6196</v>
+        <v>6219</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>6197</v>
+        <v>6220</v>
       </c>
       <c r="C25" s="12"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="43" t="s">
-        <v>6198</v>
+        <v>6221</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>6199</v>
+        <v>6222</v>
       </c>
       <c r="C26" s="12"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>6200</v>
+        <v>6223</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>6201</v>
+        <v>6224</v>
       </c>
       <c r="C27" s="12"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="43" t="s">
-        <v>6202</v>
+        <v>6225</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>6203</v>
+        <v>6226</v>
       </c>
       <c r="C28" s="12"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="43" t="s">
-        <v>6204</v>
+        <v>6227</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>6205</v>
+        <v>6228</v>
       </c>
       <c r="C29" s="12"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="43" t="s">
-        <v>6206</v>
+        <v>6229</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>6207</v>
+        <v>6230</v>
       </c>
       <c r="C30" s="12"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="43" t="s">
-        <v>6208</v>
+        <v>6231</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>6209</v>
+        <v>6232</v>
       </c>
       <c r="C31" s="12"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="43" t="s">
-        <v>6210</v>
+        <v>6233</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>6211</v>
+        <v>6234</v>
       </c>
       <c r="C32" s="12"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="43" t="s">
-        <v>6212</v>
+        <v>6235</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>6213</v>
+        <v>6236</v>
       </c>
       <c r="C33" s="12"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="43" t="s">
-        <v>6214</v>
+        <v>6237</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>6215</v>
+        <v>6238</v>
       </c>
       <c r="C34" s="12"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="43" t="s">
-        <v>6216</v>
+        <v>6239</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>6217</v>
+        <v>6240</v>
       </c>
       <c r="C35" s="12"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="43" t="s">
-        <v>6218</v>
+        <v>6241</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>6219</v>
+        <v>6242</v>
       </c>
       <c r="C36" s="12"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="43" t="s">
-        <v>6220</v>
+        <v>6243</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>6221</v>
+        <v>6244</v>
       </c>
       <c r="C37" s="12"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="43" t="s">
-        <v>6222</v>
+        <v>6245</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>6223</v>
+        <v>6246</v>
       </c>
       <c r="C38" s="12"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="43" t="s">
-        <v>6224</v>
+        <v>6247</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>6225</v>
+        <v>6248</v>
       </c>
       <c r="C39" s="12"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="43" t="s">
-        <v>6226</v>
+        <v>6249</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>6227</v>
+        <v>6250</v>
       </c>
       <c r="C40" s="12"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="43" t="s">
-        <v>6228</v>
+        <v>6251</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>6229</v>
+        <v>6252</v>
       </c>
       <c r="C41" s="12"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="43" t="s">
-        <v>6230</v>
+        <v>6253</v>
       </c>
       <c r="B42" s="43" t="s">
-        <v>6231</v>
+        <v>6254</v>
       </c>
       <c r="C42" s="12"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="43" t="s">
-        <v>6232</v>
+        <v>6255</v>
       </c>
       <c r="B43" s="43" t="s">
-        <v>6233</v>
+        <v>6256</v>
       </c>
       <c r="C43" s="12"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" s="43" t="s">
-        <v>6234</v>
+        <v>6257</v>
       </c>
       <c r="B44" s="43" t="s">
-        <v>6235</v>
+        <v>6258</v>
       </c>
       <c r="C44" s="12"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="43" t="s">
-        <v>6236</v>
+        <v>6259</v>
       </c>
       <c r="B45" s="43" t="s">
-        <v>6237</v>
+        <v>6260</v>
       </c>
       <c r="C45" s="12"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="43" t="s">
-        <v>6238</v>
+        <v>6261</v>
       </c>
       <c r="B46" s="43" t="s">
-        <v>6239</v>
+        <v>6262</v>
       </c>
       <c r="C46" s="12"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="43" t="s">
-        <v>6240</v>
+        <v>6263</v>
       </c>
       <c r="B47" s="43" t="s">
-        <v>6241</v>
+        <v>6264</v>
       </c>
       <c r="C47" s="12"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="43" t="s">
-        <v>6242</v>
+        <v>6265</v>
       </c>
       <c r="B48" s="43" t="s">
-        <v>6243</v>
+        <v>6266</v>
       </c>
       <c r="C48" s="12"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" s="43" t="s">
-        <v>6244</v>
+        <v>6267</v>
       </c>
       <c r="B49" s="43" t="s">
-        <v>6245</v>
+        <v>6268</v>
       </c>
       <c r="C49" s="12"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" s="43" t="s">
-        <v>6246</v>
+        <v>6269</v>
       </c>
       <c r="B50" s="43" t="s">
-        <v>6247</v>
+        <v>6270</v>
       </c>
       <c r="C50" s="12"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" s="43" t="s">
-        <v>6248</v>
+        <v>6271</v>
       </c>
       <c r="B51" s="43" t="s">
-        <v>6249</v>
+        <v>6272</v>
       </c>
       <c r="C51" s="12"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" s="43" t="s">
-        <v>6250</v>
+        <v>6273</v>
       </c>
       <c r="B52" s="43" t="s">
-        <v>6251</v>
+        <v>6274</v>
       </c>
       <c r="C52" s="12"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" s="43" t="s">
-        <v>6252</v>
+        <v>6275</v>
       </c>
       <c r="B53" s="43" t="s">
-        <v>6253</v>
+        <v>6276</v>
       </c>
       <c r="C53" s="12"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" s="43" t="s">
-        <v>6254</v>
+        <v>6277</v>
       </c>
       <c r="B54" s="43" t="s">
-        <v>6255</v>
+        <v>6278</v>
       </c>
       <c r="C54" s="12"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" s="43" t="s">
-        <v>6256</v>
+        <v>6279</v>
       </c>
       <c r="B55" s="43" t="s">
-        <v>6257</v>
+        <v>6280</v>
       </c>
       <c r="C55" s="12"/>
     </row>
@@ -62774,130 +63214,130 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="47" t="s">
-        <v>6258</v>
+        <v>6281</v>
       </c>
       <c r="C1" s="12"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="47" t="s">
-        <v>6259</v>
+        <v>6282</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>6260</v>
+        <v>6283</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>6261</v>
+        <v>6284</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6182</v>
+        <v>6205</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>6182</v>
+        <v>6205</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6169</v>
+        <v>6192</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>6262</v>
+        <v>6285</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>6171</v>
+        <v>6194</v>
       </c>
       <c r="C5" s="12"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="43" t="s">
-        <v>6263</v>
+        <v>6286</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6264</v>
+        <v>6287</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>6265</v>
+        <v>6288</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6266</v>
+        <v>6289</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>6267</v>
+        <v>6290</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6268</v>
+        <v>6291</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>6269</v>
+        <v>6292</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6270</v>
+        <v>6293</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>6271</v>
+        <v>6294</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6272</v>
+        <v>6295</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>6273</v>
+        <v>6296</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6274</v>
+        <v>6297</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>6275</v>
+        <v>6298</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>6276</v>
+        <v>6299</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>6277</v>
+        <v>6300</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>6278</v>
+        <v>6301</v>
       </c>
       <c r="C13" s="12"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="43" t="s">
-        <v>6279</v>
+        <v>6302</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>6280</v>
+        <v>6303</v>
       </c>
       <c r="C14" s="12"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="43" t="s">
-        <v>6281</v>
+        <v>6304</v>
       </c>
       <c r="B15" s="43" t="s">
         <v>3952</v>
@@ -62906,73 +63346,73 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6282</v>
+        <v>6305</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>6283</v>
+        <v>6306</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6284</v>
+        <v>6307</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>6285</v>
+        <v>6308</v>
       </c>
       <c r="C17" s="12"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>6286</v>
+        <v>6309</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>6287</v>
+        <v>6310</v>
       </c>
       <c r="C18" s="12"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6288</v>
+        <v>6311</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>6289</v>
+        <v>6312</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6290</v>
+        <v>6313</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>6291</v>
+        <v>6314</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6292</v>
+        <v>6315</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>6293</v>
+        <v>6316</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6294</v>
+        <v>6317</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>6295</v>
+        <v>6318</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>6296</v>
+        <v>6319</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>6297</v>
+        <v>6320</v>
       </c>
       <c r="C23" s="12"/>
     </row>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -18760,7 +18760,7 @@
     <t>ff</t>
   </si>
   <si>
-    <t>/hf/</t>
+    <t>/fː/</t>
   </si>
   <si>
     <t>g</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -18655,10 +18655,10 @@
     <t>a</t>
   </si>
   <si>
-    <t>/a/</t>
-  </si>
-  <si>
-    <t>/auː/</t>
+    <t>/ɑ/</t>
+  </si>
+  <si>
+    <t>/ɑuː/</t>
   </si>
   <si>
     <t>æ</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -3092,7 +3092,7 @@
     <t>finna kerski</t>
   </si>
   <si>
-    <t>to enjoy doing (with dative "who" + clause "doing what")</t>
+    <t>to enjoy doing something, to like doing something (with dative "who" + clause "doing what")</t>
   </si>
   <si>
     <t>fisk-hryggr</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -18562,7 +18562,7 @@
     <t>they are equal in strength / weight</t>
   </si>
   <si>
-    <t>þat hefsk sem hættuligt, segi jek</t>
+    <t>þat hefsk sem hættuligt, segja jek</t>
   </si>
   <si>
     <t>that looks dangerous, i think</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -13592,7 +13592,7 @@
     <t>to explain</t>
   </si>
   <si>
-    <t>þykkjask</t>
+    <t>þykkja</t>
   </si>
   <si>
     <t>to be known for, to be considered, to be regarded as (with sem + nominative)</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -5783,7 +5783,7 @@
     <t>inn-renna</t>
   </si>
   <si>
-    <t>to invade (intransitive or with accusative)</t>
+    <t>to invade (formal) (intransitive or with accusative)</t>
   </si>
   <si>
     <t>inni</t>
@@ -9134,7 +9134,7 @@
     <t>renna</t>
   </si>
   <si>
-    <t>to run (intransitive); to melt something (transitive)</t>
+    <t>to run (intransitive); to melt something (transitive); to run in, to rush into, to invade (intransitive or with inn + accusative)</t>
   </si>
   <si>
     <t>repsa</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -9134,7 +9134,7 @@
     <t>renna</t>
   </si>
   <si>
-    <t>to run (intransitive); to melt something (transitive); to run in, to rush into, to invade (intransitive or with inn + accusative)</t>
+    <t>to run, to sprint (intransitive); to melt something (transitive); to run into, to invade (intransitive or with inn + accusative)</t>
   </si>
   <si>
     <t>repsa</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10154" uniqueCount="6356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10154" uniqueCount="6357">
   <si>
     <t>Entry</t>
   </si>
@@ -15128,6 +15128,9 @@
   </si>
   <si>
     <t>eithvert</t>
+  </si>
+  <si>
+    <t>einhvern</t>
   </si>
   <si>
     <t>einhverja</t>
@@ -50851,10 +50854,10 @@
         <v>4549</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>5022</v>
+        <v>5024</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>5024</v>
+        <v>5025</v>
       </c>
       <c r="E23" s="9"/>
       <c r="F23" s="8" t="s">
@@ -50887,20 +50890,20 @@
         <v>4556</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>5025</v>
+        <v>5026</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>5026</v>
+        <v>5027</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>5027</v>
+        <v>5028</v>
       </c>
       <c r="E24" s="9"/>
       <c r="F24" s="8" t="s">
         <v>4538</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>5028</v>
+        <v>5029</v>
       </c>
       <c r="H24" s="10" t="s">
         <v>4974</v>
@@ -50915,10 +50918,10 @@
         <v>3291</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>5029</v>
+        <v>5030</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>5030</v>
+        <v>5031</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
@@ -50926,29 +50929,29 @@
         <v>4568</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>5031</v>
+        <v>5032</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>5032</v>
+        <v>5033</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>5033</v>
+        <v>5034</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="8" t="s">
         <v>4549</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>5034</v>
+        <v>5035</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>4549</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>5035</v>
+        <v>5036</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>5036</v>
+        <v>5037</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
@@ -50969,25 +50972,25 @@
         <v>4556</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>5037</v>
+        <v>5038</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>5038</v>
+        <v>5039</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>5039</v>
+        <v>5040</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>4556</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>5040</v>
+        <v>5041</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>5041</v>
+        <v>5042</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>5042</v>
+        <v>5043</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
@@ -50995,10 +50998,10 @@
         <v>4538</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>5043</v>
+        <v>5044</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>5032</v>
+        <v>5033</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>5022</v>
@@ -51008,25 +51011,25 @@
         <v>4568</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>5044</v>
+        <v>5045</v>
       </c>
       <c r="H27" s="10" t="s">
+        <v>5046</v>
+      </c>
+      <c r="I27" s="10" t="s">
         <v>5045</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>5044</v>
       </c>
       <c r="K27" s="8" t="s">
         <v>4568</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>5046</v>
+        <v>5047</v>
       </c>
       <c r="M27" s="10" t="s">
+        <v>5048</v>
+      </c>
+      <c r="N27" s="10" t="s">
         <v>5047</v>
-      </c>
-      <c r="N27" s="10" t="s">
-        <v>5046</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
@@ -51034,7 +51037,7 @@
         <v>4549</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>5024</v>
+        <v>5025</v>
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="8" t="s">
@@ -51067,17 +51070,17 @@
         <v>4556</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>5025</v>
+        <v>5026</v>
       </c>
       <c r="E29" s="9"/>
       <c r="F29" s="8" t="s">
         <v>4538</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>5048</v>
+        <v>5049</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>5045</v>
+        <v>5046</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>4974</v>
@@ -51086,13 +51089,13 @@
         <v>4538</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>5049</v>
+        <v>5050</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>5047</v>
+        <v>5048</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>5029</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1">
@@ -51100,20 +51103,20 @@
         <v>4568</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>5024</v>
+        <v>5025</v>
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="8" t="s">
         <v>4549</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>5050</v>
+        <v>5051</v>
       </c>
       <c r="K30" s="8" t="s">
         <v>4549</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>5036</v>
+        <v>5037</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
@@ -51122,13 +51125,13 @@
         <v>4556</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>5037</v>
+        <v>5038</v>
       </c>
       <c r="K31" s="8" t="s">
         <v>4556</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>5040</v>
+        <v>5041</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
@@ -51149,13 +51152,13 @@
         <v>4568</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>5050</v>
+        <v>5051</v>
       </c>
       <c r="K32" s="8" t="s">
         <v>4568</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>5036</v>
+        <v>5037</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
@@ -51166,10 +51169,10 @@
         <v>902</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>5051</v>
+        <v>5052</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>5052</v>
+        <v>5053</v>
       </c>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
@@ -51180,10 +51183,10 @@
         <v>4549</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>5053</v>
+        <v>5054</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>5054</v>
+        <v>5055</v>
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="8" t="s">
@@ -51204,13 +51207,13 @@
         <v>4556</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>5055</v>
+        <v>5056</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>5056</v>
+        <v>5057</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>5057</v>
+        <v>5058</v>
       </c>
       <c r="E35" s="9"/>
       <c r="F35" s="8" t="s">
@@ -51220,10 +51223,10 @@
         <v>273</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>5058</v>
+        <v>5059</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>5059</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1">
@@ -51231,20 +51234,20 @@
         <v>4556</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>5060</v>
+        <v>5061</v>
       </c>
       <c r="C36" s="10" t="s">
+        <v>5062</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>5061</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>5060</v>
       </c>
       <c r="E36" s="9"/>
       <c r="F36" s="8" t="s">
         <v>4549</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>5062</v>
+        <v>5063</v>
       </c>
     </row>
     <row r="37" ht="18.75" customHeight="1">
@@ -51265,7 +51268,7 @@
         <v>4556</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>5063</v>
+        <v>5064</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
@@ -51273,20 +51276,20 @@
         <v>4538</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>5064</v>
+        <v>5065</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>5061</v>
+        <v>5062</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>5051</v>
+        <v>5052</v>
       </c>
       <c r="E38" s="9"/>
       <c r="F38" s="8" t="s">
         <v>4568</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>5062</v>
+        <v>5063</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
@@ -51294,7 +51297,7 @@
         <v>4549</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>5054</v>
+        <v>5055</v>
       </c>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
@@ -51305,7 +51308,7 @@
         <v>4556</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>5055</v>
+        <v>5056</v>
       </c>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
@@ -51316,7 +51319,7 @@
         <v>4568</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>5054</v>
+        <v>5055</v>
       </c>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
@@ -51395,14 +51398,14 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>5065</v>
+        <v>5066</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>5066</v>
+        <v>5067</v>
       </c>
       <c r="H1" s="12"/>
       <c r="I1" s="8" t="s">
-        <v>5067</v>
+        <v>5068</v>
       </c>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
@@ -51416,7 +51419,7 @@
       </c>
       <c r="H2" s="12"/>
       <c r="I2" s="8" t="s">
-        <v>5068</v>
+        <v>5069</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>4993</v>
@@ -51432,7 +51435,7 @@
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>5068</v>
+        <v>5069</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>4993</v>
@@ -51457,13 +51460,13 @@
         <v>4538</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>5069</v>
+        <v>5070</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>5070</v>
+        <v>5071</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>5071</v>
+        <v>5072</v>
       </c>
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
@@ -51476,26 +51479,26 @@
         <v>3045</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>5072</v>
+        <v>5073</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>5073</v>
+        <v>5074</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>5074</v>
+        <v>5075</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>5075</v>
+        <v>5076</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>5075</v>
+        <v>5076</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="8" t="s">
         <v>4549</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>5076</v>
+        <v>5077</v>
       </c>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
@@ -51505,29 +51508,29 @@
         <v>4549</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>5077</v>
+        <v>5078</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>5075</v>
+        <v>5076</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>5075</v>
+        <v>5076</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>5078</v>
+        <v>5079</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="8" t="s">
         <v>4556</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>5079</v>
+        <v>5080</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>5080</v>
+        <v>5081</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>5081</v>
+        <v>5082</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
@@ -51537,26 +51540,26 @@
         <v>4556</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>5082</v>
+        <v>5083</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>5074</v>
+        <v>5075</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>5078</v>
+        <v>5079</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="8" t="s">
         <v>4568</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>5083</v>
+        <v>5084</v>
       </c>
       <c r="K6" s="10" t="s">
+        <v>5085</v>
+      </c>
+      <c r="L6" s="10" t="s">
         <v>5084</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>5083</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
@@ -51566,13 +51569,13 @@
         <v>4568</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>5085</v>
+        <v>5086</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>5087</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>5086</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>5085</v>
       </c>
       <c r="H7" s="12"/>
       <c r="M7" s="10"/>
@@ -51580,7 +51583,7 @@
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>5087</v>
+        <v>5088</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>4993</v>
@@ -51613,16 +51616,16 @@
         <v>4538</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>5088</v>
+        <v>5089</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>5086</v>
+        <v>5087</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>5072</v>
+        <v>5073</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>5078</v>
+        <v>5079</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -51637,7 +51640,7 @@
         <v>4549</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>5075</v>
+        <v>5076</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
@@ -51652,7 +51655,7 @@
         <v>4556</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>5082</v>
+        <v>5083</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
@@ -51667,7 +51670,7 @@
         <v>4568</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>5075</v>
+        <v>5076</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
@@ -51679,7 +51682,7 @@
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>5089</v>
+        <v>5090</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>4993</v>
@@ -51712,22 +51715,22 @@
         <v>4538</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>5090</v>
+        <v>5091</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>5091</v>
+        <v>5092</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>5092</v>
+        <v>5093</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>5093</v>
+        <v>5094</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>5094</v>
+        <v>5095</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>5094</v>
+        <v>5095</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
@@ -51742,16 +51745,16 @@
         <v>4549</v>
       </c>
       <c r="B15" s="10" t="s">
+        <v>5096</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>5095</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>5094</v>
-      </c>
       <c r="E15" s="10" t="s">
-        <v>5094</v>
+        <v>5095</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>5096</v>
+        <v>5097</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
@@ -51766,13 +51769,13 @@
         <v>4556</v>
       </c>
       <c r="B16" s="10" t="s">
+        <v>5098</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>5094</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>5097</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>5093</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>5096</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
@@ -51787,13 +51790,13 @@
         <v>4568</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>5098</v>
+        <v>5099</v>
       </c>
       <c r="C17" s="10" t="s">
+        <v>5100</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>5099</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>5098</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
@@ -51805,7 +51808,7 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>5100</v>
+        <v>5101</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>4993</v>
@@ -51838,16 +51841,16 @@
         <v>4538</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>5101</v>
+        <v>5102</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>5099</v>
+        <v>5100</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>5091</v>
+        <v>5092</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>5096</v>
+        <v>5097</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
@@ -51862,7 +51865,7 @@
         <v>4549</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>5094</v>
+        <v>5095</v>
       </c>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
@@ -51877,7 +51880,7 @@
         <v>4556</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>5097</v>
+        <v>5098</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
@@ -51892,7 +51895,7 @@
         <v>4568</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>5094</v>
+        <v>5095</v>
       </c>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
@@ -51904,7 +51907,7 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="8" t="s">
-        <v>5102</v>
+        <v>5103</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>4993</v>
@@ -51929,13 +51932,13 @@
         <v>4538</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>5103</v>
+        <v>5104</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>5104</v>
+        <v>5105</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>5104</v>
+        <v>5105</v>
       </c>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
@@ -51947,13 +51950,13 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="8" t="s">
+        <v>5106</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>5105</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>5104</v>
-      </c>
       <c r="C25" s="10" t="s">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -51965,7 +51968,7 @@
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="8" t="s">
-        <v>5107</v>
+        <v>5108</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>4993</v>
@@ -51986,10 +51989,10 @@
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="8" t="s">
-        <v>5108</v>
+        <v>5109</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -52017,24 +52020,24 @@
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>5065</v>
+        <v>5066</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>5109</v>
+        <v>5110</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="8" t="s">
-        <v>5065</v>
+        <v>5066</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>5110</v>
+        <v>5111</v>
       </c>
       <c r="J29" s="9"/>
       <c r="K29" s="14" t="s">
-        <v>5065</v>
+        <v>5066</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>5111</v>
+        <v>5112</v>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1">
@@ -52085,10 +52088,10 @@
         <v>1976</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>5112</v>
+        <v>5113</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>5113</v>
+        <v>5114</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="8" t="s">
@@ -52098,10 +52101,10 @@
         <v>3507</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>5114</v>
+        <v>5115</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>5115</v>
+        <v>5116</v>
       </c>
       <c r="J31" s="9"/>
       <c r="K31" s="14" t="s">
@@ -52111,10 +52114,10 @@
         <v>3443</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>5116</v>
+        <v>5117</v>
       </c>
       <c r="N31" s="16" t="s">
-        <v>5117</v>
+        <v>5118</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
@@ -52122,30 +52125,30 @@
         <v>4549</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>5118</v>
+        <v>5119</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>5119</v>
+        <v>5120</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="8" t="s">
         <v>4549</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>5120</v>
+        <v>5121</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>5121</v>
+        <v>5122</v>
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="14" t="s">
         <v>4549</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>5122</v>
+        <v>5123</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>5123</v>
+        <v>5124</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
@@ -52153,39 +52156,39 @@
         <v>4556</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>5124</v>
+        <v>5125</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>5125</v>
+        <v>5126</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>5126</v>
+        <v>5127</v>
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="8" t="s">
         <v>4556</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>5127</v>
+        <v>5128</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>5128</v>
+        <v>5129</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>5129</v>
+        <v>5130</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="14" t="s">
         <v>4556</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>5130</v>
+        <v>5131</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>5131</v>
+        <v>5132</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>5132</v>
+        <v>5133</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
@@ -52193,39 +52196,39 @@
         <v>4568</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>5133</v>
+        <v>5134</v>
       </c>
       <c r="C34" s="10" t="s">
+        <v>5135</v>
+      </c>
+      <c r="D34" s="10" t="s">
         <v>5134</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>5133</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="8" t="s">
         <v>4568</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>5135</v>
+        <v>5136</v>
       </c>
       <c r="H34" s="10" t="s">
+        <v>5137</v>
+      </c>
+      <c r="I34" s="10" t="s">
         <v>5136</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>5135</v>
       </c>
       <c r="J34" s="9"/>
       <c r="K34" s="14" t="s">
         <v>4568</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>5137</v>
+        <v>5138</v>
       </c>
       <c r="M34" s="16" t="s">
+        <v>5139</v>
+      </c>
+      <c r="N34" s="16" t="s">
         <v>5138</v>
-      </c>
-      <c r="N34" s="16" t="s">
-        <v>5137</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
@@ -52273,39 +52276,39 @@
         <v>4538</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>5139</v>
+        <v>5140</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>5134</v>
+        <v>5135</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>5112</v>
+        <v>5113</v>
       </c>
       <c r="E36" s="12"/>
       <c r="F36" s="8" t="s">
         <v>4538</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>5140</v>
+        <v>5141</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>5136</v>
+        <v>5137</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>5114</v>
+        <v>5115</v>
       </c>
       <c r="J36" s="9"/>
       <c r="K36" s="14" t="s">
         <v>4538</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>5141</v>
+        <v>5142</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>5123</v>
+        <v>5124</v>
       </c>
       <c r="N36" s="16" t="s">
-        <v>5116</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="37" ht="18.75" customHeight="1">
@@ -52313,21 +52316,21 @@
         <v>4549</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>5119</v>
+        <v>5120</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="8" t="s">
         <v>4549</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>5121</v>
+        <v>5122</v>
       </c>
       <c r="J37" s="10"/>
       <c r="K37" s="17" t="s">
         <v>4549</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>5123</v>
+        <v>5124</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
@@ -52335,21 +52338,21 @@
         <v>4556</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>5124</v>
+        <v>5125</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="8" t="s">
         <v>4556</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>5127</v>
+        <v>5128</v>
       </c>
       <c r="J38" s="10"/>
       <c r="K38" s="17" t="s">
         <v>4556</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>5130</v>
+        <v>5131</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
@@ -52357,61 +52360,61 @@
         <v>4568</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>5119</v>
+        <v>5120</v>
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="8" t="s">
         <v>4568</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>5121</v>
+        <v>5122</v>
       </c>
       <c r="J39" s="10"/>
       <c r="K39" s="17" t="s">
         <v>4568</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>5123</v>
+        <v>5124</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>5142</v>
+        <v>5143</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>5143</v>
+        <v>5144</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>5144</v>
+        <v>5145</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>5145</v>
+        <v>5146</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="8" t="s">
-        <v>5142</v>
+        <v>5143</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>3503</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>5144</v>
+        <v>5145</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>5146</v>
+        <v>5147</v>
       </c>
       <c r="J40" s="10"/>
       <c r="K40" s="8" t="s">
-        <v>5142</v>
+        <v>5143</v>
       </c>
       <c r="L40" s="10" t="s">
-        <v>5147</v>
+        <v>5148</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>5144</v>
+        <v>5145</v>
       </c>
       <c r="N40" s="10" t="s">
-        <v>5148</v>
+        <v>5149</v>
       </c>
     </row>
     <row r="41" ht="18.75" customHeight="1">
@@ -52432,10 +52435,10 @@
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="8" t="s">
-        <v>5149</v>
+        <v>5150</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>5150</v>
+        <v>5151</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="9"/>
@@ -52480,10 +52483,10 @@
         <v>989</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>5151</v>
+        <v>5152</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>5152</v>
+        <v>5153</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="9"/>
@@ -52501,7 +52504,7 @@
         <v>4549</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>5153</v>
+        <v>5154</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="9"/>
@@ -52519,13 +52522,13 @@
         <v>4556</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>5154</v>
+        <v>5155</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>5155</v>
+        <v>5156</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>5156</v>
+        <v>5157</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="9"/>
@@ -52543,13 +52546,13 @@
         <v>4568</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>5157</v>
+        <v>5158</v>
       </c>
       <c r="C47" s="10" t="s">
+        <v>5159</v>
+      </c>
+      <c r="D47" s="10" t="s">
         <v>5158</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>5157</v>
       </c>
       <c r="E47" s="12"/>
       <c r="F47" s="9"/>
@@ -52591,13 +52594,13 @@
         <v>4538</v>
       </c>
       <c r="B49" s="10" t="s">
+        <v>5160</v>
+      </c>
+      <c r="C49" s="10" t="s">
         <v>5159</v>
       </c>
-      <c r="C49" s="10" t="s">
-        <v>5158</v>
-      </c>
       <c r="D49" s="10" t="s">
-        <v>5151</v>
+        <v>5152</v>
       </c>
       <c r="E49" s="12"/>
       <c r="F49" s="9"/>
@@ -52615,7 +52618,7 @@
         <v>4549</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>5153</v>
+        <v>5154</v>
       </c>
       <c r="E50" s="12"/>
       <c r="F50" s="9"/>
@@ -52633,7 +52636,7 @@
         <v>4556</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>5154</v>
+        <v>5155</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="9"/>
@@ -52651,7 +52654,7 @@
         <v>4568</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>5153</v>
+        <v>5154</v>
       </c>
       <c r="E52" s="12"/>
       <c r="F52" s="9"/>
@@ -52666,16 +52669,16 @@
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>5142</v>
+        <v>5143</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>5160</v>
+        <v>5161</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>5144</v>
+        <v>5145</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>5161</v>
+        <v>5162</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="9"/>
@@ -52706,10 +52709,10 @@
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" s="8" t="s">
-        <v>5162</v>
+        <v>5163</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>5163</v>
+        <v>5164</v>
       </c>
       <c r="E55" s="12"/>
       <c r="F55" s="9"/>
@@ -52757,7 +52760,7 @@
         <v>1104</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>5164</v>
+        <v>5165</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="9"/>
@@ -52775,10 +52778,10 @@
         <v>4549</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>5165</v>
+        <v>5166</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>5166</v>
+        <v>5167</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="9"/>
@@ -52796,13 +52799,13 @@
         <v>4556</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>5167</v>
+        <v>5168</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>5168</v>
+        <v>5169</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>5169</v>
+        <v>5170</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="9"/>
@@ -52820,13 +52823,13 @@
         <v>4568</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>5170</v>
+        <v>5171</v>
       </c>
       <c r="C60" s="10" t="s">
+        <v>5172</v>
+      </c>
+      <c r="D60" s="10" t="s">
         <v>5171</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>5170</v>
       </c>
       <c r="E60" s="12"/>
       <c r="F60" s="9"/>
@@ -52868,10 +52871,10 @@
         <v>4538</v>
       </c>
       <c r="B62" s="10" t="s">
+        <v>5173</v>
+      </c>
+      <c r="C62" s="10" t="s">
         <v>5172</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>5171</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>1104</v>
@@ -52892,7 +52895,7 @@
         <v>4549</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>5166</v>
+        <v>5167</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="9"/>
@@ -52910,7 +52913,7 @@
         <v>4556</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>5167</v>
+        <v>5168</v>
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="9"/>
@@ -52928,7 +52931,7 @@
         <v>4568</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>5166</v>
+        <v>5167</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="9"/>
@@ -52943,16 +52946,16 @@
     </row>
     <row r="66" ht="18.75" customHeight="1">
       <c r="A66" s="8" t="s">
-        <v>5142</v>
+        <v>5143</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>5173</v>
+        <v>5174</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>5144</v>
+        <v>5145</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>5174</v>
+        <v>5175</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="9"/>
@@ -52983,10 +52986,10 @@
     </row>
     <row r="68" ht="18.75" customHeight="1">
       <c r="A68" s="8" t="s">
-        <v>5175</v>
+        <v>5176</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="9"/>
@@ -53031,10 +53034,10 @@
         <v>3216</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>5177</v>
+        <v>5178</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>5178</v>
+        <v>5179</v>
       </c>
       <c r="E70" s="12"/>
       <c r="F70" s="9"/>
@@ -53052,10 +53055,10 @@
         <v>4549</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>5179</v>
+        <v>5180</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>5180</v>
+        <v>5181</v>
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="9"/>
@@ -53073,13 +53076,13 @@
         <v>4556</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>5182</v>
+        <v>5183</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>5183</v>
+        <v>5184</v>
       </c>
       <c r="E72" s="12"/>
       <c r="F72" s="9"/>
@@ -53097,13 +53100,13 @@
         <v>4568</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>5184</v>
+        <v>5185</v>
       </c>
       <c r="C73" s="10" t="s">
+        <v>5186</v>
+      </c>
+      <c r="D73" s="10" t="s">
         <v>5185</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>5184</v>
       </c>
       <c r="E73" s="12"/>
       <c r="F73" s="9"/>
@@ -53145,13 +53148,13 @@
         <v>4538</v>
       </c>
       <c r="B75" s="10" t="s">
+        <v>5187</v>
+      </c>
+      <c r="C75" s="10" t="s">
         <v>5186</v>
       </c>
-      <c r="C75" s="10" t="s">
-        <v>5185</v>
-      </c>
       <c r="D75" s="10" t="s">
-        <v>5177</v>
+        <v>5178</v>
       </c>
       <c r="E75" s="12"/>
       <c r="F75" s="9"/>
@@ -53169,7 +53172,7 @@
         <v>4549</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>5180</v>
+        <v>5181</v>
       </c>
       <c r="E76" s="12"/>
       <c r="F76" s="9"/>
@@ -53187,7 +53190,7 @@
         <v>4556</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="E77" s="12"/>
       <c r="F77" s="9"/>
@@ -53205,7 +53208,7 @@
         <v>4568</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>5180</v>
+        <v>5181</v>
       </c>
       <c r="E78" s="12"/>
       <c r="F78" s="9"/>
@@ -53220,16 +53223,16 @@
     </row>
     <row r="79" ht="18.75" customHeight="1">
       <c r="A79" s="8" t="s">
-        <v>5142</v>
+        <v>5143</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>5187</v>
+        <v>5188</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>5144</v>
+        <v>5145</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>5188</v>
+        <v>5189</v>
       </c>
       <c r="E79" s="12"/>
       <c r="F79" s="9"/>
@@ -53326,10 +53329,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>5189</v>
+        <v>5190</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>5190</v>
+        <v>5191</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -53344,7 +53347,7 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="8" t="s">
-        <v>5191</v>
+        <v>5192</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>2827</v>
@@ -53362,7 +53365,7 @@
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>5142</v>
+        <v>5143</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>2829</v>
@@ -53380,7 +53383,7 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="8" t="s">
-        <v>5144</v>
+        <v>5145</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>2831</v>
@@ -53412,13 +53415,13 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>5192</v>
+        <v>5193</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>5193</v>
+        <v>5194</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>5194</v>
+        <v>5195</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -53432,7 +53435,7 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>5191</v>
+        <v>5192</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>2714</v>
@@ -53450,7 +53453,7 @@
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>5142</v>
+        <v>5143</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>2676</v>
@@ -53470,7 +53473,7 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>5144</v>
+        <v>5145</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>2678</v>
@@ -53637,27 +53640,27 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="18" t="s">
-        <v>5195</v>
+        <v>5196</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="20" t="s">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D1" s="19"/>
       <c r="E1" s="18" t="s">
-        <v>5197</v>
+        <v>5198</v>
       </c>
       <c r="F1" s="19"/>
       <c r="G1" s="18" t="s">
-        <v>5198</v>
+        <v>5199</v>
       </c>
       <c r="H1" s="19"/>
       <c r="I1" s="18" t="s">
-        <v>5199</v>
+        <v>5200</v>
       </c>
       <c r="J1" s="19"/>
       <c r="K1" s="18" t="s">
-        <v>5200</v>
+        <v>5201</v>
       </c>
       <c r="L1" s="19"/>
       <c r="M1" s="10"/>
@@ -53670,27 +53673,27 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="21" t="s">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="10" t="s">
-        <v>5202</v>
+        <v>5203</v>
       </c>
       <c r="D2" s="22"/>
       <c r="E2" s="23" t="s">
-        <v>5203</v>
+        <v>5204</v>
       </c>
       <c r="F2" s="22"/>
       <c r="G2" s="23" t="s">
-        <v>5204</v>
+        <v>5205</v>
       </c>
       <c r="H2" s="22"/>
       <c r="I2" s="23" t="s">
-        <v>5205</v>
+        <v>5206</v>
       </c>
       <c r="J2" s="22"/>
       <c r="K2" s="23" t="s">
-        <v>5206</v>
+        <v>5207</v>
       </c>
       <c r="L2" s="22"/>
       <c r="M2" s="10"/>
@@ -53703,27 +53706,27 @@
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="21" t="s">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="10" t="s">
-        <v>5208</v>
+        <v>5209</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" s="23" t="s">
-        <v>5209</v>
+        <v>5210</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="23" t="s">
-        <v>5210</v>
+        <v>5211</v>
       </c>
       <c r="H3" s="22"/>
       <c r="I3" s="23" t="s">
-        <v>5211</v>
+        <v>5212</v>
       </c>
       <c r="J3" s="22"/>
       <c r="K3" s="23" t="s">
-        <v>5212</v>
+        <v>5213</v>
       </c>
       <c r="L3" s="22"/>
       <c r="M3" s="10"/>
@@ -53736,27 +53739,27 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="21" t="s">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="10" t="s">
-        <v>5214</v>
+        <v>5215</v>
       </c>
       <c r="D4" s="22"/>
       <c r="E4" s="23" t="s">
-        <v>5215</v>
+        <v>5216</v>
       </c>
       <c r="F4" s="22"/>
       <c r="G4" s="23" t="s">
-        <v>5216</v>
+        <v>5217</v>
       </c>
       <c r="H4" s="22"/>
       <c r="I4" s="23" t="s">
-        <v>5217</v>
+        <v>5218</v>
       </c>
       <c r="J4" s="22"/>
       <c r="K4" s="23" t="s">
-        <v>5218</v>
+        <v>5219</v>
       </c>
       <c r="L4" s="22"/>
       <c r="M4" s="10"/>
@@ -53769,38 +53772,38 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="8" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D5" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="F5" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="G5" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="G5" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="H5" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="I5" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="I5" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="J5" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="K5" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="K5" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="L5" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
@@ -53815,37 +53818,37 @@
         <v>4955</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>864</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>5223</v>
+        <v>5224</v>
       </c>
       <c r="E6" s="23" t="s">
         <v>1206</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>5224</v>
+        <v>5225</v>
       </c>
       <c r="G6" s="23" t="s">
         <v>2071</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>5225</v>
+        <v>5226</v>
       </c>
       <c r="I6" s="23" t="s">
         <v>3437</v>
       </c>
       <c r="J6" s="25" t="s">
-        <v>5226</v>
+        <v>5227</v>
       </c>
       <c r="K6" s="23" t="s">
         <v>3689</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>5227</v>
+        <v>5228</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
@@ -53861,34 +53864,34 @@
         <v>4492</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>5228</v>
+        <v>5229</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>5229</v>
+        <v>5230</v>
       </c>
       <c r="E7" s="23" t="s">
         <v>4911</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>5230</v>
+        <v>5231</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>5231</v>
+        <v>5232</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>5232</v>
+        <v>5233</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>5233</v>
+        <v>5234</v>
       </c>
       <c r="J7" s="25" t="s">
-        <v>5234</v>
+        <v>5235</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>5235</v>
+        <v>5236</v>
       </c>
       <c r="L7" s="25" t="s">
-        <v>5236</v>
+        <v>5237</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
@@ -53901,37 +53904,37 @@
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="26"/>
       <c r="B8" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>5228</v>
+        <v>5229</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>5238</v>
+        <v>5239</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>4911</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>5239</v>
+        <v>5240</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>5231</v>
+        <v>5232</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>5240</v>
+        <v>5241</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>5233</v>
+        <v>5234</v>
       </c>
       <c r="J8" s="25" t="s">
-        <v>5241</v>
+        <v>5242</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>5235</v>
+        <v>5236</v>
       </c>
       <c r="L8" s="25" t="s">
-        <v>5242</v>
+        <v>5243</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
@@ -53949,34 +53952,34 @@
         <v>4317</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>5243</v>
+        <v>5244</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>5244</v>
+        <v>5245</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>4925</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>5245</v>
+        <v>5246</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>5246</v>
+        <v>5247</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>5247</v>
+        <v>5248</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>5248</v>
+        <v>5249</v>
       </c>
       <c r="J9" s="25" t="s">
-        <v>5249</v>
+        <v>5250</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>5250</v>
+        <v>5251</v>
       </c>
       <c r="L9" s="25" t="s">
-        <v>5251</v>
+        <v>5252</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
@@ -53992,34 +53995,34 @@
         <v>4442</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>5252</v>
+        <v>5253</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>5253</v>
+        <v>5254</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>5254</v>
+        <v>5255</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>5255</v>
+        <v>5256</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>5256</v>
+        <v>5257</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>5257</v>
+        <v>5258</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>5258</v>
+        <v>5259</v>
       </c>
       <c r="J10" s="25" t="s">
-        <v>5259</v>
+        <v>5260</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>5260</v>
+        <v>5261</v>
       </c>
       <c r="L10" s="25" t="s">
-        <v>5261</v>
+        <v>5262</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
@@ -54032,37 +54035,37 @@
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="26"/>
       <c r="B11" s="24" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>5263</v>
+        <v>5264</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>5264</v>
+        <v>5265</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>5265</v>
+        <v>5266</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>5266</v>
+        <v>5267</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>5267</v>
+        <v>5268</v>
       </c>
       <c r="H11" s="25" t="s">
-        <v>5268</v>
+        <v>5269</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>5269</v>
+        <v>5270</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>5270</v>
+        <v>5271</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>5271</v>
+        <v>5272</v>
       </c>
       <c r="L11" s="28" t="s">
-        <v>5272</v>
+        <v>5273</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
@@ -54074,14 +54077,14 @@
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="21" t="s">
-        <v>5273</v>
+        <v>5274</v>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="8" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="E12" s="29"/>
       <c r="F12" s="30"/>
@@ -54104,13 +54107,13 @@
         <v>4955</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>5274</v>
+        <v>5275</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>5275</v>
+        <v>5276</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="10"/>
@@ -54154,7 +54157,7 @@
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="26"/>
       <c r="B15" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C15" s="26"/>
       <c r="D15" s="22"/>
@@ -54182,10 +54185,10 @@
         <v>4317</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>5276</v>
+        <v>5277</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>5277</v>
+        <v>5278</v>
       </c>
       <c r="E16" s="23"/>
       <c r="F16" s="10"/>
@@ -54209,10 +54212,10 @@
         <v>4442</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>5278</v>
+        <v>5279</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>5279</v>
+        <v>5280</v>
       </c>
       <c r="E17" s="23"/>
       <c r="F17" s="10"/>
@@ -54233,7 +54236,7 @@
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="31"/>
       <c r="B18" s="32" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C18" s="33"/>
       <c r="D18" s="34"/>
@@ -54276,27 +54279,27 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>5280</v>
+        <v>5281</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="20" t="s">
-        <v>5281</v>
+        <v>5282</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="18" t="s">
-        <v>5282</v>
+        <v>5283</v>
       </c>
       <c r="F20" s="19"/>
       <c r="G20" s="18" t="s">
-        <v>5283</v>
+        <v>5284</v>
       </c>
       <c r="H20" s="19"/>
       <c r="I20" s="18" t="s">
-        <v>5284</v>
+        <v>5285</v>
       </c>
       <c r="J20" s="19"/>
       <c r="K20" s="18" t="s">
-        <v>5285</v>
+        <v>5286</v>
       </c>
       <c r="L20" s="19"/>
       <c r="M20" s="10"/>
@@ -54309,27 +54312,27 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="21" t="s">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="10" t="s">
-        <v>5286</v>
+        <v>5287</v>
       </c>
       <c r="D21" s="22"/>
       <c r="E21" s="23" t="s">
-        <v>5287</v>
+        <v>5288</v>
       </c>
       <c r="F21" s="22"/>
       <c r="G21" s="23" t="s">
-        <v>5288</v>
+        <v>5289</v>
       </c>
       <c r="H21" s="22"/>
       <c r="I21" s="23" t="s">
-        <v>5289</v>
+        <v>5290</v>
       </c>
       <c r="J21" s="22"/>
       <c r="K21" s="23" t="s">
-        <v>5290</v>
+        <v>5291</v>
       </c>
       <c r="L21" s="22"/>
       <c r="M21" s="10"/>
@@ -54342,27 +54345,27 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="21" t="s">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="10" t="s">
-        <v>5291</v>
+        <v>5292</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="23" t="s">
-        <v>5292</v>
+        <v>5293</v>
       </c>
       <c r="F22" s="22"/>
       <c r="G22" s="23" t="s">
-        <v>5293</v>
+        <v>5294</v>
       </c>
       <c r="H22" s="22"/>
       <c r="I22" s="23" t="s">
-        <v>5294</v>
+        <v>5295</v>
       </c>
       <c r="J22" s="22"/>
       <c r="K22" s="23" t="s">
-        <v>5295</v>
+        <v>5296</v>
       </c>
       <c r="L22" s="22"/>
       <c r="M22" s="10"/>
@@ -54375,27 +54378,27 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="10" t="s">
-        <v>5296</v>
+        <v>5297</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="23" t="s">
-        <v>5297</v>
+        <v>5298</v>
       </c>
       <c r="F23" s="22"/>
       <c r="G23" s="23" t="s">
-        <v>5298</v>
+        <v>5299</v>
       </c>
       <c r="H23" s="22"/>
       <c r="I23" s="23" t="s">
-        <v>5299</v>
+        <v>5300</v>
       </c>
       <c r="J23" s="22"/>
       <c r="K23" s="23" t="s">
-        <v>5300</v>
+        <v>5301</v>
       </c>
       <c r="L23" s="22"/>
       <c r="M23" s="10"/>
@@ -54408,38 +54411,38 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="8" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D24" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="E24" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="E24" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="F24" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="G24" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="G24" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="H24" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="I24" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="I24" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="J24" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="K24" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="K24" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="L24" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
@@ -54454,37 +54457,37 @@
         <v>4955</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>5301</v>
+        <v>5302</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>5302</v>
+        <v>5303</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>5303</v>
+        <v>5304</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>5304</v>
+        <v>5305</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>5305</v>
+        <v>5306</v>
       </c>
       <c r="H25" s="25" t="s">
-        <v>5306</v>
+        <v>5307</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>5307</v>
+        <v>5308</v>
       </c>
       <c r="J25" s="25" t="s">
-        <v>5308</v>
+        <v>5309</v>
       </c>
       <c r="K25" s="23" t="s">
-        <v>5309</v>
+        <v>5310</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>5310</v>
+        <v>5311</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
@@ -54500,34 +54503,34 @@
         <v>4492</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>5311</v>
+        <v>5312</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>5312</v>
+        <v>5313</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>5313</v>
+        <v>5314</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>5314</v>
+        <v>5315</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>5315</v>
+        <v>5316</v>
       </c>
       <c r="H26" s="25" t="s">
-        <v>5316</v>
+        <v>5317</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>5317</v>
+        <v>5318</v>
       </c>
       <c r="J26" s="25" t="s">
-        <v>5318</v>
+        <v>5319</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>5319</v>
+        <v>5320</v>
       </c>
       <c r="L26" s="25" t="s">
-        <v>5320</v>
+        <v>5321</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10"/>
@@ -54540,37 +54543,37 @@
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="26"/>
       <c r="B27" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>5311</v>
+        <v>5312</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>5321</v>
+        <v>5322</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>5313</v>
+        <v>5314</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>5322</v>
+        <v>5323</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>5315</v>
+        <v>5316</v>
       </c>
       <c r="H27" s="25" t="s">
-        <v>5323</v>
+        <v>5324</v>
       </c>
       <c r="I27" s="23" t="s">
-        <v>5317</v>
+        <v>5318</v>
       </c>
       <c r="J27" s="25" t="s">
-        <v>5324</v>
+        <v>5325</v>
       </c>
       <c r="K27" s="23" t="s">
-        <v>5319</v>
+        <v>5320</v>
       </c>
       <c r="L27" s="25" t="s">
-        <v>5325</v>
+        <v>5326</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
@@ -54588,34 +54591,34 @@
         <v>4317</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>5326</v>
+        <v>5327</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>5327</v>
+        <v>5328</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>5328</v>
+        <v>5329</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>5329</v>
+        <v>5330</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>5330</v>
+        <v>5331</v>
       </c>
       <c r="H28" s="25" t="s">
-        <v>5331</v>
+        <v>5332</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>5332</v>
+        <v>5333</v>
       </c>
       <c r="J28" s="25" t="s">
-        <v>5333</v>
+        <v>5334</v>
       </c>
       <c r="K28" s="23" t="s">
-        <v>5334</v>
+        <v>5335</v>
       </c>
       <c r="L28" s="25" t="s">
-        <v>5335</v>
+        <v>5336</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
@@ -54630,34 +54633,34 @@
         <v>4442</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>5336</v>
+        <v>5337</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>5337</v>
+        <v>5338</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>5338</v>
+        <v>5339</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>5339</v>
+        <v>5340</v>
       </c>
       <c r="G29" s="23" t="s">
-        <v>5340</v>
+        <v>5341</v>
       </c>
       <c r="H29" s="25" t="s">
-        <v>5341</v>
+        <v>5342</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>5342</v>
+        <v>5343</v>
       </c>
       <c r="J29" s="25" t="s">
-        <v>5343</v>
+        <v>5344</v>
       </c>
       <c r="K29" s="23" t="s">
-        <v>5344</v>
+        <v>5345</v>
       </c>
       <c r="L29" s="25" t="s">
-        <v>5345</v>
+        <v>5346</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
@@ -54669,37 +54672,37 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="B30" s="24" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>5346</v>
+        <v>5347</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>5347</v>
+        <v>5348</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>5348</v>
+        <v>5349</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>5349</v>
+        <v>5350</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>5350</v>
+        <v>5351</v>
       </c>
       <c r="H30" s="25" t="s">
-        <v>5351</v>
+        <v>5352</v>
       </c>
       <c r="I30" s="23" t="s">
-        <v>5352</v>
+        <v>5353</v>
       </c>
       <c r="J30" s="25" t="s">
-        <v>5353</v>
+        <v>5354</v>
       </c>
       <c r="K30" s="23" t="s">
-        <v>5354</v>
+        <v>5355</v>
       </c>
       <c r="L30" s="25" t="s">
-        <v>5355</v>
+        <v>5356</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
@@ -54711,7 +54714,7 @@
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="21" t="s">
-        <v>5273</v>
+        <v>5274</v>
       </c>
       <c r="B31" s="22"/>
       <c r="C31" s="29"/>
@@ -54723,10 +54726,10 @@
       <c r="I31" s="30"/>
       <c r="J31" s="35"/>
       <c r="K31" s="8" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="L31" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
@@ -54741,7 +54744,7 @@
         <v>4955</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C32" s="23"/>
       <c r="D32" s="10"/>
@@ -54752,10 +54755,10 @@
       <c r="I32" s="10"/>
       <c r="J32" s="25"/>
       <c r="K32" s="10" t="s">
-        <v>5356</v>
+        <v>5357</v>
       </c>
       <c r="L32" s="25" t="s">
-        <v>5357</v>
+        <v>5358</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
@@ -54790,7 +54793,7 @@
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="26"/>
       <c r="B34" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C34" s="23"/>
       <c r="D34" s="10"/>
@@ -54825,10 +54828,10 @@
       <c r="I35" s="10"/>
       <c r="J35" s="25"/>
       <c r="K35" s="10" t="s">
-        <v>5358</v>
+        <v>5359</v>
       </c>
       <c r="L35" s="25" t="s">
-        <v>5359</v>
+        <v>5360</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
@@ -54852,10 +54855,10 @@
       <c r="I36" s="10"/>
       <c r="J36" s="25"/>
       <c r="K36" s="10" t="s">
-        <v>5360</v>
+        <v>5361</v>
       </c>
       <c r="L36" s="25" t="s">
-        <v>5361</v>
+        <v>5362</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10"/>
@@ -54868,7 +54871,7 @@
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="31"/>
       <c r="B37" s="32" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C37" s="23"/>
       <c r="D37" s="10"/>
@@ -54913,19 +54916,19 @@
       <c r="A39" s="10"/>
       <c r="B39" s="10"/>
       <c r="C39" s="18" t="s">
-        <v>5362</v>
+        <v>5363</v>
       </c>
       <c r="D39" s="19"/>
       <c r="E39" s="18" t="s">
-        <v>5363</v>
+        <v>5364</v>
       </c>
       <c r="F39" s="19"/>
       <c r="G39" s="18" t="s">
-        <v>5364</v>
+        <v>5365</v>
       </c>
       <c r="H39" s="19"/>
       <c r="I39" s="18" t="s">
-        <v>5365</v>
+        <v>5366</v>
       </c>
       <c r="J39" s="19"/>
       <c r="K39" s="10"/>
@@ -54942,19 +54945,19 @@
       <c r="A40" s="10"/>
       <c r="B40" s="10"/>
       <c r="C40" s="23" t="s">
-        <v>5366</v>
+        <v>5367</v>
       </c>
       <c r="D40" s="22"/>
       <c r="E40" s="23" t="s">
-        <v>5367</v>
+        <v>5368</v>
       </c>
       <c r="F40" s="22"/>
       <c r="G40" s="23" t="s">
-        <v>5368</v>
+        <v>5369</v>
       </c>
       <c r="H40" s="22"/>
       <c r="I40" s="23" t="s">
-        <v>5369</v>
+        <v>5370</v>
       </c>
       <c r="J40" s="22"/>
       <c r="K40" s="10"/>
@@ -54971,19 +54974,19 @@
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="23" t="s">
-        <v>5370</v>
+        <v>5371</v>
       </c>
       <c r="D41" s="22"/>
       <c r="E41" s="23" t="s">
-        <v>5371</v>
+        <v>5372</v>
       </c>
       <c r="F41" s="22"/>
       <c r="G41" s="23" t="s">
-        <v>5372</v>
+        <v>5373</v>
       </c>
       <c r="H41" s="22"/>
       <c r="I41" s="23" t="s">
-        <v>5373</v>
+        <v>5374</v>
       </c>
       <c r="J41" s="22"/>
       <c r="K41" s="10"/>
@@ -55000,19 +55003,19 @@
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="23" t="s">
-        <v>5374</v>
+        <v>5375</v>
       </c>
       <c r="D42" s="22"/>
       <c r="E42" s="23" t="s">
-        <v>5375</v>
+        <v>5376</v>
       </c>
       <c r="F42" s="22"/>
       <c r="G42" s="23" t="s">
-        <v>5376</v>
+        <v>5377</v>
       </c>
       <c r="H42" s="22"/>
       <c r="I42" s="23" t="s">
-        <v>5377</v>
+        <v>5378</v>
       </c>
       <c r="J42" s="22"/>
       <c r="K42" s="10"/>
@@ -55029,28 +55032,28 @@
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="21" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D43" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="E43" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="E43" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="F43" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="G43" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="G43" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="H43" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="I43" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="I43" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="J43" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="K43" s="10"/>
       <c r="L43" s="10"/>
@@ -55066,28 +55069,28 @@
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="23" t="s">
-        <v>5378</v>
+        <v>5379</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>5379</v>
+        <v>5380</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>5380</v>
+        <v>5381</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>5381</v>
+        <v>5382</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>5382</v>
+        <v>5383</v>
       </c>
       <c r="H44" s="25" t="s">
-        <v>5383</v>
+        <v>5384</v>
       </c>
       <c r="I44" s="23" t="s">
-        <v>5384</v>
+        <v>5385</v>
       </c>
       <c r="J44" s="25" t="s">
-        <v>5385</v>
+        <v>5386</v>
       </c>
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
@@ -55103,28 +55106,28 @@
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="23" t="s">
-        <v>5386</v>
+        <v>5387</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>5387</v>
+        <v>5388</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>5388</v>
+        <v>5389</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>5389</v>
+        <v>5390</v>
       </c>
       <c r="G45" s="23" t="s">
-        <v>5390</v>
+        <v>5391</v>
       </c>
       <c r="H45" s="25" t="s">
-        <v>5391</v>
+        <v>5392</v>
       </c>
       <c r="I45" s="23" t="s">
-        <v>5392</v>
+        <v>5393</v>
       </c>
       <c r="J45" s="25" t="s">
-        <v>5393</v>
+        <v>5394</v>
       </c>
       <c r="K45" s="10"/>
       <c r="L45" s="10"/>
@@ -55140,28 +55143,28 @@
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="23" t="s">
-        <v>5386</v>
+        <v>5387</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>5394</v>
+        <v>5395</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>5388</v>
+        <v>5389</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>5395</v>
+        <v>5396</v>
       </c>
       <c r="G46" s="23" t="s">
-        <v>5390</v>
+        <v>5391</v>
       </c>
       <c r="H46" s="25" t="s">
-        <v>5396</v>
+        <v>5397</v>
       </c>
       <c r="I46" s="23" t="s">
-        <v>5392</v>
+        <v>5393</v>
       </c>
       <c r="J46" s="25" t="s">
-        <v>5397</v>
+        <v>5398</v>
       </c>
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
@@ -55177,28 +55180,28 @@
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="23" t="s">
-        <v>5398</v>
+        <v>5399</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>5399</v>
+        <v>5400</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>5400</v>
+        <v>5401</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>5401</v>
+        <v>5402</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="H47" s="25" t="s">
-        <v>5403</v>
+        <v>5404</v>
       </c>
       <c r="I47" s="23" t="s">
-        <v>5404</v>
+        <v>5405</v>
       </c>
       <c r="J47" s="25" t="s">
-        <v>5405</v>
+        <v>5406</v>
       </c>
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
@@ -55214,28 +55217,28 @@
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="23" t="s">
-        <v>5406</v>
+        <v>5407</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>5407</v>
+        <v>5408</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>5408</v>
+        <v>5409</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>5409</v>
+        <v>5410</v>
       </c>
       <c r="G48" s="23" t="s">
-        <v>5410</v>
+        <v>5411</v>
       </c>
       <c r="H48" s="25" t="s">
-        <v>5411</v>
+        <v>5412</v>
       </c>
       <c r="I48" s="23" t="s">
-        <v>5412</v>
+        <v>5413</v>
       </c>
       <c r="J48" s="25" t="s">
-        <v>5413</v>
+        <v>5414</v>
       </c>
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
@@ -55251,28 +55254,28 @@
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="36" t="s">
-        <v>5414</v>
+        <v>5415</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>5415</v>
+        <v>5416</v>
       </c>
       <c r="E49" s="36" t="s">
-        <v>5416</v>
+        <v>5417</v>
       </c>
       <c r="F49" s="28" t="s">
-        <v>5417</v>
+        <v>5418</v>
       </c>
       <c r="G49" s="36" t="s">
-        <v>5418</v>
+        <v>5419</v>
       </c>
       <c r="H49" s="28" t="s">
-        <v>5419</v>
+        <v>5420</v>
       </c>
       <c r="I49" s="36" t="s">
-        <v>5420</v>
+        <v>5421</v>
       </c>
       <c r="J49" s="28" t="s">
-        <v>5421</v>
+        <v>5422</v>
       </c>
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
@@ -55311,23 +55314,23 @@
       </c>
       <c r="B51" s="19"/>
       <c r="C51" s="18" t="s">
-        <v>5422</v>
+        <v>5423</v>
       </c>
       <c r="D51" s="19"/>
       <c r="E51" s="20" t="s">
-        <v>5423</v>
+        <v>5424</v>
       </c>
       <c r="F51" s="19"/>
       <c r="G51" s="18" t="s">
-        <v>5424</v>
+        <v>5425</v>
       </c>
       <c r="H51" s="19"/>
       <c r="I51" s="18" t="s">
-        <v>5425</v>
+        <v>5426</v>
       </c>
       <c r="J51" s="19"/>
       <c r="K51" s="18" t="s">
-        <v>5426</v>
+        <v>5427</v>
       </c>
       <c r="L51" s="19"/>
       <c r="M51" s="10"/>
@@ -55340,27 +55343,27 @@
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" s="21" t="s">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="B52" s="22"/>
       <c r="C52" s="10" t="s">
-        <v>5427</v>
+        <v>5428</v>
       </c>
       <c r="D52" s="22"/>
       <c r="E52" s="10" t="s">
-        <v>5428</v>
+        <v>5429</v>
       </c>
       <c r="F52" s="22"/>
       <c r="G52" s="23" t="s">
-        <v>5429</v>
+        <v>5430</v>
       </c>
       <c r="H52" s="22"/>
       <c r="I52" s="23" t="s">
-        <v>5430</v>
+        <v>5431</v>
       </c>
       <c r="J52" s="22"/>
       <c r="K52" s="23" t="s">
-        <v>5431</v>
+        <v>5432</v>
       </c>
       <c r="L52" s="22"/>
       <c r="M52" s="10"/>
@@ -55373,27 +55376,27 @@
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" s="21" t="s">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="B53" s="22"/>
       <c r="C53" s="10" t="s">
-        <v>5432</v>
+        <v>5433</v>
       </c>
       <c r="D53" s="22"/>
       <c r="E53" s="10" t="s">
-        <v>5433</v>
+        <v>5434</v>
       </c>
       <c r="F53" s="22"/>
       <c r="G53" s="23" t="s">
-        <v>5434</v>
+        <v>5435</v>
       </c>
       <c r="H53" s="22"/>
       <c r="I53" s="23" t="s">
-        <v>5435</v>
+        <v>5436</v>
       </c>
       <c r="J53" s="22"/>
       <c r="K53" s="23" t="s">
-        <v>5436</v>
+        <v>5437</v>
       </c>
       <c r="L53" s="22"/>
       <c r="M53" s="10"/>
@@ -55406,27 +55409,27 @@
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" s="21" t="s">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="B54" s="22"/>
       <c r="C54" s="10" t="s">
-        <v>5437</v>
+        <v>5438</v>
       </c>
       <c r="D54" s="22"/>
       <c r="E54" s="10" t="s">
-        <v>5438</v>
+        <v>5439</v>
       </c>
       <c r="F54" s="22"/>
       <c r="G54" s="23" t="s">
-        <v>5439</v>
+        <v>5440</v>
       </c>
       <c r="H54" s="22"/>
       <c r="I54" s="23" t="s">
-        <v>5440</v>
+        <v>5441</v>
       </c>
       <c r="J54" s="22"/>
       <c r="K54" s="23" t="s">
-        <v>5441</v>
+        <v>5442</v>
       </c>
       <c r="L54" s="22"/>
       <c r="M54" s="10"/>
@@ -55439,38 +55442,38 @@
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" s="21" t="s">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="B55" s="22"/>
       <c r="C55" s="8" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D55" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="E55" s="8" t="s">
         <v>5221</v>
       </c>
-      <c r="E55" s="8" t="s">
-        <v>5220</v>
-      </c>
       <c r="F55" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="G55" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="G55" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="H55" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="I55" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="I55" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="J55" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="K55" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="K55" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="L55" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10"/>
@@ -55485,37 +55488,37 @@
         <v>4955</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>5442</v>
+        <v>5443</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>5443</v>
+        <v>5444</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>5444</v>
+        <v>5445</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>5445</v>
+        <v>5446</v>
       </c>
       <c r="G56" s="23" t="s">
-        <v>5446</v>
+        <v>5447</v>
       </c>
       <c r="H56" s="25" t="s">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="I56" s="23" t="s">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="J56" s="25" t="s">
-        <v>5449</v>
+        <v>5450</v>
       </c>
       <c r="K56" s="23" t="s">
-        <v>5450</v>
+        <v>5451</v>
       </c>
       <c r="L56" s="25" t="s">
-        <v>5451</v>
+        <v>5452</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10"/>
@@ -55531,34 +55534,34 @@
         <v>4492</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>5452</v>
+        <v>5453</v>
       </c>
       <c r="D57" s="25" t="s">
-        <v>5453</v>
+        <v>5454</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>5454</v>
+        <v>5455</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>5455</v>
+        <v>5456</v>
       </c>
       <c r="G57" s="23" t="s">
-        <v>5456</v>
+        <v>5457</v>
       </c>
       <c r="H57" s="25" t="s">
-        <v>5457</v>
+        <v>5458</v>
       </c>
       <c r="I57" s="23" t="s">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="J57" s="25" t="s">
-        <v>5459</v>
+        <v>5460</v>
       </c>
       <c r="K57" s="23" t="s">
-        <v>5460</v>
+        <v>5461</v>
       </c>
       <c r="L57" s="25" t="s">
-        <v>5461</v>
+        <v>5462</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10"/>
@@ -55571,37 +55574,37 @@
     <row r="58" ht="18.75" customHeight="1">
       <c r="A58" s="26"/>
       <c r="B58" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>5452</v>
+        <v>5453</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>5462</v>
+        <v>5463</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>5454</v>
+        <v>5455</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>5463</v>
+        <v>5464</v>
       </c>
       <c r="G58" s="23" t="s">
-        <v>5456</v>
+        <v>5457</v>
       </c>
       <c r="H58" s="25" t="s">
-        <v>5464</v>
+        <v>5465</v>
       </c>
       <c r="I58" s="23" t="s">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="J58" s="25" t="s">
-        <v>5465</v>
+        <v>5466</v>
       </c>
       <c r="K58" s="23" t="s">
-        <v>5460</v>
+        <v>5461</v>
       </c>
       <c r="L58" s="25" t="s">
-        <v>5466</v>
+        <v>5467</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10"/>
@@ -55619,34 +55622,34 @@
         <v>4317</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>5467</v>
+        <v>5468</v>
       </c>
       <c r="D59" s="25" t="s">
         <v>3739</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>5468</v>
+        <v>5469</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>5469</v>
+        <v>5470</v>
       </c>
       <c r="G59" s="23" t="s">
-        <v>5470</v>
+        <v>5471</v>
       </c>
       <c r="H59" s="25" t="s">
-        <v>5471</v>
+        <v>5472</v>
       </c>
       <c r="I59" s="23" t="s">
-        <v>5472</v>
+        <v>5473</v>
       </c>
       <c r="J59" s="25" t="s">
-        <v>5473</v>
+        <v>5474</v>
       </c>
       <c r="K59" s="23" t="s">
-        <v>5474</v>
+        <v>5475</v>
       </c>
       <c r="L59" s="25" t="s">
-        <v>5475</v>
+        <v>5476</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10"/>
@@ -55661,34 +55664,34 @@
         <v>4442</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>5476</v>
+        <v>5477</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>5477</v>
+        <v>5478</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>5478</v>
+        <v>5479</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>5479</v>
+        <v>5480</v>
       </c>
       <c r="G60" s="23" t="s">
-        <v>5480</v>
+        <v>5481</v>
       </c>
       <c r="H60" s="25" t="s">
-        <v>5481</v>
+        <v>5482</v>
       </c>
       <c r="I60" s="23" t="s">
-        <v>5482</v>
+        <v>5483</v>
       </c>
       <c r="J60" s="25" t="s">
-        <v>5483</v>
+        <v>5484</v>
       </c>
       <c r="K60" s="23" t="s">
-        <v>5484</v>
+        <v>5485</v>
       </c>
       <c r="L60" s="25" t="s">
-        <v>5485</v>
+        <v>5486</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10"/>
@@ -55700,37 +55703,37 @@
     </row>
     <row r="61" ht="18.75" customHeight="1">
       <c r="B61" s="24" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>5486</v>
+        <v>5487</v>
       </c>
       <c r="D61" s="25" t="s">
-        <v>5487</v>
+        <v>5488</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>5488</v>
+        <v>5489</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>5489</v>
+        <v>5490</v>
       </c>
       <c r="G61" s="23" t="s">
-        <v>5490</v>
+        <v>5491</v>
       </c>
       <c r="H61" s="25" t="s">
-        <v>5491</v>
+        <v>5492</v>
       </c>
       <c r="I61" s="23" t="s">
-        <v>5492</v>
+        <v>5493</v>
       </c>
       <c r="J61" s="25" t="s">
-        <v>5493</v>
+        <v>5494</v>
       </c>
       <c r="K61" s="23" t="s">
-        <v>5494</v>
+        <v>5495</v>
       </c>
       <c r="L61" s="25" t="s">
-        <v>5495</v>
+        <v>5496</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10"/>
@@ -55742,22 +55745,22 @@
     </row>
     <row r="62" ht="18.75" customHeight="1">
       <c r="A62" s="21" t="s">
-        <v>5273</v>
+        <v>5274</v>
       </c>
       <c r="B62" s="22"/>
       <c r="C62" s="37"/>
       <c r="D62" s="35"/>
       <c r="E62" s="8" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="F62" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="G62" s="8" t="s">
         <v>5221</v>
       </c>
-      <c r="G62" s="8" t="s">
-        <v>5220</v>
-      </c>
       <c r="H62" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="I62" s="30"/>
       <c r="J62" s="38"/>
@@ -55776,21 +55779,21 @@
         <v>4955</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C63" s="39"/>
       <c r="D63" s="25"/>
       <c r="E63" s="23" t="s">
-        <v>5496</v>
+        <v>5497</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>5497</v>
+        <v>5498</v>
       </c>
       <c r="G63" s="23" t="s">
-        <v>5498</v>
+        <v>5499</v>
       </c>
       <c r="H63" s="25" t="s">
-        <v>5499</v>
+        <v>5500</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="40"/>
@@ -55830,7 +55833,7 @@
     <row r="65" ht="18.75" customHeight="1">
       <c r="A65" s="26"/>
       <c r="B65" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C65" s="39"/>
       <c r="D65" s="25"/>
@@ -55860,16 +55863,16 @@
       <c r="C66" s="39"/>
       <c r="D66" s="25"/>
       <c r="E66" s="10" t="s">
-        <v>5500</v>
+        <v>5501</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>5501</v>
+        <v>5502</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>5502</v>
+        <v>5503</v>
       </c>
       <c r="H66" s="25" t="s">
-        <v>5503</v>
+        <v>5504</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="40"/>
@@ -55891,16 +55894,16 @@
       <c r="C67" s="39"/>
       <c r="D67" s="25"/>
       <c r="E67" s="10" t="s">
-        <v>5504</v>
+        <v>5505</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>5505</v>
+        <v>5506</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>5506</v>
+        <v>5507</v>
       </c>
       <c r="H67" s="25" t="s">
-        <v>5507</v>
+        <v>5508</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="40"/>
@@ -55917,7 +55920,7 @@
     <row r="68" ht="18.75" customHeight="1">
       <c r="A68" s="31"/>
       <c r="B68" s="32" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C68" s="39"/>
       <c r="D68" s="25"/>
@@ -55981,139 +55984,139 @@
     </row>
     <row r="71" ht="18.75" customHeight="1">
       <c r="A71" s="18" t="s">
-        <v>5508</v>
+        <v>5509</v>
       </c>
       <c r="B71" s="19"/>
       <c r="C71" s="20" t="s">
-        <v>5509</v>
+        <v>5510</v>
       </c>
       <c r="D71" s="19"/>
       <c r="E71" s="18" t="s">
-        <v>5510</v>
+        <v>5511</v>
       </c>
       <c r="F71" s="41"/>
       <c r="G71" s="18" t="s">
-        <v>5511</v>
+        <v>5512</v>
       </c>
       <c r="H71" s="41"/>
       <c r="I71" s="18" t="s">
-        <v>5512</v>
+        <v>5513</v>
       </c>
       <c r="J71" s="19"/>
       <c r="K71" s="18" t="s">
-        <v>5513</v>
+        <v>5514</v>
       </c>
       <c r="L71" s="19"/>
     </row>
     <row r="72" ht="18.75" customHeight="1">
       <c r="A72" s="21" t="s">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="B72" s="22"/>
       <c r="C72" s="10" t="s">
-        <v>5514</v>
+        <v>5515</v>
       </c>
       <c r="D72" s="22"/>
       <c r="E72" s="10" t="s">
-        <v>5515</v>
+        <v>5516</v>
       </c>
       <c r="F72" s="22"/>
       <c r="G72" s="10" t="s">
-        <v>5516</v>
+        <v>5517</v>
       </c>
       <c r="I72" s="23" t="s">
-        <v>5517</v>
+        <v>5518</v>
       </c>
       <c r="J72" s="22"/>
       <c r="K72" s="23" t="s">
-        <v>5518</v>
+        <v>5519</v>
       </c>
       <c r="L72" s="22"/>
     </row>
     <row r="73" ht="18.75" customHeight="1">
       <c r="A73" s="21" t="s">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="B73" s="22"/>
       <c r="C73" s="10" t="s">
-        <v>5519</v>
+        <v>5520</v>
       </c>
       <c r="D73" s="22"/>
       <c r="E73" s="10" t="s">
-        <v>5520</v>
+        <v>5521</v>
       </c>
       <c r="F73" s="22"/>
       <c r="G73" s="10" t="s">
-        <v>5521</v>
+        <v>5522</v>
       </c>
       <c r="I73" s="23" t="s">
-        <v>5522</v>
+        <v>5523</v>
       </c>
       <c r="J73" s="22"/>
       <c r="K73" s="23" t="s">
-        <v>5523</v>
+        <v>5524</v>
       </c>
       <c r="L73" s="22"/>
     </row>
     <row r="74" ht="18.75" customHeight="1">
       <c r="A74" s="21" t="s">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="B74" s="22"/>
       <c r="C74" s="10" t="s">
-        <v>5524</v>
+        <v>5525</v>
       </c>
       <c r="D74" s="22"/>
       <c r="E74" s="10" t="s">
-        <v>5525</v>
+        <v>5526</v>
       </c>
       <c r="F74" s="22"/>
       <c r="G74" s="10" t="s">
-        <v>5526</v>
+        <v>5527</v>
       </c>
       <c r="I74" s="23" t="s">
-        <v>5527</v>
+        <v>5528</v>
       </c>
       <c r="J74" s="22"/>
       <c r="K74" s="23" t="s">
-        <v>5528</v>
+        <v>5529</v>
       </c>
       <c r="L74" s="22"/>
     </row>
     <row r="75" ht="18.75" customHeight="1">
       <c r="A75" s="21" t="s">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="B75" s="22"/>
       <c r="C75" s="8" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D75" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="E75" s="8" t="s">
         <v>5221</v>
       </c>
-      <c r="E75" s="8" t="s">
-        <v>5220</v>
-      </c>
       <c r="F75" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="G75" s="8" t="s">
         <v>5221</v>
       </c>
-      <c r="G75" s="8" t="s">
-        <v>5220</v>
-      </c>
       <c r="H75" s="8" t="s">
+        <v>5222</v>
+      </c>
+      <c r="I75" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="I75" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="J75" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="K75" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="K75" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="L75" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
     </row>
     <row r="76" ht="18.75" customHeight="1">
@@ -56121,37 +56124,37 @@
         <v>4955</v>
       </c>
       <c r="B76" s="24" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>5529</v>
+        <v>5530</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>5530</v>
+        <v>5531</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>5531</v>
+        <v>5532</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>5532</v>
+        <v>5533</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>5533</v>
+        <v>5534</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>5534</v>
+        <v>5535</v>
       </c>
       <c r="I76" s="23" t="s">
-        <v>5535</v>
+        <v>5536</v>
       </c>
       <c r="J76" s="25" t="s">
-        <v>5536</v>
+        <v>5537</v>
       </c>
       <c r="K76" s="23" t="s">
-        <v>5537</v>
+        <v>5538</v>
       </c>
       <c r="L76" s="25" t="s">
-        <v>5538</v>
+        <v>5539</v>
       </c>
     </row>
     <row r="77" ht="18.75" customHeight="1">
@@ -56160,70 +56163,70 @@
         <v>4492</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>5539</v>
+        <v>5540</v>
       </c>
       <c r="D77" s="25" t="s">
-        <v>5540</v>
+        <v>5541</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>5541</v>
+        <v>5542</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>5542</v>
+        <v>5543</v>
       </c>
       <c r="G77" s="10" t="s">
         <v>4972</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>5543</v>
+        <v>5544</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>5544</v>
+        <v>5545</v>
       </c>
       <c r="J77" s="25" t="s">
-        <v>5545</v>
+        <v>5546</v>
       </c>
       <c r="K77" s="23" t="s">
-        <v>5546</v>
+        <v>5547</v>
       </c>
       <c r="L77" s="25" t="s">
-        <v>5547</v>
+        <v>5548</v>
       </c>
     </row>
     <row r="78" ht="18.75" customHeight="1">
       <c r="A78" s="26"/>
       <c r="B78" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>5529</v>
+        <v>5530</v>
       </c>
       <c r="D78" s="25" t="s">
-        <v>5530</v>
+        <v>5531</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>5531</v>
+        <v>5532</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>5532</v>
+        <v>5533</v>
       </c>
       <c r="G78" s="10" t="s">
         <v>4972</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>5534</v>
+        <v>5535</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>5544</v>
+        <v>5545</v>
       </c>
       <c r="J78" s="25" t="s">
-        <v>5536</v>
+        <v>5537</v>
       </c>
       <c r="K78" s="23" t="s">
-        <v>5546</v>
+        <v>5547</v>
       </c>
       <c r="L78" s="25" t="s">
-        <v>5548</v>
+        <v>5549</v>
       </c>
     </row>
     <row r="79" ht="18.75" customHeight="1">
@@ -56234,34 +56237,34 @@
         <v>4317</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>5549</v>
+        <v>5550</v>
       </c>
       <c r="D79" s="25" t="s">
-        <v>5550</v>
+        <v>5551</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>5551</v>
+        <v>5552</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>5552</v>
+        <v>5553</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>5553</v>
+        <v>5554</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>5554</v>
+        <v>5555</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>5555</v>
+        <v>5556</v>
       </c>
       <c r="J79" s="25" t="s">
-        <v>5556</v>
+        <v>5557</v>
       </c>
       <c r="K79" s="23" t="s">
-        <v>5557</v>
+        <v>5558</v>
       </c>
       <c r="L79" s="25" t="s">
-        <v>5558</v>
+        <v>5559</v>
       </c>
     </row>
     <row r="80" ht="18.75" customHeight="1">
@@ -56270,70 +56273,70 @@
         <v>4442</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>5559</v>
+        <v>5560</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>5560</v>
+        <v>5561</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>5561</v>
+        <v>5562</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>5562</v>
+        <v>5563</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>5563</v>
+        <v>5564</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>5564</v>
+        <v>5565</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>5565</v>
+        <v>5566</v>
       </c>
       <c r="J80" s="25" t="s">
-        <v>5566</v>
+        <v>5567</v>
       </c>
       <c r="K80" s="23" t="s">
-        <v>5567</v>
+        <v>5568</v>
       </c>
       <c r="L80" s="25" t="s">
-        <v>5568</v>
+        <v>5569</v>
       </c>
     </row>
     <row r="81" ht="18.75" customHeight="1">
       <c r="A81" s="31"/>
       <c r="B81" s="32" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C81" s="27" t="s">
-        <v>5569</v>
+        <v>5570</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>5570</v>
+        <v>5571</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>5571</v>
+        <v>5572</v>
       </c>
       <c r="F81" s="28" t="s">
-        <v>5572</v>
+        <v>5573</v>
       </c>
       <c r="G81" s="27" t="s">
-        <v>5573</v>
+        <v>5574</v>
       </c>
       <c r="H81" s="27" t="s">
-        <v>5574</v>
+        <v>5575</v>
       </c>
       <c r="I81" s="23" t="s">
-        <v>5575</v>
+        <v>5576</v>
       </c>
       <c r="J81" s="25" t="s">
-        <v>5576</v>
+        <v>5577</v>
       </c>
       <c r="K81" s="23" t="s">
-        <v>5577</v>
+        <v>5578</v>
       </c>
       <c r="L81" s="25" t="s">
-        <v>5578</v>
+        <v>5579</v>
       </c>
     </row>
     <row r="82" ht="18.75" customHeight="1">
@@ -56346,16 +56349,16 @@
       <c r="G82" s="10"/>
       <c r="H82" s="10"/>
       <c r="I82" s="21" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="J82" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="K82" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="K82" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="L82" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10"/>
@@ -56375,16 +56378,16 @@
       <c r="G83" s="10"/>
       <c r="H83" s="10"/>
       <c r="I83" s="23" t="s">
-        <v>5579</v>
+        <v>5580</v>
       </c>
       <c r="J83" s="25" t="s">
-        <v>5580</v>
+        <v>5581</v>
       </c>
       <c r="K83" s="23" t="s">
-        <v>5581</v>
+        <v>5582</v>
       </c>
       <c r="L83" s="25" t="s">
-        <v>5582</v>
+        <v>5583</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10"/>
@@ -56446,16 +56449,16 @@
       <c r="G86" s="10"/>
       <c r="H86" s="10"/>
       <c r="I86" s="23" t="s">
-        <v>5583</v>
+        <v>5584</v>
       </c>
       <c r="J86" s="25" t="s">
-        <v>5584</v>
+        <v>5585</v>
       </c>
       <c r="K86" s="23" t="s">
-        <v>5585</v>
+        <v>5586</v>
       </c>
       <c r="L86" s="25" t="s">
-        <v>5586</v>
+        <v>5587</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10"/>
@@ -56475,16 +56478,16 @@
       <c r="G87" s="10"/>
       <c r="H87" s="10"/>
       <c r="I87" s="23" t="s">
-        <v>5587</v>
+        <v>5588</v>
       </c>
       <c r="J87" s="25" t="s">
-        <v>5588</v>
+        <v>5589</v>
       </c>
       <c r="K87" s="23" t="s">
-        <v>5589</v>
+        <v>5590</v>
       </c>
       <c r="L87" s="25" t="s">
-        <v>5590</v>
+        <v>5591</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10"/>
@@ -56538,27 +56541,27 @@
     </row>
     <row r="90" ht="18.75" customHeight="1">
       <c r="A90" s="18" t="s">
-        <v>5591</v>
+        <v>5592</v>
       </c>
       <c r="B90" s="19"/>
       <c r="C90" s="18" t="s">
-        <v>5592</v>
+        <v>5593</v>
       </c>
       <c r="D90" s="19"/>
       <c r="E90" s="18" t="s">
-        <v>5593</v>
+        <v>5594</v>
       </c>
       <c r="F90" s="19"/>
       <c r="G90" s="18" t="s">
-        <v>5594</v>
+        <v>5595</v>
       </c>
       <c r="H90" s="19"/>
       <c r="I90" s="18" t="s">
-        <v>5595</v>
+        <v>5596</v>
       </c>
       <c r="J90" s="19"/>
       <c r="K90" s="18" t="s">
-        <v>5596</v>
+        <v>5597</v>
       </c>
       <c r="L90" s="19"/>
       <c r="M90" s="10"/>
@@ -56571,27 +56574,27 @@
     </row>
     <row r="91" ht="18.75" customHeight="1">
       <c r="A91" s="23" t="s">
-        <v>5597</v>
+        <v>5598</v>
       </c>
       <c r="B91" s="22"/>
       <c r="C91" s="23" t="s">
-        <v>5598</v>
+        <v>5599</v>
       </c>
       <c r="D91" s="22"/>
       <c r="E91" s="23" t="s">
-        <v>5599</v>
+        <v>5600</v>
       </c>
       <c r="F91" s="22"/>
       <c r="G91" s="23" t="s">
-        <v>5600</v>
+        <v>5601</v>
       </c>
       <c r="H91" s="22"/>
       <c r="I91" s="23" t="s">
-        <v>5601</v>
+        <v>5602</v>
       </c>
       <c r="J91" s="22"/>
       <c r="K91" s="23" t="s">
-        <v>5602</v>
+        <v>5603</v>
       </c>
       <c r="L91" s="22"/>
       <c r="M91" s="10"/>
@@ -56604,27 +56607,27 @@
     </row>
     <row r="92" ht="18.75" customHeight="1">
       <c r="A92" s="23" t="s">
-        <v>5603</v>
+        <v>5604</v>
       </c>
       <c r="B92" s="22"/>
       <c r="C92" s="23" t="s">
-        <v>5604</v>
+        <v>5605</v>
       </c>
       <c r="D92" s="22"/>
       <c r="E92" s="23" t="s">
-        <v>5605</v>
+        <v>5606</v>
       </c>
       <c r="F92" s="22"/>
       <c r="G92" s="23" t="s">
-        <v>5606</v>
+        <v>5607</v>
       </c>
       <c r="H92" s="22"/>
       <c r="I92" s="23" t="s">
-        <v>5607</v>
+        <v>5608</v>
       </c>
       <c r="J92" s="22"/>
       <c r="K92" s="23" t="s">
-        <v>5608</v>
+        <v>5609</v>
       </c>
       <c r="L92" s="22"/>
       <c r="M92" s="10"/>
@@ -56637,27 +56640,27 @@
     </row>
     <row r="93" ht="18.75" customHeight="1">
       <c r="A93" s="23" t="s">
-        <v>5609</v>
+        <v>5610</v>
       </c>
       <c r="B93" s="22"/>
       <c r="C93" s="23" t="s">
-        <v>5610</v>
+        <v>5611</v>
       </c>
       <c r="D93" s="22"/>
       <c r="E93" s="23" t="s">
-        <v>5611</v>
+        <v>5612</v>
       </c>
       <c r="F93" s="22"/>
       <c r="G93" s="23" t="s">
-        <v>5612</v>
+        <v>5613</v>
       </c>
       <c r="H93" s="22"/>
       <c r="I93" s="23" t="s">
-        <v>5613</v>
+        <v>5614</v>
       </c>
       <c r="J93" s="22"/>
       <c r="K93" s="23" t="s">
-        <v>5614</v>
+        <v>5615</v>
       </c>
       <c r="L93" s="22"/>
       <c r="M93" s="10"/>
@@ -56670,40 +56673,40 @@
     </row>
     <row r="94" ht="18.75" customHeight="1">
       <c r="A94" s="21" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="B94" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="C94" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="C94" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="D94" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="E94" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="E94" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="F94" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="G94" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="G94" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="H94" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="I94" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="I94" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="J94" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="K94" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="K94" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="L94" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="M94" s="10"/>
       <c r="N94" s="10"/>
@@ -56715,40 +56718,40 @@
     </row>
     <row r="95" ht="18.75" customHeight="1">
       <c r="A95" s="23" t="s">
-        <v>5615</v>
+        <v>5616</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>5616</v>
+        <v>5617</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>5617</v>
+        <v>5618</v>
       </c>
       <c r="D95" s="25" t="s">
-        <v>5618</v>
+        <v>5619</v>
       </c>
       <c r="E95" s="23" t="s">
-        <v>5619</v>
+        <v>5620</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>5620</v>
+        <v>5621</v>
       </c>
       <c r="G95" s="23" t="s">
-        <v>5621</v>
+        <v>5622</v>
       </c>
       <c r="H95" s="25" t="s">
-        <v>5622</v>
+        <v>5623</v>
       </c>
       <c r="I95" s="23" t="s">
-        <v>5623</v>
+        <v>5624</v>
       </c>
       <c r="J95" s="25" t="s">
-        <v>5624</v>
+        <v>5625</v>
       </c>
       <c r="K95" s="23" t="s">
-        <v>5625</v>
+        <v>5626</v>
       </c>
       <c r="L95" s="25" t="s">
-        <v>5626</v>
+        <v>5627</v>
       </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10"/>
@@ -56760,40 +56763,40 @@
     </row>
     <row r="96" ht="18.75" customHeight="1">
       <c r="A96" s="23" t="s">
-        <v>5627</v>
+        <v>5628</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>5628</v>
+        <v>5629</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>5629</v>
+        <v>5630</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>5630</v>
+        <v>5631</v>
       </c>
       <c r="E96" s="23" t="s">
-        <v>5631</v>
+        <v>5632</v>
       </c>
       <c r="F96" s="25" t="s">
-        <v>5632</v>
+        <v>5633</v>
       </c>
       <c r="G96" s="23" t="s">
-        <v>5633</v>
+        <v>5634</v>
       </c>
       <c r="H96" s="25" t="s">
-        <v>5634</v>
+        <v>5635</v>
       </c>
       <c r="I96" s="23" t="s">
         <v>2238</v>
       </c>
       <c r="J96" s="25" t="s">
-        <v>5635</v>
+        <v>5636</v>
       </c>
       <c r="K96" s="23" t="s">
-        <v>5636</v>
+        <v>5637</v>
       </c>
       <c r="L96" s="25" t="s">
-        <v>5637</v>
+        <v>5638</v>
       </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10"/>
@@ -56805,40 +56808,40 @@
     </row>
     <row r="97" ht="18.75" customHeight="1">
       <c r="A97" s="23" t="s">
-        <v>5627</v>
+        <v>5628</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>5638</v>
+        <v>5639</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>5629</v>
+        <v>5630</v>
       </c>
       <c r="D97" s="25" t="s">
-        <v>5639</v>
+        <v>5640</v>
       </c>
       <c r="E97" s="23" t="s">
-        <v>5631</v>
+        <v>5632</v>
       </c>
       <c r="F97" s="25" t="s">
-        <v>5620</v>
+        <v>5621</v>
       </c>
       <c r="G97" s="23" t="s">
-        <v>5621</v>
+        <v>5622</v>
       </c>
       <c r="H97" s="25" t="s">
-        <v>5640</v>
+        <v>5641</v>
       </c>
       <c r="I97" s="23" t="s">
         <v>2238</v>
       </c>
       <c r="J97" s="25" t="s">
-        <v>5641</v>
+        <v>5642</v>
       </c>
       <c r="K97" s="23" t="s">
-        <v>5636</v>
+        <v>5637</v>
       </c>
       <c r="L97" s="25" t="s">
-        <v>5626</v>
+        <v>5627</v>
       </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10"/>
@@ -56850,40 +56853,40 @@
     </row>
     <row r="98" ht="18.75" customHeight="1">
       <c r="A98" s="23" t="s">
-        <v>5642</v>
+        <v>5643</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>5643</v>
+        <v>5644</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>5644</v>
+        <v>5645</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>5645</v>
+        <v>5646</v>
       </c>
       <c r="E98" s="23" t="s">
-        <v>5646</v>
+        <v>5647</v>
       </c>
       <c r="F98" s="25" t="s">
-        <v>5647</v>
+        <v>5648</v>
       </c>
       <c r="G98" s="23" t="s">
-        <v>5648</v>
+        <v>5649</v>
       </c>
       <c r="H98" s="25" t="s">
-        <v>5649</v>
+        <v>5650</v>
       </c>
       <c r="I98" s="23" t="s">
-        <v>5650</v>
+        <v>5651</v>
       </c>
       <c r="J98" s="25" t="s">
-        <v>5651</v>
+        <v>5652</v>
       </c>
       <c r="K98" s="23" t="s">
-        <v>5652</v>
+        <v>5653</v>
       </c>
       <c r="L98" s="25" t="s">
-        <v>5653</v>
+        <v>5654</v>
       </c>
       <c r="M98" s="10"/>
       <c r="N98" s="10"/>
@@ -56895,40 +56898,40 @@
     </row>
     <row r="99" ht="18.75" customHeight="1">
       <c r="A99" s="23" t="s">
-        <v>5654</v>
+        <v>5655</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>5655</v>
+        <v>5656</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>5656</v>
+        <v>5657</v>
       </c>
       <c r="D99" s="25" t="s">
-        <v>5657</v>
+        <v>5658</v>
       </c>
       <c r="E99" s="23" t="s">
-        <v>5658</v>
+        <v>5659</v>
       </c>
       <c r="F99" s="25" t="s">
-        <v>5659</v>
+        <v>5660</v>
       </c>
       <c r="G99" s="23" t="s">
-        <v>5660</v>
+        <v>5661</v>
       </c>
       <c r="H99" s="25" t="s">
-        <v>5661</v>
+        <v>5662</v>
       </c>
       <c r="I99" s="23" t="s">
-        <v>5662</v>
+        <v>5663</v>
       </c>
       <c r="J99" s="25" t="s">
-        <v>5663</v>
+        <v>5664</v>
       </c>
       <c r="K99" s="23" t="s">
-        <v>5664</v>
+        <v>5665</v>
       </c>
       <c r="L99" s="25" t="s">
-        <v>5665</v>
+        <v>5666</v>
       </c>
       <c r="M99" s="10"/>
       <c r="N99" s="10"/>
@@ -56940,40 +56943,40 @@
     </row>
     <row r="100" ht="18.75" customHeight="1">
       <c r="A100" s="36" t="s">
-        <v>5666</v>
+        <v>5667</v>
       </c>
       <c r="B100" s="28" t="s">
-        <v>5667</v>
+        <v>5668</v>
       </c>
       <c r="C100" s="36" t="s">
-        <v>5668</v>
+        <v>5669</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>5669</v>
+        <v>5670</v>
       </c>
       <c r="E100" s="23" t="s">
-        <v>5670</v>
+        <v>5671</v>
       </c>
       <c r="F100" s="25" t="s">
-        <v>5671</v>
+        <v>5672</v>
       </c>
       <c r="G100" s="36" t="s">
-        <v>5672</v>
+        <v>5673</v>
       </c>
       <c r="H100" s="28" t="s">
-        <v>5673</v>
+        <v>5674</v>
       </c>
       <c r="I100" s="36" t="s">
-        <v>5674</v>
+        <v>5675</v>
       </c>
       <c r="J100" s="28" t="s">
-        <v>5675</v>
+        <v>5676</v>
       </c>
       <c r="K100" s="36" t="s">
-        <v>5676</v>
+        <v>5677</v>
       </c>
       <c r="L100" s="28" t="s">
-        <v>5677</v>
+        <v>5678</v>
       </c>
       <c r="M100" s="10"/>
       <c r="N100" s="10"/>
@@ -56987,10 +56990,10 @@
       <c r="A101" s="10"/>
       <c r="B101" s="10"/>
       <c r="E101" s="21" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="F101" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="G101" s="10"/>
       <c r="H101" s="10"/>
@@ -57010,10 +57013,10 @@
       <c r="A102" s="10"/>
       <c r="B102" s="10"/>
       <c r="E102" s="23" t="s">
-        <v>5678</v>
+        <v>5679</v>
       </c>
       <c r="F102" s="25" t="s">
-        <v>5679</v>
+        <v>5680</v>
       </c>
       <c r="G102" s="10"/>
       <c r="H102" s="10"/>
@@ -57071,10 +57074,10 @@
       <c r="A105" s="10"/>
       <c r="B105" s="10"/>
       <c r="E105" s="23" t="s">
-        <v>5680</v>
+        <v>5681</v>
       </c>
       <c r="F105" s="25" t="s">
-        <v>5681</v>
+        <v>5682</v>
       </c>
       <c r="G105" s="10"/>
       <c r="H105" s="10"/>
@@ -57094,10 +57097,10 @@
       <c r="A106" s="10"/>
       <c r="B106" s="10"/>
       <c r="E106" s="23" t="s">
-        <v>5682</v>
+        <v>5683</v>
       </c>
       <c r="F106" s="25" t="s">
-        <v>5683</v>
+        <v>5684</v>
       </c>
       <c r="G106" s="10"/>
       <c r="H106" s="10"/>
@@ -57155,27 +57158,27 @@
     </row>
     <row r="109" ht="18.75" customHeight="1">
       <c r="A109" s="18" t="s">
-        <v>5684</v>
+        <v>5685</v>
       </c>
       <c r="B109" s="19"/>
       <c r="C109" s="18" t="s">
-        <v>5685</v>
+        <v>5686</v>
       </c>
       <c r="D109" s="19"/>
       <c r="E109" s="18" t="s">
-        <v>5686</v>
+        <v>5687</v>
       </c>
       <c r="F109" s="19"/>
       <c r="G109" s="18" t="s">
-        <v>5687</v>
+        <v>5688</v>
       </c>
       <c r="H109" s="19"/>
       <c r="I109" s="18" t="s">
-        <v>5688</v>
+        <v>5689</v>
       </c>
       <c r="J109" s="19"/>
       <c r="K109" s="18" t="s">
-        <v>5689</v>
+        <v>5690</v>
       </c>
       <c r="L109" s="19"/>
       <c r="M109" s="10"/>
@@ -57188,27 +57191,27 @@
     </row>
     <row r="110" ht="18.75" customHeight="1">
       <c r="A110" s="23" t="s">
-        <v>5690</v>
+        <v>5691</v>
       </c>
       <c r="B110" s="22"/>
       <c r="C110" s="23" t="s">
-        <v>5691</v>
+        <v>5692</v>
       </c>
       <c r="D110" s="22"/>
       <c r="E110" s="23" t="s">
-        <v>5692</v>
+        <v>5693</v>
       </c>
       <c r="F110" s="22"/>
       <c r="G110" s="23" t="s">
-        <v>5693</v>
+        <v>5694</v>
       </c>
       <c r="H110" s="22"/>
       <c r="I110" s="23" t="s">
-        <v>5694</v>
+        <v>5695</v>
       </c>
       <c r="J110" s="22"/>
       <c r="K110" s="23" t="s">
-        <v>5695</v>
+        <v>5696</v>
       </c>
       <c r="L110" s="22"/>
       <c r="M110" s="10"/>
@@ -57221,27 +57224,27 @@
     </row>
     <row r="111" ht="18.75" customHeight="1">
       <c r="A111" s="23" t="s">
-        <v>5696</v>
+        <v>5697</v>
       </c>
       <c r="B111" s="22"/>
       <c r="C111" s="23" t="s">
-        <v>5697</v>
+        <v>5698</v>
       </c>
       <c r="D111" s="22"/>
       <c r="E111" s="23" t="s">
-        <v>5698</v>
+        <v>5699</v>
       </c>
       <c r="F111" s="22"/>
       <c r="G111" s="23" t="s">
-        <v>5699</v>
+        <v>5700</v>
       </c>
       <c r="H111" s="22"/>
       <c r="I111" s="23" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="J111" s="22"/>
       <c r="K111" s="23" t="s">
-        <v>5701</v>
+        <v>5702</v>
       </c>
       <c r="L111" s="22"/>
       <c r="M111" s="10"/>
@@ -57254,27 +57257,27 @@
     </row>
     <row r="112" ht="18.75" customHeight="1">
       <c r="A112" s="23" t="s">
-        <v>5702</v>
+        <v>5703</v>
       </c>
       <c r="B112" s="22"/>
       <c r="C112" s="23" t="s">
-        <v>5703</v>
+        <v>5704</v>
       </c>
       <c r="D112" s="22"/>
       <c r="E112" s="23" t="s">
-        <v>5704</v>
+        <v>5705</v>
       </c>
       <c r="F112" s="22"/>
       <c r="G112" s="23" t="s">
-        <v>5705</v>
+        <v>5706</v>
       </c>
       <c r="H112" s="22"/>
       <c r="I112" s="23" t="s">
-        <v>5706</v>
+        <v>5707</v>
       </c>
       <c r="J112" s="22"/>
       <c r="K112" s="23" t="s">
-        <v>5707</v>
+        <v>5708</v>
       </c>
       <c r="L112" s="22"/>
       <c r="M112" s="10"/>
@@ -57287,40 +57290,40 @@
     </row>
     <row r="113" ht="18.75" customHeight="1">
       <c r="A113" s="21" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="B113" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="C113" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="C113" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="D113" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="E113" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="E113" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="F113" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="G113" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="G113" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="H113" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="I113" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="I113" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="J113" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="K113" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="K113" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="L113" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="M113" s="10"/>
       <c r="N113" s="10"/>
@@ -57332,40 +57335,40 @@
     </row>
     <row r="114" ht="18.75" customHeight="1">
       <c r="A114" s="23" t="s">
-        <v>5708</v>
+        <v>5709</v>
       </c>
       <c r="B114" s="25" t="s">
         <v>4883</v>
       </c>
       <c r="C114" s="23" t="s">
-        <v>5709</v>
+        <v>5710</v>
       </c>
       <c r="D114" s="25" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="E114" s="23" t="s">
-        <v>5711</v>
+        <v>5712</v>
       </c>
       <c r="F114" s="25" t="s">
-        <v>5712</v>
+        <v>5713</v>
       </c>
       <c r="G114" s="23" t="s">
-        <v>5713</v>
+        <v>5714</v>
       </c>
       <c r="H114" s="25" t="s">
-        <v>5714</v>
+        <v>5715</v>
       </c>
       <c r="I114" s="23" t="s">
         <v>802</v>
       </c>
       <c r="J114" s="25" t="s">
-        <v>5715</v>
+        <v>5716</v>
       </c>
       <c r="K114" s="23" t="s">
-        <v>5716</v>
+        <v>5717</v>
       </c>
       <c r="L114" s="25" t="s">
-        <v>5717</v>
+        <v>5718</v>
       </c>
       <c r="M114" s="10"/>
       <c r="N114" s="10"/>
@@ -57377,40 +57380,40 @@
     </row>
     <row r="115" ht="18.75" customHeight="1">
       <c r="A115" s="23" t="s">
-        <v>5718</v>
+        <v>5719</v>
       </c>
       <c r="B115" s="25" t="s">
-        <v>5719</v>
+        <v>5720</v>
       </c>
       <c r="C115" s="23" t="s">
-        <v>5720</v>
+        <v>5721</v>
       </c>
       <c r="D115" s="25" t="s">
-        <v>5721</v>
+        <v>5722</v>
       </c>
       <c r="E115" s="23" t="s">
-        <v>5722</v>
+        <v>5723</v>
       </c>
       <c r="F115" s="25" t="s">
-        <v>5723</v>
+        <v>5724</v>
       </c>
       <c r="G115" s="23" t="s">
-        <v>5724</v>
+        <v>5725</v>
       </c>
       <c r="H115" s="25" t="s">
-        <v>5725</v>
+        <v>5726</v>
       </c>
       <c r="I115" s="23" t="s">
-        <v>5726</v>
+        <v>5727</v>
       </c>
       <c r="J115" s="25" t="s">
-        <v>5727</v>
+        <v>5728</v>
       </c>
       <c r="K115" s="23" t="s">
-        <v>5728</v>
+        <v>5729</v>
       </c>
       <c r="L115" s="25" t="s">
-        <v>5729</v>
+        <v>5730</v>
       </c>
       <c r="M115" s="10"/>
       <c r="N115" s="10"/>
@@ -57422,40 +57425,40 @@
     </row>
     <row r="116" ht="18.75" customHeight="1">
       <c r="A116" s="23" t="s">
-        <v>5718</v>
+        <v>5719</v>
       </c>
       <c r="B116" s="25" t="s">
         <v>4883</v>
       </c>
       <c r="C116" s="23" t="s">
-        <v>5720</v>
+        <v>5721</v>
       </c>
       <c r="D116" s="25" t="s">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="E116" s="23" t="s">
-        <v>5722</v>
+        <v>5723</v>
       </c>
       <c r="F116" s="25" t="s">
-        <v>5712</v>
+        <v>5713</v>
       </c>
       <c r="G116" s="23" t="s">
-        <v>5724</v>
+        <v>5725</v>
       </c>
       <c r="H116" s="25" t="s">
-        <v>5730</v>
+        <v>5731</v>
       </c>
       <c r="I116" s="23" t="s">
-        <v>5726</v>
+        <v>5727</v>
       </c>
       <c r="J116" s="25" t="s">
-        <v>5731</v>
+        <v>5732</v>
       </c>
       <c r="K116" s="23" t="s">
-        <v>5728</v>
+        <v>5729</v>
       </c>
       <c r="L116" s="25" t="s">
-        <v>5717</v>
+        <v>5718</v>
       </c>
       <c r="M116" s="10"/>
       <c r="N116" s="10"/>
@@ -57467,40 +57470,40 @@
     </row>
     <row r="117" ht="18.75" customHeight="1">
       <c r="A117" s="23" t="s">
-        <v>5732</v>
+        <v>5733</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>5733</v>
+        <v>5734</v>
       </c>
       <c r="C117" s="23" t="s">
-        <v>5734</v>
+        <v>5735</v>
       </c>
       <c r="D117" s="25" t="s">
-        <v>5735</v>
+        <v>5736</v>
       </c>
       <c r="E117" s="23" t="s">
-        <v>5736</v>
+        <v>5737</v>
       </c>
       <c r="F117" s="25" t="s">
-        <v>5737</v>
+        <v>5738</v>
       </c>
       <c r="G117" s="23" t="s">
-        <v>5738</v>
+        <v>5739</v>
       </c>
       <c r="H117" s="25" t="s">
-        <v>5739</v>
+        <v>5740</v>
       </c>
       <c r="I117" s="23" t="s">
-        <v>5740</v>
+        <v>5741</v>
       </c>
       <c r="J117" s="25" t="s">
-        <v>5741</v>
+        <v>5742</v>
       </c>
       <c r="K117" s="23" t="s">
-        <v>5742</v>
+        <v>5743</v>
       </c>
       <c r="L117" s="25" t="s">
-        <v>5743</v>
+        <v>5744</v>
       </c>
       <c r="M117" s="10"/>
       <c r="N117" s="10"/>
@@ -57512,40 +57515,40 @@
     </row>
     <row r="118" ht="18.75" customHeight="1">
       <c r="A118" s="23" t="s">
-        <v>5744</v>
+        <v>5745</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>5745</v>
+        <v>5746</v>
       </c>
       <c r="C118" s="23" t="s">
-        <v>5746</v>
+        <v>5747</v>
       </c>
       <c r="D118" s="25" t="s">
-        <v>5747</v>
+        <v>5748</v>
       </c>
       <c r="E118" s="23" t="s">
-        <v>5748</v>
+        <v>5749</v>
       </c>
       <c r="F118" s="25" t="s">
-        <v>5749</v>
+        <v>5750</v>
       </c>
       <c r="G118" s="23" t="s">
-        <v>5750</v>
+        <v>5751</v>
       </c>
       <c r="H118" s="25" t="s">
-        <v>5751</v>
+        <v>5752</v>
       </c>
       <c r="I118" s="23" t="s">
-        <v>5752</v>
+        <v>5753</v>
       </c>
       <c r="J118" s="25" t="s">
-        <v>5753</v>
+        <v>5754</v>
       </c>
       <c r="K118" s="23" t="s">
-        <v>5754</v>
+        <v>5755</v>
       </c>
       <c r="L118" s="25" t="s">
-        <v>5755</v>
+        <v>5756</v>
       </c>
       <c r="M118" s="10"/>
       <c r="N118" s="10"/>
@@ -57557,40 +57560,40 @@
     </row>
     <row r="119" ht="18.75" customHeight="1">
       <c r="A119" s="36" t="s">
-        <v>5756</v>
+        <v>5757</v>
       </c>
       <c r="B119" s="28" t="s">
-        <v>5757</v>
+        <v>5758</v>
       </c>
       <c r="C119" s="36" t="s">
-        <v>5758</v>
+        <v>5759</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>5759</v>
+        <v>5760</v>
       </c>
       <c r="E119" s="36" t="s">
-        <v>5760</v>
+        <v>5761</v>
       </c>
       <c r="F119" s="28" t="s">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="G119" s="36" t="s">
-        <v>5762</v>
+        <v>5763</v>
       </c>
       <c r="H119" s="28" t="s">
-        <v>5763</v>
+        <v>5764</v>
       </c>
       <c r="I119" s="36" t="s">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="J119" s="28" t="s">
-        <v>5765</v>
+        <v>5766</v>
       </c>
       <c r="K119" s="36" t="s">
-        <v>5766</v>
+        <v>5767</v>
       </c>
       <c r="L119" s="28" t="s">
-        <v>5767</v>
+        <v>5768</v>
       </c>
       <c r="M119" s="10"/>
       <c r="N119" s="10"/>
@@ -57623,7 +57626,7 @@
     </row>
     <row r="121" ht="18.75" customHeight="1">
       <c r="A121" s="18" t="s">
-        <v>5768</v>
+        <v>5769</v>
       </c>
       <c r="B121" s="19"/>
       <c r="C121" s="10"/>
@@ -57646,7 +57649,7 @@
     </row>
     <row r="122" ht="18.75" customHeight="1">
       <c r="A122" s="23" t="s">
-        <v>5769</v>
+        <v>5770</v>
       </c>
       <c r="B122" s="22"/>
       <c r="C122" s="10"/>
@@ -57669,7 +57672,7 @@
     </row>
     <row r="123" ht="18.75" customHeight="1">
       <c r="A123" s="23" t="s">
-        <v>5770</v>
+        <v>5771</v>
       </c>
       <c r="B123" s="22"/>
       <c r="C123" s="10"/>
@@ -57692,7 +57695,7 @@
     </row>
     <row r="124" ht="18.75" customHeight="1">
       <c r="A124" s="23" t="s">
-        <v>5771</v>
+        <v>5772</v>
       </c>
       <c r="B124" s="22"/>
       <c r="C124" s="10"/>
@@ -57715,10 +57718,10 @@
     </row>
     <row r="125" ht="18.75" customHeight="1">
       <c r="A125" s="21" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="B125" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="10"/>
@@ -57743,7 +57746,7 @@
         <v>1687</v>
       </c>
       <c r="B126" s="25" t="s">
-        <v>5772</v>
+        <v>5773</v>
       </c>
       <c r="C126" s="10"/>
       <c r="D126" s="10"/>
@@ -57765,10 +57768,10 @@
     </row>
     <row r="127" ht="18.75" customHeight="1">
       <c r="A127" s="23" t="s">
-        <v>5773</v>
+        <v>5774</v>
       </c>
       <c r="B127" s="25" t="s">
-        <v>5774</v>
+        <v>5775</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="10"/>
@@ -57790,10 +57793,10 @@
     </row>
     <row r="128" ht="18.75" customHeight="1">
       <c r="A128" s="23" t="s">
+        <v>5774</v>
+      </c>
+      <c r="B128" s="25" t="s">
         <v>5773</v>
-      </c>
-      <c r="B128" s="25" t="s">
-        <v>5772</v>
       </c>
       <c r="C128" s="10"/>
       <c r="D128" s="10"/>
@@ -57815,10 +57818,10 @@
     </row>
     <row r="129" ht="18.75" customHeight="1">
       <c r="A129" s="23" t="s">
-        <v>5775</v>
+        <v>5776</v>
       </c>
       <c r="B129" s="25" t="s">
-        <v>5776</v>
+        <v>5777</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="10"/>
@@ -57840,10 +57843,10 @@
     </row>
     <row r="130" ht="18.75" customHeight="1">
       <c r="A130" s="23" t="s">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="B130" s="25" t="s">
-        <v>5778</v>
+        <v>5779</v>
       </c>
       <c r="C130" s="10"/>
       <c r="D130" s="10"/>
@@ -57865,10 +57868,10 @@
     </row>
     <row r="131" ht="18.75" customHeight="1">
       <c r="A131" s="36" t="s">
-        <v>5779</v>
+        <v>5780</v>
       </c>
       <c r="B131" s="28" t="s">
-        <v>5780</v>
+        <v>5781</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="10"/>
@@ -57911,175 +57914,175 @@
     </row>
     <row r="133" ht="18.75" customHeight="1">
       <c r="A133" s="18" t="s">
-        <v>5781</v>
+        <v>5782</v>
       </c>
       <c r="B133" s="19"/>
       <c r="C133" s="18" t="s">
-        <v>5782</v>
+        <v>5783</v>
       </c>
       <c r="D133" s="19"/>
       <c r="E133" s="18" t="s">
-        <v>5783</v>
+        <v>5784</v>
       </c>
       <c r="F133" s="19"/>
       <c r="G133" s="18" t="s">
-        <v>5784</v>
+        <v>5785</v>
       </c>
       <c r="H133" s="19"/>
       <c r="I133" s="18" t="s">
-        <v>5785</v>
+        <v>5786</v>
       </c>
       <c r="J133" s="19"/>
       <c r="K133" s="18" t="s">
-        <v>5786</v>
+        <v>5787</v>
       </c>
       <c r="L133" s="19"/>
       <c r="M133" s="10"/>
       <c r="N133" s="10"/>
       <c r="O133" s="10"/>
       <c r="P133" s="8" t="s">
-        <v>5787</v>
+        <v>5788</v>
       </c>
     </row>
     <row r="134" ht="18.75" customHeight="1">
       <c r="A134" s="21" t="s">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="B134" s="22"/>
       <c r="C134" s="23" t="s">
-        <v>5788</v>
+        <v>5789</v>
       </c>
       <c r="D134" s="22"/>
       <c r="E134" s="23" t="s">
-        <v>5789</v>
+        <v>5790</v>
       </c>
       <c r="F134" s="22"/>
       <c r="G134" s="23" t="s">
-        <v>5790</v>
+        <v>5791</v>
       </c>
       <c r="H134" s="22"/>
       <c r="I134" s="23" t="s">
-        <v>5791</v>
+        <v>5792</v>
       </c>
       <c r="J134" s="22"/>
       <c r="K134" s="23" t="s">
-        <v>5792</v>
+        <v>5793</v>
       </c>
       <c r="L134" s="22"/>
       <c r="M134" s="10"/>
       <c r="N134" s="10"/>
       <c r="O134" s="10"/>
       <c r="P134" s="8" t="s">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="Q134" s="10" t="s">
-        <v>5793</v>
+        <v>5794</v>
       </c>
     </row>
     <row r="135" ht="18.75" customHeight="1">
       <c r="A135" s="21" t="s">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="B135" s="22"/>
       <c r="C135" s="23" t="s">
-        <v>5794</v>
+        <v>5795</v>
       </c>
       <c r="D135" s="22"/>
       <c r="E135" s="23" t="s">
-        <v>5795</v>
+        <v>5796</v>
       </c>
       <c r="F135" s="22"/>
       <c r="G135" s="23" t="s">
-        <v>5796</v>
+        <v>5797</v>
       </c>
       <c r="H135" s="22"/>
       <c r="I135" s="23" t="s">
-        <v>5797</v>
+        <v>5798</v>
       </c>
       <c r="J135" s="22"/>
       <c r="K135" s="23" t="s">
-        <v>5798</v>
+        <v>5799</v>
       </c>
       <c r="L135" s="22"/>
       <c r="M135" s="10"/>
       <c r="N135" s="10"/>
       <c r="O135" s="10"/>
       <c r="P135" s="8" t="s">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="Q135" s="10" t="s">
-        <v>5799</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="136" ht="18.75" customHeight="1">
       <c r="A136" s="21" t="s">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="B136" s="22"/>
       <c r="C136" s="23" t="s">
-        <v>5800</v>
+        <v>5801</v>
       </c>
       <c r="D136" s="22"/>
       <c r="E136" s="23" t="s">
-        <v>5801</v>
+        <v>5802</v>
       </c>
       <c r="F136" s="22"/>
       <c r="G136" s="23" t="s">
-        <v>5802</v>
+        <v>5803</v>
       </c>
       <c r="H136" s="22"/>
       <c r="I136" s="23" t="s">
-        <v>5803</v>
+        <v>5804</v>
       </c>
       <c r="J136" s="22"/>
       <c r="K136" s="23" t="s">
-        <v>5804</v>
+        <v>5805</v>
       </c>
       <c r="L136" s="22"/>
       <c r="M136" s="10"/>
       <c r="N136" s="10"/>
       <c r="O136" s="10"/>
       <c r="P136" s="8" t="s">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="Q136" s="10" t="s">
-        <v>5805</v>
+        <v>5806</v>
       </c>
     </row>
     <row r="137" ht="18.75" customHeight="1">
       <c r="A137" s="21" t="s">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="B137" s="22"/>
       <c r="C137" s="21" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D137" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="E137" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="E137" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="F137" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="G137" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="G137" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="H137" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="I137" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="I137" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="J137" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="K137" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="K137" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="L137" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="M137" s="10"/>
       <c r="N137" s="10"/>
@@ -58087,10 +58090,10 @@
       <c r="P137" s="8"/>
       <c r="Q137" s="8"/>
       <c r="R137" s="8" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="S137" s="8" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
     </row>
     <row r="138" ht="18.75" customHeight="1">
@@ -58098,34 +58101,34 @@
         <v>4955</v>
       </c>
       <c r="B138" s="24" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C138" s="23" t="s">
         <v>993</v>
       </c>
       <c r="D138" s="25" t="s">
-        <v>5806</v>
+        <v>5807</v>
       </c>
       <c r="E138" s="23" t="s">
-        <v>5807</v>
+        <v>5808</v>
       </c>
       <c r="F138" s="25" t="s">
-        <v>5808</v>
+        <v>5809</v>
       </c>
       <c r="G138" s="23" t="s">
-        <v>5809</v>
+        <v>5810</v>
       </c>
       <c r="H138" s="25" t="s">
-        <v>5810</v>
+        <v>5811</v>
       </c>
       <c r="I138" s="23" t="s">
-        <v>5811</v>
+        <v>5812</v>
       </c>
       <c r="J138" s="25" t="s">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="K138" s="23" t="s">
-        <v>5813</v>
+        <v>5814</v>
       </c>
       <c r="L138" s="25" t="s">
         <v>4145</v>
@@ -58137,13 +58140,13 @@
         <v>4955</v>
       </c>
       <c r="Q138" s="8" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="R138" s="10" t="s">
-        <v>5814</v>
+        <v>5815</v>
       </c>
       <c r="S138" s="10" t="s">
-        <v>5815</v>
+        <v>5816</v>
       </c>
     </row>
     <row r="139" ht="18.75" customHeight="1">
@@ -58152,34 +58155,34 @@
         <v>4492</v>
       </c>
       <c r="C139" s="23" t="s">
-        <v>5816</v>
+        <v>5817</v>
       </c>
       <c r="D139" s="25" t="s">
-        <v>5817</v>
+        <v>5818</v>
       </c>
       <c r="E139" s="23" t="s">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F139" s="25" t="s">
-        <v>5819</v>
+        <v>5820</v>
       </c>
       <c r="G139" s="23" t="s">
         <v>4215</v>
       </c>
       <c r="H139" s="25" t="s">
-        <v>5820</v>
+        <v>5821</v>
       </c>
       <c r="I139" s="23" t="s">
-        <v>5821</v>
+        <v>5822</v>
       </c>
       <c r="J139" s="25" t="s">
-        <v>5822</v>
+        <v>5823</v>
       </c>
       <c r="K139" s="23" t="s">
-        <v>5823</v>
+        <v>5824</v>
       </c>
       <c r="L139" s="25" t="s">
-        <v>5824</v>
+        <v>5825</v>
       </c>
       <c r="M139" s="10"/>
       <c r="N139" s="10"/>
@@ -58188,43 +58191,43 @@
         <v>4492</v>
       </c>
       <c r="R139" s="10" t="s">
-        <v>5825</v>
+        <v>5826</v>
       </c>
       <c r="S139" s="10" t="s">
-        <v>5826</v>
+        <v>5827</v>
       </c>
     </row>
     <row r="140" ht="18.75" customHeight="1">
       <c r="A140" s="26"/>
       <c r="B140" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C140" s="23" t="s">
-        <v>5816</v>
+        <v>5817</v>
       </c>
       <c r="D140" s="25" t="s">
-        <v>5806</v>
+        <v>5807</v>
       </c>
       <c r="E140" s="23" t="s">
-        <v>5818</v>
+        <v>5819</v>
       </c>
       <c r="F140" s="25" t="s">
-        <v>5808</v>
+        <v>5809</v>
       </c>
       <c r="G140" s="23" t="s">
         <v>4215</v>
       </c>
       <c r="H140" s="25" t="s">
-        <v>5810</v>
+        <v>5811</v>
       </c>
       <c r="I140" s="23" t="s">
-        <v>5821</v>
+        <v>5822</v>
       </c>
       <c r="J140" s="25" t="s">
-        <v>5812</v>
+        <v>5813</v>
       </c>
       <c r="K140" s="23" t="s">
-        <v>5823</v>
+        <v>5824</v>
       </c>
       <c r="L140" s="25" t="s">
         <v>4145</v>
@@ -58233,13 +58236,13 @@
       <c r="N140" s="10"/>
       <c r="O140" s="10"/>
       <c r="Q140" s="8" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="R140" s="10" t="s">
-        <v>5825</v>
+        <v>5826</v>
       </c>
       <c r="S140" s="10" t="s">
-        <v>5815</v>
+        <v>5816</v>
       </c>
     </row>
     <row r="141" ht="18.75" customHeight="1">
@@ -58250,34 +58253,34 @@
         <v>4317</v>
       </c>
       <c r="C141" s="23" t="s">
-        <v>5827</v>
+        <v>5828</v>
       </c>
       <c r="D141" s="25" t="s">
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="E141" s="23" t="s">
-        <v>5829</v>
+        <v>5830</v>
       </c>
       <c r="F141" s="25" t="s">
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="G141" s="23" t="s">
-        <v>5831</v>
+        <v>5832</v>
       </c>
       <c r="H141" s="25" t="s">
-        <v>5832</v>
+        <v>5833</v>
       </c>
       <c r="I141" s="23" t="s">
-        <v>5833</v>
+        <v>5834</v>
       </c>
       <c r="J141" s="25" t="s">
-        <v>5834</v>
+        <v>5835</v>
       </c>
       <c r="K141" s="23" t="s">
-        <v>5835</v>
+        <v>5836</v>
       </c>
       <c r="L141" s="25" t="s">
-        <v>5836</v>
+        <v>5837</v>
       </c>
       <c r="M141" s="10"/>
       <c r="N141" s="10"/>
@@ -58289,10 +58292,10 @@
         <v>4317</v>
       </c>
       <c r="R141" s="10" t="s">
-        <v>5837</v>
+        <v>5838</v>
       </c>
       <c r="S141" s="10" t="s">
-        <v>5838</v>
+        <v>5839</v>
       </c>
     </row>
     <row r="142" ht="18.75" customHeight="1">
@@ -58300,34 +58303,34 @@
         <v>4442</v>
       </c>
       <c r="C142" s="23" t="s">
-        <v>5839</v>
+        <v>5840</v>
       </c>
       <c r="D142" s="25" t="s">
-        <v>5840</v>
+        <v>5841</v>
       </c>
       <c r="E142" s="23" t="s">
-        <v>5841</v>
+        <v>5842</v>
       </c>
       <c r="F142" s="25" t="s">
-        <v>5842</v>
+        <v>5843</v>
       </c>
       <c r="G142" s="23" t="s">
-        <v>5843</v>
+        <v>5844</v>
       </c>
       <c r="H142" s="25" t="s">
-        <v>5844</v>
+        <v>5845</v>
       </c>
       <c r="I142" s="23" t="s">
-        <v>5845</v>
+        <v>5846</v>
       </c>
       <c r="J142" s="25" t="s">
-        <v>5846</v>
+        <v>5847</v>
       </c>
       <c r="K142" s="23" t="s">
-        <v>5847</v>
+        <v>5848</v>
       </c>
       <c r="L142" s="25" t="s">
-        <v>5848</v>
+        <v>5849</v>
       </c>
       <c r="M142" s="10"/>
       <c r="N142" s="10"/>
@@ -58336,87 +58339,87 @@
         <v>4442</v>
       </c>
       <c r="R142" s="10" t="s">
-        <v>5849</v>
+        <v>5850</v>
       </c>
       <c r="S142" s="10" t="s">
-        <v>5850</v>
+        <v>5851</v>
       </c>
     </row>
     <row r="143" ht="18.75" customHeight="1">
       <c r="B143" s="24" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C143" s="23" t="s">
-        <v>5851</v>
+        <v>5852</v>
       </c>
       <c r="D143" s="25" t="s">
-        <v>5852</v>
+        <v>5853</v>
       </c>
       <c r="E143" s="23" t="s">
-        <v>5853</v>
+        <v>5854</v>
       </c>
       <c r="F143" s="25" t="s">
-        <v>5854</v>
+        <v>5855</v>
       </c>
       <c r="G143" s="23" t="s">
-        <v>5855</v>
+        <v>5856</v>
       </c>
       <c r="H143" s="25" t="s">
-        <v>5856</v>
+        <v>5857</v>
       </c>
       <c r="I143" s="23" t="s">
-        <v>5857</v>
+        <v>5858</v>
       </c>
       <c r="J143" s="25" t="s">
-        <v>5858</v>
+        <v>5859</v>
       </c>
       <c r="K143" s="36" t="s">
-        <v>5859</v>
+        <v>5860</v>
       </c>
       <c r="L143" s="28" t="s">
-        <v>5860</v>
+        <v>5861</v>
       </c>
       <c r="M143" s="10"/>
       <c r="N143" s="10"/>
       <c r="O143" s="10"/>
       <c r="Q143" s="8" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="R143" s="10" t="s">
-        <v>5861</v>
+        <v>5862</v>
       </c>
       <c r="S143" s="10" t="s">
-        <v>5862</v>
+        <v>5863</v>
       </c>
     </row>
     <row r="144" ht="18.75" customHeight="1">
       <c r="A144" s="21" t="s">
-        <v>5273</v>
+        <v>5274</v>
       </c>
       <c r="B144" s="22"/>
       <c r="C144" s="8" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D144" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="E144" s="8" t="s">
         <v>5221</v>
       </c>
-      <c r="E144" s="8" t="s">
-        <v>5220</v>
-      </c>
       <c r="F144" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="G144" s="8" t="s">
         <v>5221</v>
       </c>
-      <c r="G144" s="8" t="s">
-        <v>5220</v>
-      </c>
       <c r="H144" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="I144" s="8" t="s">
         <v>5221</v>
       </c>
-      <c r="I144" s="8" t="s">
-        <v>5220</v>
-      </c>
       <c r="J144" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="K144" s="10"/>
       <c r="L144" s="10"/>
@@ -58433,31 +58436,31 @@
         <v>4955</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C145" s="23" t="s">
-        <v>5863</v>
+        <v>5864</v>
       </c>
       <c r="D145" s="25" t="s">
-        <v>5864</v>
+        <v>5865</v>
       </c>
       <c r="E145" s="23" t="s">
-        <v>5865</v>
+        <v>5866</v>
       </c>
       <c r="F145" s="25" t="s">
-        <v>5866</v>
+        <v>5867</v>
       </c>
       <c r="G145" s="23" t="s">
-        <v>5867</v>
+        <v>5868</v>
       </c>
       <c r="H145" s="25" t="s">
-        <v>5868</v>
+        <v>5869</v>
       </c>
       <c r="I145" s="23" t="s">
-        <v>5869</v>
+        <v>5870</v>
       </c>
       <c r="J145" s="25" t="s">
-        <v>5870</v>
+        <v>5871</v>
       </c>
       <c r="K145" s="23"/>
       <c r="L145" s="10"/>
@@ -58495,7 +58498,7 @@
     <row r="147" ht="18.75" customHeight="1">
       <c r="A147" s="26"/>
       <c r="B147" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C147" s="26"/>
       <c r="D147" s="22"/>
@@ -58523,28 +58526,28 @@
         <v>4317</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>5871</v>
+        <v>5872</v>
       </c>
       <c r="D148" s="25" t="s">
-        <v>5872</v>
+        <v>5873</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>5873</v>
+        <v>5874</v>
       </c>
       <c r="F148" s="25" t="s">
-        <v>5874</v>
+        <v>5875</v>
       </c>
       <c r="G148" s="10" t="s">
-        <v>5875</v>
+        <v>5876</v>
       </c>
       <c r="H148" s="25" t="s">
-        <v>5876</v>
+        <v>5877</v>
       </c>
       <c r="I148" s="10" t="s">
-        <v>5877</v>
+        <v>5878</v>
       </c>
       <c r="J148" s="25" t="s">
-        <v>5878</v>
+        <v>5879</v>
       </c>
       <c r="K148" s="23"/>
       <c r="L148" s="10"/>
@@ -58562,28 +58565,28 @@
         <v>4442</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>5879</v>
+        <v>5880</v>
       </c>
       <c r="D149" s="25" t="s">
-        <v>5880</v>
+        <v>5881</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>5881</v>
+        <v>5882</v>
       </c>
       <c r="F149" s="25" t="s">
-        <v>5882</v>
+        <v>5883</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="H149" s="25" t="s">
-        <v>5884</v>
+        <v>5885</v>
       </c>
       <c r="I149" s="10" t="s">
-        <v>5885</v>
+        <v>5886</v>
       </c>
       <c r="J149" s="25" t="s">
-        <v>5886</v>
+        <v>5887</v>
       </c>
       <c r="K149" s="23"/>
       <c r="L149" s="10"/>
@@ -58598,7 +58601,7 @@
     <row r="150" ht="18.75" customHeight="1">
       <c r="A150" s="31"/>
       <c r="B150" s="32" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C150" s="33"/>
       <c r="D150" s="34"/>
@@ -58643,15 +58646,15 @@
       <c r="A152" s="10"/>
       <c r="B152" s="10"/>
       <c r="C152" s="18" t="s">
-        <v>5887</v>
+        <v>5888</v>
       </c>
       <c r="D152" s="19"/>
       <c r="E152" s="18" t="s">
-        <v>5888</v>
+        <v>5889</v>
       </c>
       <c r="F152" s="19"/>
       <c r="G152" s="18" t="s">
-        <v>5889</v>
+        <v>5890</v>
       </c>
       <c r="H152" s="19"/>
       <c r="I152" s="10"/>
@@ -58670,15 +58673,15 @@
       <c r="A153" s="10"/>
       <c r="B153" s="10"/>
       <c r="C153" s="23" t="s">
-        <v>5890</v>
+        <v>5891</v>
       </c>
       <c r="D153" s="22"/>
       <c r="E153" s="23" t="s">
-        <v>5891</v>
+        <v>5892</v>
       </c>
       <c r="F153" s="22"/>
       <c r="G153" s="23" t="s">
-        <v>5892</v>
+        <v>5893</v>
       </c>
       <c r="H153" s="22"/>
       <c r="I153" s="10"/>
@@ -58697,15 +58700,15 @@
       <c r="A154" s="10"/>
       <c r="B154" s="10"/>
       <c r="C154" s="23" t="s">
-        <v>5893</v>
+        <v>5894</v>
       </c>
       <c r="D154" s="22"/>
       <c r="E154" s="23" t="s">
-        <v>5894</v>
+        <v>5895</v>
       </c>
       <c r="F154" s="22"/>
       <c r="G154" s="23" t="s">
-        <v>5895</v>
+        <v>5896</v>
       </c>
       <c r="H154" s="22"/>
       <c r="I154" s="10"/>
@@ -58724,11 +58727,11 @@
       <c r="A155" s="10"/>
       <c r="B155" s="10"/>
       <c r="C155" s="23" t="s">
-        <v>5896</v>
+        <v>5897</v>
       </c>
       <c r="D155" s="22"/>
       <c r="E155" s="23" t="s">
-        <v>5897</v>
+        <v>5898</v>
       </c>
       <c r="F155" s="22"/>
       <c r="G155" s="23" t="s">
@@ -58751,22 +58754,22 @@
       <c r="A156" s="10"/>
       <c r="B156" s="10"/>
       <c r="C156" s="21" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D156" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="E156" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="E156" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="F156" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="G156" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="G156" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="H156" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="I156" s="10"/>
       <c r="J156" s="10"/>
@@ -58784,22 +58787,22 @@
       <c r="A157" s="10"/>
       <c r="B157" s="10"/>
       <c r="C157" s="23" t="s">
-        <v>5898</v>
+        <v>5899</v>
       </c>
       <c r="D157" s="25" t="s">
-        <v>5899</v>
+        <v>5900</v>
       </c>
       <c r="E157" s="23" t="s">
-        <v>5900</v>
+        <v>5901</v>
       </c>
       <c r="F157" s="25" t="s">
-        <v>5901</v>
+        <v>5902</v>
       </c>
       <c r="G157" s="23" t="s">
-        <v>5902</v>
+        <v>5903</v>
       </c>
       <c r="H157" s="25" t="s">
-        <v>5903</v>
+        <v>5904</v>
       </c>
       <c r="I157" s="10"/>
       <c r="J157" s="10"/>
@@ -58817,22 +58820,22 @@
       <c r="A158" s="10"/>
       <c r="B158" s="10"/>
       <c r="C158" s="23" t="s">
-        <v>5904</v>
+        <v>5905</v>
       </c>
       <c r="D158" s="25" t="s">
-        <v>5905</v>
+        <v>5906</v>
       </c>
       <c r="E158" s="23" t="s">
-        <v>5906</v>
+        <v>5907</v>
       </c>
       <c r="F158" s="25" t="s">
-        <v>5907</v>
+        <v>5908</v>
       </c>
       <c r="G158" s="23" t="s">
-        <v>5908</v>
+        <v>5909</v>
       </c>
       <c r="H158" s="25" t="s">
-        <v>5909</v>
+        <v>5910</v>
       </c>
       <c r="I158" s="10"/>
       <c r="J158" s="10"/>
@@ -58850,22 +58853,22 @@
       <c r="A159" s="10"/>
       <c r="B159" s="10"/>
       <c r="C159" s="23" t="s">
+        <v>5905</v>
+      </c>
+      <c r="D159" s="25" t="s">
+        <v>5900</v>
+      </c>
+      <c r="E159" s="23" t="s">
+        <v>5907</v>
+      </c>
+      <c r="F159" s="25" t="s">
+        <v>5902</v>
+      </c>
+      <c r="G159" s="23" t="s">
+        <v>5909</v>
+      </c>
+      <c r="H159" s="25" t="s">
         <v>5904</v>
-      </c>
-      <c r="D159" s="25" t="s">
-        <v>5899</v>
-      </c>
-      <c r="E159" s="23" t="s">
-        <v>5906</v>
-      </c>
-      <c r="F159" s="25" t="s">
-        <v>5901</v>
-      </c>
-      <c r="G159" s="23" t="s">
-        <v>5908</v>
-      </c>
-      <c r="H159" s="25" t="s">
-        <v>5903</v>
       </c>
       <c r="I159" s="10"/>
       <c r="J159" s="10"/>
@@ -58883,22 +58886,22 @@
       <c r="A160" s="10"/>
       <c r="B160" s="10"/>
       <c r="C160" s="23" t="s">
-        <v>5910</v>
+        <v>5911</v>
       </c>
       <c r="D160" s="25" t="s">
-        <v>5911</v>
+        <v>5912</v>
       </c>
       <c r="E160" s="23" t="s">
-        <v>5912</v>
+        <v>5913</v>
       </c>
       <c r="F160" s="25" t="s">
-        <v>5913</v>
+        <v>5914</v>
       </c>
       <c r="G160" s="23" t="s">
-        <v>5914</v>
+        <v>5915</v>
       </c>
       <c r="H160" s="25" t="s">
-        <v>5915</v>
+        <v>5916</v>
       </c>
       <c r="I160" s="10"/>
       <c r="J160" s="10"/>
@@ -58916,22 +58919,22 @@
       <c r="A161" s="10"/>
       <c r="B161" s="10"/>
       <c r="C161" s="23" t="s">
-        <v>5916</v>
+        <v>5917</v>
       </c>
       <c r="D161" s="25" t="s">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="E161" s="23" t="s">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="F161" s="25" t="s">
-        <v>5919</v>
+        <v>5920</v>
       </c>
       <c r="G161" s="23" t="s">
-        <v>5920</v>
+        <v>5921</v>
       </c>
       <c r="H161" s="25" t="s">
-        <v>5921</v>
+        <v>5922</v>
       </c>
       <c r="I161" s="10"/>
       <c r="J161" s="10"/>
@@ -58949,22 +58952,22 @@
       <c r="A162" s="10"/>
       <c r="B162" s="10"/>
       <c r="C162" s="36" t="s">
-        <v>5922</v>
+        <v>5923</v>
       </c>
       <c r="D162" s="28" t="s">
-        <v>5923</v>
+        <v>5924</v>
       </c>
       <c r="E162" s="36" t="s">
-        <v>5924</v>
+        <v>5925</v>
       </c>
       <c r="F162" s="28" t="s">
-        <v>5925</v>
+        <v>5926</v>
       </c>
       <c r="G162" s="36" t="s">
-        <v>5926</v>
+        <v>5927</v>
       </c>
       <c r="H162" s="28" t="s">
-        <v>5927</v>
+        <v>5928</v>
       </c>
       <c r="I162" s="10"/>
       <c r="J162" s="10"/>
@@ -59001,19 +59004,19 @@
     </row>
     <row r="164" ht="18.75" customHeight="1">
       <c r="A164" s="18" t="s">
-        <v>5928</v>
+        <v>5929</v>
       </c>
       <c r="B164" s="19"/>
       <c r="C164" s="18" t="s">
-        <v>5929</v>
+        <v>5930</v>
       </c>
       <c r="D164" s="19"/>
       <c r="E164" s="18" t="s">
-        <v>5930</v>
+        <v>5931</v>
       </c>
       <c r="F164" s="19"/>
       <c r="G164" s="18" t="s">
-        <v>5931</v>
+        <v>5932</v>
       </c>
       <c r="H164" s="19"/>
       <c r="J164" s="10"/>
@@ -59029,19 +59032,19 @@
     </row>
     <row r="165" ht="18.75" customHeight="1">
       <c r="A165" s="21" t="s">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="B165" s="22"/>
       <c r="C165" s="23" t="s">
-        <v>5932</v>
+        <v>5933</v>
       </c>
       <c r="D165" s="22"/>
       <c r="E165" s="23" t="s">
-        <v>5933</v>
+        <v>5934</v>
       </c>
       <c r="F165" s="22"/>
       <c r="G165" s="23" t="s">
-        <v>5934</v>
+        <v>5935</v>
       </c>
       <c r="H165" s="22"/>
       <c r="J165" s="10"/>
@@ -59057,19 +59060,19 @@
     </row>
     <row r="166" ht="18.75" customHeight="1">
       <c r="A166" s="21" t="s">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="B166" s="22"/>
       <c r="C166" s="23" t="s">
-        <v>5935</v>
+        <v>5936</v>
       </c>
       <c r="D166" s="22"/>
       <c r="E166" s="23" t="s">
-        <v>5936</v>
+        <v>5937</v>
       </c>
       <c r="F166" s="22"/>
       <c r="G166" s="23" t="s">
-        <v>5937</v>
+        <v>5938</v>
       </c>
       <c r="H166" s="22"/>
       <c r="J166" s="10"/>
@@ -59085,19 +59088,19 @@
     </row>
     <row r="167" ht="18.75" customHeight="1">
       <c r="A167" s="21" t="s">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="B167" s="22"/>
       <c r="C167" s="23" t="s">
-        <v>5938</v>
+        <v>5939</v>
       </c>
       <c r="D167" s="22"/>
       <c r="E167" s="23" t="s">
-        <v>5939</v>
+        <v>5940</v>
       </c>
       <c r="F167" s="22"/>
       <c r="G167" s="23" t="s">
-        <v>5940</v>
+        <v>5941</v>
       </c>
       <c r="H167" s="22"/>
       <c r="J167" s="10"/>
@@ -59113,26 +59116,26 @@
     </row>
     <row r="168" ht="18.75" customHeight="1">
       <c r="A168" s="21" t="s">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="B168" s="22"/>
       <c r="C168" s="21" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D168" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="E168" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="E168" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="F168" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="G168" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="G168" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="H168" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="J168" s="10"/>
       <c r="K168" s="10"/>
@@ -59150,25 +59153,25 @@
         <v>4955</v>
       </c>
       <c r="B169" s="24" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C169" s="23" t="s">
-        <v>5941</v>
+        <v>5942</v>
       </c>
       <c r="D169" s="25" t="s">
-        <v>5942</v>
+        <v>5943</v>
       </c>
       <c r="E169" s="23" t="s">
-        <v>5943</v>
+        <v>5944</v>
       </c>
       <c r="F169" s="25" t="s">
-        <v>5944</v>
+        <v>5945</v>
       </c>
       <c r="G169" s="23" t="s">
-        <v>5945</v>
+        <v>5946</v>
       </c>
       <c r="H169" s="25" t="s">
-        <v>5946</v>
+        <v>5947</v>
       </c>
       <c r="J169" s="10"/>
       <c r="K169" s="10"/>
@@ -59187,22 +59190,22 @@
         <v>4492</v>
       </c>
       <c r="C170" s="23" t="s">
-        <v>5947</v>
+        <v>5948</v>
       </c>
       <c r="D170" s="25" t="s">
-        <v>5948</v>
+        <v>5949</v>
       </c>
       <c r="E170" s="23" t="s">
-        <v>5949</v>
+        <v>5950</v>
       </c>
       <c r="F170" s="25" t="s">
-        <v>5950</v>
+        <v>5951</v>
       </c>
       <c r="G170" s="23" t="s">
-        <v>5951</v>
+        <v>5952</v>
       </c>
       <c r="H170" s="25" t="s">
-        <v>5952</v>
+        <v>5953</v>
       </c>
       <c r="J170" s="10"/>
       <c r="K170" s="10"/>
@@ -59218,25 +59221,25 @@
     <row r="171" ht="18.75" customHeight="1">
       <c r="A171" s="26"/>
       <c r="B171" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C171" s="23" t="s">
+        <v>5948</v>
+      </c>
+      <c r="D171" s="25" t="s">
+        <v>5943</v>
+      </c>
+      <c r="E171" s="23" t="s">
+        <v>5950</v>
+      </c>
+      <c r="F171" s="25" t="s">
+        <v>5945</v>
+      </c>
+      <c r="G171" s="23" t="s">
+        <v>5952</v>
+      </c>
+      <c r="H171" s="25" t="s">
         <v>5947</v>
-      </c>
-      <c r="D171" s="25" t="s">
-        <v>5942</v>
-      </c>
-      <c r="E171" s="23" t="s">
-        <v>5949</v>
-      </c>
-      <c r="F171" s="25" t="s">
-        <v>5944</v>
-      </c>
-      <c r="G171" s="23" t="s">
-        <v>5951</v>
-      </c>
-      <c r="H171" s="25" t="s">
-        <v>5946</v>
       </c>
       <c r="J171" s="10"/>
       <c r="K171" s="10"/>
@@ -59257,22 +59260,22 @@
         <v>4317</v>
       </c>
       <c r="C172" s="23" t="s">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="D172" s="25" t="s">
-        <v>5954</v>
+        <v>5955</v>
       </c>
       <c r="E172" s="23" t="s">
-        <v>5955</v>
+        <v>5956</v>
       </c>
       <c r="F172" s="25" t="s">
-        <v>5956</v>
+        <v>5957</v>
       </c>
       <c r="G172" s="23" t="s">
-        <v>5957</v>
+        <v>5958</v>
       </c>
       <c r="H172" s="25" t="s">
-        <v>5958</v>
+        <v>5959</v>
       </c>
       <c r="J172" s="10"/>
       <c r="K172" s="10"/>
@@ -59290,22 +59293,22 @@
         <v>4442</v>
       </c>
       <c r="C173" s="23" t="s">
-        <v>5959</v>
+        <v>5960</v>
       </c>
       <c r="D173" s="25" t="s">
-        <v>5960</v>
+        <v>5961</v>
       </c>
       <c r="E173" s="23" t="s">
-        <v>5961</v>
+        <v>5962</v>
       </c>
       <c r="F173" s="25" t="s">
-        <v>5962</v>
+        <v>5963</v>
       </c>
       <c r="G173" s="23" t="s">
-        <v>5963</v>
+        <v>5964</v>
       </c>
       <c r="H173" s="25" t="s">
-        <v>5964</v>
+        <v>5965</v>
       </c>
       <c r="J173" s="10"/>
       <c r="K173" s="10"/>
@@ -59320,25 +59323,25 @@
     </row>
     <row r="174" ht="18.75" customHeight="1">
       <c r="B174" s="24" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C174" s="23" t="s">
-        <v>5965</v>
+        <v>5966</v>
       </c>
       <c r="D174" s="25" t="s">
-        <v>5966</v>
+        <v>5967</v>
       </c>
       <c r="E174" s="23" t="s">
-        <v>5967</v>
+        <v>5968</v>
       </c>
       <c r="F174" s="25" t="s">
-        <v>5968</v>
+        <v>5969</v>
       </c>
       <c r="G174" s="23" t="s">
-        <v>5969</v>
+        <v>5970</v>
       </c>
       <c r="H174" s="25" t="s">
-        <v>5970</v>
+        <v>5971</v>
       </c>
       <c r="J174" s="10"/>
       <c r="K174" s="10"/>
@@ -59353,14 +59356,14 @@
     </row>
     <row r="175" ht="18.75" customHeight="1">
       <c r="A175" s="21" t="s">
-        <v>5273</v>
+        <v>5274</v>
       </c>
       <c r="B175" s="22"/>
       <c r="C175" s="8" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D175" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="E175" s="38"/>
       <c r="F175" s="38"/>
@@ -59383,13 +59386,13 @@
         <v>4955</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C176" s="23" t="s">
-        <v>5971</v>
+        <v>5972</v>
       </c>
       <c r="D176" s="25" t="s">
-        <v>5972</v>
+        <v>5973</v>
       </c>
       <c r="E176" s="40"/>
       <c r="F176" s="40"/>
@@ -59433,7 +59436,7 @@
     <row r="178" ht="18.75" customHeight="1">
       <c r="A178" s="26"/>
       <c r="B178" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C178" s="26"/>
       <c r="D178" s="22"/>
@@ -59461,10 +59464,10 @@
         <v>4317</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>5973</v>
+        <v>5974</v>
       </c>
       <c r="D179" s="25" t="s">
-        <v>5974</v>
+        <v>5975</v>
       </c>
       <c r="E179" s="40"/>
       <c r="F179" s="40"/>
@@ -59488,10 +59491,10 @@
         <v>4442</v>
       </c>
       <c r="C180" s="10" t="s">
-        <v>5975</v>
+        <v>5976</v>
       </c>
       <c r="D180" s="25" t="s">
-        <v>5976</v>
+        <v>5977</v>
       </c>
       <c r="E180" s="40"/>
       <c r="F180" s="40"/>
@@ -59512,7 +59515,7 @@
     <row r="181" ht="18.75" customHeight="1">
       <c r="A181" s="31"/>
       <c r="B181" s="32" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C181" s="33"/>
       <c r="D181" s="34"/>
@@ -59555,19 +59558,19 @@
     </row>
     <row r="183" ht="18.75" customHeight="1">
       <c r="A183" s="18" t="s">
-        <v>5977</v>
+        <v>5978</v>
       </c>
       <c r="B183" s="19"/>
       <c r="C183" s="20" t="s">
-        <v>5978</v>
+        <v>5979</v>
       </c>
       <c r="D183" s="19"/>
       <c r="E183" s="20" t="s">
-        <v>5979</v>
+        <v>5980</v>
       </c>
       <c r="F183" s="19"/>
       <c r="G183" s="20" t="s">
-        <v>5980</v>
+        <v>5981</v>
       </c>
       <c r="H183" s="19"/>
       <c r="I183" s="10"/>
@@ -59584,19 +59587,19 @@
     </row>
     <row r="184" ht="18.75" customHeight="1">
       <c r="A184" s="21" t="s">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="B184" s="22"/>
       <c r="C184" s="10" t="s">
-        <v>5981</v>
+        <v>5982</v>
       </c>
       <c r="D184" s="22"/>
       <c r="E184" s="10" t="s">
-        <v>5793</v>
+        <v>5794</v>
       </c>
       <c r="F184" s="22"/>
       <c r="G184" s="10" t="s">
-        <v>5982</v>
+        <v>5983</v>
       </c>
       <c r="H184" s="22"/>
       <c r="I184" s="10"/>
@@ -59613,19 +59616,19 @@
     </row>
     <row r="185" ht="18.75" customHeight="1">
       <c r="A185" s="21" t="s">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="B185" s="22"/>
       <c r="C185" s="23" t="s">
-        <v>5983</v>
+        <v>5984</v>
       </c>
       <c r="D185" s="22"/>
       <c r="E185" s="23" t="s">
-        <v>5799</v>
+        <v>5800</v>
       </c>
       <c r="F185" s="22"/>
       <c r="G185" s="23" t="s">
-        <v>5984</v>
+        <v>5985</v>
       </c>
       <c r="H185" s="22"/>
       <c r="I185" s="10"/>
@@ -59642,19 +59645,19 @@
     </row>
     <row r="186" ht="18.75" customHeight="1">
       <c r="A186" s="21" t="s">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="B186" s="22"/>
       <c r="C186" s="23" t="s">
-        <v>5985</v>
+        <v>5986</v>
       </c>
       <c r="D186" s="22"/>
       <c r="E186" s="23" t="s">
-        <v>5805</v>
+        <v>5806</v>
       </c>
       <c r="F186" s="22"/>
       <c r="G186" s="23" t="s">
-        <v>5986</v>
+        <v>5987</v>
       </c>
       <c r="H186" s="22"/>
       <c r="I186" s="10"/>
@@ -59671,26 +59674,26 @@
     </row>
     <row r="187" ht="18.75" customHeight="1">
       <c r="A187" s="21" t="s">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="B187" s="22"/>
       <c r="C187" s="21" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D187" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="E187" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="E187" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="F187" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="G187" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="G187" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="H187" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="I187" s="10"/>
       <c r="J187" s="10"/>
@@ -59709,25 +59712,25 @@
         <v>4955</v>
       </c>
       <c r="B188" s="24" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C188" s="23" t="s">
-        <v>5987</v>
+        <v>5988</v>
       </c>
       <c r="D188" s="25" t="s">
-        <v>5988</v>
+        <v>5989</v>
       </c>
       <c r="E188" s="23" t="s">
-        <v>5814</v>
+        <v>5815</v>
       </c>
       <c r="F188" s="25" t="s">
-        <v>5815</v>
+        <v>5816</v>
       </c>
       <c r="G188" s="23" t="s">
-        <v>5989</v>
+        <v>5990</v>
       </c>
       <c r="H188" s="25" t="s">
-        <v>5990</v>
+        <v>5991</v>
       </c>
       <c r="I188" s="10"/>
       <c r="J188" s="10"/>
@@ -59747,22 +59750,22 @@
         <v>4492</v>
       </c>
       <c r="C189" s="23" t="s">
-        <v>5991</v>
+        <v>5992</v>
       </c>
       <c r="D189" s="25" t="s">
-        <v>5992</v>
+        <v>5993</v>
       </c>
       <c r="E189" s="23" t="s">
-        <v>5825</v>
+        <v>5826</v>
       </c>
       <c r="F189" s="25" t="s">
-        <v>5826</v>
+        <v>5827</v>
       </c>
       <c r="G189" s="23" t="s">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="H189" s="25" t="s">
-        <v>5994</v>
+        <v>5995</v>
       </c>
       <c r="I189" s="10"/>
       <c r="J189" s="10"/>
@@ -59779,25 +59782,25 @@
     <row r="190" ht="18.75" customHeight="1">
       <c r="A190" s="26"/>
       <c r="B190" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C190" s="23" t="s">
+        <v>5992</v>
+      </c>
+      <c r="D190" s="25" t="s">
+        <v>5989</v>
+      </c>
+      <c r="E190" s="23" t="s">
+        <v>5826</v>
+      </c>
+      <c r="F190" s="25" t="s">
+        <v>5816</v>
+      </c>
+      <c r="G190" s="23" t="s">
+        <v>5994</v>
+      </c>
+      <c r="H190" s="25" t="s">
         <v>5991</v>
-      </c>
-      <c r="D190" s="25" t="s">
-        <v>5988</v>
-      </c>
-      <c r="E190" s="23" t="s">
-        <v>5825</v>
-      </c>
-      <c r="F190" s="25" t="s">
-        <v>5815</v>
-      </c>
-      <c r="G190" s="23" t="s">
-        <v>5993</v>
-      </c>
-      <c r="H190" s="25" t="s">
-        <v>5990</v>
       </c>
       <c r="I190" s="10"/>
       <c r="J190" s="10"/>
@@ -59819,22 +59822,22 @@
         <v>4317</v>
       </c>
       <c r="C191" s="23" t="s">
-        <v>5995</v>
+        <v>5996</v>
       </c>
       <c r="D191" s="25" t="s">
-        <v>5996</v>
+        <v>5997</v>
       </c>
       <c r="E191" s="23" t="s">
-        <v>5837</v>
+        <v>5838</v>
       </c>
       <c r="F191" s="25" t="s">
-        <v>5838</v>
+        <v>5839</v>
       </c>
       <c r="G191" s="23" t="s">
-        <v>5997</v>
+        <v>5998</v>
       </c>
       <c r="H191" s="25" t="s">
-        <v>5998</v>
+        <v>5999</v>
       </c>
       <c r="I191" s="10"/>
       <c r="J191" s="10"/>
@@ -59854,22 +59857,22 @@
         <v>4442</v>
       </c>
       <c r="C192" s="23" t="s">
-        <v>5999</v>
+        <v>6000</v>
       </c>
       <c r="D192" s="25" t="s">
-        <v>6000</v>
+        <v>6001</v>
       </c>
       <c r="E192" s="23" t="s">
-        <v>5849</v>
+        <v>5850</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>5850</v>
+        <v>5851</v>
       </c>
       <c r="G192" s="23" t="s">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="H192" s="25" t="s">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="I192" s="10"/>
       <c r="J192" s="10"/>
@@ -59886,25 +59889,25 @@
     <row r="193" ht="18.75" customHeight="1">
       <c r="A193" s="31"/>
       <c r="B193" s="32" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C193" s="36" t="s">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="D193" s="28" t="s">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="E193" s="36" t="s">
-        <v>5861</v>
+        <v>5862</v>
       </c>
       <c r="F193" s="28" t="s">
-        <v>5862</v>
+        <v>5863</v>
       </c>
       <c r="G193" s="36" t="s">
-        <v>6005</v>
+        <v>6006</v>
       </c>
       <c r="H193" s="28" t="s">
-        <v>6006</v>
+        <v>6007</v>
       </c>
       <c r="I193" s="10"/>
       <c r="J193" s="10"/>
@@ -59941,11 +59944,11 @@
     </row>
     <row r="195" ht="18.75" customHeight="1">
       <c r="A195" s="18" t="s">
-        <v>6007</v>
+        <v>6008</v>
       </c>
       <c r="B195" s="19"/>
       <c r="C195" s="18" t="s">
-        <v>6008</v>
+        <v>6009</v>
       </c>
       <c r="D195" s="19"/>
       <c r="E195" s="10"/>
@@ -59966,11 +59969,11 @@
     </row>
     <row r="196" ht="18.75" customHeight="1">
       <c r="A196" s="21" t="s">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="B196" s="22"/>
       <c r="C196" s="23" t="s">
-        <v>6009</v>
+        <v>6010</v>
       </c>
       <c r="D196" s="22"/>
       <c r="E196" s="10"/>
@@ -59991,11 +59994,11 @@
     </row>
     <row r="197" ht="18.75" customHeight="1">
       <c r="A197" s="21" t="s">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="B197" s="22"/>
       <c r="C197" s="23" t="s">
-        <v>6010</v>
+        <v>6011</v>
       </c>
       <c r="D197" s="22"/>
       <c r="E197" s="10"/>
@@ -60016,11 +60019,11 @@
     </row>
     <row r="198" ht="18.75" customHeight="1">
       <c r="A198" s="21" t="s">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="B198" s="22"/>
       <c r="C198" s="23" t="s">
-        <v>6011</v>
+        <v>6012</v>
       </c>
       <c r="D198" s="22"/>
       <c r="E198" s="10"/>
@@ -60041,14 +60044,14 @@
     </row>
     <row r="199" ht="18.75" customHeight="1">
       <c r="A199" s="21" t="s">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="B199" s="22"/>
       <c r="C199" s="21" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D199" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="E199" s="10"/>
       <c r="F199" s="10"/>
@@ -60071,13 +60074,13 @@
         <v>4955</v>
       </c>
       <c r="B200" s="24" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C200" s="23" t="s">
-        <v>6012</v>
+        <v>6013</v>
       </c>
       <c r="D200" s="25" t="s">
-        <v>6013</v>
+        <v>6014</v>
       </c>
       <c r="E200" s="10"/>
       <c r="F200" s="10"/>
@@ -60101,10 +60104,10 @@
         <v>4492</v>
       </c>
       <c r="C201" s="23" t="s">
-        <v>6014</v>
+        <v>6015</v>
       </c>
       <c r="D201" s="25" t="s">
-        <v>6015</v>
+        <v>6016</v>
       </c>
       <c r="E201" s="10"/>
       <c r="F201" s="10"/>
@@ -60125,13 +60128,13 @@
     <row r="202" ht="18.75" customHeight="1">
       <c r="A202" s="26"/>
       <c r="B202" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C202" s="23" t="s">
+        <v>6015</v>
+      </c>
+      <c r="D202" s="25" t="s">
         <v>6014</v>
-      </c>
-      <c r="D202" s="25" t="s">
-        <v>6013</v>
       </c>
       <c r="E202" s="10"/>
       <c r="F202" s="10"/>
@@ -60157,10 +60160,10 @@
         <v>4317</v>
       </c>
       <c r="C203" s="23" t="s">
-        <v>6016</v>
+        <v>6017</v>
       </c>
       <c r="D203" s="25" t="s">
-        <v>6017</v>
+        <v>6018</v>
       </c>
       <c r="E203" s="10"/>
       <c r="F203" s="10"/>
@@ -60183,10 +60186,10 @@
         <v>4442</v>
       </c>
       <c r="C204" s="23" t="s">
-        <v>6018</v>
+        <v>6019</v>
       </c>
       <c r="D204" s="25" t="s">
-        <v>6019</v>
+        <v>6020</v>
       </c>
       <c r="E204" s="10"/>
       <c r="F204" s="10"/>
@@ -60206,13 +60209,13 @@
     </row>
     <row r="205" ht="18.75" customHeight="1">
       <c r="B205" s="24" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C205" s="23" t="s">
-        <v>6020</v>
+        <v>6021</v>
       </c>
       <c r="D205" s="25" t="s">
-        <v>6021</v>
+        <v>6022</v>
       </c>
       <c r="E205" s="10"/>
       <c r="F205" s="10"/>
@@ -60232,14 +60235,14 @@
     </row>
     <row r="206" ht="18.75" customHeight="1">
       <c r="A206" s="21" t="s">
-        <v>5273</v>
+        <v>5274</v>
       </c>
       <c r="B206" s="22"/>
       <c r="C206" s="8" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D206" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="E206" s="10"/>
       <c r="F206" s="10"/>
@@ -60262,13 +60265,13 @@
         <v>4955</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C207" s="23" t="s">
-        <v>6022</v>
+        <v>6023</v>
       </c>
       <c r="D207" s="25" t="s">
-        <v>6023</v>
+        <v>6024</v>
       </c>
       <c r="E207" s="10"/>
       <c r="F207" s="10"/>
@@ -60312,7 +60315,7 @@
     <row r="209" ht="18.75" customHeight="1">
       <c r="A209" s="26"/>
       <c r="B209" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C209" s="26"/>
       <c r="D209" s="22"/>
@@ -60340,10 +60343,10 @@
         <v>4317</v>
       </c>
       <c r="C210" s="23" t="s">
-        <v>6024</v>
+        <v>6025</v>
       </c>
       <c r="D210" s="25" t="s">
-        <v>6025</v>
+        <v>6026</v>
       </c>
       <c r="E210" s="10"/>
       <c r="F210" s="10"/>
@@ -60367,10 +60370,10 @@
         <v>4442</v>
       </c>
       <c r="C211" s="23" t="s">
-        <v>6026</v>
+        <v>6027</v>
       </c>
       <c r="D211" s="25" t="s">
-        <v>6027</v>
+        <v>6028</v>
       </c>
       <c r="E211" s="10"/>
       <c r="F211" s="10"/>
@@ -60391,7 +60394,7 @@
     <row r="212" ht="18.75" customHeight="1">
       <c r="A212" s="31"/>
       <c r="B212" s="32" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C212" s="31"/>
       <c r="D212" s="34"/>
@@ -60434,11 +60437,11 @@
     </row>
     <row r="214" ht="18.75" customHeight="1">
       <c r="A214" s="18" t="s">
-        <v>6028</v>
+        <v>6029</v>
       </c>
       <c r="B214" s="19"/>
       <c r="C214" s="18" t="s">
-        <v>6029</v>
+        <v>6030</v>
       </c>
       <c r="D214" s="19"/>
       <c r="E214" s="10"/>
@@ -60459,11 +60462,11 @@
     </row>
     <row r="215" ht="18.75" customHeight="1">
       <c r="A215" s="21" t="s">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="B215" s="22"/>
       <c r="C215" s="23" t="s">
-        <v>6030</v>
+        <v>6031</v>
       </c>
       <c r="D215" s="22"/>
       <c r="E215" s="10"/>
@@ -60484,11 +60487,11 @@
     </row>
     <row r="216" ht="18.75" customHeight="1">
       <c r="A216" s="21" t="s">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="B216" s="22"/>
       <c r="C216" s="23" t="s">
-        <v>6031</v>
+        <v>6032</v>
       </c>
       <c r="D216" s="22"/>
       <c r="E216" s="10"/>
@@ -60509,11 +60512,11 @@
     </row>
     <row r="217" ht="18.75" customHeight="1">
       <c r="A217" s="21" t="s">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="B217" s="22"/>
       <c r="C217" s="23" t="s">
-        <v>6032</v>
+        <v>6033</v>
       </c>
       <c r="D217" s="22"/>
       <c r="E217" s="10"/>
@@ -60534,14 +60537,14 @@
     </row>
     <row r="218" ht="18.75" customHeight="1">
       <c r="A218" s="21" t="s">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="B218" s="22"/>
       <c r="C218" s="21" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D218" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="E218" s="10"/>
       <c r="F218" s="10"/>
@@ -60564,13 +60567,13 @@
         <v>4955</v>
       </c>
       <c r="B219" s="24" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C219" s="23" t="s">
-        <v>6033</v>
+        <v>6034</v>
       </c>
       <c r="D219" s="25" t="s">
-        <v>6034</v>
+        <v>6035</v>
       </c>
       <c r="E219" s="10"/>
       <c r="F219" s="10"/>
@@ -60594,10 +60597,10 @@
         <v>4492</v>
       </c>
       <c r="C220" s="23" t="s">
-        <v>6035</v>
+        <v>6036</v>
       </c>
       <c r="D220" s="25" t="s">
-        <v>6036</v>
+        <v>6037</v>
       </c>
       <c r="E220" s="10"/>
       <c r="F220" s="10"/>
@@ -60618,13 +60621,13 @@
     <row r="221" ht="18.75" customHeight="1">
       <c r="A221" s="26"/>
       <c r="B221" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C221" s="23" t="s">
+        <v>6036</v>
+      </c>
+      <c r="D221" s="25" t="s">
         <v>6035</v>
-      </c>
-      <c r="D221" s="25" t="s">
-        <v>6034</v>
       </c>
       <c r="E221" s="10"/>
       <c r="F221" s="10"/>
@@ -60650,10 +60653,10 @@
         <v>4317</v>
       </c>
       <c r="C222" s="23" t="s">
-        <v>6037</v>
+        <v>6038</v>
       </c>
       <c r="D222" s="25" t="s">
-        <v>6038</v>
+        <v>6039</v>
       </c>
       <c r="E222" s="10"/>
       <c r="F222" s="10"/>
@@ -60676,10 +60679,10 @@
         <v>4442</v>
       </c>
       <c r="C223" s="23" t="s">
-        <v>6039</v>
+        <v>6040</v>
       </c>
       <c r="D223" s="25" t="s">
-        <v>6040</v>
+        <v>6041</v>
       </c>
       <c r="E223" s="10"/>
       <c r="F223" s="10"/>
@@ -60699,13 +60702,13 @@
     </row>
     <row r="224" ht="18.75" customHeight="1">
       <c r="B224" s="24" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C224" s="23" t="s">
-        <v>6041</v>
+        <v>6042</v>
       </c>
       <c r="D224" s="25" t="s">
-        <v>6042</v>
+        <v>6043</v>
       </c>
       <c r="E224" s="10"/>
       <c r="F224" s="10"/>
@@ -60725,14 +60728,14 @@
     </row>
     <row r="225" ht="18.75" customHeight="1">
       <c r="A225" s="21" t="s">
-        <v>5273</v>
+        <v>5274</v>
       </c>
       <c r="B225" s="22"/>
       <c r="C225" s="8" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D225" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="E225" s="10"/>
       <c r="F225" s="10"/>
@@ -60755,13 +60758,13 @@
         <v>4955</v>
       </c>
       <c r="B226" s="8" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C226" s="23" t="s">
-        <v>6043</v>
+        <v>6044</v>
       </c>
       <c r="D226" s="25" t="s">
-        <v>6044</v>
+        <v>6045</v>
       </c>
       <c r="E226" s="10"/>
       <c r="F226" s="10"/>
@@ -60805,7 +60808,7 @@
     <row r="228" ht="18.75" customHeight="1">
       <c r="A228" s="26"/>
       <c r="B228" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C228" s="26"/>
       <c r="D228" s="22"/>
@@ -60833,10 +60836,10 @@
         <v>4317</v>
       </c>
       <c r="C229" s="23" t="s">
-        <v>6045</v>
+        <v>6046</v>
       </c>
       <c r="D229" s="25" t="s">
-        <v>6046</v>
+        <v>6047</v>
       </c>
       <c r="E229" s="10"/>
       <c r="F229" s="10"/>
@@ -60860,10 +60863,10 @@
         <v>4442</v>
       </c>
       <c r="C230" s="23" t="s">
-        <v>6047</v>
+        <v>6048</v>
       </c>
       <c r="D230" s="25" t="s">
-        <v>6048</v>
+        <v>6049</v>
       </c>
       <c r="E230" s="10"/>
       <c r="F230" s="10"/>
@@ -60884,7 +60887,7 @@
     <row r="231" ht="18.75" customHeight="1">
       <c r="A231" s="31"/>
       <c r="B231" s="32" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C231" s="31"/>
       <c r="D231" s="34"/>
@@ -60927,11 +60930,11 @@
     </row>
     <row r="233" ht="18.75" customHeight="1">
       <c r="A233" s="18" t="s">
-        <v>6049</v>
+        <v>6050</v>
       </c>
       <c r="B233" s="19"/>
       <c r="C233" s="18" t="s">
-        <v>6050</v>
+        <v>6051</v>
       </c>
       <c r="D233" s="19"/>
       <c r="E233" s="10"/>
@@ -60952,11 +60955,11 @@
     </row>
     <row r="234" ht="18.75" customHeight="1">
       <c r="A234" s="21" t="s">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="B234" s="22"/>
       <c r="C234" s="23" t="s">
-        <v>6051</v>
+        <v>6052</v>
       </c>
       <c r="D234" s="22"/>
       <c r="E234" s="10"/>
@@ -60977,11 +60980,11 @@
     </row>
     <row r="235" ht="18.75" customHeight="1">
       <c r="A235" s="21" t="s">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="B235" s="22"/>
       <c r="C235" s="23" t="s">
-        <v>6052</v>
+        <v>6053</v>
       </c>
       <c r="D235" s="22"/>
       <c r="E235" s="10"/>
@@ -61002,11 +61005,11 @@
     </row>
     <row r="236" ht="18.75" customHeight="1">
       <c r="A236" s="21" t="s">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="B236" s="22"/>
       <c r="C236" s="23" t="s">
-        <v>6053</v>
+        <v>6054</v>
       </c>
       <c r="D236" s="22"/>
       <c r="E236" s="10"/>
@@ -61027,14 +61030,14 @@
     </row>
     <row r="237" ht="18.75" customHeight="1">
       <c r="A237" s="21" t="s">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="B237" s="22"/>
       <c r="C237" s="21" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D237" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="E237" s="10"/>
       <c r="F237" s="10"/>
@@ -61057,13 +61060,13 @@
         <v>4955</v>
       </c>
       <c r="B238" s="24" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C238" s="23" t="s">
-        <v>6054</v>
+        <v>6055</v>
       </c>
       <c r="D238" s="25" t="s">
-        <v>6055</v>
+        <v>6056</v>
       </c>
       <c r="E238" s="10"/>
       <c r="F238" s="10"/>
@@ -61087,10 +61090,10 @@
         <v>4492</v>
       </c>
       <c r="C239" s="23" t="s">
-        <v>6056</v>
+        <v>6057</v>
       </c>
       <c r="D239" s="25" t="s">
-        <v>6057</v>
+        <v>6058</v>
       </c>
       <c r="E239" s="10"/>
       <c r="F239" s="10"/>
@@ -61111,13 +61114,13 @@
     <row r="240" ht="18.75" customHeight="1">
       <c r="A240" s="26"/>
       <c r="B240" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C240" s="23" t="s">
-        <v>6056</v>
+        <v>6057</v>
       </c>
       <c r="D240" s="25" t="s">
-        <v>6058</v>
+        <v>6059</v>
       </c>
       <c r="E240" s="10"/>
       <c r="F240" s="10"/>
@@ -61143,10 +61146,10 @@
         <v>4317</v>
       </c>
       <c r="C241" s="23" t="s">
-        <v>6059</v>
+        <v>6060</v>
       </c>
       <c r="D241" s="25" t="s">
-        <v>6060</v>
+        <v>6061</v>
       </c>
       <c r="E241" s="10"/>
       <c r="F241" s="10"/>
@@ -61170,10 +61173,10 @@
         <v>4442</v>
       </c>
       <c r="C242" s="23" t="s">
-        <v>6061</v>
+        <v>6062</v>
       </c>
       <c r="D242" s="25" t="s">
-        <v>6062</v>
+        <v>6063</v>
       </c>
       <c r="E242" s="10"/>
       <c r="F242" s="10"/>
@@ -61194,13 +61197,13 @@
     <row r="243" ht="18.75" customHeight="1">
       <c r="A243" s="31"/>
       <c r="B243" s="32" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C243" s="36" t="s">
-        <v>6063</v>
+        <v>6064</v>
       </c>
       <c r="D243" s="28" t="s">
-        <v>6064</v>
+        <v>6065</v>
       </c>
       <c r="E243" s="10"/>
       <c r="F243" s="10"/>
@@ -61241,11 +61244,11 @@
     </row>
     <row r="245" ht="18.75" customHeight="1">
       <c r="A245" s="18" t="s">
-        <v>6065</v>
+        <v>6066</v>
       </c>
       <c r="B245" s="19"/>
       <c r="C245" s="18" t="s">
-        <v>6066</v>
+        <v>6067</v>
       </c>
       <c r="D245" s="19"/>
       <c r="E245" s="10"/>
@@ -61266,11 +61269,11 @@
     </row>
     <row r="246" ht="18.75" customHeight="1">
       <c r="A246" s="21" t="s">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="B246" s="22"/>
       <c r="C246" s="23" t="s">
-        <v>6067</v>
+        <v>6068</v>
       </c>
       <c r="D246" s="22"/>
       <c r="E246" s="10"/>
@@ -61291,11 +61294,11 @@
     </row>
     <row r="247" ht="18.75" customHeight="1">
       <c r="A247" s="21" t="s">
-        <v>5207</v>
+        <v>5208</v>
       </c>
       <c r="B247" s="22"/>
       <c r="C247" s="23" t="s">
-        <v>6068</v>
+        <v>6069</v>
       </c>
       <c r="D247" s="22"/>
       <c r="E247" s="10"/>
@@ -61316,11 +61319,11 @@
     </row>
     <row r="248" ht="18.75" customHeight="1">
       <c r="A248" s="21" t="s">
-        <v>5213</v>
+        <v>5214</v>
       </c>
       <c r="B248" s="22"/>
       <c r="C248" s="23" t="s">
-        <v>6069</v>
+        <v>6070</v>
       </c>
       <c r="D248" s="22"/>
       <c r="E248" s="10"/>
@@ -61341,14 +61344,14 @@
     </row>
     <row r="249" ht="18.75" customHeight="1">
       <c r="A249" s="21" t="s">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="B249" s="22"/>
       <c r="C249" s="21" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D249" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="E249" s="10"/>
       <c r="F249" s="10"/>
@@ -61371,13 +61374,13 @@
         <v>4955</v>
       </c>
       <c r="B250" s="24" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C250" s="23" t="s">
-        <v>6070</v>
+        <v>6071</v>
       </c>
       <c r="D250" s="25" t="s">
-        <v>6071</v>
+        <v>6072</v>
       </c>
       <c r="E250" s="10"/>
       <c r="F250" s="10"/>
@@ -61401,10 +61404,10 @@
         <v>4492</v>
       </c>
       <c r="C251" s="23" t="s">
-        <v>6072</v>
+        <v>6073</v>
       </c>
       <c r="D251" s="25" t="s">
-        <v>6073</v>
+        <v>6074</v>
       </c>
       <c r="E251" s="10"/>
       <c r="F251" s="10"/>
@@ -61425,13 +61428,13 @@
     <row r="252" ht="18.75" customHeight="1">
       <c r="A252" s="26"/>
       <c r="B252" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C252" s="23" t="s">
-        <v>6070</v>
+        <v>6071</v>
       </c>
       <c r="D252" s="25" t="s">
-        <v>6074</v>
+        <v>6075</v>
       </c>
       <c r="E252" s="10"/>
       <c r="F252" s="10"/>
@@ -61457,10 +61460,10 @@
         <v>4317</v>
       </c>
       <c r="C253" s="23" t="s">
-        <v>6075</v>
+        <v>6076</v>
       </c>
       <c r="D253" s="25" t="s">
-        <v>6076</v>
+        <v>6077</v>
       </c>
       <c r="E253" s="10"/>
       <c r="F253" s="10"/>
@@ -61484,10 +61487,10 @@
         <v>4442</v>
       </c>
       <c r="C254" s="23" t="s">
-        <v>6077</v>
+        <v>6078</v>
       </c>
       <c r="D254" s="25" t="s">
-        <v>6078</v>
+        <v>6079</v>
       </c>
       <c r="E254" s="10"/>
       <c r="F254" s="10"/>
@@ -61508,13 +61511,13 @@
     <row r="255" ht="18.75" customHeight="1">
       <c r="A255" s="31"/>
       <c r="B255" s="32" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C255" s="36" t="s">
-        <v>6079</v>
+        <v>6080</v>
       </c>
       <c r="D255" s="28" t="s">
-        <v>6080</v>
+        <v>6081</v>
       </c>
       <c r="E255" s="10"/>
       <c r="F255" s="10"/>
@@ -61555,15 +61558,15 @@
     </row>
     <row r="257" ht="18.75" customHeight="1">
       <c r="A257" s="18" t="s">
-        <v>6081</v>
+        <v>6082</v>
       </c>
       <c r="B257" s="19"/>
       <c r="C257" s="18" t="s">
-        <v>6082</v>
+        <v>6083</v>
       </c>
       <c r="D257" s="19"/>
       <c r="E257" s="18" t="s">
-        <v>6083</v>
+        <v>6084</v>
       </c>
       <c r="F257" s="19"/>
       <c r="G257" s="10"/>
@@ -61582,20 +61585,20 @@
     </row>
     <row r="258" ht="18.75" customHeight="1">
       <c r="A258" s="21" t="s">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="B258" s="22"/>
       <c r="C258" s="21" t="s">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="D258" s="24" t="s">
+        <v>5222</v>
+      </c>
+      <c r="E258" s="21" t="s">
         <v>5221</v>
       </c>
-      <c r="E258" s="21" t="s">
-        <v>5220</v>
-      </c>
       <c r="F258" s="24" t="s">
-        <v>5221</v>
+        <v>5222</v>
       </c>
       <c r="G258" s="10"/>
       <c r="H258" s="10"/>
@@ -61616,19 +61619,19 @@
         <v>4955</v>
       </c>
       <c r="B259" s="24" t="s">
-        <v>5222</v>
+        <v>5223</v>
       </c>
       <c r="C259" s="23" t="s">
-        <v>6084</v>
+        <v>6085</v>
       </c>
       <c r="D259" s="25" t="s">
-        <v>6085</v>
+        <v>6086</v>
       </c>
       <c r="E259" s="23" t="s">
-        <v>6086</v>
+        <v>6087</v>
       </c>
       <c r="F259" s="25" t="s">
-        <v>6087</v>
+        <v>6088</v>
       </c>
       <c r="G259" s="10"/>
       <c r="H259" s="10"/>
@@ -61650,16 +61653,16 @@
         <v>4492</v>
       </c>
       <c r="C260" s="23" t="s">
-        <v>6088</v>
+        <v>6089</v>
       </c>
       <c r="D260" s="25" t="s">
-        <v>5319</v>
+        <v>5320</v>
       </c>
       <c r="E260" s="23" t="s">
-        <v>5903</v>
+        <v>5904</v>
       </c>
       <c r="F260" s="25" t="s">
-        <v>6089</v>
+        <v>6090</v>
       </c>
       <c r="G260" s="10"/>
       <c r="H260" s="10"/>
@@ -61678,19 +61681,19 @@
     <row r="261" ht="18.75" customHeight="1">
       <c r="A261" s="26"/>
       <c r="B261" s="24" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="C261" s="23" t="s">
-        <v>6084</v>
+        <v>6085</v>
       </c>
       <c r="D261" s="25" t="s">
-        <v>5309</v>
+        <v>5310</v>
       </c>
       <c r="E261" s="23" t="s">
-        <v>5903</v>
+        <v>5904</v>
       </c>
       <c r="F261" s="25" t="s">
-        <v>6090</v>
+        <v>6091</v>
       </c>
       <c r="G261" s="10"/>
       <c r="H261" s="10"/>
@@ -61714,16 +61717,16 @@
         <v>4317</v>
       </c>
       <c r="C262" s="23" t="s">
-        <v>6091</v>
+        <v>6092</v>
       </c>
       <c r="D262" s="25" t="s">
-        <v>6092</v>
+        <v>6093</v>
       </c>
       <c r="E262" s="23" t="s">
-        <v>6093</v>
+        <v>6094</v>
       </c>
       <c r="F262" s="25" t="s">
-        <v>6094</v>
+        <v>6095</v>
       </c>
       <c r="G262" s="10"/>
       <c r="H262" s="10"/>
@@ -61745,16 +61748,16 @@
         <v>4442</v>
       </c>
       <c r="C263" s="23" t="s">
-        <v>6095</v>
+        <v>6096</v>
       </c>
       <c r="D263" s="25" t="s">
-        <v>6096</v>
+        <v>6097</v>
       </c>
       <c r="E263" s="23" t="s">
-        <v>6097</v>
+        <v>6098</v>
       </c>
       <c r="F263" s="25" t="s">
-        <v>6098</v>
+        <v>6099</v>
       </c>
       <c r="G263" s="10"/>
       <c r="H263" s="10"/>
@@ -61773,19 +61776,19 @@
     <row r="264" ht="18.75" customHeight="1">
       <c r="A264" s="31"/>
       <c r="B264" s="32" t="s">
-        <v>5262</v>
+        <v>5263</v>
       </c>
       <c r="C264" s="36" t="s">
         <v>2593</v>
       </c>
       <c r="D264" s="28" t="s">
-        <v>6099</v>
+        <v>6100</v>
       </c>
       <c r="E264" s="36" t="s">
         <v>3431</v>
       </c>
       <c r="F264" s="28" t="s">
-        <v>6100</v>
+        <v>6101</v>
       </c>
       <c r="G264" s="10"/>
       <c r="H264" s="10"/>
@@ -62278,11 +62281,11 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="42" t="s">
-        <v>6101</v>
+        <v>6102</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="42" t="s">
-        <v>6102</v>
+        <v>6103</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
@@ -62290,14 +62293,14 @@
         <v>254</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>6103</v>
+        <v>6104</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="43" t="s">
-        <v>6104</v>
+        <v>6105</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>6105</v>
+        <v>6106</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
@@ -62305,14 +62308,14 @@
         <v>1609</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6106</v>
+        <v>6107</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="43" t="s">
-        <v>6107</v>
+        <v>6108</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>6108</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
@@ -62320,14 +62323,14 @@
         <v>2222</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6109</v>
+        <v>6110</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="43" t="s">
-        <v>6110</v>
+        <v>6111</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>6111</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
@@ -62335,14 +62338,14 @@
         <v>2340</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>6112</v>
+        <v>6113</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="43" t="s">
-        <v>6113</v>
+        <v>6114</v>
       </c>
       <c r="G5" s="43" t="s">
-        <v>6114</v>
+        <v>6115</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1">
@@ -62350,14 +62353,14 @@
         <v>2482</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6115</v>
+        <v>6116</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="43" t="s">
-        <v>6116</v>
+        <v>6117</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>6117</v>
+        <v>6118</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1">
@@ -62365,14 +62368,14 @@
         <v>2593</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6118</v>
+        <v>6119</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="43" t="s">
-        <v>6119</v>
+        <v>6120</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>6120</v>
+        <v>6121</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
@@ -62380,14 +62383,14 @@
         <v>2680</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6121</v>
+        <v>6122</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="43" t="s">
-        <v>6122</v>
+        <v>6123</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>6123</v>
+        <v>6124</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
@@ -62395,14 +62398,14 @@
         <v>3431</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6124</v>
+        <v>6125</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="43" t="s">
-        <v>6125</v>
+        <v>6126</v>
       </c>
       <c r="G9" s="43" t="s">
-        <v>6126</v>
+        <v>6127</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
@@ -62410,14 +62413,14 @@
         <v>3705</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6127</v>
+        <v>6128</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="43" t="s">
-        <v>6128</v>
+        <v>6129</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>6129</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
@@ -62425,14 +62428,14 @@
         <v>4414</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6130</v>
+        <v>6131</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="43" t="s">
-        <v>6131</v>
+        <v>6132</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>6132</v>
+        <v>6133</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
@@ -62441,10 +62444,10 @@
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
       <c r="E12" s="43" t="s">
-        <v>6133</v>
+        <v>6134</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>6134</v>
+        <v>6135</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
@@ -62453,10 +62456,10 @@
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
       <c r="E13" s="43" t="s">
-        <v>6135</v>
+        <v>6136</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>6136</v>
+        <v>6137</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1">
@@ -62465,113 +62468,113 @@
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="43" t="s">
-        <v>6137</v>
+        <v>6138</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>6138</v>
+        <v>6139</v>
       </c>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="42" t="s">
-        <v>6139</v>
+        <v>6140</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>6140</v>
+        <v>6141</v>
       </c>
       <c r="G15" s="45" t="s">
-        <v>6141</v>
+        <v>6142</v>
       </c>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6142</v>
+        <v>6143</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>6143</v>
+        <v>6144</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6144</v>
+        <v>6145</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>6145</v>
+        <v>6146</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>6146</v>
+        <v>6147</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>6147</v>
+        <v>6148</v>
       </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>6148</v>
+        <v>6149</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>6149</v>
+        <v>6150</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>6150</v>
+        <v>6151</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>6151</v>
+        <v>6152</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6152</v>
+        <v>6153</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>6153</v>
+        <v>6154</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>6154</v>
+        <v>6155</v>
       </c>
       <c r="G19" s="43" t="s">
-        <v>6155</v>
+        <v>6156</v>
       </c>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6156</v>
+        <v>6157</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>6157</v>
+        <v>6158</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>6158</v>
+        <v>6159</v>
       </c>
       <c r="G20" s="43" t="s">
-        <v>6159</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6160</v>
+        <v>6161</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>6161</v>
+        <v>6162</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>6162</v>
+        <v>6163</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>6163</v>
+        <v>6164</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6164</v>
+        <v>6165</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>6165</v>
+        <v>6166</v>
       </c>
       <c r="E22" s="46" t="s">
-        <v>6166</v>
+        <v>6167</v>
       </c>
       <c r="G22" s="46" t="s">
-        <v>6167</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1"/>
@@ -62581,71 +62584,71 @@
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
       <c r="E24" s="43" t="s">
-        <v>6168</v>
+        <v>6169</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>6169</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="E25" s="43" t="s">
-        <v>6170</v>
+        <v>6171</v>
       </c>
       <c r="G25" s="43" t="s">
-        <v>6171</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="42" t="s">
-        <v>6172</v>
+        <v>6173</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>6173</v>
+        <v>6174</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>6174</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>6175</v>
+        <v>6176</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>6176</v>
+        <v>6177</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>6177</v>
+        <v>6178</v>
       </c>
       <c r="G27" s="43" t="s">
-        <v>6178</v>
+        <v>6179</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="43" t="s">
-        <v>6179</v>
+        <v>6180</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>6180</v>
+        <v>6181</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>6181</v>
+        <v>6182</v>
       </c>
       <c r="G28" s="43" t="s">
-        <v>6182</v>
+        <v>6183</v>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="43" t="s">
-        <v>6183</v>
+        <v>6184</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>6184</v>
+        <v>6185</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>6185</v>
+        <v>6186</v>
       </c>
       <c r="G29" s="43" t="s">
-        <v>6186</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1">
@@ -62654,10 +62657,10 @@
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
       <c r="E30" s="43" t="s">
-        <v>6187</v>
+        <v>6188</v>
       </c>
       <c r="G30" s="43" t="s">
-        <v>6188</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
@@ -62666,10 +62669,10 @@
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
       <c r="E31" s="43" t="s">
-        <v>6189</v>
+        <v>6190</v>
       </c>
       <c r="G31" s="43" t="s">
-        <v>6190</v>
+        <v>6191</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
@@ -62678,10 +62681,10 @@
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
       <c r="E32" s="43" t="s">
-        <v>6191</v>
+        <v>6192</v>
       </c>
       <c r="G32" s="43" t="s">
-        <v>6192</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
@@ -62690,10 +62693,10 @@
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
       <c r="E33" s="43" t="s">
-        <v>6193</v>
+        <v>6194</v>
       </c>
       <c r="G33" s="43" t="s">
-        <v>6194</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
@@ -62702,10 +62705,10 @@
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
       <c r="E34" s="43" t="s">
-        <v>6195</v>
+        <v>6196</v>
       </c>
       <c r="G34" s="43" t="s">
-        <v>6196</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
@@ -62714,10 +62717,10 @@
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
       <c r="E35" s="45" t="s">
-        <v>6197</v>
+        <v>6198</v>
       </c>
       <c r="G35" s="45" t="s">
-        <v>6198</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1">
@@ -62732,10 +62735,10 @@
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
       <c r="E37" s="43" t="s">
-        <v>6199</v>
+        <v>6200</v>
       </c>
       <c r="G37" s="43" t="s">
-        <v>6200</v>
+        <v>6201</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
@@ -62744,10 +62747,10 @@
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
       <c r="E38" s="43" t="s">
-        <v>6201</v>
+        <v>6202</v>
       </c>
       <c r="G38" s="43" t="s">
-        <v>6202</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
@@ -62756,10 +62759,10 @@
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
       <c r="E39" s="45" t="s">
-        <v>6203</v>
+        <v>6204</v>
       </c>
       <c r="G39" s="45" t="s">
-        <v>6204</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
@@ -62774,10 +62777,10 @@
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
       <c r="E41" s="45" t="s">
-        <v>6205</v>
+        <v>6206</v>
       </c>
       <c r="G41" s="45" t="s">
-        <v>6206</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1">
@@ -62786,10 +62789,10 @@
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
       <c r="E42" s="45" t="s">
-        <v>6207</v>
+        <v>6208</v>
       </c>
       <c r="G42" s="45" t="s">
-        <v>6208</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1">
@@ -62798,10 +62801,10 @@
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
       <c r="E43" s="45" t="s">
-        <v>6209</v>
+        <v>6210</v>
       </c>
       <c r="G43" s="47" t="s">
-        <v>6210</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="44" ht="18.75" customHeight="1">
@@ -62810,10 +62813,10 @@
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
       <c r="E44" s="45" t="s">
-        <v>6211</v>
+        <v>6212</v>
       </c>
       <c r="G44" s="45" t="s">
-        <v>6212</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="45" ht="18.75" customHeight="1">
@@ -63009,10 +63012,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="43" t="s">
-        <v>6213</v>
+        <v>6214</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>6214</v>
+        <v>6215</v>
       </c>
       <c r="C1" s="12"/>
     </row>
@@ -63021,34 +63024,34 @@
         <v>38</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>6215</v>
+        <v>6216</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>6216</v>
+        <v>6217</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6217</v>
+        <v>6218</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>6218</v>
+        <v>6219</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6219</v>
+        <v>6220</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>6220</v>
+        <v>6221</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>6221</v>
+        <v>6222</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -63057,70 +63060,70 @@
         <v>1866</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6222</v>
+        <v>6223</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>6223</v>
+        <v>6224</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6224</v>
+        <v>6225</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>6225</v>
+        <v>6226</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6226</v>
+        <v>6227</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>6227</v>
+        <v>6228</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6228</v>
+        <v>6229</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>6229</v>
+        <v>6230</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6230</v>
+        <v>6231</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>6231</v>
+        <v>6232</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6232</v>
+        <v>6233</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>6233</v>
+        <v>6234</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>6234</v>
+        <v>6235</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>6235</v>
+        <v>6236</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>6236</v>
+        <v>6237</v>
       </c>
       <c r="C13" s="12"/>
     </row>
@@ -63129,7 +63132,7 @@
         <v>4919</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>6237</v>
+        <v>6238</v>
       </c>
       <c r="C14" s="12"/>
     </row>
@@ -63140,19 +63143,19 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6238</v>
+        <v>6239</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>6239</v>
+        <v>6240</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6240</v>
+        <v>6241</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>6241</v>
+        <v>6242</v>
       </c>
       <c r="C17" s="12"/>
     </row>
@@ -63163,334 +63166,334 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6242</v>
+        <v>6243</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>6243</v>
+        <v>6244</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6244</v>
+        <v>6245</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>6245</v>
+        <v>6246</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>6247</v>
+        <v>6248</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6248</v>
+        <v>6249</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>6249</v>
+        <v>6250</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>6250</v>
+        <v>6251</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>6251</v>
+        <v>6252</v>
       </c>
       <c r="C23" s="12"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="43" t="s">
-        <v>6252</v>
+        <v>6253</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>6253</v>
+        <v>6254</v>
       </c>
       <c r="C24" s="12"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="43" t="s">
-        <v>6254</v>
+        <v>6255</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>6255</v>
+        <v>6256</v>
       </c>
       <c r="C25" s="12"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="43" t="s">
-        <v>6256</v>
+        <v>6257</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>6257</v>
+        <v>6258</v>
       </c>
       <c r="C26" s="12"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>6258</v>
+        <v>6259</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>6259</v>
+        <v>6260</v>
       </c>
       <c r="C27" s="12"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="43" t="s">
-        <v>6260</v>
+        <v>6261</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>6261</v>
+        <v>6262</v>
       </c>
       <c r="C28" s="12"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="43" t="s">
-        <v>6262</v>
+        <v>6263</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>6263</v>
+        <v>6264</v>
       </c>
       <c r="C29" s="12"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="43" t="s">
-        <v>6264</v>
+        <v>6265</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>6265</v>
+        <v>6266</v>
       </c>
       <c r="C30" s="12"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="43" t="s">
-        <v>6266</v>
+        <v>6267</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>6267</v>
+        <v>6268</v>
       </c>
       <c r="C31" s="12"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="43" t="s">
-        <v>6268</v>
+        <v>6269</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>6269</v>
+        <v>6270</v>
       </c>
       <c r="C32" s="12"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="43" t="s">
-        <v>6270</v>
+        <v>6271</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>6271</v>
+        <v>6272</v>
       </c>
       <c r="C33" s="12"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="43" t="s">
-        <v>6272</v>
+        <v>6273</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>6273</v>
+        <v>6274</v>
       </c>
       <c r="C34" s="12"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="43" t="s">
-        <v>6274</v>
+        <v>6275</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>6275</v>
+        <v>6276</v>
       </c>
       <c r="C35" s="12"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="43" t="s">
-        <v>6276</v>
+        <v>6277</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>6277</v>
+        <v>6278</v>
       </c>
       <c r="C36" s="12"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="43" t="s">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>6279</v>
+        <v>6280</v>
       </c>
       <c r="C37" s="12"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="43" t="s">
-        <v>6280</v>
+        <v>6281</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>6281</v>
+        <v>6282</v>
       </c>
       <c r="C38" s="12"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="43" t="s">
-        <v>6282</v>
+        <v>6283</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>6283</v>
+        <v>6284</v>
       </c>
       <c r="C39" s="12"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="43" t="s">
-        <v>6284</v>
+        <v>6285</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>6285</v>
+        <v>6286</v>
       </c>
       <c r="C40" s="12"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="43" t="s">
-        <v>6286</v>
+        <v>6287</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>6287</v>
+        <v>6288</v>
       </c>
       <c r="C41" s="12"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="43" t="s">
-        <v>6288</v>
+        <v>6289</v>
       </c>
       <c r="B42" s="43" t="s">
-        <v>6289</v>
+        <v>6290</v>
       </c>
       <c r="C42" s="12"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="43" t="s">
-        <v>6290</v>
+        <v>6291</v>
       </c>
       <c r="B43" s="43" t="s">
-        <v>6291</v>
+        <v>6292</v>
       </c>
       <c r="C43" s="12"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" s="43" t="s">
-        <v>6292</v>
+        <v>6293</v>
       </c>
       <c r="B44" s="43" t="s">
-        <v>6293</v>
+        <v>6294</v>
       </c>
       <c r="C44" s="12"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="43" t="s">
-        <v>6294</v>
+        <v>6295</v>
       </c>
       <c r="B45" s="43" t="s">
-        <v>6295</v>
+        <v>6296</v>
       </c>
       <c r="C45" s="12"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="43" t="s">
-        <v>6296</v>
+        <v>6297</v>
       </c>
       <c r="B46" s="43" t="s">
-        <v>6297</v>
+        <v>6298</v>
       </c>
       <c r="C46" s="12"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="43" t="s">
-        <v>6298</v>
+        <v>6299</v>
       </c>
       <c r="B47" s="43" t="s">
-        <v>6299</v>
+        <v>6300</v>
       </c>
       <c r="C47" s="12"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="43" t="s">
-        <v>6300</v>
+        <v>6301</v>
       </c>
       <c r="B48" s="43" t="s">
-        <v>6301</v>
+        <v>6302</v>
       </c>
       <c r="C48" s="12"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" s="43" t="s">
-        <v>6302</v>
+        <v>6303</v>
       </c>
       <c r="B49" s="43" t="s">
-        <v>6303</v>
+        <v>6304</v>
       </c>
       <c r="C49" s="12"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" s="43" t="s">
-        <v>6304</v>
+        <v>6305</v>
       </c>
       <c r="B50" s="43" t="s">
-        <v>6305</v>
+        <v>6306</v>
       </c>
       <c r="C50" s="12"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" s="43" t="s">
-        <v>6306</v>
+        <v>6307</v>
       </c>
       <c r="B51" s="43" t="s">
-        <v>6307</v>
+        <v>6308</v>
       </c>
       <c r="C51" s="12"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" s="43" t="s">
-        <v>6308</v>
+        <v>6309</v>
       </c>
       <c r="B52" s="43" t="s">
-        <v>6309</v>
+        <v>6310</v>
       </c>
       <c r="C52" s="12"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" s="43" t="s">
-        <v>6310</v>
+        <v>6311</v>
       </c>
       <c r="B53" s="43" t="s">
-        <v>6311</v>
+        <v>6312</v>
       </c>
       <c r="C53" s="12"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" s="43" t="s">
-        <v>6312</v>
+        <v>6313</v>
       </c>
       <c r="B54" s="43" t="s">
-        <v>6313</v>
+        <v>6314</v>
       </c>
       <c r="C54" s="12"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" s="43" t="s">
-        <v>6314</v>
+        <v>6315</v>
       </c>
       <c r="B55" s="43" t="s">
-        <v>6315</v>
+        <v>6316</v>
       </c>
       <c r="C55" s="12"/>
     </row>
@@ -63513,130 +63516,130 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="48" t="s">
-        <v>6316</v>
+        <v>6317</v>
       </c>
       <c r="C1" s="12"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="48" t="s">
-        <v>6317</v>
+        <v>6318</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>6318</v>
+        <v>6319</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>6319</v>
+        <v>6320</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6240</v>
+        <v>6241</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>6240</v>
+        <v>6241</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6227</v>
+        <v>6228</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>6320</v>
+        <v>6321</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>6229</v>
+        <v>6230</v>
       </c>
       <c r="C5" s="12"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="43" t="s">
-        <v>6321</v>
+        <v>6322</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6322</v>
+        <v>6323</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>6323</v>
+        <v>6324</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6324</v>
+        <v>6325</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>6325</v>
+        <v>6326</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6326</v>
+        <v>6327</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>6327</v>
+        <v>6328</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6328</v>
+        <v>6329</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>6329</v>
+        <v>6330</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6330</v>
+        <v>6331</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>6331</v>
+        <v>6332</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6332</v>
+        <v>6333</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>6333</v>
+        <v>6334</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>6334</v>
+        <v>6335</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>6335</v>
+        <v>6336</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>6336</v>
+        <v>6337</v>
       </c>
       <c r="C13" s="12"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="43" t="s">
-        <v>6337</v>
+        <v>6338</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>6338</v>
+        <v>6339</v>
       </c>
       <c r="C14" s="12"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="43" t="s">
-        <v>6339</v>
+        <v>6340</v>
       </c>
       <c r="B15" s="43" t="s">
         <v>3974</v>
@@ -63645,73 +63648,73 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6340</v>
+        <v>6341</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>6341</v>
+        <v>6342</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6342</v>
+        <v>6343</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>6343</v>
+        <v>6344</v>
       </c>
       <c r="C17" s="12"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>6344</v>
+        <v>6345</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>6345</v>
+        <v>6346</v>
       </c>
       <c r="C18" s="12"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6346</v>
+        <v>6347</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>6347</v>
+        <v>6348</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6348</v>
+        <v>6349</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>6349</v>
+        <v>6350</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6350</v>
+        <v>6351</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>6351</v>
+        <v>6352</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6352</v>
+        <v>6353</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>6353</v>
+        <v>6354</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>6354</v>
+        <v>6355</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="C23" s="12"/>
     </row>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -5633,7 +5633,7 @@
     <t>hvort</t>
   </si>
   <si>
-    <t>whether</t>
+    <t>whether, either</t>
   </si>
   <si>
     <t>hyggja</t>
@@ -18757,7 +18757,7 @@
     <t>u</t>
   </si>
   <si>
-    <t>/ʊ/</t>
+    <t>/ʉ/</t>
   </si>
   <si>
     <t>ú</t>
@@ -30895,7 +30895,7 @@
         <v>1858</v>
       </c>
       <c r="B913" s="4" t="s">
-        <v>59</v>
+        <v>246</v>
       </c>
       <c r="C913" s="3" t="s">
         <v>1859</v>
@@ -51332,55 +51332,55 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="N24:N25"/>
     <mergeCell ref="M29:M30"/>
     <mergeCell ref="N29:N30"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L32:N32"/>
     <mergeCell ref="G13:G14"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="L13:L14"/>
     <mergeCell ref="N13:N14"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D13:D14"/>
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="D17:D18"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="N18:N19"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="D22:D23"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G21:I21"/>
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="I24:I25"/>
-    <mergeCell ref="N24:N25"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="I29:I30"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -53247,71 +53247,71 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B44:B45"/>
     <mergeCell ref="D44:D45"/>
     <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
     <mergeCell ref="B51:D51"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="B55:D55"/>
-    <mergeCell ref="D70:D71"/>
     <mergeCell ref="C75:C76"/>
     <mergeCell ref="D75:D76"/>
     <mergeCell ref="B77:D77"/>
     <mergeCell ref="B78:D78"/>
-    <mergeCell ref="D49:D50"/>
     <mergeCell ref="D57:D58"/>
     <mergeCell ref="C62:C63"/>
     <mergeCell ref="D62:D63"/>
     <mergeCell ref="B64:D64"/>
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="B68:D68"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="G14:G17"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="E19:G22"/>
+    <mergeCell ref="E23:G27"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="G4:G7"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="F5:F7"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:G12"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="G14:G17"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:G22"/>
-    <mergeCell ref="E23:G27"/>
     <mergeCell ref="D24:D25"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="G29:I29"/>
     <mergeCell ref="L29:N29"/>
+    <mergeCell ref="I31:I32"/>
     <mergeCell ref="N31:N32"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
     <mergeCell ref="H36:H37"/>
     <mergeCell ref="I36:I37"/>
     <mergeCell ref="M36:M37"/>
     <mergeCell ref="N36:N37"/>
+    <mergeCell ref="B38:D38"/>
     <mergeCell ref="G38:I38"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="B39:D39"/>
     <mergeCell ref="G39:I39"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="B42:D42"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -62904,7 +62904,6 @@
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A19:B19"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="E25:F25"/>
@@ -62983,16 +62982,17 @@
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="E15:F16"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A20:B20"/>
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="G21:H21"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="E22:F23"/>
     <mergeCell ref="G22:H23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -11666,7 +11666,7 @@
     <t>tala</t>
   </si>
   <si>
-    <t>to talk, to speak</t>
+    <t>to talk, to speak (intransitive); to talk to (with með + dative); to speak a language (with accusative)</t>
   </si>
   <si>
     <t>tala-fræði</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -8444,7 +8444,7 @@
     <t>ó-líktr</t>
   </si>
   <si>
-    <t>different</t>
+    <t>different, unlike</t>
   </si>
   <si>
     <t>ó-røð</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10199" uniqueCount="6387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10219" uniqueCount="6406">
   <si>
     <t>Entry</t>
   </si>
@@ -18655,19 +18655,31 @@
     <t>God made some men small and some men big, but man made steel and steel made them equal.</t>
   </si>
   <si>
+    <t>flatr, japn, and sami examples</t>
+  </si>
+  <si>
     <t>(jek) se allt í glasi</t>
   </si>
   <si>
     <t>everything's gone blurry (for me)</t>
   </si>
   <si>
+    <t>þeir eru sømu</t>
+  </si>
+  <si>
+    <t>they are the same thing</t>
+  </si>
+  <si>
     <t>hann þýddi þat á skýjan máta</t>
   </si>
   <si>
     <t>he explained it in a clear way</t>
   </si>
   <si>
-    <t>flatr, japn, and sami examples</t>
+    <t>þeir eru flatir</t>
+  </si>
+  <si>
+    <t>they are equal in strength / weight</t>
   </si>
   <si>
     <t>deynir menn segju engar søgur</t>
@@ -18676,10 +18688,10 @@
     <t>dead men tell no tales</t>
   </si>
   <si>
-    <t>þeir eru sømu</t>
-  </si>
-  <si>
-    <t>they are the same thing</t>
+    <t>þeir eru japnir</t>
+  </si>
+  <si>
+    <t>there's the same amount of them</t>
   </si>
   <si>
     <t>hann stendr á efra þakinu</t>
@@ -18688,22 +18700,13 @@
     <t>he is standing on top of the roof</t>
   </si>
   <si>
-    <t>þeir eru flatir</t>
-  </si>
-  <si>
-    <t>they are equal in strength / weight</t>
-  </si>
-  <si>
     <t>þat hefsk sem hættuligt, segja jek</t>
   </si>
   <si>
     <t>that looks dangerous, i think</t>
   </si>
   <si>
-    <t>þeir eru japnir</t>
-  </si>
-  <si>
-    <t>there's the same amount of them</t>
+    <t>examples of "mer er (adj)"</t>
   </si>
   <si>
     <t>gœmirðu ef et jek køkuna?</t>
@@ -18712,6 +18715,9 @@
     <t>do you mind if i eat the cake?</t>
   </si>
   <si>
+    <t>"mer er (adj)" is used when expressing a feeling or an emotion, such as being angry, happy, sad, etc. it can also be used to express sensations, such as being cold, hot, thirsty, hungry, etc</t>
+  </si>
+  <si>
     <t>jek hulda mek í hrísinu</t>
   </si>
   <si>
@@ -18724,46 +18730,97 @@
     <t>this tastes bad</t>
   </si>
   <si>
+    <t>i'm cold</t>
+  </si>
+  <si>
     <t>jek meidda mek á knjám</t>
   </si>
   <si>
     <t>i hurt my knees</t>
   </si>
   <si>
+    <t>mer er skjallað</t>
+  </si>
+  <si>
+    <t>i'm scared</t>
+  </si>
+  <si>
     <t>jek hend henni í hendi</t>
   </si>
   <si>
     <t>i hold her hand</t>
   </si>
   <si>
+    <t>mer er vel</t>
+  </si>
+  <si>
+    <t>i'm good / i'm fine</t>
+  </si>
+  <si>
     <t>hon skurðar støttu ór viði</t>
   </si>
   <si>
     <t>she carves a statue out of wood</t>
   </si>
   <si>
+    <t>mer er þurst</t>
+  </si>
+  <si>
+    <t>i'm thirsty</t>
+  </si>
+  <si>
     <t>hafmeyjarnar munu rœna at afleiða þek, ef kemsk þú of nærra til þeira</t>
   </si>
   <si>
     <t>sirens will try to seduce you if you get too close to them</t>
   </si>
   <si>
+    <t>mer er svangt</t>
+  </si>
+  <si>
+    <t>i'm hungry</t>
+  </si>
+  <si>
+    <t>mer er vreitt</t>
+  </si>
+  <si>
+    <t>i'm angry</t>
+  </si>
+  <si>
     <t>hann værir virkandi</t>
   </si>
   <si>
     <t>he might be busy</t>
   </si>
   <si>
+    <t>mer er gleðugt</t>
+  </si>
+  <si>
+    <t>i'm happy</t>
+  </si>
+  <si>
     <t>hann værði virkandi</t>
   </si>
   <si>
     <t>he could have been busy</t>
   </si>
   <si>
+    <t>hanum er vel</t>
+  </si>
+  <si>
+    <t>he is doing okay</t>
+  </si>
+  <si>
     <t>afallinn villans atlar eigi at vera svindlað af manni</t>
   </si>
   <si>
     <t>the forces of nature are not to be trifled with</t>
+  </si>
+  <si>
+    <t>hanum er illa</t>
+  </si>
+  <si>
+    <t>he is not okay</t>
   </si>
   <si>
     <t>maðr ná venjuliga eigi hleypa yfir tre</t>
@@ -62849,197 +62906,209 @@
     </row>
     <row r="23" ht="18.75" customHeight="1"/>
     <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" s="43"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
+      <c r="A24" s="42" t="s">
+        <v>6199</v>
+      </c>
       <c r="E24" s="43" t="s">
-        <v>6199</v>
+        <v>6200</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>6200</v>
+        <v>6201</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
+      <c r="A25" s="43" t="s">
+        <v>6202</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>6203</v>
+      </c>
       <c r="E25" s="43" t="s">
-        <v>6201</v>
+        <v>6204</v>
       </c>
       <c r="G25" s="43" t="s">
-        <v>6202</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="42" t="s">
-        <v>6203</v>
+      <c r="A26" s="43" t="s">
+        <v>6206</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>6207</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
       <c r="G27" s="43" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="43" t="s">
-        <v>6210</v>
-      </c>
-      <c r="C28" s="43" t="s">
-        <v>6211</v>
-      </c>
       <c r="E28" s="43" t="s">
-        <v>6212</v>
+        <v>6214</v>
       </c>
       <c r="G28" s="43" t="s">
-        <v>6213</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="43" t="s">
-        <v>6214</v>
-      </c>
-      <c r="C29" s="43" t="s">
-        <v>6215</v>
+      <c r="A29" s="42" t="s">
+        <v>6216</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>6216</v>
+        <v>6217</v>
       </c>
       <c r="G29" s="43" t="s">
-        <v>6217</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="43"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
+      <c r="A30" s="45" t="s">
+        <v>6219</v>
+      </c>
       <c r="E30" s="43" t="s">
-        <v>6218</v>
+        <v>6220</v>
       </c>
       <c r="G30" s="43" t="s">
-        <v>6219</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="43"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
       <c r="E31" s="43" t="s">
-        <v>6220</v>
+        <v>6222</v>
       </c>
       <c r="G31" s="43" t="s">
-        <v>6221</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" s="43"/>
-      <c r="B32" s="43"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
+      <c r="A32" s="43" t="s">
+        <v>6183</v>
+      </c>
+      <c r="C32" s="43" t="s">
+        <v>6224</v>
+      </c>
       <c r="E32" s="43" t="s">
-        <v>6222</v>
+        <v>6225</v>
       </c>
       <c r="G32" s="43" t="s">
-        <v>6223</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="43"/>
-      <c r="B33" s="43"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
+      <c r="A33" s="43" t="s">
+        <v>6227</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>6228</v>
+      </c>
       <c r="E33" s="43" t="s">
-        <v>6224</v>
+        <v>6229</v>
       </c>
       <c r="G33" s="43" t="s">
-        <v>6225</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="43"/>
-      <c r="B34" s="43"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
+      <c r="A34" s="43" t="s">
+        <v>6231</v>
+      </c>
+      <c r="C34" s="43" t="s">
+        <v>6232</v>
+      </c>
       <c r="E34" s="43" t="s">
-        <v>6226</v>
+        <v>6233</v>
       </c>
       <c r="G34" s="43" t="s">
-        <v>6227</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="43"/>
-      <c r="B35" s="43"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
+      <c r="A35" s="43" t="s">
+        <v>6235</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>6236</v>
+      </c>
       <c r="E35" s="45" t="s">
-        <v>6228</v>
+        <v>6237</v>
       </c>
       <c r="G35" s="45" t="s">
-        <v>6229</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="43"/>
-      <c r="B36" s="43"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
+      <c r="A36" s="43" t="s">
+        <v>6239</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>6240</v>
+      </c>
     </row>
     <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" s="43"/>
-      <c r="B37" s="43"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
+      <c r="A37" s="43" t="s">
+        <v>6241</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>6242</v>
+      </c>
       <c r="E37" s="43" t="s">
-        <v>6230</v>
+        <v>6243</v>
       </c>
       <c r="G37" s="43" t="s">
-        <v>6231</v>
+        <v>6244</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
-      <c r="A38" s="43"/>
-      <c r="B38" s="43"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
+      <c r="A38" s="43" t="s">
+        <v>6245</v>
+      </c>
+      <c r="C38" s="43" t="s">
+        <v>6246</v>
+      </c>
       <c r="E38" s="43" t="s">
-        <v>6232</v>
+        <v>6247</v>
       </c>
       <c r="G38" s="43" t="s">
-        <v>6233</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
-      <c r="A39" s="43"/>
-      <c r="B39" s="43"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
+      <c r="A39" s="43" t="s">
+        <v>6249</v>
+      </c>
+      <c r="C39" s="43" t="s">
+        <v>6250</v>
+      </c>
       <c r="E39" s="45" t="s">
-        <v>6234</v>
+        <v>6251</v>
       </c>
       <c r="G39" s="45" t="s">
-        <v>6235</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" s="43"/>
-      <c r="B40" s="43"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
+      <c r="A40" s="43" t="s">
+        <v>6253</v>
+      </c>
+      <c r="C40" s="43" t="s">
+        <v>6254</v>
+      </c>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="43"/>
@@ -63047,10 +63116,10 @@
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
       <c r="E41" s="45" t="s">
-        <v>6236</v>
+        <v>6255</v>
       </c>
       <c r="G41" s="45" t="s">
-        <v>6237</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1">
@@ -63059,10 +63128,10 @@
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
       <c r="E42" s="45" t="s">
-        <v>6238</v>
+        <v>6257</v>
       </c>
       <c r="G42" s="45" t="s">
-        <v>6239</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1">
@@ -63071,10 +63140,10 @@
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
       <c r="E43" s="45" t="s">
-        <v>6240</v>
+        <v>6259</v>
       </c>
       <c r="G43" s="47" t="s">
-        <v>6241</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="44" ht="18.75" customHeight="1">
@@ -63083,10 +63152,10 @@
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
       <c r="E44" s="45" t="s">
-        <v>6242</v>
+        <v>6261</v>
       </c>
       <c r="G44" s="45" t="s">
-        <v>6243</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="45" ht="18.75" customHeight="1">
@@ -63150,7 +63219,7 @@
       <c r="H50" s="45"/>
     </row>
   </sheetData>
-  <mergeCells count="112">
+  <mergeCells count="132">
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G10:H10"/>
@@ -63174,51 +63243,6 @@
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E35:F36"/>
-    <mergeCell ref="G35:H36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="G44:H44"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="B2:C2"/>
@@ -63263,6 +63287,71 @@
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="E22:F23"/>
     <mergeCell ref="G22:H23"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E35:F36"/>
+    <mergeCell ref="G35:H36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A30:D31"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C39:D39"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -63282,10 +63371,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="43" t="s">
-        <v>6244</v>
+        <v>6263</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>6245</v>
+        <v>6264</v>
       </c>
       <c r="C1" s="12"/>
     </row>
@@ -63294,34 +63383,34 @@
         <v>38</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>6246</v>
+        <v>6265</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>6247</v>
+        <v>6266</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6248</v>
+        <v>6267</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>6249</v>
+        <v>6268</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6250</v>
+        <v>6269</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>6251</v>
+        <v>6270</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>6252</v>
+        <v>6271</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -63330,70 +63419,70 @@
         <v>1872</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6253</v>
+        <v>6272</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>6254</v>
+        <v>6273</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6255</v>
+        <v>6274</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>6256</v>
+        <v>6275</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6257</v>
+        <v>6276</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>6258</v>
+        <v>6277</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6259</v>
+        <v>6278</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>6260</v>
+        <v>6279</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6261</v>
+        <v>6280</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>6262</v>
+        <v>6281</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6263</v>
+        <v>6282</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>6264</v>
+        <v>6283</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>6265</v>
+        <v>6284</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>6266</v>
+        <v>6285</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>6267</v>
+        <v>6286</v>
       </c>
       <c r="C13" s="12"/>
     </row>
@@ -63402,7 +63491,7 @@
         <v>4949</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>6268</v>
+        <v>6287</v>
       </c>
       <c r="C14" s="12"/>
     </row>
@@ -63413,19 +63502,19 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6269</v>
+        <v>6288</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>6270</v>
+        <v>6289</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6271</v>
+        <v>6290</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>6272</v>
+        <v>6291</v>
       </c>
       <c r="C17" s="12"/>
     </row>
@@ -63436,334 +63525,334 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6273</v>
+        <v>6292</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>6274</v>
+        <v>6293</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6275</v>
+        <v>6294</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>6276</v>
+        <v>6295</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6277</v>
+        <v>6296</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>6278</v>
+        <v>6297</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6279</v>
+        <v>6298</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>6280</v>
+        <v>6299</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>6281</v>
+        <v>6300</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>6282</v>
+        <v>6301</v>
       </c>
       <c r="C23" s="12"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="43" t="s">
-        <v>6283</v>
+        <v>6302</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>6284</v>
+        <v>6303</v>
       </c>
       <c r="C24" s="12"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="43" t="s">
-        <v>6285</v>
+        <v>6304</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>6286</v>
+        <v>6305</v>
       </c>
       <c r="C25" s="12"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="43" t="s">
-        <v>6287</v>
+        <v>6306</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>6288</v>
+        <v>6307</v>
       </c>
       <c r="C26" s="12"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>6289</v>
+        <v>6308</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>6290</v>
+        <v>6309</v>
       </c>
       <c r="C27" s="12"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="43" t="s">
-        <v>6291</v>
+        <v>6310</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>6292</v>
+        <v>6311</v>
       </c>
       <c r="C28" s="12"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="43" t="s">
-        <v>6293</v>
+        <v>6312</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>6294</v>
+        <v>6313</v>
       </c>
       <c r="C29" s="12"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="43" t="s">
-        <v>6295</v>
+        <v>6314</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>6296</v>
+        <v>6315</v>
       </c>
       <c r="C30" s="12"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="43" t="s">
-        <v>6297</v>
+        <v>6316</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>6298</v>
+        <v>6317</v>
       </c>
       <c r="C31" s="12"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="43" t="s">
-        <v>6299</v>
+        <v>6318</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>6300</v>
+        <v>6319</v>
       </c>
       <c r="C32" s="12"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="43" t="s">
-        <v>6301</v>
+        <v>6320</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>6302</v>
+        <v>6321</v>
       </c>
       <c r="C33" s="12"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="43" t="s">
-        <v>6303</v>
+        <v>6322</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>6304</v>
+        <v>6323</v>
       </c>
       <c r="C34" s="12"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="43" t="s">
-        <v>6305</v>
+        <v>6324</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>6306</v>
+        <v>6325</v>
       </c>
       <c r="C35" s="12"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="43" t="s">
-        <v>6307</v>
+        <v>6326</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>6308</v>
+        <v>6327</v>
       </c>
       <c r="C36" s="12"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="43" t="s">
-        <v>6309</v>
+        <v>6328</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>6310</v>
+        <v>6329</v>
       </c>
       <c r="C37" s="12"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="43" t="s">
-        <v>6311</v>
+        <v>6330</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>6312</v>
+        <v>6331</v>
       </c>
       <c r="C38" s="12"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="43" t="s">
-        <v>6313</v>
+        <v>6332</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>6314</v>
+        <v>6333</v>
       </c>
       <c r="C39" s="12"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="43" t="s">
-        <v>6315</v>
+        <v>6334</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>6316</v>
+        <v>6335</v>
       </c>
       <c r="C40" s="12"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="43" t="s">
-        <v>6317</v>
+        <v>6336</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>6318</v>
+        <v>6337</v>
       </c>
       <c r="C41" s="12"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="43" t="s">
-        <v>6319</v>
+        <v>6338</v>
       </c>
       <c r="B42" s="43" t="s">
-        <v>6320</v>
+        <v>6339</v>
       </c>
       <c r="C42" s="12"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="43" t="s">
-        <v>6321</v>
+        <v>6340</v>
       </c>
       <c r="B43" s="43" t="s">
-        <v>6322</v>
+        <v>6341</v>
       </c>
       <c r="C43" s="12"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" s="43" t="s">
-        <v>6323</v>
+        <v>6342</v>
       </c>
       <c r="B44" s="43" t="s">
-        <v>6324</v>
+        <v>6343</v>
       </c>
       <c r="C44" s="12"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="43" t="s">
-        <v>6325</v>
+        <v>6344</v>
       </c>
       <c r="B45" s="43" t="s">
-        <v>6326</v>
+        <v>6345</v>
       </c>
       <c r="C45" s="12"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="43" t="s">
-        <v>6327</v>
+        <v>6346</v>
       </c>
       <c r="B46" s="43" t="s">
-        <v>6328</v>
+        <v>6347</v>
       </c>
       <c r="C46" s="12"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="43" t="s">
-        <v>6329</v>
+        <v>6348</v>
       </c>
       <c r="B47" s="43" t="s">
-        <v>6330</v>
+        <v>6349</v>
       </c>
       <c r="C47" s="12"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="43" t="s">
-        <v>6331</v>
+        <v>6350</v>
       </c>
       <c r="B48" s="43" t="s">
-        <v>6332</v>
+        <v>6351</v>
       </c>
       <c r="C48" s="12"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" s="43" t="s">
-        <v>6333</v>
+        <v>6352</v>
       </c>
       <c r="B49" s="43" t="s">
-        <v>6334</v>
+        <v>6353</v>
       </c>
       <c r="C49" s="12"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" s="43" t="s">
-        <v>6335</v>
+        <v>6354</v>
       </c>
       <c r="B50" s="43" t="s">
-        <v>6336</v>
+        <v>6355</v>
       </c>
       <c r="C50" s="12"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" s="43" t="s">
-        <v>6337</v>
+        <v>6356</v>
       </c>
       <c r="B51" s="43" t="s">
-        <v>6338</v>
+        <v>6357</v>
       </c>
       <c r="C51" s="12"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" s="43" t="s">
-        <v>6339</v>
+        <v>6358</v>
       </c>
       <c r="B52" s="43" t="s">
-        <v>6340</v>
+        <v>6359</v>
       </c>
       <c r="C52" s="12"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" s="43" t="s">
-        <v>6341</v>
+        <v>6360</v>
       </c>
       <c r="B53" s="43" t="s">
-        <v>6342</v>
+        <v>6361</v>
       </c>
       <c r="C53" s="12"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" s="43" t="s">
-        <v>6343</v>
+        <v>6362</v>
       </c>
       <c r="B54" s="43" t="s">
-        <v>6344</v>
+        <v>6363</v>
       </c>
       <c r="C54" s="12"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" s="43" t="s">
-        <v>6345</v>
+        <v>6364</v>
       </c>
       <c r="B55" s="43" t="s">
-        <v>6346</v>
+        <v>6365</v>
       </c>
       <c r="C55" s="12"/>
     </row>
@@ -63786,130 +63875,130 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="48" t="s">
-        <v>6347</v>
+        <v>6366</v>
       </c>
       <c r="C1" s="12"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="48" t="s">
-        <v>6348</v>
+        <v>6367</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>6349</v>
+        <v>6368</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>6350</v>
+        <v>6369</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6271</v>
+        <v>6290</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>6271</v>
+        <v>6290</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6258</v>
+        <v>6277</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>6351</v>
+        <v>6370</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>6260</v>
+        <v>6279</v>
       </c>
       <c r="C5" s="12"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="43" t="s">
-        <v>6352</v>
+        <v>6371</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6353</v>
+        <v>6372</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>6354</v>
+        <v>6373</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6355</v>
+        <v>6374</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>6356</v>
+        <v>6375</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6357</v>
+        <v>6376</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>6358</v>
+        <v>6377</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6359</v>
+        <v>6378</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>6360</v>
+        <v>6379</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6361</v>
+        <v>6380</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>6362</v>
+        <v>6381</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6363</v>
+        <v>6382</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>6364</v>
+        <v>6383</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>6365</v>
+        <v>6384</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>6366</v>
+        <v>6385</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>6367</v>
+        <v>6386</v>
       </c>
       <c r="C13" s="12"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="43" t="s">
-        <v>6368</v>
+        <v>6387</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>6369</v>
+        <v>6388</v>
       </c>
       <c r="C14" s="12"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="43" t="s">
-        <v>6370</v>
+        <v>6389</v>
       </c>
       <c r="B15" s="43" t="s">
         <v>3998</v>
@@ -63918,73 +64007,73 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6371</v>
+        <v>6390</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>6372</v>
+        <v>6391</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6373</v>
+        <v>6392</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>6374</v>
+        <v>6393</v>
       </c>
       <c r="C17" s="12"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>6375</v>
+        <v>6394</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>6376</v>
+        <v>6395</v>
       </c>
       <c r="C18" s="12"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6377</v>
+        <v>6396</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>6378</v>
+        <v>6397</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6379</v>
+        <v>6398</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>6380</v>
+        <v>6399</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6381</v>
+        <v>6400</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>6382</v>
+        <v>6401</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6383</v>
+        <v>6402</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>6384</v>
+        <v>6403</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>6385</v>
+        <v>6404</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>6386</v>
+        <v>6405</v>
       </c>
       <c r="C23" s="12"/>
     </row>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10219" uniqueCount="6406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10222" uniqueCount="6409">
   <si>
     <t>Entry</t>
   </si>
@@ -18730,13 +18730,28 @@
     <t>this tastes bad</t>
   </si>
   <si>
+    <t>using normal SVO for this can be considered vulgar or blunt, but is acceptable when used with animals, monsters, or enemies</t>
+  </si>
+  <si>
+    <t>jek meidda mek á knjám</t>
+  </si>
+  <si>
+    <t>i hurt my knees</t>
+  </si>
+  <si>
+    <t>jek hend henni í hendi</t>
+  </si>
+  <si>
+    <t>i hold her hand</t>
+  </si>
+  <si>
     <t>i'm cold</t>
   </si>
   <si>
-    <t>jek meidda mek á knjám</t>
-  </si>
-  <si>
-    <t>i hurt my knees</t>
+    <t>hon skurðar støttu ór viði</t>
+  </si>
+  <si>
+    <t>she carves a statue out of wood</t>
   </si>
   <si>
     <t>mer er skjallað</t>
@@ -18745,10 +18760,10 @@
     <t>i'm scared</t>
   </si>
   <si>
-    <t>jek hend henni í hendi</t>
-  </si>
-  <si>
-    <t>i hold her hand</t>
+    <t>hafmeyjarnar munu rœna at afleiða þek, ef kemsk þú of nærra til þeira</t>
+  </si>
+  <si>
+    <t>sirens will try to seduce you if you get too close to them</t>
   </si>
   <si>
     <t>mer er vel</t>
@@ -18757,22 +18772,16 @@
     <t>i'm good / i'm fine</t>
   </si>
   <si>
-    <t>hon skurðar støttu ór viði</t>
-  </si>
-  <si>
-    <t>she carves a statue out of wood</t>
-  </si>
-  <si>
     <t>mer er þurst</t>
   </si>
   <si>
     <t>i'm thirsty</t>
   </si>
   <si>
-    <t>hafmeyjarnar munu rœna at afleiða þek, ef kemsk þú of nærra til þeira</t>
-  </si>
-  <si>
-    <t>sirens will try to seduce you if you get too close to them</t>
+    <t>hann værir virkandi</t>
+  </si>
+  <si>
+    <t>he might be busy</t>
   </si>
   <si>
     <t>mer er svangt</t>
@@ -18781,16 +18790,22 @@
     <t>i'm hungry</t>
   </si>
   <si>
+    <t>hann værði virkandi</t>
+  </si>
+  <si>
+    <t>he could have been busy</t>
+  </si>
+  <si>
     <t>mer er vreitt</t>
   </si>
   <si>
     <t>i'm angry</t>
   </si>
   <si>
-    <t>hann værir virkandi</t>
-  </si>
-  <si>
-    <t>he might be busy</t>
+    <t>afallinn villans atlar eigi at vera svindlað af manni</t>
+  </si>
+  <si>
+    <t>the forces of nature are not to be trifled with</t>
   </si>
   <si>
     <t>mer er gleðugt</t>
@@ -18799,22 +18814,16 @@
     <t>i'm happy</t>
   </si>
   <si>
-    <t>hann værði virkandi</t>
-  </si>
-  <si>
-    <t>he could have been busy</t>
-  </si>
-  <si>
     <t>hanum er vel</t>
   </si>
   <si>
     <t>he is doing okay</t>
   </si>
   <si>
-    <t>afallinn villans atlar eigi at vera svindlað af manni</t>
-  </si>
-  <si>
-    <t>the forces of nature are not to be trifled with</t>
+    <t>maðr ná venjuliga eigi hleypa yfir tre</t>
+  </si>
+  <si>
+    <t>one cannot normally jump over a tree</t>
   </si>
   <si>
     <t>hanum er illa</t>
@@ -18823,16 +18832,16 @@
     <t>he is not okay</t>
   </si>
   <si>
-    <t>maðr ná venjuliga eigi hleypa yfir tre</t>
-  </si>
-  <si>
-    <t>one cannot normally jump over a tree</t>
-  </si>
-  <si>
     <t>þat er dær</t>
   </si>
   <si>
     <t>there's a deer</t>
+  </si>
+  <si>
+    <t>skrímslit er svangt</t>
+  </si>
+  <si>
+    <t>the monster is hungry</t>
   </si>
   <si>
     <t>þat er dærin</t>
@@ -62997,10 +63006,7 @@
       </c>
     </row>
     <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" s="43" t="s">
-        <v>6183</v>
-      </c>
-      <c r="C32" s="43" t="s">
+      <c r="A32" s="45" t="s">
         <v>6224</v>
       </c>
       <c r="E32" s="43" t="s">
@@ -63011,139 +63017,139 @@
       </c>
     </row>
     <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="43" t="s">
+      <c r="E33" s="43" t="s">
         <v>6227</v>
       </c>
-      <c r="C33" s="43" t="s">
+      <c r="G33" s="43" t="s">
         <v>6228</v>
-      </c>
-      <c r="E33" s="43" t="s">
-        <v>6229</v>
-      </c>
-      <c r="G33" s="43" t="s">
-        <v>6230</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="43" t="s">
+        <v>6183</v>
+      </c>
+      <c r="C34" s="43" t="s">
+        <v>6229</v>
+      </c>
+      <c r="E34" s="43" t="s">
+        <v>6230</v>
+      </c>
+      <c r="G34" s="43" t="s">
         <v>6231</v>
-      </c>
-      <c r="C34" s="43" t="s">
-        <v>6232</v>
-      </c>
-      <c r="E34" s="43" t="s">
-        <v>6233</v>
-      </c>
-      <c r="G34" s="43" t="s">
-        <v>6234</v>
       </c>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="43" t="s">
+        <v>6232</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>6233</v>
+      </c>
+      <c r="E35" s="45" t="s">
+        <v>6234</v>
+      </c>
+      <c r="G35" s="45" t="s">
         <v>6235</v>
-      </c>
-      <c r="C35" s="43" t="s">
-        <v>6236</v>
-      </c>
-      <c r="E35" s="45" t="s">
-        <v>6237</v>
-      </c>
-      <c r="G35" s="45" t="s">
-        <v>6238</v>
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="43" t="s">
-        <v>6239</v>
+        <v>6236</v>
       </c>
       <c r="C36" s="43" t="s">
-        <v>6240</v>
+        <v>6237</v>
       </c>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="43" t="s">
+        <v>6238</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>6239</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>6240</v>
+      </c>
+      <c r="G37" s="43" t="s">
         <v>6241</v>
-      </c>
-      <c r="C37" s="43" t="s">
-        <v>6242</v>
-      </c>
-      <c r="E37" s="43" t="s">
-        <v>6243</v>
-      </c>
-      <c r="G37" s="43" t="s">
-        <v>6244</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="43" t="s">
+        <v>6242</v>
+      </c>
+      <c r="C38" s="43" t="s">
+        <v>6243</v>
+      </c>
+      <c r="E38" s="43" t="s">
+        <v>6244</v>
+      </c>
+      <c r="G38" s="43" t="s">
         <v>6245</v>
-      </c>
-      <c r="C38" s="43" t="s">
-        <v>6246</v>
-      </c>
-      <c r="E38" s="43" t="s">
-        <v>6247</v>
-      </c>
-      <c r="G38" s="43" t="s">
-        <v>6248</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="43" t="s">
+        <v>6246</v>
+      </c>
+      <c r="C39" s="43" t="s">
+        <v>6247</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>6248</v>
+      </c>
+      <c r="G39" s="45" t="s">
         <v>6249</v>
-      </c>
-      <c r="C39" s="43" t="s">
-        <v>6250</v>
-      </c>
-      <c r="E39" s="45" t="s">
-        <v>6251</v>
-      </c>
-      <c r="G39" s="45" t="s">
-        <v>6252</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="43" t="s">
+        <v>6250</v>
+      </c>
+      <c r="C40" s="43" t="s">
+        <v>6251</v>
+      </c>
+    </row>
+    <row r="41" ht="18.75" customHeight="1">
+      <c r="A41" s="43" t="s">
+        <v>6252</v>
+      </c>
+      <c r="C41" s="43" t="s">
         <v>6253</v>
       </c>
-      <c r="C40" s="43" t="s">
+      <c r="E41" s="45" t="s">
         <v>6254</v>
       </c>
-    </row>
-    <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" s="43"/>
-      <c r="B41" s="43"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="45" t="s">
+      <c r="G41" s="45" t="s">
         <v>6255</v>
       </c>
-      <c r="G41" s="45" t="s">
+    </row>
+    <row r="42" ht="18.75" customHeight="1">
+      <c r="A42" s="43" t="s">
         <v>6256</v>
       </c>
-    </row>
-    <row r="42" ht="18.75" customHeight="1">
-      <c r="A42" s="43"/>
-      <c r="B42" s="43"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
+      <c r="C42" s="43" t="s">
+        <v>6257</v>
+      </c>
       <c r="E42" s="45" t="s">
-        <v>6257</v>
+        <v>6258</v>
       </c>
       <c r="G42" s="45" t="s">
-        <v>6258</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1">
-      <c r="A43" s="43"/>
-      <c r="B43" s="43"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
+      <c r="A43" s="43" t="s">
+        <v>6260</v>
+      </c>
+      <c r="C43" s="43" t="s">
+        <v>6261</v>
+      </c>
       <c r="E43" s="45" t="s">
-        <v>6259</v>
+        <v>6262</v>
       </c>
       <c r="G43" s="47" t="s">
-        <v>6260</v>
+        <v>6263</v>
       </c>
     </row>
     <row r="44" ht="18.75" customHeight="1">
@@ -63152,10 +63158,10 @@
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
       <c r="E44" s="45" t="s">
-        <v>6261</v>
+        <v>6264</v>
       </c>
       <c r="G44" s="45" t="s">
-        <v>6262</v>
+        <v>6265</v>
       </c>
     </row>
     <row r="45" ht="18.75" customHeight="1">
@@ -63219,7 +63225,66 @@
       <c r="H50" s="45"/>
     </row>
   </sheetData>
-  <mergeCells count="132">
+  <mergeCells count="135">
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E35:F36"/>
+    <mergeCell ref="G35:H36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="E39:F40"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A30:D31"/>
+    <mergeCell ref="A32:D33"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G10:H10"/>
@@ -63296,62 +63361,6 @@
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="G26:H26"/>
     <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E35:F36"/>
-    <mergeCell ref="G35:H36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A30:D31"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C39:D39"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -63371,10 +63380,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="43" t="s">
-        <v>6263</v>
+        <v>6266</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>6264</v>
+        <v>6267</v>
       </c>
       <c r="C1" s="12"/>
     </row>
@@ -63383,34 +63392,34 @@
         <v>38</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>6265</v>
+        <v>6268</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>6266</v>
+        <v>6269</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6267</v>
+        <v>6270</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>6268</v>
+        <v>6271</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6269</v>
+        <v>6272</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>6270</v>
+        <v>6273</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>6271</v>
+        <v>6274</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -63419,70 +63428,70 @@
         <v>1872</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6272</v>
+        <v>6275</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>6273</v>
+        <v>6276</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6274</v>
+        <v>6277</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>6275</v>
+        <v>6278</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6276</v>
+        <v>6279</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>6277</v>
+        <v>6280</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6278</v>
+        <v>6281</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>6279</v>
+        <v>6282</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6280</v>
+        <v>6283</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>6281</v>
+        <v>6284</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6282</v>
+        <v>6285</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>6283</v>
+        <v>6286</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>6284</v>
+        <v>6287</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>6285</v>
+        <v>6288</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>6286</v>
+        <v>6289</v>
       </c>
       <c r="C13" s="12"/>
     </row>
@@ -63491,7 +63500,7 @@
         <v>4949</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>6287</v>
+        <v>6290</v>
       </c>
       <c r="C14" s="12"/>
     </row>
@@ -63502,19 +63511,19 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6288</v>
+        <v>6291</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>6289</v>
+        <v>6292</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6290</v>
+        <v>6293</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>6291</v>
+        <v>6294</v>
       </c>
       <c r="C17" s="12"/>
     </row>
@@ -63525,334 +63534,334 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6292</v>
+        <v>6295</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>6293</v>
+        <v>6296</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6294</v>
+        <v>6297</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>6295</v>
+        <v>6298</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6296</v>
+        <v>6299</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>6297</v>
+        <v>6300</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6298</v>
+        <v>6301</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>6299</v>
+        <v>6302</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>6300</v>
+        <v>6303</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>6301</v>
+        <v>6304</v>
       </c>
       <c r="C23" s="12"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="43" t="s">
-        <v>6302</v>
+        <v>6305</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>6303</v>
+        <v>6306</v>
       </c>
       <c r="C24" s="12"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="43" t="s">
-        <v>6304</v>
+        <v>6307</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>6305</v>
+        <v>6308</v>
       </c>
       <c r="C25" s="12"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="43" t="s">
-        <v>6306</v>
+        <v>6309</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>6307</v>
+        <v>6310</v>
       </c>
       <c r="C26" s="12"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="43" t="s">
-        <v>6308</v>
+        <v>6311</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>6309</v>
+        <v>6312</v>
       </c>
       <c r="C27" s="12"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="43" t="s">
-        <v>6310</v>
+        <v>6313</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>6311</v>
+        <v>6314</v>
       </c>
       <c r="C28" s="12"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="43" t="s">
-        <v>6312</v>
+        <v>6315</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>6313</v>
+        <v>6316</v>
       </c>
       <c r="C29" s="12"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="43" t="s">
-        <v>6314</v>
+        <v>6317</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>6315</v>
+        <v>6318</v>
       </c>
       <c r="C30" s="12"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="43" t="s">
-        <v>6316</v>
+        <v>6319</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>6317</v>
+        <v>6320</v>
       </c>
       <c r="C31" s="12"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="43" t="s">
-        <v>6318</v>
+        <v>6321</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>6319</v>
+        <v>6322</v>
       </c>
       <c r="C32" s="12"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="43" t="s">
-        <v>6320</v>
+        <v>6323</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>6321</v>
+        <v>6324</v>
       </c>
       <c r="C33" s="12"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="43" t="s">
-        <v>6322</v>
+        <v>6325</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>6323</v>
+        <v>6326</v>
       </c>
       <c r="C34" s="12"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="43" t="s">
-        <v>6324</v>
+        <v>6327</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>6325</v>
+        <v>6328</v>
       </c>
       <c r="C35" s="12"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="43" t="s">
-        <v>6326</v>
+        <v>6329</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>6327</v>
+        <v>6330</v>
       </c>
       <c r="C36" s="12"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="43" t="s">
-        <v>6328</v>
+        <v>6331</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>6329</v>
+        <v>6332</v>
       </c>
       <c r="C37" s="12"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="43" t="s">
-        <v>6330</v>
+        <v>6333</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>6331</v>
+        <v>6334</v>
       </c>
       <c r="C38" s="12"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="43" t="s">
-        <v>6332</v>
+        <v>6335</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>6333</v>
+        <v>6336</v>
       </c>
       <c r="C39" s="12"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="43" t="s">
-        <v>6334</v>
+        <v>6337</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>6335</v>
+        <v>6338</v>
       </c>
       <c r="C40" s="12"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="43" t="s">
-        <v>6336</v>
+        <v>6339</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>6337</v>
+        <v>6340</v>
       </c>
       <c r="C41" s="12"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="43" t="s">
-        <v>6338</v>
+        <v>6341</v>
       </c>
       <c r="B42" s="43" t="s">
-        <v>6339</v>
+        <v>6342</v>
       </c>
       <c r="C42" s="12"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="43" t="s">
-        <v>6340</v>
+        <v>6343</v>
       </c>
       <c r="B43" s="43" t="s">
-        <v>6341</v>
+        <v>6344</v>
       </c>
       <c r="C43" s="12"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" s="43" t="s">
-        <v>6342</v>
+        <v>6345</v>
       </c>
       <c r="B44" s="43" t="s">
-        <v>6343</v>
+        <v>6346</v>
       </c>
       <c r="C44" s="12"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="43" t="s">
-        <v>6344</v>
+        <v>6347</v>
       </c>
       <c r="B45" s="43" t="s">
-        <v>6345</v>
+        <v>6348</v>
       </c>
       <c r="C45" s="12"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="43" t="s">
-        <v>6346</v>
+        <v>6349</v>
       </c>
       <c r="B46" s="43" t="s">
-        <v>6347</v>
+        <v>6350</v>
       </c>
       <c r="C46" s="12"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="43" t="s">
-        <v>6348</v>
+        <v>6351</v>
       </c>
       <c r="B47" s="43" t="s">
-        <v>6349</v>
+        <v>6352</v>
       </c>
       <c r="C47" s="12"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="43" t="s">
-        <v>6350</v>
+        <v>6353</v>
       </c>
       <c r="B48" s="43" t="s">
-        <v>6351</v>
+        <v>6354</v>
       </c>
       <c r="C48" s="12"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" s="43" t="s">
-        <v>6352</v>
+        <v>6355</v>
       </c>
       <c r="B49" s="43" t="s">
-        <v>6353</v>
+        <v>6356</v>
       </c>
       <c r="C49" s="12"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" s="43" t="s">
-        <v>6354</v>
+        <v>6357</v>
       </c>
       <c r="B50" s="43" t="s">
-        <v>6355</v>
+        <v>6358</v>
       </c>
       <c r="C50" s="12"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" s="43" t="s">
-        <v>6356</v>
+        <v>6359</v>
       </c>
       <c r="B51" s="43" t="s">
-        <v>6357</v>
+        <v>6360</v>
       </c>
       <c r="C51" s="12"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" s="43" t="s">
-        <v>6358</v>
+        <v>6361</v>
       </c>
       <c r="B52" s="43" t="s">
-        <v>6359</v>
+        <v>6362</v>
       </c>
       <c r="C52" s="12"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" s="43" t="s">
-        <v>6360</v>
+        <v>6363</v>
       </c>
       <c r="B53" s="43" t="s">
-        <v>6361</v>
+        <v>6364</v>
       </c>
       <c r="C53" s="12"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" s="43" t="s">
-        <v>6362</v>
+        <v>6365</v>
       </c>
       <c r="B54" s="43" t="s">
-        <v>6363</v>
+        <v>6366</v>
       </c>
       <c r="C54" s="12"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" s="43" t="s">
-        <v>6364</v>
+        <v>6367</v>
       </c>
       <c r="B55" s="43" t="s">
-        <v>6365</v>
+        <v>6368</v>
       </c>
       <c r="C55" s="12"/>
     </row>
@@ -63875,130 +63884,130 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="48" t="s">
-        <v>6366</v>
+        <v>6369</v>
       </c>
       <c r="C1" s="12"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="48" t="s">
-        <v>6367</v>
+        <v>6370</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>6368</v>
+        <v>6371</v>
       </c>
       <c r="C2" s="12"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>6369</v>
+        <v>6372</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6290</v>
+        <v>6293</v>
       </c>
       <c r="C3" s="12"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>6290</v>
+        <v>6293</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>6277</v>
+        <v>6280</v>
       </c>
       <c r="C4" s="12"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>6370</v>
+        <v>6373</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>6279</v>
+        <v>6282</v>
       </c>
       <c r="C5" s="12"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="43" t="s">
-        <v>6371</v>
+        <v>6374</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>6372</v>
+        <v>6375</v>
       </c>
       <c r="C6" s="12"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="43" t="s">
-        <v>6373</v>
+        <v>6376</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>6374</v>
+        <v>6377</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="43" t="s">
-        <v>6375</v>
+        <v>6378</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>6376</v>
+        <v>6379</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="43" t="s">
-        <v>6377</v>
+        <v>6380</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>6378</v>
+        <v>6381</v>
       </c>
       <c r="C9" s="12"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="43" t="s">
-        <v>6379</v>
+        <v>6382</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>6380</v>
+        <v>6383</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="43" t="s">
-        <v>6381</v>
+        <v>6384</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>6382</v>
+        <v>6385</v>
       </c>
       <c r="C11" s="12"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="43" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="C12" s="12"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>6386</v>
+        <v>6389</v>
       </c>
       <c r="C13" s="12"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="43" t="s">
-        <v>6387</v>
+        <v>6390</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>6388</v>
+        <v>6391</v>
       </c>
       <c r="C14" s="12"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="43" t="s">
-        <v>6389</v>
+        <v>6392</v>
       </c>
       <c r="B15" s="43" t="s">
         <v>3998</v>
@@ -64007,73 +64016,73 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>6390</v>
+        <v>6393</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>6391</v>
+        <v>6394</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="43" t="s">
-        <v>6392</v>
+        <v>6395</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>6393</v>
+        <v>6396</v>
       </c>
       <c r="C17" s="12"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>6394</v>
+        <v>6397</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>6395</v>
+        <v>6398</v>
       </c>
       <c r="C18" s="12"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="43" t="s">
-        <v>6396</v>
+        <v>6399</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>6397</v>
+        <v>6400</v>
       </c>
       <c r="C19" s="12"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="43" t="s">
-        <v>6398</v>
+        <v>6401</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>6399</v>
+        <v>6402</v>
       </c>
       <c r="C20" s="12"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>6400</v>
+        <v>6403</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>6401</v>
+        <v>6404</v>
       </c>
       <c r="C21" s="12"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="43" t="s">
-        <v>6402</v>
+        <v>6405</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>6403</v>
+        <v>6406</v>
       </c>
       <c r="C22" s="12"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="43" t="s">
-        <v>6404</v>
+        <v>6407</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>6405</v>
+        <v>6408</v>
       </c>
       <c r="C23" s="12"/>
     </row>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -3875,7 +3875,7 @@
     <t>gjalda</t>
   </si>
   <si>
-    <t>to pay back, to repay, to tribute; to be paid by one's employer</t>
+    <t>to pay back, to repay, to tribute; to pay an employee or worker</t>
   </si>
   <si>
     <t>gjalla</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -3899,7 +3899,7 @@
     <t>gjøldun</t>
   </si>
   <si>
-    <t>wage, salary (earnings from work)</t>
+    <t>payment, tribute; wage, salary (earnings from work)</t>
   </si>
   <si>
     <t>gjølnar</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -12302,7 +12302,7 @@
     <t>urð</t>
   </si>
   <si>
-    <t>kiln, oven, furnace</t>
+    <t>kiln (an oven or furnace made of stones)</t>
   </si>
   <si>
     <t>urn</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -12302,7 +12302,7 @@
     <t>urð</t>
   </si>
   <si>
-    <t>kiln (an oven or furnace made of stones)</t>
+    <t>kiln (an oven or furnace made by piling stones)</t>
   </si>
   <si>
     <t>urn</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -13178,7 +13178,7 @@
     <t>verða</t>
   </si>
   <si>
-    <t>to become (with nominative); will be, will turn out (with nominative)</t>
+    <t>to become (with nominative); to have, to must, to need to do something (with clause); will be, will turn out (with nominative)</t>
   </si>
   <si>
     <t>verðr</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -200,7 +200,7 @@
     <t>in a ... way (with accusative adjective)</t>
   </si>
   <si>
-    <t>á-glapplega</t>
+    <t>á-glappliga</t>
   </si>
   <si>
     <t>neuter noun</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -5957,10 +5957,10 @@
     <t>around, surrounding (with dative)</t>
   </si>
   <si>
-    <t>í kveldi</t>
-  </si>
-  <si>
-    <t>in the evening</t>
+    <t>í kvøld</t>
+  </si>
+  <si>
+    <t>tonight</t>
   </si>
   <si>
     <t>í lagi</t>
@@ -5981,10 +5981,10 @@
     <t>between (with datives)</t>
   </si>
   <si>
-    <t>í mørgni</t>
-  </si>
-  <si>
-    <t>in the morning</t>
+    <t>í mørgun</t>
+  </si>
+  <si>
+    <t>tomorrow</t>
   </si>
   <si>
     <t>í órøð</t>
@@ -32472,7 +32472,7 @@
       <c r="C967" s="3" t="s">
         <v>1968</v>
       </c>
-      <c r="D967" s="5"/>
+      <c r="D967" s="3"/>
     </row>
     <row r="968" ht="18.75" customHeight="1">
       <c r="A968" s="3" t="s">
@@ -32520,7 +32520,7 @@
       <c r="C971" s="3" t="s">
         <v>1976</v>
       </c>
-      <c r="D971" s="5"/>
+      <c r="D971" s="3"/>
     </row>
     <row r="972" ht="18.75" customHeight="1">
       <c r="A972" s="3" t="s">

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -3260,7 +3260,7 @@
     <t>fen, patterned bog; a type of marshland where pools and ponds are polka-dotted everywhere but the land is otherwise solid</t>
   </si>
   <si>
-    <t>feskr</t>
+    <t>ferskr</t>
   </si>
   <si>
     <t>fresh</t>
@@ -5657,7 +5657,7 @@
     <t>horn, antler; fin (of fishes, whales, and sharks); corner (protruding, convex); mountain peak</t>
   </si>
   <si>
-    <t>horn-kýr</t>
+    <t>horn-reyt</t>
   </si>
   <si>
     <t>yak</t>
@@ -6947,6 +6947,12 @@
     <t>jar, crock</t>
   </si>
   <si>
+    <t>kú</t>
+  </si>
+  <si>
+    <t>cow (female cattle)</t>
+  </si>
+  <si>
     <t>kuldi</t>
   </si>
   <si>
@@ -7067,12 +7073,6 @@
     <t>gender, sex, race, kin</t>
   </si>
   <si>
-    <t>kýr</t>
-  </si>
-  <si>
-    <t>cow (female cattle)</t>
-  </si>
-  <si>
     <t>kyr-ligr</t>
   </si>
   <si>
@@ -8504,7 +8504,7 @@
     <t>auxiliary</t>
   </si>
   <si>
-    <t>will, shall</t>
+    <t>will probably</t>
   </si>
   <si>
     <t>mús</t>
@@ -8645,18 +8645,18 @@
     <t>pleasuring, satisfying, contenting</t>
   </si>
   <si>
+    <t>næjan</t>
+  </si>
+  <si>
+    <t>from nearby</t>
+  </si>
+  <si>
     <t>nær</t>
   </si>
   <si>
     <t>nigh, near (nærri = comparative, næstr = superlative)</t>
   </si>
   <si>
-    <t>næran</t>
-  </si>
-  <si>
-    <t>from nearby</t>
-  </si>
-  <si>
     <t>næveg</t>
   </si>
   <si>
@@ -11156,7 +11156,7 @@
     <t>skulu</t>
   </si>
   <si>
-    <t>shall, must</t>
+    <t>will, shall, must (an obligation or something that will definitely happen)</t>
   </si>
   <si>
     <t>skurða</t>
@@ -34848,7 +34848,7 @@
         <v>2297</v>
       </c>
       <c r="B1131" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C1131" s="3" t="s">
         <v>2298</v>
@@ -34872,7 +34872,7 @@
         <v>2301</v>
       </c>
       <c r="B1133" s="4" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C1133" s="3" t="s">
         <v>2302</v>
@@ -34884,7 +34884,7 @@
         <v>2303</v>
       </c>
       <c r="B1134" s="4" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C1134" s="3" t="s">
         <v>2304</v>
@@ -34896,7 +34896,7 @@
         <v>2305</v>
       </c>
       <c r="B1135" s="4" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C1135" s="3" t="s">
         <v>2306</v>
@@ -34908,40 +34908,38 @@
         <v>2307</v>
       </c>
       <c r="B1136" s="4" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C1136" s="3" t="s">
         <v>2308</v>
       </c>
-      <c r="D1136" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="D1136" s="3"/>
     </row>
     <row r="1137" ht="18.75" customHeight="1">
       <c r="A1137" s="3" t="s">
         <v>2309</v>
       </c>
       <c r="B1137" s="4" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C1137" s="3" t="s">
         <v>2310</v>
       </c>
-      <c r="D1137" s="5"/>
+      <c r="D1137" s="3" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="1138" ht="18.75" customHeight="1">
       <c r="A1138" s="3" t="s">
         <v>2311</v>
       </c>
       <c r="B1138" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C1138" s="3" t="s">
         <v>2312</v>
       </c>
-      <c r="D1138" s="3" t="s">
-        <v>223</v>
-      </c>
+      <c r="D1138" s="5"/>
     </row>
     <row r="1139" ht="18.75" customHeight="1">
       <c r="A1139" s="3" t="s">
@@ -34953,7 +34951,9 @@
       <c r="C1139" s="3" t="s">
         <v>2314</v>
       </c>
-      <c r="D1139" s="3"/>
+      <c r="D1139" s="3" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="1140" ht="18.75" customHeight="1">
       <c r="A1140" s="3" t="s">
@@ -34972,7 +34972,7 @@
         <v>2317</v>
       </c>
       <c r="B1141" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C1141" s="3" t="s">
         <v>2318</v>
@@ -34984,52 +34984,50 @@
         <v>2319</v>
       </c>
       <c r="B1142" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C1142" s="3" t="s">
         <v>2320</v>
       </c>
-      <c r="D1142" s="3" t="s">
-        <v>86</v>
-      </c>
+      <c r="D1142" s="3"/>
     </row>
     <row r="1143" ht="18.75" customHeight="1">
       <c r="A1143" s="3" t="s">
         <v>2321</v>
       </c>
       <c r="B1143" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C1143" s="3" t="s">
         <v>2322</v>
       </c>
-      <c r="D1143" s="3"/>
+      <c r="D1143" s="3" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="1144" ht="18.75" customHeight="1">
       <c r="A1144" s="3" t="s">
         <v>2323</v>
       </c>
       <c r="B1144" s="4" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C1144" s="3" t="s">
         <v>2324</v>
       </c>
-      <c r="D1144" s="5"/>
+      <c r="D1144" s="3"/>
     </row>
     <row r="1145" ht="18.75" customHeight="1">
       <c r="A1145" s="3" t="s">
         <v>2325</v>
       </c>
       <c r="B1145" s="4" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C1145" s="3" t="s">
         <v>2326</v>
       </c>
-      <c r="D1145" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="D1145" s="5"/>
     </row>
     <row r="1146" ht="18.75" customHeight="1">
       <c r="A1146" s="3" t="s">
@@ -35041,14 +35039,16 @@
       <c r="C1146" s="3" t="s">
         <v>2328</v>
       </c>
-      <c r="D1146" s="3"/>
+      <c r="D1146" s="3" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="1147" ht="18.75" customHeight="1">
       <c r="A1147" s="3" t="s">
         <v>2329</v>
       </c>
       <c r="B1147" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C1147" s="3" t="s">
         <v>2330</v>
@@ -35060,7 +35060,7 @@
         <v>2331</v>
       </c>
       <c r="B1148" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C1148" s="3" t="s">
         <v>2332</v>
@@ -35072,7 +35072,7 @@
         <v>2333</v>
       </c>
       <c r="B1149" s="4" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C1149" s="3" t="s">
         <v>2334</v>
@@ -38324,24 +38324,24 @@
         <v>2863</v>
       </c>
       <c r="B1413" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C1413" s="3" t="s">
         <v>2864</v>
       </c>
-      <c r="D1413" s="5"/>
+      <c r="D1413" s="3"/>
     </row>
     <row r="1414" ht="18.75" customHeight="1">
       <c r="A1414" s="3" t="s">
         <v>2865</v>
       </c>
       <c r="B1414" s="4" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C1414" s="3" t="s">
         <v>2866</v>
       </c>
-      <c r="D1414" s="3"/>
+      <c r="D1414" s="5"/>
     </row>
     <row r="1415" ht="18.75" customHeight="1">
       <c r="A1415" s="3" t="s">
@@ -50772,7 +50772,7 @@
         <v>4872</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="O3" s="10" t="s">
         <v>4880</v>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -5657,7 +5657,7 @@
     <t>horn, antler; fin (of fishes, whales, and sharks); corner (protruding, convex); mountain peak</t>
   </si>
   <si>
-    <t>horn-reyt</t>
+    <t>horn-neyt</t>
   </si>
   <si>
     <t>yak</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -5657,628 +5657,628 @@
     <t>horn, antler; fin (of fishes, whales, and sharks); corner (protruding, convex); mountain peak</t>
   </si>
   <si>
-    <t>horn-neyt</t>
+    <t>hórr</t>
+  </si>
+  <si>
+    <t>adulterer (a married man who has sexual intercourse with a woman not his wife)</t>
+  </si>
+  <si>
+    <t>høttr</t>
+  </si>
+  <si>
+    <t>hat, headwear</t>
+  </si>
+  <si>
+    <t>hrað-lyndr</t>
+  </si>
+  <si>
+    <t>impulsive, reckless, rash</t>
+  </si>
+  <si>
+    <t>hraði</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>hraðr</t>
+  </si>
+  <si>
+    <t>fast, quick</t>
+  </si>
+  <si>
+    <t>hræra</t>
+  </si>
+  <si>
+    <t>to mix, to stir (with an utensil) (with dative "what")</t>
+  </si>
+  <si>
+    <t>hrama</t>
+  </si>
+  <si>
+    <t>grid, frame, lattice</t>
+  </si>
+  <si>
+    <t>hrapn</t>
+  </si>
+  <si>
+    <t>raven</t>
+  </si>
+  <si>
+    <t>Hreifgría</t>
+  </si>
+  <si>
+    <t>Heirfgria (a kingdom in Myrkjørð)</t>
+  </si>
+  <si>
+    <t>hreinn</t>
+  </si>
+  <si>
+    <t>clean, bright, clear, pure</t>
+  </si>
+  <si>
+    <t>hreyst-leiki</t>
+  </si>
+  <si>
+    <t>health</t>
+  </si>
+  <si>
+    <t>hreystr</t>
+  </si>
+  <si>
+    <t>healthy, sound</t>
+  </si>
+  <si>
+    <t>hrím</t>
+  </si>
+  <si>
+    <t>hoarfrost, rime (crystalised frost)</t>
+  </si>
+  <si>
+    <t>hringja</t>
+  </si>
+  <si>
+    <t>to ring a bell</t>
+  </si>
+  <si>
+    <t>hringr</t>
+  </si>
+  <si>
+    <t>circle, ring; village, community</t>
+  </si>
+  <si>
+    <t>hrís</t>
+  </si>
+  <si>
+    <t>bush, shrub; small tree</t>
+  </si>
+  <si>
+    <t>hrís-ugr</t>
+  </si>
+  <si>
+    <t>overgrown with bushes</t>
+  </si>
+  <si>
+    <t>hrjá</t>
+  </si>
+  <si>
+    <t>to harrass, to bully, to distress, to vex</t>
+  </si>
+  <si>
+    <t>hrjáun</t>
+  </si>
+  <si>
+    <t>harassment, bullying</t>
+  </si>
+  <si>
+    <t>hrók</t>
+  </si>
+  <si>
+    <t>dress, gown</t>
+  </si>
+  <si>
+    <t>hrømu-breyð</t>
+  </si>
+  <si>
+    <t>waffle</t>
+  </si>
+  <si>
+    <t>hross</t>
+  </si>
+  <si>
+    <t>horse, steed</t>
+  </si>
+  <si>
+    <t>hruggr</t>
+  </si>
+  <si>
+    <t>spine</t>
+  </si>
+  <si>
+    <t>hrútr</t>
+  </si>
+  <si>
+    <t>ram (male sheep)</t>
+  </si>
+  <si>
+    <t>hrynja</t>
+  </si>
+  <si>
+    <t>to collapse onto the ground (objects)</t>
+  </si>
+  <si>
+    <t>weak verb c</t>
+  </si>
+  <si>
+    <t>húð</t>
+  </si>
+  <si>
+    <t>skin (of someone)</t>
+  </si>
+  <si>
+    <t>hug-mynd</t>
+  </si>
+  <si>
+    <t>idea, concept</t>
+  </si>
+  <si>
+    <t>hug-vá</t>
+  </si>
+  <si>
+    <t>stress, trauma</t>
+  </si>
+  <si>
+    <t>hugg-ligr</t>
+  </si>
+  <si>
+    <t>comfortable</t>
+  </si>
+  <si>
+    <t>hugga</t>
+  </si>
+  <si>
+    <t>to comfort someone (with accusative)</t>
+  </si>
+  <si>
+    <t>huggandi</t>
+  </si>
+  <si>
+    <t>comforting</t>
+  </si>
+  <si>
+    <t>hugr</t>
+  </si>
+  <si>
+    <t>mind, thoughts</t>
+  </si>
+  <si>
+    <t>hugsa</t>
+  </si>
+  <si>
+    <t>to think, to consider</t>
+  </si>
+  <si>
+    <t>huldinn</t>
+  </si>
+  <si>
+    <t>secluded, isolated, remote (of places); hidden (past participle of hylja)</t>
+  </si>
+  <si>
+    <t>hunang</t>
+  </si>
+  <si>
+    <t>honey</t>
+  </si>
+  <si>
+    <t>hundr</t>
+  </si>
+  <si>
+    <t>dog, hound</t>
+  </si>
+  <si>
+    <t>hundrað</t>
+  </si>
+  <si>
+    <t>hundred (hundrað = all singular, hundruð = all plural)</t>
+  </si>
+  <si>
+    <t>hungr</t>
+  </si>
+  <si>
+    <t>famine, dearth, starvation, severe hunger</t>
+  </si>
+  <si>
+    <t>hungr-laginn</t>
+  </si>
+  <si>
+    <t>faminated, wrought with famine</t>
+  </si>
+  <si>
+    <t>hunsa</t>
+  </si>
+  <si>
+    <t>to ignore, to pay no attention to (with accusative)</t>
+  </si>
+  <si>
+    <t>hurð</t>
+  </si>
+  <si>
+    <t>door</t>
+  </si>
+  <si>
+    <t>hurðar-fangr</t>
+  </si>
+  <si>
+    <t>doorknob</t>
+  </si>
+  <si>
+    <t>hús</t>
+  </si>
+  <si>
+    <t>house, home</t>
+  </si>
+  <si>
+    <t>hús-bóndi</t>
+  </si>
+  <si>
+    <t>head of the house</t>
+  </si>
+  <si>
+    <t>hús-karl</t>
+  </si>
+  <si>
+    <t>housecarl (huskarl); knight</t>
+  </si>
+  <si>
+    <t>hvaðan</t>
+  </si>
+  <si>
+    <t>question word</t>
+  </si>
+  <si>
+    <t>from where</t>
+  </si>
+  <si>
+    <t>hval-feiti</t>
+  </si>
+  <si>
+    <t>blubber, fat (of whales, dolphins, orcas, narwhals, etc)</t>
+  </si>
+  <si>
+    <t>hvalr</t>
+  </si>
+  <si>
+    <t>whale (rorquals, dolphins, orcas, narwhals, etc)</t>
+  </si>
+  <si>
+    <t>hvar</t>
+  </si>
+  <si>
+    <t>where</t>
+  </si>
+  <si>
+    <t>hvat</t>
+  </si>
+  <si>
+    <t>what</t>
+  </si>
+  <si>
+    <t>hve</t>
+  </si>
+  <si>
+    <t>how much/many of; how, in what manner, which way</t>
+  </si>
+  <si>
+    <t>hveiti</t>
+  </si>
+  <si>
+    <t>wheat</t>
+  </si>
+  <si>
+    <t>hvelpr</t>
+  </si>
+  <si>
+    <t>puppy</t>
+  </si>
+  <si>
+    <t>hven</t>
+  </si>
+  <si>
+    <t>when</t>
+  </si>
+  <si>
+    <t>hverfa</t>
+  </si>
+  <si>
+    <t>to disappear, to vanish</t>
+  </si>
+  <si>
+    <t>hverr</t>
+  </si>
+  <si>
+    <t>which, who</t>
+  </si>
+  <si>
+    <t>hví</t>
+  </si>
+  <si>
+    <t>why</t>
+  </si>
+  <si>
+    <t>hvika</t>
+  </si>
+  <si>
+    <t>to quail, to shiver, to cower, to shrink (intransitive)</t>
+  </si>
+  <si>
+    <t>hvikari</t>
+  </si>
+  <si>
+    <t>coward</t>
+  </si>
+  <si>
+    <t>hvíld</t>
+  </si>
+  <si>
+    <t>rest, break, paise</t>
+  </si>
+  <si>
+    <t>hvíldar-leyss</t>
+  </si>
+  <si>
+    <t>persistent, unyielding, relentless, restless, constant, stubborn</t>
+  </si>
+  <si>
+    <t>hvísla</t>
+  </si>
+  <si>
+    <t>to whisper</t>
+  </si>
+  <si>
+    <t>hvít-blár</t>
+  </si>
+  <si>
+    <t>light blue</t>
+  </si>
+  <si>
+    <t>hvít-brúnn</t>
+  </si>
+  <si>
+    <t>light brown</t>
+  </si>
+  <si>
+    <t>hvít-grár</t>
+  </si>
+  <si>
+    <t>light grey</t>
+  </si>
+  <si>
+    <t>hvít-grønn</t>
+  </si>
+  <si>
+    <t>light green, lime</t>
+  </si>
+  <si>
+    <t>hvít-gulr</t>
+  </si>
+  <si>
+    <t>light yellow</t>
+  </si>
+  <si>
+    <t>hvítr</t>
+  </si>
+  <si>
+    <t>white</t>
+  </si>
+  <si>
+    <t>hvort</t>
+  </si>
+  <si>
+    <t>whether, either</t>
+  </si>
+  <si>
+    <t>hyggja</t>
+  </si>
+  <si>
+    <t>to inspect, to examine (with ann + accusative)</t>
+  </si>
+  <si>
+    <t>hygli</t>
+  </si>
+  <si>
+    <t>consideration</t>
+  </si>
+  <si>
+    <t>hylja</t>
+  </si>
+  <si>
+    <t>to hide, to conceal, to cover (reflexive, or with accusative "hide what")</t>
+  </si>
+  <si>
+    <t>í</t>
+  </si>
+  <si>
+    <t>inside of (with accusative)</t>
+  </si>
+  <si>
+    <t>í dag</t>
+  </si>
+  <si>
+    <t>today</t>
+  </si>
+  <si>
+    <t>í gær</t>
+  </si>
+  <si>
+    <t>yesterday</t>
+  </si>
+  <si>
+    <t>í gøgnum</t>
+  </si>
+  <si>
+    <t>through (with dative)</t>
+  </si>
+  <si>
+    <t>í kringum með</t>
+  </si>
+  <si>
+    <t>around, surrounding (with dative)</t>
+  </si>
+  <si>
+    <t>í kvøld</t>
+  </si>
+  <si>
+    <t>tonight</t>
+  </si>
+  <si>
+    <t>í lagi</t>
+  </si>
+  <si>
+    <t>in order, all right; okay</t>
+  </si>
+  <si>
+    <t>í lífi</t>
+  </si>
+  <si>
+    <t>alive</t>
+  </si>
+  <si>
+    <t>í miðju með</t>
+  </si>
+  <si>
+    <t>between (with datives)</t>
+  </si>
+  <si>
+    <t>í mørgun</t>
+  </si>
+  <si>
+    <t>tomorrow</t>
+  </si>
+  <si>
+    <t>í órøð</t>
+  </si>
+  <si>
+    <t>chaotic, messy; wrong</t>
+  </si>
+  <si>
+    <t>í smæsta kosti</t>
+  </si>
+  <si>
+    <t>at least</t>
+  </si>
+  <si>
+    <t>í sømu stundunni</t>
+  </si>
+  <si>
+    <t>at the same time</t>
+  </si>
+  <si>
+    <t>í-fletta</t>
+  </si>
+  <si>
+    <t>emboidery</t>
+  </si>
+  <si>
+    <t>illa</t>
+  </si>
+  <si>
+    <t>badly, unwel (illar = worse, illast = worst)</t>
+  </si>
+  <si>
+    <t>illa-gras</t>
+  </si>
+  <si>
+    <t>unwanted weeds</t>
+  </si>
+  <si>
+    <t>inn</t>
+  </si>
+  <si>
+    <t>into (with accusative)</t>
+  </si>
+  <si>
+    <t>inn-lendingi</t>
+  </si>
+  <si>
+    <t>native, aboriginal, tribesman</t>
+  </si>
+  <si>
+    <t>inn-lendr</t>
+  </si>
+  <si>
+    <t>native, aboriginal</t>
+  </si>
+  <si>
+    <t>inn-lifinn</t>
+  </si>
+  <si>
+    <t>introverted</t>
+  </si>
+  <si>
+    <t>inn-rás</t>
+  </si>
+  <si>
+    <t>invasion</t>
+  </si>
+  <si>
+    <t>inn-renna</t>
+  </si>
+  <si>
+    <t>to invade (formal) (intransitive or with accusative)</t>
+  </si>
+  <si>
+    <t>inni</t>
+  </si>
+  <si>
+    <t>inside</t>
+  </si>
+  <si>
+    <t>innrás-maðr</t>
+  </si>
+  <si>
+    <t>invader</t>
+  </si>
+  <si>
+    <t>ís-alfr</t>
+  </si>
+  <si>
+    <t>ice spirit</t>
+  </si>
+  <si>
+    <t>ís-dreki</t>
+  </si>
+  <si>
+    <t>frost dragon</t>
+  </si>
+  <si>
+    <t>ís-kaldr</t>
+  </si>
+  <si>
+    <t>ice-cold, icy, freezing</t>
+  </si>
+  <si>
+    <t>íss</t>
+  </si>
+  <si>
+    <t>ice</t>
+  </si>
+  <si>
+    <t>já</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>jaki</t>
+  </si>
+  <si>
+    <t>broken ice</t>
+  </si>
+  <si>
+    <t>jakk</t>
   </si>
   <si>
     <t>yak</t>
-  </si>
-  <si>
-    <t>hórr</t>
-  </si>
-  <si>
-    <t>adulterer (a married man who has sexual intercourse with a woman not his wife)</t>
-  </si>
-  <si>
-    <t>høttr</t>
-  </si>
-  <si>
-    <t>hat, headwear</t>
-  </si>
-  <si>
-    <t>hrað-lyndr</t>
-  </si>
-  <si>
-    <t>impulsive, reckless, rash</t>
-  </si>
-  <si>
-    <t>hraði</t>
-  </si>
-  <si>
-    <t>speed</t>
-  </si>
-  <si>
-    <t>hraðr</t>
-  </si>
-  <si>
-    <t>fast, quick</t>
-  </si>
-  <si>
-    <t>hræra</t>
-  </si>
-  <si>
-    <t>to mix, to stir (with an utensil) (with dative "what")</t>
-  </si>
-  <si>
-    <t>hrama</t>
-  </si>
-  <si>
-    <t>grid, frame, lattice</t>
-  </si>
-  <si>
-    <t>hrapn</t>
-  </si>
-  <si>
-    <t>raven</t>
-  </si>
-  <si>
-    <t>Hreifgría</t>
-  </si>
-  <si>
-    <t>Heirfgria (a kingdom in Myrkjørð)</t>
-  </si>
-  <si>
-    <t>hreinn</t>
-  </si>
-  <si>
-    <t>clean, bright, clear, pure</t>
-  </si>
-  <si>
-    <t>hreyst-leiki</t>
-  </si>
-  <si>
-    <t>health</t>
-  </si>
-  <si>
-    <t>hreystr</t>
-  </si>
-  <si>
-    <t>healthy, sound</t>
-  </si>
-  <si>
-    <t>hrím</t>
-  </si>
-  <si>
-    <t>hoarfrost, rime (crystalised frost)</t>
-  </si>
-  <si>
-    <t>hringja</t>
-  </si>
-  <si>
-    <t>to ring a bell</t>
-  </si>
-  <si>
-    <t>hringr</t>
-  </si>
-  <si>
-    <t>circle, ring; village, community</t>
-  </si>
-  <si>
-    <t>hrís</t>
-  </si>
-  <si>
-    <t>bush, shrub; small tree</t>
-  </si>
-  <si>
-    <t>hrís-ugr</t>
-  </si>
-  <si>
-    <t>overgrown with bushes</t>
-  </si>
-  <si>
-    <t>hrjá</t>
-  </si>
-  <si>
-    <t>to harrass, to bully, to distress, to vex</t>
-  </si>
-  <si>
-    <t>hrjáun</t>
-  </si>
-  <si>
-    <t>harassment, bullying</t>
-  </si>
-  <si>
-    <t>hrók</t>
-  </si>
-  <si>
-    <t>dress, gown</t>
-  </si>
-  <si>
-    <t>hrømu-breyð</t>
-  </si>
-  <si>
-    <t>waffle</t>
-  </si>
-  <si>
-    <t>hross</t>
-  </si>
-  <si>
-    <t>horse, steed</t>
-  </si>
-  <si>
-    <t>hruggr</t>
-  </si>
-  <si>
-    <t>spine</t>
-  </si>
-  <si>
-    <t>hrútr</t>
-  </si>
-  <si>
-    <t>ram (male sheep)</t>
-  </si>
-  <si>
-    <t>hrynja</t>
-  </si>
-  <si>
-    <t>to collapse onto the ground (objects)</t>
-  </si>
-  <si>
-    <t>weak verb c</t>
-  </si>
-  <si>
-    <t>húð</t>
-  </si>
-  <si>
-    <t>skin (of someone)</t>
-  </si>
-  <si>
-    <t>hug-mynd</t>
-  </si>
-  <si>
-    <t>idea, concept</t>
-  </si>
-  <si>
-    <t>hug-vá</t>
-  </si>
-  <si>
-    <t>stress, trauma</t>
-  </si>
-  <si>
-    <t>hugg-ligr</t>
-  </si>
-  <si>
-    <t>comfortable</t>
-  </si>
-  <si>
-    <t>hugga</t>
-  </si>
-  <si>
-    <t>to comfort someone (with accusative)</t>
-  </si>
-  <si>
-    <t>huggandi</t>
-  </si>
-  <si>
-    <t>comforting</t>
-  </si>
-  <si>
-    <t>hugr</t>
-  </si>
-  <si>
-    <t>mind, thoughts</t>
-  </si>
-  <si>
-    <t>hugsa</t>
-  </si>
-  <si>
-    <t>to think, to consider</t>
-  </si>
-  <si>
-    <t>huldinn</t>
-  </si>
-  <si>
-    <t>secluded, isolated, remote (of places); hidden (past participle of hylja)</t>
-  </si>
-  <si>
-    <t>hunang</t>
-  </si>
-  <si>
-    <t>honey</t>
-  </si>
-  <si>
-    <t>hundr</t>
-  </si>
-  <si>
-    <t>dog, hound</t>
-  </si>
-  <si>
-    <t>hundrað</t>
-  </si>
-  <si>
-    <t>hundred (hundrað = all singular, hundruð = all plural)</t>
-  </si>
-  <si>
-    <t>hungr</t>
-  </si>
-  <si>
-    <t>famine, dearth, starvation, severe hunger</t>
-  </si>
-  <si>
-    <t>hungr-laginn</t>
-  </si>
-  <si>
-    <t>faminated, wrought with famine</t>
-  </si>
-  <si>
-    <t>hunsa</t>
-  </si>
-  <si>
-    <t>to ignore, to pay no attention to (with accusative)</t>
-  </si>
-  <si>
-    <t>hurð</t>
-  </si>
-  <si>
-    <t>door</t>
-  </si>
-  <si>
-    <t>hurðar-fangr</t>
-  </si>
-  <si>
-    <t>doorknob</t>
-  </si>
-  <si>
-    <t>hús</t>
-  </si>
-  <si>
-    <t>house, home</t>
-  </si>
-  <si>
-    <t>hús-bóndi</t>
-  </si>
-  <si>
-    <t>head of the house</t>
-  </si>
-  <si>
-    <t>hús-karl</t>
-  </si>
-  <si>
-    <t>housecarl (huskarl); knight</t>
-  </si>
-  <si>
-    <t>hvaðan</t>
-  </si>
-  <si>
-    <t>question word</t>
-  </si>
-  <si>
-    <t>from where</t>
-  </si>
-  <si>
-    <t>hval-feiti</t>
-  </si>
-  <si>
-    <t>blubber, fat (of whales, dolphins, orcas, narwhals, etc)</t>
-  </si>
-  <si>
-    <t>hvalr</t>
-  </si>
-  <si>
-    <t>whale (rorquals, dolphins, orcas, narwhals, etc)</t>
-  </si>
-  <si>
-    <t>hvar</t>
-  </si>
-  <si>
-    <t>where</t>
-  </si>
-  <si>
-    <t>hvat</t>
-  </si>
-  <si>
-    <t>what</t>
-  </si>
-  <si>
-    <t>hve</t>
-  </si>
-  <si>
-    <t>how much/many of; how, in what manner, which way</t>
-  </si>
-  <si>
-    <t>hveiti</t>
-  </si>
-  <si>
-    <t>wheat</t>
-  </si>
-  <si>
-    <t>hvelpr</t>
-  </si>
-  <si>
-    <t>puppy</t>
-  </si>
-  <si>
-    <t>hven</t>
-  </si>
-  <si>
-    <t>when</t>
-  </si>
-  <si>
-    <t>hverfa</t>
-  </si>
-  <si>
-    <t>to disappear, to vanish</t>
-  </si>
-  <si>
-    <t>hverr</t>
-  </si>
-  <si>
-    <t>which, who</t>
-  </si>
-  <si>
-    <t>hví</t>
-  </si>
-  <si>
-    <t>why</t>
-  </si>
-  <si>
-    <t>hvika</t>
-  </si>
-  <si>
-    <t>to quail, to shiver, to cower, to shrink (intransitive)</t>
-  </si>
-  <si>
-    <t>hvikari</t>
-  </si>
-  <si>
-    <t>coward</t>
-  </si>
-  <si>
-    <t>hvíld</t>
-  </si>
-  <si>
-    <t>rest, break, paise</t>
-  </si>
-  <si>
-    <t>hvíldar-leyss</t>
-  </si>
-  <si>
-    <t>persistent, unyielding, relentless, restless, constant, stubborn</t>
-  </si>
-  <si>
-    <t>hvísla</t>
-  </si>
-  <si>
-    <t>to whisper</t>
-  </si>
-  <si>
-    <t>hvít-blár</t>
-  </si>
-  <si>
-    <t>light blue</t>
-  </si>
-  <si>
-    <t>hvít-brúnn</t>
-  </si>
-  <si>
-    <t>light brown</t>
-  </si>
-  <si>
-    <t>hvít-grár</t>
-  </si>
-  <si>
-    <t>light grey</t>
-  </si>
-  <si>
-    <t>hvít-grønn</t>
-  </si>
-  <si>
-    <t>light green, lime</t>
-  </si>
-  <si>
-    <t>hvít-gulr</t>
-  </si>
-  <si>
-    <t>light yellow</t>
-  </si>
-  <si>
-    <t>hvítr</t>
-  </si>
-  <si>
-    <t>white</t>
-  </si>
-  <si>
-    <t>hvort</t>
-  </si>
-  <si>
-    <t>whether, either</t>
-  </si>
-  <si>
-    <t>hyggja</t>
-  </si>
-  <si>
-    <t>to inspect, to examine (with ann + accusative)</t>
-  </si>
-  <si>
-    <t>hygli</t>
-  </si>
-  <si>
-    <t>consideration</t>
-  </si>
-  <si>
-    <t>hylja</t>
-  </si>
-  <si>
-    <t>to hide, to conceal, to cover (reflexive, or with accusative "hide what")</t>
-  </si>
-  <si>
-    <t>í</t>
-  </si>
-  <si>
-    <t>inside of (with accusative)</t>
-  </si>
-  <si>
-    <t>í dag</t>
-  </si>
-  <si>
-    <t>today</t>
-  </si>
-  <si>
-    <t>í gær</t>
-  </si>
-  <si>
-    <t>yesterday</t>
-  </si>
-  <si>
-    <t>í gøgnum</t>
-  </si>
-  <si>
-    <t>through (with dative)</t>
-  </si>
-  <si>
-    <t>í kringum með</t>
-  </si>
-  <si>
-    <t>around, surrounding (with dative)</t>
-  </si>
-  <si>
-    <t>í kvøld</t>
-  </si>
-  <si>
-    <t>tonight</t>
-  </si>
-  <si>
-    <t>í lagi</t>
-  </si>
-  <si>
-    <t>in order, all right; okay</t>
-  </si>
-  <si>
-    <t>í lífi</t>
-  </si>
-  <si>
-    <t>alive</t>
-  </si>
-  <si>
-    <t>í miðju með</t>
-  </si>
-  <si>
-    <t>between (with datives)</t>
-  </si>
-  <si>
-    <t>í mørgun</t>
-  </si>
-  <si>
-    <t>tomorrow</t>
-  </si>
-  <si>
-    <t>í órøð</t>
-  </si>
-  <si>
-    <t>chaotic, messy; wrong</t>
-  </si>
-  <si>
-    <t>í smæsta kosti</t>
-  </si>
-  <si>
-    <t>at least</t>
-  </si>
-  <si>
-    <t>í sømu stundunni</t>
-  </si>
-  <si>
-    <t>at the same time</t>
-  </si>
-  <si>
-    <t>í-fletta</t>
-  </si>
-  <si>
-    <t>emboidery</t>
-  </si>
-  <si>
-    <t>illa</t>
-  </si>
-  <si>
-    <t>badly, unwel (illar = worse, illast = worst)</t>
-  </si>
-  <si>
-    <t>illa-gras</t>
-  </si>
-  <si>
-    <t>unwanted weeds</t>
-  </si>
-  <si>
-    <t>inn</t>
-  </si>
-  <si>
-    <t>into (with accusative)</t>
-  </si>
-  <si>
-    <t>inn-lendingi</t>
-  </si>
-  <si>
-    <t>native, aboriginal, tribesman</t>
-  </si>
-  <si>
-    <t>inn-lendr</t>
-  </si>
-  <si>
-    <t>native, aboriginal</t>
-  </si>
-  <si>
-    <t>inn-lifinn</t>
-  </si>
-  <si>
-    <t>introverted</t>
-  </si>
-  <si>
-    <t>inn-rás</t>
-  </si>
-  <si>
-    <t>invasion</t>
-  </si>
-  <si>
-    <t>inn-renna</t>
-  </si>
-  <si>
-    <t>to invade (formal) (intransitive or with accusative)</t>
-  </si>
-  <si>
-    <t>inni</t>
-  </si>
-  <si>
-    <t>inside</t>
-  </si>
-  <si>
-    <t>innrás-maðr</t>
-  </si>
-  <si>
-    <t>invader</t>
-  </si>
-  <si>
-    <t>ís-alfr</t>
-  </si>
-  <si>
-    <t>ice spirit</t>
-  </si>
-  <si>
-    <t>ís-dreki</t>
-  </si>
-  <si>
-    <t>frost dragon</t>
-  </si>
-  <si>
-    <t>ís-kaldr</t>
-  </si>
-  <si>
-    <t>ice-cold, icy, freezing</t>
-  </si>
-  <si>
-    <t>íss</t>
-  </si>
-  <si>
-    <t>ice</t>
-  </si>
-  <si>
-    <t>já</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>jaki</t>
-  </si>
-  <si>
-    <t>broken ice</t>
   </si>
   <si>
     <t>japn</t>
@@ -32244,7 +32244,7 @@
         <v>1867</v>
       </c>
       <c r="B918" s="4" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C918" s="3" t="s">
         <v>1868</v>
@@ -32261,26 +32261,26 @@
       <c r="C919" s="3" t="s">
         <v>1870</v>
       </c>
-      <c r="D919" s="3"/>
+      <c r="D919" s="5"/>
     </row>
     <row r="920" ht="18.75" customHeight="1">
       <c r="A920" s="3" t="s">
         <v>1871</v>
       </c>
       <c r="B920" s="4" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C920" s="3" t="s">
         <v>1872</v>
       </c>
-      <c r="D920" s="5"/>
+      <c r="D920" s="3"/>
     </row>
     <row r="921" ht="18.75" customHeight="1">
       <c r="A921" s="3" t="s">
         <v>1873</v>
       </c>
       <c r="B921" s="4" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C921" s="3" t="s">
         <v>1874</v>
@@ -32292,31 +32292,31 @@
         <v>1875</v>
       </c>
       <c r="B922" s="4" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C922" s="3" t="s">
         <v>1876</v>
       </c>
-      <c r="D922" s="3"/>
+      <c r="D922" s="5"/>
     </row>
     <row r="923" ht="18.75" customHeight="1">
       <c r="A923" s="3" t="s">
         <v>1877</v>
       </c>
       <c r="B923" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C923" s="3" t="s">
         <v>1878</v>
       </c>
-      <c r="D923" s="5"/>
+      <c r="D923" s="3"/>
     </row>
     <row r="924" ht="18.75" customHeight="1">
       <c r="A924" s="3" t="s">
         <v>1879</v>
       </c>
       <c r="B924" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C924" s="3" t="s">
         <v>1880</v>
@@ -32328,31 +32328,31 @@
         <v>1881</v>
       </c>
       <c r="B925" s="4" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C925" s="3" t="s">
         <v>1882</v>
       </c>
-      <c r="D925" s="3"/>
+      <c r="D925" s="5"/>
     </row>
     <row r="926" ht="18.75" customHeight="1">
       <c r="A926" s="3" t="s">
         <v>1883</v>
       </c>
       <c r="B926" s="4" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C926" s="3" t="s">
         <v>1884</v>
       </c>
-      <c r="D926" s="5"/>
+      <c r="D926" s="3"/>
     </row>
     <row r="927" ht="18.75" customHeight="1">
       <c r="A927" s="3" t="s">
         <v>1885</v>
       </c>
       <c r="B927" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C927" s="3" t="s">
         <v>1886</v>
@@ -32364,7 +32364,7 @@
         <v>1887</v>
       </c>
       <c r="B928" s="4" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C928" s="3" t="s">
         <v>1888</v>
@@ -32376,7 +32376,7 @@
         <v>1889</v>
       </c>
       <c r="B929" s="4" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C929" s="3" t="s">
         <v>1890</v>
@@ -32388,7 +32388,7 @@
         <v>1891</v>
       </c>
       <c r="B930" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C930" s="3" t="s">
         <v>1892</v>
@@ -32400,36 +32400,36 @@
         <v>1893</v>
       </c>
       <c r="B931" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C931" s="3" t="s">
         <v>1894</v>
       </c>
-      <c r="D931" s="3"/>
+      <c r="D931" s="5"/>
     </row>
     <row r="932" ht="18.75" customHeight="1">
       <c r="A932" s="3" t="s">
         <v>1895</v>
       </c>
       <c r="B932" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C932" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C932" s="6" t="s">
         <v>1896</v>
       </c>
-      <c r="D932" s="5"/>
+      <c r="D932" s="3"/>
     </row>
     <row r="933" ht="18.75" customHeight="1">
       <c r="A933" s="3" t="s">
         <v>1897</v>
       </c>
       <c r="B933" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C933" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C933" s="3" t="s">
         <v>1898</v>
       </c>
-      <c r="D933" s="3"/>
+      <c r="D933" s="5"/>
     </row>
     <row r="934" ht="18.75" customHeight="1">
       <c r="A934" s="3" t="s">
@@ -32448,26 +32448,26 @@
         <v>1901</v>
       </c>
       <c r="B935" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C935" s="3" t="s">
         <v>1902</v>
       </c>
-      <c r="D935" s="5"/>
+      <c r="D935" s="3" t="s">
+        <v>1027</v>
+      </c>
     </row>
     <row r="936" ht="18.75" customHeight="1">
       <c r="A936" s="3" t="s">
         <v>1903</v>
       </c>
       <c r="B936" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C936" s="3" t="s">
         <v>1904</v>
       </c>
-      <c r="D936" s="3" t="s">
-        <v>1027</v>
-      </c>
+      <c r="D936" s="3"/>
     </row>
     <row r="937" ht="18.75" customHeight="1">
       <c r="A937" s="3" t="s">
@@ -32479,43 +32479,43 @@
       <c r="C937" s="3" t="s">
         <v>1906</v>
       </c>
-      <c r="D937" s="3"/>
+      <c r="D937" s="5"/>
     </row>
     <row r="938" ht="18.75" customHeight="1">
       <c r="A938" s="3" t="s">
         <v>1907</v>
       </c>
       <c r="B938" s="4" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C938" s="3" t="s">
         <v>1908</v>
       </c>
-      <c r="D938" s="5"/>
+      <c r="D938" s="3"/>
     </row>
     <row r="939" ht="18.75" customHeight="1">
       <c r="A939" s="3" t="s">
         <v>1909</v>
       </c>
       <c r="B939" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C939" s="3" t="s">
         <v>1910</v>
       </c>
-      <c r="D939" s="3"/>
+      <c r="D939" s="5"/>
     </row>
     <row r="940" ht="18.75" customHeight="1">
       <c r="A940" s="3" t="s">
         <v>1911</v>
       </c>
       <c r="B940" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C940" s="3" t="s">
         <v>1912</v>
       </c>
-      <c r="D940" s="5"/>
+      <c r="D940" s="3"/>
     </row>
     <row r="941" ht="18.75" customHeight="1">
       <c r="A941" s="3" t="s">
@@ -32534,26 +32534,26 @@
         <v>1915</v>
       </c>
       <c r="B942" s="4" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C942" s="3" t="s">
         <v>1916</v>
       </c>
-      <c r="D942" s="3"/>
+      <c r="D942" s="3" t="s">
+        <v>1917</v>
+      </c>
     </row>
     <row r="943" ht="18.75" customHeight="1">
       <c r="A943" s="3" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="B943" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C943" s="3" t="s">
-        <v>1918</v>
-      </c>
-      <c r="D943" s="3" t="s">
         <v>1919</v>
       </c>
+      <c r="D943" s="3"/>
     </row>
     <row r="944" ht="18.75" customHeight="1">
       <c r="A944" s="3" t="s">
@@ -32584,7 +32584,7 @@
         <v>1924</v>
       </c>
       <c r="B946" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C946" s="3" t="s">
         <v>1925</v>
@@ -32596,7 +32596,7 @@
         <v>1926</v>
       </c>
       <c r="B947" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C947" s="3" t="s">
         <v>1927</v>
@@ -32608,33 +32608,33 @@
         <v>1928</v>
       </c>
       <c r="B948" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C948" s="3" t="s">
         <v>1929</v>
       </c>
-      <c r="D948" s="3"/>
+      <c r="D948" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="949" ht="18.75" customHeight="1">
       <c r="A949" s="3" t="s">
         <v>1930</v>
       </c>
       <c r="B949" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C949" s="3" t="s">
         <v>1931</v>
       </c>
-      <c r="D949" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="D949" s="3"/>
     </row>
     <row r="950" ht="18.75" customHeight="1">
       <c r="A950" s="3" t="s">
         <v>1932</v>
       </c>
       <c r="B950" s="4" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C950" s="3" t="s">
         <v>1933</v>
@@ -32646,7 +32646,7 @@
         <v>1934</v>
       </c>
       <c r="B951" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C951" s="3" t="s">
         <v>1935</v>
@@ -32658,45 +32658,45 @@
         <v>1936</v>
       </c>
       <c r="B952" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C952" s="3" t="s">
         <v>1937</v>
       </c>
-      <c r="D952" s="3"/>
+      <c r="D952" s="3" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="953" ht="18.75" customHeight="1">
       <c r="A953" s="3" t="s">
         <v>1938</v>
       </c>
       <c r="B953" s="4" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C953" s="3" t="s">
         <v>1939</v>
       </c>
-      <c r="D953" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="D953" s="5"/>
     </row>
     <row r="954" ht="18.75" customHeight="1">
       <c r="A954" s="3" t="s">
         <v>1940</v>
       </c>
       <c r="B954" s="4" t="s">
-        <v>65</v>
+        <v>286</v>
       </c>
       <c r="C954" s="3" t="s">
         <v>1941</v>
       </c>
-      <c r="D954" s="5"/>
+      <c r="D954" s="3"/>
     </row>
     <row r="955" ht="18.75" customHeight="1">
       <c r="A955" s="3" t="s">
         <v>1942</v>
       </c>
       <c r="B955" s="4" t="s">
-        <v>286</v>
+        <v>49</v>
       </c>
       <c r="C955" s="3" t="s">
         <v>1943</v>
@@ -32708,7 +32708,7 @@
         <v>1944</v>
       </c>
       <c r="B956" s="4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C956" s="3" t="s">
         <v>1945</v>
@@ -32720,7 +32720,7 @@
         <v>1946</v>
       </c>
       <c r="B957" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C957" s="3" t="s">
         <v>1947</v>
@@ -32732,31 +32732,31 @@
         <v>1948</v>
       </c>
       <c r="B958" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C958" s="3" t="s">
         <v>1949</v>
       </c>
-      <c r="D958" s="3"/>
+      <c r="D958" s="5"/>
     </row>
     <row r="959" ht="18.75" customHeight="1">
       <c r="A959" s="3" t="s">
         <v>1950</v>
       </c>
       <c r="B959" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C959" s="3" t="s">
         <v>1951</v>
       </c>
-      <c r="D959" s="5"/>
+      <c r="D959" s="3"/>
     </row>
     <row r="960" ht="18.75" customHeight="1">
       <c r="A960" s="3" t="s">
         <v>1952</v>
       </c>
       <c r="B960" s="4" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C960" s="3" t="s">
         <v>1953</v>
@@ -32768,7 +32768,7 @@
         <v>1954</v>
       </c>
       <c r="B961" s="4" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C961" s="3" t="s">
         <v>1955</v>
@@ -32785,54 +32785,54 @@
       <c r="C962" s="3" t="s">
         <v>1957</v>
       </c>
-      <c r="D962" s="3"/>
+      <c r="D962" s="3" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="963" ht="18.75" customHeight="1">
       <c r="A963" s="3" t="s">
         <v>1958</v>
       </c>
       <c r="B963" s="4" t="s">
-        <v>65</v>
+        <v>1959</v>
       </c>
       <c r="C963" s="3" t="s">
-        <v>1959</v>
-      </c>
-      <c r="D963" s="3" t="s">
-        <v>70</v>
-      </c>
+        <v>1960</v>
+      </c>
+      <c r="D963" s="3"/>
     </row>
     <row r="964" ht="18.75" customHeight="1">
       <c r="A964" s="3" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="B964" s="4" t="s">
-        <v>1961</v>
+        <v>49</v>
       </c>
       <c r="C964" s="3" t="s">
         <v>1962</v>
       </c>
-      <c r="D964" s="3"/>
+      <c r="D964" s="3" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="965" ht="18.75" customHeight="1">
       <c r="A965" s="3" t="s">
         <v>1963</v>
       </c>
       <c r="B965" s="4" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C965" s="3" t="s">
         <v>1964</v>
       </c>
-      <c r="D965" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="D965" s="5"/>
     </row>
     <row r="966" ht="18.75" customHeight="1">
       <c r="A966" s="3" t="s">
         <v>1965</v>
       </c>
       <c r="B966" s="4" t="s">
-        <v>65</v>
+        <v>1959</v>
       </c>
       <c r="C966" s="3" t="s">
         <v>1966</v>
@@ -32844,7 +32844,7 @@
         <v>1967</v>
       </c>
       <c r="B967" s="4" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="C967" s="3" t="s">
         <v>1968</v>
@@ -32856,81 +32856,81 @@
         <v>1969</v>
       </c>
       <c r="B968" s="4" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="C968" s="3" t="s">
         <v>1970</v>
       </c>
-      <c r="D968" s="5"/>
+      <c r="D968" s="3"/>
     </row>
     <row r="969" ht="18.75" customHeight="1">
       <c r="A969" s="3" t="s">
         <v>1971</v>
       </c>
       <c r="B969" s="4" t="s">
-        <v>1961</v>
+        <v>49</v>
       </c>
       <c r="C969" s="3" t="s">
         <v>1972</v>
       </c>
-      <c r="D969" s="3"/>
+      <c r="D969" s="3" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="970" ht="18.75" customHeight="1">
       <c r="A970" s="3" t="s">
         <v>1973</v>
       </c>
       <c r="B970" s="4" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C970" s="3" t="s">
         <v>1974</v>
       </c>
-      <c r="D970" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="D970" s="3"/>
     </row>
     <row r="971" ht="18.75" customHeight="1">
       <c r="A971" s="3" t="s">
         <v>1975</v>
       </c>
       <c r="B971" s="4" t="s">
-        <v>65</v>
+        <v>1959</v>
       </c>
       <c r="C971" s="3" t="s">
         <v>1976</v>
       </c>
-      <c r="D971" s="3"/>
+      <c r="D971" s="5"/>
     </row>
     <row r="972" ht="18.75" customHeight="1">
       <c r="A972" s="3" t="s">
         <v>1977</v>
       </c>
       <c r="B972" s="4" t="s">
-        <v>1961</v>
+        <v>52</v>
       </c>
       <c r="C972" s="3" t="s">
         <v>1978</v>
       </c>
-      <c r="D972" s="5"/>
+      <c r="D972" s="3"/>
     </row>
     <row r="973" ht="18.75" customHeight="1">
       <c r="A973" s="3" t="s">
         <v>1979</v>
       </c>
       <c r="B973" s="4" t="s">
-        <v>52</v>
+        <v>1959</v>
       </c>
       <c r="C973" s="3" t="s">
         <v>1980</v>
       </c>
-      <c r="D973" s="3"/>
+      <c r="D973" s="5"/>
     </row>
     <row r="974" ht="18.75" customHeight="1">
       <c r="A974" s="3" t="s">
         <v>1981</v>
       </c>
       <c r="B974" s="4" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="C974" s="3" t="s">
         <v>1982</v>
@@ -32942,19 +32942,19 @@
         <v>1983</v>
       </c>
       <c r="B975" s="4" t="s">
-        <v>1961</v>
+        <v>52</v>
       </c>
       <c r="C975" s="3" t="s">
         <v>1984</v>
       </c>
-      <c r="D975" s="5"/>
+      <c r="D975" s="3"/>
     </row>
     <row r="976" ht="18.75" customHeight="1">
       <c r="A976" s="3" t="s">
         <v>1985</v>
       </c>
       <c r="B976" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C976" s="3" t="s">
         <v>1986</v>
@@ -32966,7 +32966,7 @@
         <v>1987</v>
       </c>
       <c r="B977" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C977" s="3" t="s">
         <v>1988</v>
@@ -32978,7 +32978,7 @@
         <v>1989</v>
       </c>
       <c r="B978" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C978" s="3" t="s">
         <v>1990</v>
@@ -32990,7 +32990,7 @@
         <v>1991</v>
       </c>
       <c r="B979" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C979" s="3" t="s">
         <v>1992</v>
@@ -33002,12 +33002,12 @@
         <v>1993</v>
       </c>
       <c r="B980" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C980" s="3" t="s">
         <v>1994</v>
       </c>
-      <c r="D980" s="3"/>
+      <c r="D980" s="5"/>
     </row>
     <row r="981" ht="18.75" customHeight="1">
       <c r="A981" s="3" t="s">
@@ -33074,45 +33074,45 @@
         <v>2005</v>
       </c>
       <c r="B986" s="4" t="s">
-        <v>55</v>
+        <v>273</v>
       </c>
       <c r="C986" s="3" t="s">
         <v>2006</v>
       </c>
-      <c r="D986" s="5"/>
+      <c r="D986" s="3"/>
     </row>
     <row r="987" ht="18.75" customHeight="1">
       <c r="A987" s="3" t="s">
         <v>2007</v>
       </c>
       <c r="B987" s="4" t="s">
-        <v>273</v>
+        <v>52</v>
       </c>
       <c r="C987" s="3" t="s">
         <v>2008</v>
       </c>
-      <c r="D987" s="3"/>
+      <c r="D987" s="3" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="988" ht="18.75" customHeight="1">
       <c r="A988" s="3" t="s">
         <v>2009</v>
       </c>
       <c r="B988" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C988" s="3" t="s">
         <v>2010</v>
       </c>
-      <c r="D988" s="3" t="s">
-        <v>406</v>
-      </c>
+      <c r="D988" s="3"/>
     </row>
     <row r="989" ht="18.75" customHeight="1">
       <c r="A989" s="3" t="s">
         <v>2011</v>
       </c>
       <c r="B989" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C989" s="3" t="s">
         <v>2012</v>
@@ -33124,24 +33124,24 @@
         <v>2013</v>
       </c>
       <c r="B990" s="4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C990" s="3" t="s">
         <v>2014</v>
       </c>
-      <c r="D990" s="3"/>
+      <c r="D990" s="5"/>
     </row>
     <row r="991" ht="18.75" customHeight="1">
       <c r="A991" s="3" t="s">
         <v>2015</v>
       </c>
       <c r="B991" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C991" s="3" t="s">
         <v>2016</v>
       </c>
-      <c r="D991" s="5"/>
+      <c r="D991" s="3"/>
     </row>
     <row r="992" ht="18.75" customHeight="1">
       <c r="A992" s="3" t="s">
@@ -33172,24 +33172,24 @@
         <v>2021</v>
       </c>
       <c r="B994" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C994" s="3" t="s">
         <v>2022</v>
       </c>
-      <c r="D994" s="3"/>
+      <c r="D994" s="5"/>
     </row>
     <row r="995" ht="18.75" customHeight="1">
       <c r="A995" s="3" t="s">
         <v>2023</v>
       </c>
       <c r="B995" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C995" s="3" t="s">
         <v>2024</v>
       </c>
-      <c r="D995" s="5"/>
+      <c r="D995" s="3"/>
     </row>
     <row r="996" ht="18.75" customHeight="1">
       <c r="A996" s="3" t="s">
@@ -33220,7 +33220,7 @@
         <v>2029</v>
       </c>
       <c r="B998" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C998" s="3" t="s">
         <v>2030</v>
@@ -33232,7 +33232,7 @@
         <v>2031</v>
       </c>
       <c r="B999" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C999" s="3" t="s">
         <v>2032</v>
@@ -33273,26 +33273,26 @@
       <c r="C1002" s="3" t="s">
         <v>2038</v>
       </c>
-      <c r="D1002" s="3"/>
+      <c r="D1002" s="5"/>
     </row>
     <row r="1003" ht="18.75" customHeight="1">
       <c r="A1003" s="3" t="s">
         <v>2039</v>
       </c>
       <c r="B1003" s="4" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C1003" s="3" t="s">
         <v>2040</v>
       </c>
-      <c r="D1003" s="5"/>
+      <c r="D1003" s="3"/>
     </row>
     <row r="1004" ht="18.75" customHeight="1">
       <c r="A1004" s="3" t="s">
         <v>2041</v>
       </c>
       <c r="B1004" s="4" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C1004" s="3" t="s">
         <v>2042</v>
@@ -33304,33 +33304,33 @@
         <v>2043</v>
       </c>
       <c r="B1005" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C1005" s="3" t="s">
         <v>2044</v>
       </c>
-      <c r="D1005" s="3"/>
+      <c r="D1005" s="3" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="1006" ht="18.75" customHeight="1">
       <c r="A1006" s="3" t="s">
         <v>2045</v>
       </c>
       <c r="B1006" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C1006" s="3" t="s">
         <v>2046</v>
       </c>
-      <c r="D1006" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="D1006" s="5"/>
     </row>
     <row r="1007" ht="18.75" customHeight="1">
       <c r="A1007" s="3" t="s">
         <v>2047</v>
       </c>
       <c r="B1007" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C1007" s="3" t="s">
         <v>2048</v>
@@ -33342,7 +33342,7 @@
         <v>2049</v>
       </c>
       <c r="B1008" s="4" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C1008" s="3" t="s">
         <v>2050</v>
@@ -33366,50 +33366,50 @@
         <v>2053</v>
       </c>
       <c r="B1010" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1010" s="3" t="s">
         <v>2054</v>
       </c>
-      <c r="D1010" s="5"/>
+      <c r="D1010" s="3"/>
     </row>
     <row r="1011" ht="18.75" customHeight="1">
       <c r="A1011" s="3" t="s">
         <v>2055</v>
       </c>
       <c r="B1011" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C1011" s="3" t="s">
         <v>2056</v>
       </c>
-      <c r="D1011" s="3"/>
+      <c r="D1011" s="3" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="1012" ht="18.75" customHeight="1">
       <c r="A1012" s="3" t="s">
         <v>2057</v>
       </c>
       <c r="B1012" s="4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C1012" s="3" t="s">
         <v>2058</v>
       </c>
-      <c r="D1012" s="3" t="s">
-        <v>223</v>
-      </c>
+      <c r="D1012" s="5"/>
     </row>
     <row r="1013" ht="18.75" customHeight="1">
       <c r="A1013" s="3" t="s">
         <v>2059</v>
       </c>
       <c r="B1013" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C1013" s="3" t="s">
         <v>2060</v>
       </c>
-      <c r="D1013" s="5"/>
+      <c r="D1013" s="3"/>
     </row>
     <row r="1014" ht="18.75" customHeight="1">
       <c r="A1014" s="3" t="s">
@@ -33421,7 +33421,7 @@
       <c r="C1014" s="3" t="s">
         <v>2062</v>
       </c>
-      <c r="D1014" s="3"/>
+      <c r="D1014" s="5"/>
     </row>
     <row r="1015" ht="18.75" customHeight="1">
       <c r="A1015" s="3" t="s">
@@ -33433,14 +33433,14 @@
       <c r="C1015" s="3" t="s">
         <v>2064</v>
       </c>
-      <c r="D1015" s="5"/>
+      <c r="D1015" s="3"/>
     </row>
     <row r="1016" ht="18.75" customHeight="1">
       <c r="A1016" s="3" t="s">
         <v>2065</v>
       </c>
       <c r="B1016" s="4" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C1016" s="3" t="s">
         <v>2066</v>
@@ -33452,19 +33452,19 @@
         <v>2067</v>
       </c>
       <c r="B1017" s="4" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C1017" s="3" t="s">
         <v>2068</v>
       </c>
-      <c r="D1017" s="3"/>
+      <c r="D1017" s="5"/>
     </row>
     <row r="1018" ht="18.75" customHeight="1">
       <c r="A1018" s="3" t="s">
         <v>2069</v>
       </c>
       <c r="B1018" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C1018" s="3" t="s">
         <v>2070</v>
@@ -33476,7 +33476,7 @@
         <v>2071</v>
       </c>
       <c r="B1019" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C1019" s="3" t="s">
         <v>2072</v>
@@ -33488,12 +33488,12 @@
         <v>2073</v>
       </c>
       <c r="B1020" s="4" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C1020" s="3" t="s">
         <v>2074</v>
       </c>
-      <c r="D1020" s="5"/>
+      <c r="D1020" s="3"/>
     </row>
     <row r="1021" ht="18.75" customHeight="1">
       <c r="A1021" s="3" t="s">
@@ -43510,7 +43510,7 @@
         <v>3708</v>
       </c>
       <c r="D1834" s="3" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="1835" ht="18.75" customHeight="1">
@@ -59021,7 +59021,7 @@
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" s="19" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="B52" s="20"/>
       <c r="C52" s="19" t="s">
@@ -66211,7 +66211,7 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="44" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B20" s="44" t="s">
         <v>6538</v>
@@ -66916,7 +66916,7 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="44" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B6" s="44" t="s">
         <v>6648</v>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -908,7 +908,7 @@
     <t>atla</t>
   </si>
   <si>
-    <t>to ought, to be obligated to; should do something (with infinitive); should go somewhere (with adverb)</t>
+    <t>to ought, to be obligated to (with infinitive); should do something (with infinitive); should go somewhere (with adverb)</t>
   </si>
   <si>
     <t>atta</t>
@@ -5921,7 +5921,7 @@
     <t>hús-bóndi</t>
   </si>
   <si>
-    <t>head of the house</t>
+    <t>head of the house, master of the house</t>
   </si>
   <si>
     <t>hús-karl</t>
@@ -7718,7 +7718,7 @@
     <t>loka</t>
   </si>
   <si>
-    <t>to close</t>
+    <t>to close, to shut</t>
   </si>
   <si>
     <t>lokaðr</t>
@@ -8504,7 +8504,7 @@
     <t>auxiliary</t>
   </si>
   <si>
-    <t>will probably</t>
+    <t>will probably, is likely to, might</t>
   </si>
   <si>
     <t>mús</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10851" uniqueCount="6822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10870" uniqueCount="6822">
   <si>
     <t>Entry</t>
   </si>
@@ -164,7 +164,7 @@
     <t>-teen (in numbers)</t>
   </si>
   <si>
-    <t>-tugr</t>
+    <t>-tug</t>
   </si>
   <si>
     <t>number</t>
@@ -944,7 +944,7 @@
     <t>eighteen</t>
   </si>
   <si>
-    <t>atta-tugr</t>
+    <t>atta-tug</t>
   </si>
   <si>
     <t>eighty</t>
@@ -3332,7 +3332,7 @@
     <t>fifteen</t>
   </si>
   <si>
-    <t>fimm-tugr</t>
+    <t>fimm-tug</t>
   </si>
   <si>
     <t>fifty</t>
@@ -3428,7 +3428,7 @@
     <t>fourteen</t>
   </si>
   <si>
-    <t>fjø-tugr</t>
+    <t>fjø-tug</t>
   </si>
   <si>
     <t>fourty</t>
@@ -5939,7 +5939,7 @@
     <t>hundrað</t>
   </si>
   <si>
-    <t>hundred (hundrað = all singular, hundruð = all plural)</t>
+    <t>a long hundred (120)</t>
   </si>
   <si>
     <t>hungr</t>
@@ -8969,7 +8969,7 @@
     <t>nineteen</t>
   </si>
   <si>
-    <t>níu-tugr</t>
+    <t>níu-tug</t>
   </si>
   <si>
     <t>ninety</t>
@@ -10661,7 +10661,7 @@
     <t>sixteen</t>
   </si>
   <si>
-    <t>sex-tugr</t>
+    <t>sex-tug</t>
   </si>
   <si>
     <t>sixty</t>
@@ -10793,7 +10793,7 @@
     <t>seventeen</t>
   </si>
   <si>
-    <t>sja-tugr</t>
+    <t>sja-tug</t>
   </si>
   <si>
     <t>seventy</t>
@@ -12965,7 +12965,7 @@
     <t>two</t>
   </si>
   <si>
-    <t>tvø-tugr</t>
+    <t>tvø-tug</t>
   </si>
   <si>
     <t>twenty</t>
@@ -14588,7 +14588,7 @@
     <t>thirteen</t>
   </si>
   <si>
-    <t>þræ-tugr</t>
+    <t>þræ-tug</t>
   </si>
   <si>
     <t>thirty</t>
@@ -21351,7 +21351,9 @@
       <c r="C17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="3" t="s">
@@ -22833,7 +22835,9 @@
       <c r="C138" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D138" s="3"/>
+      <c r="D138" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="139" ht="18.75" customHeight="1">
       <c r="A139" s="3" t="s">
@@ -22845,7 +22849,9 @@
       <c r="C139" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="D139" s="3"/>
+      <c r="D139" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="140" ht="18.75" customHeight="1">
       <c r="A140" s="3" t="s">
@@ -26705,7 +26711,9 @@
       <c r="C455" s="3" t="s">
         <v>938</v>
       </c>
-      <c r="D455" s="3"/>
+      <c r="D455" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="456" ht="18.75" customHeight="1">
       <c r="A456" s="3" t="s">
@@ -27641,7 +27649,9 @@
       <c r="C531" s="3" t="s">
         <v>1091</v>
       </c>
-      <c r="D531" s="3"/>
+      <c r="D531" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="532" ht="18.75" customHeight="1">
       <c r="A532" s="3" t="s">
@@ -27653,7 +27663,9 @@
       <c r="C532" s="3" t="s">
         <v>1093</v>
       </c>
-      <c r="D532" s="3"/>
+      <c r="D532" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="533" ht="18.75" customHeight="1">
       <c r="A533" s="3" t="s">
@@ -27841,7 +27853,9 @@
       <c r="C547" s="3" t="s">
         <v>1123</v>
       </c>
-      <c r="D547" s="3"/>
+      <c r="D547" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="548" ht="18.75" customHeight="1">
       <c r="A548" s="3" t="s">
@@ -27853,7 +27867,9 @@
       <c r="C548" s="3" t="s">
         <v>1125</v>
       </c>
-      <c r="D548" s="3"/>
+      <c r="D548" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="549" ht="18.75" customHeight="1">
       <c r="A549" s="3" t="s">
@@ -32985,7 +33001,9 @@
       <c r="C964" s="3" t="s">
         <v>1961</v>
       </c>
-      <c r="D964" s="3"/>
+      <c r="D964" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="965" ht="18.75" customHeight="1">
       <c r="A965" s="3" t="s">
@@ -39151,7 +39169,9 @@
       <c r="C1466" s="3" t="s">
         <v>2970</v>
       </c>
-      <c r="D1466" s="3"/>
+      <c r="D1466" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="1467" ht="18.75" customHeight="1">
       <c r="A1467" s="3" t="s">
@@ -39163,7 +39183,9 @@
       <c r="C1467" s="3" t="s">
         <v>2972</v>
       </c>
-      <c r="D1467" s="3"/>
+      <c r="D1467" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="1468" ht="18.75" customHeight="1">
       <c r="A1468" s="3" t="s">
@@ -42597,7 +42619,9 @@
       <c r="C1747" s="3" t="s">
         <v>3534</v>
       </c>
-      <c r="D1747" s="3"/>
+      <c r="D1747" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="1748" ht="18.75" customHeight="1">
       <c r="A1748" s="3" t="s">
@@ -42609,7 +42633,9 @@
       <c r="C1748" s="3" t="s">
         <v>3536</v>
       </c>
-      <c r="D1748" s="3"/>
+      <c r="D1748" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="1749" ht="18.75" customHeight="1">
       <c r="A1749" s="3" t="s">
@@ -42873,7 +42899,9 @@
       <c r="C1769" s="3" t="s">
         <v>3578</v>
       </c>
-      <c r="D1769" s="3"/>
+      <c r="D1769" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="1770" ht="18.75" customHeight="1">
       <c r="A1770" s="3" t="s">
@@ -42885,7 +42913,9 @@
       <c r="C1770" s="3" t="s">
         <v>3580</v>
       </c>
-      <c r="D1770" s="3"/>
+      <c r="D1770" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="1771" ht="18.75" customHeight="1">
       <c r="A1771" s="3" t="s">
@@ -46923,7 +46953,9 @@
       <c r="C2098" s="3" t="s">
         <v>4236</v>
       </c>
-      <c r="D2098" s="3"/>
+      <c r="D2098" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2099" ht="18.75" customHeight="1">
       <c r="A2099" s="3" t="s">
@@ -47337,7 +47369,9 @@
       <c r="C2132" s="3" t="s">
         <v>4304</v>
       </c>
-      <c r="D2132" s="3"/>
+      <c r="D2132" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2133" ht="18.75" customHeight="1">
       <c r="A2133" s="3" t="s">
@@ -50693,7 +50727,9 @@
       <c r="C2402" s="3" t="s">
         <v>4843</v>
       </c>
-      <c r="D2402" s="3"/>
+      <c r="D2402" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2403" ht="18.75" customHeight="1">
       <c r="A2403" s="3" t="s">
@@ -50705,7 +50741,9 @@
       <c r="C2403" s="3" t="s">
         <v>4845</v>
       </c>
-      <c r="D2403" s="3"/>
+      <c r="D2403" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2404" ht="18.75" customHeight="1">
       <c r="A2404" s="3" t="s">

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -3290,7 +3290,7 @@
     <t>fen, patterned bog; a type of marshland where pools and ponds are polka-dotted everywhere but the land is otherwise solid</t>
   </si>
   <si>
-    <t>ferskr</t>
+    <t>feskr</t>
   </si>
   <si>
     <t>fresh</t>
@@ -11750,6 +11750,12 @@
     <t>wise</t>
   </si>
   <si>
+    <t>spal</t>
+  </si>
+  <si>
+    <t>dance</t>
+  </si>
+  <si>
     <t>spana</t>
   </si>
   <si>
@@ -11804,19 +11810,13 @@
     <t>to enlighten, to grant wisdom</t>
   </si>
   <si>
-    <t>spil</t>
-  </si>
-  <si>
-    <t>dance</t>
-  </si>
-  <si>
-    <t>spila</t>
+    <t>spelja</t>
   </si>
   <si>
     <t>to dance</t>
   </si>
   <si>
-    <t>spilandi</t>
+    <t>speljandi</t>
   </si>
   <si>
     <t>dancer</t>
@@ -44955,19 +44955,19 @@
         <v>3898</v>
       </c>
       <c r="B1930" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C1930" s="3" t="s">
         <v>3899</v>
       </c>
-      <c r="D1930" s="3"/>
+      <c r="D1930" s="5"/>
     </row>
     <row r="1931" ht="18.75" customHeight="1">
       <c r="A1931" s="3" t="s">
         <v>3900</v>
       </c>
       <c r="B1931" s="4" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C1931" s="3" t="s">
         <v>3901</v>
@@ -44979,33 +44979,33 @@
         <v>3902</v>
       </c>
       <c r="B1932" s="4" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C1932" s="3" t="s">
         <v>3903</v>
       </c>
-      <c r="D1932" s="3" t="s">
-        <v>228</v>
-      </c>
+      <c r="D1932" s="3"/>
     </row>
     <row r="1933" ht="18.75" customHeight="1">
       <c r="A1933" s="3" t="s">
         <v>3904</v>
       </c>
       <c r="B1933" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C1933" s="3" t="s">
         <v>3905</v>
       </c>
-      <c r="D1933" s="3"/>
+      <c r="D1933" s="3" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="1934" ht="18.75" customHeight="1">
       <c r="A1934" s="3" t="s">
         <v>3906</v>
       </c>
       <c r="B1934" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C1934" s="3" t="s">
         <v>3907</v>
@@ -45017,7 +45017,7 @@
         <v>3908</v>
       </c>
       <c r="B1935" s="4" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C1935" s="3" t="s">
         <v>3909</v>
@@ -45029,7 +45029,7 @@
         <v>3910</v>
       </c>
       <c r="B1936" s="4" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C1936" s="3" t="s">
         <v>3911</v>
@@ -45041,7 +45041,7 @@
         <v>3912</v>
       </c>
       <c r="B1937" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C1937" s="3" t="s">
         <v>3913</v>
@@ -45053,7 +45053,7 @@
         <v>3914</v>
       </c>
       <c r="B1938" s="4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C1938" s="3" t="s">
         <v>3915</v>
@@ -45065,12 +45065,12 @@
         <v>3916</v>
       </c>
       <c r="B1939" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C1939" s="3" t="s">
         <v>3917</v>
       </c>
-      <c r="D1939" s="5"/>
+      <c r="D1939" s="3"/>
     </row>
     <row r="1940" ht="18.75" customHeight="1">
       <c r="A1940" s="3" t="s">

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -9257,7 +9257,7 @@
     <t>ó-huggligr</t>
   </si>
   <si>
-    <t>uncomfortable</t>
+    <t>uncomfortable; disturbing, uncanny</t>
   </si>
   <si>
     <t>ó-kunnigr</t>

--- a/Literature/Languages/Northmannish.xlsx
+++ b/Literature/Languages/Northmannish.xlsx
@@ -197,7 +197,7 @@
     <t>-ment, -dom</t>
   </si>
   <si>
-    <t>-þit</t>
+    <t>-þi</t>
   </si>
   <si>
     <t>imperative plural suffix</t>
@@ -206,7 +206,7 @@
     <t>-þu</t>
   </si>
   <si>
-    <t>imperative singular suffix; contraction of þú</t>
+    <t>imperative singular suffix; contraction of þú (becomes -tu if the verb form ends with a -t, such as ert + þu = ertu)</t>
   </si>
   <si>
     <t>á</t>
